--- a/stock-statement/PEI-Stock-Register.xlsx
+++ b/stock-statement/PEI-Stock-Register.xlsx
@@ -5,18 +5,20 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Read me" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Stock" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Daily Entry" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Summary" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Daily Report" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">'Daily Entry'!$6:$6</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Daily Entry'!$A$6:$E$250</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Read me'!$A$1:$B$33</definedName>
+    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">'Daily Report'!$A$1:$F$48</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Read me'!$A$1:$B$38</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Stock!$A$1:$J$50</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">Stock!$7:$7</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Stock!$A$7:$J$49</definedName>
@@ -45,9 +47,8 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Position recorded on the purchase &amp; processing statement of 20/08/26.
-This is a fixed baseline — do not update it daily. Closing slabs is
-derived from it plus the Daily Entry log.</t>
+          <t xml:space="preserve">The position this register starts from. A fixed baseline — do not update
+it daily. Closing Balance is derived from it plus the Daily Entry log.</t>
         </r>
       </text>
     </comment>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="132">
   <si>
     <t xml:space="preserve">PREMIER EXPORTS INTERNATIONAL</t>
   </si>
@@ -64,31 +65,46 @@
     <t xml:space="preserve">STOCK REGISTER — HOW IT WORKS</t>
   </si>
   <si>
-    <t xml:space="preserve">The daily routine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">After each day's production, open 'Daily Entry' and add one row per grade that moved.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick the item from the dropdown, type the date, and enter slabs produced and/or shipped.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">That is the whole job — 'Stock' and 'Summary' update themselves.</t>
+    <t xml:space="preserve">Every day, in one minute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.  Open 'Daily Entry' and add one row per product that moved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.  Type the date, pick the product from the dropdown, enter slabs produced and/or shipped.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.  On 'Stock', set the Statement date to today.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.  Open 'Daily Report' and save it as PDF — that is the directors' copy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sending the report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Daily Report' is already sized to one A4 page. In Excel: File ▸ Export ▸ Create PDF/XPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(or File ▸ Save a Copy and choose PDF), pick "Selected sheet", and send that file.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nothing else needs installing — Excel writes the PDF itself.</t>
   </si>
   <si>
     <t xml:space="preserve">Why you never re-type an opening balance</t>
   </si>
   <si>
-    <t xml:space="preserve">Opening balance is a fixed baseline: the position recorded on 20/08/2026.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closing slabs = opening balance + production to date − shipment to date,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">counted from every row in 'Daily Entry'. So the register rolls forward on its own,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">and yesterday's closing is today's starting point without anyone copying a number.</t>
+    <t xml:space="preserve">Opening balance is a fixed baseline, not a daily figure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closing balance = opening balance + production to date − shipment to date,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">counted from every row on 'Daily Entry'. The register rolls forward on its own,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">so yesterday's closing is today's starting point without anyone copying a number.</t>
   </si>
   <si>
     <t xml:space="preserve">Which cells you edit</t>
@@ -97,31 +113,28 @@
     <t xml:space="preserve">Blue figures — typed by you. Opening balance on 'Stock'; everything on 'Daily Entry'.</t>
   </si>
   <si>
-    <t xml:space="preserve">Yellow cells — rate per slab. Fill these in to value the stock.</t>
+    <t xml:space="preserve">Yellow cells — the statement date, and rate per slab. Fill the rates in to value the stock.</t>
   </si>
   <si>
     <t xml:space="preserve">Black figures — calculated. Do not type over them, or the sheet stops adding up.</t>
   </si>
   <si>
-    <t xml:space="preserve">Grey — the Key column, which links a stock row to its entries. Leave it alone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A worked entry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Daily Entry' already holds the production recorded on 20/08/2026 — 14 rows,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,880 slabs. Copy the shape of those rows. With them, 'Stock' shows a closing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">position of 1,07,750 slabs, which is the total on the paper statement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adding a grade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add the row at the bottom of 'Stock' (brand, grade, opening balance), then copy the</t>
+    <t xml:space="preserve">Grey — Key, Moved today and Rank. Machinery for the dropdown and the report. Leave alone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dates must be real dates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type 21/08/2026, not text. A date stored as text never matches the Statement date,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and the two 'today' columns would quietly read zero.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adding a product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add the row at the bottom of 'Stock' (brand, product, opening balance), then copy the</t>
   </si>
   <si>
     <t xml:space="preserve">formulas down from the row above. The dropdown picks it up automatically.</t>
@@ -130,7 +143,7 @@
     <t xml:space="preserve">Source</t>
   </si>
   <si>
-    <t xml:space="preserve">Opening balances and the 20/08 production are taken from the purchase &amp; processing</t>
+    <t xml:space="preserve">Opening balances and the first day of production come from the purchase &amp; processing</t>
   </si>
   <si>
     <t xml:space="preserve">statement dated 20/08/26, supplied by Premier Exports International.</t>
@@ -142,100 +155,103 @@
     <t xml:space="preserve">Statement date</t>
   </si>
   <si>
-    <t xml:space="preserve">20/08/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">← set this to drive the two "today" columns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opening balance is the frozen baseline of 20/08/2026 — never re-key it. Closing follows from the dated rows on 'Daily Entry'.</t>
+    <t xml:space="preserve">← set to today; drives the two "today" columns and the Daily Report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opening balance is a frozen baseline — never re-key it. Closing follows from the dated rows on 'Daily Entry'.</t>
   </si>
   <si>
     <t xml:space="preserve">Brand</t>
   </si>
   <si>
-    <t xml:space="preserve">Count / grade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opening balance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Today's production</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Today's shipment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production to date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shipment to date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closing slabs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rate / slab (₹)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stock value (₹)</t>
+    <t xml:space="preserve">Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opening Balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today's Production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today's Shipment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production to Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipment to Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closing Balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rate / Slab (₹)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stock Value (₹)</t>
   </si>
   <si>
     <t xml:space="preserve">Key (do not edit)</t>
   </si>
   <si>
+    <t xml:space="preserve">Moved today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
     <t xml:space="preserve">Blue Dolphin</t>
   </si>
   <si>
-    <t xml:space="preserve">PD 100/200 P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PD 100/200 K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PUD 200/300 P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PUD 200/300 K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PUD 300/500 P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PUD 300/500 K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PD 200/300 P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primus PUD Japan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PUD 40/60 KZN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PUD 60/80 KZN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PUD 80/120 P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PUD 80/120 KZN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PUD 80/120 N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PUD 100/200 P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PUD 100/200 N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PUD 100/200 KZN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PUD 200/300 KZN</t>
+    <t xml:space="preserve">PD PVN 100/200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD KKD 100/200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUD PVN 200/300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUD KKD 200/300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUD PVN 300/500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUD KKD 300/500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD PVN 200/300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primus Japan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUD KZN 40/60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUD KZN 60/80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUD PVN 80/120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUD KZN 80/120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUD NRN 80/120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUD PVN 100/200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUD NRN 100/200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUD KZN 100/200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUD KZN 200/300</t>
   </si>
   <si>
     <t xml:space="preserve">Primus EU</t>
@@ -268,16 +284,7 @@
     <t xml:space="preserve">AMF Brand</t>
   </si>
   <si>
-    <t xml:space="preserve">THT Brand PUD PVN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80/120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100/200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200/300</t>
+    <t xml:space="preserve">THT Brand</t>
   </si>
   <si>
     <t xml:space="preserve">Deepsea</t>
@@ -286,31 +293,31 @@
     <t xml:space="preserve">300/500</t>
   </si>
   <si>
-    <t xml:space="preserve">China PUD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300/500 P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300/500 K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500/800 P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500/800 K</t>
+    <t xml:space="preserve">China</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUD PVN 500/800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUD KKD 500/800</t>
   </si>
   <si>
     <t xml:space="preserve">GRAND TOTAL</t>
   </si>
   <si>
-    <t xml:space="preserve">Closing slabs = opening balance + production to date − shipment to date        Stock value = closing slabs × rate per slab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DAILY ENTRY — ADD ONE ROW PER GRADE THAT MOVED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">After production, add a row below: date, item from the dropdown, slabs produced and/or shipped. Never delete past rows — they are what the closing position is built from.</t>
+    <t xml:space="preserve">Closing Balance = Opening Balance + Production to Date − Shipment to Date        Stock Value = Closing Balance × Rate per Slab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAILY ENTRY — ADD ONE ROW PER PRODUCT THAT MOVED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After production, add a row below: date, product from the dropdown, slabs produced and/or shipped. Never delete past rows — they are what the closing position is built from.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rows that will not reach Stock:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">← must stay at 0; anything else is a mistyped product</t>
   </si>
   <si>
     <t xml:space="preserve">Date</t>
@@ -328,58 +335,58 @@
     <t xml:space="preserve">Note</t>
   </si>
   <si>
-    <t xml:space="preserve">Blue Dolphin - PD 100/200 P</t>
+    <t xml:space="preserve">Blue Dolphin - PD PVN 100/200</t>
   </si>
   <si>
     <t xml:space="preserve">Day's production per statement 20/08/26</t>
   </si>
   <si>
-    <t xml:space="preserve">Blue Dolphin - PD 100/200 K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blue Dolphin - PUD 200/300 P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primus PUD Japan - PUD 40/60 KZN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primus PUD Japan - PUD 60/80 KZN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primus PUD Japan - PUD 80/120 KZN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primus PUD Japan - PUD 80/120 N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primus PUD Japan - PUD 100/200 KZN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primus PUD Japan - PUD 200/300 KZN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primus PUD Japan - PUD 300/500 P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primus PUD Japan - PUD 300/500 K</t>
+    <t xml:space="preserve">Blue Dolphin - PD KKD 100/200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue Dolphin - PUD PVN 200/300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primus Japan - PUD KZN 40/60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primus Japan - PUD KZN 60/80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primus Japan - PUD KZN 80/120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primus Japan - PUD NRN 80/120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primus Japan - PUD KZN 100/200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primus Japan - PUD KZN 200/300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primus Japan - PUD PVN 300/500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primus Japan - PUD KKD 300/500</t>
   </si>
   <si>
     <t xml:space="preserve">Primus EU - BKN</t>
   </si>
   <si>
-    <t xml:space="preserve">THT Brand PUD PVN - 80/120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THT Brand PUD PVN - 100/200</t>
+    <t xml:space="preserve">THT Brand - PUD PVN 80/120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THT Brand - PUD PVN 100/200</t>
   </si>
   <si>
     <t xml:space="preserve">SUMMARY BY BRAND</t>
   </si>
   <si>
-    <t xml:space="preserve">Closing stock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stock value</t>
+    <t xml:space="preserve">Closing Stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stock Value</t>
   </si>
   <si>
     <t xml:space="preserve">slabs</t>
@@ -392,20 +399,76 @@
   </si>
   <si>
     <t xml:space="preserve">Brand totals read straight off 'Stock', so they can never disagree with it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premier Exports International</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AP X/453, NH-66 Highway, Chandiroor P.O.,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aroor, Alappuzha, Kerala - 688 537, India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSTIN 32AADFP3158P1ZZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAILY STOCK REPORT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PURCHASE &amp; PROCESSING · PRODUCTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STATEMENT DATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPENING BALANCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TODAY'S PRODUCTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TODAY'S SHIPMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLOSING BALANCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STOCK VALUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POSITION BY BRAND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TODAY'S MOVEMENTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL MOVED TODAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepared from the stock register. Closing Balance = Opening Balance + Production to Date − Shipment to Date.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="[&gt;=10000000]##\,##\,##\,##0;[&gt;=100000]##\,##\,##0;#,##0"/>
-    <numFmt numFmtId="166" formatCode="#,##0;\-#,##0;\–"/>
-    <numFmt numFmtId="167" formatCode="#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="[&gt;=10000000]&quot;₹ &quot;##\,##\,##\,##0.00;[&gt;=100000]&quot;₹ &quot;##\,##\,##0.00;&quot;₹ &quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="[&gt;=10000000]##\,##\,##\,##0;[&gt;=100000]##\,##\,##0;#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0;\-#,##0;\–"/>
+    <numFmt numFmtId="168" formatCode="#,##0.00"/>
+    <numFmt numFmtId="169" formatCode="[&gt;=10000000]&quot;₹ &quot;##\,##\,##\,##0.00;[&gt;=100000]&quot;₹ &quot;##\,##\,##0.00;&quot;₹ &quot;#,##0.00"/>
+    <numFmt numFmtId="170" formatCode="General"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -542,14 +605,131 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFB3261E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="16"/>
       <color rgb="FF065E7A"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="17"/>
+      <color rgb="FF00A2D3"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF5E7C8B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="17"/>
+      <color rgb="FF0B2C3A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FF065E7A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="8"/>
+      <color rgb="FF5E7C8B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="8"/>
+      <color rgb="FFCFE8F2"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF0B2C3A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF065E7A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="8"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0B2C3A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF0B2C3A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="8"/>
+      <color rgb="FFB3261E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="8"/>
+      <color rgb="FF5E7C8B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -583,11 +763,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F8FB"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFE7F3F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F3F9"/>
+        <bgColor rgb="FFF2F8FB"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -610,6 +796,76 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF00A2D3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFCBDFE8"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCBDFE8"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCBDFE8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFCBDFE8"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCBDFE8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFCBDFE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCBDFE8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCBDFE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFCBDFE8"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCBDFE8"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF065E7A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCBDFE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCBDFE8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -636,7 +892,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="79">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -673,7 +929,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -701,83 +957,91 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -785,15 +1049,163 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="27" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="27" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="28" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="32" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="32" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -806,7 +1218,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="10">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -885,6 +1297,23 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border diagonalUp="false" diagonalDown="false">
+        <left style="thin">
+          <color rgb="FFCBDFE8"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBDFE8"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBDFE8"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBDFE8"/>
+        </bottom>
+        <diagonal/>
+      </border>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -907,7 +1336,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFF2F8FB"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFE7F3F9"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -920,8 +1349,8 @@
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF00A2D3"/>
+      <rgbColor rgb="FFCFE8F2"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -955,6 +1384,48 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>495000</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>399600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="495000" cy="399600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1137,7 +1608,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -1175,15 +1646,15 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4"/>
+      <c r="B8" s="4" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="B9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1211,12 +1682,12 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1226,7 +1697,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="4" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1239,12 +1710,12 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="6" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1254,15 +1725,15 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="4"/>
+      <c r="B25" s="7" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="B26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1272,21 +1743,44 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="4"/>
+      <c r="B29" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="B30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="4"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1305,17 +1799,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L52"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="4" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="7"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1325,67 +1820,73 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>28</v>
+        <v>31</v>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>46254</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K7" s="13"/>
       <c r="L7" s="14" t="s">
-        <v>41</v>
+        <v>44</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C8" s="16" t="n">
         <v>11459</v>
@@ -1417,15 +1918,23 @@
       </c>
       <c r="L8" s="22" t="str">
         <f aca="false">$A8&amp;" - "&amp;$B8</f>
-        <v>Blue Dolphin - PD 100/200 P</v>
+        <v>Blue Dolphin - PD PVN 100/200</v>
+      </c>
+      <c r="M8" s="22" t="n">
+        <f aca="false">IF(OR($D8&lt;&gt;0,$E8&lt;&gt;0),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="N8" s="22" t="n">
+        <f aca="false">IF($M8=1,SUM($M$8:$M8),"")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C9" s="24" t="n">
         <v>517</v>
@@ -1457,15 +1966,23 @@
       </c>
       <c r="L9" s="22" t="str">
         <f aca="false">$A9&amp;" - "&amp;$B9</f>
-        <v>Blue Dolphin - PD 100/200 K</v>
+        <v>Blue Dolphin - PD KKD 100/200</v>
+      </c>
+      <c r="M9" s="22" t="n">
+        <f aca="false">IF(OR($D9&lt;&gt;0,$E9&lt;&gt;0),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="N9" s="22" t="n">
+        <f aca="false">IF($M9=1,SUM($M$8:$M9),"")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C10" s="16" t="n">
         <v>2262</v>
@@ -1497,15 +2014,23 @@
       </c>
       <c r="L10" s="22" t="str">
         <f aca="false">$A10&amp;" - "&amp;$B10</f>
-        <v>Blue Dolphin - PUD 200/300 P</v>
+        <v>Blue Dolphin - PUD PVN 200/300</v>
+      </c>
+      <c r="M10" s="22" t="n">
+        <f aca="false">IF(OR($D10&lt;&gt;0,$E10&lt;&gt;0),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="N10" s="22" t="n">
+        <f aca="false">IF($M10=1,SUM($M$8:$M10),"")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C11" s="24" t="n">
         <v>2835</v>
@@ -1537,15 +2062,23 @@
       </c>
       <c r="L11" s="22" t="str">
         <f aca="false">$A11&amp;" - "&amp;$B11</f>
-        <v>Blue Dolphin - PUD 200/300 K</v>
+        <v>Blue Dolphin - PUD KKD 200/300</v>
+      </c>
+      <c r="M11" s="22" t="n">
+        <f aca="false">IF(OR($D11&lt;&gt;0,$E11&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="22" t="str">
+        <f aca="false">IF($M11=1,SUM($M$8:$M11),"")</f>
+        <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C12" s="16" t="n">
         <v>1673</v>
@@ -1577,15 +2110,23 @@
       </c>
       <c r="L12" s="22" t="str">
         <f aca="false">$A12&amp;" - "&amp;$B12</f>
-        <v>Blue Dolphin - PUD 300/500 P</v>
+        <v>Blue Dolphin - PUD PVN 300/500</v>
+      </c>
+      <c r="M12" s="22" t="n">
+        <f aca="false">IF(OR($D12&lt;&gt;0,$E12&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="22" t="str">
+        <f aca="false">IF($M12=1,SUM($M$8:$M12),"")</f>
+        <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C13" s="24" t="n">
         <v>7542</v>
@@ -1617,15 +2158,23 @@
       </c>
       <c r="L13" s="22" t="str">
         <f aca="false">$A13&amp;" - "&amp;$B13</f>
-        <v>Blue Dolphin - PUD 300/500 K</v>
+        <v>Blue Dolphin - PUD KKD 300/500</v>
+      </c>
+      <c r="M13" s="22" t="n">
+        <f aca="false">IF(OR($D13&lt;&gt;0,$E13&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="22" t="str">
+        <f aca="false">IF($M13=1,SUM($M$8:$M13),"")</f>
+        <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C14" s="16" t="n">
         <v>2357</v>
@@ -1657,15 +2206,23 @@
       </c>
       <c r="L14" s="22" t="str">
         <f aca="false">$A14&amp;" - "&amp;$B14</f>
-        <v>Blue Dolphin - PD 200/300 P</v>
+        <v>Blue Dolphin - PD PVN 200/300</v>
+      </c>
+      <c r="M14" s="22" t="n">
+        <f aca="false">IF(OR($D14&lt;&gt;0,$E14&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="22" t="str">
+        <f aca="false">IF($M14=1,SUM($M$8:$M14),"")</f>
+        <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C15" s="24" t="n">
         <v>64</v>
@@ -1697,15 +2254,23 @@
       </c>
       <c r="L15" s="22" t="str">
         <f aca="false">$A15&amp;" - "&amp;$B15</f>
-        <v>Primus PUD Japan - PUD 40/60 KZN</v>
+        <v>Primus Japan - PUD KZN 40/60</v>
+      </c>
+      <c r="M15" s="22" t="n">
+        <f aca="false">IF(OR($D15&lt;&gt;0,$E15&lt;&gt;0),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="N15" s="22" t="n">
+        <f aca="false">IF($M15=1,SUM($M$8:$M15),"")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C16" s="16" t="n">
         <v>191</v>
@@ -1737,15 +2302,23 @@
       </c>
       <c r="L16" s="22" t="str">
         <f aca="false">$A16&amp;" - "&amp;$B16</f>
-        <v>Primus PUD Japan - PUD 60/80 KZN</v>
+        <v>Primus Japan - PUD KZN 60/80</v>
+      </c>
+      <c r="M16" s="22" t="n">
+        <f aca="false">IF(OR($D16&lt;&gt;0,$E16&lt;&gt;0),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="N16" s="22" t="n">
+        <f aca="false">IF($M16=1,SUM($M$8:$M16),"")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="23" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C17" s="24" t="n">
         <v>16849</v>
@@ -1777,15 +2350,23 @@
       </c>
       <c r="L17" s="22" t="str">
         <f aca="false">$A17&amp;" - "&amp;$B17</f>
-        <v>Primus PUD Japan - PUD 80/120 P</v>
+        <v>Primus Japan - PUD PVN 80/120</v>
+      </c>
+      <c r="M17" s="22" t="n">
+        <f aca="false">IF(OR($D17&lt;&gt;0,$E17&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="22" t="str">
+        <f aca="false">IF($M17=1,SUM($M$8:$M17),"")</f>
+        <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C18" s="16" t="n">
         <v>466</v>
@@ -1817,15 +2398,23 @@
       </c>
       <c r="L18" s="22" t="str">
         <f aca="false">$A18&amp;" - "&amp;$B18</f>
-        <v>Primus PUD Japan - PUD 80/120 KZN</v>
+        <v>Primus Japan - PUD KZN 80/120</v>
+      </c>
+      <c r="M18" s="22" t="n">
+        <f aca="false">IF(OR($D18&lt;&gt;0,$E18&lt;&gt;0),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="N18" s="22" t="n">
+        <f aca="false">IF($M18=1,SUM($M$8:$M18),"")</f>
+        <v>6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C19" s="24" t="n">
         <v>69</v>
@@ -1857,15 +2446,23 @@
       </c>
       <c r="L19" s="22" t="str">
         <f aca="false">$A19&amp;" - "&amp;$B19</f>
-        <v>Primus PUD Japan - PUD 80/120 N</v>
+        <v>Primus Japan - PUD NRN 80/120</v>
+      </c>
+      <c r="M19" s="22" t="n">
+        <f aca="false">IF(OR($D19&lt;&gt;0,$E19&lt;&gt;0),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="N19" s="22" t="n">
+        <f aca="false">IF($M19=1,SUM($M$8:$M19),"")</f>
+        <v>7</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C20" s="16" t="n">
         <v>2617</v>
@@ -1897,15 +2494,23 @@
       </c>
       <c r="L20" s="22" t="str">
         <f aca="false">$A20&amp;" - "&amp;$B20</f>
-        <v>Primus PUD Japan - PUD 100/200 P</v>
+        <v>Primus Japan - PUD PVN 100/200</v>
+      </c>
+      <c r="M20" s="22" t="n">
+        <f aca="false">IF(OR($D20&lt;&gt;0,$E20&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="22" t="str">
+        <f aca="false">IF($M20=1,SUM($M$8:$M20),"")</f>
+        <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C21" s="24" t="n">
         <v>13</v>
@@ -1937,15 +2542,23 @@
       </c>
       <c r="L21" s="22" t="str">
         <f aca="false">$A21&amp;" - "&amp;$B21</f>
-        <v>Primus PUD Japan - PUD 100/200 N</v>
+        <v>Primus Japan - PUD NRN 100/200</v>
+      </c>
+      <c r="M21" s="22" t="n">
+        <f aca="false">IF(OR($D21&lt;&gt;0,$E21&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N21" s="22" t="str">
+        <f aca="false">IF($M21=1,SUM($M$8:$M21),"")</f>
+        <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C22" s="16" t="n">
         <v>4209</v>
@@ -1977,15 +2590,23 @@
       </c>
       <c r="L22" s="22" t="str">
         <f aca="false">$A22&amp;" - "&amp;$B22</f>
-        <v>Primus PUD Japan - PUD 100/200 KZN</v>
+        <v>Primus Japan - PUD KZN 100/200</v>
+      </c>
+      <c r="M22" s="22" t="n">
+        <f aca="false">IF(OR($D22&lt;&gt;0,$E22&lt;&gt;0),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="N22" s="22" t="n">
+        <f aca="false">IF($M22=1,SUM($M$8:$M22),"")</f>
+        <v>8</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="23" t="s">
         <v>50</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>45</v>
       </c>
       <c r="C23" s="24" t="n">
         <v>0</v>
@@ -2017,15 +2638,23 @@
       </c>
       <c r="L23" s="22" t="str">
         <f aca="false">$A23&amp;" - "&amp;$B23</f>
-        <v>Primus PUD Japan - PUD 200/300 P</v>
+        <v>Primus Japan - PUD PVN 200/300</v>
+      </c>
+      <c r="M23" s="22" t="n">
+        <f aca="false">IF(OR($D23&lt;&gt;0,$E23&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N23" s="22" t="str">
+        <f aca="false">IF($M23=1,SUM($M$8:$M23),"")</f>
+        <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C24" s="16" t="n">
         <v>2757</v>
@@ -2057,15 +2686,23 @@
       </c>
       <c r="L24" s="22" t="str">
         <f aca="false">$A24&amp;" - "&amp;$B24</f>
-        <v>Primus PUD Japan - PUD 200/300 K</v>
+        <v>Primus Japan - PUD KKD 200/300</v>
+      </c>
+      <c r="M24" s="22" t="n">
+        <f aca="false">IF(OR($D24&lt;&gt;0,$E24&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N24" s="22" t="str">
+        <f aca="false">IF($M24=1,SUM($M$8:$M24),"")</f>
+        <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>1080</v>
@@ -2097,15 +2734,23 @@
       </c>
       <c r="L25" s="22" t="str">
         <f aca="false">$A25&amp;" - "&amp;$B25</f>
-        <v>Primus PUD Japan - PUD 200/300 KZN</v>
+        <v>Primus Japan - PUD KZN 200/300</v>
+      </c>
+      <c r="M25" s="22" t="n">
+        <f aca="false">IF(OR($D25&lt;&gt;0,$E25&lt;&gt;0),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="N25" s="22" t="n">
+        <f aca="false">IF($M25=1,SUM($M$8:$M25),"")</f>
+        <v>9</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C26" s="16" t="n">
         <v>421</v>
@@ -2137,15 +2782,23 @@
       </c>
       <c r="L26" s="22" t="str">
         <f aca="false">$A26&amp;" - "&amp;$B26</f>
-        <v>Primus PUD Japan - PUD 300/500 P</v>
+        <v>Primus Japan - PUD PVN 300/500</v>
+      </c>
+      <c r="M26" s="22" t="n">
+        <f aca="false">IF(OR($D26&lt;&gt;0,$E26&lt;&gt;0),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="N26" s="22" t="n">
+        <f aca="false">IF($M26=1,SUM($M$8:$M26),"")</f>
+        <v>10</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="23" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>580</v>
@@ -2177,15 +2830,23 @@
       </c>
       <c r="L27" s="22" t="str">
         <f aca="false">$A27&amp;" - "&amp;$B27</f>
-        <v>Primus PUD Japan - PUD 300/500 K</v>
+        <v>Primus Japan - PUD KKD 300/500</v>
+      </c>
+      <c r="M27" s="22" t="n">
+        <f aca="false">IF(OR($D27&lt;&gt;0,$E27&lt;&gt;0),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="N27" s="22" t="n">
+        <f aca="false">IF($M27=1,SUM($M$8:$M27),"")</f>
+        <v>11</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C28" s="16" t="n">
         <v>185</v>
@@ -2219,13 +2880,21 @@
         <f aca="false">$A28&amp;" - "&amp;$B28</f>
         <v>Primus EU - PUD 20/40</v>
       </c>
+      <c r="M28" s="22" t="n">
+        <f aca="false">IF(OR($D28&lt;&gt;0,$E28&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N28" s="22" t="str">
+        <f aca="false">IF($M28=1,SUM($M$8:$M28),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="23" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C29" s="24" t="n">
         <v>368</v>
@@ -2259,13 +2928,21 @@
         <f aca="false">$A29&amp;" - "&amp;$B29</f>
         <v>Primus EU - PUD 40/60</v>
       </c>
+      <c r="M29" s="22" t="n">
+        <f aca="false">IF(OR($D29&lt;&gt;0,$E29&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N29" s="22" t="str">
+        <f aca="false">IF($M29=1,SUM($M$8:$M29),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C30" s="16" t="n">
         <v>380</v>
@@ -2299,13 +2976,21 @@
         <f aca="false">$A30&amp;" - "&amp;$B30</f>
         <v>Primus EU - PUD 60/80</v>
       </c>
+      <c r="M30" s="22" t="n">
+        <f aca="false">IF(OR($D30&lt;&gt;0,$E30&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N30" s="22" t="str">
+        <f aca="false">IF($M30=1,SUM($M$8:$M30),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="23" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C31" s="24" t="n">
         <v>1151</v>
@@ -2339,13 +3024,21 @@
         <f aca="false">$A31&amp;" - "&amp;$B31</f>
         <v>Primus EU - PUD 80/120</v>
       </c>
+      <c r="M31" s="22" t="n">
+        <f aca="false">IF(OR($D31&lt;&gt;0,$E31&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N31" s="22" t="str">
+        <f aca="false">IF($M31=1,SUM($M$8:$M31),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C32" s="16" t="n">
         <v>3797</v>
@@ -2379,13 +3072,21 @@
         <f aca="false">$A32&amp;" - "&amp;$B32</f>
         <v>Primus EU - PUD 100/200</v>
       </c>
+      <c r="M32" s="22" t="n">
+        <f aca="false">IF(OR($D32&lt;&gt;0,$E32&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N32" s="22" t="str">
+        <f aca="false">IF($M32=1,SUM($M$8:$M32),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="23" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>4118</v>
@@ -2419,13 +3120,21 @@
         <f aca="false">$A33&amp;" - "&amp;$B33</f>
         <v>Primus EU - PUD 200/300</v>
       </c>
+      <c r="M33" s="22" t="n">
+        <f aca="false">IF(OR($D33&lt;&gt;0,$E33&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N33" s="22" t="str">
+        <f aca="false">IF($M33=1,SUM($M$8:$M33),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C34" s="16" t="n">
         <v>1490</v>
@@ -2459,13 +3168,21 @@
         <f aca="false">$A34&amp;" - "&amp;$B34</f>
         <v>Primus EU - PUD 300/500</v>
       </c>
+      <c r="M34" s="22" t="n">
+        <f aca="false">IF(OR($D34&lt;&gt;0,$E34&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N34" s="22" t="str">
+        <f aca="false">IF($M34=1,SUM($M$8:$M34),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="23" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C35" s="24" t="n">
         <v>15130</v>
@@ -2499,13 +3216,21 @@
         <f aca="false">$A35&amp;" - "&amp;$B35</f>
         <v>Primus EU - BKN</v>
       </c>
+      <c r="M35" s="22" t="n">
+        <f aca="false">IF(OR($D35&lt;&gt;0,$E35&lt;&gt;0),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="N35" s="22" t="n">
+        <f aca="false">IF($M35=1,SUM($M$8:$M35),"")</f>
+        <v>12</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C36" s="16" t="n">
         <v>0</v>
@@ -2537,15 +3262,23 @@
       </c>
       <c r="L36" s="22" t="str">
         <f aca="false">$A36&amp;" - "&amp;$B36</f>
-        <v>AMF Brand - PD 100/200 P</v>
+        <v>AMF Brand - PD PVN 100/200</v>
+      </c>
+      <c r="M36" s="22" t="n">
+        <f aca="false">IF(OR($D36&lt;&gt;0,$E36&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N36" s="22" t="str">
+        <f aca="false">IF($M36=1,SUM($M$8:$M36),"")</f>
+        <v/>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="23" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C37" s="24" t="n">
         <v>0</v>
@@ -2577,15 +3310,23 @@
       </c>
       <c r="L37" s="22" t="str">
         <f aca="false">$A37&amp;" - "&amp;$B37</f>
-        <v>AMF Brand - PD 100/200 K</v>
+        <v>AMF Brand - PD KKD 100/200</v>
+      </c>
+      <c r="M37" s="22" t="n">
+        <f aca="false">IF(OR($D37&lt;&gt;0,$E37&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N37" s="22" t="str">
+        <f aca="false">IF($M37=1,SUM($M$8:$M37),"")</f>
+        <v/>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C38" s="16" t="n">
         <v>1516</v>
@@ -2617,15 +3358,23 @@
       </c>
       <c r="L38" s="22" t="str">
         <f aca="false">$A38&amp;" - "&amp;$B38</f>
-        <v>AMF Brand - PUD 200/300 P</v>
+        <v>AMF Brand - PUD PVN 200/300</v>
+      </c>
+      <c r="M38" s="22" t="n">
+        <f aca="false">IF(OR($D38&lt;&gt;0,$E38&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N38" s="22" t="str">
+        <f aca="false">IF($M38=1,SUM($M$8:$M38),"")</f>
+        <v/>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="23" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C39" s="24" t="n">
         <v>0</v>
@@ -2657,15 +3406,23 @@
       </c>
       <c r="L39" s="22" t="str">
         <f aca="false">$A39&amp;" - "&amp;$B39</f>
-        <v>AMF Brand - PUD 200/300 K</v>
+        <v>AMF Brand - PUD KKD 200/300</v>
+      </c>
+      <c r="M39" s="22" t="n">
+        <f aca="false">IF(OR($D39&lt;&gt;0,$E39&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N39" s="22" t="str">
+        <f aca="false">IF($M39=1,SUM($M$8:$M39),"")</f>
+        <v/>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C40" s="16" t="n">
         <v>18</v>
@@ -2697,15 +3454,23 @@
       </c>
       <c r="L40" s="22" t="str">
         <f aca="false">$A40&amp;" - "&amp;$B40</f>
-        <v>AMF Brand - PUD 300/500 P</v>
+        <v>AMF Brand - PUD PVN 300/500</v>
+      </c>
+      <c r="M40" s="22" t="n">
+        <f aca="false">IF(OR($D40&lt;&gt;0,$E40&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N40" s="22" t="str">
+        <f aca="false">IF($M40=1,SUM($M$8:$M40),"")</f>
+        <v/>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="23" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C41" s="24" t="n">
         <v>0</v>
@@ -2737,15 +3502,23 @@
       </c>
       <c r="L41" s="22" t="str">
         <f aca="false">$A41&amp;" - "&amp;$B41</f>
-        <v>AMF Brand - PUD 300/500 K</v>
+        <v>AMF Brand - PUD KKD 300/500</v>
+      </c>
+      <c r="M41" s="22" t="n">
+        <f aca="false">IF(OR($D41&lt;&gt;0,$E41&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N41" s="22" t="str">
+        <f aca="false">IF($M41=1,SUM($M$8:$M41),"")</f>
+        <v/>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C42" s="16" t="n">
         <v>1389</v>
@@ -2777,15 +3550,23 @@
       </c>
       <c r="L42" s="22" t="str">
         <f aca="false">$A42&amp;" - "&amp;$B42</f>
-        <v>THT Brand PUD PVN - 80/120</v>
+        <v>THT Brand - PUD PVN 80/120</v>
+      </c>
+      <c r="M42" s="22" t="n">
+        <f aca="false">IF(OR($D42&lt;&gt;0,$E42&lt;&gt;0),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="N42" s="22" t="n">
+        <f aca="false">IF($M42=1,SUM($M$8:$M42),"")</f>
+        <v>13</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="23" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C43" s="24" t="n">
         <v>7055</v>
@@ -2817,15 +3598,23 @@
       </c>
       <c r="L43" s="22" t="str">
         <f aca="false">$A43&amp;" - "&amp;$B43</f>
-        <v>THT Brand PUD PVN - 100/200</v>
+        <v>THT Brand - PUD PVN 100/200</v>
+      </c>
+      <c r="M43" s="22" t="n">
+        <f aca="false">IF(OR($D43&lt;&gt;0,$E43&lt;&gt;0),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="N43" s="22" t="n">
+        <f aca="false">IF($M43=1,SUM($M$8:$M43),"")</f>
+        <v>14</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="C44" s="16" t="n">
         <v>4682</v>
@@ -2857,15 +3646,23 @@
       </c>
       <c r="L44" s="22" t="str">
         <f aca="false">$A44&amp;" - "&amp;$B44</f>
-        <v>THT Brand PUD PVN - 200/300</v>
+        <v>THT Brand - PUD PVN 200/300</v>
+      </c>
+      <c r="M44" s="22" t="n">
+        <f aca="false">IF(OR($D44&lt;&gt;0,$E44&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N44" s="22" t="str">
+        <f aca="false">IF($M44=1,SUM($M$8:$M44),"")</f>
+        <v/>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="23" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C45" s="24" t="n">
         <v>670</v>
@@ -2899,13 +3696,21 @@
         <f aca="false">$A45&amp;" - "&amp;$B45</f>
         <v>Deepsea - 300/500</v>
       </c>
+      <c r="M45" s="22" t="n">
+        <f aca="false">IF(OR($D45&lt;&gt;0,$E45&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N45" s="22" t="str">
+        <f aca="false">IF($M45=1,SUM($M$8:$M45),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="C46" s="16" t="n">
         <v>451</v>
@@ -2937,15 +3742,23 @@
       </c>
       <c r="L46" s="22" t="str">
         <f aca="false">$A46&amp;" - "&amp;$B46</f>
-        <v>China PUD - 300/500 P</v>
+        <v>China - PUD PVN 300/500</v>
+      </c>
+      <c r="M46" s="22" t="n">
+        <f aca="false">IF(OR($D46&lt;&gt;0,$E46&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N46" s="22" t="str">
+        <f aca="false">IF($M46=1,SUM($M$8:$M46),"")</f>
+        <v/>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="C47" s="24" t="n">
         <v>188</v>
@@ -2977,12 +3790,20 @@
       </c>
       <c r="L47" s="22" t="str">
         <f aca="false">$A47&amp;" - "&amp;$B47</f>
-        <v>China PUD - 300/500 K</v>
+        <v>China - PUD KKD 300/500</v>
+      </c>
+      <c r="M47" s="22" t="n">
+        <f aca="false">IF(OR($D47&lt;&gt;0,$E47&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N47" s="22" t="str">
+        <f aca="false">IF($M47=1,SUM($M$8:$M47),"")</f>
+        <v/>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B48" s="15" t="s">
         <v>79</v>
@@ -3017,12 +3838,20 @@
       </c>
       <c r="L48" s="22" t="str">
         <f aca="false">$A48&amp;" - "&amp;$B48</f>
-        <v>China PUD - 500/800 P</v>
+        <v>China - PUD PVN 500/800</v>
+      </c>
+      <c r="M48" s="22" t="n">
+        <f aca="false">IF(OR($D48&lt;&gt;0,$E48&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N48" s="22" t="str">
+        <f aca="false">IF($M48=1,SUM($M$8:$M48),"")</f>
+        <v/>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B49" s="23" t="s">
         <v>80</v>
@@ -3057,40 +3886,48 @@
       </c>
       <c r="L49" s="22" t="str">
         <f aca="false">$A49&amp;" - "&amp;$B49</f>
-        <v>China PUD - 500/800 K</v>
+        <v>China - PUD KKD 500/800</v>
+      </c>
+      <c r="M49" s="22" t="n">
+        <f aca="false">IF(OR($D49&lt;&gt;0,$E49&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N49" s="22" t="str">
+        <f aca="false">IF($M49=1,SUM($M$8:$M49),"")</f>
+        <v/>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="B50" s="30"/>
-      <c r="C50" s="31" t="n">
+      <c r="B50" s="29"/>
+      <c r="C50" s="30" t="n">
         <f aca="false">SUM(C8:C49)</f>
         <v>102870</v>
       </c>
-      <c r="D50" s="32" t="n">
+      <c r="D50" s="31" t="n">
         <f aca="false">SUM(D8:D49)</f>
         <v>4880</v>
       </c>
-      <c r="E50" s="32" t="n">
+      <c r="E50" s="31" t="n">
         <f aca="false">SUM(E8:E49)</f>
         <v>0</v>
       </c>
-      <c r="F50" s="31" t="n">
+      <c r="F50" s="30" t="n">
         <f aca="false">SUM(F8:F49)</f>
         <v>4880</v>
       </c>
-      <c r="G50" s="31" t="n">
+      <c r="G50" s="30" t="n">
         <f aca="false">SUM(G8:G49)</f>
         <v>0</v>
       </c>
-      <c r="H50" s="31" t="n">
+      <c r="H50" s="30" t="n">
         <f aca="false">SUM(H8:H49)</f>
         <v>107750</v>
       </c>
       <c r="I50" s="29"/>
-      <c r="J50" s="33" t="str">
+      <c r="J50" s="32" t="str">
         <f aca="false">IF(SUM(J8:J49)=0,"",SUM(J8:J49))</f>
         <v/>
       </c>
@@ -3124,13 +3961,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E250"/>
+  <dimension ref="A1:K250"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3147,1827 +3986,1869 @@
       <c r="A4" s="10" t="s">
         <v>84</v>
       </c>
+      <c r="G4" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="J4" s="34" t="n">
+        <f aca="false">SUMPRODUCT((B7:B5000&lt;&gt;"")*(COUNTIF(Stock!$L$8:$L$49,B7:B5000)=0))</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" s="35" t="n">
+      <c r="A7" s="35" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="37" t="n">
         <v>1068</v>
       </c>
-      <c r="D7" s="35"/>
-      <c r="E7" s="36" t="s">
-        <v>91</v>
+      <c r="D7" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="38" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="C8" s="35" t="n">
+      <c r="A8" s="35" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="37" t="n">
         <v>65</v>
       </c>
-      <c r="D8" s="35"/>
-      <c r="E8" s="36"/>
+      <c r="D8" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="38"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="C9" s="35" t="n">
+      <c r="A9" s="35" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" s="37" t="n">
         <v>267</v>
       </c>
-      <c r="D9" s="35"/>
-      <c r="E9" s="36"/>
+      <c r="D9" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="38"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" s="35" t="n">
+      <c r="A10" s="35" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="37" t="n">
         <v>29</v>
       </c>
-      <c r="D10" s="35"/>
-      <c r="E10" s="36"/>
+      <c r="D10" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="38"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="C11" s="35" t="n">
+      <c r="A11" s="35" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" s="37" t="n">
         <v>39</v>
       </c>
-      <c r="D11" s="35"/>
-      <c r="E11" s="36"/>
+      <c r="D11" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="38"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="35" t="n">
+      <c r="A12" s="35" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B12" s="36" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="37" t="n">
         <v>50</v>
       </c>
-      <c r="D12" s="35"/>
-      <c r="E12" s="36"/>
+      <c r="D12" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="38"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="C13" s="35" t="n">
+      <c r="A13" s="35" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B13" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="35"/>
-      <c r="E13" s="36"/>
+      <c r="D13" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="38"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="C14" s="35" t="n">
+      <c r="A14" s="35" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B14" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="37" t="n">
         <v>50</v>
       </c>
-      <c r="D14" s="35"/>
-      <c r="E14" s="36"/>
+      <c r="D14" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="38"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="C15" s="35" t="n">
+      <c r="A15" s="35" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B15" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="37" t="n">
         <v>33</v>
       </c>
-      <c r="D15" s="35"/>
-      <c r="E15" s="36"/>
+      <c r="D15" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="38"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" s="35" t="n">
+      <c r="A16" s="35" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B16" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" s="37" t="n">
         <v>156</v>
       </c>
-      <c r="D16" s="35"/>
-      <c r="E16" s="36"/>
+      <c r="D16" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="38"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="C17" s="35" t="n">
+      <c r="A17" s="35" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="C17" s="37" t="n">
         <v>596</v>
       </c>
-      <c r="D17" s="35"/>
-      <c r="E17" s="36"/>
+      <c r="D17" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="38"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="C18" s="35" t="n">
+      <c r="A18" s="35" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B18" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="37" t="n">
         <v>52</v>
       </c>
-      <c r="D18" s="35"/>
-      <c r="E18" s="36"/>
+      <c r="D18" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="38"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="C19" s="35" t="n">
+      <c r="A19" s="35" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B19" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="37" t="n">
         <v>1872</v>
       </c>
-      <c r="D19" s="35"/>
-      <c r="E19" s="36"/>
+      <c r="D19" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="38"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="C20" s="35" t="n">
+      <c r="A20" s="35" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="37" t="n">
         <v>600</v>
       </c>
-      <c r="D20" s="35"/>
-      <c r="E20" s="36"/>
+      <c r="D20" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="38"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="34"/>
-      <c r="B21" s="34"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="34"/>
+      <c r="A21" s="35"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="36"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="34"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="34"/>
+      <c r="A22" s="35"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="36"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="34"/>
-      <c r="B23" s="34"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="34"/>
+      <c r="A23" s="35"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="36"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="34"/>
-      <c r="B24" s="34"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="34"/>
+      <c r="A24" s="35"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="36"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="34"/>
-      <c r="B25" s="34"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="34"/>
+      <c r="A25" s="35"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="36"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="34"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="34"/>
+      <c r="A26" s="35"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="36"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="34"/>
-      <c r="B27" s="34"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="34"/>
+      <c r="A27" s="35"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="36"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="34"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="34"/>
+      <c r="A28" s="35"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="36"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="34"/>
-      <c r="B29" s="34"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="34"/>
+      <c r="A29" s="35"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="36"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="34"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="35"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="34"/>
+      <c r="A30" s="35"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="36"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="34"/>
-      <c r="B31" s="34"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="34"/>
+      <c r="A31" s="35"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="36"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="34"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="34"/>
+      <c r="A32" s="35"/>
+      <c r="B32" s="36"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="36"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="34"/>
-      <c r="B33" s="34"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="34"/>
+      <c r="A33" s="35"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="36"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="34"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="35"/>
-      <c r="E34" s="34"/>
+      <c r="A34" s="35"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="36"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="34"/>
-      <c r="B35" s="34"/>
-      <c r="C35" s="35"/>
-      <c r="D35" s="35"/>
-      <c r="E35" s="34"/>
+      <c r="A35" s="35"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="36"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="34"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="35"/>
-      <c r="D36" s="35"/>
-      <c r="E36" s="34"/>
+      <c r="A36" s="35"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="36"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="34"/>
-      <c r="B37" s="34"/>
-      <c r="C37" s="35"/>
-      <c r="D37" s="35"/>
-      <c r="E37" s="34"/>
+      <c r="A37" s="35"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="36"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="34"/>
-      <c r="B38" s="34"/>
-      <c r="C38" s="35"/>
-      <c r="D38" s="35"/>
-      <c r="E38" s="34"/>
+      <c r="A38" s="35"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="37"/>
+      <c r="D38" s="37"/>
+      <c r="E38" s="36"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="34"/>
-      <c r="B39" s="34"/>
-      <c r="C39" s="35"/>
-      <c r="D39" s="35"/>
-      <c r="E39" s="34"/>
+      <c r="A39" s="35"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="37"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="36"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="34"/>
-      <c r="B40" s="34"/>
-      <c r="C40" s="35"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="34"/>
+      <c r="A40" s="35"/>
+      <c r="B40" s="36"/>
+      <c r="C40" s="37"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="36"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="34"/>
-      <c r="B41" s="34"/>
-      <c r="C41" s="35"/>
-      <c r="D41" s="35"/>
-      <c r="E41" s="34"/>
+      <c r="A41" s="35"/>
+      <c r="B41" s="36"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="37"/>
+      <c r="E41" s="36"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="34"/>
-      <c r="B42" s="34"/>
-      <c r="C42" s="35"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="34"/>
+      <c r="A42" s="35"/>
+      <c r="B42" s="36"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="36"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="34"/>
-      <c r="B43" s="34"/>
-      <c r="C43" s="35"/>
-      <c r="D43" s="35"/>
-      <c r="E43" s="34"/>
+      <c r="A43" s="35"/>
+      <c r="B43" s="36"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="36"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="34"/>
-      <c r="B44" s="34"/>
-      <c r="C44" s="35"/>
-      <c r="D44" s="35"/>
-      <c r="E44" s="34"/>
+      <c r="A44" s="35"/>
+      <c r="B44" s="36"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="36"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="34"/>
-      <c r="B45" s="34"/>
-      <c r="C45" s="35"/>
-      <c r="D45" s="35"/>
-      <c r="E45" s="34"/>
+      <c r="A45" s="35"/>
+      <c r="B45" s="36"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="36"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="34"/>
-      <c r="B46" s="34"/>
-      <c r="C46" s="35"/>
-      <c r="D46" s="35"/>
-      <c r="E46" s="34"/>
+      <c r="A46" s="35"/>
+      <c r="B46" s="36"/>
+      <c r="C46" s="37"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="36"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="34"/>
-      <c r="B47" s="34"/>
-      <c r="C47" s="35"/>
-      <c r="D47" s="35"/>
-      <c r="E47" s="34"/>
+      <c r="A47" s="35"/>
+      <c r="B47" s="36"/>
+      <c r="C47" s="37"/>
+      <c r="D47" s="37"/>
+      <c r="E47" s="36"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="34"/>
-      <c r="B48" s="34"/>
-      <c r="C48" s="35"/>
-      <c r="D48" s="35"/>
-      <c r="E48" s="34"/>
+      <c r="A48" s="35"/>
+      <c r="B48" s="36"/>
+      <c r="C48" s="37"/>
+      <c r="D48" s="37"/>
+      <c r="E48" s="36"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="34"/>
-      <c r="B49" s="34"/>
-      <c r="C49" s="35"/>
-      <c r="D49" s="35"/>
-      <c r="E49" s="34"/>
+      <c r="A49" s="35"/>
+      <c r="B49" s="36"/>
+      <c r="C49" s="37"/>
+      <c r="D49" s="37"/>
+      <c r="E49" s="36"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="34"/>
-      <c r="B50" s="34"/>
-      <c r="C50" s="35"/>
-      <c r="D50" s="35"/>
-      <c r="E50" s="34"/>
+      <c r="A50" s="35"/>
+      <c r="B50" s="36"/>
+      <c r="C50" s="37"/>
+      <c r="D50" s="37"/>
+      <c r="E50" s="36"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="34"/>
-      <c r="B51" s="34"/>
-      <c r="C51" s="35"/>
-      <c r="D51" s="35"/>
-      <c r="E51" s="34"/>
+      <c r="A51" s="35"/>
+      <c r="B51" s="36"/>
+      <c r="C51" s="37"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="36"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="34"/>
-      <c r="B52" s="34"/>
-      <c r="C52" s="35"/>
-      <c r="D52" s="35"/>
-      <c r="E52" s="34"/>
+      <c r="A52" s="35"/>
+      <c r="B52" s="36"/>
+      <c r="C52" s="37"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="36"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="34"/>
-      <c r="B53" s="34"/>
-      <c r="C53" s="35"/>
-      <c r="D53" s="35"/>
-      <c r="E53" s="34"/>
+      <c r="A53" s="35"/>
+      <c r="B53" s="36"/>
+      <c r="C53" s="37"/>
+      <c r="D53" s="37"/>
+      <c r="E53" s="36"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="34"/>
-      <c r="B54" s="34"/>
-      <c r="C54" s="35"/>
-      <c r="D54" s="35"/>
-      <c r="E54" s="34"/>
+      <c r="A54" s="35"/>
+      <c r="B54" s="36"/>
+      <c r="C54" s="37"/>
+      <c r="D54" s="37"/>
+      <c r="E54" s="36"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="34"/>
-      <c r="B55" s="34"/>
-      <c r="C55" s="35"/>
-      <c r="D55" s="35"/>
-      <c r="E55" s="34"/>
+      <c r="A55" s="35"/>
+      <c r="B55" s="36"/>
+      <c r="C55" s="37"/>
+      <c r="D55" s="37"/>
+      <c r="E55" s="36"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="34"/>
-      <c r="B56" s="34"/>
-      <c r="C56" s="35"/>
-      <c r="D56" s="35"/>
-      <c r="E56" s="34"/>
+      <c r="A56" s="35"/>
+      <c r="B56" s="36"/>
+      <c r="C56" s="37"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="36"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="34"/>
-      <c r="B57" s="34"/>
-      <c r="C57" s="35"/>
-      <c r="D57" s="35"/>
-      <c r="E57" s="34"/>
+      <c r="A57" s="35"/>
+      <c r="B57" s="36"/>
+      <c r="C57" s="37"/>
+      <c r="D57" s="37"/>
+      <c r="E57" s="36"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="34"/>
-      <c r="B58" s="34"/>
-      <c r="C58" s="35"/>
-      <c r="D58" s="35"/>
-      <c r="E58" s="34"/>
+      <c r="A58" s="35"/>
+      <c r="B58" s="36"/>
+      <c r="C58" s="37"/>
+      <c r="D58" s="37"/>
+      <c r="E58" s="36"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="34"/>
-      <c r="B59" s="34"/>
-      <c r="C59" s="35"/>
-      <c r="D59" s="35"/>
-      <c r="E59" s="34"/>
+      <c r="A59" s="35"/>
+      <c r="B59" s="36"/>
+      <c r="C59" s="37"/>
+      <c r="D59" s="37"/>
+      <c r="E59" s="36"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="34"/>
-      <c r="B60" s="34"/>
-      <c r="C60" s="35"/>
-      <c r="D60" s="35"/>
-      <c r="E60" s="34"/>
+      <c r="A60" s="35"/>
+      <c r="B60" s="36"/>
+      <c r="C60" s="37"/>
+      <c r="D60" s="37"/>
+      <c r="E60" s="36"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="34"/>
-      <c r="B61" s="34"/>
-      <c r="C61" s="35"/>
-      <c r="D61" s="35"/>
-      <c r="E61" s="34"/>
+      <c r="A61" s="35"/>
+      <c r="B61" s="36"/>
+      <c r="C61" s="37"/>
+      <c r="D61" s="37"/>
+      <c r="E61" s="36"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="34"/>
-      <c r="B62" s="34"/>
-      <c r="C62" s="35"/>
-      <c r="D62" s="35"/>
-      <c r="E62" s="34"/>
+      <c r="A62" s="35"/>
+      <c r="B62" s="36"/>
+      <c r="C62" s="37"/>
+      <c r="D62" s="37"/>
+      <c r="E62" s="36"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="34"/>
-      <c r="B63" s="34"/>
-      <c r="C63" s="35"/>
-      <c r="D63" s="35"/>
-      <c r="E63" s="34"/>
+      <c r="A63" s="35"/>
+      <c r="B63" s="36"/>
+      <c r="C63" s="37"/>
+      <c r="D63" s="37"/>
+      <c r="E63" s="36"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="34"/>
-      <c r="B64" s="34"/>
-      <c r="C64" s="35"/>
-      <c r="D64" s="35"/>
-      <c r="E64" s="34"/>
+      <c r="A64" s="35"/>
+      <c r="B64" s="36"/>
+      <c r="C64" s="37"/>
+      <c r="D64" s="37"/>
+      <c r="E64" s="36"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="34"/>
-      <c r="B65" s="34"/>
-      <c r="C65" s="35"/>
-      <c r="D65" s="35"/>
-      <c r="E65" s="34"/>
+      <c r="A65" s="35"/>
+      <c r="B65" s="36"/>
+      <c r="C65" s="37"/>
+      <c r="D65" s="37"/>
+      <c r="E65" s="36"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="34"/>
-      <c r="B66" s="34"/>
-      <c r="C66" s="35"/>
-      <c r="D66" s="35"/>
-      <c r="E66" s="34"/>
+      <c r="A66" s="35"/>
+      <c r="B66" s="36"/>
+      <c r="C66" s="37"/>
+      <c r="D66" s="37"/>
+      <c r="E66" s="36"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="34"/>
-      <c r="B67" s="34"/>
-      <c r="C67" s="35"/>
-      <c r="D67" s="35"/>
-      <c r="E67" s="34"/>
+      <c r="A67" s="35"/>
+      <c r="B67" s="36"/>
+      <c r="C67" s="37"/>
+      <c r="D67" s="37"/>
+      <c r="E67" s="36"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="34"/>
-      <c r="B68" s="34"/>
-      <c r="C68" s="35"/>
-      <c r="D68" s="35"/>
-      <c r="E68" s="34"/>
+      <c r="A68" s="35"/>
+      <c r="B68" s="36"/>
+      <c r="C68" s="37"/>
+      <c r="D68" s="37"/>
+      <c r="E68" s="36"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="34"/>
-      <c r="B69" s="34"/>
-      <c r="C69" s="35"/>
-      <c r="D69" s="35"/>
-      <c r="E69" s="34"/>
+      <c r="A69" s="35"/>
+      <c r="B69" s="36"/>
+      <c r="C69" s="37"/>
+      <c r="D69" s="37"/>
+      <c r="E69" s="36"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="34"/>
-      <c r="B70" s="34"/>
-      <c r="C70" s="35"/>
-      <c r="D70" s="35"/>
-      <c r="E70" s="34"/>
+      <c r="A70" s="35"/>
+      <c r="B70" s="36"/>
+      <c r="C70" s="37"/>
+      <c r="D70" s="37"/>
+      <c r="E70" s="36"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="34"/>
-      <c r="B71" s="34"/>
-      <c r="C71" s="35"/>
-      <c r="D71" s="35"/>
-      <c r="E71" s="34"/>
+      <c r="A71" s="35"/>
+      <c r="B71" s="36"/>
+      <c r="C71" s="37"/>
+      <c r="D71" s="37"/>
+      <c r="E71" s="36"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="34"/>
-      <c r="B72" s="34"/>
-      <c r="C72" s="35"/>
-      <c r="D72" s="35"/>
-      <c r="E72" s="34"/>
+      <c r="A72" s="35"/>
+      <c r="B72" s="36"/>
+      <c r="C72" s="37"/>
+      <c r="D72" s="37"/>
+      <c r="E72" s="36"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="34"/>
-      <c r="B73" s="34"/>
-      <c r="C73" s="35"/>
-      <c r="D73" s="35"/>
-      <c r="E73" s="34"/>
+      <c r="A73" s="35"/>
+      <c r="B73" s="36"/>
+      <c r="C73" s="37"/>
+      <c r="D73" s="37"/>
+      <c r="E73" s="36"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="34"/>
-      <c r="B74" s="34"/>
-      <c r="C74" s="35"/>
-      <c r="D74" s="35"/>
-      <c r="E74" s="34"/>
+      <c r="A74" s="35"/>
+      <c r="B74" s="36"/>
+      <c r="C74" s="37"/>
+      <c r="D74" s="37"/>
+      <c r="E74" s="36"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="34"/>
-      <c r="B75" s="34"/>
-      <c r="C75" s="35"/>
-      <c r="D75" s="35"/>
-      <c r="E75" s="34"/>
+      <c r="A75" s="35"/>
+      <c r="B75" s="36"/>
+      <c r="C75" s="37"/>
+      <c r="D75" s="37"/>
+      <c r="E75" s="36"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="34"/>
-      <c r="B76" s="34"/>
-      <c r="C76" s="35"/>
-      <c r="D76" s="35"/>
-      <c r="E76" s="34"/>
+      <c r="A76" s="35"/>
+      <c r="B76" s="36"/>
+      <c r="C76" s="37"/>
+      <c r="D76" s="37"/>
+      <c r="E76" s="36"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="34"/>
-      <c r="B77" s="34"/>
-      <c r="C77" s="35"/>
-      <c r="D77" s="35"/>
-      <c r="E77" s="34"/>
+      <c r="A77" s="35"/>
+      <c r="B77" s="36"/>
+      <c r="C77" s="37"/>
+      <c r="D77" s="37"/>
+      <c r="E77" s="36"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="34"/>
-      <c r="B78" s="34"/>
-      <c r="C78" s="35"/>
-      <c r="D78" s="35"/>
-      <c r="E78" s="34"/>
+      <c r="A78" s="35"/>
+      <c r="B78" s="36"/>
+      <c r="C78" s="37"/>
+      <c r="D78" s="37"/>
+      <c r="E78" s="36"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="34"/>
-      <c r="B79" s="34"/>
-      <c r="C79" s="35"/>
-      <c r="D79" s="35"/>
-      <c r="E79" s="34"/>
+      <c r="A79" s="35"/>
+      <c r="B79" s="36"/>
+      <c r="C79" s="37"/>
+      <c r="D79" s="37"/>
+      <c r="E79" s="36"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="34"/>
-      <c r="B80" s="34"/>
-      <c r="C80" s="35"/>
-      <c r="D80" s="35"/>
-      <c r="E80" s="34"/>
+      <c r="A80" s="35"/>
+      <c r="B80" s="36"/>
+      <c r="C80" s="37"/>
+      <c r="D80" s="37"/>
+      <c r="E80" s="36"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="34"/>
-      <c r="B81" s="34"/>
-      <c r="C81" s="35"/>
-      <c r="D81" s="35"/>
-      <c r="E81" s="34"/>
+      <c r="A81" s="35"/>
+      <c r="B81" s="36"/>
+      <c r="C81" s="37"/>
+      <c r="D81" s="37"/>
+      <c r="E81" s="36"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="34"/>
-      <c r="B82" s="34"/>
-      <c r="C82" s="35"/>
-      <c r="D82" s="35"/>
-      <c r="E82" s="34"/>
+      <c r="A82" s="35"/>
+      <c r="B82" s="36"/>
+      <c r="C82" s="37"/>
+      <c r="D82" s="37"/>
+      <c r="E82" s="36"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="34"/>
-      <c r="B83" s="34"/>
-      <c r="C83" s="35"/>
-      <c r="D83" s="35"/>
-      <c r="E83" s="34"/>
+      <c r="A83" s="35"/>
+      <c r="B83" s="36"/>
+      <c r="C83" s="37"/>
+      <c r="D83" s="37"/>
+      <c r="E83" s="36"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="34"/>
-      <c r="B84" s="34"/>
-      <c r="C84" s="35"/>
-      <c r="D84" s="35"/>
-      <c r="E84" s="34"/>
+      <c r="A84" s="35"/>
+      <c r="B84" s="36"/>
+      <c r="C84" s="37"/>
+      <c r="D84" s="37"/>
+      <c r="E84" s="36"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="34"/>
-      <c r="B85" s="34"/>
-      <c r="C85" s="35"/>
-      <c r="D85" s="35"/>
-      <c r="E85" s="34"/>
+      <c r="A85" s="35"/>
+      <c r="B85" s="36"/>
+      <c r="C85" s="37"/>
+      <c r="D85" s="37"/>
+      <c r="E85" s="36"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="34"/>
-      <c r="B86" s="34"/>
-      <c r="C86" s="35"/>
-      <c r="D86" s="35"/>
-      <c r="E86" s="34"/>
+      <c r="A86" s="35"/>
+      <c r="B86" s="36"/>
+      <c r="C86" s="37"/>
+      <c r="D86" s="37"/>
+      <c r="E86" s="36"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="34"/>
-      <c r="B87" s="34"/>
-      <c r="C87" s="35"/>
-      <c r="D87" s="35"/>
-      <c r="E87" s="34"/>
+      <c r="A87" s="35"/>
+      <c r="B87" s="36"/>
+      <c r="C87" s="37"/>
+      <c r="D87" s="37"/>
+      <c r="E87" s="36"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="34"/>
-      <c r="B88" s="34"/>
-      <c r="C88" s="35"/>
-      <c r="D88" s="35"/>
-      <c r="E88" s="34"/>
+      <c r="A88" s="35"/>
+      <c r="B88" s="36"/>
+      <c r="C88" s="37"/>
+      <c r="D88" s="37"/>
+      <c r="E88" s="36"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="34"/>
-      <c r="B89" s="34"/>
-      <c r="C89" s="35"/>
-      <c r="D89" s="35"/>
-      <c r="E89" s="34"/>
+      <c r="A89" s="35"/>
+      <c r="B89" s="36"/>
+      <c r="C89" s="37"/>
+      <c r="D89" s="37"/>
+      <c r="E89" s="36"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="34"/>
-      <c r="B90" s="34"/>
-      <c r="C90" s="35"/>
-      <c r="D90" s="35"/>
-      <c r="E90" s="34"/>
+      <c r="A90" s="35"/>
+      <c r="B90" s="36"/>
+      <c r="C90" s="37"/>
+      <c r="D90" s="37"/>
+      <c r="E90" s="36"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="34"/>
-      <c r="B91" s="34"/>
-      <c r="C91" s="35"/>
-      <c r="D91" s="35"/>
-      <c r="E91" s="34"/>
+      <c r="A91" s="35"/>
+      <c r="B91" s="36"/>
+      <c r="C91" s="37"/>
+      <c r="D91" s="37"/>
+      <c r="E91" s="36"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="34"/>
-      <c r="B92" s="34"/>
-      <c r="C92" s="35"/>
-      <c r="D92" s="35"/>
-      <c r="E92" s="34"/>
+      <c r="A92" s="35"/>
+      <c r="B92" s="36"/>
+      <c r="C92" s="37"/>
+      <c r="D92" s="37"/>
+      <c r="E92" s="36"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="34"/>
-      <c r="B93" s="34"/>
-      <c r="C93" s="35"/>
-      <c r="D93" s="35"/>
-      <c r="E93" s="34"/>
+      <c r="A93" s="35"/>
+      <c r="B93" s="36"/>
+      <c r="C93" s="37"/>
+      <c r="D93" s="37"/>
+      <c r="E93" s="36"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="34"/>
-      <c r="B94" s="34"/>
-      <c r="C94" s="35"/>
-      <c r="D94" s="35"/>
-      <c r="E94" s="34"/>
+      <c r="A94" s="35"/>
+      <c r="B94" s="36"/>
+      <c r="C94" s="37"/>
+      <c r="D94" s="37"/>
+      <c r="E94" s="36"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="34"/>
-      <c r="B95" s="34"/>
-      <c r="C95" s="35"/>
-      <c r="D95" s="35"/>
-      <c r="E95" s="34"/>
+      <c r="A95" s="35"/>
+      <c r="B95" s="36"/>
+      <c r="C95" s="37"/>
+      <c r="D95" s="37"/>
+      <c r="E95" s="36"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="34"/>
-      <c r="B96" s="34"/>
-      <c r="C96" s="35"/>
-      <c r="D96" s="35"/>
-      <c r="E96" s="34"/>
+      <c r="A96" s="35"/>
+      <c r="B96" s="36"/>
+      <c r="C96" s="37"/>
+      <c r="D96" s="37"/>
+      <c r="E96" s="36"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="34"/>
-      <c r="B97" s="34"/>
-      <c r="C97" s="35"/>
-      <c r="D97" s="35"/>
-      <c r="E97" s="34"/>
+      <c r="A97" s="35"/>
+      <c r="B97" s="36"/>
+      <c r="C97" s="37"/>
+      <c r="D97" s="37"/>
+      <c r="E97" s="36"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="34"/>
-      <c r="B98" s="34"/>
-      <c r="C98" s="35"/>
-      <c r="D98" s="35"/>
-      <c r="E98" s="34"/>
+      <c r="A98" s="35"/>
+      <c r="B98" s="36"/>
+      <c r="C98" s="37"/>
+      <c r="D98" s="37"/>
+      <c r="E98" s="36"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="34"/>
-      <c r="B99" s="34"/>
-      <c r="C99" s="35"/>
-      <c r="D99" s="35"/>
-      <c r="E99" s="34"/>
+      <c r="A99" s="35"/>
+      <c r="B99" s="36"/>
+      <c r="C99" s="37"/>
+      <c r="D99" s="37"/>
+      <c r="E99" s="36"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="34"/>
-      <c r="B100" s="34"/>
-      <c r="C100" s="35"/>
-      <c r="D100" s="35"/>
-      <c r="E100" s="34"/>
+      <c r="A100" s="35"/>
+      <c r="B100" s="36"/>
+      <c r="C100" s="37"/>
+      <c r="D100" s="37"/>
+      <c r="E100" s="36"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="34"/>
-      <c r="B101" s="34"/>
-      <c r="C101" s="35"/>
-      <c r="D101" s="35"/>
-      <c r="E101" s="34"/>
+      <c r="A101" s="35"/>
+      <c r="B101" s="36"/>
+      <c r="C101" s="37"/>
+      <c r="D101" s="37"/>
+      <c r="E101" s="36"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="34"/>
-      <c r="B102" s="34"/>
-      <c r="C102" s="35"/>
-      <c r="D102" s="35"/>
-      <c r="E102" s="34"/>
+      <c r="A102" s="35"/>
+      <c r="B102" s="36"/>
+      <c r="C102" s="37"/>
+      <c r="D102" s="37"/>
+      <c r="E102" s="36"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="34"/>
-      <c r="B103" s="34"/>
-      <c r="C103" s="35"/>
-      <c r="D103" s="35"/>
-      <c r="E103" s="34"/>
+      <c r="A103" s="35"/>
+      <c r="B103" s="36"/>
+      <c r="C103" s="37"/>
+      <c r="D103" s="37"/>
+      <c r="E103" s="36"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="34"/>
-      <c r="B104" s="34"/>
-      <c r="C104" s="35"/>
-      <c r="D104" s="35"/>
-      <c r="E104" s="34"/>
+      <c r="A104" s="35"/>
+      <c r="B104" s="36"/>
+      <c r="C104" s="37"/>
+      <c r="D104" s="37"/>
+      <c r="E104" s="36"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="34"/>
-      <c r="B105" s="34"/>
-      <c r="C105" s="35"/>
-      <c r="D105" s="35"/>
-      <c r="E105" s="34"/>
+      <c r="A105" s="35"/>
+      <c r="B105" s="36"/>
+      <c r="C105" s="37"/>
+      <c r="D105" s="37"/>
+      <c r="E105" s="36"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="34"/>
-      <c r="B106" s="34"/>
-      <c r="C106" s="35"/>
-      <c r="D106" s="35"/>
-      <c r="E106" s="34"/>
+      <c r="A106" s="35"/>
+      <c r="B106" s="36"/>
+      <c r="C106" s="37"/>
+      <c r="D106" s="37"/>
+      <c r="E106" s="36"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="34"/>
-      <c r="B107" s="34"/>
-      <c r="C107" s="35"/>
-      <c r="D107" s="35"/>
-      <c r="E107" s="34"/>
+      <c r="A107" s="35"/>
+      <c r="B107" s="36"/>
+      <c r="C107" s="37"/>
+      <c r="D107" s="37"/>
+      <c r="E107" s="36"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="34"/>
-      <c r="B108" s="34"/>
-      <c r="C108" s="35"/>
-      <c r="D108" s="35"/>
-      <c r="E108" s="34"/>
+      <c r="A108" s="35"/>
+      <c r="B108" s="36"/>
+      <c r="C108" s="37"/>
+      <c r="D108" s="37"/>
+      <c r="E108" s="36"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="34"/>
-      <c r="B109" s="34"/>
-      <c r="C109" s="35"/>
-      <c r="D109" s="35"/>
-      <c r="E109" s="34"/>
+      <c r="A109" s="35"/>
+      <c r="B109" s="36"/>
+      <c r="C109" s="37"/>
+      <c r="D109" s="37"/>
+      <c r="E109" s="36"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="34"/>
-      <c r="B110" s="34"/>
-      <c r="C110" s="35"/>
-      <c r="D110" s="35"/>
-      <c r="E110" s="34"/>
+      <c r="A110" s="35"/>
+      <c r="B110" s="36"/>
+      <c r="C110" s="37"/>
+      <c r="D110" s="37"/>
+      <c r="E110" s="36"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="34"/>
-      <c r="B111" s="34"/>
-      <c r="C111" s="35"/>
-      <c r="D111" s="35"/>
-      <c r="E111" s="34"/>
+      <c r="A111" s="35"/>
+      <c r="B111" s="36"/>
+      <c r="C111" s="37"/>
+      <c r="D111" s="37"/>
+      <c r="E111" s="36"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="34"/>
-      <c r="B112" s="34"/>
-      <c r="C112" s="35"/>
-      <c r="D112" s="35"/>
-      <c r="E112" s="34"/>
+      <c r="A112" s="35"/>
+      <c r="B112" s="36"/>
+      <c r="C112" s="37"/>
+      <c r="D112" s="37"/>
+      <c r="E112" s="36"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="34"/>
-      <c r="B113" s="34"/>
-      <c r="C113" s="35"/>
-      <c r="D113" s="35"/>
-      <c r="E113" s="34"/>
+      <c r="A113" s="35"/>
+      <c r="B113" s="36"/>
+      <c r="C113" s="37"/>
+      <c r="D113" s="37"/>
+      <c r="E113" s="36"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="34"/>
-      <c r="B114" s="34"/>
-      <c r="C114" s="35"/>
-      <c r="D114" s="35"/>
-      <c r="E114" s="34"/>
+      <c r="A114" s="35"/>
+      <c r="B114" s="36"/>
+      <c r="C114" s="37"/>
+      <c r="D114" s="37"/>
+      <c r="E114" s="36"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="34"/>
-      <c r="B115" s="34"/>
-      <c r="C115" s="35"/>
-      <c r="D115" s="35"/>
-      <c r="E115" s="34"/>
+      <c r="A115" s="35"/>
+      <c r="B115" s="36"/>
+      <c r="C115" s="37"/>
+      <c r="D115" s="37"/>
+      <c r="E115" s="36"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="34"/>
-      <c r="B116" s="34"/>
-      <c r="C116" s="35"/>
-      <c r="D116" s="35"/>
-      <c r="E116" s="34"/>
+      <c r="A116" s="35"/>
+      <c r="B116" s="36"/>
+      <c r="C116" s="37"/>
+      <c r="D116" s="37"/>
+      <c r="E116" s="36"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="34"/>
-      <c r="B117" s="34"/>
-      <c r="C117" s="35"/>
-      <c r="D117" s="35"/>
-      <c r="E117" s="34"/>
+      <c r="A117" s="35"/>
+      <c r="B117" s="36"/>
+      <c r="C117" s="37"/>
+      <c r="D117" s="37"/>
+      <c r="E117" s="36"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="34"/>
-      <c r="B118" s="34"/>
-      <c r="C118" s="35"/>
-      <c r="D118" s="35"/>
-      <c r="E118" s="34"/>
+      <c r="A118" s="35"/>
+      <c r="B118" s="36"/>
+      <c r="C118" s="37"/>
+      <c r="D118" s="37"/>
+      <c r="E118" s="36"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="34"/>
-      <c r="B119" s="34"/>
-      <c r="C119" s="35"/>
-      <c r="D119" s="35"/>
-      <c r="E119" s="34"/>
+      <c r="A119" s="35"/>
+      <c r="B119" s="36"/>
+      <c r="C119" s="37"/>
+      <c r="D119" s="37"/>
+      <c r="E119" s="36"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="34"/>
-      <c r="B120" s="34"/>
-      <c r="C120" s="35"/>
-      <c r="D120" s="35"/>
-      <c r="E120" s="34"/>
+      <c r="A120" s="35"/>
+      <c r="B120" s="36"/>
+      <c r="C120" s="37"/>
+      <c r="D120" s="37"/>
+      <c r="E120" s="36"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="34"/>
-      <c r="B121" s="34"/>
-      <c r="C121" s="35"/>
-      <c r="D121" s="35"/>
-      <c r="E121" s="34"/>
+      <c r="A121" s="35"/>
+      <c r="B121" s="36"/>
+      <c r="C121" s="37"/>
+      <c r="D121" s="37"/>
+      <c r="E121" s="36"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="34"/>
-      <c r="B122" s="34"/>
-      <c r="C122" s="35"/>
-      <c r="D122" s="35"/>
-      <c r="E122" s="34"/>
+      <c r="A122" s="35"/>
+      <c r="B122" s="36"/>
+      <c r="C122" s="37"/>
+      <c r="D122" s="37"/>
+      <c r="E122" s="36"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="34"/>
-      <c r="B123" s="34"/>
-      <c r="C123" s="35"/>
-      <c r="D123" s="35"/>
-      <c r="E123" s="34"/>
+      <c r="A123" s="35"/>
+      <c r="B123" s="36"/>
+      <c r="C123" s="37"/>
+      <c r="D123" s="37"/>
+      <c r="E123" s="36"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="34"/>
-      <c r="B124" s="34"/>
-      <c r="C124" s="35"/>
-      <c r="D124" s="35"/>
-      <c r="E124" s="34"/>
+      <c r="A124" s="35"/>
+      <c r="B124" s="36"/>
+      <c r="C124" s="37"/>
+      <c r="D124" s="37"/>
+      <c r="E124" s="36"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="34"/>
-      <c r="B125" s="34"/>
-      <c r="C125" s="35"/>
-      <c r="D125" s="35"/>
-      <c r="E125" s="34"/>
+      <c r="A125" s="35"/>
+      <c r="B125" s="36"/>
+      <c r="C125" s="37"/>
+      <c r="D125" s="37"/>
+      <c r="E125" s="36"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="34"/>
-      <c r="B126" s="34"/>
-      <c r="C126" s="35"/>
-      <c r="D126" s="35"/>
-      <c r="E126" s="34"/>
+      <c r="A126" s="35"/>
+      <c r="B126" s="36"/>
+      <c r="C126" s="37"/>
+      <c r="D126" s="37"/>
+      <c r="E126" s="36"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="34"/>
-      <c r="B127" s="34"/>
-      <c r="C127" s="35"/>
-      <c r="D127" s="35"/>
-      <c r="E127" s="34"/>
+      <c r="A127" s="35"/>
+      <c r="B127" s="36"/>
+      <c r="C127" s="37"/>
+      <c r="D127" s="37"/>
+      <c r="E127" s="36"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="34"/>
-      <c r="B128" s="34"/>
-      <c r="C128" s="35"/>
-      <c r="D128" s="35"/>
-      <c r="E128" s="34"/>
+      <c r="A128" s="35"/>
+      <c r="B128" s="36"/>
+      <c r="C128" s="37"/>
+      <c r="D128" s="37"/>
+      <c r="E128" s="36"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="34"/>
-      <c r="B129" s="34"/>
-      <c r="C129" s="35"/>
-      <c r="D129" s="35"/>
-      <c r="E129" s="34"/>
+      <c r="A129" s="35"/>
+      <c r="B129" s="36"/>
+      <c r="C129" s="37"/>
+      <c r="D129" s="37"/>
+      <c r="E129" s="36"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="34"/>
-      <c r="B130" s="34"/>
-      <c r="C130" s="35"/>
-      <c r="D130" s="35"/>
-      <c r="E130" s="34"/>
+      <c r="A130" s="35"/>
+      <c r="B130" s="36"/>
+      <c r="C130" s="37"/>
+      <c r="D130" s="37"/>
+      <c r="E130" s="36"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="34"/>
-      <c r="B131" s="34"/>
-      <c r="C131" s="35"/>
-      <c r="D131" s="35"/>
-      <c r="E131" s="34"/>
+      <c r="A131" s="35"/>
+      <c r="B131" s="36"/>
+      <c r="C131" s="37"/>
+      <c r="D131" s="37"/>
+      <c r="E131" s="36"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="34"/>
-      <c r="B132" s="34"/>
-      <c r="C132" s="35"/>
-      <c r="D132" s="35"/>
-      <c r="E132" s="34"/>
+      <c r="A132" s="35"/>
+      <c r="B132" s="36"/>
+      <c r="C132" s="37"/>
+      <c r="D132" s="37"/>
+      <c r="E132" s="36"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="34"/>
-      <c r="B133" s="34"/>
-      <c r="C133" s="35"/>
-      <c r="D133" s="35"/>
-      <c r="E133" s="34"/>
+      <c r="A133" s="35"/>
+      <c r="B133" s="36"/>
+      <c r="C133" s="37"/>
+      <c r="D133" s="37"/>
+      <c r="E133" s="36"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="34"/>
-      <c r="B134" s="34"/>
-      <c r="C134" s="35"/>
-      <c r="D134" s="35"/>
-      <c r="E134" s="34"/>
+      <c r="A134" s="35"/>
+      <c r="B134" s="36"/>
+      <c r="C134" s="37"/>
+      <c r="D134" s="37"/>
+      <c r="E134" s="36"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="34"/>
-      <c r="B135" s="34"/>
-      <c r="C135" s="35"/>
-      <c r="D135" s="35"/>
-      <c r="E135" s="34"/>
+      <c r="A135" s="35"/>
+      <c r="B135" s="36"/>
+      <c r="C135" s="37"/>
+      <c r="D135" s="37"/>
+      <c r="E135" s="36"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="34"/>
-      <c r="B136" s="34"/>
-      <c r="C136" s="35"/>
-      <c r="D136" s="35"/>
-      <c r="E136" s="34"/>
+      <c r="A136" s="35"/>
+      <c r="B136" s="36"/>
+      <c r="C136" s="37"/>
+      <c r="D136" s="37"/>
+      <c r="E136" s="36"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="34"/>
-      <c r="B137" s="34"/>
-      <c r="C137" s="35"/>
-      <c r="D137" s="35"/>
-      <c r="E137" s="34"/>
+      <c r="A137" s="35"/>
+      <c r="B137" s="36"/>
+      <c r="C137" s="37"/>
+      <c r="D137" s="37"/>
+      <c r="E137" s="36"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="34"/>
-      <c r="B138" s="34"/>
-      <c r="C138" s="35"/>
-      <c r="D138" s="35"/>
-      <c r="E138" s="34"/>
+      <c r="A138" s="35"/>
+      <c r="B138" s="36"/>
+      <c r="C138" s="37"/>
+      <c r="D138" s="37"/>
+      <c r="E138" s="36"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="34"/>
-      <c r="B139" s="34"/>
-      <c r="C139" s="35"/>
-      <c r="D139" s="35"/>
-      <c r="E139" s="34"/>
+      <c r="A139" s="35"/>
+      <c r="B139" s="36"/>
+      <c r="C139" s="37"/>
+      <c r="D139" s="37"/>
+      <c r="E139" s="36"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="34"/>
-      <c r="B140" s="34"/>
-      <c r="C140" s="35"/>
-      <c r="D140" s="35"/>
-      <c r="E140" s="34"/>
+      <c r="A140" s="35"/>
+      <c r="B140" s="36"/>
+      <c r="C140" s="37"/>
+      <c r="D140" s="37"/>
+      <c r="E140" s="36"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="34"/>
-      <c r="B141" s="34"/>
-      <c r="C141" s="35"/>
-      <c r="D141" s="35"/>
-      <c r="E141" s="34"/>
+      <c r="A141" s="35"/>
+      <c r="B141" s="36"/>
+      <c r="C141" s="37"/>
+      <c r="D141" s="37"/>
+      <c r="E141" s="36"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="34"/>
-      <c r="B142" s="34"/>
-      <c r="C142" s="35"/>
-      <c r="D142" s="35"/>
-      <c r="E142" s="34"/>
+      <c r="A142" s="35"/>
+      <c r="B142" s="36"/>
+      <c r="C142" s="37"/>
+      <c r="D142" s="37"/>
+      <c r="E142" s="36"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="34"/>
-      <c r="B143" s="34"/>
-      <c r="C143" s="35"/>
-      <c r="D143" s="35"/>
-      <c r="E143" s="34"/>
+      <c r="A143" s="35"/>
+      <c r="B143" s="36"/>
+      <c r="C143" s="37"/>
+      <c r="D143" s="37"/>
+      <c r="E143" s="36"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="34"/>
-      <c r="B144" s="34"/>
-      <c r="C144" s="35"/>
-      <c r="D144" s="35"/>
-      <c r="E144" s="34"/>
+      <c r="A144" s="35"/>
+      <c r="B144" s="36"/>
+      <c r="C144" s="37"/>
+      <c r="D144" s="37"/>
+      <c r="E144" s="36"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="34"/>
-      <c r="B145" s="34"/>
-      <c r="C145" s="35"/>
-      <c r="D145" s="35"/>
-      <c r="E145" s="34"/>
+      <c r="A145" s="35"/>
+      <c r="B145" s="36"/>
+      <c r="C145" s="37"/>
+      <c r="D145" s="37"/>
+      <c r="E145" s="36"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="34"/>
-      <c r="B146" s="34"/>
-      <c r="C146" s="35"/>
-      <c r="D146" s="35"/>
-      <c r="E146" s="34"/>
+      <c r="A146" s="35"/>
+      <c r="B146" s="36"/>
+      <c r="C146" s="37"/>
+      <c r="D146" s="37"/>
+      <c r="E146" s="36"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="34"/>
-      <c r="B147" s="34"/>
-      <c r="C147" s="35"/>
-      <c r="D147" s="35"/>
-      <c r="E147" s="34"/>
+      <c r="A147" s="35"/>
+      <c r="B147" s="36"/>
+      <c r="C147" s="37"/>
+      <c r="D147" s="37"/>
+      <c r="E147" s="36"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="34"/>
-      <c r="B148" s="34"/>
-      <c r="C148" s="35"/>
-      <c r="D148" s="35"/>
-      <c r="E148" s="34"/>
+      <c r="A148" s="35"/>
+      <c r="B148" s="36"/>
+      <c r="C148" s="37"/>
+      <c r="D148" s="37"/>
+      <c r="E148" s="36"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="34"/>
-      <c r="B149" s="34"/>
-      <c r="C149" s="35"/>
-      <c r="D149" s="35"/>
-      <c r="E149" s="34"/>
+      <c r="A149" s="35"/>
+      <c r="B149" s="36"/>
+      <c r="C149" s="37"/>
+      <c r="D149" s="37"/>
+      <c r="E149" s="36"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="34"/>
-      <c r="B150" s="34"/>
-      <c r="C150" s="35"/>
-      <c r="D150" s="35"/>
-      <c r="E150" s="34"/>
+      <c r="A150" s="35"/>
+      <c r="B150" s="36"/>
+      <c r="C150" s="37"/>
+      <c r="D150" s="37"/>
+      <c r="E150" s="36"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="34"/>
-      <c r="B151" s="34"/>
-      <c r="C151" s="35"/>
-      <c r="D151" s="35"/>
-      <c r="E151" s="34"/>
+      <c r="A151" s="35"/>
+      <c r="B151" s="36"/>
+      <c r="C151" s="37"/>
+      <c r="D151" s="37"/>
+      <c r="E151" s="36"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="34"/>
-      <c r="B152" s="34"/>
-      <c r="C152" s="35"/>
-      <c r="D152" s="35"/>
-      <c r="E152" s="34"/>
+      <c r="A152" s="35"/>
+      <c r="B152" s="36"/>
+      <c r="C152" s="37"/>
+      <c r="D152" s="37"/>
+      <c r="E152" s="36"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="34"/>
-      <c r="B153" s="34"/>
-      <c r="C153" s="35"/>
-      <c r="D153" s="35"/>
-      <c r="E153" s="34"/>
+      <c r="A153" s="35"/>
+      <c r="B153" s="36"/>
+      <c r="C153" s="37"/>
+      <c r="D153" s="37"/>
+      <c r="E153" s="36"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="34"/>
-      <c r="B154" s="34"/>
-      <c r="C154" s="35"/>
-      <c r="D154" s="35"/>
-      <c r="E154" s="34"/>
+      <c r="A154" s="35"/>
+      <c r="B154" s="36"/>
+      <c r="C154" s="37"/>
+      <c r="D154" s="37"/>
+      <c r="E154" s="36"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="34"/>
-      <c r="B155" s="34"/>
-      <c r="C155" s="35"/>
-      <c r="D155" s="35"/>
-      <c r="E155" s="34"/>
+      <c r="A155" s="35"/>
+      <c r="B155" s="36"/>
+      <c r="C155" s="37"/>
+      <c r="D155" s="37"/>
+      <c r="E155" s="36"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="34"/>
-      <c r="B156" s="34"/>
-      <c r="C156" s="35"/>
-      <c r="D156" s="35"/>
-      <c r="E156" s="34"/>
+      <c r="A156" s="35"/>
+      <c r="B156" s="36"/>
+      <c r="C156" s="37"/>
+      <c r="D156" s="37"/>
+      <c r="E156" s="36"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="34"/>
-      <c r="B157" s="34"/>
-      <c r="C157" s="35"/>
-      <c r="D157" s="35"/>
-      <c r="E157" s="34"/>
+      <c r="A157" s="35"/>
+      <c r="B157" s="36"/>
+      <c r="C157" s="37"/>
+      <c r="D157" s="37"/>
+      <c r="E157" s="36"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="34"/>
-      <c r="B158" s="34"/>
-      <c r="C158" s="35"/>
-      <c r="D158" s="35"/>
-      <c r="E158" s="34"/>
+      <c r="A158" s="35"/>
+      <c r="B158" s="36"/>
+      <c r="C158" s="37"/>
+      <c r="D158" s="37"/>
+      <c r="E158" s="36"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="34"/>
-      <c r="B159" s="34"/>
-      <c r="C159" s="35"/>
-      <c r="D159" s="35"/>
-      <c r="E159" s="34"/>
+      <c r="A159" s="35"/>
+      <c r="B159" s="36"/>
+      <c r="C159" s="37"/>
+      <c r="D159" s="37"/>
+      <c r="E159" s="36"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="34"/>
-      <c r="B160" s="34"/>
-      <c r="C160" s="35"/>
-      <c r="D160" s="35"/>
-      <c r="E160" s="34"/>
+      <c r="A160" s="35"/>
+      <c r="B160" s="36"/>
+      <c r="C160" s="37"/>
+      <c r="D160" s="37"/>
+      <c r="E160" s="36"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="34"/>
-      <c r="B161" s="34"/>
-      <c r="C161" s="35"/>
-      <c r="D161" s="35"/>
-      <c r="E161" s="34"/>
+      <c r="A161" s="35"/>
+      <c r="B161" s="36"/>
+      <c r="C161" s="37"/>
+      <c r="D161" s="37"/>
+      <c r="E161" s="36"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="34"/>
-      <c r="B162" s="34"/>
-      <c r="C162" s="35"/>
-      <c r="D162" s="35"/>
-      <c r="E162" s="34"/>
+      <c r="A162" s="35"/>
+      <c r="B162" s="36"/>
+      <c r="C162" s="37"/>
+      <c r="D162" s="37"/>
+      <c r="E162" s="36"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="34"/>
-      <c r="B163" s="34"/>
-      <c r="C163" s="35"/>
-      <c r="D163" s="35"/>
-      <c r="E163" s="34"/>
+      <c r="A163" s="35"/>
+      <c r="B163" s="36"/>
+      <c r="C163" s="37"/>
+      <c r="D163" s="37"/>
+      <c r="E163" s="36"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="34"/>
-      <c r="B164" s="34"/>
-      <c r="C164" s="35"/>
-      <c r="D164" s="35"/>
-      <c r="E164" s="34"/>
+      <c r="A164" s="35"/>
+      <c r="B164" s="36"/>
+      <c r="C164" s="37"/>
+      <c r="D164" s="37"/>
+      <c r="E164" s="36"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="34"/>
-      <c r="B165" s="34"/>
-      <c r="C165" s="35"/>
-      <c r="D165" s="35"/>
-      <c r="E165" s="34"/>
+      <c r="A165" s="35"/>
+      <c r="B165" s="36"/>
+      <c r="C165" s="37"/>
+      <c r="D165" s="37"/>
+      <c r="E165" s="36"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="34"/>
-      <c r="B166" s="34"/>
-      <c r="C166" s="35"/>
-      <c r="D166" s="35"/>
-      <c r="E166" s="34"/>
+      <c r="A166" s="35"/>
+      <c r="B166" s="36"/>
+      <c r="C166" s="37"/>
+      <c r="D166" s="37"/>
+      <c r="E166" s="36"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="34"/>
-      <c r="B167" s="34"/>
-      <c r="C167" s="35"/>
-      <c r="D167" s="35"/>
-      <c r="E167" s="34"/>
+      <c r="A167" s="35"/>
+      <c r="B167" s="36"/>
+      <c r="C167" s="37"/>
+      <c r="D167" s="37"/>
+      <c r="E167" s="36"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="34"/>
-      <c r="B168" s="34"/>
-      <c r="C168" s="35"/>
-      <c r="D168" s="35"/>
-      <c r="E168" s="34"/>
+      <c r="A168" s="35"/>
+      <c r="B168" s="36"/>
+      <c r="C168" s="37"/>
+      <c r="D168" s="37"/>
+      <c r="E168" s="36"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="34"/>
-      <c r="B169" s="34"/>
-      <c r="C169" s="35"/>
-      <c r="D169" s="35"/>
-      <c r="E169" s="34"/>
+      <c r="A169" s="35"/>
+      <c r="B169" s="36"/>
+      <c r="C169" s="37"/>
+      <c r="D169" s="37"/>
+      <c r="E169" s="36"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="34"/>
-      <c r="B170" s="34"/>
-      <c r="C170" s="35"/>
-      <c r="D170" s="35"/>
-      <c r="E170" s="34"/>
+      <c r="A170" s="35"/>
+      <c r="B170" s="36"/>
+      <c r="C170" s="37"/>
+      <c r="D170" s="37"/>
+      <c r="E170" s="36"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="34"/>
-      <c r="B171" s="34"/>
-      <c r="C171" s="35"/>
-      <c r="D171" s="35"/>
-      <c r="E171" s="34"/>
+      <c r="A171" s="35"/>
+      <c r="B171" s="36"/>
+      <c r="C171" s="37"/>
+      <c r="D171" s="37"/>
+      <c r="E171" s="36"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="34"/>
-      <c r="B172" s="34"/>
-      <c r="C172" s="35"/>
-      <c r="D172" s="35"/>
-      <c r="E172" s="34"/>
+      <c r="A172" s="35"/>
+      <c r="B172" s="36"/>
+      <c r="C172" s="37"/>
+      <c r="D172" s="37"/>
+      <c r="E172" s="36"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="34"/>
-      <c r="B173" s="34"/>
-      <c r="C173" s="35"/>
-      <c r="D173" s="35"/>
-      <c r="E173" s="34"/>
+      <c r="A173" s="35"/>
+      <c r="B173" s="36"/>
+      <c r="C173" s="37"/>
+      <c r="D173" s="37"/>
+      <c r="E173" s="36"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="34"/>
-      <c r="B174" s="34"/>
-      <c r="C174" s="35"/>
-      <c r="D174" s="35"/>
-      <c r="E174" s="34"/>
+      <c r="A174" s="35"/>
+      <c r="B174" s="36"/>
+      <c r="C174" s="37"/>
+      <c r="D174" s="37"/>
+      <c r="E174" s="36"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="34"/>
-      <c r="B175" s="34"/>
-      <c r="C175" s="35"/>
-      <c r="D175" s="35"/>
-      <c r="E175" s="34"/>
+      <c r="A175" s="35"/>
+      <c r="B175" s="36"/>
+      <c r="C175" s="37"/>
+      <c r="D175" s="37"/>
+      <c r="E175" s="36"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="34"/>
-      <c r="B176" s="34"/>
-      <c r="C176" s="35"/>
-      <c r="D176" s="35"/>
-      <c r="E176" s="34"/>
+      <c r="A176" s="35"/>
+      <c r="B176" s="36"/>
+      <c r="C176" s="37"/>
+      <c r="D176" s="37"/>
+      <c r="E176" s="36"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="34"/>
-      <c r="B177" s="34"/>
-      <c r="C177" s="35"/>
-      <c r="D177" s="35"/>
-      <c r="E177" s="34"/>
+      <c r="A177" s="35"/>
+      <c r="B177" s="36"/>
+      <c r="C177" s="37"/>
+      <c r="D177" s="37"/>
+      <c r="E177" s="36"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="34"/>
-      <c r="B178" s="34"/>
-      <c r="C178" s="35"/>
-      <c r="D178" s="35"/>
-      <c r="E178" s="34"/>
+      <c r="A178" s="35"/>
+      <c r="B178" s="36"/>
+      <c r="C178" s="37"/>
+      <c r="D178" s="37"/>
+      <c r="E178" s="36"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="34"/>
-      <c r="B179" s="34"/>
-      <c r="C179" s="35"/>
-      <c r="D179" s="35"/>
-      <c r="E179" s="34"/>
+      <c r="A179" s="35"/>
+      <c r="B179" s="36"/>
+      <c r="C179" s="37"/>
+      <c r="D179" s="37"/>
+      <c r="E179" s="36"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="34"/>
-      <c r="B180" s="34"/>
-      <c r="C180" s="35"/>
-      <c r="D180" s="35"/>
-      <c r="E180" s="34"/>
+      <c r="A180" s="35"/>
+      <c r="B180" s="36"/>
+      <c r="C180" s="37"/>
+      <c r="D180" s="37"/>
+      <c r="E180" s="36"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="34"/>
-      <c r="B181" s="34"/>
-      <c r="C181" s="35"/>
-      <c r="D181" s="35"/>
-      <c r="E181" s="34"/>
+      <c r="A181" s="35"/>
+      <c r="B181" s="36"/>
+      <c r="C181" s="37"/>
+      <c r="D181" s="37"/>
+      <c r="E181" s="36"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="34"/>
-      <c r="B182" s="34"/>
-      <c r="C182" s="35"/>
-      <c r="D182" s="35"/>
-      <c r="E182" s="34"/>
+      <c r="A182" s="35"/>
+      <c r="B182" s="36"/>
+      <c r="C182" s="37"/>
+      <c r="D182" s="37"/>
+      <c r="E182" s="36"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="34"/>
-      <c r="B183" s="34"/>
-      <c r="C183" s="35"/>
-      <c r="D183" s="35"/>
-      <c r="E183" s="34"/>
+      <c r="A183" s="35"/>
+      <c r="B183" s="36"/>
+      <c r="C183" s="37"/>
+      <c r="D183" s="37"/>
+      <c r="E183" s="36"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="34"/>
-      <c r="B184" s="34"/>
-      <c r="C184" s="35"/>
-      <c r="D184" s="35"/>
-      <c r="E184" s="34"/>
+      <c r="A184" s="35"/>
+      <c r="B184" s="36"/>
+      <c r="C184" s="37"/>
+      <c r="D184" s="37"/>
+      <c r="E184" s="36"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="34"/>
-      <c r="B185" s="34"/>
-      <c r="C185" s="35"/>
-      <c r="D185" s="35"/>
-      <c r="E185" s="34"/>
+      <c r="A185" s="35"/>
+      <c r="B185" s="36"/>
+      <c r="C185" s="37"/>
+      <c r="D185" s="37"/>
+      <c r="E185" s="36"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="34"/>
-      <c r="B186" s="34"/>
-      <c r="C186" s="35"/>
-      <c r="D186" s="35"/>
-      <c r="E186" s="34"/>
+      <c r="A186" s="35"/>
+      <c r="B186" s="36"/>
+      <c r="C186" s="37"/>
+      <c r="D186" s="37"/>
+      <c r="E186" s="36"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="34"/>
-      <c r="B187" s="34"/>
-      <c r="C187" s="35"/>
-      <c r="D187" s="35"/>
-      <c r="E187" s="34"/>
+      <c r="A187" s="35"/>
+      <c r="B187" s="36"/>
+      <c r="C187" s="37"/>
+      <c r="D187" s="37"/>
+      <c r="E187" s="36"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="34"/>
-      <c r="B188" s="34"/>
-      <c r="C188" s="35"/>
-      <c r="D188" s="35"/>
-      <c r="E188" s="34"/>
+      <c r="A188" s="35"/>
+      <c r="B188" s="36"/>
+      <c r="C188" s="37"/>
+      <c r="D188" s="37"/>
+      <c r="E188" s="36"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="34"/>
-      <c r="B189" s="34"/>
-      <c r="C189" s="35"/>
-      <c r="D189" s="35"/>
-      <c r="E189" s="34"/>
+      <c r="A189" s="35"/>
+      <c r="B189" s="36"/>
+      <c r="C189" s="37"/>
+      <c r="D189" s="37"/>
+      <c r="E189" s="36"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="34"/>
-      <c r="B190" s="34"/>
-      <c r="C190" s="35"/>
-      <c r="D190" s="35"/>
-      <c r="E190" s="34"/>
+      <c r="A190" s="35"/>
+      <c r="B190" s="36"/>
+      <c r="C190" s="37"/>
+      <c r="D190" s="37"/>
+      <c r="E190" s="36"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="34"/>
-      <c r="B191" s="34"/>
-      <c r="C191" s="35"/>
-      <c r="D191" s="35"/>
-      <c r="E191" s="34"/>
+      <c r="A191" s="35"/>
+      <c r="B191" s="36"/>
+      <c r="C191" s="37"/>
+      <c r="D191" s="37"/>
+      <c r="E191" s="36"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="34"/>
-      <c r="B192" s="34"/>
-      <c r="C192" s="35"/>
-      <c r="D192" s="35"/>
-      <c r="E192" s="34"/>
+      <c r="A192" s="35"/>
+      <c r="B192" s="36"/>
+      <c r="C192" s="37"/>
+      <c r="D192" s="37"/>
+      <c r="E192" s="36"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="34"/>
-      <c r="B193" s="34"/>
-      <c r="C193" s="35"/>
-      <c r="D193" s="35"/>
-      <c r="E193" s="34"/>
+      <c r="A193" s="35"/>
+      <c r="B193" s="36"/>
+      <c r="C193" s="37"/>
+      <c r="D193" s="37"/>
+      <c r="E193" s="36"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="34"/>
-      <c r="B194" s="34"/>
-      <c r="C194" s="35"/>
-      <c r="D194" s="35"/>
-      <c r="E194" s="34"/>
+      <c r="A194" s="35"/>
+      <c r="B194" s="36"/>
+      <c r="C194" s="37"/>
+      <c r="D194" s="37"/>
+      <c r="E194" s="36"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="34"/>
-      <c r="B195" s="34"/>
-      <c r="C195" s="35"/>
-      <c r="D195" s="35"/>
-      <c r="E195" s="34"/>
+      <c r="A195" s="35"/>
+      <c r="B195" s="36"/>
+      <c r="C195" s="37"/>
+      <c r="D195" s="37"/>
+      <c r="E195" s="36"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="34"/>
-      <c r="B196" s="34"/>
-      <c r="C196" s="35"/>
-      <c r="D196" s="35"/>
-      <c r="E196" s="34"/>
+      <c r="A196" s="35"/>
+      <c r="B196" s="36"/>
+      <c r="C196" s="37"/>
+      <c r="D196" s="37"/>
+      <c r="E196" s="36"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="34"/>
-      <c r="B197" s="34"/>
-      <c r="C197" s="35"/>
-      <c r="D197" s="35"/>
-      <c r="E197" s="34"/>
+      <c r="A197" s="35"/>
+      <c r="B197" s="36"/>
+      <c r="C197" s="37"/>
+      <c r="D197" s="37"/>
+      <c r="E197" s="36"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="34"/>
-      <c r="B198" s="34"/>
-      <c r="C198" s="35"/>
-      <c r="D198" s="35"/>
-      <c r="E198" s="34"/>
+      <c r="A198" s="35"/>
+      <c r="B198" s="36"/>
+      <c r="C198" s="37"/>
+      <c r="D198" s="37"/>
+      <c r="E198" s="36"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="34"/>
-      <c r="B199" s="34"/>
-      <c r="C199" s="35"/>
-      <c r="D199" s="35"/>
-      <c r="E199" s="34"/>
+      <c r="A199" s="35"/>
+      <c r="B199" s="36"/>
+      <c r="C199" s="37"/>
+      <c r="D199" s="37"/>
+      <c r="E199" s="36"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="34"/>
-      <c r="B200" s="34"/>
-      <c r="C200" s="35"/>
-      <c r="D200" s="35"/>
-      <c r="E200" s="34"/>
+      <c r="A200" s="35"/>
+      <c r="B200" s="36"/>
+      <c r="C200" s="37"/>
+      <c r="D200" s="37"/>
+      <c r="E200" s="36"/>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="34"/>
-      <c r="B201" s="34"/>
-      <c r="C201" s="35"/>
-      <c r="D201" s="35"/>
-      <c r="E201" s="34"/>
+      <c r="A201" s="35"/>
+      <c r="B201" s="36"/>
+      <c r="C201" s="37"/>
+      <c r="D201" s="37"/>
+      <c r="E201" s="36"/>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="34"/>
-      <c r="B202" s="34"/>
-      <c r="C202" s="35"/>
-      <c r="D202" s="35"/>
-      <c r="E202" s="34"/>
+      <c r="A202" s="35"/>
+      <c r="B202" s="36"/>
+      <c r="C202" s="37"/>
+      <c r="D202" s="37"/>
+      <c r="E202" s="36"/>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="34"/>
-      <c r="B203" s="34"/>
-      <c r="C203" s="35"/>
-      <c r="D203" s="35"/>
-      <c r="E203" s="34"/>
+      <c r="A203" s="35"/>
+      <c r="B203" s="36"/>
+      <c r="C203" s="37"/>
+      <c r="D203" s="37"/>
+      <c r="E203" s="36"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="34"/>
-      <c r="B204" s="34"/>
-      <c r="C204" s="35"/>
-      <c r="D204" s="35"/>
-      <c r="E204" s="34"/>
+      <c r="A204" s="35"/>
+      <c r="B204" s="36"/>
+      <c r="C204" s="37"/>
+      <c r="D204" s="37"/>
+      <c r="E204" s="36"/>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="34"/>
-      <c r="B205" s="34"/>
-      <c r="C205" s="35"/>
-      <c r="D205" s="35"/>
-      <c r="E205" s="34"/>
+      <c r="A205" s="35"/>
+      <c r="B205" s="36"/>
+      <c r="C205" s="37"/>
+      <c r="D205" s="37"/>
+      <c r="E205" s="36"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="34"/>
-      <c r="B206" s="34"/>
-      <c r="C206" s="35"/>
-      <c r="D206" s="35"/>
-      <c r="E206" s="34"/>
+      <c r="A206" s="35"/>
+      <c r="B206" s="36"/>
+      <c r="C206" s="37"/>
+      <c r="D206" s="37"/>
+      <c r="E206" s="36"/>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="34"/>
-      <c r="B207" s="34"/>
-      <c r="C207" s="35"/>
-      <c r="D207" s="35"/>
-      <c r="E207" s="34"/>
+      <c r="A207" s="35"/>
+      <c r="B207" s="36"/>
+      <c r="C207" s="37"/>
+      <c r="D207" s="37"/>
+      <c r="E207" s="36"/>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="34"/>
-      <c r="B208" s="34"/>
-      <c r="C208" s="35"/>
-      <c r="D208" s="35"/>
-      <c r="E208" s="34"/>
+      <c r="A208" s="35"/>
+      <c r="B208" s="36"/>
+      <c r="C208" s="37"/>
+      <c r="D208" s="37"/>
+      <c r="E208" s="36"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="34"/>
-      <c r="B209" s="34"/>
-      <c r="C209" s="35"/>
-      <c r="D209" s="35"/>
-      <c r="E209" s="34"/>
+      <c r="A209" s="35"/>
+      <c r="B209" s="36"/>
+      <c r="C209" s="37"/>
+      <c r="D209" s="37"/>
+      <c r="E209" s="36"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="34"/>
-      <c r="B210" s="34"/>
-      <c r="C210" s="35"/>
-      <c r="D210" s="35"/>
-      <c r="E210" s="34"/>
+      <c r="A210" s="35"/>
+      <c r="B210" s="36"/>
+      <c r="C210" s="37"/>
+      <c r="D210" s="37"/>
+      <c r="E210" s="36"/>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="34"/>
-      <c r="B211" s="34"/>
-      <c r="C211" s="35"/>
-      <c r="D211" s="35"/>
-      <c r="E211" s="34"/>
+      <c r="A211" s="35"/>
+      <c r="B211" s="36"/>
+      <c r="C211" s="37"/>
+      <c r="D211" s="37"/>
+      <c r="E211" s="36"/>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="34"/>
-      <c r="B212" s="34"/>
-      <c r="C212" s="35"/>
-      <c r="D212" s="35"/>
-      <c r="E212" s="34"/>
+      <c r="A212" s="35"/>
+      <c r="B212" s="36"/>
+      <c r="C212" s="37"/>
+      <c r="D212" s="37"/>
+      <c r="E212" s="36"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="34"/>
-      <c r="B213" s="34"/>
-      <c r="C213" s="35"/>
-      <c r="D213" s="35"/>
-      <c r="E213" s="34"/>
+      <c r="A213" s="35"/>
+      <c r="B213" s="36"/>
+      <c r="C213" s="37"/>
+      <c r="D213" s="37"/>
+      <c r="E213" s="36"/>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="34"/>
-      <c r="B214" s="34"/>
-      <c r="C214" s="35"/>
-      <c r="D214" s="35"/>
-      <c r="E214" s="34"/>
+      <c r="A214" s="35"/>
+      <c r="B214" s="36"/>
+      <c r="C214" s="37"/>
+      <c r="D214" s="37"/>
+      <c r="E214" s="36"/>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="34"/>
-      <c r="B215" s="34"/>
-      <c r="C215" s="35"/>
-      <c r="D215" s="35"/>
-      <c r="E215" s="34"/>
+      <c r="A215" s="35"/>
+      <c r="B215" s="36"/>
+      <c r="C215" s="37"/>
+      <c r="D215" s="37"/>
+      <c r="E215" s="36"/>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="34"/>
-      <c r="B216" s="34"/>
-      <c r="C216" s="35"/>
-      <c r="D216" s="35"/>
-      <c r="E216" s="34"/>
+      <c r="A216" s="35"/>
+      <c r="B216" s="36"/>
+      <c r="C216" s="37"/>
+      <c r="D216" s="37"/>
+      <c r="E216" s="36"/>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="34"/>
-      <c r="B217" s="34"/>
-      <c r="C217" s="35"/>
-      <c r="D217" s="35"/>
-      <c r="E217" s="34"/>
+      <c r="A217" s="35"/>
+      <c r="B217" s="36"/>
+      <c r="C217" s="37"/>
+      <c r="D217" s="37"/>
+      <c r="E217" s="36"/>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="34"/>
-      <c r="B218" s="34"/>
-      <c r="C218" s="35"/>
-      <c r="D218" s="35"/>
-      <c r="E218" s="34"/>
+      <c r="A218" s="35"/>
+      <c r="B218" s="36"/>
+      <c r="C218" s="37"/>
+      <c r="D218" s="37"/>
+      <c r="E218" s="36"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="34"/>
-      <c r="B219" s="34"/>
-      <c r="C219" s="35"/>
-      <c r="D219" s="35"/>
-      <c r="E219" s="34"/>
+      <c r="A219" s="35"/>
+      <c r="B219" s="36"/>
+      <c r="C219" s="37"/>
+      <c r="D219" s="37"/>
+      <c r="E219" s="36"/>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="34"/>
-      <c r="B220" s="34"/>
-      <c r="C220" s="35"/>
-      <c r="D220" s="35"/>
-      <c r="E220" s="34"/>
+      <c r="A220" s="35"/>
+      <c r="B220" s="36"/>
+      <c r="C220" s="37"/>
+      <c r="D220" s="37"/>
+      <c r="E220" s="36"/>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="34"/>
-      <c r="B221" s="34"/>
-      <c r="C221" s="35"/>
-      <c r="D221" s="35"/>
-      <c r="E221" s="34"/>
+      <c r="A221" s="35"/>
+      <c r="B221" s="36"/>
+      <c r="C221" s="37"/>
+      <c r="D221" s="37"/>
+      <c r="E221" s="36"/>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="34"/>
-      <c r="B222" s="34"/>
-      <c r="C222" s="35"/>
-      <c r="D222" s="35"/>
-      <c r="E222" s="34"/>
+      <c r="A222" s="35"/>
+      <c r="B222" s="36"/>
+      <c r="C222" s="37"/>
+      <c r="D222" s="37"/>
+      <c r="E222" s="36"/>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="34"/>
-      <c r="B223" s="34"/>
-      <c r="C223" s="35"/>
-      <c r="D223" s="35"/>
-      <c r="E223" s="34"/>
+      <c r="A223" s="35"/>
+      <c r="B223" s="36"/>
+      <c r="C223" s="37"/>
+      <c r="D223" s="37"/>
+      <c r="E223" s="36"/>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="34"/>
-      <c r="B224" s="34"/>
-      <c r="C224" s="35"/>
-      <c r="D224" s="35"/>
-      <c r="E224" s="34"/>
+      <c r="A224" s="35"/>
+      <c r="B224" s="36"/>
+      <c r="C224" s="37"/>
+      <c r="D224" s="37"/>
+      <c r="E224" s="36"/>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="34"/>
-      <c r="B225" s="34"/>
-      <c r="C225" s="35"/>
-      <c r="D225" s="35"/>
-      <c r="E225" s="34"/>
+      <c r="A225" s="35"/>
+      <c r="B225" s="36"/>
+      <c r="C225" s="37"/>
+      <c r="D225" s="37"/>
+      <c r="E225" s="36"/>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="34"/>
-      <c r="B226" s="34"/>
-      <c r="C226" s="35"/>
-      <c r="D226" s="35"/>
-      <c r="E226" s="34"/>
+      <c r="A226" s="35"/>
+      <c r="B226" s="36"/>
+      <c r="C226" s="37"/>
+      <c r="D226" s="37"/>
+      <c r="E226" s="36"/>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="34"/>
-      <c r="B227" s="34"/>
-      <c r="C227" s="35"/>
-      <c r="D227" s="35"/>
-      <c r="E227" s="34"/>
+      <c r="A227" s="35"/>
+      <c r="B227" s="36"/>
+      <c r="C227" s="37"/>
+      <c r="D227" s="37"/>
+      <c r="E227" s="36"/>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="34"/>
-      <c r="B228" s="34"/>
-      <c r="C228" s="35"/>
-      <c r="D228" s="35"/>
-      <c r="E228" s="34"/>
+      <c r="A228" s="35"/>
+      <c r="B228" s="36"/>
+      <c r="C228" s="37"/>
+      <c r="D228" s="37"/>
+      <c r="E228" s="36"/>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="34"/>
-      <c r="B229" s="34"/>
-      <c r="C229" s="35"/>
-      <c r="D229" s="35"/>
-      <c r="E229" s="34"/>
+      <c r="A229" s="35"/>
+      <c r="B229" s="36"/>
+      <c r="C229" s="37"/>
+      <c r="D229" s="37"/>
+      <c r="E229" s="36"/>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="34"/>
-      <c r="B230" s="34"/>
-      <c r="C230" s="35"/>
-      <c r="D230" s="35"/>
-      <c r="E230" s="34"/>
+      <c r="A230" s="35"/>
+      <c r="B230" s="36"/>
+      <c r="C230" s="37"/>
+      <c r="D230" s="37"/>
+      <c r="E230" s="36"/>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="34"/>
-      <c r="B231" s="34"/>
-      <c r="C231" s="35"/>
-      <c r="D231" s="35"/>
-      <c r="E231" s="34"/>
+      <c r="A231" s="35"/>
+      <c r="B231" s="36"/>
+      <c r="C231" s="37"/>
+      <c r="D231" s="37"/>
+      <c r="E231" s="36"/>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="34"/>
-      <c r="B232" s="34"/>
-      <c r="C232" s="35"/>
-      <c r="D232" s="35"/>
-      <c r="E232" s="34"/>
+      <c r="A232" s="35"/>
+      <c r="B232" s="36"/>
+      <c r="C232" s="37"/>
+      <c r="D232" s="37"/>
+      <c r="E232" s="36"/>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="34"/>
-      <c r="B233" s="34"/>
-      <c r="C233" s="35"/>
-      <c r="D233" s="35"/>
-      <c r="E233" s="34"/>
+      <c r="A233" s="35"/>
+      <c r="B233" s="36"/>
+      <c r="C233" s="37"/>
+      <c r="D233" s="37"/>
+      <c r="E233" s="36"/>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="34"/>
-      <c r="B234" s="34"/>
-      <c r="C234" s="35"/>
-      <c r="D234" s="35"/>
-      <c r="E234" s="34"/>
+      <c r="A234" s="35"/>
+      <c r="B234" s="36"/>
+      <c r="C234" s="37"/>
+      <c r="D234" s="37"/>
+      <c r="E234" s="36"/>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="34"/>
-      <c r="B235" s="34"/>
-      <c r="C235" s="35"/>
-      <c r="D235" s="35"/>
-      <c r="E235" s="34"/>
+      <c r="A235" s="35"/>
+      <c r="B235" s="36"/>
+      <c r="C235" s="37"/>
+      <c r="D235" s="37"/>
+      <c r="E235" s="36"/>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="34"/>
-      <c r="B236" s="34"/>
-      <c r="C236" s="35"/>
-      <c r="D236" s="35"/>
-      <c r="E236" s="34"/>
+      <c r="A236" s="35"/>
+      <c r="B236" s="36"/>
+      <c r="C236" s="37"/>
+      <c r="D236" s="37"/>
+      <c r="E236" s="36"/>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="34"/>
-      <c r="B237" s="34"/>
-      <c r="C237" s="35"/>
-      <c r="D237" s="35"/>
-      <c r="E237" s="34"/>
+      <c r="A237" s="35"/>
+      <c r="B237" s="36"/>
+      <c r="C237" s="37"/>
+      <c r="D237" s="37"/>
+      <c r="E237" s="36"/>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="34"/>
-      <c r="B238" s="34"/>
-      <c r="C238" s="35"/>
-      <c r="D238" s="35"/>
-      <c r="E238" s="34"/>
+      <c r="A238" s="35"/>
+      <c r="B238" s="36"/>
+      <c r="C238" s="37"/>
+      <c r="D238" s="37"/>
+      <c r="E238" s="36"/>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="34"/>
-      <c r="B239" s="34"/>
-      <c r="C239" s="35"/>
-      <c r="D239" s="35"/>
-      <c r="E239" s="34"/>
+      <c r="A239" s="35"/>
+      <c r="B239" s="36"/>
+      <c r="C239" s="37"/>
+      <c r="D239" s="37"/>
+      <c r="E239" s="36"/>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="34"/>
-      <c r="B240" s="34"/>
-      <c r="C240" s="35"/>
-      <c r="D240" s="35"/>
-      <c r="E240" s="34"/>
+      <c r="A240" s="35"/>
+      <c r="B240" s="36"/>
+      <c r="C240" s="37"/>
+      <c r="D240" s="37"/>
+      <c r="E240" s="36"/>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="34"/>
-      <c r="B241" s="34"/>
-      <c r="C241" s="35"/>
-      <c r="D241" s="35"/>
-      <c r="E241" s="34"/>
+      <c r="A241" s="35"/>
+      <c r="B241" s="36"/>
+      <c r="C241" s="37"/>
+      <c r="D241" s="37"/>
+      <c r="E241" s="36"/>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="34"/>
-      <c r="B242" s="34"/>
-      <c r="C242" s="35"/>
-      <c r="D242" s="35"/>
-      <c r="E242" s="34"/>
+      <c r="A242" s="35"/>
+      <c r="B242" s="36"/>
+      <c r="C242" s="37"/>
+      <c r="D242" s="37"/>
+      <c r="E242" s="36"/>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="34"/>
-      <c r="B243" s="34"/>
-      <c r="C243" s="35"/>
-      <c r="D243" s="35"/>
-      <c r="E243" s="34"/>
+      <c r="A243" s="35"/>
+      <c r="B243" s="36"/>
+      <c r="C243" s="37"/>
+      <c r="D243" s="37"/>
+      <c r="E243" s="36"/>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="34"/>
-      <c r="B244" s="34"/>
-      <c r="C244" s="35"/>
-      <c r="D244" s="35"/>
-      <c r="E244" s="34"/>
+      <c r="A244" s="35"/>
+      <c r="B244" s="36"/>
+      <c r="C244" s="37"/>
+      <c r="D244" s="37"/>
+      <c r="E244" s="36"/>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="34"/>
-      <c r="B245" s="34"/>
-      <c r="C245" s="35"/>
-      <c r="D245" s="35"/>
-      <c r="E245" s="34"/>
+      <c r="A245" s="35"/>
+      <c r="B245" s="36"/>
+      <c r="C245" s="37"/>
+      <c r="D245" s="37"/>
+      <c r="E245" s="36"/>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="34"/>
-      <c r="B246" s="34"/>
-      <c r="C246" s="35"/>
-      <c r="D246" s="35"/>
-      <c r="E246" s="34"/>
+      <c r="A246" s="35"/>
+      <c r="B246" s="36"/>
+      <c r="C246" s="37"/>
+      <c r="D246" s="37"/>
+      <c r="E246" s="36"/>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="34"/>
-      <c r="B247" s="34"/>
-      <c r="C247" s="35"/>
-      <c r="D247" s="35"/>
-      <c r="E247" s="34"/>
+      <c r="A247" s="35"/>
+      <c r="B247" s="36"/>
+      <c r="C247" s="37"/>
+      <c r="D247" s="37"/>
+      <c r="E247" s="36"/>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="34"/>
-      <c r="B248" s="34"/>
-      <c r="C248" s="35"/>
-      <c r="D248" s="35"/>
-      <c r="E248" s="34"/>
+      <c r="A248" s="35"/>
+      <c r="B248" s="36"/>
+      <c r="C248" s="37"/>
+      <c r="D248" s="37"/>
+      <c r="E248" s="36"/>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="34"/>
-      <c r="B249" s="34"/>
-      <c r="C249" s="35"/>
-      <c r="D249" s="35"/>
-      <c r="E249" s="34"/>
+      <c r="A249" s="35"/>
+      <c r="B249" s="36"/>
+      <c r="C249" s="37"/>
+      <c r="D249" s="37"/>
+      <c r="E249" s="36"/>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="34"/>
-      <c r="B250" s="34"/>
-      <c r="C250" s="35"/>
-      <c r="D250" s="35"/>
-      <c r="E250" s="34"/>
+      <c r="A250" s="35"/>
+      <c r="B250" s="36"/>
+      <c r="C250" s="37"/>
+      <c r="D250" s="37"/>
+      <c r="E250" s="36"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:E250"/>
-  <dataValidations count="2">
-    <dataValidation allowBlank="true" error="Pick an item from the dropdown so the entry reaches the Stock sheet." errorStyle="stop" errorTitle="Unknown item" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B7:B1020" type="list">
+  <dataValidations count="3">
+    <dataValidation allowBlank="true" error="Pick a product from the dropdown so the entry reaches the Stock sheet." errorStyle="stop" errorTitle="Unknown product" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B7:B1020" type="list">
       <formula1>Stock!$L$8:$L$49</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Slabs cannot be negative. Record a despatch in the Shipment column." errorStyle="stop" errorTitle="Negative quantity" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C7:D1020" type="decimal">
       <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Enter a real date such as 21/08/2026, not text." errorStyle="stop" errorTitle="Date required" operator="greaterThan" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="A7:A1020" type="date">
+      <formula1>DATE(2000,1,1)</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -5003,58 +5884,58 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>107</v>
+      <c r="A4" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="38" t="n">
+      <c r="A5" s="39" t="n">
         <f aca="false">Stock!$H$50</f>
         <v>107750</v>
       </c>
-      <c r="C5" s="39" t="str">
+      <c r="C5" s="40" t="str">
         <f aca="false">IF(Stock!$J$50="","—",Stock!$J$50)</f>
         <v>—</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>36</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B9" s="18" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A9,Stock!$C$8:$C$49)</f>
@@ -5079,7 +5960,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B10" s="26" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A10,Stock!$C$8:$C$49)</f>
@@ -5104,7 +5985,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B11" s="18" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A11,Stock!$C$8:$C$49)</f>
@@ -5129,7 +6010,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B12" s="26" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A12,Stock!$C$8:$C$49)</f>
@@ -5154,7 +6035,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B13" s="18" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A13,Stock!$C$8:$C$49)</f>
@@ -5179,7 +6060,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B14" s="26" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A14,Stock!$C$8:$C$49)</f>
@@ -5204,7 +6085,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B15" s="18" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A15,Stock!$C$8:$C$49)</f>
@@ -5229,7 +6110,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B16" s="26" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A16,Stock!$C$8:$C$49)</f>
@@ -5256,30 +6137,30 @@
       <c r="A17" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="B17" s="31" t="n">
+      <c r="B17" s="30" t="n">
         <f aca="false">SUM(B9:B16)</f>
         <v>102870</v>
       </c>
-      <c r="C17" s="32" t="n">
+      <c r="C17" s="31" t="n">
         <f aca="false">SUM(C9:C16)</f>
         <v>4880</v>
       </c>
-      <c r="D17" s="32" t="n">
+      <c r="D17" s="31" t="n">
         <f aca="false">SUM(D9:D16)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="31" t="n">
+      <c r="E17" s="30" t="n">
         <f aca="false">SUM(E9:E16)</f>
         <v>107750</v>
       </c>
-      <c r="F17" s="33" t="str">
+      <c r="F17" s="32" t="str">
         <f aca="false">IF(SUM(F9:F16)=0,"",SUM(F9:F16))</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -5291,4 +6172,992 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:H48"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B1" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="F1" s="42"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E2" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="F2" s="42"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E3" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="42"/>
+    </row>
+    <row r="4" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="43"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+    </row>
+    <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" s="45" t="n">
+        <f aca="false">Stock!$C$3</f>
+        <v>46254</v>
+      </c>
+      <c r="F5" s="45"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="E6" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="F6" s="47"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="48" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="48" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="E8" s="49" t="s">
+        <v>125</v>
+      </c>
+      <c r="F8" s="49"/>
+    </row>
+    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="50" t="n">
+        <f aca="false">Stock!$C$50</f>
+        <v>102870</v>
+      </c>
+      <c r="B9" s="51" t="n">
+        <f aca="false">Stock!$D$50</f>
+        <v>4880</v>
+      </c>
+      <c r="C9" s="51" t="n">
+        <f aca="false">Stock!$E$50</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="50" t="n">
+        <f aca="false">Stock!$H$50</f>
+        <v>107750</v>
+      </c>
+      <c r="E9" s="52" t="str">
+        <f aca="false">IF(Stock!$J$50="","Rate not entered",Stock!$J$50)</f>
+        <v>Rate not entered</v>
+      </c>
+      <c r="F9" s="52"/>
+    </row>
+    <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+    </row>
+    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="54" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="55" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="55" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="55" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="56" t="str">
+        <f aca="false">Summary!$A$9</f>
+        <v>Blue Dolphin</v>
+      </c>
+      <c r="B13" s="57" t="n">
+        <f aca="false">Summary!$B$9</f>
+        <v>28645</v>
+      </c>
+      <c r="C13" s="58" t="n">
+        <f aca="false">Summary!$C$9</f>
+        <v>1400</v>
+      </c>
+      <c r="D13" s="58" t="n">
+        <f aca="false">Summary!$D$9</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="59" t="n">
+        <f aca="false">Summary!$E$9</f>
+        <v>30045</v>
+      </c>
+      <c r="F13" s="60" t="str">
+        <f aca="false">Summary!$F$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="61" t="str">
+        <f aca="false">Summary!$A$10</f>
+        <v>Primus Japan</v>
+      </c>
+      <c r="B14" s="62" t="n">
+        <f aca="false">Summary!$B$10</f>
+        <v>29316</v>
+      </c>
+      <c r="C14" s="63" t="n">
+        <f aca="false">Summary!$C$10</f>
+        <v>956</v>
+      </c>
+      <c r="D14" s="63" t="n">
+        <f aca="false">Summary!$D$10</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="64" t="n">
+        <f aca="false">Summary!$E$10</f>
+        <v>30272</v>
+      </c>
+      <c r="F14" s="65" t="str">
+        <f aca="false">Summary!$F$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="56" t="str">
+        <f aca="false">Summary!$A$11</f>
+        <v>Primus EU</v>
+      </c>
+      <c r="B15" s="57" t="n">
+        <f aca="false">Summary!$B$11</f>
+        <v>26619</v>
+      </c>
+      <c r="C15" s="58" t="n">
+        <f aca="false">Summary!$C$11</f>
+        <v>52</v>
+      </c>
+      <c r="D15" s="58" t="n">
+        <f aca="false">Summary!$D$11</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="59" t="n">
+        <f aca="false">Summary!$E$11</f>
+        <v>26671</v>
+      </c>
+      <c r="F15" s="60" t="str">
+        <f aca="false">Summary!$F$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="61" t="str">
+        <f aca="false">Summary!$A$12</f>
+        <v>AMF Brand</v>
+      </c>
+      <c r="B16" s="62" t="n">
+        <f aca="false">Summary!$B$12</f>
+        <v>1534</v>
+      </c>
+      <c r="C16" s="63" t="n">
+        <f aca="false">Summary!$C$12</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="63" t="n">
+        <f aca="false">Summary!$D$12</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="64" t="n">
+        <f aca="false">Summary!$E$12</f>
+        <v>1534</v>
+      </c>
+      <c r="F16" s="65" t="str">
+        <f aca="false">Summary!$F$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="56" t="str">
+        <f aca="false">Summary!$A$13</f>
+        <v>THT Brand</v>
+      </c>
+      <c r="B17" s="57" t="n">
+        <f aca="false">Summary!$B$13</f>
+        <v>13126</v>
+      </c>
+      <c r="C17" s="58" t="n">
+        <f aca="false">Summary!$C$13</f>
+        <v>2472</v>
+      </c>
+      <c r="D17" s="58" t="n">
+        <f aca="false">Summary!$D$13</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="59" t="n">
+        <f aca="false">Summary!$E$13</f>
+        <v>15598</v>
+      </c>
+      <c r="F17" s="60" t="str">
+        <f aca="false">Summary!$F$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="61" t="str">
+        <f aca="false">Summary!$A$14</f>
+        <v>Deepsea</v>
+      </c>
+      <c r="B18" s="62" t="n">
+        <f aca="false">Summary!$B$14</f>
+        <v>670</v>
+      </c>
+      <c r="C18" s="63" t="n">
+        <f aca="false">Summary!$C$14</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="63" t="n">
+        <f aca="false">Summary!$D$14</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="64" t="n">
+        <f aca="false">Summary!$E$14</f>
+        <v>670</v>
+      </c>
+      <c r="F18" s="65" t="str">
+        <f aca="false">Summary!$F$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="56" t="str">
+        <f aca="false">Summary!$A$15</f>
+        <v>China</v>
+      </c>
+      <c r="B19" s="57" t="n">
+        <f aca="false">Summary!$B$15</f>
+        <v>2960</v>
+      </c>
+      <c r="C19" s="58" t="n">
+        <f aca="false">Summary!$C$15</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="58" t="n">
+        <f aca="false">Summary!$D$15</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="59" t="n">
+        <f aca="false">Summary!$E$15</f>
+        <v>2960</v>
+      </c>
+      <c r="F19" s="60" t="str">
+        <f aca="false">Summary!$F$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="61" t="str">
+        <f aca="false">Summary!$A$16</f>
+        <v>Shrimp Whole 5x3kgs</v>
+      </c>
+      <c r="B20" s="62" t="n">
+        <f aca="false">Summary!$B$16</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="63" t="n">
+        <f aca="false">Summary!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="63" t="n">
+        <f aca="false">Summary!$D$16</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="64" t="n">
+        <f aca="false">Summary!$E$16</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="65" t="str">
+        <f aca="false">Summary!$F$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="66" t="str">
+        <f aca="false">Summary!$A$17</f>
+        <v>GRAND TOTAL</v>
+      </c>
+      <c r="B21" s="67" t="n">
+        <f aca="false">Summary!$B$17</f>
+        <v>102870</v>
+      </c>
+      <c r="C21" s="68" t="n">
+        <f aca="false">Summary!$C$17</f>
+        <v>4880</v>
+      </c>
+      <c r="D21" s="68" t="n">
+        <f aca="false">Summary!$D$17</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="67" t="n">
+        <f aca="false">Summary!$E$17</f>
+        <v>107750</v>
+      </c>
+      <c r="F21" s="69" t="str">
+        <f aca="false">Summary!$F$17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="53" t="s">
+        <v>127</v>
+      </c>
+      <c r="B23" s="53"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+    </row>
+    <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="54" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="55" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="55" t="s">
+        <v>129</v>
+      </c>
+      <c r="E24" s="55" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="55"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="70" t="str">
+        <f aca="false">IF($H25="","",INDEX(Stock!$A$8:$A$49,$H25))</f>
+        <v>Blue Dolphin</v>
+      </c>
+      <c r="B25" s="70" t="str">
+        <f aca="false">IF($H25="","",INDEX(Stock!$B$8:$B$49,$H25))</f>
+        <v>PD PVN 100/200</v>
+      </c>
+      <c r="C25" s="71" t="n">
+        <f aca="false">IF($H25="","",INDEX(Stock!$D$8:$D$49,$H25))</f>
+        <v>1068</v>
+      </c>
+      <c r="D25" s="71" t="n">
+        <f aca="false">IF($H25="","",INDEX(Stock!$E$8:$E$49,$H25))</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="72" t="n">
+        <f aca="false">IF($H25="","",INDEX(Stock!$H$8:$H$49,$H25))</f>
+        <v>12527</v>
+      </c>
+      <c r="H25" s="73" t="n">
+        <f aca="false">IFERROR(MATCH(1,Stock!$N$8:$N$49,0),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="70" t="str">
+        <f aca="false">IF($H26="","",INDEX(Stock!$A$8:$A$49,$H26))</f>
+        <v>Blue Dolphin</v>
+      </c>
+      <c r="B26" s="70" t="str">
+        <f aca="false">IF($H26="","",INDEX(Stock!$B$8:$B$49,$H26))</f>
+        <v>PD KKD 100/200</v>
+      </c>
+      <c r="C26" s="71" t="n">
+        <f aca="false">IF($H26="","",INDEX(Stock!$D$8:$D$49,$H26))</f>
+        <v>65</v>
+      </c>
+      <c r="D26" s="71" t="n">
+        <f aca="false">IF($H26="","",INDEX(Stock!$E$8:$E$49,$H26))</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="72" t="n">
+        <f aca="false">IF($H26="","",INDEX(Stock!$H$8:$H$49,$H26))</f>
+        <v>582</v>
+      </c>
+      <c r="H26" s="73" t="n">
+        <f aca="false">IFERROR(MATCH(2,Stock!$N$8:$N$49,0),"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="70" t="str">
+        <f aca="false">IF($H27="","",INDEX(Stock!$A$8:$A$49,$H27))</f>
+        <v>Blue Dolphin</v>
+      </c>
+      <c r="B27" s="70" t="str">
+        <f aca="false">IF($H27="","",INDEX(Stock!$B$8:$B$49,$H27))</f>
+        <v>PUD PVN 200/300</v>
+      </c>
+      <c r="C27" s="71" t="n">
+        <f aca="false">IF($H27="","",INDEX(Stock!$D$8:$D$49,$H27))</f>
+        <v>267</v>
+      </c>
+      <c r="D27" s="71" t="n">
+        <f aca="false">IF($H27="","",INDEX(Stock!$E$8:$E$49,$H27))</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="72" t="n">
+        <f aca="false">IF($H27="","",INDEX(Stock!$H$8:$H$49,$H27))</f>
+        <v>2529</v>
+      </c>
+      <c r="H27" s="73" t="n">
+        <f aca="false">IFERROR(MATCH(3,Stock!$N$8:$N$49,0),"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="70" t="str">
+        <f aca="false">IF($H28="","",INDEX(Stock!$A$8:$A$49,$H28))</f>
+        <v>Primus Japan</v>
+      </c>
+      <c r="B28" s="70" t="str">
+        <f aca="false">IF($H28="","",INDEX(Stock!$B$8:$B$49,$H28))</f>
+        <v>PUD KZN 40/60</v>
+      </c>
+      <c r="C28" s="71" t="n">
+        <f aca="false">IF($H28="","",INDEX(Stock!$D$8:$D$49,$H28))</f>
+        <v>29</v>
+      </c>
+      <c r="D28" s="71" t="n">
+        <f aca="false">IF($H28="","",INDEX(Stock!$E$8:$E$49,$H28))</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="72" t="n">
+        <f aca="false">IF($H28="","",INDEX(Stock!$H$8:$H$49,$H28))</f>
+        <v>93</v>
+      </c>
+      <c r="H28" s="73" t="n">
+        <f aca="false">IFERROR(MATCH(4,Stock!$N$8:$N$49,0),"")</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="70" t="str">
+        <f aca="false">IF($H29="","",INDEX(Stock!$A$8:$A$49,$H29))</f>
+        <v>Primus Japan</v>
+      </c>
+      <c r="B29" s="70" t="str">
+        <f aca="false">IF($H29="","",INDEX(Stock!$B$8:$B$49,$H29))</f>
+        <v>PUD KZN 60/80</v>
+      </c>
+      <c r="C29" s="71" t="n">
+        <f aca="false">IF($H29="","",INDEX(Stock!$D$8:$D$49,$H29))</f>
+        <v>39</v>
+      </c>
+      <c r="D29" s="71" t="n">
+        <f aca="false">IF($H29="","",INDEX(Stock!$E$8:$E$49,$H29))</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="72" t="n">
+        <f aca="false">IF($H29="","",INDEX(Stock!$H$8:$H$49,$H29))</f>
+        <v>230</v>
+      </c>
+      <c r="H29" s="73" t="n">
+        <f aca="false">IFERROR(MATCH(5,Stock!$N$8:$N$49,0),"")</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="70" t="str">
+        <f aca="false">IF($H30="","",INDEX(Stock!$A$8:$A$49,$H30))</f>
+        <v>Primus Japan</v>
+      </c>
+      <c r="B30" s="70" t="str">
+        <f aca="false">IF($H30="","",INDEX(Stock!$B$8:$B$49,$H30))</f>
+        <v>PUD KZN 80/120</v>
+      </c>
+      <c r="C30" s="71" t="n">
+        <f aca="false">IF($H30="","",INDEX(Stock!$D$8:$D$49,$H30))</f>
+        <v>50</v>
+      </c>
+      <c r="D30" s="71" t="n">
+        <f aca="false">IF($H30="","",INDEX(Stock!$E$8:$E$49,$H30))</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="72" t="n">
+        <f aca="false">IF($H30="","",INDEX(Stock!$H$8:$H$49,$H30))</f>
+        <v>516</v>
+      </c>
+      <c r="H30" s="73" t="n">
+        <f aca="false">IFERROR(MATCH(6,Stock!$N$8:$N$49,0),"")</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="70" t="str">
+        <f aca="false">IF($H31="","",INDEX(Stock!$A$8:$A$49,$H31))</f>
+        <v>Primus Japan</v>
+      </c>
+      <c r="B31" s="70" t="str">
+        <f aca="false">IF($H31="","",INDEX(Stock!$B$8:$B$49,$H31))</f>
+        <v>PUD NRN 80/120</v>
+      </c>
+      <c r="C31" s="71" t="n">
+        <f aca="false">IF($H31="","",INDEX(Stock!$D$8:$D$49,$H31))</f>
+        <v>3</v>
+      </c>
+      <c r="D31" s="71" t="n">
+        <f aca="false">IF($H31="","",INDEX(Stock!$E$8:$E$49,$H31))</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="72" t="n">
+        <f aca="false">IF($H31="","",INDEX(Stock!$H$8:$H$49,$H31))</f>
+        <v>72</v>
+      </c>
+      <c r="H31" s="73" t="n">
+        <f aca="false">IFERROR(MATCH(7,Stock!$N$8:$N$49,0),"")</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="70" t="str">
+        <f aca="false">IF($H32="","",INDEX(Stock!$A$8:$A$49,$H32))</f>
+        <v>Primus Japan</v>
+      </c>
+      <c r="B32" s="70" t="str">
+        <f aca="false">IF($H32="","",INDEX(Stock!$B$8:$B$49,$H32))</f>
+        <v>PUD KZN 100/200</v>
+      </c>
+      <c r="C32" s="71" t="n">
+        <f aca="false">IF($H32="","",INDEX(Stock!$D$8:$D$49,$H32))</f>
+        <v>50</v>
+      </c>
+      <c r="D32" s="71" t="n">
+        <f aca="false">IF($H32="","",INDEX(Stock!$E$8:$E$49,$H32))</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="72" t="n">
+        <f aca="false">IF($H32="","",INDEX(Stock!$H$8:$H$49,$H32))</f>
+        <v>4259</v>
+      </c>
+      <c r="H32" s="73" t="n">
+        <f aca="false">IFERROR(MATCH(8,Stock!$N$8:$N$49,0),"")</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="70" t="str">
+        <f aca="false">IF($H33="","",INDEX(Stock!$A$8:$A$49,$H33))</f>
+        <v>Primus Japan</v>
+      </c>
+      <c r="B33" s="70" t="str">
+        <f aca="false">IF($H33="","",INDEX(Stock!$B$8:$B$49,$H33))</f>
+        <v>PUD KZN 200/300</v>
+      </c>
+      <c r="C33" s="71" t="n">
+        <f aca="false">IF($H33="","",INDEX(Stock!$D$8:$D$49,$H33))</f>
+        <v>33</v>
+      </c>
+      <c r="D33" s="71" t="n">
+        <f aca="false">IF($H33="","",INDEX(Stock!$E$8:$E$49,$H33))</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="72" t="n">
+        <f aca="false">IF($H33="","",INDEX(Stock!$H$8:$H$49,$H33))</f>
+        <v>1113</v>
+      </c>
+      <c r="H33" s="73" t="n">
+        <f aca="false">IFERROR(MATCH(9,Stock!$N$8:$N$49,0),"")</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="70" t="str">
+        <f aca="false">IF($H34="","",INDEX(Stock!$A$8:$A$49,$H34))</f>
+        <v>Primus Japan</v>
+      </c>
+      <c r="B34" s="70" t="str">
+        <f aca="false">IF($H34="","",INDEX(Stock!$B$8:$B$49,$H34))</f>
+        <v>PUD PVN 300/500</v>
+      </c>
+      <c r="C34" s="71" t="n">
+        <f aca="false">IF($H34="","",INDEX(Stock!$D$8:$D$49,$H34))</f>
+        <v>156</v>
+      </c>
+      <c r="D34" s="71" t="n">
+        <f aca="false">IF($H34="","",INDEX(Stock!$E$8:$E$49,$H34))</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="72" t="n">
+        <f aca="false">IF($H34="","",INDEX(Stock!$H$8:$H$49,$H34))</f>
+        <v>577</v>
+      </c>
+      <c r="H34" s="73" t="n">
+        <f aca="false">IFERROR(MATCH(10,Stock!$N$8:$N$49,0),"")</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="70" t="str">
+        <f aca="false">IF($H35="","",INDEX(Stock!$A$8:$A$49,$H35))</f>
+        <v>Primus Japan</v>
+      </c>
+      <c r="B35" s="70" t="str">
+        <f aca="false">IF($H35="","",INDEX(Stock!$B$8:$B$49,$H35))</f>
+        <v>PUD KKD 300/500</v>
+      </c>
+      <c r="C35" s="71" t="n">
+        <f aca="false">IF($H35="","",INDEX(Stock!$D$8:$D$49,$H35))</f>
+        <v>596</v>
+      </c>
+      <c r="D35" s="71" t="n">
+        <f aca="false">IF($H35="","",INDEX(Stock!$E$8:$E$49,$H35))</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="72" t="n">
+        <f aca="false">IF($H35="","",INDEX(Stock!$H$8:$H$49,$H35))</f>
+        <v>1176</v>
+      </c>
+      <c r="H35" s="73" t="n">
+        <f aca="false">IFERROR(MATCH(11,Stock!$N$8:$N$49,0),"")</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="70" t="str">
+        <f aca="false">IF($H36="","",INDEX(Stock!$A$8:$A$49,$H36))</f>
+        <v>Primus EU</v>
+      </c>
+      <c r="B36" s="70" t="str">
+        <f aca="false">IF($H36="","",INDEX(Stock!$B$8:$B$49,$H36))</f>
+        <v>BKN</v>
+      </c>
+      <c r="C36" s="71" t="n">
+        <f aca="false">IF($H36="","",INDEX(Stock!$D$8:$D$49,$H36))</f>
+        <v>52</v>
+      </c>
+      <c r="D36" s="71" t="n">
+        <f aca="false">IF($H36="","",INDEX(Stock!$E$8:$E$49,$H36))</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="72" t="n">
+        <f aca="false">IF($H36="","",INDEX(Stock!$H$8:$H$49,$H36))</f>
+        <v>15182</v>
+      </c>
+      <c r="H36" s="73" t="n">
+        <f aca="false">IFERROR(MATCH(12,Stock!$N$8:$N$49,0),"")</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="70" t="str">
+        <f aca="false">IF($H37="","",INDEX(Stock!$A$8:$A$49,$H37))</f>
+        <v>THT Brand</v>
+      </c>
+      <c r="B37" s="70" t="str">
+        <f aca="false">IF($H37="","",INDEX(Stock!$B$8:$B$49,$H37))</f>
+        <v>PUD PVN 80/120</v>
+      </c>
+      <c r="C37" s="71" t="n">
+        <f aca="false">IF($H37="","",INDEX(Stock!$D$8:$D$49,$H37))</f>
+        <v>1872</v>
+      </c>
+      <c r="D37" s="71" t="n">
+        <f aca="false">IF($H37="","",INDEX(Stock!$E$8:$E$49,$H37))</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="72" t="n">
+        <f aca="false">IF($H37="","",INDEX(Stock!$H$8:$H$49,$H37))</f>
+        <v>3261</v>
+      </c>
+      <c r="H37" s="73" t="n">
+        <f aca="false">IFERROR(MATCH(13,Stock!$N$8:$N$49,0),"")</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="70" t="str">
+        <f aca="false">IF($H38="","",INDEX(Stock!$A$8:$A$49,$H38))</f>
+        <v>THT Brand</v>
+      </c>
+      <c r="B38" s="70" t="str">
+        <f aca="false">IF($H38="","",INDEX(Stock!$B$8:$B$49,$H38))</f>
+        <v>PUD PVN 100/200</v>
+      </c>
+      <c r="C38" s="71" t="n">
+        <f aca="false">IF($H38="","",INDEX(Stock!$D$8:$D$49,$H38))</f>
+        <v>600</v>
+      </c>
+      <c r="D38" s="71" t="n">
+        <f aca="false">IF($H38="","",INDEX(Stock!$E$8:$E$49,$H38))</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="72" t="n">
+        <f aca="false">IF($H38="","",INDEX(Stock!$H$8:$H$49,$H38))</f>
+        <v>7655</v>
+      </c>
+      <c r="H38" s="73" t="n">
+        <f aca="false">IFERROR(MATCH(14,Stock!$N$8:$N$49,0),"")</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="70" t="str">
+        <f aca="false">IF($H39="","",INDEX(Stock!$A$8:$A$49,$H39))</f>
+        <v/>
+      </c>
+      <c r="B39" s="70" t="str">
+        <f aca="false">IF($H39="","",INDEX(Stock!$B$8:$B$49,$H39))</f>
+        <v/>
+      </c>
+      <c r="C39" s="71" t="str">
+        <f aca="false">IF($H39="","",INDEX(Stock!$D$8:$D$49,$H39))</f>
+        <v/>
+      </c>
+      <c r="D39" s="71" t="str">
+        <f aca="false">IF($H39="","",INDEX(Stock!$E$8:$E$49,$H39))</f>
+        <v/>
+      </c>
+      <c r="E39" s="72" t="str">
+        <f aca="false">IF($H39="","",INDEX(Stock!$H$8:$H$49,$H39))</f>
+        <v/>
+      </c>
+      <c r="H39" s="73" t="str">
+        <f aca="false">IFERROR(MATCH(15,Stock!$N$8:$N$49,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="70" t="str">
+        <f aca="false">IF($H40="","",INDEX(Stock!$A$8:$A$49,$H40))</f>
+        <v/>
+      </c>
+      <c r="B40" s="70" t="str">
+        <f aca="false">IF($H40="","",INDEX(Stock!$B$8:$B$49,$H40))</f>
+        <v/>
+      </c>
+      <c r="C40" s="71" t="str">
+        <f aca="false">IF($H40="","",INDEX(Stock!$D$8:$D$49,$H40))</f>
+        <v/>
+      </c>
+      <c r="D40" s="71" t="str">
+        <f aca="false">IF($H40="","",INDEX(Stock!$E$8:$E$49,$H40))</f>
+        <v/>
+      </c>
+      <c r="E40" s="72" t="str">
+        <f aca="false">IF($H40="","",INDEX(Stock!$H$8:$H$49,$H40))</f>
+        <v/>
+      </c>
+      <c r="H40" s="73" t="str">
+        <f aca="false">IFERROR(MATCH(16,Stock!$N$8:$N$49,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="70" t="str">
+        <f aca="false">IF($H41="","",INDEX(Stock!$A$8:$A$49,$H41))</f>
+        <v/>
+      </c>
+      <c r="B41" s="70" t="str">
+        <f aca="false">IF($H41="","",INDEX(Stock!$B$8:$B$49,$H41))</f>
+        <v/>
+      </c>
+      <c r="C41" s="71" t="str">
+        <f aca="false">IF($H41="","",INDEX(Stock!$D$8:$D$49,$H41))</f>
+        <v/>
+      </c>
+      <c r="D41" s="71" t="str">
+        <f aca="false">IF($H41="","",INDEX(Stock!$E$8:$E$49,$H41))</f>
+        <v/>
+      </c>
+      <c r="E41" s="72" t="str">
+        <f aca="false">IF($H41="","",INDEX(Stock!$H$8:$H$49,$H41))</f>
+        <v/>
+      </c>
+      <c r="H41" s="73" t="str">
+        <f aca="false">IFERROR(MATCH(17,Stock!$N$8:$N$49,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="70" t="str">
+        <f aca="false">IF($H42="","",INDEX(Stock!$A$8:$A$49,$H42))</f>
+        <v/>
+      </c>
+      <c r="B42" s="70" t="str">
+        <f aca="false">IF($H42="","",INDEX(Stock!$B$8:$B$49,$H42))</f>
+        <v/>
+      </c>
+      <c r="C42" s="71" t="str">
+        <f aca="false">IF($H42="","",INDEX(Stock!$D$8:$D$49,$H42))</f>
+        <v/>
+      </c>
+      <c r="D42" s="71" t="str">
+        <f aca="false">IF($H42="","",INDEX(Stock!$E$8:$E$49,$H42))</f>
+        <v/>
+      </c>
+      <c r="E42" s="72" t="str">
+        <f aca="false">IF($H42="","",INDEX(Stock!$H$8:$H$49,$H42))</f>
+        <v/>
+      </c>
+      <c r="H42" s="73" t="str">
+        <f aca="false">IFERROR(MATCH(18,Stock!$N$8:$N$49,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="70" t="str">
+        <f aca="false">IF($H43="","",INDEX(Stock!$A$8:$A$49,$H43))</f>
+        <v/>
+      </c>
+      <c r="B43" s="70" t="str">
+        <f aca="false">IF($H43="","",INDEX(Stock!$B$8:$B$49,$H43))</f>
+        <v/>
+      </c>
+      <c r="C43" s="71" t="str">
+        <f aca="false">IF($H43="","",INDEX(Stock!$D$8:$D$49,$H43))</f>
+        <v/>
+      </c>
+      <c r="D43" s="71" t="str">
+        <f aca="false">IF($H43="","",INDEX(Stock!$E$8:$E$49,$H43))</f>
+        <v/>
+      </c>
+      <c r="E43" s="72" t="str">
+        <f aca="false">IF($H43="","",INDEX(Stock!$H$8:$H$49,$H43))</f>
+        <v/>
+      </c>
+      <c r="H43" s="73" t="str">
+        <f aca="false">IFERROR(MATCH(19,Stock!$N$8:$N$49,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="70" t="str">
+        <f aca="false">IF($H44="","",INDEX(Stock!$A$8:$A$49,$H44))</f>
+        <v/>
+      </c>
+      <c r="B44" s="70" t="str">
+        <f aca="false">IF($H44="","",INDEX(Stock!$B$8:$B$49,$H44))</f>
+        <v/>
+      </c>
+      <c r="C44" s="71" t="str">
+        <f aca="false">IF($H44="","",INDEX(Stock!$D$8:$D$49,$H44))</f>
+        <v/>
+      </c>
+      <c r="D44" s="71" t="str">
+        <f aca="false">IF($H44="","",INDEX(Stock!$E$8:$E$49,$H44))</f>
+        <v/>
+      </c>
+      <c r="E44" s="72" t="str">
+        <f aca="false">IF($H44="","",INDEX(Stock!$H$8:$H$49,$H44))</f>
+        <v/>
+      </c>
+      <c r="H44" s="73" t="str">
+        <f aca="false">IFERROR(MATCH(20,Stock!$N$8:$N$49,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="74" t="s">
+        <v>130</v>
+      </c>
+      <c r="B45" s="75" t="str">
+        <f aca="false">COUNTIF(Stock!$M$8:$M$49,1)&amp;" product(s)"</f>
+        <v>14 product(s)</v>
+      </c>
+      <c r="C45" s="76" t="n">
+        <f aca="false">SUM(C25:C44)</f>
+        <v>4880</v>
+      </c>
+      <c r="D45" s="76" t="n">
+        <f aca="false">SUM(D25:D44)</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="74"/>
+      <c r="F45" s="74"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="77" t="str">
+        <f aca="false">IF(COUNTIF(Stock!$M$8:$M$49,1)&gt;20,"Note: "&amp;(COUNTIF(Stock!$M$8:$M$49,1)-20)&amp;" further product(s) moved today — see the Stock sheet for the full list.","")</f>
+        <v/>
+      </c>
+      <c r="B46" s="77"/>
+      <c r="C46" s="77"/>
+      <c r="D46" s="77"/>
+      <c r="E46" s="77"/>
+      <c r="F46" s="77"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="78" t="s">
+        <v>131</v>
+      </c>
+      <c r="B48" s="78"/>
+      <c r="C48" s="78"/>
+      <c r="D48" s="78"/>
+      <c r="E48" s="78"/>
+      <c r="F48" s="78"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A48:F48"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A25:F44">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>$B25&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/stock-statement/PEI-Stock-Register.xlsx
+++ b/stock-statement/PEI-Stock-Register.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookProtection workbookPassword="DF10" lockStructure="1"/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">'Daily Entry'!$6:$6</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Daily Entry'!$A$6:$E$250</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">'Daily Report'!$A$1:$F$48</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Read me'!$A$1:$B$38</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Read me'!$A$1:$B$41</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Stock!$A$1:$J$50</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">Stock!$7:$7</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Stock!$A$7:$J$49</definedName>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="135">
   <si>
     <t xml:space="preserve">PREMIER EXPORTS INTERNATIONAL</t>
   </si>
@@ -107,19 +107,28 @@
     <t xml:space="preserve">so yesterday's closing is today's starting point without anyone copying a number.</t>
   </si>
   <si>
-    <t xml:space="preserve">Which cells you edit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blue figures — typed by you. Opening balance on 'Stock'; everything on 'Daily Entry'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yellow cells — the statement date, and rate per slab. Fill the rates in to value the stock.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black figures — calculated. Do not type over them, or the sheet stops adding up.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grey — Key, Moved today and Rank. Machinery for the dropdown and the report. Leave alone.</t>
+    <t xml:space="preserve">What can be typed into — everything else is locked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Daily Entry' — the whole grid: date, product, production, shipment, note.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Stock' — the Statement date, and the yellow Rate / Slab column.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every other cell is protected: headings, opening balances, formulas, totals,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the Summary and the Daily Report. Formatting is locked too, so column widths,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fonts, colours and number formats cannot be changed by accident.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The owner holds the password. To change a locked cell: Review ▸ Unprotect Sheet,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">make the change, then Review ▸ Protect Sheet again to put the guard back.</t>
   </si>
   <si>
     <t xml:space="preserve">Dates must be real dates</t>
@@ -468,7 +477,7 @@
     <numFmt numFmtId="169" formatCode="[&gt;=10000000]&quot;₹ &quot;##\,##\,##\,##0.00;[&gt;=100000]&quot;₹ &quot;##\,##\,##0.00;&quot;₹ &quot;#,##0.00"/>
     <numFmt numFmtId="170" formatCode="General"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -533,13 +542,6 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF5E7C8B"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -892,7 +894,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="85">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -925,31 +927,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -957,7 +955,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -969,19 +967,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -989,7 +987,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1001,7 +999,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1009,59 +1007,71 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1069,55 +1079,63 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="27" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="26" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="27" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="26" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="28" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="27" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1125,19 +1143,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="30" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="30" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1145,69 +1163,77 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="30" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="32" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="31" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="32" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1608,7 +1634,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -1725,65 +1751,81 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="4"/>
+      <c r="B26" s="4" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="3" t="s">
-        <v>21</v>
+      <c r="B27" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="B29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="4"/>
+      <c r="B30" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="3" t="s">
-        <v>24</v>
+      <c r="B31" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="4" t="s">
-        <v>26</v>
-      </c>
+      <c r="B33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="4"/>
+      <c r="B34" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="3" t="s">
-        <v>27</v>
+      <c r="B35" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="4" t="s">
-        <v>29</v>
+      <c r="B37" s="4"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" password="df10" objects="true" scenarios="true" autoFilter="false"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1820,2124 +1862,2125 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="9" t="n">
+      <c r="A3" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="8" t="n">
         <v>46254</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>32</v>
+      <c r="D3" s="9" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>33</v>
+      <c r="A5" s="9" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="12" t="s">
+      <c r="A7" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="B7" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="C7" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="D7" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="E7" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="F7" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="G7" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="K7" s="13"/>
-      <c r="L7" s="14" t="s">
+      <c r="H7" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="M7" s="14" t="s">
+      <c r="I7" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="N7" s="14" t="s">
+      <c r="J7" s="11" t="s">
         <v>46</v>
       </c>
+      <c r="K7" s="12"/>
+      <c r="L7" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="16" t="n">
+      <c r="A8" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="15" t="n">
         <v>11459</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L8,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>1068</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L8,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L8)</f>
         <v>1068</v>
       </c>
-      <c r="G8" s="18" t="n">
+      <c r="G8" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L8)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="19" t="n">
+      <c r="H8" s="18" t="n">
         <f aca="false">$C8+$F8-$G8</f>
         <v>12527</v>
       </c>
-      <c r="I8" s="20"/>
-      <c r="J8" s="21" t="str">
+      <c r="I8" s="19"/>
+      <c r="J8" s="20" t="str">
         <f aca="false">IF($I8="","",$H8*$I8)</f>
         <v/>
       </c>
-      <c r="L8" s="22" t="str">
+      <c r="L8" s="21" t="str">
         <f aca="false">$A8&amp;" - "&amp;$B8</f>
         <v>Blue Dolphin - PD PVN 100/200</v>
       </c>
-      <c r="M8" s="22" t="n">
+      <c r="M8" s="21" t="n">
         <f aca="false">IF(OR($D8&lt;&gt;0,$E8&lt;&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="N8" s="22" t="n">
+      <c r="N8" s="21" t="n">
         <f aca="false">IF($M8=1,SUM($M$8:$M8),"")</f>
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="24" t="n">
+      <c r="A9" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="23" t="n">
         <v>517</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L9,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>65</v>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L9,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="26" t="n">
+      <c r="F9" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L9)</f>
         <v>65</v>
       </c>
-      <c r="G9" s="26" t="n">
+      <c r="G9" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L9)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="27" t="n">
+      <c r="H9" s="26" t="n">
         <f aca="false">$C9+$F9-$G9</f>
         <v>582</v>
       </c>
-      <c r="I9" s="20"/>
-      <c r="J9" s="28" t="str">
+      <c r="I9" s="19"/>
+      <c r="J9" s="27" t="str">
         <f aca="false">IF($I9="","",$H9*$I9)</f>
         <v/>
       </c>
-      <c r="L9" s="22" t="str">
+      <c r="L9" s="21" t="str">
         <f aca="false">$A9&amp;" - "&amp;$B9</f>
         <v>Blue Dolphin - PD KKD 100/200</v>
       </c>
-      <c r="M9" s="22" t="n">
+      <c r="M9" s="21" t="n">
         <f aca="false">IF(OR($D9&lt;&gt;0,$E9&lt;&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="N9" s="22" t="n">
+      <c r="N9" s="21" t="n">
         <f aca="false">IF($M9=1,SUM($M$8:$M9),"")</f>
         <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="15" t="s">
+      <c r="A10" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="15" t="n">
         <v>2262</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L10,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>267</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L10,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L10)</f>
         <v>267</v>
       </c>
-      <c r="G10" s="18" t="n">
+      <c r="G10" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L10)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H10" s="18" t="n">
         <f aca="false">$C10+$F10-$G10</f>
         <v>2529</v>
       </c>
-      <c r="I10" s="20"/>
-      <c r="J10" s="21" t="str">
+      <c r="I10" s="19"/>
+      <c r="J10" s="20" t="str">
         <f aca="false">IF($I10="","",$H10*$I10)</f>
         <v/>
       </c>
-      <c r="L10" s="22" t="str">
+      <c r="L10" s="21" t="str">
         <f aca="false">$A10&amp;" - "&amp;$B10</f>
         <v>Blue Dolphin - PUD PVN 200/300</v>
       </c>
-      <c r="M10" s="22" t="n">
+      <c r="M10" s="21" t="n">
         <f aca="false">IF(OR($D10&lt;&gt;0,$E10&lt;&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="N10" s="22" t="n">
+      <c r="N10" s="21" t="n">
         <f aca="false">IF($M10=1,SUM($M$8:$M10),"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="24" t="n">
+      <c r="A11" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="23" t="n">
         <v>2835</v>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L11,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L11,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="26" t="n">
+      <c r="F11" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L11)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="26" t="n">
+      <c r="G11" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L11)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="27" t="n">
+      <c r="H11" s="26" t="n">
         <f aca="false">$C11+$F11-$G11</f>
         <v>2835</v>
       </c>
-      <c r="I11" s="20"/>
-      <c r="J11" s="28" t="str">
+      <c r="I11" s="19"/>
+      <c r="J11" s="27" t="str">
         <f aca="false">IF($I11="","",$H11*$I11)</f>
         <v/>
       </c>
-      <c r="L11" s="22" t="str">
+      <c r="L11" s="21" t="str">
         <f aca="false">$A11&amp;" - "&amp;$B11</f>
         <v>Blue Dolphin - PUD KKD 200/300</v>
       </c>
-      <c r="M11" s="22" t="n">
+      <c r="M11" s="21" t="n">
         <f aca="false">IF(OR($D11&lt;&gt;0,$E11&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N11" s="22" t="str">
+      <c r="N11" s="21" t="str">
         <f aca="false">IF($M11=1,SUM($M$8:$M11),"")</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="16" t="n">
+      <c r="A12" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="15" t="n">
         <v>1673</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L12,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L12,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L12)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L12)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="19" t="n">
+      <c r="H12" s="18" t="n">
         <f aca="false">$C12+$F12-$G12</f>
         <v>1673</v>
       </c>
-      <c r="I12" s="20"/>
-      <c r="J12" s="21" t="str">
+      <c r="I12" s="19"/>
+      <c r="J12" s="20" t="str">
         <f aca="false">IF($I12="","",$H12*$I12)</f>
         <v/>
       </c>
-      <c r="L12" s="22" t="str">
+      <c r="L12" s="21" t="str">
         <f aca="false">$A12&amp;" - "&amp;$B12</f>
         <v>Blue Dolphin - PUD PVN 300/500</v>
       </c>
-      <c r="M12" s="22" t="n">
+      <c r="M12" s="21" t="n">
         <f aca="false">IF(OR($D12&lt;&gt;0,$E12&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N12" s="22" t="str">
+      <c r="N12" s="21" t="str">
         <f aca="false">IF($M12=1,SUM($M$8:$M12),"")</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="24" t="n">
+      <c r="A13" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="23" t="n">
         <v>7542</v>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L13,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L13,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="26" t="n">
+      <c r="F13" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L13)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="26" t="n">
+      <c r="G13" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L13)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="27" t="n">
+      <c r="H13" s="26" t="n">
         <f aca="false">$C13+$F13-$G13</f>
         <v>7542</v>
       </c>
-      <c r="I13" s="20"/>
-      <c r="J13" s="28" t="str">
+      <c r="I13" s="19"/>
+      <c r="J13" s="27" t="str">
         <f aca="false">IF($I13="","",$H13*$I13)</f>
         <v/>
       </c>
-      <c r="L13" s="22" t="str">
+      <c r="L13" s="21" t="str">
         <f aca="false">$A13&amp;" - "&amp;$B13</f>
         <v>Blue Dolphin - PUD KKD 300/500</v>
       </c>
-      <c r="M13" s="22" t="n">
+      <c r="M13" s="21" t="n">
         <f aca="false">IF(OR($D13&lt;&gt;0,$E13&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N13" s="22" t="str">
+      <c r="N13" s="21" t="str">
         <f aca="false">IF($M13=1,SUM($M$8:$M13),"")</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="A14" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="15" t="n">
         <v>2357</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L14,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L14,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L14)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="G14" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L14)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="19" t="n">
+      <c r="H14" s="18" t="n">
         <f aca="false">$C14+$F14-$G14</f>
         <v>2357</v>
       </c>
-      <c r="I14" s="20"/>
-      <c r="J14" s="21" t="str">
+      <c r="I14" s="19"/>
+      <c r="J14" s="20" t="str">
         <f aca="false">IF($I14="","",$H14*$I14)</f>
         <v/>
       </c>
-      <c r="L14" s="22" t="str">
+      <c r="L14" s="21" t="str">
         <f aca="false">$A14&amp;" - "&amp;$B14</f>
         <v>Blue Dolphin - PD PVN 200/300</v>
       </c>
-      <c r="M14" s="22" t="n">
+      <c r="M14" s="21" t="n">
         <f aca="false">IF(OR($D14&lt;&gt;0,$E14&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N14" s="22" t="str">
+      <c r="N14" s="21" t="str">
         <f aca="false">IF($M14=1,SUM($M$8:$M14),"")</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" s="24" t="n">
+      <c r="A15" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="23" t="n">
         <v>64</v>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L15,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>29</v>
       </c>
-      <c r="E15" s="25" t="n">
+      <c r="E15" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L15,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="26" t="n">
+      <c r="F15" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L15)</f>
         <v>29</v>
       </c>
-      <c r="G15" s="26" t="n">
+      <c r="G15" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L15)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="27" t="n">
+      <c r="H15" s="26" t="n">
         <f aca="false">$C15+$F15-$G15</f>
         <v>93</v>
       </c>
-      <c r="I15" s="20"/>
-      <c r="J15" s="28" t="str">
+      <c r="I15" s="19"/>
+      <c r="J15" s="27" t="str">
         <f aca="false">IF($I15="","",$H15*$I15)</f>
         <v/>
       </c>
-      <c r="L15" s="22" t="str">
+      <c r="L15" s="21" t="str">
         <f aca="false">$A15&amp;" - "&amp;$B15</f>
         <v>Primus Japan - PUD KZN 40/60</v>
       </c>
-      <c r="M15" s="22" t="n">
+      <c r="M15" s="21" t="n">
         <f aca="false">IF(OR($D15&lt;&gt;0,$E15&lt;&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="N15" s="22" t="n">
+      <c r="N15" s="21" t="n">
         <f aca="false">IF($M15=1,SUM($M$8:$M15),"")</f>
         <v>4</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="A16" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="15" t="n">
         <v>191</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L16,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>39</v>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E16" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L16,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="F16" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L16)</f>
         <v>39</v>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L16)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="19" t="n">
+      <c r="H16" s="18" t="n">
         <f aca="false">$C16+$F16-$G16</f>
         <v>230</v>
       </c>
-      <c r="I16" s="20"/>
-      <c r="J16" s="21" t="str">
+      <c r="I16" s="19"/>
+      <c r="J16" s="20" t="str">
         <f aca="false">IF($I16="","",$H16*$I16)</f>
         <v/>
       </c>
-      <c r="L16" s="22" t="str">
+      <c r="L16" s="21" t="str">
         <f aca="false">$A16&amp;" - "&amp;$B16</f>
         <v>Primus Japan - PUD KZN 60/80</v>
       </c>
-      <c r="M16" s="22" t="n">
+      <c r="M16" s="21" t="n">
         <f aca="false">IF(OR($D16&lt;&gt;0,$E16&lt;&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="N16" s="22" t="n">
+      <c r="N16" s="21" t="n">
         <f aca="false">IF($M16=1,SUM($M$8:$M16),"")</f>
         <v>5</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" s="23" t="s">
+      <c r="A17" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="24" t="n">
+      <c r="B17" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="23" t="n">
         <v>16849</v>
       </c>
-      <c r="D17" s="25" t="n">
+      <c r="D17" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L17,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="25" t="n">
+      <c r="E17" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L17,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="26" t="n">
+      <c r="F17" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L17)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="26" t="n">
+      <c r="G17" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L17)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="27" t="n">
+      <c r="H17" s="26" t="n">
         <f aca="false">$C17+$F17-$G17</f>
         <v>16849</v>
       </c>
-      <c r="I17" s="20"/>
-      <c r="J17" s="28" t="str">
+      <c r="I17" s="19"/>
+      <c r="J17" s="27" t="str">
         <f aca="false">IF($I17="","",$H17*$I17)</f>
         <v/>
       </c>
-      <c r="L17" s="22" t="str">
+      <c r="L17" s="21" t="str">
         <f aca="false">$A17&amp;" - "&amp;$B17</f>
         <v>Primus Japan - PUD PVN 80/120</v>
       </c>
-      <c r="M17" s="22" t="n">
+      <c r="M17" s="21" t="n">
         <f aca="false">IF(OR($D17&lt;&gt;0,$E17&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N17" s="22" t="str">
+      <c r="N17" s="21" t="str">
         <f aca="false">IF($M17=1,SUM($M$8:$M17),"")</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="A18" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="15" t="n">
         <v>466</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L18,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>50</v>
       </c>
-      <c r="E18" s="17" t="n">
+      <c r="E18" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L18,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F18" s="18" t="n">
+      <c r="F18" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L18)</f>
         <v>50</v>
       </c>
-      <c r="G18" s="18" t="n">
+      <c r="G18" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L18)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="19" t="n">
+      <c r="H18" s="18" t="n">
         <f aca="false">$C18+$F18-$G18</f>
         <v>516</v>
       </c>
-      <c r="I18" s="20"/>
-      <c r="J18" s="21" t="str">
+      <c r="I18" s="19"/>
+      <c r="J18" s="20" t="str">
         <f aca="false">IF($I18="","",$H18*$I18)</f>
         <v/>
       </c>
-      <c r="L18" s="22" t="str">
+      <c r="L18" s="21" t="str">
         <f aca="false">$A18&amp;" - "&amp;$B18</f>
         <v>Primus Japan - PUD KZN 80/120</v>
       </c>
-      <c r="M18" s="22" t="n">
+      <c r="M18" s="21" t="n">
         <f aca="false">IF(OR($D18&lt;&gt;0,$E18&lt;&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="N18" s="22" t="n">
+      <c r="N18" s="21" t="n">
         <f aca="false">IF($M18=1,SUM($M$8:$M18),"")</f>
         <v>6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" s="24" t="n">
+      <c r="A19" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="23" t="n">
         <v>69</v>
       </c>
-      <c r="D19" s="25" t="n">
+      <c r="D19" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L19,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>3</v>
       </c>
-      <c r="E19" s="25" t="n">
+      <c r="E19" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L19,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L19)</f>
         <v>3</v>
       </c>
-      <c r="G19" s="26" t="n">
+      <c r="G19" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L19)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="27" t="n">
+      <c r="H19" s="26" t="n">
         <f aca="false">$C19+$F19-$G19</f>
         <v>72</v>
       </c>
-      <c r="I19" s="20"/>
-      <c r="J19" s="28" t="str">
+      <c r="I19" s="19"/>
+      <c r="J19" s="27" t="str">
         <f aca="false">IF($I19="","",$H19*$I19)</f>
         <v/>
       </c>
-      <c r="L19" s="22" t="str">
+      <c r="L19" s="21" t="str">
         <f aca="false">$A19&amp;" - "&amp;$B19</f>
         <v>Primus Japan - PUD NRN 80/120</v>
       </c>
-      <c r="M19" s="22" t="n">
+      <c r="M19" s="21" t="n">
         <f aca="false">IF(OR($D19&lt;&gt;0,$E19&lt;&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="N19" s="22" t="n">
+      <c r="N19" s="21" t="n">
         <f aca="false">IF($M19=1,SUM($M$8:$M19),"")</f>
         <v>7</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="16" t="n">
+      <c r="A20" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="15" t="n">
         <v>2617</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L20,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="17" t="n">
+      <c r="E20" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L20,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="18" t="n">
+      <c r="F20" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L20)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="18" t="n">
+      <c r="G20" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L20)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="19" t="n">
+      <c r="H20" s="18" t="n">
         <f aca="false">$C20+$F20-$G20</f>
         <v>2617</v>
       </c>
-      <c r="I20" s="20"/>
-      <c r="J20" s="21" t="str">
+      <c r="I20" s="19"/>
+      <c r="J20" s="20" t="str">
         <f aca="false">IF($I20="","",$H20*$I20)</f>
         <v/>
       </c>
-      <c r="L20" s="22" t="str">
+      <c r="L20" s="21" t="str">
         <f aca="false">$A20&amp;" - "&amp;$B20</f>
         <v>Primus Japan - PUD PVN 100/200</v>
       </c>
-      <c r="M20" s="22" t="n">
+      <c r="M20" s="21" t="n">
         <f aca="false">IF(OR($D20&lt;&gt;0,$E20&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N20" s="22" t="str">
+      <c r="N20" s="21" t="str">
         <f aca="false">IF($M20=1,SUM($M$8:$M20),"")</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" s="24" t="n">
+      <c r="A21" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="D21" s="25" t="n">
+      <c r="D21" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L21,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E21" s="25" t="n">
+      <c r="E21" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L21,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F21" s="26" t="n">
+      <c r="F21" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L21)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="26" t="n">
+      <c r="G21" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L21)</f>
         <v>0</v>
       </c>
-      <c r="H21" s="27" t="n">
+      <c r="H21" s="26" t="n">
         <f aca="false">$C21+$F21-$G21</f>
         <v>13</v>
       </c>
-      <c r="I21" s="20"/>
-      <c r="J21" s="28" t="str">
+      <c r="I21" s="19"/>
+      <c r="J21" s="27" t="str">
         <f aca="false">IF($I21="","",$H21*$I21)</f>
         <v/>
       </c>
-      <c r="L21" s="22" t="str">
+      <c r="L21" s="21" t="str">
         <f aca="false">$A21&amp;" - "&amp;$B21</f>
         <v>Primus Japan - PUD NRN 100/200</v>
       </c>
-      <c r="M21" s="22" t="n">
+      <c r="M21" s="21" t="n">
         <f aca="false">IF(OR($D21&lt;&gt;0,$E21&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N21" s="22" t="str">
+      <c r="N21" s="21" t="str">
         <f aca="false">IF($M21=1,SUM($M$8:$M21),"")</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="16" t="n">
+      <c r="A22" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="15" t="n">
         <v>4209</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L22,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>50</v>
       </c>
-      <c r="E22" s="17" t="n">
+      <c r="E22" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L22,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="18" t="n">
+      <c r="F22" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L22)</f>
         <v>50</v>
       </c>
-      <c r="G22" s="18" t="n">
+      <c r="G22" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L22)</f>
         <v>0</v>
       </c>
-      <c r="H22" s="19" t="n">
+      <c r="H22" s="18" t="n">
         <f aca="false">$C22+$F22-$G22</f>
         <v>4259</v>
       </c>
-      <c r="I22" s="20"/>
-      <c r="J22" s="21" t="str">
+      <c r="I22" s="19"/>
+      <c r="J22" s="20" t="str">
         <f aca="false">IF($I22="","",$H22*$I22)</f>
         <v/>
       </c>
-      <c r="L22" s="22" t="str">
+      <c r="L22" s="21" t="str">
         <f aca="false">$A22&amp;" - "&amp;$B22</f>
         <v>Primus Japan - PUD KZN 100/200</v>
       </c>
-      <c r="M22" s="22" t="n">
+      <c r="M22" s="21" t="n">
         <f aca="false">IF(OR($D22&lt;&gt;0,$E22&lt;&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="N22" s="22" t="n">
+      <c r="N22" s="21" t="n">
         <f aca="false">IF($M22=1,SUM($M$8:$M22),"")</f>
         <v>8</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="25" t="n">
+      <c r="A23" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L23,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E23" s="25" t="n">
+      <c r="E23" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L23,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F23" s="26" t="n">
+      <c r="F23" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L23)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="26" t="n">
+      <c r="G23" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L23)</f>
         <v>0</v>
       </c>
-      <c r="H23" s="27" t="n">
+      <c r="H23" s="26" t="n">
         <f aca="false">$C23+$F23-$G23</f>
         <v>0</v>
       </c>
-      <c r="I23" s="20"/>
-      <c r="J23" s="28" t="str">
+      <c r="I23" s="19"/>
+      <c r="J23" s="27" t="str">
         <f aca="false">IF($I23="","",$H23*$I23)</f>
         <v/>
       </c>
-      <c r="L23" s="22" t="str">
+      <c r="L23" s="21" t="str">
         <f aca="false">$A23&amp;" - "&amp;$B23</f>
         <v>Primus Japan - PUD PVN 200/300</v>
       </c>
-      <c r="M23" s="22" t="n">
+      <c r="M23" s="21" t="n">
         <f aca="false">IF(OR($D23&lt;&gt;0,$E23&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N23" s="22" t="str">
+      <c r="N23" s="21" t="str">
         <f aca="false">IF($M23=1,SUM($M$8:$M23),"")</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="16" t="n">
+      <c r="A24" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="15" t="n">
         <v>2757</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L24,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="17" t="n">
+      <c r="E24" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L24,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F24" s="18" t="n">
+      <c r="F24" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L24)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="18" t="n">
+      <c r="G24" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L24)</f>
         <v>0</v>
       </c>
-      <c r="H24" s="19" t="n">
+      <c r="H24" s="18" t="n">
         <f aca="false">$C24+$F24-$G24</f>
         <v>2757</v>
       </c>
-      <c r="I24" s="20"/>
-      <c r="J24" s="21" t="str">
+      <c r="I24" s="19"/>
+      <c r="J24" s="20" t="str">
         <f aca="false">IF($I24="","",$H24*$I24)</f>
         <v/>
       </c>
-      <c r="L24" s="22" t="str">
+      <c r="L24" s="21" t="str">
         <f aca="false">$A24&amp;" - "&amp;$B24</f>
         <v>Primus Japan - PUD KKD 200/300</v>
       </c>
-      <c r="M24" s="22" t="n">
+      <c r="M24" s="21" t="n">
         <f aca="false">IF(OR($D24&lt;&gt;0,$E24&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N24" s="22" t="str">
+      <c r="N24" s="21" t="str">
         <f aca="false">IF($M24=1,SUM($M$8:$M24),"")</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="24" t="n">
+      <c r="A25" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="23" t="n">
         <v>1080</v>
       </c>
-      <c r="D25" s="25" t="n">
+      <c r="D25" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L25,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>33</v>
       </c>
-      <c r="E25" s="25" t="n">
+      <c r="E25" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L25,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F25" s="26" t="n">
+      <c r="F25" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L25)</f>
         <v>33</v>
       </c>
-      <c r="G25" s="26" t="n">
+      <c r="G25" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L25)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="27" t="n">
+      <c r="H25" s="26" t="n">
         <f aca="false">$C25+$F25-$G25</f>
         <v>1113</v>
       </c>
-      <c r="I25" s="20"/>
-      <c r="J25" s="28" t="str">
+      <c r="I25" s="19"/>
+      <c r="J25" s="27" t="str">
         <f aca="false">IF($I25="","",$H25*$I25)</f>
         <v/>
       </c>
-      <c r="L25" s="22" t="str">
+      <c r="L25" s="21" t="str">
         <f aca="false">$A25&amp;" - "&amp;$B25</f>
         <v>Primus Japan - PUD KZN 200/300</v>
       </c>
-      <c r="M25" s="22" t="n">
+      <c r="M25" s="21" t="n">
         <f aca="false">IF(OR($D25&lt;&gt;0,$E25&lt;&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="N25" s="22" t="n">
+      <c r="N25" s="21" t="n">
         <f aca="false">IF($M25=1,SUM($M$8:$M25),"")</f>
         <v>9</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B26" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="16" t="n">
+      <c r="C26" s="15" t="n">
         <v>421</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L26,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>156</v>
       </c>
-      <c r="E26" s="17" t="n">
+      <c r="E26" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L26,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F26" s="18" t="n">
+      <c r="F26" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L26)</f>
         <v>156</v>
       </c>
-      <c r="G26" s="18" t="n">
+      <c r="G26" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L26)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="19" t="n">
+      <c r="H26" s="18" t="n">
         <f aca="false">$C26+$F26-$G26</f>
         <v>577</v>
       </c>
-      <c r="I26" s="20"/>
-      <c r="J26" s="21" t="str">
+      <c r="I26" s="19"/>
+      <c r="J26" s="20" t="str">
         <f aca="false">IF($I26="","",$H26*$I26)</f>
         <v/>
       </c>
-      <c r="L26" s="22" t="str">
+      <c r="L26" s="21" t="str">
         <f aca="false">$A26&amp;" - "&amp;$B26</f>
         <v>Primus Japan - PUD PVN 300/500</v>
       </c>
-      <c r="M26" s="22" t="n">
+      <c r="M26" s="21" t="n">
         <f aca="false">IF(OR($D26&lt;&gt;0,$E26&lt;&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="N26" s="22" t="n">
+      <c r="N26" s="21" t="n">
         <f aca="false">IF($M26=1,SUM($M$8:$M26),"")</f>
         <v>10</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="24" t="n">
+      <c r="A27" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="23" t="n">
         <v>580</v>
       </c>
-      <c r="D27" s="25" t="n">
+      <c r="D27" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L27,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>596</v>
       </c>
-      <c r="E27" s="25" t="n">
+      <c r="E27" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L27,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F27" s="26" t="n">
+      <c r="F27" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L27)</f>
         <v>596</v>
       </c>
-      <c r="G27" s="26" t="n">
+      <c r="G27" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L27)</f>
         <v>0</v>
       </c>
-      <c r="H27" s="27" t="n">
+      <c r="H27" s="26" t="n">
         <f aca="false">$C27+$F27-$G27</f>
         <v>1176</v>
       </c>
-      <c r="I27" s="20"/>
-      <c r="J27" s="28" t="str">
+      <c r="I27" s="19"/>
+      <c r="J27" s="27" t="str">
         <f aca="false">IF($I27="","",$H27*$I27)</f>
         <v/>
       </c>
-      <c r="L27" s="22" t="str">
+      <c r="L27" s="21" t="str">
         <f aca="false">$A27&amp;" - "&amp;$B27</f>
         <v>Primus Japan - PUD KKD 300/500</v>
       </c>
-      <c r="M27" s="22" t="n">
+      <c r="M27" s="21" t="n">
         <f aca="false">IF(OR($D27&lt;&gt;0,$E27&lt;&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="N27" s="22" t="n">
+      <c r="N27" s="21" t="n">
         <f aca="false">IF($M27=1,SUM($M$8:$M27),"")</f>
         <v>11</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="B28" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C28" s="16" t="n">
+      <c r="A28" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="15" t="n">
         <v>185</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L28,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E28" s="17" t="n">
+      <c r="E28" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L28,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F28" s="18" t="n">
+      <c r="F28" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L28)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="18" t="n">
+      <c r="G28" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L28)</f>
         <v>0</v>
       </c>
-      <c r="H28" s="19" t="n">
+      <c r="H28" s="18" t="n">
         <f aca="false">$C28+$F28-$G28</f>
         <v>185</v>
       </c>
-      <c r="I28" s="20"/>
-      <c r="J28" s="21" t="str">
+      <c r="I28" s="19"/>
+      <c r="J28" s="20" t="str">
         <f aca="false">IF($I28="","",$H28*$I28)</f>
         <v/>
       </c>
-      <c r="L28" s="22" t="str">
+      <c r="L28" s="21" t="str">
         <f aca="false">$A28&amp;" - "&amp;$B28</f>
         <v>Primus EU - PUD 20/40</v>
       </c>
-      <c r="M28" s="22" t="n">
+      <c r="M28" s="21" t="n">
         <f aca="false">IF(OR($D28&lt;&gt;0,$E28&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N28" s="22" t="str">
+      <c r="N28" s="21" t="str">
         <f aca="false">IF($M28=1,SUM($M$8:$M28),"")</f>
         <v/>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" s="24" t="n">
+      <c r="A29" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="23" t="n">
         <v>368</v>
       </c>
-      <c r="D29" s="25" t="n">
+      <c r="D29" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L29,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E29" s="25" t="n">
+      <c r="E29" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L29,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F29" s="26" t="n">
+      <c r="F29" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L29)</f>
         <v>0</v>
       </c>
-      <c r="G29" s="26" t="n">
+      <c r="G29" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L29)</f>
         <v>0</v>
       </c>
-      <c r="H29" s="27" t="n">
+      <c r="H29" s="26" t="n">
         <f aca="false">$C29+$F29-$G29</f>
         <v>368</v>
       </c>
-      <c r="I29" s="20"/>
-      <c r="J29" s="28" t="str">
+      <c r="I29" s="19"/>
+      <c r="J29" s="27" t="str">
         <f aca="false">IF($I29="","",$H29*$I29)</f>
         <v/>
       </c>
-      <c r="L29" s="22" t="str">
+      <c r="L29" s="21" t="str">
         <f aca="false">$A29&amp;" - "&amp;$B29</f>
         <v>Primus EU - PUD 40/60</v>
       </c>
-      <c r="M29" s="22" t="n">
+      <c r="M29" s="21" t="n">
         <f aca="false">IF(OR($D29&lt;&gt;0,$E29&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N29" s="22" t="str">
+      <c r="N29" s="21" t="str">
         <f aca="false">IF($M29=1,SUM($M$8:$M29),"")</f>
         <v/>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="B30" s="15" t="s">
+      <c r="A30" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="16" t="n">
+      <c r="B30" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="15" t="n">
         <v>380</v>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L30,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E30" s="17" t="n">
+      <c r="E30" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L30,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F30" s="18" t="n">
+      <c r="F30" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L30)</f>
         <v>0</v>
       </c>
-      <c r="G30" s="18" t="n">
+      <c r="G30" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L30)</f>
         <v>0</v>
       </c>
-      <c r="H30" s="19" t="n">
+      <c r="H30" s="18" t="n">
         <f aca="false">$C30+$F30-$G30</f>
         <v>380</v>
       </c>
-      <c r="I30" s="20"/>
-      <c r="J30" s="21" t="str">
+      <c r="I30" s="19"/>
+      <c r="J30" s="20" t="str">
         <f aca="false">IF($I30="","",$H30*$I30)</f>
         <v/>
       </c>
-      <c r="L30" s="22" t="str">
+      <c r="L30" s="21" t="str">
         <f aca="false">$A30&amp;" - "&amp;$B30</f>
         <v>Primus EU - PUD 60/80</v>
       </c>
-      <c r="M30" s="22" t="n">
+      <c r="M30" s="21" t="n">
         <f aca="false">IF(OR($D30&lt;&gt;0,$E30&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N30" s="22" t="str">
+      <c r="N30" s="21" t="str">
         <f aca="false">IF($M30=1,SUM($M$8:$M30),"")</f>
         <v/>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="C31" s="24" t="n">
+      <c r="A31" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="23" t="n">
         <v>1151</v>
       </c>
-      <c r="D31" s="25" t="n">
+      <c r="D31" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L31,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E31" s="25" t="n">
+      <c r="E31" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L31,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F31" s="26" t="n">
+      <c r="F31" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L31)</f>
         <v>0</v>
       </c>
-      <c r="G31" s="26" t="n">
+      <c r="G31" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L31)</f>
         <v>0</v>
       </c>
-      <c r="H31" s="27" t="n">
+      <c r="H31" s="26" t="n">
         <f aca="false">$C31+$F31-$G31</f>
         <v>1151</v>
       </c>
-      <c r="I31" s="20"/>
-      <c r="J31" s="28" t="str">
+      <c r="I31" s="19"/>
+      <c r="J31" s="27" t="str">
         <f aca="false">IF($I31="","",$H31*$I31)</f>
         <v/>
       </c>
-      <c r="L31" s="22" t="str">
+      <c r="L31" s="21" t="str">
         <f aca="false">$A31&amp;" - "&amp;$B31</f>
         <v>Primus EU - PUD 80/120</v>
       </c>
-      <c r="M31" s="22" t="n">
+      <c r="M31" s="21" t="n">
         <f aca="false">IF(OR($D31&lt;&gt;0,$E31&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N31" s="22" t="str">
+      <c r="N31" s="21" t="str">
         <f aca="false">IF($M31=1,SUM($M$8:$M31),"")</f>
         <v/>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" s="16" t="n">
+      <c r="A32" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="15" t="n">
         <v>3797</v>
       </c>
-      <c r="D32" s="17" t="n">
+      <c r="D32" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L32,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E32" s="17" t="n">
+      <c r="E32" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L32,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F32" s="18" t="n">
+      <c r="F32" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L32)</f>
         <v>0</v>
       </c>
-      <c r="G32" s="18" t="n">
+      <c r="G32" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L32)</f>
         <v>0</v>
       </c>
-      <c r="H32" s="19" t="n">
+      <c r="H32" s="18" t="n">
         <f aca="false">$C32+$F32-$G32</f>
         <v>3797</v>
       </c>
-      <c r="I32" s="20"/>
-      <c r="J32" s="21" t="str">
+      <c r="I32" s="19"/>
+      <c r="J32" s="20" t="str">
         <f aca="false">IF($I32="","",$H32*$I32)</f>
         <v/>
       </c>
-      <c r="L32" s="22" t="str">
+      <c r="L32" s="21" t="str">
         <f aca="false">$A32&amp;" - "&amp;$B32</f>
         <v>Primus EU - PUD 100/200</v>
       </c>
-      <c r="M32" s="22" t="n">
+      <c r="M32" s="21" t="n">
         <f aca="false">IF(OR($D32&lt;&gt;0,$E32&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N32" s="22" t="str">
+      <c r="N32" s="21" t="str">
         <f aca="false">IF($M32=1,SUM($M$8:$M32),"")</f>
         <v/>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="B33" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="C33" s="24" t="n">
+      <c r="A33" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="23" t="n">
         <v>4118</v>
       </c>
-      <c r="D33" s="25" t="n">
+      <c r="D33" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L33,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E33" s="25" t="n">
+      <c r="E33" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L33,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F33" s="26" t="n">
+      <c r="F33" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L33)</f>
         <v>0</v>
       </c>
-      <c r="G33" s="26" t="n">
+      <c r="G33" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L33)</f>
         <v>0</v>
       </c>
-      <c r="H33" s="27" t="n">
+      <c r="H33" s="26" t="n">
         <f aca="false">$C33+$F33-$G33</f>
         <v>4118</v>
       </c>
-      <c r="I33" s="20"/>
-      <c r="J33" s="28" t="str">
+      <c r="I33" s="19"/>
+      <c r="J33" s="27" t="str">
         <f aca="false">IF($I33="","",$H33*$I33)</f>
         <v/>
       </c>
-      <c r="L33" s="22" t="str">
+      <c r="L33" s="21" t="str">
         <f aca="false">$A33&amp;" - "&amp;$B33</f>
         <v>Primus EU - PUD 200/300</v>
       </c>
-      <c r="M33" s="22" t="n">
+      <c r="M33" s="21" t="n">
         <f aca="false">IF(OR($D33&lt;&gt;0,$E33&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N33" s="22" t="str">
+      <c r="N33" s="21" t="str">
         <f aca="false">IF($M33=1,SUM($M$8:$M33),"")</f>
         <v/>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C34" s="16" t="n">
+      <c r="A34" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="15" t="n">
         <v>1490</v>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L34,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E34" s="17" t="n">
+      <c r="E34" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L34,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F34" s="18" t="n">
+      <c r="F34" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L34)</f>
         <v>0</v>
       </c>
-      <c r="G34" s="18" t="n">
+      <c r="G34" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L34)</f>
         <v>0</v>
       </c>
-      <c r="H34" s="19" t="n">
+      <c r="H34" s="18" t="n">
         <f aca="false">$C34+$F34-$G34</f>
         <v>1490</v>
       </c>
-      <c r="I34" s="20"/>
-      <c r="J34" s="21" t="str">
+      <c r="I34" s="19"/>
+      <c r="J34" s="20" t="str">
         <f aca="false">IF($I34="","",$H34*$I34)</f>
         <v/>
       </c>
-      <c r="L34" s="22" t="str">
+      <c r="L34" s="21" t="str">
         <f aca="false">$A34&amp;" - "&amp;$B34</f>
         <v>Primus EU - PUD 300/500</v>
       </c>
-      <c r="M34" s="22" t="n">
+      <c r="M34" s="21" t="n">
         <f aca="false">IF(OR($D34&lt;&gt;0,$E34&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N34" s="22" t="str">
+      <c r="N34" s="21" t="str">
         <f aca="false">IF($M34=1,SUM($M$8:$M34),"")</f>
         <v/>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="B35" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="C35" s="24" t="n">
+      <c r="A35" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" s="23" t="n">
         <v>15130</v>
       </c>
-      <c r="D35" s="25" t="n">
+      <c r="D35" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L35,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>52</v>
       </c>
-      <c r="E35" s="25" t="n">
+      <c r="E35" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L35,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F35" s="26" t="n">
+      <c r="F35" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L35)</f>
         <v>52</v>
       </c>
-      <c r="G35" s="26" t="n">
+      <c r="G35" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L35)</f>
         <v>0</v>
       </c>
-      <c r="H35" s="27" t="n">
+      <c r="H35" s="26" t="n">
         <f aca="false">$C35+$F35-$G35</f>
         <v>15182</v>
       </c>
-      <c r="I35" s="20"/>
-      <c r="J35" s="28" t="str">
+      <c r="I35" s="19"/>
+      <c r="J35" s="27" t="str">
         <f aca="false">IF($I35="","",$H35*$I35)</f>
         <v/>
       </c>
-      <c r="L35" s="22" t="str">
+      <c r="L35" s="21" t="str">
         <f aca="false">$A35&amp;" - "&amp;$B35</f>
         <v>Primus EU - BKN</v>
       </c>
-      <c r="M35" s="22" t="n">
+      <c r="M35" s="21" t="n">
         <f aca="false">IF(OR($D35&lt;&gt;0,$E35&lt;&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="N35" s="22" t="n">
+      <c r="N35" s="21" t="n">
         <f aca="false">IF($M35=1,SUM($M$8:$M35),"")</f>
         <v>12</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C36" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="17" t="n">
+      <c r="A36" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L36,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E36" s="17" t="n">
+      <c r="E36" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L36,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F36" s="18" t="n">
+      <c r="F36" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L36)</f>
         <v>0</v>
       </c>
-      <c r="G36" s="18" t="n">
+      <c r="G36" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L36)</f>
         <v>0</v>
       </c>
-      <c r="H36" s="19" t="n">
+      <c r="H36" s="18" t="n">
         <f aca="false">$C36+$F36-$G36</f>
         <v>0</v>
       </c>
-      <c r="I36" s="20"/>
-      <c r="J36" s="21" t="str">
+      <c r="I36" s="19"/>
+      <c r="J36" s="20" t="str">
         <f aca="false">IF($I36="","",$H36*$I36)</f>
         <v/>
       </c>
-      <c r="L36" s="22" t="str">
+      <c r="L36" s="21" t="str">
         <f aca="false">$A36&amp;" - "&amp;$B36</f>
         <v>AMF Brand - PD PVN 100/200</v>
       </c>
-      <c r="M36" s="22" t="n">
+      <c r="M36" s="21" t="n">
         <f aca="false">IF(OR($D36&lt;&gt;0,$E36&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N36" s="22" t="str">
+      <c r="N36" s="21" t="str">
         <f aca="false">IF($M36=1,SUM($M$8:$M36),"")</f>
         <v/>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="B37" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="C37" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="25" t="n">
+      <c r="A37" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L37,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E37" s="25" t="n">
+      <c r="E37" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L37,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F37" s="26" t="n">
+      <c r="F37" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L37)</f>
         <v>0</v>
       </c>
-      <c r="G37" s="26" t="n">
+      <c r="G37" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L37)</f>
         <v>0</v>
       </c>
-      <c r="H37" s="27" t="n">
+      <c r="H37" s="26" t="n">
         <f aca="false">$C37+$F37-$G37</f>
         <v>0</v>
       </c>
-      <c r="I37" s="20"/>
-      <c r="J37" s="28" t="str">
+      <c r="I37" s="19"/>
+      <c r="J37" s="27" t="str">
         <f aca="false">IF($I37="","",$H37*$I37)</f>
         <v/>
       </c>
-      <c r="L37" s="22" t="str">
+      <c r="L37" s="21" t="str">
         <f aca="false">$A37&amp;" - "&amp;$B37</f>
         <v>AMF Brand - PD KKD 100/200</v>
       </c>
-      <c r="M37" s="22" t="n">
+      <c r="M37" s="21" t="n">
         <f aca="false">IF(OR($D37&lt;&gt;0,$E37&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N37" s="22" t="str">
+      <c r="N37" s="21" t="str">
         <f aca="false">IF($M37=1,SUM($M$8:$M37),"")</f>
         <v/>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C38" s="16" t="n">
+      <c r="A38" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="15" t="n">
         <v>1516</v>
       </c>
-      <c r="D38" s="17" t="n">
+      <c r="D38" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L38,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E38" s="17" t="n">
+      <c r="E38" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L38,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F38" s="18" t="n">
+      <c r="F38" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L38)</f>
         <v>0</v>
       </c>
-      <c r="G38" s="18" t="n">
+      <c r="G38" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L38)</f>
         <v>0</v>
       </c>
-      <c r="H38" s="19" t="n">
+      <c r="H38" s="18" t="n">
         <f aca="false">$C38+$F38-$G38</f>
         <v>1516</v>
       </c>
-      <c r="I38" s="20"/>
-      <c r="J38" s="21" t="str">
+      <c r="I38" s="19"/>
+      <c r="J38" s="20" t="str">
         <f aca="false">IF($I38="","",$H38*$I38)</f>
         <v/>
       </c>
-      <c r="L38" s="22" t="str">
+      <c r="L38" s="21" t="str">
         <f aca="false">$A38&amp;" - "&amp;$B38</f>
         <v>AMF Brand - PUD PVN 200/300</v>
       </c>
-      <c r="M38" s="22" t="n">
+      <c r="M38" s="21" t="n">
         <f aca="false">IF(OR($D38&lt;&gt;0,$E38&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N38" s="22" t="str">
+      <c r="N38" s="21" t="str">
         <f aca="false">IF($M38=1,SUM($M$8:$M38),"")</f>
         <v/>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="B39" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="C39" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="25" t="n">
+      <c r="A39" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L39,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E39" s="25" t="n">
+      <c r="E39" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L39,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F39" s="26" t="n">
+      <c r="F39" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L39)</f>
         <v>0</v>
       </c>
-      <c r="G39" s="26" t="n">
+      <c r="G39" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L39)</f>
         <v>0</v>
       </c>
-      <c r="H39" s="27" t="n">
+      <c r="H39" s="26" t="n">
         <f aca="false">$C39+$F39-$G39</f>
         <v>0</v>
       </c>
-      <c r="I39" s="20"/>
-      <c r="J39" s="28" t="str">
+      <c r="I39" s="19"/>
+      <c r="J39" s="27" t="str">
         <f aca="false">IF($I39="","",$H39*$I39)</f>
         <v/>
       </c>
-      <c r="L39" s="22" t="str">
+      <c r="L39" s="21" t="str">
         <f aca="false">$A39&amp;" - "&amp;$B39</f>
         <v>AMF Brand - PUD KKD 200/300</v>
       </c>
-      <c r="M39" s="22" t="n">
+      <c r="M39" s="21" t="n">
         <f aca="false">IF(OR($D39&lt;&gt;0,$E39&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N39" s="22" t="str">
+      <c r="N39" s="21" t="str">
         <f aca="false">IF($M39=1,SUM($M$8:$M39),"")</f>
         <v/>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C40" s="16" t="n">
+      <c r="A40" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="D40" s="17" t="n">
+      <c r="D40" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L40,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E40" s="17" t="n">
+      <c r="E40" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L40,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F40" s="18" t="n">
+      <c r="F40" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L40)</f>
         <v>0</v>
       </c>
-      <c r="G40" s="18" t="n">
+      <c r="G40" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L40)</f>
         <v>0</v>
       </c>
-      <c r="H40" s="19" t="n">
+      <c r="H40" s="18" t="n">
         <f aca="false">$C40+$F40-$G40</f>
         <v>18</v>
       </c>
-      <c r="I40" s="20"/>
-      <c r="J40" s="21" t="str">
+      <c r="I40" s="19"/>
+      <c r="J40" s="20" t="str">
         <f aca="false">IF($I40="","",$H40*$I40)</f>
         <v/>
       </c>
-      <c r="L40" s="22" t="str">
+      <c r="L40" s="21" t="str">
         <f aca="false">$A40&amp;" - "&amp;$B40</f>
         <v>AMF Brand - PUD PVN 300/500</v>
       </c>
-      <c r="M40" s="22" t="n">
+      <c r="M40" s="21" t="n">
         <f aca="false">IF(OR($D40&lt;&gt;0,$E40&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N40" s="22" t="str">
+      <c r="N40" s="21" t="str">
         <f aca="false">IF($M40=1,SUM($M$8:$M40),"")</f>
         <v/>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="B41" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="C41" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="25" t="n">
+      <c r="A41" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B41" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C41" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L41,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E41" s="25" t="n">
+      <c r="E41" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L41,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F41" s="26" t="n">
+      <c r="F41" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L41)</f>
         <v>0</v>
       </c>
-      <c r="G41" s="26" t="n">
+      <c r="G41" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L41)</f>
         <v>0</v>
       </c>
-      <c r="H41" s="27" t="n">
+      <c r="H41" s="26" t="n">
         <f aca="false">$C41+$F41-$G41</f>
         <v>0</v>
       </c>
-      <c r="I41" s="20"/>
-      <c r="J41" s="28" t="str">
+      <c r="I41" s="19"/>
+      <c r="J41" s="27" t="str">
         <f aca="false">IF($I41="","",$H41*$I41)</f>
         <v/>
       </c>
-      <c r="L41" s="22" t="str">
+      <c r="L41" s="21" t="str">
         <f aca="false">$A41&amp;" - "&amp;$B41</f>
         <v>AMF Brand - PUD KKD 300/500</v>
       </c>
-      <c r="M41" s="22" t="n">
+      <c r="M41" s="21" t="n">
         <f aca="false">IF(OR($D41&lt;&gt;0,$E41&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N41" s="22" t="str">
+      <c r="N41" s="21" t="str">
         <f aca="false">IF($M41=1,SUM($M$8:$M41),"")</f>
         <v/>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C42" s="16" t="n">
+      <c r="A42" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C42" s="15" t="n">
         <v>1389</v>
       </c>
-      <c r="D42" s="17" t="n">
+      <c r="D42" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L42,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>1872</v>
       </c>
-      <c r="E42" s="17" t="n">
+      <c r="E42" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L42,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F42" s="18" t="n">
+      <c r="F42" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L42)</f>
         <v>1872</v>
       </c>
-      <c r="G42" s="18" t="n">
+      <c r="G42" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L42)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="19" t="n">
+      <c r="H42" s="18" t="n">
         <f aca="false">$C42+$F42-$G42</f>
         <v>3261</v>
       </c>
-      <c r="I42" s="20"/>
-      <c r="J42" s="21" t="str">
+      <c r="I42" s="19"/>
+      <c r="J42" s="20" t="str">
         <f aca="false">IF($I42="","",$H42*$I42)</f>
         <v/>
       </c>
-      <c r="L42" s="22" t="str">
+      <c r="L42" s="21" t="str">
         <f aca="false">$A42&amp;" - "&amp;$B42</f>
         <v>THT Brand - PUD PVN 80/120</v>
       </c>
-      <c r="M42" s="22" t="n">
+      <c r="M42" s="21" t="n">
         <f aca="false">IF(OR($D42&lt;&gt;0,$E42&lt;&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="N42" s="22" t="n">
+      <c r="N42" s="21" t="n">
         <f aca="false">IF($M42=1,SUM($M$8:$M42),"")</f>
         <v>13</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="B43" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="C43" s="24" t="n">
+      <c r="A43" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B43" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" s="23" t="n">
         <v>7055</v>
       </c>
-      <c r="D43" s="25" t="n">
+      <c r="D43" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L43,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>600</v>
       </c>
-      <c r="E43" s="25" t="n">
+      <c r="E43" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L43,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F43" s="26" t="n">
+      <c r="F43" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L43)</f>
         <v>600</v>
       </c>
-      <c r="G43" s="26" t="n">
+      <c r="G43" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L43)</f>
         <v>0</v>
       </c>
-      <c r="H43" s="27" t="n">
+      <c r="H43" s="26" t="n">
         <f aca="false">$C43+$F43-$G43</f>
         <v>7655</v>
       </c>
-      <c r="I43" s="20"/>
-      <c r="J43" s="28" t="str">
+      <c r="I43" s="19"/>
+      <c r="J43" s="27" t="str">
         <f aca="false">IF($I43="","",$H43*$I43)</f>
         <v/>
       </c>
-      <c r="L43" s="22" t="str">
+      <c r="L43" s="21" t="str">
         <f aca="false">$A43&amp;" - "&amp;$B43</f>
         <v>THT Brand - PUD PVN 100/200</v>
       </c>
-      <c r="M43" s="22" t="n">
+      <c r="M43" s="21" t="n">
         <f aca="false">IF(OR($D43&lt;&gt;0,$E43&lt;&gt;0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="N43" s="22" t="n">
+      <c r="N43" s="21" t="n">
         <f aca="false">IF($M43=1,SUM($M$8:$M43),"")</f>
         <v>14</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B44" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C44" s="16" t="n">
+      <c r="A44" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" s="15" t="n">
         <v>4682</v>
       </c>
-      <c r="D44" s="17" t="n">
+      <c r="D44" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L44,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E44" s="17" t="n">
+      <c r="E44" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L44,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F44" s="18" t="n">
+      <c r="F44" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L44)</f>
         <v>0</v>
       </c>
-      <c r="G44" s="18" t="n">
+      <c r="G44" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L44)</f>
         <v>0</v>
       </c>
-      <c r="H44" s="19" t="n">
+      <c r="H44" s="18" t="n">
         <f aca="false">$C44+$F44-$G44</f>
         <v>4682</v>
       </c>
-      <c r="I44" s="20"/>
-      <c r="J44" s="21" t="str">
+      <c r="I44" s="19"/>
+      <c r="J44" s="20" t="str">
         <f aca="false">IF($I44="","",$H44*$I44)</f>
         <v/>
       </c>
-      <c r="L44" s="22" t="str">
+      <c r="L44" s="21" t="str">
         <f aca="false">$A44&amp;" - "&amp;$B44</f>
         <v>THT Brand - PUD PVN 200/300</v>
       </c>
-      <c r="M44" s="22" t="n">
+      <c r="M44" s="21" t="n">
         <f aca="false">IF(OR($D44&lt;&gt;0,$E44&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N44" s="22" t="str">
+      <c r="N44" s="21" t="str">
         <f aca="false">IF($M44=1,SUM($M$8:$M44),"")</f>
         <v/>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="B45" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C45" s="24" t="n">
+      <c r="A45" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="B45" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="C45" s="23" t="n">
         <v>670</v>
       </c>
-      <c r="D45" s="25" t="n">
+      <c r="D45" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L45,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E45" s="25" t="n">
+      <c r="E45" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L45,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F45" s="26" t="n">
+      <c r="F45" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L45)</f>
         <v>0</v>
       </c>
-      <c r="G45" s="26" t="n">
+      <c r="G45" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L45)</f>
         <v>0</v>
       </c>
-      <c r="H45" s="27" t="n">
+      <c r="H45" s="26" t="n">
         <f aca="false">$C45+$F45-$G45</f>
         <v>670</v>
       </c>
-      <c r="I45" s="20"/>
-      <c r="J45" s="28" t="str">
+      <c r="I45" s="19"/>
+      <c r="J45" s="27" t="str">
         <f aca="false">IF($I45="","",$H45*$I45)</f>
         <v/>
       </c>
-      <c r="L45" s="22" t="str">
+      <c r="L45" s="21" t="str">
         <f aca="false">$A45&amp;" - "&amp;$B45</f>
         <v>Deepsea - 300/500</v>
       </c>
-      <c r="M45" s="22" t="n">
+      <c r="M45" s="21" t="n">
         <f aca="false">IF(OR($D45&lt;&gt;0,$E45&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N45" s="22" t="str">
+      <c r="N45" s="21" t="str">
         <f aca="false">IF($M45=1,SUM($M$8:$M45),"")</f>
         <v/>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="B46" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C46" s="16" t="n">
+      <c r="A46" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" s="15" t="n">
         <v>451</v>
       </c>
-      <c r="D46" s="17" t="n">
+      <c r="D46" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L46,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E46" s="17" t="n">
+      <c r="E46" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L46,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F46" s="18" t="n">
+      <c r="F46" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L46)</f>
         <v>0</v>
       </c>
-      <c r="G46" s="18" t="n">
+      <c r="G46" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L46)</f>
         <v>0</v>
       </c>
-      <c r="H46" s="19" t="n">
+      <c r="H46" s="18" t="n">
         <f aca="false">$C46+$F46-$G46</f>
         <v>451</v>
       </c>
-      <c r="I46" s="20"/>
-      <c r="J46" s="21" t="str">
+      <c r="I46" s="19"/>
+      <c r="J46" s="20" t="str">
         <f aca="false">IF($I46="","",$H46*$I46)</f>
         <v/>
       </c>
-      <c r="L46" s="22" t="str">
+      <c r="L46" s="21" t="str">
         <f aca="false">$A46&amp;" - "&amp;$B46</f>
         <v>China - PUD PVN 300/500</v>
       </c>
-      <c r="M46" s="22" t="n">
+      <c r="M46" s="21" t="n">
         <f aca="false">IF(OR($D46&lt;&gt;0,$E46&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N46" s="22" t="str">
+      <c r="N46" s="21" t="str">
         <f aca="false">IF($M46=1,SUM($M$8:$M46),"")</f>
         <v/>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="B47" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="C47" s="24" t="n">
+      <c r="A47" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="B47" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47" s="23" t="n">
         <v>188</v>
       </c>
-      <c r="D47" s="25" t="n">
+      <c r="D47" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L47,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E47" s="25" t="n">
+      <c r="E47" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L47,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F47" s="26" t="n">
+      <c r="F47" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L47)</f>
         <v>0</v>
       </c>
-      <c r="G47" s="26" t="n">
+      <c r="G47" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L47)</f>
         <v>0</v>
       </c>
-      <c r="H47" s="27" t="n">
+      <c r="H47" s="26" t="n">
         <f aca="false">$C47+$F47-$G47</f>
         <v>188</v>
       </c>
-      <c r="I47" s="20"/>
-      <c r="J47" s="28" t="str">
+      <c r="I47" s="19"/>
+      <c r="J47" s="27" t="str">
         <f aca="false">IF($I47="","",$H47*$I47)</f>
         <v/>
       </c>
-      <c r="L47" s="22" t="str">
+      <c r="L47" s="21" t="str">
         <f aca="false">$A47&amp;" - "&amp;$B47</f>
         <v>China - PUD KKD 300/500</v>
       </c>
-      <c r="M47" s="22" t="n">
+      <c r="M47" s="21" t="n">
         <f aca="false">IF(OR($D47&lt;&gt;0,$E47&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N47" s="22" t="str">
+      <c r="N47" s="21" t="str">
         <f aca="false">IF($M47=1,SUM($M$8:$M47),"")</f>
         <v/>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="B48" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C48" s="16" t="n">
+      <c r="A48" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C48" s="15" t="n">
         <v>401</v>
       </c>
-      <c r="D48" s="17" t="n">
+      <c r="D48" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L48,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E48" s="17" t="n">
+      <c r="E48" s="16" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L48,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F48" s="18" t="n">
+      <c r="F48" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L48)</f>
         <v>0</v>
       </c>
-      <c r="G48" s="18" t="n">
+      <c r="G48" s="17" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L48)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="19" t="n">
+      <c r="H48" s="18" t="n">
         <f aca="false">$C48+$F48-$G48</f>
         <v>401</v>
       </c>
-      <c r="I48" s="20"/>
-      <c r="J48" s="21" t="str">
+      <c r="I48" s="19"/>
+      <c r="J48" s="20" t="str">
         <f aca="false">IF($I48="","",$H48*$I48)</f>
         <v/>
       </c>
-      <c r="L48" s="22" t="str">
+      <c r="L48" s="21" t="str">
         <f aca="false">$A48&amp;" - "&amp;$B48</f>
         <v>China - PUD PVN 500/800</v>
       </c>
-      <c r="M48" s="22" t="n">
+      <c r="M48" s="21" t="n">
         <f aca="false">IF(OR($D48&lt;&gt;0,$E48&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N48" s="22" t="str">
+      <c r="N48" s="21" t="str">
         <f aca="false">IF($M48=1,SUM($M$8:$M48),"")</f>
         <v/>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="B49" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C49" s="24" t="n">
+      <c r="A49" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C49" s="23" t="n">
         <v>1920</v>
       </c>
-      <c r="D49" s="25" t="n">
+      <c r="D49" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L49,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="E49" s="25" t="n">
+      <c r="E49" s="24" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L49,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
         <v>0</v>
       </c>
-      <c r="F49" s="26" t="n">
+      <c r="F49" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L49)</f>
         <v>0</v>
       </c>
-      <c r="G49" s="26" t="n">
+      <c r="G49" s="25" t="n">
         <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L49)</f>
         <v>0</v>
       </c>
-      <c r="H49" s="27" t="n">
+      <c r="H49" s="26" t="n">
         <f aca="false">$C49+$F49-$G49</f>
         <v>1920</v>
       </c>
-      <c r="I49" s="20"/>
-      <c r="J49" s="28" t="str">
+      <c r="I49" s="19"/>
+      <c r="J49" s="27" t="str">
         <f aca="false">IF($I49="","",$H49*$I49)</f>
         <v/>
       </c>
-      <c r="L49" s="22" t="str">
+      <c r="L49" s="21" t="str">
         <f aca="false">$A49&amp;" - "&amp;$B49</f>
         <v>China - PUD KKD 500/800</v>
       </c>
-      <c r="M49" s="22" t="n">
+      <c r="M49" s="21" t="n">
         <f aca="false">IF(OR($D49&lt;&gt;0,$E49&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="N49" s="22" t="str">
+      <c r="N49" s="21" t="str">
         <f aca="false">IF($M49=1,SUM($M$8:$M49),"")</f>
         <v/>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="B50" s="29"/>
-      <c r="C50" s="30" t="n">
+      <c r="A50" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="B50" s="28"/>
+      <c r="C50" s="29" t="n">
         <f aca="false">SUM(C8:C49)</f>
         <v>102870</v>
       </c>
-      <c r="D50" s="31" t="n">
+      <c r="D50" s="30" t="n">
         <f aca="false">SUM(D8:D49)</f>
         <v>4880</v>
       </c>
-      <c r="E50" s="31" t="n">
+      <c r="E50" s="30" t="n">
         <f aca="false">SUM(E8:E49)</f>
         <v>0</v>
       </c>
-      <c r="F50" s="30" t="n">
+      <c r="F50" s="29" t="n">
         <f aca="false">SUM(F8:F49)</f>
         <v>4880</v>
       </c>
-      <c r="G50" s="30" t="n">
+      <c r="G50" s="29" t="n">
         <f aca="false">SUM(G8:G49)</f>
         <v>0</v>
       </c>
-      <c r="H50" s="30" t="n">
+      <c r="H50" s="29" t="n">
         <f aca="false">SUM(H8:H49)</f>
         <v>107750</v>
       </c>
-      <c r="I50" s="29"/>
-      <c r="J50" s="32" t="str">
+      <c r="I50" s="28"/>
+      <c r="J50" s="31" t="str">
         <f aca="false">IF(SUM(J8:J49)=0,"",SUM(J8:J49))</f>
         <v/>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="10" t="s">
-        <v>82</v>
+      <c r="A52" s="9" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" password="df10" objects="true" scenarios="true" autoFilter="false"/>
   <autoFilter ref="A7:J49"/>
   <conditionalFormatting sqref="H8:H49">
     <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
@@ -3964,10 +4007,10 @@
   <dimension ref="A1:K250"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="81" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="82" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="83" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="84" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="6"/>
   </cols>
@@ -3979,1875 +4022,1876 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="G4" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="J4" s="34" t="n">
+      <c r="A4" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="J4" s="36" t="n">
         <f aca="false">SUMPRODUCT((B7:B5000&lt;&gt;"")*(COUNTIF(Stock!$L$8:$L$49,B7:B5000)=0))</f>
         <v>0</v>
       </c>
-      <c r="K4" s="10" t="s">
-        <v>86</v>
+      <c r="K4" s="9" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="A6" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>91</v>
       </c>
+      <c r="C6" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="35" t="n">
+      <c r="A7" s="37" t="n">
         <v>46254</v>
       </c>
-      <c r="B7" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="C7" s="37" t="n">
+      <c r="B7" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="39" t="n">
         <v>1068</v>
       </c>
-      <c r="D7" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="38" t="s">
-        <v>93</v>
+      <c r="D7" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="40" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="35" t="n">
+      <c r="A8" s="37" t="n">
         <v>46254</v>
       </c>
-      <c r="B8" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="C8" s="37" t="n">
+      <c r="B8" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="39" t="n">
         <v>65</v>
       </c>
-      <c r="D8" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="38"/>
+      <c r="D8" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="40"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="35" t="n">
+      <c r="A9" s="37" t="n">
         <v>46254</v>
       </c>
-      <c r="B9" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="C9" s="37" t="n">
+      <c r="B9" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="39" t="n">
         <v>267</v>
       </c>
-      <c r="D9" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="38"/>
+      <c r="D9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="40"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="35" t="n">
+      <c r="A10" s="37" t="n">
         <v>46254</v>
       </c>
-      <c r="B10" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="C10" s="37" t="n">
+      <c r="B10" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="39" t="n">
         <v>29</v>
       </c>
-      <c r="D10" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="38"/>
+      <c r="D10" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="40"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="35" t="n">
+      <c r="A11" s="37" t="n">
         <v>46254</v>
       </c>
-      <c r="B11" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="C11" s="37" t="n">
+      <c r="B11" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="39" t="n">
         <v>39</v>
       </c>
-      <c r="D11" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="38"/>
+      <c r="D11" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="40"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="35" t="n">
+      <c r="A12" s="37" t="n">
         <v>46254</v>
       </c>
-      <c r="B12" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="C12" s="37" t="n">
+      <c r="B12" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="39" t="n">
         <v>50</v>
       </c>
-      <c r="D12" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="38"/>
+      <c r="D12" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="40"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="35" t="n">
+      <c r="A13" s="37" t="n">
         <v>46254</v>
       </c>
-      <c r="B13" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="C13" s="37" t="n">
+      <c r="B13" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="38"/>
+      <c r="D13" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="40"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="35" t="n">
+      <c r="A14" s="37" t="n">
         <v>46254</v>
       </c>
-      <c r="B14" s="36" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" s="37" t="n">
+      <c r="B14" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="39" t="n">
         <v>50</v>
       </c>
-      <c r="D14" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="38"/>
+      <c r="D14" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="40"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="35" t="n">
+      <c r="A15" s="37" t="n">
         <v>46254</v>
       </c>
-      <c r="B15" s="36" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="37" t="n">
+      <c r="B15" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="39" t="n">
         <v>33</v>
       </c>
-      <c r="D15" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="38"/>
+      <c r="D15" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="40"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="35" t="n">
+      <c r="A16" s="37" t="n">
         <v>46254</v>
       </c>
-      <c r="B16" s="36" t="s">
-        <v>102</v>
-      </c>
-      <c r="C16" s="37" t="n">
+      <c r="B16" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="39" t="n">
         <v>156</v>
       </c>
-      <c r="D16" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="38"/>
+      <c r="D16" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="40"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="35" t="n">
+      <c r="A17" s="37" t="n">
         <v>46254</v>
       </c>
-      <c r="B17" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="C17" s="37" t="n">
+      <c r="B17" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="39" t="n">
         <v>596</v>
       </c>
-      <c r="D17" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="38"/>
+      <c r="D17" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="40"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="35" t="n">
+      <c r="A18" s="37" t="n">
         <v>46254</v>
       </c>
-      <c r="B18" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="C18" s="37" t="n">
+      <c r="B18" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="39" t="n">
         <v>52</v>
       </c>
-      <c r="D18" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="38"/>
+      <c r="D18" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="40"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="35" t="n">
+      <c r="A19" s="37" t="n">
         <v>46254</v>
       </c>
-      <c r="B19" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="C19" s="37" t="n">
+      <c r="B19" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" s="39" t="n">
         <v>1872</v>
       </c>
-      <c r="D19" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="38"/>
+      <c r="D19" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="40"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="35" t="n">
+      <c r="A20" s="37" t="n">
         <v>46254</v>
       </c>
-      <c r="B20" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="C20" s="37" t="n">
+      <c r="B20" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="D20" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="38"/>
+      <c r="D20" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="40"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="35"/>
-      <c r="B21" s="36"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="36"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="38"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="35"/>
-      <c r="B22" s="36"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="36"/>
+      <c r="A22" s="37"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="38"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="35"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="36"/>
+      <c r="A23" s="37"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="38"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="35"/>
-      <c r="B24" s="36"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="36"/>
+      <c r="A24" s="37"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="38"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="35"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="36"/>
+      <c r="A25" s="37"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="38"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="35"/>
-      <c r="B26" s="36"/>
-      <c r="C26" s="37"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="36"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="38"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="35"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="36"/>
+      <c r="A27" s="37"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="38"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="35"/>
-      <c r="B28" s="36"/>
-      <c r="C28" s="37"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="36"/>
+      <c r="A28" s="37"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="38"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="35"/>
-      <c r="B29" s="36"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="36"/>
+      <c r="A29" s="37"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="38"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="35"/>
-      <c r="B30" s="36"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="36"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="38"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="35"/>
-      <c r="B31" s="36"/>
-      <c r="C31" s="37"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="36"/>
+      <c r="A31" s="37"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="38"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="35"/>
-      <c r="B32" s="36"/>
-      <c r="C32" s="37"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="36"/>
+      <c r="A32" s="37"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="38"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="35"/>
-      <c r="B33" s="36"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="36"/>
+      <c r="A33" s="37"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="38"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="35"/>
-      <c r="B34" s="36"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="36"/>
+      <c r="A34" s="37"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="38"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="35"/>
-      <c r="B35" s="36"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="36"/>
+      <c r="A35" s="37"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="38"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="35"/>
-      <c r="B36" s="36"/>
-      <c r="C36" s="37"/>
-      <c r="D36" s="37"/>
-      <c r="E36" s="36"/>
+      <c r="A36" s="37"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="38"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="35"/>
-      <c r="B37" s="36"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="37"/>
-      <c r="E37" s="36"/>
+      <c r="A37" s="37"/>
+      <c r="B37" s="38"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="38"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="35"/>
-      <c r="B38" s="36"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="37"/>
-      <c r="E38" s="36"/>
+      <c r="A38" s="37"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="38"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="35"/>
-      <c r="B39" s="36"/>
-      <c r="C39" s="37"/>
-      <c r="D39" s="37"/>
-      <c r="E39" s="36"/>
+      <c r="A39" s="37"/>
+      <c r="B39" s="38"/>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="38"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="35"/>
-      <c r="B40" s="36"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="36"/>
+      <c r="A40" s="37"/>
+      <c r="B40" s="38"/>
+      <c r="C40" s="39"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="38"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="35"/>
-      <c r="B41" s="36"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="36"/>
+      <c r="A41" s="37"/>
+      <c r="B41" s="38"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="38"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="35"/>
-      <c r="B42" s="36"/>
-      <c r="C42" s="37"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="36"/>
+      <c r="A42" s="37"/>
+      <c r="B42" s="38"/>
+      <c r="C42" s="39"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="38"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="35"/>
-      <c r="B43" s="36"/>
-      <c r="C43" s="37"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="36"/>
+      <c r="A43" s="37"/>
+      <c r="B43" s="38"/>
+      <c r="C43" s="39"/>
+      <c r="D43" s="39"/>
+      <c r="E43" s="38"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="35"/>
-      <c r="B44" s="36"/>
-      <c r="C44" s="37"/>
-      <c r="D44" s="37"/>
-      <c r="E44" s="36"/>
+      <c r="A44" s="37"/>
+      <c r="B44" s="38"/>
+      <c r="C44" s="39"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="38"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="35"/>
-      <c r="B45" s="36"/>
-      <c r="C45" s="37"/>
-      <c r="D45" s="37"/>
-      <c r="E45" s="36"/>
+      <c r="A45" s="37"/>
+      <c r="B45" s="38"/>
+      <c r="C45" s="39"/>
+      <c r="D45" s="39"/>
+      <c r="E45" s="38"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="35"/>
-      <c r="B46" s="36"/>
-      <c r="C46" s="37"/>
-      <c r="D46" s="37"/>
-      <c r="E46" s="36"/>
+      <c r="A46" s="37"/>
+      <c r="B46" s="38"/>
+      <c r="C46" s="39"/>
+      <c r="D46" s="39"/>
+      <c r="E46" s="38"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="35"/>
-      <c r="B47" s="36"/>
-      <c r="C47" s="37"/>
-      <c r="D47" s="37"/>
-      <c r="E47" s="36"/>
+      <c r="A47" s="37"/>
+      <c r="B47" s="38"/>
+      <c r="C47" s="39"/>
+      <c r="D47" s="39"/>
+      <c r="E47" s="38"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="35"/>
-      <c r="B48" s="36"/>
-      <c r="C48" s="37"/>
-      <c r="D48" s="37"/>
-      <c r="E48" s="36"/>
+      <c r="A48" s="37"/>
+      <c r="B48" s="38"/>
+      <c r="C48" s="39"/>
+      <c r="D48" s="39"/>
+      <c r="E48" s="38"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="35"/>
-      <c r="B49" s="36"/>
-      <c r="C49" s="37"/>
-      <c r="D49" s="37"/>
-      <c r="E49" s="36"/>
+      <c r="A49" s="37"/>
+      <c r="B49" s="38"/>
+      <c r="C49" s="39"/>
+      <c r="D49" s="39"/>
+      <c r="E49" s="38"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="35"/>
-      <c r="B50" s="36"/>
-      <c r="C50" s="37"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="36"/>
+      <c r="A50" s="37"/>
+      <c r="B50" s="38"/>
+      <c r="C50" s="39"/>
+      <c r="D50" s="39"/>
+      <c r="E50" s="38"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="35"/>
-      <c r="B51" s="36"/>
-      <c r="C51" s="37"/>
-      <c r="D51" s="37"/>
-      <c r="E51" s="36"/>
+      <c r="A51" s="37"/>
+      <c r="B51" s="38"/>
+      <c r="C51" s="39"/>
+      <c r="D51" s="39"/>
+      <c r="E51" s="38"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="35"/>
-      <c r="B52" s="36"/>
-      <c r="C52" s="37"/>
-      <c r="D52" s="37"/>
-      <c r="E52" s="36"/>
+      <c r="A52" s="37"/>
+      <c r="B52" s="38"/>
+      <c r="C52" s="39"/>
+      <c r="D52" s="39"/>
+      <c r="E52" s="38"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="35"/>
-      <c r="B53" s="36"/>
-      <c r="C53" s="37"/>
-      <c r="D53" s="37"/>
-      <c r="E53" s="36"/>
+      <c r="A53" s="37"/>
+      <c r="B53" s="38"/>
+      <c r="C53" s="39"/>
+      <c r="D53" s="39"/>
+      <c r="E53" s="38"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="35"/>
-      <c r="B54" s="36"/>
-      <c r="C54" s="37"/>
-      <c r="D54" s="37"/>
-      <c r="E54" s="36"/>
+      <c r="A54" s="37"/>
+      <c r="B54" s="38"/>
+      <c r="C54" s="39"/>
+      <c r="D54" s="39"/>
+      <c r="E54" s="38"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="35"/>
-      <c r="B55" s="36"/>
-      <c r="C55" s="37"/>
-      <c r="D55" s="37"/>
-      <c r="E55" s="36"/>
+      <c r="A55" s="37"/>
+      <c r="B55" s="38"/>
+      <c r="C55" s="39"/>
+      <c r="D55" s="39"/>
+      <c r="E55" s="38"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="35"/>
-      <c r="B56" s="36"/>
-      <c r="C56" s="37"/>
-      <c r="D56" s="37"/>
-      <c r="E56" s="36"/>
+      <c r="A56" s="37"/>
+      <c r="B56" s="38"/>
+      <c r="C56" s="39"/>
+      <c r="D56" s="39"/>
+      <c r="E56" s="38"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="35"/>
-      <c r="B57" s="36"/>
-      <c r="C57" s="37"/>
-      <c r="D57" s="37"/>
-      <c r="E57" s="36"/>
+      <c r="A57" s="37"/>
+      <c r="B57" s="38"/>
+      <c r="C57" s="39"/>
+      <c r="D57" s="39"/>
+      <c r="E57" s="38"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="35"/>
-      <c r="B58" s="36"/>
-      <c r="C58" s="37"/>
-      <c r="D58" s="37"/>
-      <c r="E58" s="36"/>
+      <c r="A58" s="37"/>
+      <c r="B58" s="38"/>
+      <c r="C58" s="39"/>
+      <c r="D58" s="39"/>
+      <c r="E58" s="38"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="35"/>
-      <c r="B59" s="36"/>
-      <c r="C59" s="37"/>
-      <c r="D59" s="37"/>
-      <c r="E59" s="36"/>
+      <c r="A59" s="37"/>
+      <c r="B59" s="38"/>
+      <c r="C59" s="39"/>
+      <c r="D59" s="39"/>
+      <c r="E59" s="38"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="35"/>
-      <c r="B60" s="36"/>
-      <c r="C60" s="37"/>
-      <c r="D60" s="37"/>
-      <c r="E60" s="36"/>
+      <c r="A60" s="37"/>
+      <c r="B60" s="38"/>
+      <c r="C60" s="39"/>
+      <c r="D60" s="39"/>
+      <c r="E60" s="38"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="35"/>
-      <c r="B61" s="36"/>
-      <c r="C61" s="37"/>
-      <c r="D61" s="37"/>
-      <c r="E61" s="36"/>
+      <c r="A61" s="37"/>
+      <c r="B61" s="38"/>
+      <c r="C61" s="39"/>
+      <c r="D61" s="39"/>
+      <c r="E61" s="38"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="35"/>
-      <c r="B62" s="36"/>
-      <c r="C62" s="37"/>
-      <c r="D62" s="37"/>
-      <c r="E62" s="36"/>
+      <c r="A62" s="37"/>
+      <c r="B62" s="38"/>
+      <c r="C62" s="39"/>
+      <c r="D62" s="39"/>
+      <c r="E62" s="38"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="35"/>
-      <c r="B63" s="36"/>
-      <c r="C63" s="37"/>
-      <c r="D63" s="37"/>
-      <c r="E63" s="36"/>
+      <c r="A63" s="37"/>
+      <c r="B63" s="38"/>
+      <c r="C63" s="39"/>
+      <c r="D63" s="39"/>
+      <c r="E63" s="38"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="35"/>
-      <c r="B64" s="36"/>
-      <c r="C64" s="37"/>
-      <c r="D64" s="37"/>
-      <c r="E64" s="36"/>
+      <c r="A64" s="37"/>
+      <c r="B64" s="38"/>
+      <c r="C64" s="39"/>
+      <c r="D64" s="39"/>
+      <c r="E64" s="38"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="35"/>
-      <c r="B65" s="36"/>
-      <c r="C65" s="37"/>
-      <c r="D65" s="37"/>
-      <c r="E65" s="36"/>
+      <c r="A65" s="37"/>
+      <c r="B65" s="38"/>
+      <c r="C65" s="39"/>
+      <c r="D65" s="39"/>
+      <c r="E65" s="38"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="35"/>
-      <c r="B66" s="36"/>
-      <c r="C66" s="37"/>
-      <c r="D66" s="37"/>
-      <c r="E66" s="36"/>
+      <c r="A66" s="37"/>
+      <c r="B66" s="38"/>
+      <c r="C66" s="39"/>
+      <c r="D66" s="39"/>
+      <c r="E66" s="38"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="35"/>
-      <c r="B67" s="36"/>
-      <c r="C67" s="37"/>
-      <c r="D67" s="37"/>
-      <c r="E67" s="36"/>
+      <c r="A67" s="37"/>
+      <c r="B67" s="38"/>
+      <c r="C67" s="39"/>
+      <c r="D67" s="39"/>
+      <c r="E67" s="38"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="35"/>
-      <c r="B68" s="36"/>
-      <c r="C68" s="37"/>
-      <c r="D68" s="37"/>
-      <c r="E68" s="36"/>
+      <c r="A68" s="37"/>
+      <c r="B68" s="38"/>
+      <c r="C68" s="39"/>
+      <c r="D68" s="39"/>
+      <c r="E68" s="38"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="35"/>
-      <c r="B69" s="36"/>
-      <c r="C69" s="37"/>
-      <c r="D69" s="37"/>
-      <c r="E69" s="36"/>
+      <c r="A69" s="37"/>
+      <c r="B69" s="38"/>
+      <c r="C69" s="39"/>
+      <c r="D69" s="39"/>
+      <c r="E69" s="38"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="35"/>
-      <c r="B70" s="36"/>
-      <c r="C70" s="37"/>
-      <c r="D70" s="37"/>
-      <c r="E70" s="36"/>
+      <c r="A70" s="37"/>
+      <c r="B70" s="38"/>
+      <c r="C70" s="39"/>
+      <c r="D70" s="39"/>
+      <c r="E70" s="38"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="35"/>
-      <c r="B71" s="36"/>
-      <c r="C71" s="37"/>
-      <c r="D71" s="37"/>
-      <c r="E71" s="36"/>
+      <c r="A71" s="37"/>
+      <c r="B71" s="38"/>
+      <c r="C71" s="39"/>
+      <c r="D71" s="39"/>
+      <c r="E71" s="38"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="35"/>
-      <c r="B72" s="36"/>
-      <c r="C72" s="37"/>
-      <c r="D72" s="37"/>
-      <c r="E72" s="36"/>
+      <c r="A72" s="37"/>
+      <c r="B72" s="38"/>
+      <c r="C72" s="39"/>
+      <c r="D72" s="39"/>
+      <c r="E72" s="38"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="35"/>
-      <c r="B73" s="36"/>
-      <c r="C73" s="37"/>
-      <c r="D73" s="37"/>
-      <c r="E73" s="36"/>
+      <c r="A73" s="37"/>
+      <c r="B73" s="38"/>
+      <c r="C73" s="39"/>
+      <c r="D73" s="39"/>
+      <c r="E73" s="38"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="35"/>
-      <c r="B74" s="36"/>
-      <c r="C74" s="37"/>
-      <c r="D74" s="37"/>
-      <c r="E74" s="36"/>
+      <c r="A74" s="37"/>
+      <c r="B74" s="38"/>
+      <c r="C74" s="39"/>
+      <c r="D74" s="39"/>
+      <c r="E74" s="38"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="35"/>
-      <c r="B75" s="36"/>
-      <c r="C75" s="37"/>
-      <c r="D75" s="37"/>
-      <c r="E75" s="36"/>
+      <c r="A75" s="37"/>
+      <c r="B75" s="38"/>
+      <c r="C75" s="39"/>
+      <c r="D75" s="39"/>
+      <c r="E75" s="38"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="35"/>
-      <c r="B76" s="36"/>
-      <c r="C76" s="37"/>
-      <c r="D76" s="37"/>
-      <c r="E76" s="36"/>
+      <c r="A76" s="37"/>
+      <c r="B76" s="38"/>
+      <c r="C76" s="39"/>
+      <c r="D76" s="39"/>
+      <c r="E76" s="38"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="35"/>
-      <c r="B77" s="36"/>
-      <c r="C77" s="37"/>
-      <c r="D77" s="37"/>
-      <c r="E77" s="36"/>
+      <c r="A77" s="37"/>
+      <c r="B77" s="38"/>
+      <c r="C77" s="39"/>
+      <c r="D77" s="39"/>
+      <c r="E77" s="38"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="35"/>
-      <c r="B78" s="36"/>
-      <c r="C78" s="37"/>
-      <c r="D78" s="37"/>
-      <c r="E78" s="36"/>
+      <c r="A78" s="37"/>
+      <c r="B78" s="38"/>
+      <c r="C78" s="39"/>
+      <c r="D78" s="39"/>
+      <c r="E78" s="38"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="35"/>
-      <c r="B79" s="36"/>
-      <c r="C79" s="37"/>
-      <c r="D79" s="37"/>
-      <c r="E79" s="36"/>
+      <c r="A79" s="37"/>
+      <c r="B79" s="38"/>
+      <c r="C79" s="39"/>
+      <c r="D79" s="39"/>
+      <c r="E79" s="38"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="35"/>
-      <c r="B80" s="36"/>
-      <c r="C80" s="37"/>
-      <c r="D80" s="37"/>
-      <c r="E80" s="36"/>
+      <c r="A80" s="37"/>
+      <c r="B80" s="38"/>
+      <c r="C80" s="39"/>
+      <c r="D80" s="39"/>
+      <c r="E80" s="38"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="35"/>
-      <c r="B81" s="36"/>
-      <c r="C81" s="37"/>
-      <c r="D81" s="37"/>
-      <c r="E81" s="36"/>
+      <c r="A81" s="37"/>
+      <c r="B81" s="38"/>
+      <c r="C81" s="39"/>
+      <c r="D81" s="39"/>
+      <c r="E81" s="38"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="35"/>
-      <c r="B82" s="36"/>
-      <c r="C82" s="37"/>
-      <c r="D82" s="37"/>
-      <c r="E82" s="36"/>
+      <c r="A82" s="37"/>
+      <c r="B82" s="38"/>
+      <c r="C82" s="39"/>
+      <c r="D82" s="39"/>
+      <c r="E82" s="38"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="35"/>
-      <c r="B83" s="36"/>
-      <c r="C83" s="37"/>
-      <c r="D83" s="37"/>
-      <c r="E83" s="36"/>
+      <c r="A83" s="37"/>
+      <c r="B83" s="38"/>
+      <c r="C83" s="39"/>
+      <c r="D83" s="39"/>
+      <c r="E83" s="38"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="35"/>
-      <c r="B84" s="36"/>
-      <c r="C84" s="37"/>
-      <c r="D84" s="37"/>
-      <c r="E84" s="36"/>
+      <c r="A84" s="37"/>
+      <c r="B84" s="38"/>
+      <c r="C84" s="39"/>
+      <c r="D84" s="39"/>
+      <c r="E84" s="38"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="35"/>
-      <c r="B85" s="36"/>
-      <c r="C85" s="37"/>
-      <c r="D85" s="37"/>
-      <c r="E85" s="36"/>
+      <c r="A85" s="37"/>
+      <c r="B85" s="38"/>
+      <c r="C85" s="39"/>
+      <c r="D85" s="39"/>
+      <c r="E85" s="38"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="35"/>
-      <c r="B86" s="36"/>
-      <c r="C86" s="37"/>
-      <c r="D86" s="37"/>
-      <c r="E86" s="36"/>
+      <c r="A86" s="37"/>
+      <c r="B86" s="38"/>
+      <c r="C86" s="39"/>
+      <c r="D86" s="39"/>
+      <c r="E86" s="38"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="35"/>
-      <c r="B87" s="36"/>
-      <c r="C87" s="37"/>
-      <c r="D87" s="37"/>
-      <c r="E87" s="36"/>
+      <c r="A87" s="37"/>
+      <c r="B87" s="38"/>
+      <c r="C87" s="39"/>
+      <c r="D87" s="39"/>
+      <c r="E87" s="38"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="35"/>
-      <c r="B88" s="36"/>
-      <c r="C88" s="37"/>
-      <c r="D88" s="37"/>
-      <c r="E88" s="36"/>
+      <c r="A88" s="37"/>
+      <c r="B88" s="38"/>
+      <c r="C88" s="39"/>
+      <c r="D88" s="39"/>
+      <c r="E88" s="38"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="35"/>
-      <c r="B89" s="36"/>
-      <c r="C89" s="37"/>
-      <c r="D89" s="37"/>
-      <c r="E89" s="36"/>
+      <c r="A89" s="37"/>
+      <c r="B89" s="38"/>
+      <c r="C89" s="39"/>
+      <c r="D89" s="39"/>
+      <c r="E89" s="38"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="35"/>
-      <c r="B90" s="36"/>
-      <c r="C90" s="37"/>
-      <c r="D90" s="37"/>
-      <c r="E90" s="36"/>
+      <c r="A90" s="37"/>
+      <c r="B90" s="38"/>
+      <c r="C90" s="39"/>
+      <c r="D90" s="39"/>
+      <c r="E90" s="38"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="35"/>
-      <c r="B91" s="36"/>
-      <c r="C91" s="37"/>
-      <c r="D91" s="37"/>
-      <c r="E91" s="36"/>
+      <c r="A91" s="37"/>
+      <c r="B91" s="38"/>
+      <c r="C91" s="39"/>
+      <c r="D91" s="39"/>
+      <c r="E91" s="38"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="35"/>
-      <c r="B92" s="36"/>
-      <c r="C92" s="37"/>
-      <c r="D92" s="37"/>
-      <c r="E92" s="36"/>
+      <c r="A92" s="37"/>
+      <c r="B92" s="38"/>
+      <c r="C92" s="39"/>
+      <c r="D92" s="39"/>
+      <c r="E92" s="38"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="35"/>
-      <c r="B93" s="36"/>
-      <c r="C93" s="37"/>
-      <c r="D93" s="37"/>
-      <c r="E93" s="36"/>
+      <c r="A93" s="37"/>
+      <c r="B93" s="38"/>
+      <c r="C93" s="39"/>
+      <c r="D93" s="39"/>
+      <c r="E93" s="38"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="35"/>
-      <c r="B94" s="36"/>
-      <c r="C94" s="37"/>
-      <c r="D94" s="37"/>
-      <c r="E94" s="36"/>
+      <c r="A94" s="37"/>
+      <c r="B94" s="38"/>
+      <c r="C94" s="39"/>
+      <c r="D94" s="39"/>
+      <c r="E94" s="38"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="35"/>
-      <c r="B95" s="36"/>
-      <c r="C95" s="37"/>
-      <c r="D95" s="37"/>
-      <c r="E95" s="36"/>
+      <c r="A95" s="37"/>
+      <c r="B95" s="38"/>
+      <c r="C95" s="39"/>
+      <c r="D95" s="39"/>
+      <c r="E95" s="38"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="35"/>
-      <c r="B96" s="36"/>
-      <c r="C96" s="37"/>
-      <c r="D96" s="37"/>
-      <c r="E96" s="36"/>
+      <c r="A96" s="37"/>
+      <c r="B96" s="38"/>
+      <c r="C96" s="39"/>
+      <c r="D96" s="39"/>
+      <c r="E96" s="38"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="35"/>
-      <c r="B97" s="36"/>
-      <c r="C97" s="37"/>
-      <c r="D97" s="37"/>
-      <c r="E97" s="36"/>
+      <c r="A97" s="37"/>
+      <c r="B97" s="38"/>
+      <c r="C97" s="39"/>
+      <c r="D97" s="39"/>
+      <c r="E97" s="38"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="35"/>
-      <c r="B98" s="36"/>
-      <c r="C98" s="37"/>
-      <c r="D98" s="37"/>
-      <c r="E98" s="36"/>
+      <c r="A98" s="37"/>
+      <c r="B98" s="38"/>
+      <c r="C98" s="39"/>
+      <c r="D98" s="39"/>
+      <c r="E98" s="38"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="35"/>
-      <c r="B99" s="36"/>
-      <c r="C99" s="37"/>
-      <c r="D99" s="37"/>
-      <c r="E99" s="36"/>
+      <c r="A99" s="37"/>
+      <c r="B99" s="38"/>
+      <c r="C99" s="39"/>
+      <c r="D99" s="39"/>
+      <c r="E99" s="38"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="35"/>
-      <c r="B100" s="36"/>
-      <c r="C100" s="37"/>
-      <c r="D100" s="37"/>
-      <c r="E100" s="36"/>
+      <c r="A100" s="37"/>
+      <c r="B100" s="38"/>
+      <c r="C100" s="39"/>
+      <c r="D100" s="39"/>
+      <c r="E100" s="38"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="35"/>
-      <c r="B101" s="36"/>
-      <c r="C101" s="37"/>
-      <c r="D101" s="37"/>
-      <c r="E101" s="36"/>
+      <c r="A101" s="37"/>
+      <c r="B101" s="38"/>
+      <c r="C101" s="39"/>
+      <c r="D101" s="39"/>
+      <c r="E101" s="38"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="35"/>
-      <c r="B102" s="36"/>
-      <c r="C102" s="37"/>
-      <c r="D102" s="37"/>
-      <c r="E102" s="36"/>
+      <c r="A102" s="37"/>
+      <c r="B102" s="38"/>
+      <c r="C102" s="39"/>
+      <c r="D102" s="39"/>
+      <c r="E102" s="38"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="35"/>
-      <c r="B103" s="36"/>
-      <c r="C103" s="37"/>
-      <c r="D103" s="37"/>
-      <c r="E103" s="36"/>
+      <c r="A103" s="37"/>
+      <c r="B103" s="38"/>
+      <c r="C103" s="39"/>
+      <c r="D103" s="39"/>
+      <c r="E103" s="38"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="35"/>
-      <c r="B104" s="36"/>
-      <c r="C104" s="37"/>
-      <c r="D104" s="37"/>
-      <c r="E104" s="36"/>
+      <c r="A104" s="37"/>
+      <c r="B104" s="38"/>
+      <c r="C104" s="39"/>
+      <c r="D104" s="39"/>
+      <c r="E104" s="38"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="35"/>
-      <c r="B105" s="36"/>
-      <c r="C105" s="37"/>
-      <c r="D105" s="37"/>
-      <c r="E105" s="36"/>
+      <c r="A105" s="37"/>
+      <c r="B105" s="38"/>
+      <c r="C105" s="39"/>
+      <c r="D105" s="39"/>
+      <c r="E105" s="38"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="35"/>
-      <c r="B106" s="36"/>
-      <c r="C106" s="37"/>
-      <c r="D106" s="37"/>
-      <c r="E106" s="36"/>
+      <c r="A106" s="37"/>
+      <c r="B106" s="38"/>
+      <c r="C106" s="39"/>
+      <c r="D106" s="39"/>
+      <c r="E106" s="38"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="35"/>
-      <c r="B107" s="36"/>
-      <c r="C107" s="37"/>
-      <c r="D107" s="37"/>
-      <c r="E107" s="36"/>
+      <c r="A107" s="37"/>
+      <c r="B107" s="38"/>
+      <c r="C107" s="39"/>
+      <c r="D107" s="39"/>
+      <c r="E107" s="38"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="35"/>
-      <c r="B108" s="36"/>
-      <c r="C108" s="37"/>
-      <c r="D108" s="37"/>
-      <c r="E108" s="36"/>
+      <c r="A108" s="37"/>
+      <c r="B108" s="38"/>
+      <c r="C108" s="39"/>
+      <c r="D108" s="39"/>
+      <c r="E108" s="38"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="35"/>
-      <c r="B109" s="36"/>
-      <c r="C109" s="37"/>
-      <c r="D109" s="37"/>
-      <c r="E109" s="36"/>
+      <c r="A109" s="37"/>
+      <c r="B109" s="38"/>
+      <c r="C109" s="39"/>
+      <c r="D109" s="39"/>
+      <c r="E109" s="38"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="35"/>
-      <c r="B110" s="36"/>
-      <c r="C110" s="37"/>
-      <c r="D110" s="37"/>
-      <c r="E110" s="36"/>
+      <c r="A110" s="37"/>
+      <c r="B110" s="38"/>
+      <c r="C110" s="39"/>
+      <c r="D110" s="39"/>
+      <c r="E110" s="38"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="35"/>
-      <c r="B111" s="36"/>
-      <c r="C111" s="37"/>
-      <c r="D111" s="37"/>
-      <c r="E111" s="36"/>
+      <c r="A111" s="37"/>
+      <c r="B111" s="38"/>
+      <c r="C111" s="39"/>
+      <c r="D111" s="39"/>
+      <c r="E111" s="38"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="35"/>
-      <c r="B112" s="36"/>
-      <c r="C112" s="37"/>
-      <c r="D112" s="37"/>
-      <c r="E112" s="36"/>
+      <c r="A112" s="37"/>
+      <c r="B112" s="38"/>
+      <c r="C112" s="39"/>
+      <c r="D112" s="39"/>
+      <c r="E112" s="38"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="35"/>
-      <c r="B113" s="36"/>
-      <c r="C113" s="37"/>
-      <c r="D113" s="37"/>
-      <c r="E113" s="36"/>
+      <c r="A113" s="37"/>
+      <c r="B113" s="38"/>
+      <c r="C113" s="39"/>
+      <c r="D113" s="39"/>
+      <c r="E113" s="38"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="35"/>
-      <c r="B114" s="36"/>
-      <c r="C114" s="37"/>
-      <c r="D114" s="37"/>
-      <c r="E114" s="36"/>
+      <c r="A114" s="37"/>
+      <c r="B114" s="38"/>
+      <c r="C114" s="39"/>
+      <c r="D114" s="39"/>
+      <c r="E114" s="38"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="35"/>
-      <c r="B115" s="36"/>
-      <c r="C115" s="37"/>
-      <c r="D115" s="37"/>
-      <c r="E115" s="36"/>
+      <c r="A115" s="37"/>
+      <c r="B115" s="38"/>
+      <c r="C115" s="39"/>
+      <c r="D115" s="39"/>
+      <c r="E115" s="38"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="35"/>
-      <c r="B116" s="36"/>
-      <c r="C116" s="37"/>
-      <c r="D116" s="37"/>
-      <c r="E116" s="36"/>
+      <c r="A116" s="37"/>
+      <c r="B116" s="38"/>
+      <c r="C116" s="39"/>
+      <c r="D116" s="39"/>
+      <c r="E116" s="38"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="35"/>
-      <c r="B117" s="36"/>
-      <c r="C117" s="37"/>
-      <c r="D117" s="37"/>
-      <c r="E117" s="36"/>
+      <c r="A117" s="37"/>
+      <c r="B117" s="38"/>
+      <c r="C117" s="39"/>
+      <c r="D117" s="39"/>
+      <c r="E117" s="38"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="35"/>
-      <c r="B118" s="36"/>
-      <c r="C118" s="37"/>
-      <c r="D118" s="37"/>
-      <c r="E118" s="36"/>
+      <c r="A118" s="37"/>
+      <c r="B118" s="38"/>
+      <c r="C118" s="39"/>
+      <c r="D118" s="39"/>
+      <c r="E118" s="38"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="35"/>
-      <c r="B119" s="36"/>
-      <c r="C119" s="37"/>
-      <c r="D119" s="37"/>
-      <c r="E119" s="36"/>
+      <c r="A119" s="37"/>
+      <c r="B119" s="38"/>
+      <c r="C119" s="39"/>
+      <c r="D119" s="39"/>
+      <c r="E119" s="38"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="35"/>
-      <c r="B120" s="36"/>
-      <c r="C120" s="37"/>
-      <c r="D120" s="37"/>
-      <c r="E120" s="36"/>
+      <c r="A120" s="37"/>
+      <c r="B120" s="38"/>
+      <c r="C120" s="39"/>
+      <c r="D120" s="39"/>
+      <c r="E120" s="38"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="35"/>
-      <c r="B121" s="36"/>
-      <c r="C121" s="37"/>
-      <c r="D121" s="37"/>
-      <c r="E121" s="36"/>
+      <c r="A121" s="37"/>
+      <c r="B121" s="38"/>
+      <c r="C121" s="39"/>
+      <c r="D121" s="39"/>
+      <c r="E121" s="38"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="35"/>
-      <c r="B122" s="36"/>
-      <c r="C122" s="37"/>
-      <c r="D122" s="37"/>
-      <c r="E122" s="36"/>
+      <c r="A122" s="37"/>
+      <c r="B122" s="38"/>
+      <c r="C122" s="39"/>
+      <c r="D122" s="39"/>
+      <c r="E122" s="38"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="35"/>
-      <c r="B123" s="36"/>
-      <c r="C123" s="37"/>
-      <c r="D123" s="37"/>
-      <c r="E123" s="36"/>
+      <c r="A123" s="37"/>
+      <c r="B123" s="38"/>
+      <c r="C123" s="39"/>
+      <c r="D123" s="39"/>
+      <c r="E123" s="38"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="35"/>
-      <c r="B124" s="36"/>
-      <c r="C124" s="37"/>
-      <c r="D124" s="37"/>
-      <c r="E124" s="36"/>
+      <c r="A124" s="37"/>
+      <c r="B124" s="38"/>
+      <c r="C124" s="39"/>
+      <c r="D124" s="39"/>
+      <c r="E124" s="38"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="35"/>
-      <c r="B125" s="36"/>
-      <c r="C125" s="37"/>
-      <c r="D125" s="37"/>
-      <c r="E125" s="36"/>
+      <c r="A125" s="37"/>
+      <c r="B125" s="38"/>
+      <c r="C125" s="39"/>
+      <c r="D125" s="39"/>
+      <c r="E125" s="38"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="35"/>
-      <c r="B126" s="36"/>
-      <c r="C126" s="37"/>
-      <c r="D126" s="37"/>
-      <c r="E126" s="36"/>
+      <c r="A126" s="37"/>
+      <c r="B126" s="38"/>
+      <c r="C126" s="39"/>
+      <c r="D126" s="39"/>
+      <c r="E126" s="38"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="35"/>
-      <c r="B127" s="36"/>
-      <c r="C127" s="37"/>
-      <c r="D127" s="37"/>
-      <c r="E127" s="36"/>
+      <c r="A127" s="37"/>
+      <c r="B127" s="38"/>
+      <c r="C127" s="39"/>
+      <c r="D127" s="39"/>
+      <c r="E127" s="38"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="35"/>
-      <c r="B128" s="36"/>
-      <c r="C128" s="37"/>
-      <c r="D128" s="37"/>
-      <c r="E128" s="36"/>
+      <c r="A128" s="37"/>
+      <c r="B128" s="38"/>
+      <c r="C128" s="39"/>
+      <c r="D128" s="39"/>
+      <c r="E128" s="38"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="35"/>
-      <c r="B129" s="36"/>
-      <c r="C129" s="37"/>
-      <c r="D129" s="37"/>
-      <c r="E129" s="36"/>
+      <c r="A129" s="37"/>
+      <c r="B129" s="38"/>
+      <c r="C129" s="39"/>
+      <c r="D129" s="39"/>
+      <c r="E129" s="38"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="35"/>
-      <c r="B130" s="36"/>
-      <c r="C130" s="37"/>
-      <c r="D130" s="37"/>
-      <c r="E130" s="36"/>
+      <c r="A130" s="37"/>
+      <c r="B130" s="38"/>
+      <c r="C130" s="39"/>
+      <c r="D130" s="39"/>
+      <c r="E130" s="38"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="35"/>
-      <c r="B131" s="36"/>
-      <c r="C131" s="37"/>
-      <c r="D131" s="37"/>
-      <c r="E131" s="36"/>
+      <c r="A131" s="37"/>
+      <c r="B131" s="38"/>
+      <c r="C131" s="39"/>
+      <c r="D131" s="39"/>
+      <c r="E131" s="38"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="35"/>
-      <c r="B132" s="36"/>
-      <c r="C132" s="37"/>
-      <c r="D132" s="37"/>
-      <c r="E132" s="36"/>
+      <c r="A132" s="37"/>
+      <c r="B132" s="38"/>
+      <c r="C132" s="39"/>
+      <c r="D132" s="39"/>
+      <c r="E132" s="38"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="35"/>
-      <c r="B133" s="36"/>
-      <c r="C133" s="37"/>
-      <c r="D133" s="37"/>
-      <c r="E133" s="36"/>
+      <c r="A133" s="37"/>
+      <c r="B133" s="38"/>
+      <c r="C133" s="39"/>
+      <c r="D133" s="39"/>
+      <c r="E133" s="38"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="35"/>
-      <c r="B134" s="36"/>
-      <c r="C134" s="37"/>
-      <c r="D134" s="37"/>
-      <c r="E134" s="36"/>
+      <c r="A134" s="37"/>
+      <c r="B134" s="38"/>
+      <c r="C134" s="39"/>
+      <c r="D134" s="39"/>
+      <c r="E134" s="38"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="35"/>
-      <c r="B135" s="36"/>
-      <c r="C135" s="37"/>
-      <c r="D135" s="37"/>
-      <c r="E135" s="36"/>
+      <c r="A135" s="37"/>
+      <c r="B135" s="38"/>
+      <c r="C135" s="39"/>
+      <c r="D135" s="39"/>
+      <c r="E135" s="38"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="35"/>
-      <c r="B136" s="36"/>
-      <c r="C136" s="37"/>
-      <c r="D136" s="37"/>
-      <c r="E136" s="36"/>
+      <c r="A136" s="37"/>
+      <c r="B136" s="38"/>
+      <c r="C136" s="39"/>
+      <c r="D136" s="39"/>
+      <c r="E136" s="38"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="35"/>
-      <c r="B137" s="36"/>
-      <c r="C137" s="37"/>
-      <c r="D137" s="37"/>
-      <c r="E137" s="36"/>
+      <c r="A137" s="37"/>
+      <c r="B137" s="38"/>
+      <c r="C137" s="39"/>
+      <c r="D137" s="39"/>
+      <c r="E137" s="38"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="35"/>
-      <c r="B138" s="36"/>
-      <c r="C138" s="37"/>
-      <c r="D138" s="37"/>
-      <c r="E138" s="36"/>
+      <c r="A138" s="37"/>
+      <c r="B138" s="38"/>
+      <c r="C138" s="39"/>
+      <c r="D138" s="39"/>
+      <c r="E138" s="38"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="35"/>
-      <c r="B139" s="36"/>
-      <c r="C139" s="37"/>
-      <c r="D139" s="37"/>
-      <c r="E139" s="36"/>
+      <c r="A139" s="37"/>
+      <c r="B139" s="38"/>
+      <c r="C139" s="39"/>
+      <c r="D139" s="39"/>
+      <c r="E139" s="38"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="35"/>
-      <c r="B140" s="36"/>
-      <c r="C140" s="37"/>
-      <c r="D140" s="37"/>
-      <c r="E140" s="36"/>
+      <c r="A140" s="37"/>
+      <c r="B140" s="38"/>
+      <c r="C140" s="39"/>
+      <c r="D140" s="39"/>
+      <c r="E140" s="38"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="35"/>
-      <c r="B141" s="36"/>
-      <c r="C141" s="37"/>
-      <c r="D141" s="37"/>
-      <c r="E141" s="36"/>
+      <c r="A141" s="37"/>
+      <c r="B141" s="38"/>
+      <c r="C141" s="39"/>
+      <c r="D141" s="39"/>
+      <c r="E141" s="38"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="35"/>
-      <c r="B142" s="36"/>
-      <c r="C142" s="37"/>
-      <c r="D142" s="37"/>
-      <c r="E142" s="36"/>
+      <c r="A142" s="37"/>
+      <c r="B142" s="38"/>
+      <c r="C142" s="39"/>
+      <c r="D142" s="39"/>
+      <c r="E142" s="38"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="35"/>
-      <c r="B143" s="36"/>
-      <c r="C143" s="37"/>
-      <c r="D143" s="37"/>
-      <c r="E143" s="36"/>
+      <c r="A143" s="37"/>
+      <c r="B143" s="38"/>
+      <c r="C143" s="39"/>
+      <c r="D143" s="39"/>
+      <c r="E143" s="38"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="35"/>
-      <c r="B144" s="36"/>
-      <c r="C144" s="37"/>
-      <c r="D144" s="37"/>
-      <c r="E144" s="36"/>
+      <c r="A144" s="37"/>
+      <c r="B144" s="38"/>
+      <c r="C144" s="39"/>
+      <c r="D144" s="39"/>
+      <c r="E144" s="38"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="35"/>
-      <c r="B145" s="36"/>
-      <c r="C145" s="37"/>
-      <c r="D145" s="37"/>
-      <c r="E145" s="36"/>
+      <c r="A145" s="37"/>
+      <c r="B145" s="38"/>
+      <c r="C145" s="39"/>
+      <c r="D145" s="39"/>
+      <c r="E145" s="38"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="35"/>
-      <c r="B146" s="36"/>
-      <c r="C146" s="37"/>
-      <c r="D146" s="37"/>
-      <c r="E146" s="36"/>
+      <c r="A146" s="37"/>
+      <c r="B146" s="38"/>
+      <c r="C146" s="39"/>
+      <c r="D146" s="39"/>
+      <c r="E146" s="38"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="35"/>
-      <c r="B147" s="36"/>
-      <c r="C147" s="37"/>
-      <c r="D147" s="37"/>
-      <c r="E147" s="36"/>
+      <c r="A147" s="37"/>
+      <c r="B147" s="38"/>
+      <c r="C147" s="39"/>
+      <c r="D147" s="39"/>
+      <c r="E147" s="38"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="35"/>
-      <c r="B148" s="36"/>
-      <c r="C148" s="37"/>
-      <c r="D148" s="37"/>
-      <c r="E148" s="36"/>
+      <c r="A148" s="37"/>
+      <c r="B148" s="38"/>
+      <c r="C148" s="39"/>
+      <c r="D148" s="39"/>
+      <c r="E148" s="38"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="35"/>
-      <c r="B149" s="36"/>
-      <c r="C149" s="37"/>
-      <c r="D149" s="37"/>
-      <c r="E149" s="36"/>
+      <c r="A149" s="37"/>
+      <c r="B149" s="38"/>
+      <c r="C149" s="39"/>
+      <c r="D149" s="39"/>
+      <c r="E149" s="38"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="35"/>
-      <c r="B150" s="36"/>
-      <c r="C150" s="37"/>
-      <c r="D150" s="37"/>
-      <c r="E150" s="36"/>
+      <c r="A150" s="37"/>
+      <c r="B150" s="38"/>
+      <c r="C150" s="39"/>
+      <c r="D150" s="39"/>
+      <c r="E150" s="38"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="35"/>
-      <c r="B151" s="36"/>
-      <c r="C151" s="37"/>
-      <c r="D151" s="37"/>
-      <c r="E151" s="36"/>
+      <c r="A151" s="37"/>
+      <c r="B151" s="38"/>
+      <c r="C151" s="39"/>
+      <c r="D151" s="39"/>
+      <c r="E151" s="38"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="35"/>
-      <c r="B152" s="36"/>
-      <c r="C152" s="37"/>
-      <c r="D152" s="37"/>
-      <c r="E152" s="36"/>
+      <c r="A152" s="37"/>
+      <c r="B152" s="38"/>
+      <c r="C152" s="39"/>
+      <c r="D152" s="39"/>
+      <c r="E152" s="38"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="35"/>
-      <c r="B153" s="36"/>
-      <c r="C153" s="37"/>
-      <c r="D153" s="37"/>
-      <c r="E153" s="36"/>
+      <c r="A153" s="37"/>
+      <c r="B153" s="38"/>
+      <c r="C153" s="39"/>
+      <c r="D153" s="39"/>
+      <c r="E153" s="38"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="35"/>
-      <c r="B154" s="36"/>
-      <c r="C154" s="37"/>
-      <c r="D154" s="37"/>
-      <c r="E154" s="36"/>
+      <c r="A154" s="37"/>
+      <c r="B154" s="38"/>
+      <c r="C154" s="39"/>
+      <c r="D154" s="39"/>
+      <c r="E154" s="38"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="35"/>
-      <c r="B155" s="36"/>
-      <c r="C155" s="37"/>
-      <c r="D155" s="37"/>
-      <c r="E155" s="36"/>
+      <c r="A155" s="37"/>
+      <c r="B155" s="38"/>
+      <c r="C155" s="39"/>
+      <c r="D155" s="39"/>
+      <c r="E155" s="38"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="35"/>
-      <c r="B156" s="36"/>
-      <c r="C156" s="37"/>
-      <c r="D156" s="37"/>
-      <c r="E156" s="36"/>
+      <c r="A156" s="37"/>
+      <c r="B156" s="38"/>
+      <c r="C156" s="39"/>
+      <c r="D156" s="39"/>
+      <c r="E156" s="38"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="35"/>
-      <c r="B157" s="36"/>
-      <c r="C157" s="37"/>
-      <c r="D157" s="37"/>
-      <c r="E157" s="36"/>
+      <c r="A157" s="37"/>
+      <c r="B157" s="38"/>
+      <c r="C157" s="39"/>
+      <c r="D157" s="39"/>
+      <c r="E157" s="38"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="35"/>
-      <c r="B158" s="36"/>
-      <c r="C158" s="37"/>
-      <c r="D158" s="37"/>
-      <c r="E158" s="36"/>
+      <c r="A158" s="37"/>
+      <c r="B158" s="38"/>
+      <c r="C158" s="39"/>
+      <c r="D158" s="39"/>
+      <c r="E158" s="38"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="35"/>
-      <c r="B159" s="36"/>
-      <c r="C159" s="37"/>
-      <c r="D159" s="37"/>
-      <c r="E159" s="36"/>
+      <c r="A159" s="37"/>
+      <c r="B159" s="38"/>
+      <c r="C159" s="39"/>
+      <c r="D159" s="39"/>
+      <c r="E159" s="38"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="35"/>
-      <c r="B160" s="36"/>
-      <c r="C160" s="37"/>
-      <c r="D160" s="37"/>
-      <c r="E160" s="36"/>
+      <c r="A160" s="37"/>
+      <c r="B160" s="38"/>
+      <c r="C160" s="39"/>
+      <c r="D160" s="39"/>
+      <c r="E160" s="38"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="35"/>
-      <c r="B161" s="36"/>
-      <c r="C161" s="37"/>
-      <c r="D161" s="37"/>
-      <c r="E161" s="36"/>
+      <c r="A161" s="37"/>
+      <c r="B161" s="38"/>
+      <c r="C161" s="39"/>
+      <c r="D161" s="39"/>
+      <c r="E161" s="38"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="35"/>
-      <c r="B162" s="36"/>
-      <c r="C162" s="37"/>
-      <c r="D162" s="37"/>
-      <c r="E162" s="36"/>
+      <c r="A162" s="37"/>
+      <c r="B162" s="38"/>
+      <c r="C162" s="39"/>
+      <c r="D162" s="39"/>
+      <c r="E162" s="38"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="35"/>
-      <c r="B163" s="36"/>
-      <c r="C163" s="37"/>
-      <c r="D163" s="37"/>
-      <c r="E163" s="36"/>
+      <c r="A163" s="37"/>
+      <c r="B163" s="38"/>
+      <c r="C163" s="39"/>
+      <c r="D163" s="39"/>
+      <c r="E163" s="38"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="35"/>
-      <c r="B164" s="36"/>
-      <c r="C164" s="37"/>
-      <c r="D164" s="37"/>
-      <c r="E164" s="36"/>
+      <c r="A164" s="37"/>
+      <c r="B164" s="38"/>
+      <c r="C164" s="39"/>
+      <c r="D164" s="39"/>
+      <c r="E164" s="38"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="35"/>
-      <c r="B165" s="36"/>
-      <c r="C165" s="37"/>
-      <c r="D165" s="37"/>
-      <c r="E165" s="36"/>
+      <c r="A165" s="37"/>
+      <c r="B165" s="38"/>
+      <c r="C165" s="39"/>
+      <c r="D165" s="39"/>
+      <c r="E165" s="38"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="35"/>
-      <c r="B166" s="36"/>
-      <c r="C166" s="37"/>
-      <c r="D166" s="37"/>
-      <c r="E166" s="36"/>
+      <c r="A166" s="37"/>
+      <c r="B166" s="38"/>
+      <c r="C166" s="39"/>
+      <c r="D166" s="39"/>
+      <c r="E166" s="38"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="35"/>
-      <c r="B167" s="36"/>
-      <c r="C167" s="37"/>
-      <c r="D167" s="37"/>
-      <c r="E167" s="36"/>
+      <c r="A167" s="37"/>
+      <c r="B167" s="38"/>
+      <c r="C167" s="39"/>
+      <c r="D167" s="39"/>
+      <c r="E167" s="38"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="35"/>
-      <c r="B168" s="36"/>
-      <c r="C168" s="37"/>
-      <c r="D168" s="37"/>
-      <c r="E168" s="36"/>
+      <c r="A168" s="37"/>
+      <c r="B168" s="38"/>
+      <c r="C168" s="39"/>
+      <c r="D168" s="39"/>
+      <c r="E168" s="38"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="35"/>
-      <c r="B169" s="36"/>
-      <c r="C169" s="37"/>
-      <c r="D169" s="37"/>
-      <c r="E169" s="36"/>
+      <c r="A169" s="37"/>
+      <c r="B169" s="38"/>
+      <c r="C169" s="39"/>
+      <c r="D169" s="39"/>
+      <c r="E169" s="38"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="35"/>
-      <c r="B170" s="36"/>
-      <c r="C170" s="37"/>
-      <c r="D170" s="37"/>
-      <c r="E170" s="36"/>
+      <c r="A170" s="37"/>
+      <c r="B170" s="38"/>
+      <c r="C170" s="39"/>
+      <c r="D170" s="39"/>
+      <c r="E170" s="38"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="35"/>
-      <c r="B171" s="36"/>
-      <c r="C171" s="37"/>
-      <c r="D171" s="37"/>
-      <c r="E171" s="36"/>
+      <c r="A171" s="37"/>
+      <c r="B171" s="38"/>
+      <c r="C171" s="39"/>
+      <c r="D171" s="39"/>
+      <c r="E171" s="38"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="35"/>
-      <c r="B172" s="36"/>
-      <c r="C172" s="37"/>
-      <c r="D172" s="37"/>
-      <c r="E172" s="36"/>
+      <c r="A172" s="37"/>
+      <c r="B172" s="38"/>
+      <c r="C172" s="39"/>
+      <c r="D172" s="39"/>
+      <c r="E172" s="38"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="35"/>
-      <c r="B173" s="36"/>
-      <c r="C173" s="37"/>
-      <c r="D173" s="37"/>
-      <c r="E173" s="36"/>
+      <c r="A173" s="37"/>
+      <c r="B173" s="38"/>
+      <c r="C173" s="39"/>
+      <c r="D173" s="39"/>
+      <c r="E173" s="38"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="35"/>
-      <c r="B174" s="36"/>
-      <c r="C174" s="37"/>
-      <c r="D174" s="37"/>
-      <c r="E174" s="36"/>
+      <c r="A174" s="37"/>
+      <c r="B174" s="38"/>
+      <c r="C174" s="39"/>
+      <c r="D174" s="39"/>
+      <c r="E174" s="38"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="35"/>
-      <c r="B175" s="36"/>
-      <c r="C175" s="37"/>
-      <c r="D175" s="37"/>
-      <c r="E175" s="36"/>
+      <c r="A175" s="37"/>
+      <c r="B175" s="38"/>
+      <c r="C175" s="39"/>
+      <c r="D175" s="39"/>
+      <c r="E175" s="38"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="35"/>
-      <c r="B176" s="36"/>
-      <c r="C176" s="37"/>
-      <c r="D176" s="37"/>
-      <c r="E176" s="36"/>
+      <c r="A176" s="37"/>
+      <c r="B176" s="38"/>
+      <c r="C176" s="39"/>
+      <c r="D176" s="39"/>
+      <c r="E176" s="38"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="35"/>
-      <c r="B177" s="36"/>
-      <c r="C177" s="37"/>
-      <c r="D177" s="37"/>
-      <c r="E177" s="36"/>
+      <c r="A177" s="37"/>
+      <c r="B177" s="38"/>
+      <c r="C177" s="39"/>
+      <c r="D177" s="39"/>
+      <c r="E177" s="38"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="35"/>
-      <c r="B178" s="36"/>
-      <c r="C178" s="37"/>
-      <c r="D178" s="37"/>
-      <c r="E178" s="36"/>
+      <c r="A178" s="37"/>
+      <c r="B178" s="38"/>
+      <c r="C178" s="39"/>
+      <c r="D178" s="39"/>
+      <c r="E178" s="38"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="35"/>
-      <c r="B179" s="36"/>
-      <c r="C179" s="37"/>
-      <c r="D179" s="37"/>
-      <c r="E179" s="36"/>
+      <c r="A179" s="37"/>
+      <c r="B179" s="38"/>
+      <c r="C179" s="39"/>
+      <c r="D179" s="39"/>
+      <c r="E179" s="38"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="35"/>
-      <c r="B180" s="36"/>
-      <c r="C180" s="37"/>
-      <c r="D180" s="37"/>
-      <c r="E180" s="36"/>
+      <c r="A180" s="37"/>
+      <c r="B180" s="38"/>
+      <c r="C180" s="39"/>
+      <c r="D180" s="39"/>
+      <c r="E180" s="38"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="35"/>
-      <c r="B181" s="36"/>
-      <c r="C181" s="37"/>
-      <c r="D181" s="37"/>
-      <c r="E181" s="36"/>
+      <c r="A181" s="37"/>
+      <c r="B181" s="38"/>
+      <c r="C181" s="39"/>
+      <c r="D181" s="39"/>
+      <c r="E181" s="38"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="35"/>
-      <c r="B182" s="36"/>
-      <c r="C182" s="37"/>
-      <c r="D182" s="37"/>
-      <c r="E182" s="36"/>
+      <c r="A182" s="37"/>
+      <c r="B182" s="38"/>
+      <c r="C182" s="39"/>
+      <c r="D182" s="39"/>
+      <c r="E182" s="38"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="35"/>
-      <c r="B183" s="36"/>
-      <c r="C183" s="37"/>
-      <c r="D183" s="37"/>
-      <c r="E183" s="36"/>
+      <c r="A183" s="37"/>
+      <c r="B183" s="38"/>
+      <c r="C183" s="39"/>
+      <c r="D183" s="39"/>
+      <c r="E183" s="38"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="35"/>
-      <c r="B184" s="36"/>
-      <c r="C184" s="37"/>
-      <c r="D184" s="37"/>
-      <c r="E184" s="36"/>
+      <c r="A184" s="37"/>
+      <c r="B184" s="38"/>
+      <c r="C184" s="39"/>
+      <c r="D184" s="39"/>
+      <c r="E184" s="38"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="35"/>
-      <c r="B185" s="36"/>
-      <c r="C185" s="37"/>
-      <c r="D185" s="37"/>
-      <c r="E185" s="36"/>
+      <c r="A185" s="37"/>
+      <c r="B185" s="38"/>
+      <c r="C185" s="39"/>
+      <c r="D185" s="39"/>
+      <c r="E185" s="38"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="35"/>
-      <c r="B186" s="36"/>
-      <c r="C186" s="37"/>
-      <c r="D186" s="37"/>
-      <c r="E186" s="36"/>
+      <c r="A186" s="37"/>
+      <c r="B186" s="38"/>
+      <c r="C186" s="39"/>
+      <c r="D186" s="39"/>
+      <c r="E186" s="38"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="35"/>
-      <c r="B187" s="36"/>
-      <c r="C187" s="37"/>
-      <c r="D187" s="37"/>
-      <c r="E187" s="36"/>
+      <c r="A187" s="37"/>
+      <c r="B187" s="38"/>
+      <c r="C187" s="39"/>
+      <c r="D187" s="39"/>
+      <c r="E187" s="38"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="35"/>
-      <c r="B188" s="36"/>
-      <c r="C188" s="37"/>
-      <c r="D188" s="37"/>
-      <c r="E188" s="36"/>
+      <c r="A188" s="37"/>
+      <c r="B188" s="38"/>
+      <c r="C188" s="39"/>
+      <c r="D188" s="39"/>
+      <c r="E188" s="38"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="35"/>
-      <c r="B189" s="36"/>
-      <c r="C189" s="37"/>
-      <c r="D189" s="37"/>
-      <c r="E189" s="36"/>
+      <c r="A189" s="37"/>
+      <c r="B189" s="38"/>
+      <c r="C189" s="39"/>
+      <c r="D189" s="39"/>
+      <c r="E189" s="38"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="35"/>
-      <c r="B190" s="36"/>
-      <c r="C190" s="37"/>
-      <c r="D190" s="37"/>
-      <c r="E190" s="36"/>
+      <c r="A190" s="37"/>
+      <c r="B190" s="38"/>
+      <c r="C190" s="39"/>
+      <c r="D190" s="39"/>
+      <c r="E190" s="38"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="35"/>
-      <c r="B191" s="36"/>
-      <c r="C191" s="37"/>
-      <c r="D191" s="37"/>
-      <c r="E191" s="36"/>
+      <c r="A191" s="37"/>
+      <c r="B191" s="38"/>
+      <c r="C191" s="39"/>
+      <c r="D191" s="39"/>
+      <c r="E191" s="38"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="35"/>
-      <c r="B192" s="36"/>
-      <c r="C192" s="37"/>
-      <c r="D192" s="37"/>
-      <c r="E192" s="36"/>
+      <c r="A192" s="37"/>
+      <c r="B192" s="38"/>
+      <c r="C192" s="39"/>
+      <c r="D192" s="39"/>
+      <c r="E192" s="38"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="35"/>
-      <c r="B193" s="36"/>
-      <c r="C193" s="37"/>
-      <c r="D193" s="37"/>
-      <c r="E193" s="36"/>
+      <c r="A193" s="37"/>
+      <c r="B193" s="38"/>
+      <c r="C193" s="39"/>
+      <c r="D193" s="39"/>
+      <c r="E193" s="38"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="35"/>
-      <c r="B194" s="36"/>
-      <c r="C194" s="37"/>
-      <c r="D194" s="37"/>
-      <c r="E194" s="36"/>
+      <c r="A194" s="37"/>
+      <c r="B194" s="38"/>
+      <c r="C194" s="39"/>
+      <c r="D194" s="39"/>
+      <c r="E194" s="38"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="35"/>
-      <c r="B195" s="36"/>
-      <c r="C195" s="37"/>
-      <c r="D195" s="37"/>
-      <c r="E195" s="36"/>
+      <c r="A195" s="37"/>
+      <c r="B195" s="38"/>
+      <c r="C195" s="39"/>
+      <c r="D195" s="39"/>
+      <c r="E195" s="38"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="35"/>
-      <c r="B196" s="36"/>
-      <c r="C196" s="37"/>
-      <c r="D196" s="37"/>
-      <c r="E196" s="36"/>
+      <c r="A196" s="37"/>
+      <c r="B196" s="38"/>
+      <c r="C196" s="39"/>
+      <c r="D196" s="39"/>
+      <c r="E196" s="38"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="35"/>
-      <c r="B197" s="36"/>
-      <c r="C197" s="37"/>
-      <c r="D197" s="37"/>
-      <c r="E197" s="36"/>
+      <c r="A197" s="37"/>
+      <c r="B197" s="38"/>
+      <c r="C197" s="39"/>
+      <c r="D197" s="39"/>
+      <c r="E197" s="38"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="35"/>
-      <c r="B198" s="36"/>
-      <c r="C198" s="37"/>
-      <c r="D198" s="37"/>
-      <c r="E198" s="36"/>
+      <c r="A198" s="37"/>
+      <c r="B198" s="38"/>
+      <c r="C198" s="39"/>
+      <c r="D198" s="39"/>
+      <c r="E198" s="38"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="35"/>
-      <c r="B199" s="36"/>
-      <c r="C199" s="37"/>
-      <c r="D199" s="37"/>
-      <c r="E199" s="36"/>
+      <c r="A199" s="37"/>
+      <c r="B199" s="38"/>
+      <c r="C199" s="39"/>
+      <c r="D199" s="39"/>
+      <c r="E199" s="38"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="35"/>
-      <c r="B200" s="36"/>
-      <c r="C200" s="37"/>
-      <c r="D200" s="37"/>
-      <c r="E200" s="36"/>
+      <c r="A200" s="37"/>
+      <c r="B200" s="38"/>
+      <c r="C200" s="39"/>
+      <c r="D200" s="39"/>
+      <c r="E200" s="38"/>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="35"/>
-      <c r="B201" s="36"/>
-      <c r="C201" s="37"/>
-      <c r="D201" s="37"/>
-      <c r="E201" s="36"/>
+      <c r="A201" s="37"/>
+      <c r="B201" s="38"/>
+      <c r="C201" s="39"/>
+      <c r="D201" s="39"/>
+      <c r="E201" s="38"/>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="35"/>
-      <c r="B202" s="36"/>
-      <c r="C202" s="37"/>
-      <c r="D202" s="37"/>
-      <c r="E202" s="36"/>
+      <c r="A202" s="37"/>
+      <c r="B202" s="38"/>
+      <c r="C202" s="39"/>
+      <c r="D202" s="39"/>
+      <c r="E202" s="38"/>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="35"/>
-      <c r="B203" s="36"/>
-      <c r="C203" s="37"/>
-      <c r="D203" s="37"/>
-      <c r="E203" s="36"/>
+      <c r="A203" s="37"/>
+      <c r="B203" s="38"/>
+      <c r="C203" s="39"/>
+      <c r="D203" s="39"/>
+      <c r="E203" s="38"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="35"/>
-      <c r="B204" s="36"/>
-      <c r="C204" s="37"/>
-      <c r="D204" s="37"/>
-      <c r="E204" s="36"/>
+      <c r="A204" s="37"/>
+      <c r="B204" s="38"/>
+      <c r="C204" s="39"/>
+      <c r="D204" s="39"/>
+      <c r="E204" s="38"/>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="35"/>
-      <c r="B205" s="36"/>
-      <c r="C205" s="37"/>
-      <c r="D205" s="37"/>
-      <c r="E205" s="36"/>
+      <c r="A205" s="37"/>
+      <c r="B205" s="38"/>
+      <c r="C205" s="39"/>
+      <c r="D205" s="39"/>
+      <c r="E205" s="38"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="35"/>
-      <c r="B206" s="36"/>
-      <c r="C206" s="37"/>
-      <c r="D206" s="37"/>
-      <c r="E206" s="36"/>
+      <c r="A206" s="37"/>
+      <c r="B206" s="38"/>
+      <c r="C206" s="39"/>
+      <c r="D206" s="39"/>
+      <c r="E206" s="38"/>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="35"/>
-      <c r="B207" s="36"/>
-      <c r="C207" s="37"/>
-      <c r="D207" s="37"/>
-      <c r="E207" s="36"/>
+      <c r="A207" s="37"/>
+      <c r="B207" s="38"/>
+      <c r="C207" s="39"/>
+      <c r="D207" s="39"/>
+      <c r="E207" s="38"/>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="35"/>
-      <c r="B208" s="36"/>
-      <c r="C208" s="37"/>
-      <c r="D208" s="37"/>
-      <c r="E208" s="36"/>
+      <c r="A208" s="37"/>
+      <c r="B208" s="38"/>
+      <c r="C208" s="39"/>
+      <c r="D208" s="39"/>
+      <c r="E208" s="38"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="35"/>
-      <c r="B209" s="36"/>
-      <c r="C209" s="37"/>
-      <c r="D209" s="37"/>
-      <c r="E209" s="36"/>
+      <c r="A209" s="37"/>
+      <c r="B209" s="38"/>
+      <c r="C209" s="39"/>
+      <c r="D209" s="39"/>
+      <c r="E209" s="38"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="35"/>
-      <c r="B210" s="36"/>
-      <c r="C210" s="37"/>
-      <c r="D210" s="37"/>
-      <c r="E210" s="36"/>
+      <c r="A210" s="37"/>
+      <c r="B210" s="38"/>
+      <c r="C210" s="39"/>
+      <c r="D210" s="39"/>
+      <c r="E210" s="38"/>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="35"/>
-      <c r="B211" s="36"/>
-      <c r="C211" s="37"/>
-      <c r="D211" s="37"/>
-      <c r="E211" s="36"/>
+      <c r="A211" s="37"/>
+      <c r="B211" s="38"/>
+      <c r="C211" s="39"/>
+      <c r="D211" s="39"/>
+      <c r="E211" s="38"/>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="35"/>
-      <c r="B212" s="36"/>
-      <c r="C212" s="37"/>
-      <c r="D212" s="37"/>
-      <c r="E212" s="36"/>
+      <c r="A212" s="37"/>
+      <c r="B212" s="38"/>
+      <c r="C212" s="39"/>
+      <c r="D212" s="39"/>
+      <c r="E212" s="38"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="35"/>
-      <c r="B213" s="36"/>
-      <c r="C213" s="37"/>
-      <c r="D213" s="37"/>
-      <c r="E213" s="36"/>
+      <c r="A213" s="37"/>
+      <c r="B213" s="38"/>
+      <c r="C213" s="39"/>
+      <c r="D213" s="39"/>
+      <c r="E213" s="38"/>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="35"/>
-      <c r="B214" s="36"/>
-      <c r="C214" s="37"/>
-      <c r="D214" s="37"/>
-      <c r="E214" s="36"/>
+      <c r="A214" s="37"/>
+      <c r="B214" s="38"/>
+      <c r="C214" s="39"/>
+      <c r="D214" s="39"/>
+      <c r="E214" s="38"/>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="35"/>
-      <c r="B215" s="36"/>
-      <c r="C215" s="37"/>
-      <c r="D215" s="37"/>
-      <c r="E215" s="36"/>
+      <c r="A215" s="37"/>
+      <c r="B215" s="38"/>
+      <c r="C215" s="39"/>
+      <c r="D215" s="39"/>
+      <c r="E215" s="38"/>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="35"/>
-      <c r="B216" s="36"/>
-      <c r="C216" s="37"/>
-      <c r="D216" s="37"/>
-      <c r="E216" s="36"/>
+      <c r="A216" s="37"/>
+      <c r="B216" s="38"/>
+      <c r="C216" s="39"/>
+      <c r="D216" s="39"/>
+      <c r="E216" s="38"/>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="35"/>
-      <c r="B217" s="36"/>
-      <c r="C217" s="37"/>
-      <c r="D217" s="37"/>
-      <c r="E217" s="36"/>
+      <c r="A217" s="37"/>
+      <c r="B217" s="38"/>
+      <c r="C217" s="39"/>
+      <c r="D217" s="39"/>
+      <c r="E217" s="38"/>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="35"/>
-      <c r="B218" s="36"/>
-      <c r="C218" s="37"/>
-      <c r="D218" s="37"/>
-      <c r="E218" s="36"/>
+      <c r="A218" s="37"/>
+      <c r="B218" s="38"/>
+      <c r="C218" s="39"/>
+      <c r="D218" s="39"/>
+      <c r="E218" s="38"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="35"/>
-      <c r="B219" s="36"/>
-      <c r="C219" s="37"/>
-      <c r="D219" s="37"/>
-      <c r="E219" s="36"/>
+      <c r="A219" s="37"/>
+      <c r="B219" s="38"/>
+      <c r="C219" s="39"/>
+      <c r="D219" s="39"/>
+      <c r="E219" s="38"/>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="35"/>
-      <c r="B220" s="36"/>
-      <c r="C220" s="37"/>
-      <c r="D220" s="37"/>
-      <c r="E220" s="36"/>
+      <c r="A220" s="37"/>
+      <c r="B220" s="38"/>
+      <c r="C220" s="39"/>
+      <c r="D220" s="39"/>
+      <c r="E220" s="38"/>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="35"/>
-      <c r="B221" s="36"/>
-      <c r="C221" s="37"/>
-      <c r="D221" s="37"/>
-      <c r="E221" s="36"/>
+      <c r="A221" s="37"/>
+      <c r="B221" s="38"/>
+      <c r="C221" s="39"/>
+      <c r="D221" s="39"/>
+      <c r="E221" s="38"/>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="35"/>
-      <c r="B222" s="36"/>
-      <c r="C222" s="37"/>
-      <c r="D222" s="37"/>
-      <c r="E222" s="36"/>
+      <c r="A222" s="37"/>
+      <c r="B222" s="38"/>
+      <c r="C222" s="39"/>
+      <c r="D222" s="39"/>
+      <c r="E222" s="38"/>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="35"/>
-      <c r="B223" s="36"/>
-      <c r="C223" s="37"/>
-      <c r="D223" s="37"/>
-      <c r="E223" s="36"/>
+      <c r="A223" s="37"/>
+      <c r="B223" s="38"/>
+      <c r="C223" s="39"/>
+      <c r="D223" s="39"/>
+      <c r="E223" s="38"/>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="35"/>
-      <c r="B224" s="36"/>
-      <c r="C224" s="37"/>
-      <c r="D224" s="37"/>
-      <c r="E224" s="36"/>
+      <c r="A224" s="37"/>
+      <c r="B224" s="38"/>
+      <c r="C224" s="39"/>
+      <c r="D224" s="39"/>
+      <c r="E224" s="38"/>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="35"/>
-      <c r="B225" s="36"/>
-      <c r="C225" s="37"/>
-      <c r="D225" s="37"/>
-      <c r="E225" s="36"/>
+      <c r="A225" s="37"/>
+      <c r="B225" s="38"/>
+      <c r="C225" s="39"/>
+      <c r="D225" s="39"/>
+      <c r="E225" s="38"/>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="35"/>
-      <c r="B226" s="36"/>
-      <c r="C226" s="37"/>
-      <c r="D226" s="37"/>
-      <c r="E226" s="36"/>
+      <c r="A226" s="37"/>
+      <c r="B226" s="38"/>
+      <c r="C226" s="39"/>
+      <c r="D226" s="39"/>
+      <c r="E226" s="38"/>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="35"/>
-      <c r="B227" s="36"/>
-      <c r="C227" s="37"/>
-      <c r="D227" s="37"/>
-      <c r="E227" s="36"/>
+      <c r="A227" s="37"/>
+      <c r="B227" s="38"/>
+      <c r="C227" s="39"/>
+      <c r="D227" s="39"/>
+      <c r="E227" s="38"/>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="35"/>
-      <c r="B228" s="36"/>
-      <c r="C228" s="37"/>
-      <c r="D228" s="37"/>
-      <c r="E228" s="36"/>
+      <c r="A228" s="37"/>
+      <c r="B228" s="38"/>
+      <c r="C228" s="39"/>
+      <c r="D228" s="39"/>
+      <c r="E228" s="38"/>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="35"/>
-      <c r="B229" s="36"/>
-      <c r="C229" s="37"/>
-      <c r="D229" s="37"/>
-      <c r="E229" s="36"/>
+      <c r="A229" s="37"/>
+      <c r="B229" s="38"/>
+      <c r="C229" s="39"/>
+      <c r="D229" s="39"/>
+      <c r="E229" s="38"/>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="35"/>
-      <c r="B230" s="36"/>
-      <c r="C230" s="37"/>
-      <c r="D230" s="37"/>
-      <c r="E230" s="36"/>
+      <c r="A230" s="37"/>
+      <c r="B230" s="38"/>
+      <c r="C230" s="39"/>
+      <c r="D230" s="39"/>
+      <c r="E230" s="38"/>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="35"/>
-      <c r="B231" s="36"/>
-      <c r="C231" s="37"/>
-      <c r="D231" s="37"/>
-      <c r="E231" s="36"/>
+      <c r="A231" s="37"/>
+      <c r="B231" s="38"/>
+      <c r="C231" s="39"/>
+      <c r="D231" s="39"/>
+      <c r="E231" s="38"/>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="35"/>
-      <c r="B232" s="36"/>
-      <c r="C232" s="37"/>
-      <c r="D232" s="37"/>
-      <c r="E232" s="36"/>
+      <c r="A232" s="37"/>
+      <c r="B232" s="38"/>
+      <c r="C232" s="39"/>
+      <c r="D232" s="39"/>
+      <c r="E232" s="38"/>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="35"/>
-      <c r="B233" s="36"/>
-      <c r="C233" s="37"/>
-      <c r="D233" s="37"/>
-      <c r="E233" s="36"/>
+      <c r="A233" s="37"/>
+      <c r="B233" s="38"/>
+      <c r="C233" s="39"/>
+      <c r="D233" s="39"/>
+      <c r="E233" s="38"/>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="35"/>
-      <c r="B234" s="36"/>
-      <c r="C234" s="37"/>
-      <c r="D234" s="37"/>
-      <c r="E234" s="36"/>
+      <c r="A234" s="37"/>
+      <c r="B234" s="38"/>
+      <c r="C234" s="39"/>
+      <c r="D234" s="39"/>
+      <c r="E234" s="38"/>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="35"/>
-      <c r="B235" s="36"/>
-      <c r="C235" s="37"/>
-      <c r="D235" s="37"/>
-      <c r="E235" s="36"/>
+      <c r="A235" s="37"/>
+      <c r="B235" s="38"/>
+      <c r="C235" s="39"/>
+      <c r="D235" s="39"/>
+      <c r="E235" s="38"/>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="35"/>
-      <c r="B236" s="36"/>
-      <c r="C236" s="37"/>
-      <c r="D236" s="37"/>
-      <c r="E236" s="36"/>
+      <c r="A236" s="37"/>
+      <c r="B236" s="38"/>
+      <c r="C236" s="39"/>
+      <c r="D236" s="39"/>
+      <c r="E236" s="38"/>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="35"/>
-      <c r="B237" s="36"/>
-      <c r="C237" s="37"/>
-      <c r="D237" s="37"/>
-      <c r="E237" s="36"/>
+      <c r="A237" s="37"/>
+      <c r="B237" s="38"/>
+      <c r="C237" s="39"/>
+      <c r="D237" s="39"/>
+      <c r="E237" s="38"/>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="35"/>
-      <c r="B238" s="36"/>
-      <c r="C238" s="37"/>
-      <c r="D238" s="37"/>
-      <c r="E238" s="36"/>
+      <c r="A238" s="37"/>
+      <c r="B238" s="38"/>
+      <c r="C238" s="39"/>
+      <c r="D238" s="39"/>
+      <c r="E238" s="38"/>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="35"/>
-      <c r="B239" s="36"/>
-      <c r="C239" s="37"/>
-      <c r="D239" s="37"/>
-      <c r="E239" s="36"/>
+      <c r="A239" s="37"/>
+      <c r="B239" s="38"/>
+      <c r="C239" s="39"/>
+      <c r="D239" s="39"/>
+      <c r="E239" s="38"/>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="35"/>
-      <c r="B240" s="36"/>
-      <c r="C240" s="37"/>
-      <c r="D240" s="37"/>
-      <c r="E240" s="36"/>
+      <c r="A240" s="37"/>
+      <c r="B240" s="38"/>
+      <c r="C240" s="39"/>
+      <c r="D240" s="39"/>
+      <c r="E240" s="38"/>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="35"/>
-      <c r="B241" s="36"/>
-      <c r="C241" s="37"/>
-      <c r="D241" s="37"/>
-      <c r="E241" s="36"/>
+      <c r="A241" s="37"/>
+      <c r="B241" s="38"/>
+      <c r="C241" s="39"/>
+      <c r="D241" s="39"/>
+      <c r="E241" s="38"/>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="35"/>
-      <c r="B242" s="36"/>
-      <c r="C242" s="37"/>
-      <c r="D242" s="37"/>
-      <c r="E242" s="36"/>
+      <c r="A242" s="37"/>
+      <c r="B242" s="38"/>
+      <c r="C242" s="39"/>
+      <c r="D242" s="39"/>
+      <c r="E242" s="38"/>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="35"/>
-      <c r="B243" s="36"/>
-      <c r="C243" s="37"/>
-      <c r="D243" s="37"/>
-      <c r="E243" s="36"/>
+      <c r="A243" s="37"/>
+      <c r="B243" s="38"/>
+      <c r="C243" s="39"/>
+      <c r="D243" s="39"/>
+      <c r="E243" s="38"/>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="35"/>
-      <c r="B244" s="36"/>
-      <c r="C244" s="37"/>
-      <c r="D244" s="37"/>
-      <c r="E244" s="36"/>
+      <c r="A244" s="37"/>
+      <c r="B244" s="38"/>
+      <c r="C244" s="39"/>
+      <c r="D244" s="39"/>
+      <c r="E244" s="38"/>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="35"/>
-      <c r="B245" s="36"/>
-      <c r="C245" s="37"/>
-      <c r="D245" s="37"/>
-      <c r="E245" s="36"/>
+      <c r="A245" s="37"/>
+      <c r="B245" s="38"/>
+      <c r="C245" s="39"/>
+      <c r="D245" s="39"/>
+      <c r="E245" s="38"/>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="35"/>
-      <c r="B246" s="36"/>
-      <c r="C246" s="37"/>
-      <c r="D246" s="37"/>
-      <c r="E246" s="36"/>
+      <c r="A246" s="37"/>
+      <c r="B246" s="38"/>
+      <c r="C246" s="39"/>
+      <c r="D246" s="39"/>
+      <c r="E246" s="38"/>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="35"/>
-      <c r="B247" s="36"/>
-      <c r="C247" s="37"/>
-      <c r="D247" s="37"/>
-      <c r="E247" s="36"/>
+      <c r="A247" s="37"/>
+      <c r="B247" s="38"/>
+      <c r="C247" s="39"/>
+      <c r="D247" s="39"/>
+      <c r="E247" s="38"/>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="35"/>
-      <c r="B248" s="36"/>
-      <c r="C248" s="37"/>
-      <c r="D248" s="37"/>
-      <c r="E248" s="36"/>
+      <c r="A248" s="37"/>
+      <c r="B248" s="38"/>
+      <c r="C248" s="39"/>
+      <c r="D248" s="39"/>
+      <c r="E248" s="38"/>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="35"/>
-      <c r="B249" s="36"/>
-      <c r="C249" s="37"/>
-      <c r="D249" s="37"/>
-      <c r="E249" s="36"/>
+      <c r="A249" s="37"/>
+      <c r="B249" s="38"/>
+      <c r="C249" s="39"/>
+      <c r="D249" s="39"/>
+      <c r="E249" s="38"/>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="35"/>
-      <c r="B250" s="36"/>
-      <c r="C250" s="37"/>
-      <c r="D250" s="37"/>
-      <c r="E250" s="36"/>
+      <c r="A250" s="37"/>
+      <c r="B250" s="38"/>
+      <c r="C250" s="39"/>
+      <c r="D250" s="39"/>
+      <c r="E250" s="38"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" password="df10" objects="true" scenarios="true" autoFilter="false"/>
   <autoFilter ref="A6:E250"/>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" error="Pick a product from the dropdown so the entry reaches the Stock sheet." errorStyle="stop" errorTitle="Unknown product" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B7:B1020" type="list">
+    <dataValidation allowBlank="true" error="Pick a product from the dropdown so the entry reaches the Stock sheet." errorStyle="stop" errorTitle="Unknown product" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B7:B5000" type="list">
       <formula1>Stock!$L$8:$L$49</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Slabs cannot be negative. Record a despatch in the Shipment column." errorStyle="stop" errorTitle="Negative quantity" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C7:D1020" type="decimal">
+    <dataValidation allowBlank="true" error="Slabs cannot be negative. Record a despatch in the Shipment column." errorStyle="stop" errorTitle="Negative quantity" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C7:D5000" type="decimal">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Enter a real date such as 21/08/2026, not text." errorStyle="stop" errorTitle="Date required" operator="greaterThan" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="A7:A1020" type="date">
+    <dataValidation allowBlank="true" error="Enter a real date such as 21/08/2026, not text." errorStyle="stop" errorTitle="Date required" operator="greaterThan" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="A7:A5000" type="date">
       <formula1>DATE(2000,1,1)</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5884,286 +5928,287 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>109</v>
+      <c r="A4" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="39" t="n">
+      <c r="A5" s="41" t="n">
         <f aca="false">Stock!$H$50</f>
         <v>107750</v>
       </c>
-      <c r="C5" s="40" t="str">
+      <c r="C5" s="42" t="str">
         <f aca="false">IF(Stock!$J$50="","—",Stock!$J$50)</f>
         <v>—</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>111</v>
+      <c r="A6" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="12" t="s">
+      <c r="A8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="12" t="s">
+      <c r="B8" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>43</v>
+      <c r="E8" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="18" t="n">
+      <c r="A9" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="17" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A9,Stock!$C$8:$C$49)</f>
         <v>28645</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="16" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A9,Stock!$D$8:$D$49)</f>
         <v>1400</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="16" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A9,Stock!$E$8:$E$49)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="18" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A9,Stock!$H$8:$H$49)</f>
         <v>30045</v>
       </c>
-      <c r="F9" s="21" t="str">
+      <c r="F9" s="20" t="str">
         <f aca="false">IF(SUMIF(Stock!$A$8:$A$49,$A9,Stock!$J$8:$J$49)=0,"",SUMIF(Stock!$A$8:$A$49,$A9,Stock!$J$8:$J$49))</f>
         <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="26" t="n">
+      <c r="A10" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="25" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A10,Stock!$C$8:$C$49)</f>
         <v>29316</v>
       </c>
-      <c r="C10" s="25" t="n">
+      <c r="C10" s="24" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A10,Stock!$D$8:$D$49)</f>
         <v>956</v>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="24" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A10,Stock!$E$8:$E$49)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="26" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A10,Stock!$H$8:$H$49)</f>
         <v>30272</v>
       </c>
-      <c r="F10" s="28" t="str">
+      <c r="F10" s="27" t="str">
         <f aca="false">IF(SUMIF(Stock!$A$8:$A$49,$A10,Stock!$J$8:$J$49)=0,"",SUMIF(Stock!$A$8:$A$49,$A10,Stock!$J$8:$J$49))</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" s="18" t="n">
+      <c r="A11" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="17" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A11,Stock!$C$8:$C$49)</f>
         <v>26619</v>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="16" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A11,Stock!$D$8:$D$49)</f>
         <v>52</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="16" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A11,Stock!$E$8:$E$49)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="18" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A11,Stock!$H$8:$H$49)</f>
         <v>26671</v>
       </c>
-      <c r="F11" s="21" t="str">
+      <c r="F11" s="20" t="str">
         <f aca="false">IF(SUMIF(Stock!$A$8:$A$49,$A11,Stock!$J$8:$J$49)=0,"",SUMIF(Stock!$A$8:$A$49,$A11,Stock!$J$8:$J$49))</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12" s="26" t="n">
+      <c r="A12" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="25" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A12,Stock!$C$8:$C$49)</f>
         <v>1534</v>
       </c>
-      <c r="C12" s="25" t="n">
+      <c r="C12" s="24" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A12,Stock!$D$8:$D$49)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="24" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A12,Stock!$E$8:$E$49)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="26" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A12,Stock!$H$8:$H$49)</f>
         <v>1534</v>
       </c>
-      <c r="F12" s="28" t="str">
+      <c r="F12" s="27" t="str">
         <f aca="false">IF(SUMIF(Stock!$A$8:$A$49,$A12,Stock!$J$8:$J$49)=0,"",SUMIF(Stock!$A$8:$A$49,$A12,Stock!$J$8:$J$49))</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" s="18" t="n">
+      <c r="A13" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="17" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A13,Stock!$C$8:$C$49)</f>
         <v>13126</v>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="16" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A13,Stock!$D$8:$D$49)</f>
         <v>2472</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="16" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A13,Stock!$E$8:$E$49)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="18" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A13,Stock!$H$8:$H$49)</f>
         <v>15598</v>
       </c>
-      <c r="F13" s="21" t="str">
+      <c r="F13" s="20" t="str">
         <f aca="false">IF(SUMIF(Stock!$A$8:$A$49,$A13,Stock!$J$8:$J$49)=0,"",SUMIF(Stock!$A$8:$A$49,$A13,Stock!$J$8:$J$49))</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="B14" s="26" t="n">
+      <c r="A14" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="25" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A14,Stock!$C$8:$C$49)</f>
         <v>670</v>
       </c>
-      <c r="C14" s="25" t="n">
+      <c r="C14" s="24" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A14,Stock!$D$8:$D$49)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="24" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A14,Stock!$E$8:$E$49)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="27" t="n">
+      <c r="E14" s="26" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A14,Stock!$H$8:$H$49)</f>
         <v>670</v>
       </c>
-      <c r="F14" s="28" t="str">
+      <c r="F14" s="27" t="str">
         <f aca="false">IF(SUMIF(Stock!$A$8:$A$49,$A14,Stock!$J$8:$J$49)=0,"",SUMIF(Stock!$A$8:$A$49,$A14,Stock!$J$8:$J$49))</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="B15" s="18" t="n">
+      <c r="A15" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="17" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A15,Stock!$C$8:$C$49)</f>
         <v>2960</v>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="16" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A15,Stock!$D$8:$D$49)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="16" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A15,Stock!$E$8:$E$49)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="18" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A15,Stock!$H$8:$H$49)</f>
         <v>2960</v>
       </c>
-      <c r="F15" s="21" t="str">
+      <c r="F15" s="20" t="str">
         <f aca="false">IF(SUMIF(Stock!$A$8:$A$49,$A15,Stock!$J$8:$J$49)=0,"",SUMIF(Stock!$A$8:$A$49,$A15,Stock!$J$8:$J$49))</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="B16" s="26" t="n">
+      <c r="A16" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="25" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A16,Stock!$C$8:$C$49)</f>
         <v>0</v>
       </c>
-      <c r="C16" s="25" t="n">
+      <c r="C16" s="24" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A16,Stock!$D$8:$D$49)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D16" s="24" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A16,Stock!$E$8:$E$49)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="27" t="n">
+      <c r="E16" s="26" t="n">
         <f aca="false">SUMIF(Stock!$A$8:$A$49,$A16,Stock!$H$8:$H$49)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="28" t="str">
+      <c r="F16" s="27" t="str">
         <f aca="false">IF(SUMIF(Stock!$A$8:$A$49,$A16,Stock!$J$8:$J$49)=0,"",SUMIF(Stock!$A$8:$A$49,$A16,Stock!$J$8:$J$49))</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="B17" s="30" t="n">
+      <c r="A17" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" s="29" t="n">
         <f aca="false">SUM(B9:B16)</f>
         <v>102870</v>
       </c>
-      <c r="C17" s="31" t="n">
+      <c r="C17" s="30" t="n">
         <f aca="false">SUM(C9:C16)</f>
         <v>4880</v>
       </c>
-      <c r="D17" s="31" t="n">
+      <c r="D17" s="30" t="n">
         <f aca="false">SUM(D9:D16)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="30" t="n">
+      <c r="E17" s="29" t="n">
         <f aca="false">SUM(E9:E16)</f>
         <v>107750</v>
       </c>
-      <c r="F17" s="32" t="str">
+      <c r="F17" s="31" t="str">
         <f aca="false">IF(SUM(F9:F16)=0,"",SUM(F9:F16))</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="s">
-        <v>113</v>
+      <c r="A19" s="9" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" password="df10" objects="true" scenarios="true" autoFilter="false"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -6192,947 +6237,948 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="41" t="s">
-        <v>114</v>
-      </c>
-      <c r="E1" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="F1" s="42"/>
+      <c r="B1" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="F1" s="44"/>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E2" s="42" t="s">
-        <v>116</v>
-      </c>
-      <c r="F2" s="42"/>
+      <c r="E2" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="44"/>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E3" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="F3" s="42"/>
+      <c r="E3" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="F3" s="44"/>
     </row>
     <row r="4" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="43"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
+      <c r="A4" s="45"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="E5" s="45" t="n">
+      <c r="A5" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="E5" s="47" t="n">
         <f aca="false">Stock!$C$3</f>
         <v>46254</v>
       </c>
-      <c r="F5" s="45"/>
+      <c r="F5" s="47"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="46" t="s">
-        <v>119</v>
-      </c>
-      <c r="E6" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="F6" s="47"/>
+      <c r="A6" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="E6" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" s="49"/>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="48" t="s">
-        <v>121</v>
-      </c>
-      <c r="B8" s="48" t="s">
-        <v>122</v>
-      </c>
-      <c r="C8" s="48" t="s">
-        <v>123</v>
-      </c>
-      <c r="D8" s="48" t="s">
+      <c r="A8" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="E8" s="49" t="s">
+      <c r="B8" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="F8" s="49"/>
+      <c r="C8" s="50" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="F8" s="51"/>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="50" t="n">
+      <c r="A9" s="52" t="n">
         <f aca="false">Stock!$C$50</f>
         <v>102870</v>
       </c>
-      <c r="B9" s="51" t="n">
+      <c r="B9" s="53" t="n">
         <f aca="false">Stock!$D$50</f>
         <v>4880</v>
       </c>
-      <c r="C9" s="51" t="n">
+      <c r="C9" s="53" t="n">
         <f aca="false">Stock!$E$50</f>
         <v>0</v>
       </c>
-      <c r="D9" s="50" t="n">
+      <c r="D9" s="52" t="n">
         <f aca="false">Stock!$H$50</f>
         <v>107750</v>
       </c>
-      <c r="E9" s="52" t="str">
+      <c r="E9" s="54" t="str">
         <f aca="false">IF(Stock!$J$50="","Rate not entered",Stock!$J$50)</f>
         <v>Rate not entered</v>
       </c>
-      <c r="F9" s="52"/>
+      <c r="F9" s="54"/>
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
+      <c r="A11" s="55" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="54" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="55" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="55" t="s">
+      <c r="A12" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="55" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="55" t="s">
+      <c r="B12" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="57" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="55" t="s">
-        <v>43</v>
+      <c r="E12" s="57" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="57" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="56" t="str">
+      <c r="A13" s="58" t="str">
         <f aca="false">Summary!$A$9</f>
         <v>Blue Dolphin</v>
       </c>
-      <c r="B13" s="57" t="n">
+      <c r="B13" s="59" t="n">
         <f aca="false">Summary!$B$9</f>
         <v>28645</v>
       </c>
-      <c r="C13" s="58" t="n">
+      <c r="C13" s="60" t="n">
         <f aca="false">Summary!$C$9</f>
         <v>1400</v>
       </c>
-      <c r="D13" s="58" t="n">
+      <c r="D13" s="60" t="n">
         <f aca="false">Summary!$D$9</f>
         <v>0</v>
       </c>
-      <c r="E13" s="59" t="n">
+      <c r="E13" s="61" t="n">
         <f aca="false">Summary!$E$9</f>
         <v>30045</v>
       </c>
-      <c r="F13" s="60" t="str">
+      <c r="F13" s="62" t="str">
         <f aca="false">Summary!$F$9</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="61" t="str">
+      <c r="A14" s="63" t="str">
         <f aca="false">Summary!$A$10</f>
         <v>Primus Japan</v>
       </c>
-      <c r="B14" s="62" t="n">
+      <c r="B14" s="64" t="n">
         <f aca="false">Summary!$B$10</f>
         <v>29316</v>
       </c>
-      <c r="C14" s="63" t="n">
+      <c r="C14" s="65" t="n">
         <f aca="false">Summary!$C$10</f>
         <v>956</v>
       </c>
-      <c r="D14" s="63" t="n">
+      <c r="D14" s="65" t="n">
         <f aca="false">Summary!$D$10</f>
         <v>0</v>
       </c>
-      <c r="E14" s="64" t="n">
+      <c r="E14" s="66" t="n">
         <f aca="false">Summary!$E$10</f>
         <v>30272</v>
       </c>
-      <c r="F14" s="65" t="str">
+      <c r="F14" s="67" t="str">
         <f aca="false">Summary!$F$10</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="56" t="str">
+      <c r="A15" s="58" t="str">
         <f aca="false">Summary!$A$11</f>
         <v>Primus EU</v>
       </c>
-      <c r="B15" s="57" t="n">
+      <c r="B15" s="59" t="n">
         <f aca="false">Summary!$B$11</f>
         <v>26619</v>
       </c>
-      <c r="C15" s="58" t="n">
+      <c r="C15" s="60" t="n">
         <f aca="false">Summary!$C$11</f>
         <v>52</v>
       </c>
-      <c r="D15" s="58" t="n">
+      <c r="D15" s="60" t="n">
         <f aca="false">Summary!$D$11</f>
         <v>0</v>
       </c>
-      <c r="E15" s="59" t="n">
+      <c r="E15" s="61" t="n">
         <f aca="false">Summary!$E$11</f>
         <v>26671</v>
       </c>
-      <c r="F15" s="60" t="str">
+      <c r="F15" s="62" t="str">
         <f aca="false">Summary!$F$11</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="61" t="str">
+      <c r="A16" s="63" t="str">
         <f aca="false">Summary!$A$12</f>
         <v>AMF Brand</v>
       </c>
-      <c r="B16" s="62" t="n">
+      <c r="B16" s="64" t="n">
         <f aca="false">Summary!$B$12</f>
         <v>1534</v>
       </c>
-      <c r="C16" s="63" t="n">
+      <c r="C16" s="65" t="n">
         <f aca="false">Summary!$C$12</f>
         <v>0</v>
       </c>
-      <c r="D16" s="63" t="n">
+      <c r="D16" s="65" t="n">
         <f aca="false">Summary!$D$12</f>
         <v>0</v>
       </c>
-      <c r="E16" s="64" t="n">
+      <c r="E16" s="66" t="n">
         <f aca="false">Summary!$E$12</f>
         <v>1534</v>
       </c>
-      <c r="F16" s="65" t="str">
+      <c r="F16" s="67" t="str">
         <f aca="false">Summary!$F$12</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="56" t="str">
+      <c r="A17" s="58" t="str">
         <f aca="false">Summary!$A$13</f>
         <v>THT Brand</v>
       </c>
-      <c r="B17" s="57" t="n">
+      <c r="B17" s="59" t="n">
         <f aca="false">Summary!$B$13</f>
         <v>13126</v>
       </c>
-      <c r="C17" s="58" t="n">
+      <c r="C17" s="60" t="n">
         <f aca="false">Summary!$C$13</f>
         <v>2472</v>
       </c>
-      <c r="D17" s="58" t="n">
+      <c r="D17" s="60" t="n">
         <f aca="false">Summary!$D$13</f>
         <v>0</v>
       </c>
-      <c r="E17" s="59" t="n">
+      <c r="E17" s="61" t="n">
         <f aca="false">Summary!$E$13</f>
         <v>15598</v>
       </c>
-      <c r="F17" s="60" t="str">
+      <c r="F17" s="62" t="str">
         <f aca="false">Summary!$F$13</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="61" t="str">
+      <c r="A18" s="63" t="str">
         <f aca="false">Summary!$A$14</f>
         <v>Deepsea</v>
       </c>
-      <c r="B18" s="62" t="n">
+      <c r="B18" s="64" t="n">
         <f aca="false">Summary!$B$14</f>
         <v>670</v>
       </c>
-      <c r="C18" s="63" t="n">
+      <c r="C18" s="65" t="n">
         <f aca="false">Summary!$C$14</f>
         <v>0</v>
       </c>
-      <c r="D18" s="63" t="n">
+      <c r="D18" s="65" t="n">
         <f aca="false">Summary!$D$14</f>
         <v>0</v>
       </c>
-      <c r="E18" s="64" t="n">
+      <c r="E18" s="66" t="n">
         <f aca="false">Summary!$E$14</f>
         <v>670</v>
       </c>
-      <c r="F18" s="65" t="str">
+      <c r="F18" s="67" t="str">
         <f aca="false">Summary!$F$14</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="56" t="str">
+      <c r="A19" s="58" t="str">
         <f aca="false">Summary!$A$15</f>
         <v>China</v>
       </c>
-      <c r="B19" s="57" t="n">
+      <c r="B19" s="59" t="n">
         <f aca="false">Summary!$B$15</f>
         <v>2960</v>
       </c>
-      <c r="C19" s="58" t="n">
+      <c r="C19" s="60" t="n">
         <f aca="false">Summary!$C$15</f>
         <v>0</v>
       </c>
-      <c r="D19" s="58" t="n">
+      <c r="D19" s="60" t="n">
         <f aca="false">Summary!$D$15</f>
         <v>0</v>
       </c>
-      <c r="E19" s="59" t="n">
+      <c r="E19" s="61" t="n">
         <f aca="false">Summary!$E$15</f>
         <v>2960</v>
       </c>
-      <c r="F19" s="60" t="str">
+      <c r="F19" s="62" t="str">
         <f aca="false">Summary!$F$15</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="61" t="str">
+      <c r="A20" s="63" t="str">
         <f aca="false">Summary!$A$16</f>
         <v>Shrimp Whole 5x3kgs</v>
       </c>
-      <c r="B20" s="62" t="n">
+      <c r="B20" s="64" t="n">
         <f aca="false">Summary!$B$16</f>
         <v>0</v>
       </c>
-      <c r="C20" s="63" t="n">
+      <c r="C20" s="65" t="n">
         <f aca="false">Summary!$C$16</f>
         <v>0</v>
       </c>
-      <c r="D20" s="63" t="n">
+      <c r="D20" s="65" t="n">
         <f aca="false">Summary!$D$16</f>
         <v>0</v>
       </c>
-      <c r="E20" s="64" t="n">
+      <c r="E20" s="66" t="n">
         <f aca="false">Summary!$E$16</f>
         <v>0</v>
       </c>
-      <c r="F20" s="65" t="str">
+      <c r="F20" s="67" t="str">
         <f aca="false">Summary!$F$16</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="66" t="str">
+      <c r="A21" s="68" t="str">
         <f aca="false">Summary!$A$17</f>
         <v>GRAND TOTAL</v>
       </c>
-      <c r="B21" s="67" t="n">
+      <c r="B21" s="69" t="n">
         <f aca="false">Summary!$B$17</f>
         <v>102870</v>
       </c>
-      <c r="C21" s="68" t="n">
+      <c r="C21" s="70" t="n">
         <f aca="false">Summary!$C$17</f>
         <v>4880</v>
       </c>
-      <c r="D21" s="68" t="n">
+      <c r="D21" s="70" t="n">
         <f aca="false">Summary!$D$17</f>
         <v>0</v>
       </c>
-      <c r="E21" s="67" t="n">
+      <c r="E21" s="69" t="n">
         <f aca="false">Summary!$E$17</f>
         <v>107750</v>
       </c>
-      <c r="F21" s="69" t="str">
+      <c r="F21" s="71" t="str">
         <f aca="false">Summary!$F$17</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="53"/>
-      <c r="F23" s="53"/>
+      <c r="A23" s="55" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" s="55"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="55"/>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="54" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="54" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="55" t="s">
-        <v>128</v>
-      </c>
-      <c r="D24" s="55" t="s">
-        <v>129</v>
-      </c>
-      <c r="E24" s="55" t="s">
-        <v>41</v>
-      </c>
-      <c r="F24" s="55"/>
+      <c r="A24" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="56" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" s="57" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" s="57" t="s">
+        <v>44</v>
+      </c>
+      <c r="F24" s="57"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="70" t="str">
+      <c r="A25" s="72" t="str">
         <f aca="false">IF($H25="","",INDEX(Stock!$A$8:$A$49,$H25))</f>
         <v>Blue Dolphin</v>
       </c>
-      <c r="B25" s="70" t="str">
+      <c r="B25" s="72" t="str">
         <f aca="false">IF($H25="","",INDEX(Stock!$B$8:$B$49,$H25))</f>
         <v>PD PVN 100/200</v>
       </c>
-      <c r="C25" s="71" t="n">
+      <c r="C25" s="73" t="n">
         <f aca="false">IF($H25="","",INDEX(Stock!$D$8:$D$49,$H25))</f>
         <v>1068</v>
       </c>
-      <c r="D25" s="71" t="n">
+      <c r="D25" s="73" t="n">
         <f aca="false">IF($H25="","",INDEX(Stock!$E$8:$E$49,$H25))</f>
         <v>0</v>
       </c>
-      <c r="E25" s="72" t="n">
+      <c r="E25" s="74" t="n">
         <f aca="false">IF($H25="","",INDEX(Stock!$H$8:$H$49,$H25))</f>
         <v>12527</v>
       </c>
-      <c r="H25" s="73" t="n">
+      <c r="H25" s="75" t="n">
         <f aca="false">IFERROR(MATCH(1,Stock!$N$8:$N$49,0),"")</f>
         <v>1</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="70" t="str">
+      <c r="A26" s="72" t="str">
         <f aca="false">IF($H26="","",INDEX(Stock!$A$8:$A$49,$H26))</f>
         <v>Blue Dolphin</v>
       </c>
-      <c r="B26" s="70" t="str">
+      <c r="B26" s="72" t="str">
         <f aca="false">IF($H26="","",INDEX(Stock!$B$8:$B$49,$H26))</f>
         <v>PD KKD 100/200</v>
       </c>
-      <c r="C26" s="71" t="n">
+      <c r="C26" s="73" t="n">
         <f aca="false">IF($H26="","",INDEX(Stock!$D$8:$D$49,$H26))</f>
         <v>65</v>
       </c>
-      <c r="D26" s="71" t="n">
+      <c r="D26" s="73" t="n">
         <f aca="false">IF($H26="","",INDEX(Stock!$E$8:$E$49,$H26))</f>
         <v>0</v>
       </c>
-      <c r="E26" s="72" t="n">
+      <c r="E26" s="74" t="n">
         <f aca="false">IF($H26="","",INDEX(Stock!$H$8:$H$49,$H26))</f>
         <v>582</v>
       </c>
-      <c r="H26" s="73" t="n">
+      <c r="H26" s="75" t="n">
         <f aca="false">IFERROR(MATCH(2,Stock!$N$8:$N$49,0),"")</f>
         <v>2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="70" t="str">
+      <c r="A27" s="72" t="str">
         <f aca="false">IF($H27="","",INDEX(Stock!$A$8:$A$49,$H27))</f>
         <v>Blue Dolphin</v>
       </c>
-      <c r="B27" s="70" t="str">
+      <c r="B27" s="72" t="str">
         <f aca="false">IF($H27="","",INDEX(Stock!$B$8:$B$49,$H27))</f>
         <v>PUD PVN 200/300</v>
       </c>
-      <c r="C27" s="71" t="n">
+      <c r="C27" s="73" t="n">
         <f aca="false">IF($H27="","",INDEX(Stock!$D$8:$D$49,$H27))</f>
         <v>267</v>
       </c>
-      <c r="D27" s="71" t="n">
+      <c r="D27" s="73" t="n">
         <f aca="false">IF($H27="","",INDEX(Stock!$E$8:$E$49,$H27))</f>
         <v>0</v>
       </c>
-      <c r="E27" s="72" t="n">
+      <c r="E27" s="74" t="n">
         <f aca="false">IF($H27="","",INDEX(Stock!$H$8:$H$49,$H27))</f>
         <v>2529</v>
       </c>
-      <c r="H27" s="73" t="n">
+      <c r="H27" s="75" t="n">
         <f aca="false">IFERROR(MATCH(3,Stock!$N$8:$N$49,0),"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="70" t="str">
+      <c r="A28" s="72" t="str">
         <f aca="false">IF($H28="","",INDEX(Stock!$A$8:$A$49,$H28))</f>
         <v>Primus Japan</v>
       </c>
-      <c r="B28" s="70" t="str">
+      <c r="B28" s="72" t="str">
         <f aca="false">IF($H28="","",INDEX(Stock!$B$8:$B$49,$H28))</f>
         <v>PUD KZN 40/60</v>
       </c>
-      <c r="C28" s="71" t="n">
+      <c r="C28" s="73" t="n">
         <f aca="false">IF($H28="","",INDEX(Stock!$D$8:$D$49,$H28))</f>
         <v>29</v>
       </c>
-      <c r="D28" s="71" t="n">
+      <c r="D28" s="73" t="n">
         <f aca="false">IF($H28="","",INDEX(Stock!$E$8:$E$49,$H28))</f>
         <v>0</v>
       </c>
-      <c r="E28" s="72" t="n">
+      <c r="E28" s="74" t="n">
         <f aca="false">IF($H28="","",INDEX(Stock!$H$8:$H$49,$H28))</f>
         <v>93</v>
       </c>
-      <c r="H28" s="73" t="n">
+      <c r="H28" s="75" t="n">
         <f aca="false">IFERROR(MATCH(4,Stock!$N$8:$N$49,0),"")</f>
         <v>8</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="70" t="str">
+      <c r="A29" s="72" t="str">
         <f aca="false">IF($H29="","",INDEX(Stock!$A$8:$A$49,$H29))</f>
         <v>Primus Japan</v>
       </c>
-      <c r="B29" s="70" t="str">
+      <c r="B29" s="72" t="str">
         <f aca="false">IF($H29="","",INDEX(Stock!$B$8:$B$49,$H29))</f>
         <v>PUD KZN 60/80</v>
       </c>
-      <c r="C29" s="71" t="n">
+      <c r="C29" s="73" t="n">
         <f aca="false">IF($H29="","",INDEX(Stock!$D$8:$D$49,$H29))</f>
         <v>39</v>
       </c>
-      <c r="D29" s="71" t="n">
+      <c r="D29" s="73" t="n">
         <f aca="false">IF($H29="","",INDEX(Stock!$E$8:$E$49,$H29))</f>
         <v>0</v>
       </c>
-      <c r="E29" s="72" t="n">
+      <c r="E29" s="74" t="n">
         <f aca="false">IF($H29="","",INDEX(Stock!$H$8:$H$49,$H29))</f>
         <v>230</v>
       </c>
-      <c r="H29" s="73" t="n">
+      <c r="H29" s="75" t="n">
         <f aca="false">IFERROR(MATCH(5,Stock!$N$8:$N$49,0),"")</f>
         <v>9</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="70" t="str">
+      <c r="A30" s="72" t="str">
         <f aca="false">IF($H30="","",INDEX(Stock!$A$8:$A$49,$H30))</f>
         <v>Primus Japan</v>
       </c>
-      <c r="B30" s="70" t="str">
+      <c r="B30" s="72" t="str">
         <f aca="false">IF($H30="","",INDEX(Stock!$B$8:$B$49,$H30))</f>
         <v>PUD KZN 80/120</v>
       </c>
-      <c r="C30" s="71" t="n">
+      <c r="C30" s="73" t="n">
         <f aca="false">IF($H30="","",INDEX(Stock!$D$8:$D$49,$H30))</f>
         <v>50</v>
       </c>
-      <c r="D30" s="71" t="n">
+      <c r="D30" s="73" t="n">
         <f aca="false">IF($H30="","",INDEX(Stock!$E$8:$E$49,$H30))</f>
         <v>0</v>
       </c>
-      <c r="E30" s="72" t="n">
+      <c r="E30" s="74" t="n">
         <f aca="false">IF($H30="","",INDEX(Stock!$H$8:$H$49,$H30))</f>
         <v>516</v>
       </c>
-      <c r="H30" s="73" t="n">
+      <c r="H30" s="75" t="n">
         <f aca="false">IFERROR(MATCH(6,Stock!$N$8:$N$49,0),"")</f>
         <v>11</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="70" t="str">
+      <c r="A31" s="72" t="str">
         <f aca="false">IF($H31="","",INDEX(Stock!$A$8:$A$49,$H31))</f>
         <v>Primus Japan</v>
       </c>
-      <c r="B31" s="70" t="str">
+      <c r="B31" s="72" t="str">
         <f aca="false">IF($H31="","",INDEX(Stock!$B$8:$B$49,$H31))</f>
         <v>PUD NRN 80/120</v>
       </c>
-      <c r="C31" s="71" t="n">
+      <c r="C31" s="73" t="n">
         <f aca="false">IF($H31="","",INDEX(Stock!$D$8:$D$49,$H31))</f>
         <v>3</v>
       </c>
-      <c r="D31" s="71" t="n">
+      <c r="D31" s="73" t="n">
         <f aca="false">IF($H31="","",INDEX(Stock!$E$8:$E$49,$H31))</f>
         <v>0</v>
       </c>
-      <c r="E31" s="72" t="n">
+      <c r="E31" s="74" t="n">
         <f aca="false">IF($H31="","",INDEX(Stock!$H$8:$H$49,$H31))</f>
         <v>72</v>
       </c>
-      <c r="H31" s="73" t="n">
+      <c r="H31" s="75" t="n">
         <f aca="false">IFERROR(MATCH(7,Stock!$N$8:$N$49,0),"")</f>
         <v>12</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="70" t="str">
+      <c r="A32" s="72" t="str">
         <f aca="false">IF($H32="","",INDEX(Stock!$A$8:$A$49,$H32))</f>
         <v>Primus Japan</v>
       </c>
-      <c r="B32" s="70" t="str">
+      <c r="B32" s="72" t="str">
         <f aca="false">IF($H32="","",INDEX(Stock!$B$8:$B$49,$H32))</f>
         <v>PUD KZN 100/200</v>
       </c>
-      <c r="C32" s="71" t="n">
+      <c r="C32" s="73" t="n">
         <f aca="false">IF($H32="","",INDEX(Stock!$D$8:$D$49,$H32))</f>
         <v>50</v>
       </c>
-      <c r="D32" s="71" t="n">
+      <c r="D32" s="73" t="n">
         <f aca="false">IF($H32="","",INDEX(Stock!$E$8:$E$49,$H32))</f>
         <v>0</v>
       </c>
-      <c r="E32" s="72" t="n">
+      <c r="E32" s="74" t="n">
         <f aca="false">IF($H32="","",INDEX(Stock!$H$8:$H$49,$H32))</f>
         <v>4259</v>
       </c>
-      <c r="H32" s="73" t="n">
+      <c r="H32" s="75" t="n">
         <f aca="false">IFERROR(MATCH(8,Stock!$N$8:$N$49,0),"")</f>
         <v>15</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="70" t="str">
+      <c r="A33" s="72" t="str">
         <f aca="false">IF($H33="","",INDEX(Stock!$A$8:$A$49,$H33))</f>
         <v>Primus Japan</v>
       </c>
-      <c r="B33" s="70" t="str">
+      <c r="B33" s="72" t="str">
         <f aca="false">IF($H33="","",INDEX(Stock!$B$8:$B$49,$H33))</f>
         <v>PUD KZN 200/300</v>
       </c>
-      <c r="C33" s="71" t="n">
+      <c r="C33" s="73" t="n">
         <f aca="false">IF($H33="","",INDEX(Stock!$D$8:$D$49,$H33))</f>
         <v>33</v>
       </c>
-      <c r="D33" s="71" t="n">
+      <c r="D33" s="73" t="n">
         <f aca="false">IF($H33="","",INDEX(Stock!$E$8:$E$49,$H33))</f>
         <v>0</v>
       </c>
-      <c r="E33" s="72" t="n">
+      <c r="E33" s="74" t="n">
         <f aca="false">IF($H33="","",INDEX(Stock!$H$8:$H$49,$H33))</f>
         <v>1113</v>
       </c>
-      <c r="H33" s="73" t="n">
+      <c r="H33" s="75" t="n">
         <f aca="false">IFERROR(MATCH(9,Stock!$N$8:$N$49,0),"")</f>
         <v>18</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="70" t="str">
+      <c r="A34" s="72" t="str">
         <f aca="false">IF($H34="","",INDEX(Stock!$A$8:$A$49,$H34))</f>
         <v>Primus Japan</v>
       </c>
-      <c r="B34" s="70" t="str">
+      <c r="B34" s="72" t="str">
         <f aca="false">IF($H34="","",INDEX(Stock!$B$8:$B$49,$H34))</f>
         <v>PUD PVN 300/500</v>
       </c>
-      <c r="C34" s="71" t="n">
+      <c r="C34" s="73" t="n">
         <f aca="false">IF($H34="","",INDEX(Stock!$D$8:$D$49,$H34))</f>
         <v>156</v>
       </c>
-      <c r="D34" s="71" t="n">
+      <c r="D34" s="73" t="n">
         <f aca="false">IF($H34="","",INDEX(Stock!$E$8:$E$49,$H34))</f>
         <v>0</v>
       </c>
-      <c r="E34" s="72" t="n">
+      <c r="E34" s="74" t="n">
         <f aca="false">IF($H34="","",INDEX(Stock!$H$8:$H$49,$H34))</f>
         <v>577</v>
       </c>
-      <c r="H34" s="73" t="n">
+      <c r="H34" s="75" t="n">
         <f aca="false">IFERROR(MATCH(10,Stock!$N$8:$N$49,0),"")</f>
         <v>19</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="70" t="str">
+      <c r="A35" s="72" t="str">
         <f aca="false">IF($H35="","",INDEX(Stock!$A$8:$A$49,$H35))</f>
         <v>Primus Japan</v>
       </c>
-      <c r="B35" s="70" t="str">
+      <c r="B35" s="72" t="str">
         <f aca="false">IF($H35="","",INDEX(Stock!$B$8:$B$49,$H35))</f>
         <v>PUD KKD 300/500</v>
       </c>
-      <c r="C35" s="71" t="n">
+      <c r="C35" s="73" t="n">
         <f aca="false">IF($H35="","",INDEX(Stock!$D$8:$D$49,$H35))</f>
         <v>596</v>
       </c>
-      <c r="D35" s="71" t="n">
+      <c r="D35" s="73" t="n">
         <f aca="false">IF($H35="","",INDEX(Stock!$E$8:$E$49,$H35))</f>
         <v>0</v>
       </c>
-      <c r="E35" s="72" t="n">
+      <c r="E35" s="74" t="n">
         <f aca="false">IF($H35="","",INDEX(Stock!$H$8:$H$49,$H35))</f>
         <v>1176</v>
       </c>
-      <c r="H35" s="73" t="n">
+      <c r="H35" s="75" t="n">
         <f aca="false">IFERROR(MATCH(11,Stock!$N$8:$N$49,0),"")</f>
         <v>20</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="70" t="str">
+      <c r="A36" s="72" t="str">
         <f aca="false">IF($H36="","",INDEX(Stock!$A$8:$A$49,$H36))</f>
         <v>Primus EU</v>
       </c>
-      <c r="B36" s="70" t="str">
+      <c r="B36" s="72" t="str">
         <f aca="false">IF($H36="","",INDEX(Stock!$B$8:$B$49,$H36))</f>
         <v>BKN</v>
       </c>
-      <c r="C36" s="71" t="n">
+      <c r="C36" s="73" t="n">
         <f aca="false">IF($H36="","",INDEX(Stock!$D$8:$D$49,$H36))</f>
         <v>52</v>
       </c>
-      <c r="D36" s="71" t="n">
+      <c r="D36" s="73" t="n">
         <f aca="false">IF($H36="","",INDEX(Stock!$E$8:$E$49,$H36))</f>
         <v>0</v>
       </c>
-      <c r="E36" s="72" t="n">
+      <c r="E36" s="74" t="n">
         <f aca="false">IF($H36="","",INDEX(Stock!$H$8:$H$49,$H36))</f>
         <v>15182</v>
       </c>
-      <c r="H36" s="73" t="n">
+      <c r="H36" s="75" t="n">
         <f aca="false">IFERROR(MATCH(12,Stock!$N$8:$N$49,0),"")</f>
         <v>28</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="70" t="str">
+      <c r="A37" s="72" t="str">
         <f aca="false">IF($H37="","",INDEX(Stock!$A$8:$A$49,$H37))</f>
         <v>THT Brand</v>
       </c>
-      <c r="B37" s="70" t="str">
+      <c r="B37" s="72" t="str">
         <f aca="false">IF($H37="","",INDEX(Stock!$B$8:$B$49,$H37))</f>
         <v>PUD PVN 80/120</v>
       </c>
-      <c r="C37" s="71" t="n">
+      <c r="C37" s="73" t="n">
         <f aca="false">IF($H37="","",INDEX(Stock!$D$8:$D$49,$H37))</f>
         <v>1872</v>
       </c>
-      <c r="D37" s="71" t="n">
+      <c r="D37" s="73" t="n">
         <f aca="false">IF($H37="","",INDEX(Stock!$E$8:$E$49,$H37))</f>
         <v>0</v>
       </c>
-      <c r="E37" s="72" t="n">
+      <c r="E37" s="74" t="n">
         <f aca="false">IF($H37="","",INDEX(Stock!$H$8:$H$49,$H37))</f>
         <v>3261</v>
       </c>
-      <c r="H37" s="73" t="n">
+      <c r="H37" s="75" t="n">
         <f aca="false">IFERROR(MATCH(13,Stock!$N$8:$N$49,0),"")</f>
         <v>35</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="70" t="str">
+      <c r="A38" s="72" t="str">
         <f aca="false">IF($H38="","",INDEX(Stock!$A$8:$A$49,$H38))</f>
         <v>THT Brand</v>
       </c>
-      <c r="B38" s="70" t="str">
+      <c r="B38" s="72" t="str">
         <f aca="false">IF($H38="","",INDEX(Stock!$B$8:$B$49,$H38))</f>
         <v>PUD PVN 100/200</v>
       </c>
-      <c r="C38" s="71" t="n">
+      <c r="C38" s="73" t="n">
         <f aca="false">IF($H38="","",INDEX(Stock!$D$8:$D$49,$H38))</f>
         <v>600</v>
       </c>
-      <c r="D38" s="71" t="n">
+      <c r="D38" s="73" t="n">
         <f aca="false">IF($H38="","",INDEX(Stock!$E$8:$E$49,$H38))</f>
         <v>0</v>
       </c>
-      <c r="E38" s="72" t="n">
+      <c r="E38" s="74" t="n">
         <f aca="false">IF($H38="","",INDEX(Stock!$H$8:$H$49,$H38))</f>
         <v>7655</v>
       </c>
-      <c r="H38" s="73" t="n">
+      <c r="H38" s="75" t="n">
         <f aca="false">IFERROR(MATCH(14,Stock!$N$8:$N$49,0),"")</f>
         <v>36</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="70" t="str">
+      <c r="A39" s="72" t="str">
         <f aca="false">IF($H39="","",INDEX(Stock!$A$8:$A$49,$H39))</f>
         <v/>
       </c>
-      <c r="B39" s="70" t="str">
+      <c r="B39" s="72" t="str">
         <f aca="false">IF($H39="","",INDEX(Stock!$B$8:$B$49,$H39))</f>
         <v/>
       </c>
-      <c r="C39" s="71" t="str">
+      <c r="C39" s="73" t="str">
         <f aca="false">IF($H39="","",INDEX(Stock!$D$8:$D$49,$H39))</f>
         <v/>
       </c>
-      <c r="D39" s="71" t="str">
+      <c r="D39" s="73" t="str">
         <f aca="false">IF($H39="","",INDEX(Stock!$E$8:$E$49,$H39))</f>
         <v/>
       </c>
-      <c r="E39" s="72" t="str">
+      <c r="E39" s="74" t="str">
         <f aca="false">IF($H39="","",INDEX(Stock!$H$8:$H$49,$H39))</f>
         <v/>
       </c>
-      <c r="H39" s="73" t="str">
+      <c r="H39" s="75" t="str">
         <f aca="false">IFERROR(MATCH(15,Stock!$N$8:$N$49,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="70" t="str">
+      <c r="A40" s="72" t="str">
         <f aca="false">IF($H40="","",INDEX(Stock!$A$8:$A$49,$H40))</f>
         <v/>
       </c>
-      <c r="B40" s="70" t="str">
+      <c r="B40" s="72" t="str">
         <f aca="false">IF($H40="","",INDEX(Stock!$B$8:$B$49,$H40))</f>
         <v/>
       </c>
-      <c r="C40" s="71" t="str">
+      <c r="C40" s="73" t="str">
         <f aca="false">IF($H40="","",INDEX(Stock!$D$8:$D$49,$H40))</f>
         <v/>
       </c>
-      <c r="D40" s="71" t="str">
+      <c r="D40" s="73" t="str">
         <f aca="false">IF($H40="","",INDEX(Stock!$E$8:$E$49,$H40))</f>
         <v/>
       </c>
-      <c r="E40" s="72" t="str">
+      <c r="E40" s="74" t="str">
         <f aca="false">IF($H40="","",INDEX(Stock!$H$8:$H$49,$H40))</f>
         <v/>
       </c>
-      <c r="H40" s="73" t="str">
+      <c r="H40" s="75" t="str">
         <f aca="false">IFERROR(MATCH(16,Stock!$N$8:$N$49,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="70" t="str">
+      <c r="A41" s="72" t="str">
         <f aca="false">IF($H41="","",INDEX(Stock!$A$8:$A$49,$H41))</f>
         <v/>
       </c>
-      <c r="B41" s="70" t="str">
+      <c r="B41" s="72" t="str">
         <f aca="false">IF($H41="","",INDEX(Stock!$B$8:$B$49,$H41))</f>
         <v/>
       </c>
-      <c r="C41" s="71" t="str">
+      <c r="C41" s="73" t="str">
         <f aca="false">IF($H41="","",INDEX(Stock!$D$8:$D$49,$H41))</f>
         <v/>
       </c>
-      <c r="D41" s="71" t="str">
+      <c r="D41" s="73" t="str">
         <f aca="false">IF($H41="","",INDEX(Stock!$E$8:$E$49,$H41))</f>
         <v/>
       </c>
-      <c r="E41" s="72" t="str">
+      <c r="E41" s="74" t="str">
         <f aca="false">IF($H41="","",INDEX(Stock!$H$8:$H$49,$H41))</f>
         <v/>
       </c>
-      <c r="H41" s="73" t="str">
+      <c r="H41" s="75" t="str">
         <f aca="false">IFERROR(MATCH(17,Stock!$N$8:$N$49,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="70" t="str">
+      <c r="A42" s="72" t="str">
         <f aca="false">IF($H42="","",INDEX(Stock!$A$8:$A$49,$H42))</f>
         <v/>
       </c>
-      <c r="B42" s="70" t="str">
+      <c r="B42" s="72" t="str">
         <f aca="false">IF($H42="","",INDEX(Stock!$B$8:$B$49,$H42))</f>
         <v/>
       </c>
-      <c r="C42" s="71" t="str">
+      <c r="C42" s="73" t="str">
         <f aca="false">IF($H42="","",INDEX(Stock!$D$8:$D$49,$H42))</f>
         <v/>
       </c>
-      <c r="D42" s="71" t="str">
+      <c r="D42" s="73" t="str">
         <f aca="false">IF($H42="","",INDEX(Stock!$E$8:$E$49,$H42))</f>
         <v/>
       </c>
-      <c r="E42" s="72" t="str">
+      <c r="E42" s="74" t="str">
         <f aca="false">IF($H42="","",INDEX(Stock!$H$8:$H$49,$H42))</f>
         <v/>
       </c>
-      <c r="H42" s="73" t="str">
+      <c r="H42" s="75" t="str">
         <f aca="false">IFERROR(MATCH(18,Stock!$N$8:$N$49,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="70" t="str">
+      <c r="A43" s="72" t="str">
         <f aca="false">IF($H43="","",INDEX(Stock!$A$8:$A$49,$H43))</f>
         <v/>
       </c>
-      <c r="B43" s="70" t="str">
+      <c r="B43" s="72" t="str">
         <f aca="false">IF($H43="","",INDEX(Stock!$B$8:$B$49,$H43))</f>
         <v/>
       </c>
-      <c r="C43" s="71" t="str">
+      <c r="C43" s="73" t="str">
         <f aca="false">IF($H43="","",INDEX(Stock!$D$8:$D$49,$H43))</f>
         <v/>
       </c>
-      <c r="D43" s="71" t="str">
+      <c r="D43" s="73" t="str">
         <f aca="false">IF($H43="","",INDEX(Stock!$E$8:$E$49,$H43))</f>
         <v/>
       </c>
-      <c r="E43" s="72" t="str">
+      <c r="E43" s="74" t="str">
         <f aca="false">IF($H43="","",INDEX(Stock!$H$8:$H$49,$H43))</f>
         <v/>
       </c>
-      <c r="H43" s="73" t="str">
+      <c r="H43" s="75" t="str">
         <f aca="false">IFERROR(MATCH(19,Stock!$N$8:$N$49,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="70" t="str">
+      <c r="A44" s="72" t="str">
         <f aca="false">IF($H44="","",INDEX(Stock!$A$8:$A$49,$H44))</f>
         <v/>
       </c>
-      <c r="B44" s="70" t="str">
+      <c r="B44" s="72" t="str">
         <f aca="false">IF($H44="","",INDEX(Stock!$B$8:$B$49,$H44))</f>
         <v/>
       </c>
-      <c r="C44" s="71" t="str">
+      <c r="C44" s="73" t="str">
         <f aca="false">IF($H44="","",INDEX(Stock!$D$8:$D$49,$H44))</f>
         <v/>
       </c>
-      <c r="D44" s="71" t="str">
+      <c r="D44" s="73" t="str">
         <f aca="false">IF($H44="","",INDEX(Stock!$E$8:$E$49,$H44))</f>
         <v/>
       </c>
-      <c r="E44" s="72" t="str">
+      <c r="E44" s="74" t="str">
         <f aca="false">IF($H44="","",INDEX(Stock!$H$8:$H$49,$H44))</f>
         <v/>
       </c>
-      <c r="H44" s="73" t="str">
+      <c r="H44" s="75" t="str">
         <f aca="false">IFERROR(MATCH(20,Stock!$N$8:$N$49,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="74" t="s">
-        <v>130</v>
-      </c>
-      <c r="B45" s="75" t="str">
+      <c r="A45" s="76" t="s">
+        <v>133</v>
+      </c>
+      <c r="B45" s="77" t="str">
         <f aca="false">COUNTIF(Stock!$M$8:$M$49,1)&amp;" product(s)"</f>
         <v>14 product(s)</v>
       </c>
-      <c r="C45" s="76" t="n">
+      <c r="C45" s="78" t="n">
         <f aca="false">SUM(C25:C44)</f>
         <v>4880</v>
       </c>
-      <c r="D45" s="76" t="n">
+      <c r="D45" s="78" t="n">
         <f aca="false">SUM(D25:D44)</f>
         <v>0</v>
       </c>
-      <c r="E45" s="74"/>
-      <c r="F45" s="74"/>
+      <c r="E45" s="76"/>
+      <c r="F45" s="76"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="77" t="str">
+      <c r="A46" s="79" t="str">
         <f aca="false">IF(COUNTIF(Stock!$M$8:$M$49,1)&gt;20,"Note: "&amp;(COUNTIF(Stock!$M$8:$M$49,1)-20)&amp;" further product(s) moved today — see the Stock sheet for the full list.","")</f>
         <v/>
       </c>
-      <c r="B46" s="77"/>
-      <c r="C46" s="77"/>
-      <c r="D46" s="77"/>
-      <c r="E46" s="77"/>
-      <c r="F46" s="77"/>
+      <c r="B46" s="79"/>
+      <c r="C46" s="79"/>
+      <c r="D46" s="79"/>
+      <c r="E46" s="79"/>
+      <c r="F46" s="79"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="78" t="s">
-        <v>131</v>
-      </c>
-      <c r="B48" s="78"/>
-      <c r="C48" s="78"/>
-      <c r="D48" s="78"/>
-      <c r="E48" s="78"/>
-      <c r="F48" s="78"/>
+      <c r="A48" s="80" t="s">
+        <v>134</v>
+      </c>
+      <c r="B48" s="80"/>
+      <c r="C48" s="80"/>
+      <c r="D48" s="80"/>
+      <c r="E48" s="80"/>
+      <c r="F48" s="80"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" password="df10" objects="true" scenarios="true" autoFilter="false"/>
   <mergeCells count="11">
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="E2:F2"/>

--- a/stock-statement/PEI-Stock-Register.xlsx
+++ b/stock-statement/PEI-Stock-Register.xlsx
@@ -17,12 +17,13 @@
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">'Daily Entry'!$6:$6</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Daily Entry'!$A$6:$E$250</definedName>
-    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">'Daily Report'!$A$1:$F$48</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Read me'!$A$1:$B$41</definedName>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Stock!$A$1:$J$50</definedName>
+    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">'Daily Report'!$A$1:$F$51</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Read me'!$A$1:$B$51</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Stock!$A$1:$J$70</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">Stock!$7:$7</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Stock!$A$7:$J$49</definedName>
-    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Summary!$A$1:$F$17</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Stock!$A$7:$J$69</definedName>
+    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Summary!$A$1:$F$20</definedName>
+    <definedName function="false" hidden="false" name="Products" vbProcedure="false">OFFSET(Stock!$L$8,0,0,MAX(1,COUNTA(Stock!$A$8:$A$69)),1)</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="143">
   <si>
     <t xml:space="preserve">PREMIER EXPORTS INTERNATIONAL</t>
   </si>
@@ -143,10 +144,34 @@
     <t xml:space="preserve">Adding a product</t>
   </si>
   <si>
-    <t xml:space="preserve">Add the row at the bottom of 'Stock' (brand, product, opening balance), then copy the</t>
-  </si>
-  <si>
-    <t xml:space="preserve">formulas down from the row above. The dropdown picks it up automatically.</t>
+    <t xml:space="preserve">'Stock' keeps 20 blank rows under the last product. Type the Brand, the Product and</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the Opening Balance into the first blank row — nothing else, and no unprotecting.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every formula on that row is already in place, and the row stays blank until you</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fill it. The 'Daily Entry' dropdown picks the new product up straight away.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adding a brand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do the same on 'Stock', then type the brand name into a blank row on 'Summary'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Until you do, a red line on Summary and on the Daily Report will tell you the</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brand list is incomplete and the totals are understated. Both clear themselves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When the blank rows run out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask for a rebuild — the file is generated, and a new one carries your data across.</t>
   </si>
   <si>
     <t xml:space="preserve">Source</t>
@@ -477,7 +502,7 @@
     <numFmt numFmtId="169" formatCode="[&gt;=10000000]&quot;₹ &quot;##\,##\,##\,##0.00;[&gt;=100000]&quot;₹ &quot;##\,##\,##0.00;&quot;₹ &quot;#,##0.00"/>
     <numFmt numFmtId="170" formatCode="General"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -686,6 +711,14 @@
     <font>
       <b val="true"/>
       <sz val="9"/>
+      <color rgb="FFB3261E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
       <color rgb="FF065E7A"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -894,7 +927,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="90">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1007,6 +1040,22 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1115,27 +1164,23 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1143,19 +1188,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="30" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="30" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1163,7 +1208,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="30" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="32" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1183,15 +1236,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1199,7 +1252,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1207,15 +1260,15 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="31" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="32" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1244,7 +1297,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1340,6 +1393,7 @@
         <diagonal/>
       </border>
     </dxf>
+    <dxf/>
   </dxfs>
   <colors>
     <indexedColors>
@@ -1634,7 +1688,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -1807,21 +1861,67 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="4"/>
+      <c r="B37" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="3" t="s">
-        <v>30</v>
+      <c r="B38" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="4" t="s">
-        <v>31</v>
-      </c>
+      <c r="B39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="3" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="4"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="4"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1841,7 +1941,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:N72"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="22"/>
@@ -1862,95 +1962,95 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C3" s="8" t="n">
         <v>46254</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K7" s="12"/>
       <c r="L7" s="13" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="M7" s="13" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C8" s="15" t="n">
         <v>11459</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L8,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A8="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L8,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>1068</v>
       </c>
       <c r="E8" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L8,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A8="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L8,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F8" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L8)</f>
+        <f aca="false">IF($A8="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L8))</f>
         <v>1068</v>
       </c>
       <c r="G8" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L8)</f>
+        <f aca="false">IF($A8="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L8))</f>
         <v>0</v>
       </c>
       <c r="H8" s="18" t="n">
-        <f aca="false">$C8+$F8-$G8</f>
+        <f aca="false">IF($A8="","",$C8+$F8-$G8)</f>
         <v>12527</v>
       </c>
       <c r="I8" s="19"/>
@@ -1959,11 +2059,11 @@
         <v/>
       </c>
       <c r="L8" s="21" t="str">
-        <f aca="false">$A8&amp;" - "&amp;$B8</f>
+        <f aca="false">IF($A8="","",$A8&amp;" - "&amp;$B8)</f>
         <v>Blue Dolphin - PD PVN 100/200</v>
       </c>
       <c r="M8" s="21" t="n">
-        <f aca="false">IF(OR($D8&lt;&gt;0,$E8&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A8="",0,IF(OR($D8&lt;&gt;0,$E8&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
       <c r="N8" s="21" t="n">
@@ -1973,32 +2073,32 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="22" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>517</v>
       </c>
       <c r="D9" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L9,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A9="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L9,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>65</v>
       </c>
       <c r="E9" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L9,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A9="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L9,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F9" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L9)</f>
+        <f aca="false">IF($A9="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L9))</f>
         <v>65</v>
       </c>
       <c r="G9" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L9)</f>
+        <f aca="false">IF($A9="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L9))</f>
         <v>0</v>
       </c>
       <c r="H9" s="26" t="n">
-        <f aca="false">$C9+$F9-$G9</f>
+        <f aca="false">IF($A9="","",$C9+$F9-$G9)</f>
         <v>582</v>
       </c>
       <c r="I9" s="19"/>
@@ -2007,11 +2107,11 @@
         <v/>
       </c>
       <c r="L9" s="21" t="str">
-        <f aca="false">$A9&amp;" - "&amp;$B9</f>
+        <f aca="false">IF($A9="","",$A9&amp;" - "&amp;$B9)</f>
         <v>Blue Dolphin - PD KKD 100/200</v>
       </c>
       <c r="M9" s="21" t="n">
-        <f aca="false">IF(OR($D9&lt;&gt;0,$E9&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A9="",0,IF(OR($D9&lt;&gt;0,$E9&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
       <c r="N9" s="21" t="n">
@@ -2021,32 +2121,32 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C10" s="15" t="n">
         <v>2262</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L10,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A10="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L10,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>267</v>
       </c>
       <c r="E10" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L10,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A10="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L10,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F10" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L10)</f>
+        <f aca="false">IF($A10="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L10))</f>
         <v>267</v>
       </c>
       <c r="G10" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L10)</f>
+        <f aca="false">IF($A10="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L10))</f>
         <v>0</v>
       </c>
       <c r="H10" s="18" t="n">
-        <f aca="false">$C10+$F10-$G10</f>
+        <f aca="false">IF($A10="","",$C10+$F10-$G10)</f>
         <v>2529</v>
       </c>
       <c r="I10" s="19"/>
@@ -2055,11 +2155,11 @@
         <v/>
       </c>
       <c r="L10" s="21" t="str">
-        <f aca="false">$A10&amp;" - "&amp;$B10</f>
+        <f aca="false">IF($A10="","",$A10&amp;" - "&amp;$B10)</f>
         <v>Blue Dolphin - PUD PVN 200/300</v>
       </c>
       <c r="M10" s="21" t="n">
-        <f aca="false">IF(OR($D10&lt;&gt;0,$E10&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A10="",0,IF(OR($D10&lt;&gt;0,$E10&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
       <c r="N10" s="21" t="n">
@@ -2069,32 +2169,32 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="22" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>2835</v>
       </c>
       <c r="D11" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L11,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A11="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L11,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E11" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L11,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A11="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L11,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F11" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L11)</f>
+        <f aca="false">IF($A11="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L11))</f>
         <v>0</v>
       </c>
       <c r="G11" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L11)</f>
+        <f aca="false">IF($A11="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L11))</f>
         <v>0</v>
       </c>
       <c r="H11" s="26" t="n">
-        <f aca="false">$C11+$F11-$G11</f>
+        <f aca="false">IF($A11="","",$C11+$F11-$G11)</f>
         <v>2835</v>
       </c>
       <c r="I11" s="19"/>
@@ -2103,11 +2203,11 @@
         <v/>
       </c>
       <c r="L11" s="21" t="str">
-        <f aca="false">$A11&amp;" - "&amp;$B11</f>
+        <f aca="false">IF($A11="","",$A11&amp;" - "&amp;$B11)</f>
         <v>Blue Dolphin - PUD KKD 200/300</v>
       </c>
       <c r="M11" s="21" t="n">
-        <f aca="false">IF(OR($D11&lt;&gt;0,$E11&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A11="",0,IF(OR($D11&lt;&gt;0,$E11&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N11" s="21" t="str">
@@ -2117,32 +2217,32 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C12" s="15" t="n">
         <v>1673</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L12,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A12="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L12,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E12" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L12,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A12="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L12,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F12" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L12)</f>
+        <f aca="false">IF($A12="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L12))</f>
         <v>0</v>
       </c>
       <c r="G12" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L12)</f>
+        <f aca="false">IF($A12="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L12))</f>
         <v>0</v>
       </c>
       <c r="H12" s="18" t="n">
-        <f aca="false">$C12+$F12-$G12</f>
+        <f aca="false">IF($A12="","",$C12+$F12-$G12)</f>
         <v>1673</v>
       </c>
       <c r="I12" s="19"/>
@@ -2151,11 +2251,11 @@
         <v/>
       </c>
       <c r="L12" s="21" t="str">
-        <f aca="false">$A12&amp;" - "&amp;$B12</f>
+        <f aca="false">IF($A12="","",$A12&amp;" - "&amp;$B12)</f>
         <v>Blue Dolphin - PUD PVN 300/500</v>
       </c>
       <c r="M12" s="21" t="n">
-        <f aca="false">IF(OR($D12&lt;&gt;0,$E12&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A12="",0,IF(OR($D12&lt;&gt;0,$E12&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N12" s="21" t="str">
@@ -2165,32 +2265,32 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="22" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>7542</v>
       </c>
       <c r="D13" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L13,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A13="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L13,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E13" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L13,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A13="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L13,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F13" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L13)</f>
+        <f aca="false">IF($A13="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L13))</f>
         <v>0</v>
       </c>
       <c r="G13" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L13)</f>
+        <f aca="false">IF($A13="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L13))</f>
         <v>0</v>
       </c>
       <c r="H13" s="26" t="n">
-        <f aca="false">$C13+$F13-$G13</f>
+        <f aca="false">IF($A13="","",$C13+$F13-$G13)</f>
         <v>7542</v>
       </c>
       <c r="I13" s="19"/>
@@ -2199,11 +2299,11 @@
         <v/>
       </c>
       <c r="L13" s="21" t="str">
-        <f aca="false">$A13&amp;" - "&amp;$B13</f>
+        <f aca="false">IF($A13="","",$A13&amp;" - "&amp;$B13)</f>
         <v>Blue Dolphin - PUD KKD 300/500</v>
       </c>
       <c r="M13" s="21" t="n">
-        <f aca="false">IF(OR($D13&lt;&gt;0,$E13&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A13="",0,IF(OR($D13&lt;&gt;0,$E13&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N13" s="21" t="str">
@@ -2213,32 +2313,32 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>2357</v>
       </c>
       <c r="D14" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L14,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A14="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L14,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E14" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L14,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A14="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L14,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F14" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L14)</f>
+        <f aca="false">IF($A14="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L14))</f>
         <v>0</v>
       </c>
       <c r="G14" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L14)</f>
+        <f aca="false">IF($A14="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L14))</f>
         <v>0</v>
       </c>
       <c r="H14" s="18" t="n">
-        <f aca="false">$C14+$F14-$G14</f>
+        <f aca="false">IF($A14="","",$C14+$F14-$G14)</f>
         <v>2357</v>
       </c>
       <c r="I14" s="19"/>
@@ -2247,11 +2347,11 @@
         <v/>
       </c>
       <c r="L14" s="21" t="str">
-        <f aca="false">$A14&amp;" - "&amp;$B14</f>
+        <f aca="false">IF($A14="","",$A14&amp;" - "&amp;$B14)</f>
         <v>Blue Dolphin - PD PVN 200/300</v>
       </c>
       <c r="M14" s="21" t="n">
-        <f aca="false">IF(OR($D14&lt;&gt;0,$E14&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A14="",0,IF(OR($D14&lt;&gt;0,$E14&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N14" s="21" t="str">
@@ -2261,32 +2361,32 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="22" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>64</v>
       </c>
       <c r="D15" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L15,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A15="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L15,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>29</v>
       </c>
       <c r="E15" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L15,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A15="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L15,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F15" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L15)</f>
+        <f aca="false">IF($A15="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L15))</f>
         <v>29</v>
       </c>
       <c r="G15" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L15)</f>
+        <f aca="false">IF($A15="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L15))</f>
         <v>0</v>
       </c>
       <c r="H15" s="26" t="n">
-        <f aca="false">$C15+$F15-$G15</f>
+        <f aca="false">IF($A15="","",$C15+$F15-$G15)</f>
         <v>93</v>
       </c>
       <c r="I15" s="19"/>
@@ -2295,11 +2395,11 @@
         <v/>
       </c>
       <c r="L15" s="21" t="str">
-        <f aca="false">$A15&amp;" - "&amp;$B15</f>
+        <f aca="false">IF($A15="","",$A15&amp;" - "&amp;$B15)</f>
         <v>Primus Japan - PUD KZN 40/60</v>
       </c>
       <c r="M15" s="21" t="n">
-        <f aca="false">IF(OR($D15&lt;&gt;0,$E15&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A15="",0,IF(OR($D15&lt;&gt;0,$E15&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
       <c r="N15" s="21" t="n">
@@ -2309,32 +2409,32 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C16" s="15" t="n">
         <v>191</v>
       </c>
       <c r="D16" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L16,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A16="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L16,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>39</v>
       </c>
       <c r="E16" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L16,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A16="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L16,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F16" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L16)</f>
+        <f aca="false">IF($A16="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L16))</f>
         <v>39</v>
       </c>
       <c r="G16" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L16)</f>
+        <f aca="false">IF($A16="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L16))</f>
         <v>0</v>
       </c>
       <c r="H16" s="18" t="n">
-        <f aca="false">$C16+$F16-$G16</f>
+        <f aca="false">IF($A16="","",$C16+$F16-$G16)</f>
         <v>230</v>
       </c>
       <c r="I16" s="19"/>
@@ -2343,11 +2443,11 @@
         <v/>
       </c>
       <c r="L16" s="21" t="str">
-        <f aca="false">$A16&amp;" - "&amp;$B16</f>
+        <f aca="false">IF($A16="","",$A16&amp;" - "&amp;$B16)</f>
         <v>Primus Japan - PUD KZN 60/80</v>
       </c>
       <c r="M16" s="21" t="n">
-        <f aca="false">IF(OR($D16&lt;&gt;0,$E16&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A16="",0,IF(OR($D16&lt;&gt;0,$E16&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
       <c r="N16" s="21" t="n">
@@ -2357,32 +2457,32 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="22" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>16849</v>
       </c>
       <c r="D17" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L17,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A17="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L17,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E17" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L17,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A17="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L17,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F17" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L17)</f>
+        <f aca="false">IF($A17="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L17))</f>
         <v>0</v>
       </c>
       <c r="G17" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L17)</f>
+        <f aca="false">IF($A17="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L17))</f>
         <v>0</v>
       </c>
       <c r="H17" s="26" t="n">
-        <f aca="false">$C17+$F17-$G17</f>
+        <f aca="false">IF($A17="","",$C17+$F17-$G17)</f>
         <v>16849</v>
       </c>
       <c r="I17" s="19"/>
@@ -2391,11 +2491,11 @@
         <v/>
       </c>
       <c r="L17" s="21" t="str">
-        <f aca="false">$A17&amp;" - "&amp;$B17</f>
+        <f aca="false">IF($A17="","",$A17&amp;" - "&amp;$B17)</f>
         <v>Primus Japan - PUD PVN 80/120</v>
       </c>
       <c r="M17" s="21" t="n">
-        <f aca="false">IF(OR($D17&lt;&gt;0,$E17&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A17="",0,IF(OR($D17&lt;&gt;0,$E17&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N17" s="21" t="str">
@@ -2405,32 +2505,32 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C18" s="15" t="n">
         <v>466</v>
       </c>
       <c r="D18" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L18,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A18="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L18,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>50</v>
       </c>
       <c r="E18" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L18,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A18="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L18,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F18" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L18)</f>
+        <f aca="false">IF($A18="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L18))</f>
         <v>50</v>
       </c>
       <c r="G18" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L18)</f>
+        <f aca="false">IF($A18="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L18))</f>
         <v>0</v>
       </c>
       <c r="H18" s="18" t="n">
-        <f aca="false">$C18+$F18-$G18</f>
+        <f aca="false">IF($A18="","",$C18+$F18-$G18)</f>
         <v>516</v>
       </c>
       <c r="I18" s="19"/>
@@ -2439,11 +2539,11 @@
         <v/>
       </c>
       <c r="L18" s="21" t="str">
-        <f aca="false">$A18&amp;" - "&amp;$B18</f>
+        <f aca="false">IF($A18="","",$A18&amp;" - "&amp;$B18)</f>
         <v>Primus Japan - PUD KZN 80/120</v>
       </c>
       <c r="M18" s="21" t="n">
-        <f aca="false">IF(OR($D18&lt;&gt;0,$E18&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A18="",0,IF(OR($D18&lt;&gt;0,$E18&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
       <c r="N18" s="21" t="n">
@@ -2453,32 +2553,32 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="22" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>69</v>
       </c>
       <c r="D19" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L19,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A19="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L19,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>3</v>
       </c>
       <c r="E19" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L19,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A19="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L19,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F19" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L19)</f>
+        <f aca="false">IF($A19="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L19))</f>
         <v>3</v>
       </c>
       <c r="G19" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L19)</f>
+        <f aca="false">IF($A19="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L19))</f>
         <v>0</v>
       </c>
       <c r="H19" s="26" t="n">
-        <f aca="false">$C19+$F19-$G19</f>
+        <f aca="false">IF($A19="","",$C19+$F19-$G19)</f>
         <v>72</v>
       </c>
       <c r="I19" s="19"/>
@@ -2487,11 +2587,11 @@
         <v/>
       </c>
       <c r="L19" s="21" t="str">
-        <f aca="false">$A19&amp;" - "&amp;$B19</f>
+        <f aca="false">IF($A19="","",$A19&amp;" - "&amp;$B19)</f>
         <v>Primus Japan - PUD NRN 80/120</v>
       </c>
       <c r="M19" s="21" t="n">
-        <f aca="false">IF(OR($D19&lt;&gt;0,$E19&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A19="",0,IF(OR($D19&lt;&gt;0,$E19&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
       <c r="N19" s="21" t="n">
@@ -2501,32 +2601,32 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C20" s="15" t="n">
         <v>2617</v>
       </c>
       <c r="D20" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L20,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A20="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L20,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E20" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L20,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A20="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L20,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F20" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L20)</f>
+        <f aca="false">IF($A20="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L20))</f>
         <v>0</v>
       </c>
       <c r="G20" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L20)</f>
+        <f aca="false">IF($A20="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L20))</f>
         <v>0</v>
       </c>
       <c r="H20" s="18" t="n">
-        <f aca="false">$C20+$F20-$G20</f>
+        <f aca="false">IF($A20="","",$C20+$F20-$G20)</f>
         <v>2617</v>
       </c>
       <c r="I20" s="19"/>
@@ -2535,11 +2635,11 @@
         <v/>
       </c>
       <c r="L20" s="21" t="str">
-        <f aca="false">$A20&amp;" - "&amp;$B20</f>
+        <f aca="false">IF($A20="","",$A20&amp;" - "&amp;$B20)</f>
         <v>Primus Japan - PUD PVN 100/200</v>
       </c>
       <c r="M20" s="21" t="n">
-        <f aca="false">IF(OR($D20&lt;&gt;0,$E20&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A20="",0,IF(OR($D20&lt;&gt;0,$E20&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N20" s="21" t="str">
@@ -2549,32 +2649,32 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="22" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C21" s="23" t="n">
         <v>13</v>
       </c>
       <c r="D21" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L21,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A21="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L21,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E21" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L21,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A21="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L21,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F21" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L21)</f>
+        <f aca="false">IF($A21="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L21))</f>
         <v>0</v>
       </c>
       <c r="G21" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L21)</f>
+        <f aca="false">IF($A21="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L21))</f>
         <v>0</v>
       </c>
       <c r="H21" s="26" t="n">
-        <f aca="false">$C21+$F21-$G21</f>
+        <f aca="false">IF($A21="","",$C21+$F21-$G21)</f>
         <v>13</v>
       </c>
       <c r="I21" s="19"/>
@@ -2583,11 +2683,11 @@
         <v/>
       </c>
       <c r="L21" s="21" t="str">
-        <f aca="false">$A21&amp;" - "&amp;$B21</f>
+        <f aca="false">IF($A21="","",$A21&amp;" - "&amp;$B21)</f>
         <v>Primus Japan - PUD NRN 100/200</v>
       </c>
       <c r="M21" s="21" t="n">
-        <f aca="false">IF(OR($D21&lt;&gt;0,$E21&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A21="",0,IF(OR($D21&lt;&gt;0,$E21&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N21" s="21" t="str">
@@ -2597,32 +2697,32 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C22" s="15" t="n">
         <v>4209</v>
       </c>
       <c r="D22" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L22,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A22="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L22,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>50</v>
       </c>
       <c r="E22" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L22,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A22="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L22,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F22" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L22)</f>
+        <f aca="false">IF($A22="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L22))</f>
         <v>50</v>
       </c>
       <c r="G22" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L22)</f>
+        <f aca="false">IF($A22="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L22))</f>
         <v>0</v>
       </c>
       <c r="H22" s="18" t="n">
-        <f aca="false">$C22+$F22-$G22</f>
+        <f aca="false">IF($A22="","",$C22+$F22-$G22)</f>
         <v>4259</v>
       </c>
       <c r="I22" s="19"/>
@@ -2631,11 +2731,11 @@
         <v/>
       </c>
       <c r="L22" s="21" t="str">
-        <f aca="false">$A22&amp;" - "&amp;$B22</f>
+        <f aca="false">IF($A22="","",$A22&amp;" - "&amp;$B22)</f>
         <v>Primus Japan - PUD KZN 100/200</v>
       </c>
       <c r="M22" s="21" t="n">
-        <f aca="false">IF(OR($D22&lt;&gt;0,$E22&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A22="",0,IF(OR($D22&lt;&gt;0,$E22&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
       <c r="N22" s="21" t="n">
@@ -2645,32 +2745,32 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="22" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C23" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L23,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A23="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L23,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E23" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L23,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A23="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L23,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F23" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L23)</f>
+        <f aca="false">IF($A23="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L23))</f>
         <v>0</v>
       </c>
       <c r="G23" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L23)</f>
+        <f aca="false">IF($A23="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L23))</f>
         <v>0</v>
       </c>
       <c r="H23" s="26" t="n">
-        <f aca="false">$C23+$F23-$G23</f>
+        <f aca="false">IF($A23="","",$C23+$F23-$G23)</f>
         <v>0</v>
       </c>
       <c r="I23" s="19"/>
@@ -2679,11 +2779,11 @@
         <v/>
       </c>
       <c r="L23" s="21" t="str">
-        <f aca="false">$A23&amp;" - "&amp;$B23</f>
+        <f aca="false">IF($A23="","",$A23&amp;" - "&amp;$B23)</f>
         <v>Primus Japan - PUD PVN 200/300</v>
       </c>
       <c r="M23" s="21" t="n">
-        <f aca="false">IF(OR($D23&lt;&gt;0,$E23&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A23="",0,IF(OR($D23&lt;&gt;0,$E23&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N23" s="21" t="str">
@@ -2693,32 +2793,32 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C24" s="15" t="n">
         <v>2757</v>
       </c>
       <c r="D24" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L24,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A24="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L24,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E24" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L24,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A24="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L24,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F24" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L24)</f>
+        <f aca="false">IF($A24="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L24))</f>
         <v>0</v>
       </c>
       <c r="G24" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L24)</f>
+        <f aca="false">IF($A24="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L24))</f>
         <v>0</v>
       </c>
       <c r="H24" s="18" t="n">
-        <f aca="false">$C24+$F24-$G24</f>
+        <f aca="false">IF($A24="","",$C24+$F24-$G24)</f>
         <v>2757</v>
       </c>
       <c r="I24" s="19"/>
@@ -2727,11 +2827,11 @@
         <v/>
       </c>
       <c r="L24" s="21" t="str">
-        <f aca="false">$A24&amp;" - "&amp;$B24</f>
+        <f aca="false">IF($A24="","",$A24&amp;" - "&amp;$B24)</f>
         <v>Primus Japan - PUD KKD 200/300</v>
       </c>
       <c r="M24" s="21" t="n">
-        <f aca="false">IF(OR($D24&lt;&gt;0,$E24&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A24="",0,IF(OR($D24&lt;&gt;0,$E24&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N24" s="21" t="str">
@@ -2741,32 +2841,32 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="22" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C25" s="23" t="n">
         <v>1080</v>
       </c>
       <c r="D25" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L25,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A25="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L25,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>33</v>
       </c>
       <c r="E25" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L25,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A25="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L25,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F25" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L25)</f>
+        <f aca="false">IF($A25="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L25))</f>
         <v>33</v>
       </c>
       <c r="G25" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L25)</f>
+        <f aca="false">IF($A25="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L25))</f>
         <v>0</v>
       </c>
       <c r="H25" s="26" t="n">
-        <f aca="false">$C25+$F25-$G25</f>
+        <f aca="false">IF($A25="","",$C25+$F25-$G25)</f>
         <v>1113</v>
       </c>
       <c r="I25" s="19"/>
@@ -2775,11 +2875,11 @@
         <v/>
       </c>
       <c r="L25" s="21" t="str">
-        <f aca="false">$A25&amp;" - "&amp;$B25</f>
+        <f aca="false">IF($A25="","",$A25&amp;" - "&amp;$B25)</f>
         <v>Primus Japan - PUD KZN 200/300</v>
       </c>
       <c r="M25" s="21" t="n">
-        <f aca="false">IF(OR($D25&lt;&gt;0,$E25&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A25="",0,IF(OR($D25&lt;&gt;0,$E25&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
       <c r="N25" s="21" t="n">
@@ -2789,32 +2889,32 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C26" s="15" t="n">
         <v>421</v>
       </c>
       <c r="D26" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L26,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A26="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L26,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>156</v>
       </c>
       <c r="E26" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L26,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A26="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L26,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F26" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L26)</f>
+        <f aca="false">IF($A26="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L26))</f>
         <v>156</v>
       </c>
       <c r="G26" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L26)</f>
+        <f aca="false">IF($A26="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L26))</f>
         <v>0</v>
       </c>
       <c r="H26" s="18" t="n">
-        <f aca="false">$C26+$F26-$G26</f>
+        <f aca="false">IF($A26="","",$C26+$F26-$G26)</f>
         <v>577</v>
       </c>
       <c r="I26" s="19"/>
@@ -2823,11 +2923,11 @@
         <v/>
       </c>
       <c r="L26" s="21" t="str">
-        <f aca="false">$A26&amp;" - "&amp;$B26</f>
+        <f aca="false">IF($A26="","",$A26&amp;" - "&amp;$B26)</f>
         <v>Primus Japan - PUD PVN 300/500</v>
       </c>
       <c r="M26" s="21" t="n">
-        <f aca="false">IF(OR($D26&lt;&gt;0,$E26&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A26="",0,IF(OR($D26&lt;&gt;0,$E26&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
       <c r="N26" s="21" t="n">
@@ -2837,32 +2937,32 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="22" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C27" s="23" t="n">
         <v>580</v>
       </c>
       <c r="D27" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L27,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A27="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L27,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>596</v>
       </c>
       <c r="E27" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L27,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A27="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L27,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F27" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L27)</f>
+        <f aca="false">IF($A27="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L27))</f>
         <v>596</v>
       </c>
       <c r="G27" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L27)</f>
+        <f aca="false">IF($A27="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L27))</f>
         <v>0</v>
       </c>
       <c r="H27" s="26" t="n">
-        <f aca="false">$C27+$F27-$G27</f>
+        <f aca="false">IF($A27="","",$C27+$F27-$G27)</f>
         <v>1176</v>
       </c>
       <c r="I27" s="19"/>
@@ -2871,11 +2971,11 @@
         <v/>
       </c>
       <c r="L27" s="21" t="str">
-        <f aca="false">$A27&amp;" - "&amp;$B27</f>
+        <f aca="false">IF($A27="","",$A27&amp;" - "&amp;$B27)</f>
         <v>Primus Japan - PUD KKD 300/500</v>
       </c>
       <c r="M27" s="21" t="n">
-        <f aca="false">IF(OR($D27&lt;&gt;0,$E27&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A27="",0,IF(OR($D27&lt;&gt;0,$E27&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
       <c r="N27" s="21" t="n">
@@ -2885,32 +2985,32 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C28" s="15" t="n">
         <v>185</v>
       </c>
       <c r="D28" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L28,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A28="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L28,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E28" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L28,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A28="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L28,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F28" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L28)</f>
+        <f aca="false">IF($A28="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L28))</f>
         <v>0</v>
       </c>
       <c r="G28" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L28)</f>
+        <f aca="false">IF($A28="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L28))</f>
         <v>0</v>
       </c>
       <c r="H28" s="18" t="n">
-        <f aca="false">$C28+$F28-$G28</f>
+        <f aca="false">IF($A28="","",$C28+$F28-$G28)</f>
         <v>185</v>
       </c>
       <c r="I28" s="19"/>
@@ -2919,11 +3019,11 @@
         <v/>
       </c>
       <c r="L28" s="21" t="str">
-        <f aca="false">$A28&amp;" - "&amp;$B28</f>
+        <f aca="false">IF($A28="","",$A28&amp;" - "&amp;$B28)</f>
         <v>Primus EU - PUD 20/40</v>
       </c>
       <c r="M28" s="21" t="n">
-        <f aca="false">IF(OR($D28&lt;&gt;0,$E28&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A28="",0,IF(OR($D28&lt;&gt;0,$E28&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N28" s="21" t="str">
@@ -2933,32 +3033,32 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="22" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C29" s="23" t="n">
         <v>368</v>
       </c>
       <c r="D29" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L29,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A29="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L29,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E29" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L29,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A29="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L29,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F29" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L29)</f>
+        <f aca="false">IF($A29="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L29))</f>
         <v>0</v>
       </c>
       <c r="G29" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L29)</f>
+        <f aca="false">IF($A29="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L29))</f>
         <v>0</v>
       </c>
       <c r="H29" s="26" t="n">
-        <f aca="false">$C29+$F29-$G29</f>
+        <f aca="false">IF($A29="","",$C29+$F29-$G29)</f>
         <v>368</v>
       </c>
       <c r="I29" s="19"/>
@@ -2967,11 +3067,11 @@
         <v/>
       </c>
       <c r="L29" s="21" t="str">
-        <f aca="false">$A29&amp;" - "&amp;$B29</f>
+        <f aca="false">IF($A29="","",$A29&amp;" - "&amp;$B29)</f>
         <v>Primus EU - PUD 40/60</v>
       </c>
       <c r="M29" s="21" t="n">
-        <f aca="false">IF(OR($D29&lt;&gt;0,$E29&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A29="",0,IF(OR($D29&lt;&gt;0,$E29&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N29" s="21" t="str">
@@ -2981,32 +3081,32 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C30" s="15" t="n">
         <v>380</v>
       </c>
       <c r="D30" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L30,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A30="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L30,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E30" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L30,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A30="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L30,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F30" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L30)</f>
+        <f aca="false">IF($A30="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L30))</f>
         <v>0</v>
       </c>
       <c r="G30" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L30)</f>
+        <f aca="false">IF($A30="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L30))</f>
         <v>0</v>
       </c>
       <c r="H30" s="18" t="n">
-        <f aca="false">$C30+$F30-$G30</f>
+        <f aca="false">IF($A30="","",$C30+$F30-$G30)</f>
         <v>380</v>
       </c>
       <c r="I30" s="19"/>
@@ -3015,11 +3115,11 @@
         <v/>
       </c>
       <c r="L30" s="21" t="str">
-        <f aca="false">$A30&amp;" - "&amp;$B30</f>
+        <f aca="false">IF($A30="","",$A30&amp;" - "&amp;$B30)</f>
         <v>Primus EU - PUD 60/80</v>
       </c>
       <c r="M30" s="21" t="n">
-        <f aca="false">IF(OR($D30&lt;&gt;0,$E30&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A30="",0,IF(OR($D30&lt;&gt;0,$E30&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N30" s="21" t="str">
@@ -3029,32 +3129,32 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="22" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C31" s="23" t="n">
         <v>1151</v>
       </c>
       <c r="D31" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L31,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A31="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L31,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E31" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L31,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A31="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L31,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F31" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L31)</f>
+        <f aca="false">IF($A31="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L31))</f>
         <v>0</v>
       </c>
       <c r="G31" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L31)</f>
+        <f aca="false">IF($A31="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L31))</f>
         <v>0</v>
       </c>
       <c r="H31" s="26" t="n">
-        <f aca="false">$C31+$F31-$G31</f>
+        <f aca="false">IF($A31="","",$C31+$F31-$G31)</f>
         <v>1151</v>
       </c>
       <c r="I31" s="19"/>
@@ -3063,11 +3163,11 @@
         <v/>
       </c>
       <c r="L31" s="21" t="str">
-        <f aca="false">$A31&amp;" - "&amp;$B31</f>
+        <f aca="false">IF($A31="","",$A31&amp;" - "&amp;$B31)</f>
         <v>Primus EU - PUD 80/120</v>
       </c>
       <c r="M31" s="21" t="n">
-        <f aca="false">IF(OR($D31&lt;&gt;0,$E31&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A31="",0,IF(OR($D31&lt;&gt;0,$E31&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N31" s="21" t="str">
@@ -3077,32 +3177,32 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C32" s="15" t="n">
         <v>3797</v>
       </c>
       <c r="D32" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L32,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A32="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L32,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E32" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L32,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A32="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L32,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F32" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L32)</f>
+        <f aca="false">IF($A32="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L32))</f>
         <v>0</v>
       </c>
       <c r="G32" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L32)</f>
+        <f aca="false">IF($A32="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L32))</f>
         <v>0</v>
       </c>
       <c r="H32" s="18" t="n">
-        <f aca="false">$C32+$F32-$G32</f>
+        <f aca="false">IF($A32="","",$C32+$F32-$G32)</f>
         <v>3797</v>
       </c>
       <c r="I32" s="19"/>
@@ -3111,11 +3211,11 @@
         <v/>
       </c>
       <c r="L32" s="21" t="str">
-        <f aca="false">$A32&amp;" - "&amp;$B32</f>
+        <f aca="false">IF($A32="","",$A32&amp;" - "&amp;$B32)</f>
         <v>Primus EU - PUD 100/200</v>
       </c>
       <c r="M32" s="21" t="n">
-        <f aca="false">IF(OR($D32&lt;&gt;0,$E32&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A32="",0,IF(OR($D32&lt;&gt;0,$E32&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N32" s="21" t="str">
@@ -3125,32 +3225,32 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="22" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C33" s="23" t="n">
         <v>4118</v>
       </c>
       <c r="D33" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L33,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A33="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L33,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E33" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L33,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A33="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L33,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F33" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L33)</f>
+        <f aca="false">IF($A33="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L33))</f>
         <v>0</v>
       </c>
       <c r="G33" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L33)</f>
+        <f aca="false">IF($A33="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L33))</f>
         <v>0</v>
       </c>
       <c r="H33" s="26" t="n">
-        <f aca="false">$C33+$F33-$G33</f>
+        <f aca="false">IF($A33="","",$C33+$F33-$G33)</f>
         <v>4118</v>
       </c>
       <c r="I33" s="19"/>
@@ -3159,11 +3259,11 @@
         <v/>
       </c>
       <c r="L33" s="21" t="str">
-        <f aca="false">$A33&amp;" - "&amp;$B33</f>
+        <f aca="false">IF($A33="","",$A33&amp;" - "&amp;$B33)</f>
         <v>Primus EU - PUD 200/300</v>
       </c>
       <c r="M33" s="21" t="n">
-        <f aca="false">IF(OR($D33&lt;&gt;0,$E33&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A33="",0,IF(OR($D33&lt;&gt;0,$E33&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N33" s="21" t="str">
@@ -3173,32 +3273,32 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C34" s="15" t="n">
         <v>1490</v>
       </c>
       <c r="D34" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L34,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A34="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L34,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E34" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L34,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A34="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L34,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F34" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L34)</f>
+        <f aca="false">IF($A34="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L34))</f>
         <v>0</v>
       </c>
       <c r="G34" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L34)</f>
+        <f aca="false">IF($A34="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L34))</f>
         <v>0</v>
       </c>
       <c r="H34" s="18" t="n">
-        <f aca="false">$C34+$F34-$G34</f>
+        <f aca="false">IF($A34="","",$C34+$F34-$G34)</f>
         <v>1490</v>
       </c>
       <c r="I34" s="19"/>
@@ -3207,11 +3307,11 @@
         <v/>
       </c>
       <c r="L34" s="21" t="str">
-        <f aca="false">$A34&amp;" - "&amp;$B34</f>
+        <f aca="false">IF($A34="","",$A34&amp;" - "&amp;$B34)</f>
         <v>Primus EU - PUD 300/500</v>
       </c>
       <c r="M34" s="21" t="n">
-        <f aca="false">IF(OR($D34&lt;&gt;0,$E34&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A34="",0,IF(OR($D34&lt;&gt;0,$E34&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N34" s="21" t="str">
@@ -3221,32 +3321,32 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="22" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C35" s="23" t="n">
         <v>15130</v>
       </c>
       <c r="D35" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L35,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A35="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L35,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>52</v>
       </c>
       <c r="E35" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L35,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A35="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L35,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F35" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L35)</f>
+        <f aca="false">IF($A35="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L35))</f>
         <v>52</v>
       </c>
       <c r="G35" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L35)</f>
+        <f aca="false">IF($A35="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L35))</f>
         <v>0</v>
       </c>
       <c r="H35" s="26" t="n">
-        <f aca="false">$C35+$F35-$G35</f>
+        <f aca="false">IF($A35="","",$C35+$F35-$G35)</f>
         <v>15182</v>
       </c>
       <c r="I35" s="19"/>
@@ -3255,11 +3355,11 @@
         <v/>
       </c>
       <c r="L35" s="21" t="str">
-        <f aca="false">$A35&amp;" - "&amp;$B35</f>
+        <f aca="false">IF($A35="","",$A35&amp;" - "&amp;$B35)</f>
         <v>Primus EU - BKN</v>
       </c>
       <c r="M35" s="21" t="n">
-        <f aca="false">IF(OR($D35&lt;&gt;0,$E35&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A35="",0,IF(OR($D35&lt;&gt;0,$E35&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
       <c r="N35" s="21" t="n">
@@ -3269,32 +3369,32 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C36" s="15" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L36,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A36="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L36,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E36" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L36,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A36="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L36,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F36" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L36)</f>
+        <f aca="false">IF($A36="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L36))</f>
         <v>0</v>
       </c>
       <c r="G36" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L36)</f>
+        <f aca="false">IF($A36="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L36))</f>
         <v>0</v>
       </c>
       <c r="H36" s="18" t="n">
-        <f aca="false">$C36+$F36-$G36</f>
+        <f aca="false">IF($A36="","",$C36+$F36-$G36)</f>
         <v>0</v>
       </c>
       <c r="I36" s="19"/>
@@ -3303,11 +3403,11 @@
         <v/>
       </c>
       <c r="L36" s="21" t="str">
-        <f aca="false">$A36&amp;" - "&amp;$B36</f>
+        <f aca="false">IF($A36="","",$A36&amp;" - "&amp;$B36)</f>
         <v>AMF Brand - PD PVN 100/200</v>
       </c>
       <c r="M36" s="21" t="n">
-        <f aca="false">IF(OR($D36&lt;&gt;0,$E36&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A36="",0,IF(OR($D36&lt;&gt;0,$E36&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N36" s="21" t="str">
@@ -3317,32 +3417,32 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="22" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C37" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L37,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A37="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L37,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E37" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L37,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A37="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L37,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F37" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L37)</f>
+        <f aca="false">IF($A37="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L37))</f>
         <v>0</v>
       </c>
       <c r="G37" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L37)</f>
+        <f aca="false">IF($A37="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L37))</f>
         <v>0</v>
       </c>
       <c r="H37" s="26" t="n">
-        <f aca="false">$C37+$F37-$G37</f>
+        <f aca="false">IF($A37="","",$C37+$F37-$G37)</f>
         <v>0</v>
       </c>
       <c r="I37" s="19"/>
@@ -3351,11 +3451,11 @@
         <v/>
       </c>
       <c r="L37" s="21" t="str">
-        <f aca="false">$A37&amp;" - "&amp;$B37</f>
+        <f aca="false">IF($A37="","",$A37&amp;" - "&amp;$B37)</f>
         <v>AMF Brand - PD KKD 100/200</v>
       </c>
       <c r="M37" s="21" t="n">
-        <f aca="false">IF(OR($D37&lt;&gt;0,$E37&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A37="",0,IF(OR($D37&lt;&gt;0,$E37&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N37" s="21" t="str">
@@ -3365,32 +3465,32 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C38" s="15" t="n">
         <v>1516</v>
       </c>
       <c r="D38" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L38,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A38="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L38,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E38" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L38,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A38="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L38,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F38" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L38)</f>
+        <f aca="false">IF($A38="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L38))</f>
         <v>0</v>
       </c>
       <c r="G38" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L38)</f>
+        <f aca="false">IF($A38="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L38))</f>
         <v>0</v>
       </c>
       <c r="H38" s="18" t="n">
-        <f aca="false">$C38+$F38-$G38</f>
+        <f aca="false">IF($A38="","",$C38+$F38-$G38)</f>
         <v>1516</v>
       </c>
       <c r="I38" s="19"/>
@@ -3399,11 +3499,11 @@
         <v/>
       </c>
       <c r="L38" s="21" t="str">
-        <f aca="false">$A38&amp;" - "&amp;$B38</f>
+        <f aca="false">IF($A38="","",$A38&amp;" - "&amp;$B38)</f>
         <v>AMF Brand - PUD PVN 200/300</v>
       </c>
       <c r="M38" s="21" t="n">
-        <f aca="false">IF(OR($D38&lt;&gt;0,$E38&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A38="",0,IF(OR($D38&lt;&gt;0,$E38&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N38" s="21" t="str">
@@ -3413,32 +3513,32 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="22" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C39" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D39" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L39,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A39="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L39,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E39" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L39,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A39="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L39,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F39" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L39)</f>
+        <f aca="false">IF($A39="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L39))</f>
         <v>0</v>
       </c>
       <c r="G39" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L39)</f>
+        <f aca="false">IF($A39="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L39))</f>
         <v>0</v>
       </c>
       <c r="H39" s="26" t="n">
-        <f aca="false">$C39+$F39-$G39</f>
+        <f aca="false">IF($A39="","",$C39+$F39-$G39)</f>
         <v>0</v>
       </c>
       <c r="I39" s="19"/>
@@ -3447,11 +3547,11 @@
         <v/>
       </c>
       <c r="L39" s="21" t="str">
-        <f aca="false">$A39&amp;" - "&amp;$B39</f>
+        <f aca="false">IF($A39="","",$A39&amp;" - "&amp;$B39)</f>
         <v>AMF Brand - PUD KKD 200/300</v>
       </c>
       <c r="M39" s="21" t="n">
-        <f aca="false">IF(OR($D39&lt;&gt;0,$E39&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A39="",0,IF(OR($D39&lt;&gt;0,$E39&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N39" s="21" t="str">
@@ -3461,32 +3561,32 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C40" s="15" t="n">
         <v>18</v>
       </c>
       <c r="D40" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L40,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A40="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L40,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E40" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L40,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A40="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L40,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F40" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L40)</f>
+        <f aca="false">IF($A40="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L40))</f>
         <v>0</v>
       </c>
       <c r="G40" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L40)</f>
+        <f aca="false">IF($A40="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L40))</f>
         <v>0</v>
       </c>
       <c r="H40" s="18" t="n">
-        <f aca="false">$C40+$F40-$G40</f>
+        <f aca="false">IF($A40="","",$C40+$F40-$G40)</f>
         <v>18</v>
       </c>
       <c r="I40" s="19"/>
@@ -3495,11 +3595,11 @@
         <v/>
       </c>
       <c r="L40" s="21" t="str">
-        <f aca="false">$A40&amp;" - "&amp;$B40</f>
+        <f aca="false">IF($A40="","",$A40&amp;" - "&amp;$B40)</f>
         <v>AMF Brand - PUD PVN 300/500</v>
       </c>
       <c r="M40" s="21" t="n">
-        <f aca="false">IF(OR($D40&lt;&gt;0,$E40&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A40="",0,IF(OR($D40&lt;&gt;0,$E40&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N40" s="21" t="str">
@@ -3509,32 +3609,32 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="22" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C41" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D41" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L41,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A41="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L41,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E41" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L41,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A41="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L41,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F41" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L41)</f>
+        <f aca="false">IF($A41="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L41))</f>
         <v>0</v>
       </c>
       <c r="G41" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L41)</f>
+        <f aca="false">IF($A41="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L41))</f>
         <v>0</v>
       </c>
       <c r="H41" s="26" t="n">
-        <f aca="false">$C41+$F41-$G41</f>
+        <f aca="false">IF($A41="","",$C41+$F41-$G41)</f>
         <v>0</v>
       </c>
       <c r="I41" s="19"/>
@@ -3543,11 +3643,11 @@
         <v/>
       </c>
       <c r="L41" s="21" t="str">
-        <f aca="false">$A41&amp;" - "&amp;$B41</f>
+        <f aca="false">IF($A41="","",$A41&amp;" - "&amp;$B41)</f>
         <v>AMF Brand - PUD KKD 300/500</v>
       </c>
       <c r="M41" s="21" t="n">
-        <f aca="false">IF(OR($D41&lt;&gt;0,$E41&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A41="",0,IF(OR($D41&lt;&gt;0,$E41&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N41" s="21" t="str">
@@ -3557,32 +3657,32 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="14" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C42" s="15" t="n">
         <v>1389</v>
       </c>
       <c r="D42" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L42,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A42="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L42,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>1872</v>
       </c>
       <c r="E42" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L42,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A42="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L42,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F42" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L42)</f>
+        <f aca="false">IF($A42="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L42))</f>
         <v>1872</v>
       </c>
       <c r="G42" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L42)</f>
+        <f aca="false">IF($A42="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L42))</f>
         <v>0</v>
       </c>
       <c r="H42" s="18" t="n">
-        <f aca="false">$C42+$F42-$G42</f>
+        <f aca="false">IF($A42="","",$C42+$F42-$G42)</f>
         <v>3261</v>
       </c>
       <c r="I42" s="19"/>
@@ -3591,11 +3691,11 @@
         <v/>
       </c>
       <c r="L42" s="21" t="str">
-        <f aca="false">$A42&amp;" - "&amp;$B42</f>
+        <f aca="false">IF($A42="","",$A42&amp;" - "&amp;$B42)</f>
         <v>THT Brand - PUD PVN 80/120</v>
       </c>
       <c r="M42" s="21" t="n">
-        <f aca="false">IF(OR($D42&lt;&gt;0,$E42&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A42="",0,IF(OR($D42&lt;&gt;0,$E42&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
       <c r="N42" s="21" t="n">
@@ -3605,32 +3705,32 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="22" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C43" s="23" t="n">
         <v>7055</v>
       </c>
       <c r="D43" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L43,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A43="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L43,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>600</v>
       </c>
       <c r="E43" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L43,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A43="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L43,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F43" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L43)</f>
+        <f aca="false">IF($A43="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L43))</f>
         <v>600</v>
       </c>
       <c r="G43" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L43)</f>
+        <f aca="false">IF($A43="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L43))</f>
         <v>0</v>
       </c>
       <c r="H43" s="26" t="n">
-        <f aca="false">$C43+$F43-$G43</f>
+        <f aca="false">IF($A43="","",$C43+$F43-$G43)</f>
         <v>7655</v>
       </c>
       <c r="I43" s="19"/>
@@ -3639,11 +3739,11 @@
         <v/>
       </c>
       <c r="L43" s="21" t="str">
-        <f aca="false">$A43&amp;" - "&amp;$B43</f>
+        <f aca="false">IF($A43="","",$A43&amp;" - "&amp;$B43)</f>
         <v>THT Brand - PUD PVN 100/200</v>
       </c>
       <c r="M43" s="21" t="n">
-        <f aca="false">IF(OR($D43&lt;&gt;0,$E43&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A43="",0,IF(OR($D43&lt;&gt;0,$E43&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
       <c r="N43" s="21" t="n">
@@ -3653,32 +3753,32 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="14" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C44" s="15" t="n">
         <v>4682</v>
       </c>
       <c r="D44" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L44,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A44="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L44,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E44" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L44,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A44="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L44,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F44" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L44)</f>
+        <f aca="false">IF($A44="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L44))</f>
         <v>0</v>
       </c>
       <c r="G44" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L44)</f>
+        <f aca="false">IF($A44="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L44))</f>
         <v>0</v>
       </c>
       <c r="H44" s="18" t="n">
-        <f aca="false">$C44+$F44-$G44</f>
+        <f aca="false">IF($A44="","",$C44+$F44-$G44)</f>
         <v>4682</v>
       </c>
       <c r="I44" s="19"/>
@@ -3687,11 +3787,11 @@
         <v/>
       </c>
       <c r="L44" s="21" t="str">
-        <f aca="false">$A44&amp;" - "&amp;$B44</f>
+        <f aca="false">IF($A44="","",$A44&amp;" - "&amp;$B44)</f>
         <v>THT Brand - PUD PVN 200/300</v>
       </c>
       <c r="M44" s="21" t="n">
-        <f aca="false">IF(OR($D44&lt;&gt;0,$E44&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A44="",0,IF(OR($D44&lt;&gt;0,$E44&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N44" s="21" t="str">
@@ -3701,32 +3801,32 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="22" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C45" s="23" t="n">
         <v>670</v>
       </c>
       <c r="D45" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L45,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A45="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L45,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E45" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L45,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A45="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L45,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F45" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L45)</f>
+        <f aca="false">IF($A45="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L45))</f>
         <v>0</v>
       </c>
       <c r="G45" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L45)</f>
+        <f aca="false">IF($A45="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L45))</f>
         <v>0</v>
       </c>
       <c r="H45" s="26" t="n">
-        <f aca="false">$C45+$F45-$G45</f>
+        <f aca="false">IF($A45="","",$C45+$F45-$G45)</f>
         <v>670</v>
       </c>
       <c r="I45" s="19"/>
@@ -3735,11 +3835,11 @@
         <v/>
       </c>
       <c r="L45" s="21" t="str">
-        <f aca="false">$A45&amp;" - "&amp;$B45</f>
+        <f aca="false">IF($A45="","",$A45&amp;" - "&amp;$B45)</f>
         <v>Deepsea - 300/500</v>
       </c>
       <c r="M45" s="21" t="n">
-        <f aca="false">IF(OR($D45&lt;&gt;0,$E45&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A45="",0,IF(OR($D45&lt;&gt;0,$E45&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N45" s="21" t="str">
@@ -3749,32 +3849,32 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="14" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C46" s="15" t="n">
         <v>451</v>
       </c>
       <c r="D46" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L46,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A46="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L46,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E46" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L46,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A46="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L46,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F46" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L46)</f>
+        <f aca="false">IF($A46="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L46))</f>
         <v>0</v>
       </c>
       <c r="G46" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L46)</f>
+        <f aca="false">IF($A46="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L46))</f>
         <v>0</v>
       </c>
       <c r="H46" s="18" t="n">
-        <f aca="false">$C46+$F46-$G46</f>
+        <f aca="false">IF($A46="","",$C46+$F46-$G46)</f>
         <v>451</v>
       </c>
       <c r="I46" s="19"/>
@@ -3783,11 +3883,11 @@
         <v/>
       </c>
       <c r="L46" s="21" t="str">
-        <f aca="false">$A46&amp;" - "&amp;$B46</f>
+        <f aca="false">IF($A46="","",$A46&amp;" - "&amp;$B46)</f>
         <v>China - PUD PVN 300/500</v>
       </c>
       <c r="M46" s="21" t="n">
-        <f aca="false">IF(OR($D46&lt;&gt;0,$E46&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A46="",0,IF(OR($D46&lt;&gt;0,$E46&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N46" s="21" t="str">
@@ -3797,32 +3897,32 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="22" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C47" s="23" t="n">
         <v>188</v>
       </c>
       <c r="D47" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L47,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A47="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L47,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E47" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L47,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A47="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L47,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F47" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L47)</f>
+        <f aca="false">IF($A47="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L47))</f>
         <v>0</v>
       </c>
       <c r="G47" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L47)</f>
+        <f aca="false">IF($A47="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L47))</f>
         <v>0</v>
       </c>
       <c r="H47" s="26" t="n">
-        <f aca="false">$C47+$F47-$G47</f>
+        <f aca="false">IF($A47="","",$C47+$F47-$G47)</f>
         <v>188</v>
       </c>
       <c r="I47" s="19"/>
@@ -3831,11 +3931,11 @@
         <v/>
       </c>
       <c r="L47" s="21" t="str">
-        <f aca="false">$A47&amp;" - "&amp;$B47</f>
+        <f aca="false">IF($A47="","",$A47&amp;" - "&amp;$B47)</f>
         <v>China - PUD KKD 300/500</v>
       </c>
       <c r="M47" s="21" t="n">
-        <f aca="false">IF(OR($D47&lt;&gt;0,$E47&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A47="",0,IF(OR($D47&lt;&gt;0,$E47&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N47" s="21" t="str">
@@ -3845,32 +3945,32 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="14" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C48" s="15" t="n">
         <v>401</v>
       </c>
       <c r="D48" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L48,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A48="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L48,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E48" s="16" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L48,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A48="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L48,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F48" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L48)</f>
+        <f aca="false">IF($A48="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L48))</f>
         <v>0</v>
       </c>
       <c r="G48" s="17" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L48)</f>
+        <f aca="false">IF($A48="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L48))</f>
         <v>0</v>
       </c>
       <c r="H48" s="18" t="n">
-        <f aca="false">$C48+$F48-$G48</f>
+        <f aca="false">IF($A48="","",$C48+$F48-$G48)</f>
         <v>401</v>
       </c>
       <c r="I48" s="19"/>
@@ -3879,11 +3979,11 @@
         <v/>
       </c>
       <c r="L48" s="21" t="str">
-        <f aca="false">$A48&amp;" - "&amp;$B48</f>
+        <f aca="false">IF($A48="","",$A48&amp;" - "&amp;$B48)</f>
         <v>China - PUD PVN 500/800</v>
       </c>
       <c r="M48" s="21" t="n">
-        <f aca="false">IF(OR($D48&lt;&gt;0,$E48&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A48="",0,IF(OR($D48&lt;&gt;0,$E48&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N48" s="21" t="str">
@@ -3893,32 +3993,32 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="22" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C49" s="23" t="n">
         <v>1920</v>
       </c>
       <c r="D49" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L49,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A49="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L49,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="E49" s="24" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L49,'Daily Entry'!$A$7:$A$5000,$C$3)</f>
+        <f aca="false">IF($A49="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L49,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
       <c r="F49" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L49)</f>
+        <f aca="false">IF($A49="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L49))</f>
         <v>0</v>
       </c>
       <c r="G49" s="25" t="n">
-        <f aca="false">SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L49)</f>
+        <f aca="false">IF($A49="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L49))</f>
         <v>0</v>
       </c>
       <c r="H49" s="26" t="n">
-        <f aca="false">$C49+$F49-$G49</f>
+        <f aca="false">IF($A49="","",$C49+$F49-$G49)</f>
         <v>1920</v>
       </c>
       <c r="I49" s="19"/>
@@ -3927,11 +4027,11 @@
         <v/>
       </c>
       <c r="L49" s="21" t="str">
-        <f aca="false">$A49&amp;" - "&amp;$B49</f>
+        <f aca="false">IF($A49="","",$A49&amp;" - "&amp;$B49)</f>
         <v>China - PUD KKD 500/800</v>
       </c>
       <c r="M49" s="21" t="n">
-        <f aca="false">IF(OR($D49&lt;&gt;0,$E49&lt;&gt;0),1,0)</f>
+        <f aca="false">IF($A49="",0,IF(OR($D49&lt;&gt;0,$E49&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
       <c r="N49" s="21" t="str">
@@ -3940,49 +4040,889 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="28" t="s">
-        <v>84</v>
-      </c>
+      <c r="A50" s="28"/>
       <c r="B50" s="28"/>
-      <c r="C50" s="29" t="n">
-        <f aca="false">SUM(C8:C49)</f>
+      <c r="C50" s="29"/>
+      <c r="D50" s="16" t="str">
+        <f aca="false">IF($A50="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L50,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="E50" s="16" t="str">
+        <f aca="false">IF($A50="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L50,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="F50" s="17" t="str">
+        <f aca="false">IF($A50="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L50))</f>
+        <v/>
+      </c>
+      <c r="G50" s="17" t="str">
+        <f aca="false">IF($A50="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L50))</f>
+        <v/>
+      </c>
+      <c r="H50" s="18" t="str">
+        <f aca="false">IF($A50="","",$C50+$F50-$G50)</f>
+        <v/>
+      </c>
+      <c r="I50" s="19"/>
+      <c r="J50" s="20" t="str">
+        <f aca="false">IF($I50="","",$H50*$I50)</f>
+        <v/>
+      </c>
+      <c r="L50" s="21" t="str">
+        <f aca="false">IF($A50="","",$A50&amp;" - "&amp;$B50)</f>
+        <v/>
+      </c>
+      <c r="M50" s="21" t="n">
+        <f aca="false">IF($A50="",0,IF(OR($D50&lt;&gt;0,$E50&lt;&gt;0),1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N50" s="21" t="str">
+        <f aca="false">IF($M50=1,SUM($M$8:$M50),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="30"/>
+      <c r="B51" s="30"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="24" t="str">
+        <f aca="false">IF($A51="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L51,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="E51" s="24" t="str">
+        <f aca="false">IF($A51="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L51,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="F51" s="25" t="str">
+        <f aca="false">IF($A51="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L51))</f>
+        <v/>
+      </c>
+      <c r="G51" s="25" t="str">
+        <f aca="false">IF($A51="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L51))</f>
+        <v/>
+      </c>
+      <c r="H51" s="26" t="str">
+        <f aca="false">IF($A51="","",$C51+$F51-$G51)</f>
+        <v/>
+      </c>
+      <c r="I51" s="19"/>
+      <c r="J51" s="27" t="str">
+        <f aca="false">IF($I51="","",$H51*$I51)</f>
+        <v/>
+      </c>
+      <c r="L51" s="21" t="str">
+        <f aca="false">IF($A51="","",$A51&amp;" - "&amp;$B51)</f>
+        <v/>
+      </c>
+      <c r="M51" s="21" t="n">
+        <f aca="false">IF($A51="",0,IF(OR($D51&lt;&gt;0,$E51&lt;&gt;0),1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N51" s="21" t="str">
+        <f aca="false">IF($M51=1,SUM($M$8:$M51),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="28"/>
+      <c r="B52" s="28"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="16" t="str">
+        <f aca="false">IF($A52="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L52,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="E52" s="16" t="str">
+        <f aca="false">IF($A52="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L52,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="F52" s="17" t="str">
+        <f aca="false">IF($A52="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L52))</f>
+        <v/>
+      </c>
+      <c r="G52" s="17" t="str">
+        <f aca="false">IF($A52="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L52))</f>
+        <v/>
+      </c>
+      <c r="H52" s="18" t="str">
+        <f aca="false">IF($A52="","",$C52+$F52-$G52)</f>
+        <v/>
+      </c>
+      <c r="I52" s="19"/>
+      <c r="J52" s="20" t="str">
+        <f aca="false">IF($I52="","",$H52*$I52)</f>
+        <v/>
+      </c>
+      <c r="L52" s="21" t="str">
+        <f aca="false">IF($A52="","",$A52&amp;" - "&amp;$B52)</f>
+        <v/>
+      </c>
+      <c r="M52" s="21" t="n">
+        <f aca="false">IF($A52="",0,IF(OR($D52&lt;&gt;0,$E52&lt;&gt;0),1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N52" s="21" t="str">
+        <f aca="false">IF($M52=1,SUM($M$8:$M52),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="30"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="24" t="str">
+        <f aca="false">IF($A53="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L53,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="E53" s="24" t="str">
+        <f aca="false">IF($A53="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L53,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="F53" s="25" t="str">
+        <f aca="false">IF($A53="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L53))</f>
+        <v/>
+      </c>
+      <c r="G53" s="25" t="str">
+        <f aca="false">IF($A53="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L53))</f>
+        <v/>
+      </c>
+      <c r="H53" s="26" t="str">
+        <f aca="false">IF($A53="","",$C53+$F53-$G53)</f>
+        <v/>
+      </c>
+      <c r="I53" s="19"/>
+      <c r="J53" s="27" t="str">
+        <f aca="false">IF($I53="","",$H53*$I53)</f>
+        <v/>
+      </c>
+      <c r="L53" s="21" t="str">
+        <f aca="false">IF($A53="","",$A53&amp;" - "&amp;$B53)</f>
+        <v/>
+      </c>
+      <c r="M53" s="21" t="n">
+        <f aca="false">IF($A53="",0,IF(OR($D53&lt;&gt;0,$E53&lt;&gt;0),1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N53" s="21" t="str">
+        <f aca="false">IF($M53=1,SUM($M$8:$M53),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="28"/>
+      <c r="B54" s="28"/>
+      <c r="C54" s="29"/>
+      <c r="D54" s="16" t="str">
+        <f aca="false">IF($A54="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L54,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="E54" s="16" t="str">
+        <f aca="false">IF($A54="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L54,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="F54" s="17" t="str">
+        <f aca="false">IF($A54="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L54))</f>
+        <v/>
+      </c>
+      <c r="G54" s="17" t="str">
+        <f aca="false">IF($A54="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L54))</f>
+        <v/>
+      </c>
+      <c r="H54" s="18" t="str">
+        <f aca="false">IF($A54="","",$C54+$F54-$G54)</f>
+        <v/>
+      </c>
+      <c r="I54" s="19"/>
+      <c r="J54" s="20" t="str">
+        <f aca="false">IF($I54="","",$H54*$I54)</f>
+        <v/>
+      </c>
+      <c r="L54" s="21" t="str">
+        <f aca="false">IF($A54="","",$A54&amp;" - "&amp;$B54)</f>
+        <v/>
+      </c>
+      <c r="M54" s="21" t="n">
+        <f aca="false">IF($A54="",0,IF(OR($D54&lt;&gt;0,$E54&lt;&gt;0),1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N54" s="21" t="str">
+        <f aca="false">IF($M54=1,SUM($M$8:$M54),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="31"/>
+      <c r="D55" s="24" t="str">
+        <f aca="false">IF($A55="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L55,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="E55" s="24" t="str">
+        <f aca="false">IF($A55="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L55,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="F55" s="25" t="str">
+        <f aca="false">IF($A55="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L55))</f>
+        <v/>
+      </c>
+      <c r="G55" s="25" t="str">
+        <f aca="false">IF($A55="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L55))</f>
+        <v/>
+      </c>
+      <c r="H55" s="26" t="str">
+        <f aca="false">IF($A55="","",$C55+$F55-$G55)</f>
+        <v/>
+      </c>
+      <c r="I55" s="19"/>
+      <c r="J55" s="27" t="str">
+        <f aca="false">IF($I55="","",$H55*$I55)</f>
+        <v/>
+      </c>
+      <c r="L55" s="21" t="str">
+        <f aca="false">IF($A55="","",$A55&amp;" - "&amp;$B55)</f>
+        <v/>
+      </c>
+      <c r="M55" s="21" t="n">
+        <f aca="false">IF($A55="",0,IF(OR($D55&lt;&gt;0,$E55&lt;&gt;0),1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N55" s="21" t="str">
+        <f aca="false">IF($M55=1,SUM($M$8:$M55),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="28"/>
+      <c r="B56" s="28"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="16" t="str">
+        <f aca="false">IF($A56="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L56,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="E56" s="16" t="str">
+        <f aca="false">IF($A56="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L56,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="F56" s="17" t="str">
+        <f aca="false">IF($A56="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L56))</f>
+        <v/>
+      </c>
+      <c r="G56" s="17" t="str">
+        <f aca="false">IF($A56="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L56))</f>
+        <v/>
+      </c>
+      <c r="H56" s="18" t="str">
+        <f aca="false">IF($A56="","",$C56+$F56-$G56)</f>
+        <v/>
+      </c>
+      <c r="I56" s="19"/>
+      <c r="J56" s="20" t="str">
+        <f aca="false">IF($I56="","",$H56*$I56)</f>
+        <v/>
+      </c>
+      <c r="L56" s="21" t="str">
+        <f aca="false">IF($A56="","",$A56&amp;" - "&amp;$B56)</f>
+        <v/>
+      </c>
+      <c r="M56" s="21" t="n">
+        <f aca="false">IF($A56="",0,IF(OR($D56&lt;&gt;0,$E56&lt;&gt;0),1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N56" s="21" t="str">
+        <f aca="false">IF($M56=1,SUM($M$8:$M56),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="30"/>
+      <c r="B57" s="30"/>
+      <c r="C57" s="31"/>
+      <c r="D57" s="24" t="str">
+        <f aca="false">IF($A57="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L57,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="E57" s="24" t="str">
+        <f aca="false">IF($A57="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L57,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="F57" s="25" t="str">
+        <f aca="false">IF($A57="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L57))</f>
+        <v/>
+      </c>
+      <c r="G57" s="25" t="str">
+        <f aca="false">IF($A57="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L57))</f>
+        <v/>
+      </c>
+      <c r="H57" s="26" t="str">
+        <f aca="false">IF($A57="","",$C57+$F57-$G57)</f>
+        <v/>
+      </c>
+      <c r="I57" s="19"/>
+      <c r="J57" s="27" t="str">
+        <f aca="false">IF($I57="","",$H57*$I57)</f>
+        <v/>
+      </c>
+      <c r="L57" s="21" t="str">
+        <f aca="false">IF($A57="","",$A57&amp;" - "&amp;$B57)</f>
+        <v/>
+      </c>
+      <c r="M57" s="21" t="n">
+        <f aca="false">IF($A57="",0,IF(OR($D57&lt;&gt;0,$E57&lt;&gt;0),1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N57" s="21" t="str">
+        <f aca="false">IF($M57=1,SUM($M$8:$M57),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="28"/>
+      <c r="B58" s="28"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="16" t="str">
+        <f aca="false">IF($A58="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L58,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="E58" s="16" t="str">
+        <f aca="false">IF($A58="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L58,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="F58" s="17" t="str">
+        <f aca="false">IF($A58="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L58))</f>
+        <v/>
+      </c>
+      <c r="G58" s="17" t="str">
+        <f aca="false">IF($A58="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L58))</f>
+        <v/>
+      </c>
+      <c r="H58" s="18" t="str">
+        <f aca="false">IF($A58="","",$C58+$F58-$G58)</f>
+        <v/>
+      </c>
+      <c r="I58" s="19"/>
+      <c r="J58" s="20" t="str">
+        <f aca="false">IF($I58="","",$H58*$I58)</f>
+        <v/>
+      </c>
+      <c r="L58" s="21" t="str">
+        <f aca="false">IF($A58="","",$A58&amp;" - "&amp;$B58)</f>
+        <v/>
+      </c>
+      <c r="M58" s="21" t="n">
+        <f aca="false">IF($A58="",0,IF(OR($D58&lt;&gt;0,$E58&lt;&gt;0),1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="21" t="str">
+        <f aca="false">IF($M58=1,SUM($M$8:$M58),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="31"/>
+      <c r="D59" s="24" t="str">
+        <f aca="false">IF($A59="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L59,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="E59" s="24" t="str">
+        <f aca="false">IF($A59="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L59,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="F59" s="25" t="str">
+        <f aca="false">IF($A59="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L59))</f>
+        <v/>
+      </c>
+      <c r="G59" s="25" t="str">
+        <f aca="false">IF($A59="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L59))</f>
+        <v/>
+      </c>
+      <c r="H59" s="26" t="str">
+        <f aca="false">IF($A59="","",$C59+$F59-$G59)</f>
+        <v/>
+      </c>
+      <c r="I59" s="19"/>
+      <c r="J59" s="27" t="str">
+        <f aca="false">IF($I59="","",$H59*$I59)</f>
+        <v/>
+      </c>
+      <c r="L59" s="21" t="str">
+        <f aca="false">IF($A59="","",$A59&amp;" - "&amp;$B59)</f>
+        <v/>
+      </c>
+      <c r="M59" s="21" t="n">
+        <f aca="false">IF($A59="",0,IF(OR($D59&lt;&gt;0,$E59&lt;&gt;0),1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N59" s="21" t="str">
+        <f aca="false">IF($M59=1,SUM($M$8:$M59),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="28"/>
+      <c r="B60" s="28"/>
+      <c r="C60" s="29"/>
+      <c r="D60" s="16" t="str">
+        <f aca="false">IF($A60="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L60,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="E60" s="16" t="str">
+        <f aca="false">IF($A60="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L60,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="F60" s="17" t="str">
+        <f aca="false">IF($A60="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L60))</f>
+        <v/>
+      </c>
+      <c r="G60" s="17" t="str">
+        <f aca="false">IF($A60="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L60))</f>
+        <v/>
+      </c>
+      <c r="H60" s="18" t="str">
+        <f aca="false">IF($A60="","",$C60+$F60-$G60)</f>
+        <v/>
+      </c>
+      <c r="I60" s="19"/>
+      <c r="J60" s="20" t="str">
+        <f aca="false">IF($I60="","",$H60*$I60)</f>
+        <v/>
+      </c>
+      <c r="L60" s="21" t="str">
+        <f aca="false">IF($A60="","",$A60&amp;" - "&amp;$B60)</f>
+        <v/>
+      </c>
+      <c r="M60" s="21" t="n">
+        <f aca="false">IF($A60="",0,IF(OR($D60&lt;&gt;0,$E60&lt;&gt;0),1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N60" s="21" t="str">
+        <f aca="false">IF($M60=1,SUM($M$8:$M60),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="30"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="31"/>
+      <c r="D61" s="24" t="str">
+        <f aca="false">IF($A61="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L61,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="E61" s="24" t="str">
+        <f aca="false">IF($A61="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L61,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="F61" s="25" t="str">
+        <f aca="false">IF($A61="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L61))</f>
+        <v/>
+      </c>
+      <c r="G61" s="25" t="str">
+        <f aca="false">IF($A61="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L61))</f>
+        <v/>
+      </c>
+      <c r="H61" s="26" t="str">
+        <f aca="false">IF($A61="","",$C61+$F61-$G61)</f>
+        <v/>
+      </c>
+      <c r="I61" s="19"/>
+      <c r="J61" s="27" t="str">
+        <f aca="false">IF($I61="","",$H61*$I61)</f>
+        <v/>
+      </c>
+      <c r="L61" s="21" t="str">
+        <f aca="false">IF($A61="","",$A61&amp;" - "&amp;$B61)</f>
+        <v/>
+      </c>
+      <c r="M61" s="21" t="n">
+        <f aca="false">IF($A61="",0,IF(OR($D61&lt;&gt;0,$E61&lt;&gt;0),1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N61" s="21" t="str">
+        <f aca="false">IF($M61=1,SUM($M$8:$M61),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="28"/>
+      <c r="B62" s="28"/>
+      <c r="C62" s="29"/>
+      <c r="D62" s="16" t="str">
+        <f aca="false">IF($A62="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L62,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="E62" s="16" t="str">
+        <f aca="false">IF($A62="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L62,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="F62" s="17" t="str">
+        <f aca="false">IF($A62="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L62))</f>
+        <v/>
+      </c>
+      <c r="G62" s="17" t="str">
+        <f aca="false">IF($A62="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L62))</f>
+        <v/>
+      </c>
+      <c r="H62" s="18" t="str">
+        <f aca="false">IF($A62="","",$C62+$F62-$G62)</f>
+        <v/>
+      </c>
+      <c r="I62" s="19"/>
+      <c r="J62" s="20" t="str">
+        <f aca="false">IF($I62="","",$H62*$I62)</f>
+        <v/>
+      </c>
+      <c r="L62" s="21" t="str">
+        <f aca="false">IF($A62="","",$A62&amp;" - "&amp;$B62)</f>
+        <v/>
+      </c>
+      <c r="M62" s="21" t="n">
+        <f aca="false">IF($A62="",0,IF(OR($D62&lt;&gt;0,$E62&lt;&gt;0),1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N62" s="21" t="str">
+        <f aca="false">IF($M62=1,SUM($M$8:$M62),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="30"/>
+      <c r="B63" s="30"/>
+      <c r="C63" s="31"/>
+      <c r="D63" s="24" t="str">
+        <f aca="false">IF($A63="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L63,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="E63" s="24" t="str">
+        <f aca="false">IF($A63="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L63,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="F63" s="25" t="str">
+        <f aca="false">IF($A63="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L63))</f>
+        <v/>
+      </c>
+      <c r="G63" s="25" t="str">
+        <f aca="false">IF($A63="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L63))</f>
+        <v/>
+      </c>
+      <c r="H63" s="26" t="str">
+        <f aca="false">IF($A63="","",$C63+$F63-$G63)</f>
+        <v/>
+      </c>
+      <c r="I63" s="19"/>
+      <c r="J63" s="27" t="str">
+        <f aca="false">IF($I63="","",$H63*$I63)</f>
+        <v/>
+      </c>
+      <c r="L63" s="21" t="str">
+        <f aca="false">IF($A63="","",$A63&amp;" - "&amp;$B63)</f>
+        <v/>
+      </c>
+      <c r="M63" s="21" t="n">
+        <f aca="false">IF($A63="",0,IF(OR($D63&lt;&gt;0,$E63&lt;&gt;0),1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N63" s="21" t="str">
+        <f aca="false">IF($M63=1,SUM($M$8:$M63),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="28"/>
+      <c r="B64" s="28"/>
+      <c r="C64" s="29"/>
+      <c r="D64" s="16" t="str">
+        <f aca="false">IF($A64="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L64,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="E64" s="16" t="str">
+        <f aca="false">IF($A64="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L64,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="F64" s="17" t="str">
+        <f aca="false">IF($A64="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L64))</f>
+        <v/>
+      </c>
+      <c r="G64" s="17" t="str">
+        <f aca="false">IF($A64="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L64))</f>
+        <v/>
+      </c>
+      <c r="H64" s="18" t="str">
+        <f aca="false">IF($A64="","",$C64+$F64-$G64)</f>
+        <v/>
+      </c>
+      <c r="I64" s="19"/>
+      <c r="J64" s="20" t="str">
+        <f aca="false">IF($I64="","",$H64*$I64)</f>
+        <v/>
+      </c>
+      <c r="L64" s="21" t="str">
+        <f aca="false">IF($A64="","",$A64&amp;" - "&amp;$B64)</f>
+        <v/>
+      </c>
+      <c r="M64" s="21" t="n">
+        <f aca="false">IF($A64="",0,IF(OR($D64&lt;&gt;0,$E64&lt;&gt;0),1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N64" s="21" t="str">
+        <f aca="false">IF($M64=1,SUM($M$8:$M64),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="30"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="31"/>
+      <c r="D65" s="24" t="str">
+        <f aca="false">IF($A65="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L65,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="E65" s="24" t="str">
+        <f aca="false">IF($A65="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L65,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="F65" s="25" t="str">
+        <f aca="false">IF($A65="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L65))</f>
+        <v/>
+      </c>
+      <c r="G65" s="25" t="str">
+        <f aca="false">IF($A65="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L65))</f>
+        <v/>
+      </c>
+      <c r="H65" s="26" t="str">
+        <f aca="false">IF($A65="","",$C65+$F65-$G65)</f>
+        <v/>
+      </c>
+      <c r="I65" s="19"/>
+      <c r="J65" s="27" t="str">
+        <f aca="false">IF($I65="","",$H65*$I65)</f>
+        <v/>
+      </c>
+      <c r="L65" s="21" t="str">
+        <f aca="false">IF($A65="","",$A65&amp;" - "&amp;$B65)</f>
+        <v/>
+      </c>
+      <c r="M65" s="21" t="n">
+        <f aca="false">IF($A65="",0,IF(OR($D65&lt;&gt;0,$E65&lt;&gt;0),1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N65" s="21" t="str">
+        <f aca="false">IF($M65=1,SUM($M$8:$M65),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="28"/>
+      <c r="B66" s="28"/>
+      <c r="C66" s="29"/>
+      <c r="D66" s="16" t="str">
+        <f aca="false">IF($A66="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L66,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="E66" s="16" t="str">
+        <f aca="false">IF($A66="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L66,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="F66" s="17" t="str">
+        <f aca="false">IF($A66="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L66))</f>
+        <v/>
+      </c>
+      <c r="G66" s="17" t="str">
+        <f aca="false">IF($A66="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L66))</f>
+        <v/>
+      </c>
+      <c r="H66" s="18" t="str">
+        <f aca="false">IF($A66="","",$C66+$F66-$G66)</f>
+        <v/>
+      </c>
+      <c r="I66" s="19"/>
+      <c r="J66" s="20" t="str">
+        <f aca="false">IF($I66="","",$H66*$I66)</f>
+        <v/>
+      </c>
+      <c r="L66" s="21" t="str">
+        <f aca="false">IF($A66="","",$A66&amp;" - "&amp;$B66)</f>
+        <v/>
+      </c>
+      <c r="M66" s="21" t="n">
+        <f aca="false">IF($A66="",0,IF(OR($D66&lt;&gt;0,$E66&lt;&gt;0),1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N66" s="21" t="str">
+        <f aca="false">IF($M66=1,SUM($M$8:$M66),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="30"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="31"/>
+      <c r="D67" s="24" t="str">
+        <f aca="false">IF($A67="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L67,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="E67" s="24" t="str">
+        <f aca="false">IF($A67="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L67,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="F67" s="25" t="str">
+        <f aca="false">IF($A67="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L67))</f>
+        <v/>
+      </c>
+      <c r="G67" s="25" t="str">
+        <f aca="false">IF($A67="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L67))</f>
+        <v/>
+      </c>
+      <c r="H67" s="26" t="str">
+        <f aca="false">IF($A67="","",$C67+$F67-$G67)</f>
+        <v/>
+      </c>
+      <c r="I67" s="19"/>
+      <c r="J67" s="27" t="str">
+        <f aca="false">IF($I67="","",$H67*$I67)</f>
+        <v/>
+      </c>
+      <c r="L67" s="21" t="str">
+        <f aca="false">IF($A67="","",$A67&amp;" - "&amp;$B67)</f>
+        <v/>
+      </c>
+      <c r="M67" s="21" t="n">
+        <f aca="false">IF($A67="",0,IF(OR($D67&lt;&gt;0,$E67&lt;&gt;0),1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N67" s="21" t="str">
+        <f aca="false">IF($M67=1,SUM($M$8:$M67),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="28"/>
+      <c r="B68" s="28"/>
+      <c r="C68" s="29"/>
+      <c r="D68" s="16" t="str">
+        <f aca="false">IF($A68="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L68,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="E68" s="16" t="str">
+        <f aca="false">IF($A68="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L68,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="F68" s="17" t="str">
+        <f aca="false">IF($A68="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L68))</f>
+        <v/>
+      </c>
+      <c r="G68" s="17" t="str">
+        <f aca="false">IF($A68="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L68))</f>
+        <v/>
+      </c>
+      <c r="H68" s="18" t="str">
+        <f aca="false">IF($A68="","",$C68+$F68-$G68)</f>
+        <v/>
+      </c>
+      <c r="I68" s="19"/>
+      <c r="J68" s="20" t="str">
+        <f aca="false">IF($I68="","",$H68*$I68)</f>
+        <v/>
+      </c>
+      <c r="L68" s="21" t="str">
+        <f aca="false">IF($A68="","",$A68&amp;" - "&amp;$B68)</f>
+        <v/>
+      </c>
+      <c r="M68" s="21" t="n">
+        <f aca="false">IF($A68="",0,IF(OR($D68&lt;&gt;0,$E68&lt;&gt;0),1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N68" s="21" t="str">
+        <f aca="false">IF($M68=1,SUM($M$8:$M68),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="30"/>
+      <c r="B69" s="30"/>
+      <c r="C69" s="31"/>
+      <c r="D69" s="24" t="str">
+        <f aca="false">IF($A69="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L69,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="E69" s="24" t="str">
+        <f aca="false">IF($A69="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L69,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
+        <v/>
+      </c>
+      <c r="F69" s="25" t="str">
+        <f aca="false">IF($A69="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L69))</f>
+        <v/>
+      </c>
+      <c r="G69" s="25" t="str">
+        <f aca="false">IF($A69="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L69))</f>
+        <v/>
+      </c>
+      <c r="H69" s="26" t="str">
+        <f aca="false">IF($A69="","",$C69+$F69-$G69)</f>
+        <v/>
+      </c>
+      <c r="I69" s="19"/>
+      <c r="J69" s="27" t="str">
+        <f aca="false">IF($I69="","",$H69*$I69)</f>
+        <v/>
+      </c>
+      <c r="L69" s="21" t="str">
+        <f aca="false">IF($A69="","",$A69&amp;" - "&amp;$B69)</f>
+        <v/>
+      </c>
+      <c r="M69" s="21" t="n">
+        <f aca="false">IF($A69="",0,IF(OR($D69&lt;&gt;0,$E69&lt;&gt;0),1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N69" s="21" t="str">
+        <f aca="false">IF($M69=1,SUM($M$8:$M69),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="B70" s="32"/>
+      <c r="C70" s="33" t="n">
+        <f aca="false">SUM(C8:C69)</f>
         <v>102870</v>
       </c>
-      <c r="D50" s="30" t="n">
-        <f aca="false">SUM(D8:D49)</f>
+      <c r="D70" s="34" t="n">
+        <f aca="false">SUM(D8:D69)</f>
         <v>4880</v>
       </c>
-      <c r="E50" s="30" t="n">
-        <f aca="false">SUM(E8:E49)</f>
-        <v>0</v>
-      </c>
-      <c r="F50" s="29" t="n">
-        <f aca="false">SUM(F8:F49)</f>
+      <c r="E70" s="34" t="n">
+        <f aca="false">SUM(E8:E69)</f>
+        <v>0</v>
+      </c>
+      <c r="F70" s="33" t="n">
+        <f aca="false">SUM(F8:F69)</f>
         <v>4880</v>
       </c>
-      <c r="G50" s="29" t="n">
-        <f aca="false">SUM(G8:G49)</f>
-        <v>0</v>
-      </c>
-      <c r="H50" s="29" t="n">
-        <f aca="false">SUM(H8:H49)</f>
+      <c r="G70" s="33" t="n">
+        <f aca="false">SUM(G8:G69)</f>
+        <v>0</v>
+      </c>
+      <c r="H70" s="33" t="n">
+        <f aca="false">SUM(H8:H69)</f>
         <v>107750</v>
       </c>
-      <c r="I50" s="28"/>
-      <c r="J50" s="31" t="str">
-        <f aca="false">IF(SUM(J8:J49)=0,"",SUM(J8:J49))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="9" t="s">
-        <v>85</v>
+      <c r="I70" s="32"/>
+      <c r="J70" s="35" t="str">
+        <f aca="false">IF(SUM(J8:J69)=0,"",SUM(J8:J69))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="9" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" password="df10" objects="true" scenarios="true" autoFilter="false"/>
-  <autoFilter ref="A7:J49"/>
-  <conditionalFormatting sqref="H8:H49">
+  <autoFilter ref="A7:J69"/>
+  <conditionalFormatting sqref="H8:H69">
     <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
@@ -4007,10 +4947,10 @@
   <dimension ref="A1:K250"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="81" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="82" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="83" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="84" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="86" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="87" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="88" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="89" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="6"/>
   </cols>
@@ -4022,1869 +4962,1869 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="35" t="s">
-        <v>88</v>
-      </c>
-      <c r="J4" s="36" t="n">
-        <f aca="false">SUMPRODUCT((B7:B5000&lt;&gt;"")*(COUNTIF(Stock!$L$8:$L$49,B7:B5000)=0))</f>
+        <v>95</v>
+      </c>
+      <c r="G4" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="J4" s="40" t="n">
+        <f aca="false">SUMPRODUCT((B7:B5000&lt;&gt;"")*(COUNTIF(Stock!$L$8:$L$69,B7:B5000)=0))</f>
         <v>0</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="37" t="n">
+      <c r="A7" s="41" t="n">
         <v>46254</v>
       </c>
-      <c r="B7" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="C7" s="39" t="n">
+      <c r="B7" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="43" t="n">
         <v>1068</v>
       </c>
-      <c r="D7" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="40" t="s">
-        <v>96</v>
+      <c r="D7" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="44" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="37" t="n">
+      <c r="A8" s="41" t="n">
         <v>46254</v>
       </c>
-      <c r="B8" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="39" t="n">
+      <c r="B8" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="43" t="n">
         <v>65</v>
       </c>
-      <c r="D8" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="40"/>
+      <c r="D8" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="44"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="37" t="n">
+      <c r="A9" s="41" t="n">
         <v>46254</v>
       </c>
-      <c r="B9" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="39" t="n">
+      <c r="B9" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="43" t="n">
         <v>267</v>
       </c>
-      <c r="D9" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="40"/>
+      <c r="D9" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="44"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="37" t="n">
+      <c r="A10" s="41" t="n">
         <v>46254</v>
       </c>
-      <c r="B10" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="39" t="n">
+      <c r="B10" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="43" t="n">
         <v>29</v>
       </c>
-      <c r="D10" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="40"/>
+      <c r="D10" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="44"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="37" t="n">
+      <c r="A11" s="41" t="n">
         <v>46254</v>
       </c>
-      <c r="B11" s="38" t="s">
-        <v>100</v>
-      </c>
-      <c r="C11" s="39" t="n">
+      <c r="B11" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="43" t="n">
         <v>39</v>
       </c>
-      <c r="D11" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="40"/>
+      <c r="D11" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="44"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="37" t="n">
+      <c r="A12" s="41" t="n">
         <v>46254</v>
       </c>
-      <c r="B12" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="C12" s="39" t="n">
+      <c r="B12" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" s="43" t="n">
         <v>50</v>
       </c>
-      <c r="D12" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="40"/>
+      <c r="D12" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="44"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="37" t="n">
+      <c r="A13" s="41" t="n">
         <v>46254</v>
       </c>
-      <c r="B13" s="38" t="s">
-        <v>102</v>
-      </c>
-      <c r="C13" s="39" t="n">
+      <c r="B13" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="40"/>
+      <c r="D13" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="44"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37" t="n">
+      <c r="A14" s="41" t="n">
         <v>46254</v>
       </c>
-      <c r="B14" s="38" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" s="39" t="n">
+      <c r="B14" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" s="43" t="n">
         <v>50</v>
       </c>
-      <c r="D14" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="40"/>
+      <c r="D14" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="44"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="37" t="n">
+      <c r="A15" s="41" t="n">
         <v>46254</v>
       </c>
-      <c r="B15" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="C15" s="39" t="n">
+      <c r="B15" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="43" t="n">
         <v>33</v>
       </c>
-      <c r="D15" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="40"/>
+      <c r="D15" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="44"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="37" t="n">
+      <c r="A16" s="41" t="n">
         <v>46254</v>
       </c>
-      <c r="B16" s="38" t="s">
-        <v>105</v>
-      </c>
-      <c r="C16" s="39" t="n">
+      <c r="B16" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16" s="43" t="n">
         <v>156</v>
       </c>
-      <c r="D16" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="40"/>
+      <c r="D16" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="44"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="37" t="n">
+      <c r="A17" s="41" t="n">
         <v>46254</v>
       </c>
-      <c r="B17" s="38" t="s">
-        <v>106</v>
-      </c>
-      <c r="C17" s="39" t="n">
+      <c r="B17" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17" s="43" t="n">
         <v>596</v>
       </c>
-      <c r="D17" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="40"/>
+      <c r="D17" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="44"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="37" t="n">
+      <c r="A18" s="41" t="n">
         <v>46254</v>
       </c>
-      <c r="B18" s="38" t="s">
-        <v>107</v>
-      </c>
-      <c r="C18" s="39" t="n">
+      <c r="B18" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="C18" s="43" t="n">
         <v>52</v>
       </c>
-      <c r="D18" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="40"/>
+      <c r="D18" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="44"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="37" t="n">
+      <c r="A19" s="41" t="n">
         <v>46254</v>
       </c>
-      <c r="B19" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="C19" s="39" t="n">
+      <c r="B19" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19" s="43" t="n">
         <v>1872</v>
       </c>
-      <c r="D19" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="40"/>
+      <c r="D19" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="44"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="37" t="n">
+      <c r="A20" s="41" t="n">
         <v>46254</v>
       </c>
-      <c r="B20" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="C20" s="39" t="n">
+      <c r="B20" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" s="43" t="n">
         <v>600</v>
       </c>
-      <c r="D20" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="40"/>
+      <c r="D20" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="44"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="37"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="38"/>
+      <c r="A21" s="41"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="42"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="37"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="38"/>
+      <c r="A22" s="41"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="42"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="37"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="38"/>
+      <c r="A23" s="41"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="42"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="37"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="38"/>
+      <c r="A24" s="41"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="42"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="37"/>
-      <c r="B25" s="38"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="38"/>
+      <c r="A25" s="41"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="42"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="37"/>
-      <c r="B26" s="38"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="38"/>
+      <c r="A26" s="41"/>
+      <c r="B26" s="42"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="42"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="37"/>
-      <c r="B27" s="38"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="38"/>
+      <c r="A27" s="41"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="42"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="37"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="38"/>
+      <c r="A28" s="41"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="42"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="37"/>
-      <c r="B29" s="38"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="38"/>
+      <c r="A29" s="41"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="42"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="37"/>
-      <c r="B30" s="38"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="38"/>
+      <c r="A30" s="41"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="42"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="37"/>
-      <c r="B31" s="38"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="38"/>
+      <c r="A31" s="41"/>
+      <c r="B31" s="42"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="42"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="37"/>
-      <c r="B32" s="38"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="38"/>
+      <c r="A32" s="41"/>
+      <c r="B32" s="42"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="42"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="37"/>
-      <c r="B33" s="38"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="38"/>
+      <c r="A33" s="41"/>
+      <c r="B33" s="42"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="42"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="37"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="38"/>
+      <c r="A34" s="41"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="42"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="37"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="39"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="38"/>
+      <c r="A35" s="41"/>
+      <c r="B35" s="42"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="42"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="37"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="38"/>
+      <c r="A36" s="41"/>
+      <c r="B36" s="42"/>
+      <c r="C36" s="43"/>
+      <c r="D36" s="43"/>
+      <c r="E36" s="42"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="37"/>
-      <c r="B37" s="38"/>
-      <c r="C37" s="39"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="38"/>
+      <c r="A37" s="41"/>
+      <c r="B37" s="42"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="42"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="37"/>
-      <c r="B38" s="38"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="39"/>
-      <c r="E38" s="38"/>
+      <c r="A38" s="41"/>
+      <c r="B38" s="42"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="42"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="37"/>
-      <c r="B39" s="38"/>
-      <c r="C39" s="39"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="38"/>
+      <c r="A39" s="41"/>
+      <c r="B39" s="42"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="42"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="37"/>
-      <c r="B40" s="38"/>
-      <c r="C40" s="39"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="38"/>
+      <c r="A40" s="41"/>
+      <c r="B40" s="42"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="42"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="37"/>
-      <c r="B41" s="38"/>
-      <c r="C41" s="39"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="38"/>
+      <c r="A41" s="41"/>
+      <c r="B41" s="42"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="42"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="37"/>
-      <c r="B42" s="38"/>
-      <c r="C42" s="39"/>
-      <c r="D42" s="39"/>
-      <c r="E42" s="38"/>
+      <c r="A42" s="41"/>
+      <c r="B42" s="42"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="42"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="37"/>
-      <c r="B43" s="38"/>
-      <c r="C43" s="39"/>
-      <c r="D43" s="39"/>
-      <c r="E43" s="38"/>
+      <c r="A43" s="41"/>
+      <c r="B43" s="42"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="42"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="37"/>
-      <c r="B44" s="38"/>
-      <c r="C44" s="39"/>
-      <c r="D44" s="39"/>
-      <c r="E44" s="38"/>
+      <c r="A44" s="41"/>
+      <c r="B44" s="42"/>
+      <c r="C44" s="43"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="42"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="37"/>
-      <c r="B45" s="38"/>
-      <c r="C45" s="39"/>
-      <c r="D45" s="39"/>
-      <c r="E45" s="38"/>
+      <c r="A45" s="41"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="42"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="37"/>
-      <c r="B46" s="38"/>
-      <c r="C46" s="39"/>
-      <c r="D46" s="39"/>
-      <c r="E46" s="38"/>
+      <c r="A46" s="41"/>
+      <c r="B46" s="42"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="42"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="37"/>
-      <c r="B47" s="38"/>
-      <c r="C47" s="39"/>
-      <c r="D47" s="39"/>
-      <c r="E47" s="38"/>
+      <c r="A47" s="41"/>
+      <c r="B47" s="42"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="42"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="37"/>
-      <c r="B48" s="38"/>
-      <c r="C48" s="39"/>
-      <c r="D48" s="39"/>
-      <c r="E48" s="38"/>
+      <c r="A48" s="41"/>
+      <c r="B48" s="42"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="42"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="37"/>
-      <c r="B49" s="38"/>
-      <c r="C49" s="39"/>
-      <c r="D49" s="39"/>
-      <c r="E49" s="38"/>
+      <c r="A49" s="41"/>
+      <c r="B49" s="42"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="42"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="37"/>
-      <c r="B50" s="38"/>
-      <c r="C50" s="39"/>
-      <c r="D50" s="39"/>
-      <c r="E50" s="38"/>
+      <c r="A50" s="41"/>
+      <c r="B50" s="42"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="42"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="37"/>
-      <c r="B51" s="38"/>
-      <c r="C51" s="39"/>
-      <c r="D51" s="39"/>
-      <c r="E51" s="38"/>
+      <c r="A51" s="41"/>
+      <c r="B51" s="42"/>
+      <c r="C51" s="43"/>
+      <c r="D51" s="43"/>
+      <c r="E51" s="42"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="37"/>
-      <c r="B52" s="38"/>
-      <c r="C52" s="39"/>
-      <c r="D52" s="39"/>
-      <c r="E52" s="38"/>
+      <c r="A52" s="41"/>
+      <c r="B52" s="42"/>
+      <c r="C52" s="43"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="42"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="37"/>
-      <c r="B53" s="38"/>
-      <c r="C53" s="39"/>
-      <c r="D53" s="39"/>
-      <c r="E53" s="38"/>
+      <c r="A53" s="41"/>
+      <c r="B53" s="42"/>
+      <c r="C53" s="43"/>
+      <c r="D53" s="43"/>
+      <c r="E53" s="42"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="37"/>
-      <c r="B54" s="38"/>
-      <c r="C54" s="39"/>
-      <c r="D54" s="39"/>
-      <c r="E54" s="38"/>
+      <c r="A54" s="41"/>
+      <c r="B54" s="42"/>
+      <c r="C54" s="43"/>
+      <c r="D54" s="43"/>
+      <c r="E54" s="42"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="37"/>
-      <c r="B55" s="38"/>
-      <c r="C55" s="39"/>
-      <c r="D55" s="39"/>
-      <c r="E55" s="38"/>
+      <c r="A55" s="41"/>
+      <c r="B55" s="42"/>
+      <c r="C55" s="43"/>
+      <c r="D55" s="43"/>
+      <c r="E55" s="42"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="37"/>
-      <c r="B56" s="38"/>
-      <c r="C56" s="39"/>
-      <c r="D56" s="39"/>
-      <c r="E56" s="38"/>
+      <c r="A56" s="41"/>
+      <c r="B56" s="42"/>
+      <c r="C56" s="43"/>
+      <c r="D56" s="43"/>
+      <c r="E56" s="42"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="37"/>
-      <c r="B57" s="38"/>
-      <c r="C57" s="39"/>
-      <c r="D57" s="39"/>
-      <c r="E57" s="38"/>
+      <c r="A57" s="41"/>
+      <c r="B57" s="42"/>
+      <c r="C57" s="43"/>
+      <c r="D57" s="43"/>
+      <c r="E57" s="42"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="37"/>
-      <c r="B58" s="38"/>
-      <c r="C58" s="39"/>
-      <c r="D58" s="39"/>
-      <c r="E58" s="38"/>
+      <c r="A58" s="41"/>
+      <c r="B58" s="42"/>
+      <c r="C58" s="43"/>
+      <c r="D58" s="43"/>
+      <c r="E58" s="42"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="37"/>
-      <c r="B59" s="38"/>
-      <c r="C59" s="39"/>
-      <c r="D59" s="39"/>
-      <c r="E59" s="38"/>
+      <c r="A59" s="41"/>
+      <c r="B59" s="42"/>
+      <c r="C59" s="43"/>
+      <c r="D59" s="43"/>
+      <c r="E59" s="42"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="37"/>
-      <c r="B60" s="38"/>
-      <c r="C60" s="39"/>
-      <c r="D60" s="39"/>
-      <c r="E60" s="38"/>
+      <c r="A60" s="41"/>
+      <c r="B60" s="42"/>
+      <c r="C60" s="43"/>
+      <c r="D60" s="43"/>
+      <c r="E60" s="42"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="37"/>
-      <c r="B61" s="38"/>
-      <c r="C61" s="39"/>
-      <c r="D61" s="39"/>
-      <c r="E61" s="38"/>
+      <c r="A61" s="41"/>
+      <c r="B61" s="42"/>
+      <c r="C61" s="43"/>
+      <c r="D61" s="43"/>
+      <c r="E61" s="42"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="37"/>
-      <c r="B62" s="38"/>
-      <c r="C62" s="39"/>
-      <c r="D62" s="39"/>
-      <c r="E62" s="38"/>
+      <c r="A62" s="41"/>
+      <c r="B62" s="42"/>
+      <c r="C62" s="43"/>
+      <c r="D62" s="43"/>
+      <c r="E62" s="42"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="37"/>
-      <c r="B63" s="38"/>
-      <c r="C63" s="39"/>
-      <c r="D63" s="39"/>
-      <c r="E63" s="38"/>
+      <c r="A63" s="41"/>
+      <c r="B63" s="42"/>
+      <c r="C63" s="43"/>
+      <c r="D63" s="43"/>
+      <c r="E63" s="42"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="37"/>
-      <c r="B64" s="38"/>
-      <c r="C64" s="39"/>
-      <c r="D64" s="39"/>
-      <c r="E64" s="38"/>
+      <c r="A64" s="41"/>
+      <c r="B64" s="42"/>
+      <c r="C64" s="43"/>
+      <c r="D64" s="43"/>
+      <c r="E64" s="42"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="37"/>
-      <c r="B65" s="38"/>
-      <c r="C65" s="39"/>
-      <c r="D65" s="39"/>
-      <c r="E65" s="38"/>
+      <c r="A65" s="41"/>
+      <c r="B65" s="42"/>
+      <c r="C65" s="43"/>
+      <c r="D65" s="43"/>
+      <c r="E65" s="42"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="37"/>
-      <c r="B66" s="38"/>
-      <c r="C66" s="39"/>
-      <c r="D66" s="39"/>
-      <c r="E66" s="38"/>
+      <c r="A66" s="41"/>
+      <c r="B66" s="42"/>
+      <c r="C66" s="43"/>
+      <c r="D66" s="43"/>
+      <c r="E66" s="42"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="37"/>
-      <c r="B67" s="38"/>
-      <c r="C67" s="39"/>
-      <c r="D67" s="39"/>
-      <c r="E67" s="38"/>
+      <c r="A67" s="41"/>
+      <c r="B67" s="42"/>
+      <c r="C67" s="43"/>
+      <c r="D67" s="43"/>
+      <c r="E67" s="42"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="37"/>
-      <c r="B68" s="38"/>
-      <c r="C68" s="39"/>
-      <c r="D68" s="39"/>
-      <c r="E68" s="38"/>
+      <c r="A68" s="41"/>
+      <c r="B68" s="42"/>
+      <c r="C68" s="43"/>
+      <c r="D68" s="43"/>
+      <c r="E68" s="42"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="37"/>
-      <c r="B69" s="38"/>
-      <c r="C69" s="39"/>
-      <c r="D69" s="39"/>
-      <c r="E69" s="38"/>
+      <c r="A69" s="41"/>
+      <c r="B69" s="42"/>
+      <c r="C69" s="43"/>
+      <c r="D69" s="43"/>
+      <c r="E69" s="42"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="37"/>
-      <c r="B70" s="38"/>
-      <c r="C70" s="39"/>
-      <c r="D70" s="39"/>
-      <c r="E70" s="38"/>
+      <c r="A70" s="41"/>
+      <c r="B70" s="42"/>
+      <c r="C70" s="43"/>
+      <c r="D70" s="43"/>
+      <c r="E70" s="42"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="37"/>
-      <c r="B71" s="38"/>
-      <c r="C71" s="39"/>
-      <c r="D71" s="39"/>
-      <c r="E71" s="38"/>
+      <c r="A71" s="41"/>
+      <c r="B71" s="42"/>
+      <c r="C71" s="43"/>
+      <c r="D71" s="43"/>
+      <c r="E71" s="42"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="37"/>
-      <c r="B72" s="38"/>
-      <c r="C72" s="39"/>
-      <c r="D72" s="39"/>
-      <c r="E72" s="38"/>
+      <c r="A72" s="41"/>
+      <c r="B72" s="42"/>
+      <c r="C72" s="43"/>
+      <c r="D72" s="43"/>
+      <c r="E72" s="42"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="37"/>
-      <c r="B73" s="38"/>
-      <c r="C73" s="39"/>
-      <c r="D73" s="39"/>
-      <c r="E73" s="38"/>
+      <c r="A73" s="41"/>
+      <c r="B73" s="42"/>
+      <c r="C73" s="43"/>
+      <c r="D73" s="43"/>
+      <c r="E73" s="42"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="37"/>
-      <c r="B74" s="38"/>
-      <c r="C74" s="39"/>
-      <c r="D74" s="39"/>
-      <c r="E74" s="38"/>
+      <c r="A74" s="41"/>
+      <c r="B74" s="42"/>
+      <c r="C74" s="43"/>
+      <c r="D74" s="43"/>
+      <c r="E74" s="42"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="37"/>
-      <c r="B75" s="38"/>
-      <c r="C75" s="39"/>
-      <c r="D75" s="39"/>
-      <c r="E75" s="38"/>
+      <c r="A75" s="41"/>
+      <c r="B75" s="42"/>
+      <c r="C75" s="43"/>
+      <c r="D75" s="43"/>
+      <c r="E75" s="42"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="37"/>
-      <c r="B76" s="38"/>
-      <c r="C76" s="39"/>
-      <c r="D76" s="39"/>
-      <c r="E76" s="38"/>
+      <c r="A76" s="41"/>
+      <c r="B76" s="42"/>
+      <c r="C76" s="43"/>
+      <c r="D76" s="43"/>
+      <c r="E76" s="42"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="37"/>
-      <c r="B77" s="38"/>
-      <c r="C77" s="39"/>
-      <c r="D77" s="39"/>
-      <c r="E77" s="38"/>
+      <c r="A77" s="41"/>
+      <c r="B77" s="42"/>
+      <c r="C77" s="43"/>
+      <c r="D77" s="43"/>
+      <c r="E77" s="42"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="37"/>
-      <c r="B78" s="38"/>
-      <c r="C78" s="39"/>
-      <c r="D78" s="39"/>
-      <c r="E78" s="38"/>
+      <c r="A78" s="41"/>
+      <c r="B78" s="42"/>
+      <c r="C78" s="43"/>
+      <c r="D78" s="43"/>
+      <c r="E78" s="42"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="37"/>
-      <c r="B79" s="38"/>
-      <c r="C79" s="39"/>
-      <c r="D79" s="39"/>
-      <c r="E79" s="38"/>
+      <c r="A79" s="41"/>
+      <c r="B79" s="42"/>
+      <c r="C79" s="43"/>
+      <c r="D79" s="43"/>
+      <c r="E79" s="42"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="37"/>
-      <c r="B80" s="38"/>
-      <c r="C80" s="39"/>
-      <c r="D80" s="39"/>
-      <c r="E80" s="38"/>
+      <c r="A80" s="41"/>
+      <c r="B80" s="42"/>
+      <c r="C80" s="43"/>
+      <c r="D80" s="43"/>
+      <c r="E80" s="42"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="37"/>
-      <c r="B81" s="38"/>
-      <c r="C81" s="39"/>
-      <c r="D81" s="39"/>
-      <c r="E81" s="38"/>
+      <c r="A81" s="41"/>
+      <c r="B81" s="42"/>
+      <c r="C81" s="43"/>
+      <c r="D81" s="43"/>
+      <c r="E81" s="42"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="37"/>
-      <c r="B82" s="38"/>
-      <c r="C82" s="39"/>
-      <c r="D82" s="39"/>
-      <c r="E82" s="38"/>
+      <c r="A82" s="41"/>
+      <c r="B82" s="42"/>
+      <c r="C82" s="43"/>
+      <c r="D82" s="43"/>
+      <c r="E82" s="42"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="37"/>
-      <c r="B83" s="38"/>
-      <c r="C83" s="39"/>
-      <c r="D83" s="39"/>
-      <c r="E83" s="38"/>
+      <c r="A83" s="41"/>
+      <c r="B83" s="42"/>
+      <c r="C83" s="43"/>
+      <c r="D83" s="43"/>
+      <c r="E83" s="42"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="37"/>
-      <c r="B84" s="38"/>
-      <c r="C84" s="39"/>
-      <c r="D84" s="39"/>
-      <c r="E84" s="38"/>
+      <c r="A84" s="41"/>
+      <c r="B84" s="42"/>
+      <c r="C84" s="43"/>
+      <c r="D84" s="43"/>
+      <c r="E84" s="42"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="37"/>
-      <c r="B85" s="38"/>
-      <c r="C85" s="39"/>
-      <c r="D85" s="39"/>
-      <c r="E85" s="38"/>
+      <c r="A85" s="41"/>
+      <c r="B85" s="42"/>
+      <c r="C85" s="43"/>
+      <c r="D85" s="43"/>
+      <c r="E85" s="42"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="37"/>
-      <c r="B86" s="38"/>
-      <c r="C86" s="39"/>
-      <c r="D86" s="39"/>
-      <c r="E86" s="38"/>
+      <c r="A86" s="41"/>
+      <c r="B86" s="42"/>
+      <c r="C86" s="43"/>
+      <c r="D86" s="43"/>
+      <c r="E86" s="42"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="37"/>
-      <c r="B87" s="38"/>
-      <c r="C87" s="39"/>
-      <c r="D87" s="39"/>
-      <c r="E87" s="38"/>
+      <c r="A87" s="41"/>
+      <c r="B87" s="42"/>
+      <c r="C87" s="43"/>
+      <c r="D87" s="43"/>
+      <c r="E87" s="42"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="37"/>
-      <c r="B88" s="38"/>
-      <c r="C88" s="39"/>
-      <c r="D88" s="39"/>
-      <c r="E88" s="38"/>
+      <c r="A88" s="41"/>
+      <c r="B88" s="42"/>
+      <c r="C88" s="43"/>
+      <c r="D88" s="43"/>
+      <c r="E88" s="42"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="37"/>
-      <c r="B89" s="38"/>
-      <c r="C89" s="39"/>
-      <c r="D89" s="39"/>
-      <c r="E89" s="38"/>
+      <c r="A89" s="41"/>
+      <c r="B89" s="42"/>
+      <c r="C89" s="43"/>
+      <c r="D89" s="43"/>
+      <c r="E89" s="42"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="37"/>
-      <c r="B90" s="38"/>
-      <c r="C90" s="39"/>
-      <c r="D90" s="39"/>
-      <c r="E90" s="38"/>
+      <c r="A90" s="41"/>
+      <c r="B90" s="42"/>
+      <c r="C90" s="43"/>
+      <c r="D90" s="43"/>
+      <c r="E90" s="42"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="37"/>
-      <c r="B91" s="38"/>
-      <c r="C91" s="39"/>
-      <c r="D91" s="39"/>
-      <c r="E91" s="38"/>
+      <c r="A91" s="41"/>
+      <c r="B91" s="42"/>
+      <c r="C91" s="43"/>
+      <c r="D91" s="43"/>
+      <c r="E91" s="42"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="37"/>
-      <c r="B92" s="38"/>
-      <c r="C92" s="39"/>
-      <c r="D92" s="39"/>
-      <c r="E92" s="38"/>
+      <c r="A92" s="41"/>
+      <c r="B92" s="42"/>
+      <c r="C92" s="43"/>
+      <c r="D92" s="43"/>
+      <c r="E92" s="42"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="37"/>
-      <c r="B93" s="38"/>
-      <c r="C93" s="39"/>
-      <c r="D93" s="39"/>
-      <c r="E93" s="38"/>
+      <c r="A93" s="41"/>
+      <c r="B93" s="42"/>
+      <c r="C93" s="43"/>
+      <c r="D93" s="43"/>
+      <c r="E93" s="42"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="37"/>
-      <c r="B94" s="38"/>
-      <c r="C94" s="39"/>
-      <c r="D94" s="39"/>
-      <c r="E94" s="38"/>
+      <c r="A94" s="41"/>
+      <c r="B94" s="42"/>
+      <c r="C94" s="43"/>
+      <c r="D94" s="43"/>
+      <c r="E94" s="42"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="37"/>
-      <c r="B95" s="38"/>
-      <c r="C95" s="39"/>
-      <c r="D95" s="39"/>
-      <c r="E95" s="38"/>
+      <c r="A95" s="41"/>
+      <c r="B95" s="42"/>
+      <c r="C95" s="43"/>
+      <c r="D95" s="43"/>
+      <c r="E95" s="42"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="37"/>
-      <c r="B96" s="38"/>
-      <c r="C96" s="39"/>
-      <c r="D96" s="39"/>
-      <c r="E96" s="38"/>
+      <c r="A96" s="41"/>
+      <c r="B96" s="42"/>
+      <c r="C96" s="43"/>
+      <c r="D96" s="43"/>
+      <c r="E96" s="42"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="37"/>
-      <c r="B97" s="38"/>
-      <c r="C97" s="39"/>
-      <c r="D97" s="39"/>
-      <c r="E97" s="38"/>
+      <c r="A97" s="41"/>
+      <c r="B97" s="42"/>
+      <c r="C97" s="43"/>
+      <c r="D97" s="43"/>
+      <c r="E97" s="42"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="37"/>
-      <c r="B98" s="38"/>
-      <c r="C98" s="39"/>
-      <c r="D98" s="39"/>
-      <c r="E98" s="38"/>
+      <c r="A98" s="41"/>
+      <c r="B98" s="42"/>
+      <c r="C98" s="43"/>
+      <c r="D98" s="43"/>
+      <c r="E98" s="42"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="37"/>
-      <c r="B99" s="38"/>
-      <c r="C99" s="39"/>
-      <c r="D99" s="39"/>
-      <c r="E99" s="38"/>
+      <c r="A99" s="41"/>
+      <c r="B99" s="42"/>
+      <c r="C99" s="43"/>
+      <c r="D99" s="43"/>
+      <c r="E99" s="42"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="37"/>
-      <c r="B100" s="38"/>
-      <c r="C100" s="39"/>
-      <c r="D100" s="39"/>
-      <c r="E100" s="38"/>
+      <c r="A100" s="41"/>
+      <c r="B100" s="42"/>
+      <c r="C100" s="43"/>
+      <c r="D100" s="43"/>
+      <c r="E100" s="42"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="37"/>
-      <c r="B101" s="38"/>
-      <c r="C101" s="39"/>
-      <c r="D101" s="39"/>
-      <c r="E101" s="38"/>
+      <c r="A101" s="41"/>
+      <c r="B101" s="42"/>
+      <c r="C101" s="43"/>
+      <c r="D101" s="43"/>
+      <c r="E101" s="42"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="37"/>
-      <c r="B102" s="38"/>
-      <c r="C102" s="39"/>
-      <c r="D102" s="39"/>
-      <c r="E102" s="38"/>
+      <c r="A102" s="41"/>
+      <c r="B102" s="42"/>
+      <c r="C102" s="43"/>
+      <c r="D102" s="43"/>
+      <c r="E102" s="42"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="37"/>
-      <c r="B103" s="38"/>
-      <c r="C103" s="39"/>
-      <c r="D103" s="39"/>
-      <c r="E103" s="38"/>
+      <c r="A103" s="41"/>
+      <c r="B103" s="42"/>
+      <c r="C103" s="43"/>
+      <c r="D103" s="43"/>
+      <c r="E103" s="42"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="37"/>
-      <c r="B104" s="38"/>
-      <c r="C104" s="39"/>
-      <c r="D104" s="39"/>
-      <c r="E104" s="38"/>
+      <c r="A104" s="41"/>
+      <c r="B104" s="42"/>
+      <c r="C104" s="43"/>
+      <c r="D104" s="43"/>
+      <c r="E104" s="42"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="37"/>
-      <c r="B105" s="38"/>
-      <c r="C105" s="39"/>
-      <c r="D105" s="39"/>
-      <c r="E105" s="38"/>
+      <c r="A105" s="41"/>
+      <c r="B105" s="42"/>
+      <c r="C105" s="43"/>
+      <c r="D105" s="43"/>
+      <c r="E105" s="42"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="37"/>
-      <c r="B106" s="38"/>
-      <c r="C106" s="39"/>
-      <c r="D106" s="39"/>
-      <c r="E106" s="38"/>
+      <c r="A106" s="41"/>
+      <c r="B106" s="42"/>
+      <c r="C106" s="43"/>
+      <c r="D106" s="43"/>
+      <c r="E106" s="42"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="37"/>
-      <c r="B107" s="38"/>
-      <c r="C107" s="39"/>
-      <c r="D107" s="39"/>
-      <c r="E107" s="38"/>
+      <c r="A107" s="41"/>
+      <c r="B107" s="42"/>
+      <c r="C107" s="43"/>
+      <c r="D107" s="43"/>
+      <c r="E107" s="42"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="37"/>
-      <c r="B108" s="38"/>
-      <c r="C108" s="39"/>
-      <c r="D108" s="39"/>
-      <c r="E108" s="38"/>
+      <c r="A108" s="41"/>
+      <c r="B108" s="42"/>
+      <c r="C108" s="43"/>
+      <c r="D108" s="43"/>
+      <c r="E108" s="42"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="37"/>
-      <c r="B109" s="38"/>
-      <c r="C109" s="39"/>
-      <c r="D109" s="39"/>
-      <c r="E109" s="38"/>
+      <c r="A109" s="41"/>
+      <c r="B109" s="42"/>
+      <c r="C109" s="43"/>
+      <c r="D109" s="43"/>
+      <c r="E109" s="42"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="37"/>
-      <c r="B110" s="38"/>
-      <c r="C110" s="39"/>
-      <c r="D110" s="39"/>
-      <c r="E110" s="38"/>
+      <c r="A110" s="41"/>
+      <c r="B110" s="42"/>
+      <c r="C110" s="43"/>
+      <c r="D110" s="43"/>
+      <c r="E110" s="42"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="37"/>
-      <c r="B111" s="38"/>
-      <c r="C111" s="39"/>
-      <c r="D111" s="39"/>
-      <c r="E111" s="38"/>
+      <c r="A111" s="41"/>
+      <c r="B111" s="42"/>
+      <c r="C111" s="43"/>
+      <c r="D111" s="43"/>
+      <c r="E111" s="42"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="37"/>
-      <c r="B112" s="38"/>
-      <c r="C112" s="39"/>
-      <c r="D112" s="39"/>
-      <c r="E112" s="38"/>
+      <c r="A112" s="41"/>
+      <c r="B112" s="42"/>
+      <c r="C112" s="43"/>
+      <c r="D112" s="43"/>
+      <c r="E112" s="42"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="37"/>
-      <c r="B113" s="38"/>
-      <c r="C113" s="39"/>
-      <c r="D113" s="39"/>
-      <c r="E113" s="38"/>
+      <c r="A113" s="41"/>
+      <c r="B113" s="42"/>
+      <c r="C113" s="43"/>
+      <c r="D113" s="43"/>
+      <c r="E113" s="42"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="37"/>
-      <c r="B114" s="38"/>
-      <c r="C114" s="39"/>
-      <c r="D114" s="39"/>
-      <c r="E114" s="38"/>
+      <c r="A114" s="41"/>
+      <c r="B114" s="42"/>
+      <c r="C114" s="43"/>
+      <c r="D114" s="43"/>
+      <c r="E114" s="42"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="37"/>
-      <c r="B115" s="38"/>
-      <c r="C115" s="39"/>
-      <c r="D115" s="39"/>
-      <c r="E115" s="38"/>
+      <c r="A115" s="41"/>
+      <c r="B115" s="42"/>
+      <c r="C115" s="43"/>
+      <c r="D115" s="43"/>
+      <c r="E115" s="42"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="37"/>
-      <c r="B116" s="38"/>
-      <c r="C116" s="39"/>
-      <c r="D116" s="39"/>
-      <c r="E116" s="38"/>
+      <c r="A116" s="41"/>
+      <c r="B116" s="42"/>
+      <c r="C116" s="43"/>
+      <c r="D116" s="43"/>
+      <c r="E116" s="42"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="37"/>
-      <c r="B117" s="38"/>
-      <c r="C117" s="39"/>
-      <c r="D117" s="39"/>
-      <c r="E117" s="38"/>
+      <c r="A117" s="41"/>
+      <c r="B117" s="42"/>
+      <c r="C117" s="43"/>
+      <c r="D117" s="43"/>
+      <c r="E117" s="42"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="37"/>
-      <c r="B118" s="38"/>
-      <c r="C118" s="39"/>
-      <c r="D118" s="39"/>
-      <c r="E118" s="38"/>
+      <c r="A118" s="41"/>
+      <c r="B118" s="42"/>
+      <c r="C118" s="43"/>
+      <c r="D118" s="43"/>
+      <c r="E118" s="42"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="37"/>
-      <c r="B119" s="38"/>
-      <c r="C119" s="39"/>
-      <c r="D119" s="39"/>
-      <c r="E119" s="38"/>
+      <c r="A119" s="41"/>
+      <c r="B119" s="42"/>
+      <c r="C119" s="43"/>
+      <c r="D119" s="43"/>
+      <c r="E119" s="42"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="37"/>
-      <c r="B120" s="38"/>
-      <c r="C120" s="39"/>
-      <c r="D120" s="39"/>
-      <c r="E120" s="38"/>
+      <c r="A120" s="41"/>
+      <c r="B120" s="42"/>
+      <c r="C120" s="43"/>
+      <c r="D120" s="43"/>
+      <c r="E120" s="42"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="37"/>
-      <c r="B121" s="38"/>
-      <c r="C121" s="39"/>
-      <c r="D121" s="39"/>
-      <c r="E121" s="38"/>
+      <c r="A121" s="41"/>
+      <c r="B121" s="42"/>
+      <c r="C121" s="43"/>
+      <c r="D121" s="43"/>
+      <c r="E121" s="42"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="37"/>
-      <c r="B122" s="38"/>
-      <c r="C122" s="39"/>
-      <c r="D122" s="39"/>
-      <c r="E122" s="38"/>
+      <c r="A122" s="41"/>
+      <c r="B122" s="42"/>
+      <c r="C122" s="43"/>
+      <c r="D122" s="43"/>
+      <c r="E122" s="42"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="37"/>
-      <c r="B123" s="38"/>
-      <c r="C123" s="39"/>
-      <c r="D123" s="39"/>
-      <c r="E123" s="38"/>
+      <c r="A123" s="41"/>
+      <c r="B123" s="42"/>
+      <c r="C123" s="43"/>
+      <c r="D123" s="43"/>
+      <c r="E123" s="42"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="37"/>
-      <c r="B124" s="38"/>
-      <c r="C124" s="39"/>
-      <c r="D124" s="39"/>
-      <c r="E124" s="38"/>
+      <c r="A124" s="41"/>
+      <c r="B124" s="42"/>
+      <c r="C124" s="43"/>
+      <c r="D124" s="43"/>
+      <c r="E124" s="42"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="37"/>
-      <c r="B125" s="38"/>
-      <c r="C125" s="39"/>
-      <c r="D125" s="39"/>
-      <c r="E125" s="38"/>
+      <c r="A125" s="41"/>
+      <c r="B125" s="42"/>
+      <c r="C125" s="43"/>
+      <c r="D125" s="43"/>
+      <c r="E125" s="42"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="37"/>
-      <c r="B126" s="38"/>
-      <c r="C126" s="39"/>
-      <c r="D126" s="39"/>
-      <c r="E126" s="38"/>
+      <c r="A126" s="41"/>
+      <c r="B126" s="42"/>
+      <c r="C126" s="43"/>
+      <c r="D126" s="43"/>
+      <c r="E126" s="42"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="37"/>
-      <c r="B127" s="38"/>
-      <c r="C127" s="39"/>
-      <c r="D127" s="39"/>
-      <c r="E127" s="38"/>
+      <c r="A127" s="41"/>
+      <c r="B127" s="42"/>
+      <c r="C127" s="43"/>
+      <c r="D127" s="43"/>
+      <c r="E127" s="42"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="37"/>
-      <c r="B128" s="38"/>
-      <c r="C128" s="39"/>
-      <c r="D128" s="39"/>
-      <c r="E128" s="38"/>
+      <c r="A128" s="41"/>
+      <c r="B128" s="42"/>
+      <c r="C128" s="43"/>
+      <c r="D128" s="43"/>
+      <c r="E128" s="42"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="37"/>
-      <c r="B129" s="38"/>
-      <c r="C129" s="39"/>
-      <c r="D129" s="39"/>
-      <c r="E129" s="38"/>
+      <c r="A129" s="41"/>
+      <c r="B129" s="42"/>
+      <c r="C129" s="43"/>
+      <c r="D129" s="43"/>
+      <c r="E129" s="42"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="37"/>
-      <c r="B130" s="38"/>
-      <c r="C130" s="39"/>
-      <c r="D130" s="39"/>
-      <c r="E130" s="38"/>
+      <c r="A130" s="41"/>
+      <c r="B130" s="42"/>
+      <c r="C130" s="43"/>
+      <c r="D130" s="43"/>
+      <c r="E130" s="42"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="37"/>
-      <c r="B131" s="38"/>
-      <c r="C131" s="39"/>
-      <c r="D131" s="39"/>
-      <c r="E131" s="38"/>
+      <c r="A131" s="41"/>
+      <c r="B131" s="42"/>
+      <c r="C131" s="43"/>
+      <c r="D131" s="43"/>
+      <c r="E131" s="42"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="37"/>
-      <c r="B132" s="38"/>
-      <c r="C132" s="39"/>
-      <c r="D132" s="39"/>
-      <c r="E132" s="38"/>
+      <c r="A132" s="41"/>
+      <c r="B132" s="42"/>
+      <c r="C132" s="43"/>
+      <c r="D132" s="43"/>
+      <c r="E132" s="42"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="37"/>
-      <c r="B133" s="38"/>
-      <c r="C133" s="39"/>
-      <c r="D133" s="39"/>
-      <c r="E133" s="38"/>
+      <c r="A133" s="41"/>
+      <c r="B133" s="42"/>
+      <c r="C133" s="43"/>
+      <c r="D133" s="43"/>
+      <c r="E133" s="42"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="37"/>
-      <c r="B134" s="38"/>
-      <c r="C134" s="39"/>
-      <c r="D134" s="39"/>
-      <c r="E134" s="38"/>
+      <c r="A134" s="41"/>
+      <c r="B134" s="42"/>
+      <c r="C134" s="43"/>
+      <c r="D134" s="43"/>
+      <c r="E134" s="42"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="37"/>
-      <c r="B135" s="38"/>
-      <c r="C135" s="39"/>
-      <c r="D135" s="39"/>
-      <c r="E135" s="38"/>
+      <c r="A135" s="41"/>
+      <c r="B135" s="42"/>
+      <c r="C135" s="43"/>
+      <c r="D135" s="43"/>
+      <c r="E135" s="42"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="37"/>
-      <c r="B136" s="38"/>
-      <c r="C136" s="39"/>
-      <c r="D136" s="39"/>
-      <c r="E136" s="38"/>
+      <c r="A136" s="41"/>
+      <c r="B136" s="42"/>
+      <c r="C136" s="43"/>
+      <c r="D136" s="43"/>
+      <c r="E136" s="42"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="37"/>
-      <c r="B137" s="38"/>
-      <c r="C137" s="39"/>
-      <c r="D137" s="39"/>
-      <c r="E137" s="38"/>
+      <c r="A137" s="41"/>
+      <c r="B137" s="42"/>
+      <c r="C137" s="43"/>
+      <c r="D137" s="43"/>
+      <c r="E137" s="42"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="37"/>
-      <c r="B138" s="38"/>
-      <c r="C138" s="39"/>
-      <c r="D138" s="39"/>
-      <c r="E138" s="38"/>
+      <c r="A138" s="41"/>
+      <c r="B138" s="42"/>
+      <c r="C138" s="43"/>
+      <c r="D138" s="43"/>
+      <c r="E138" s="42"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="37"/>
-      <c r="B139" s="38"/>
-      <c r="C139" s="39"/>
-      <c r="D139" s="39"/>
-      <c r="E139" s="38"/>
+      <c r="A139" s="41"/>
+      <c r="B139" s="42"/>
+      <c r="C139" s="43"/>
+      <c r="D139" s="43"/>
+      <c r="E139" s="42"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="37"/>
-      <c r="B140" s="38"/>
-      <c r="C140" s="39"/>
-      <c r="D140" s="39"/>
-      <c r="E140" s="38"/>
+      <c r="A140" s="41"/>
+      <c r="B140" s="42"/>
+      <c r="C140" s="43"/>
+      <c r="D140" s="43"/>
+      <c r="E140" s="42"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="37"/>
-      <c r="B141" s="38"/>
-      <c r="C141" s="39"/>
-      <c r="D141" s="39"/>
-      <c r="E141" s="38"/>
+      <c r="A141" s="41"/>
+      <c r="B141" s="42"/>
+      <c r="C141" s="43"/>
+      <c r="D141" s="43"/>
+      <c r="E141" s="42"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="37"/>
-      <c r="B142" s="38"/>
-      <c r="C142" s="39"/>
-      <c r="D142" s="39"/>
-      <c r="E142" s="38"/>
+      <c r="A142" s="41"/>
+      <c r="B142" s="42"/>
+      <c r="C142" s="43"/>
+      <c r="D142" s="43"/>
+      <c r="E142" s="42"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="37"/>
-      <c r="B143" s="38"/>
-      <c r="C143" s="39"/>
-      <c r="D143" s="39"/>
-      <c r="E143" s="38"/>
+      <c r="A143" s="41"/>
+      <c r="B143" s="42"/>
+      <c r="C143" s="43"/>
+      <c r="D143" s="43"/>
+      <c r="E143" s="42"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="37"/>
-      <c r="B144" s="38"/>
-      <c r="C144" s="39"/>
-      <c r="D144" s="39"/>
-      <c r="E144" s="38"/>
+      <c r="A144" s="41"/>
+      <c r="B144" s="42"/>
+      <c r="C144" s="43"/>
+      <c r="D144" s="43"/>
+      <c r="E144" s="42"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="37"/>
-      <c r="B145" s="38"/>
-      <c r="C145" s="39"/>
-      <c r="D145" s="39"/>
-      <c r="E145" s="38"/>
+      <c r="A145" s="41"/>
+      <c r="B145" s="42"/>
+      <c r="C145" s="43"/>
+      <c r="D145" s="43"/>
+      <c r="E145" s="42"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="37"/>
-      <c r="B146" s="38"/>
-      <c r="C146" s="39"/>
-      <c r="D146" s="39"/>
-      <c r="E146" s="38"/>
+      <c r="A146" s="41"/>
+      <c r="B146" s="42"/>
+      <c r="C146" s="43"/>
+      <c r="D146" s="43"/>
+      <c r="E146" s="42"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="37"/>
-      <c r="B147" s="38"/>
-      <c r="C147" s="39"/>
-      <c r="D147" s="39"/>
-      <c r="E147" s="38"/>
+      <c r="A147" s="41"/>
+      <c r="B147" s="42"/>
+      <c r="C147" s="43"/>
+      <c r="D147" s="43"/>
+      <c r="E147" s="42"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="37"/>
-      <c r="B148" s="38"/>
-      <c r="C148" s="39"/>
-      <c r="D148" s="39"/>
-      <c r="E148" s="38"/>
+      <c r="A148" s="41"/>
+      <c r="B148" s="42"/>
+      <c r="C148" s="43"/>
+      <c r="D148" s="43"/>
+      <c r="E148" s="42"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="37"/>
-      <c r="B149" s="38"/>
-      <c r="C149" s="39"/>
-      <c r="D149" s="39"/>
-      <c r="E149" s="38"/>
+      <c r="A149" s="41"/>
+      <c r="B149" s="42"/>
+      <c r="C149" s="43"/>
+      <c r="D149" s="43"/>
+      <c r="E149" s="42"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="37"/>
-      <c r="B150" s="38"/>
-      <c r="C150" s="39"/>
-      <c r="D150" s="39"/>
-      <c r="E150" s="38"/>
+      <c r="A150" s="41"/>
+      <c r="B150" s="42"/>
+      <c r="C150" s="43"/>
+      <c r="D150" s="43"/>
+      <c r="E150" s="42"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="37"/>
-      <c r="B151" s="38"/>
-      <c r="C151" s="39"/>
-      <c r="D151" s="39"/>
-      <c r="E151" s="38"/>
+      <c r="A151" s="41"/>
+      <c r="B151" s="42"/>
+      <c r="C151" s="43"/>
+      <c r="D151" s="43"/>
+      <c r="E151" s="42"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="37"/>
-      <c r="B152" s="38"/>
-      <c r="C152" s="39"/>
-      <c r="D152" s="39"/>
-      <c r="E152" s="38"/>
+      <c r="A152" s="41"/>
+      <c r="B152" s="42"/>
+      <c r="C152" s="43"/>
+      <c r="D152" s="43"/>
+      <c r="E152" s="42"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="37"/>
-      <c r="B153" s="38"/>
-      <c r="C153" s="39"/>
-      <c r="D153" s="39"/>
-      <c r="E153" s="38"/>
+      <c r="A153" s="41"/>
+      <c r="B153" s="42"/>
+      <c r="C153" s="43"/>
+      <c r="D153" s="43"/>
+      <c r="E153" s="42"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="37"/>
-      <c r="B154" s="38"/>
-      <c r="C154" s="39"/>
-      <c r="D154" s="39"/>
-      <c r="E154" s="38"/>
+      <c r="A154" s="41"/>
+      <c r="B154" s="42"/>
+      <c r="C154" s="43"/>
+      <c r="D154" s="43"/>
+      <c r="E154" s="42"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="37"/>
-      <c r="B155" s="38"/>
-      <c r="C155" s="39"/>
-      <c r="D155" s="39"/>
-      <c r="E155" s="38"/>
+      <c r="A155" s="41"/>
+      <c r="B155" s="42"/>
+      <c r="C155" s="43"/>
+      <c r="D155" s="43"/>
+      <c r="E155" s="42"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="37"/>
-      <c r="B156" s="38"/>
-      <c r="C156" s="39"/>
-      <c r="D156" s="39"/>
-      <c r="E156" s="38"/>
+      <c r="A156" s="41"/>
+      <c r="B156" s="42"/>
+      <c r="C156" s="43"/>
+      <c r="D156" s="43"/>
+      <c r="E156" s="42"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="37"/>
-      <c r="B157" s="38"/>
-      <c r="C157" s="39"/>
-      <c r="D157" s="39"/>
-      <c r="E157" s="38"/>
+      <c r="A157" s="41"/>
+      <c r="B157" s="42"/>
+      <c r="C157" s="43"/>
+      <c r="D157" s="43"/>
+      <c r="E157" s="42"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="37"/>
-      <c r="B158" s="38"/>
-      <c r="C158" s="39"/>
-      <c r="D158" s="39"/>
-      <c r="E158" s="38"/>
+      <c r="A158" s="41"/>
+      <c r="B158" s="42"/>
+      <c r="C158" s="43"/>
+      <c r="D158" s="43"/>
+      <c r="E158" s="42"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="37"/>
-      <c r="B159" s="38"/>
-      <c r="C159" s="39"/>
-      <c r="D159" s="39"/>
-      <c r="E159" s="38"/>
+      <c r="A159" s="41"/>
+      <c r="B159" s="42"/>
+      <c r="C159" s="43"/>
+      <c r="D159" s="43"/>
+      <c r="E159" s="42"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="37"/>
-      <c r="B160" s="38"/>
-      <c r="C160" s="39"/>
-      <c r="D160" s="39"/>
-      <c r="E160" s="38"/>
+      <c r="A160" s="41"/>
+      <c r="B160" s="42"/>
+      <c r="C160" s="43"/>
+      <c r="D160" s="43"/>
+      <c r="E160" s="42"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="37"/>
-      <c r="B161" s="38"/>
-      <c r="C161" s="39"/>
-      <c r="D161" s="39"/>
-      <c r="E161" s="38"/>
+      <c r="A161" s="41"/>
+      <c r="B161" s="42"/>
+      <c r="C161" s="43"/>
+      <c r="D161" s="43"/>
+      <c r="E161" s="42"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="37"/>
-      <c r="B162" s="38"/>
-      <c r="C162" s="39"/>
-      <c r="D162" s="39"/>
-      <c r="E162" s="38"/>
+      <c r="A162" s="41"/>
+      <c r="B162" s="42"/>
+      <c r="C162" s="43"/>
+      <c r="D162" s="43"/>
+      <c r="E162" s="42"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="37"/>
-      <c r="B163" s="38"/>
-      <c r="C163" s="39"/>
-      <c r="D163" s="39"/>
-      <c r="E163" s="38"/>
+      <c r="A163" s="41"/>
+      <c r="B163" s="42"/>
+      <c r="C163" s="43"/>
+      <c r="D163" s="43"/>
+      <c r="E163" s="42"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="37"/>
-      <c r="B164" s="38"/>
-      <c r="C164" s="39"/>
-      <c r="D164" s="39"/>
-      <c r="E164" s="38"/>
+      <c r="A164" s="41"/>
+      <c r="B164" s="42"/>
+      <c r="C164" s="43"/>
+      <c r="D164" s="43"/>
+      <c r="E164" s="42"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="37"/>
-      <c r="B165" s="38"/>
-      <c r="C165" s="39"/>
-      <c r="D165" s="39"/>
-      <c r="E165" s="38"/>
+      <c r="A165" s="41"/>
+      <c r="B165" s="42"/>
+      <c r="C165" s="43"/>
+      <c r="D165" s="43"/>
+      <c r="E165" s="42"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="37"/>
-      <c r="B166" s="38"/>
-      <c r="C166" s="39"/>
-      <c r="D166" s="39"/>
-      <c r="E166" s="38"/>
+      <c r="A166" s="41"/>
+      <c r="B166" s="42"/>
+      <c r="C166" s="43"/>
+      <c r="D166" s="43"/>
+      <c r="E166" s="42"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="37"/>
-      <c r="B167" s="38"/>
-      <c r="C167" s="39"/>
-      <c r="D167" s="39"/>
-      <c r="E167" s="38"/>
+      <c r="A167" s="41"/>
+      <c r="B167" s="42"/>
+      <c r="C167" s="43"/>
+      <c r="D167" s="43"/>
+      <c r="E167" s="42"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="37"/>
-      <c r="B168" s="38"/>
-      <c r="C168" s="39"/>
-      <c r="D168" s="39"/>
-      <c r="E168" s="38"/>
+      <c r="A168" s="41"/>
+      <c r="B168" s="42"/>
+      <c r="C168" s="43"/>
+      <c r="D168" s="43"/>
+      <c r="E168" s="42"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="37"/>
-      <c r="B169" s="38"/>
-      <c r="C169" s="39"/>
-      <c r="D169" s="39"/>
-      <c r="E169" s="38"/>
+      <c r="A169" s="41"/>
+      <c r="B169" s="42"/>
+      <c r="C169" s="43"/>
+      <c r="D169" s="43"/>
+      <c r="E169" s="42"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="37"/>
-      <c r="B170" s="38"/>
-      <c r="C170" s="39"/>
-      <c r="D170" s="39"/>
-      <c r="E170" s="38"/>
+      <c r="A170" s="41"/>
+      <c r="B170" s="42"/>
+      <c r="C170" s="43"/>
+      <c r="D170" s="43"/>
+      <c r="E170" s="42"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="37"/>
-      <c r="B171" s="38"/>
-      <c r="C171" s="39"/>
-      <c r="D171" s="39"/>
-      <c r="E171" s="38"/>
+      <c r="A171" s="41"/>
+      <c r="B171" s="42"/>
+      <c r="C171" s="43"/>
+      <c r="D171" s="43"/>
+      <c r="E171" s="42"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="37"/>
-      <c r="B172" s="38"/>
-      <c r="C172" s="39"/>
-      <c r="D172" s="39"/>
-      <c r="E172" s="38"/>
+      <c r="A172" s="41"/>
+      <c r="B172" s="42"/>
+      <c r="C172" s="43"/>
+      <c r="D172" s="43"/>
+      <c r="E172" s="42"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="37"/>
-      <c r="B173" s="38"/>
-      <c r="C173" s="39"/>
-      <c r="D173" s="39"/>
-      <c r="E173" s="38"/>
+      <c r="A173" s="41"/>
+      <c r="B173" s="42"/>
+      <c r="C173" s="43"/>
+      <c r="D173" s="43"/>
+      <c r="E173" s="42"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="37"/>
-      <c r="B174" s="38"/>
-      <c r="C174" s="39"/>
-      <c r="D174" s="39"/>
-      <c r="E174" s="38"/>
+      <c r="A174" s="41"/>
+      <c r="B174" s="42"/>
+      <c r="C174" s="43"/>
+      <c r="D174" s="43"/>
+      <c r="E174" s="42"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="37"/>
-      <c r="B175" s="38"/>
-      <c r="C175" s="39"/>
-      <c r="D175" s="39"/>
-      <c r="E175" s="38"/>
+      <c r="A175" s="41"/>
+      <c r="B175" s="42"/>
+      <c r="C175" s="43"/>
+      <c r="D175" s="43"/>
+      <c r="E175" s="42"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="37"/>
-      <c r="B176" s="38"/>
-      <c r="C176" s="39"/>
-      <c r="D176" s="39"/>
-      <c r="E176" s="38"/>
+      <c r="A176" s="41"/>
+      <c r="B176" s="42"/>
+      <c r="C176" s="43"/>
+      <c r="D176" s="43"/>
+      <c r="E176" s="42"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="37"/>
-      <c r="B177" s="38"/>
-      <c r="C177" s="39"/>
-      <c r="D177" s="39"/>
-      <c r="E177" s="38"/>
+      <c r="A177" s="41"/>
+      <c r="B177" s="42"/>
+      <c r="C177" s="43"/>
+      <c r="D177" s="43"/>
+      <c r="E177" s="42"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="37"/>
-      <c r="B178" s="38"/>
-      <c r="C178" s="39"/>
-      <c r="D178" s="39"/>
-      <c r="E178" s="38"/>
+      <c r="A178" s="41"/>
+      <c r="B178" s="42"/>
+      <c r="C178" s="43"/>
+      <c r="D178" s="43"/>
+      <c r="E178" s="42"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="37"/>
-      <c r="B179" s="38"/>
-      <c r="C179" s="39"/>
-      <c r="D179" s="39"/>
-      <c r="E179" s="38"/>
+      <c r="A179" s="41"/>
+      <c r="B179" s="42"/>
+      <c r="C179" s="43"/>
+      <c r="D179" s="43"/>
+      <c r="E179" s="42"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="37"/>
-      <c r="B180" s="38"/>
-      <c r="C180" s="39"/>
-      <c r="D180" s="39"/>
-      <c r="E180" s="38"/>
+      <c r="A180" s="41"/>
+      <c r="B180" s="42"/>
+      <c r="C180" s="43"/>
+      <c r="D180" s="43"/>
+      <c r="E180" s="42"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="37"/>
-      <c r="B181" s="38"/>
-      <c r="C181" s="39"/>
-      <c r="D181" s="39"/>
-      <c r="E181" s="38"/>
+      <c r="A181" s="41"/>
+      <c r="B181" s="42"/>
+      <c r="C181" s="43"/>
+      <c r="D181" s="43"/>
+      <c r="E181" s="42"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="37"/>
-      <c r="B182" s="38"/>
-      <c r="C182" s="39"/>
-      <c r="D182" s="39"/>
-      <c r="E182" s="38"/>
+      <c r="A182" s="41"/>
+      <c r="B182" s="42"/>
+      <c r="C182" s="43"/>
+      <c r="D182" s="43"/>
+      <c r="E182" s="42"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="37"/>
-      <c r="B183" s="38"/>
-      <c r="C183" s="39"/>
-      <c r="D183" s="39"/>
-      <c r="E183" s="38"/>
+      <c r="A183" s="41"/>
+      <c r="B183" s="42"/>
+      <c r="C183" s="43"/>
+      <c r="D183" s="43"/>
+      <c r="E183" s="42"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="37"/>
-      <c r="B184" s="38"/>
-      <c r="C184" s="39"/>
-      <c r="D184" s="39"/>
-      <c r="E184" s="38"/>
+      <c r="A184" s="41"/>
+      <c r="B184" s="42"/>
+      <c r="C184" s="43"/>
+      <c r="D184" s="43"/>
+      <c r="E184" s="42"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="37"/>
-      <c r="B185" s="38"/>
-      <c r="C185" s="39"/>
-      <c r="D185" s="39"/>
-      <c r="E185" s="38"/>
+      <c r="A185" s="41"/>
+      <c r="B185" s="42"/>
+      <c r="C185" s="43"/>
+      <c r="D185" s="43"/>
+      <c r="E185" s="42"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="37"/>
-      <c r="B186" s="38"/>
-      <c r="C186" s="39"/>
-      <c r="D186" s="39"/>
-      <c r="E186" s="38"/>
+      <c r="A186" s="41"/>
+      <c r="B186" s="42"/>
+      <c r="C186" s="43"/>
+      <c r="D186" s="43"/>
+      <c r="E186" s="42"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="37"/>
-      <c r="B187" s="38"/>
-      <c r="C187" s="39"/>
-      <c r="D187" s="39"/>
-      <c r="E187" s="38"/>
+      <c r="A187" s="41"/>
+      <c r="B187" s="42"/>
+      <c r="C187" s="43"/>
+      <c r="D187" s="43"/>
+      <c r="E187" s="42"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="37"/>
-      <c r="B188" s="38"/>
-      <c r="C188" s="39"/>
-      <c r="D188" s="39"/>
-      <c r="E188" s="38"/>
+      <c r="A188" s="41"/>
+      <c r="B188" s="42"/>
+      <c r="C188" s="43"/>
+      <c r="D188" s="43"/>
+      <c r="E188" s="42"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="37"/>
-      <c r="B189" s="38"/>
-      <c r="C189" s="39"/>
-      <c r="D189" s="39"/>
-      <c r="E189" s="38"/>
+      <c r="A189" s="41"/>
+      <c r="B189" s="42"/>
+      <c r="C189" s="43"/>
+      <c r="D189" s="43"/>
+      <c r="E189" s="42"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="37"/>
-      <c r="B190" s="38"/>
-      <c r="C190" s="39"/>
-      <c r="D190" s="39"/>
-      <c r="E190" s="38"/>
+      <c r="A190" s="41"/>
+      <c r="B190" s="42"/>
+      <c r="C190" s="43"/>
+      <c r="D190" s="43"/>
+      <c r="E190" s="42"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="37"/>
-      <c r="B191" s="38"/>
-      <c r="C191" s="39"/>
-      <c r="D191" s="39"/>
-      <c r="E191" s="38"/>
+      <c r="A191" s="41"/>
+      <c r="B191" s="42"/>
+      <c r="C191" s="43"/>
+      <c r="D191" s="43"/>
+      <c r="E191" s="42"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="37"/>
-      <c r="B192" s="38"/>
-      <c r="C192" s="39"/>
-      <c r="D192" s="39"/>
-      <c r="E192" s="38"/>
+      <c r="A192" s="41"/>
+      <c r="B192" s="42"/>
+      <c r="C192" s="43"/>
+      <c r="D192" s="43"/>
+      <c r="E192" s="42"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="37"/>
-      <c r="B193" s="38"/>
-      <c r="C193" s="39"/>
-      <c r="D193" s="39"/>
-      <c r="E193" s="38"/>
+      <c r="A193" s="41"/>
+      <c r="B193" s="42"/>
+      <c r="C193" s="43"/>
+      <c r="D193" s="43"/>
+      <c r="E193" s="42"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="37"/>
-      <c r="B194" s="38"/>
-      <c r="C194" s="39"/>
-      <c r="D194" s="39"/>
-      <c r="E194" s="38"/>
+      <c r="A194" s="41"/>
+      <c r="B194" s="42"/>
+      <c r="C194" s="43"/>
+      <c r="D194" s="43"/>
+      <c r="E194" s="42"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="37"/>
-      <c r="B195" s="38"/>
-      <c r="C195" s="39"/>
-      <c r="D195" s="39"/>
-      <c r="E195" s="38"/>
+      <c r="A195" s="41"/>
+      <c r="B195" s="42"/>
+      <c r="C195" s="43"/>
+      <c r="D195" s="43"/>
+      <c r="E195" s="42"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="37"/>
-      <c r="B196" s="38"/>
-      <c r="C196" s="39"/>
-      <c r="D196" s="39"/>
-      <c r="E196" s="38"/>
+      <c r="A196" s="41"/>
+      <c r="B196" s="42"/>
+      <c r="C196" s="43"/>
+      <c r="D196" s="43"/>
+      <c r="E196" s="42"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="37"/>
-      <c r="B197" s="38"/>
-      <c r="C197" s="39"/>
-      <c r="D197" s="39"/>
-      <c r="E197" s="38"/>
+      <c r="A197" s="41"/>
+      <c r="B197" s="42"/>
+      <c r="C197" s="43"/>
+      <c r="D197" s="43"/>
+      <c r="E197" s="42"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="37"/>
-      <c r="B198" s="38"/>
-      <c r="C198" s="39"/>
-      <c r="D198" s="39"/>
-      <c r="E198" s="38"/>
+      <c r="A198" s="41"/>
+      <c r="B198" s="42"/>
+      <c r="C198" s="43"/>
+      <c r="D198" s="43"/>
+      <c r="E198" s="42"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="37"/>
-      <c r="B199" s="38"/>
-      <c r="C199" s="39"/>
-      <c r="D199" s="39"/>
-      <c r="E199" s="38"/>
+      <c r="A199" s="41"/>
+      <c r="B199" s="42"/>
+      <c r="C199" s="43"/>
+      <c r="D199" s="43"/>
+      <c r="E199" s="42"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="37"/>
-      <c r="B200" s="38"/>
-      <c r="C200" s="39"/>
-      <c r="D200" s="39"/>
-      <c r="E200" s="38"/>
+      <c r="A200" s="41"/>
+      <c r="B200" s="42"/>
+      <c r="C200" s="43"/>
+      <c r="D200" s="43"/>
+      <c r="E200" s="42"/>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="37"/>
-      <c r="B201" s="38"/>
-      <c r="C201" s="39"/>
-      <c r="D201" s="39"/>
-      <c r="E201" s="38"/>
+      <c r="A201" s="41"/>
+      <c r="B201" s="42"/>
+      <c r="C201" s="43"/>
+      <c r="D201" s="43"/>
+      <c r="E201" s="42"/>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="37"/>
-      <c r="B202" s="38"/>
-      <c r="C202" s="39"/>
-      <c r="D202" s="39"/>
-      <c r="E202" s="38"/>
+      <c r="A202" s="41"/>
+      <c r="B202" s="42"/>
+      <c r="C202" s="43"/>
+      <c r="D202" s="43"/>
+      <c r="E202" s="42"/>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="37"/>
-      <c r="B203" s="38"/>
-      <c r="C203" s="39"/>
-      <c r="D203" s="39"/>
-      <c r="E203" s="38"/>
+      <c r="A203" s="41"/>
+      <c r="B203" s="42"/>
+      <c r="C203" s="43"/>
+      <c r="D203" s="43"/>
+      <c r="E203" s="42"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="37"/>
-      <c r="B204" s="38"/>
-      <c r="C204" s="39"/>
-      <c r="D204" s="39"/>
-      <c r="E204" s="38"/>
+      <c r="A204" s="41"/>
+      <c r="B204" s="42"/>
+      <c r="C204" s="43"/>
+      <c r="D204" s="43"/>
+      <c r="E204" s="42"/>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="37"/>
-      <c r="B205" s="38"/>
-      <c r="C205" s="39"/>
-      <c r="D205" s="39"/>
-      <c r="E205" s="38"/>
+      <c r="A205" s="41"/>
+      <c r="B205" s="42"/>
+      <c r="C205" s="43"/>
+      <c r="D205" s="43"/>
+      <c r="E205" s="42"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="37"/>
-      <c r="B206" s="38"/>
-      <c r="C206" s="39"/>
-      <c r="D206" s="39"/>
-      <c r="E206" s="38"/>
+      <c r="A206" s="41"/>
+      <c r="B206" s="42"/>
+      <c r="C206" s="43"/>
+      <c r="D206" s="43"/>
+      <c r="E206" s="42"/>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="37"/>
-      <c r="B207" s="38"/>
-      <c r="C207" s="39"/>
-      <c r="D207" s="39"/>
-      <c r="E207" s="38"/>
+      <c r="A207" s="41"/>
+      <c r="B207" s="42"/>
+      <c r="C207" s="43"/>
+      <c r="D207" s="43"/>
+      <c r="E207" s="42"/>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="37"/>
-      <c r="B208" s="38"/>
-      <c r="C208" s="39"/>
-      <c r="D208" s="39"/>
-      <c r="E208" s="38"/>
+      <c r="A208" s="41"/>
+      <c r="B208" s="42"/>
+      <c r="C208" s="43"/>
+      <c r="D208" s="43"/>
+      <c r="E208" s="42"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="37"/>
-      <c r="B209" s="38"/>
-      <c r="C209" s="39"/>
-      <c r="D209" s="39"/>
-      <c r="E209" s="38"/>
+      <c r="A209" s="41"/>
+      <c r="B209" s="42"/>
+      <c r="C209" s="43"/>
+      <c r="D209" s="43"/>
+      <c r="E209" s="42"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="37"/>
-      <c r="B210" s="38"/>
-      <c r="C210" s="39"/>
-      <c r="D210" s="39"/>
-      <c r="E210" s="38"/>
+      <c r="A210" s="41"/>
+      <c r="B210" s="42"/>
+      <c r="C210" s="43"/>
+      <c r="D210" s="43"/>
+      <c r="E210" s="42"/>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="37"/>
-      <c r="B211" s="38"/>
-      <c r="C211" s="39"/>
-      <c r="D211" s="39"/>
-      <c r="E211" s="38"/>
+      <c r="A211" s="41"/>
+      <c r="B211" s="42"/>
+      <c r="C211" s="43"/>
+      <c r="D211" s="43"/>
+      <c r="E211" s="42"/>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="37"/>
-      <c r="B212" s="38"/>
-      <c r="C212" s="39"/>
-      <c r="D212" s="39"/>
-      <c r="E212" s="38"/>
+      <c r="A212" s="41"/>
+      <c r="B212" s="42"/>
+      <c r="C212" s="43"/>
+      <c r="D212" s="43"/>
+      <c r="E212" s="42"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="37"/>
-      <c r="B213" s="38"/>
-      <c r="C213" s="39"/>
-      <c r="D213" s="39"/>
-      <c r="E213" s="38"/>
+      <c r="A213" s="41"/>
+      <c r="B213" s="42"/>
+      <c r="C213" s="43"/>
+      <c r="D213" s="43"/>
+      <c r="E213" s="42"/>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="37"/>
-      <c r="B214" s="38"/>
-      <c r="C214" s="39"/>
-      <c r="D214" s="39"/>
-      <c r="E214" s="38"/>
+      <c r="A214" s="41"/>
+      <c r="B214" s="42"/>
+      <c r="C214" s="43"/>
+      <c r="D214" s="43"/>
+      <c r="E214" s="42"/>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="37"/>
-      <c r="B215" s="38"/>
-      <c r="C215" s="39"/>
-      <c r="D215" s="39"/>
-      <c r="E215" s="38"/>
+      <c r="A215" s="41"/>
+      <c r="B215" s="42"/>
+      <c r="C215" s="43"/>
+      <c r="D215" s="43"/>
+      <c r="E215" s="42"/>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="37"/>
-      <c r="B216" s="38"/>
-      <c r="C216" s="39"/>
-      <c r="D216" s="39"/>
-      <c r="E216" s="38"/>
+      <c r="A216" s="41"/>
+      <c r="B216" s="42"/>
+      <c r="C216" s="43"/>
+      <c r="D216" s="43"/>
+      <c r="E216" s="42"/>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="37"/>
-      <c r="B217" s="38"/>
-      <c r="C217" s="39"/>
-      <c r="D217" s="39"/>
-      <c r="E217" s="38"/>
+      <c r="A217" s="41"/>
+      <c r="B217" s="42"/>
+      <c r="C217" s="43"/>
+      <c r="D217" s="43"/>
+      <c r="E217" s="42"/>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="37"/>
-      <c r="B218" s="38"/>
-      <c r="C218" s="39"/>
-      <c r="D218" s="39"/>
-      <c r="E218" s="38"/>
+      <c r="A218" s="41"/>
+      <c r="B218" s="42"/>
+      <c r="C218" s="43"/>
+      <c r="D218" s="43"/>
+      <c r="E218" s="42"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="37"/>
-      <c r="B219" s="38"/>
-      <c r="C219" s="39"/>
-      <c r="D219" s="39"/>
-      <c r="E219" s="38"/>
+      <c r="A219" s="41"/>
+      <c r="B219" s="42"/>
+      <c r="C219" s="43"/>
+      <c r="D219" s="43"/>
+      <c r="E219" s="42"/>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="37"/>
-      <c r="B220" s="38"/>
-      <c r="C220" s="39"/>
-      <c r="D220" s="39"/>
-      <c r="E220" s="38"/>
+      <c r="A220" s="41"/>
+      <c r="B220" s="42"/>
+      <c r="C220" s="43"/>
+      <c r="D220" s="43"/>
+      <c r="E220" s="42"/>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="37"/>
-      <c r="B221" s="38"/>
-      <c r="C221" s="39"/>
-      <c r="D221" s="39"/>
-      <c r="E221" s="38"/>
+      <c r="A221" s="41"/>
+      <c r="B221" s="42"/>
+      <c r="C221" s="43"/>
+      <c r="D221" s="43"/>
+      <c r="E221" s="42"/>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="37"/>
-      <c r="B222" s="38"/>
-      <c r="C222" s="39"/>
-      <c r="D222" s="39"/>
-      <c r="E222" s="38"/>
+      <c r="A222" s="41"/>
+      <c r="B222" s="42"/>
+      <c r="C222" s="43"/>
+      <c r="D222" s="43"/>
+      <c r="E222" s="42"/>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="37"/>
-      <c r="B223" s="38"/>
-      <c r="C223" s="39"/>
-      <c r="D223" s="39"/>
-      <c r="E223" s="38"/>
+      <c r="A223" s="41"/>
+      <c r="B223" s="42"/>
+      <c r="C223" s="43"/>
+      <c r="D223" s="43"/>
+      <c r="E223" s="42"/>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="37"/>
-      <c r="B224" s="38"/>
-      <c r="C224" s="39"/>
-      <c r="D224" s="39"/>
-      <c r="E224" s="38"/>
+      <c r="A224" s="41"/>
+      <c r="B224" s="42"/>
+      <c r="C224" s="43"/>
+      <c r="D224" s="43"/>
+      <c r="E224" s="42"/>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="37"/>
-      <c r="B225" s="38"/>
-      <c r="C225" s="39"/>
-      <c r="D225" s="39"/>
-      <c r="E225" s="38"/>
+      <c r="A225" s="41"/>
+      <c r="B225" s="42"/>
+      <c r="C225" s="43"/>
+      <c r="D225" s="43"/>
+      <c r="E225" s="42"/>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="37"/>
-      <c r="B226" s="38"/>
-      <c r="C226" s="39"/>
-      <c r="D226" s="39"/>
-      <c r="E226" s="38"/>
+      <c r="A226" s="41"/>
+      <c r="B226" s="42"/>
+      <c r="C226" s="43"/>
+      <c r="D226" s="43"/>
+      <c r="E226" s="42"/>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="37"/>
-      <c r="B227" s="38"/>
-      <c r="C227" s="39"/>
-      <c r="D227" s="39"/>
-      <c r="E227" s="38"/>
+      <c r="A227" s="41"/>
+      <c r="B227" s="42"/>
+      <c r="C227" s="43"/>
+      <c r="D227" s="43"/>
+      <c r="E227" s="42"/>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="37"/>
-      <c r="B228" s="38"/>
-      <c r="C228" s="39"/>
-      <c r="D228" s="39"/>
-      <c r="E228" s="38"/>
+      <c r="A228" s="41"/>
+      <c r="B228" s="42"/>
+      <c r="C228" s="43"/>
+      <c r="D228" s="43"/>
+      <c r="E228" s="42"/>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="37"/>
-      <c r="B229" s="38"/>
-      <c r="C229" s="39"/>
-      <c r="D229" s="39"/>
-      <c r="E229" s="38"/>
+      <c r="A229" s="41"/>
+      <c r="B229" s="42"/>
+      <c r="C229" s="43"/>
+      <c r="D229" s="43"/>
+      <c r="E229" s="42"/>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="37"/>
-      <c r="B230" s="38"/>
-      <c r="C230" s="39"/>
-      <c r="D230" s="39"/>
-      <c r="E230" s="38"/>
+      <c r="A230" s="41"/>
+      <c r="B230" s="42"/>
+      <c r="C230" s="43"/>
+      <c r="D230" s="43"/>
+      <c r="E230" s="42"/>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="37"/>
-      <c r="B231" s="38"/>
-      <c r="C231" s="39"/>
-      <c r="D231" s="39"/>
-      <c r="E231" s="38"/>
+      <c r="A231" s="41"/>
+      <c r="B231" s="42"/>
+      <c r="C231" s="43"/>
+      <c r="D231" s="43"/>
+      <c r="E231" s="42"/>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="37"/>
-      <c r="B232" s="38"/>
-      <c r="C232" s="39"/>
-      <c r="D232" s="39"/>
-      <c r="E232" s="38"/>
+      <c r="A232" s="41"/>
+      <c r="B232" s="42"/>
+      <c r="C232" s="43"/>
+      <c r="D232" s="43"/>
+      <c r="E232" s="42"/>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="37"/>
-      <c r="B233" s="38"/>
-      <c r="C233" s="39"/>
-      <c r="D233" s="39"/>
-      <c r="E233" s="38"/>
+      <c r="A233" s="41"/>
+      <c r="B233" s="42"/>
+      <c r="C233" s="43"/>
+      <c r="D233" s="43"/>
+      <c r="E233" s="42"/>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="37"/>
-      <c r="B234" s="38"/>
-      <c r="C234" s="39"/>
-      <c r="D234" s="39"/>
-      <c r="E234" s="38"/>
+      <c r="A234" s="41"/>
+      <c r="B234" s="42"/>
+      <c r="C234" s="43"/>
+      <c r="D234" s="43"/>
+      <c r="E234" s="42"/>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="37"/>
-      <c r="B235" s="38"/>
-      <c r="C235" s="39"/>
-      <c r="D235" s="39"/>
-      <c r="E235" s="38"/>
+      <c r="A235" s="41"/>
+      <c r="B235" s="42"/>
+      <c r="C235" s="43"/>
+      <c r="D235" s="43"/>
+      <c r="E235" s="42"/>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="37"/>
-      <c r="B236" s="38"/>
-      <c r="C236" s="39"/>
-      <c r="D236" s="39"/>
-      <c r="E236" s="38"/>
+      <c r="A236" s="41"/>
+      <c r="B236" s="42"/>
+      <c r="C236" s="43"/>
+      <c r="D236" s="43"/>
+      <c r="E236" s="42"/>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="37"/>
-      <c r="B237" s="38"/>
-      <c r="C237" s="39"/>
-      <c r="D237" s="39"/>
-      <c r="E237" s="38"/>
+      <c r="A237" s="41"/>
+      <c r="B237" s="42"/>
+      <c r="C237" s="43"/>
+      <c r="D237" s="43"/>
+      <c r="E237" s="42"/>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="37"/>
-      <c r="B238" s="38"/>
-      <c r="C238" s="39"/>
-      <c r="D238" s="39"/>
-      <c r="E238" s="38"/>
+      <c r="A238" s="41"/>
+      <c r="B238" s="42"/>
+      <c r="C238" s="43"/>
+      <c r="D238" s="43"/>
+      <c r="E238" s="42"/>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="37"/>
-      <c r="B239" s="38"/>
-      <c r="C239" s="39"/>
-      <c r="D239" s="39"/>
-      <c r="E239" s="38"/>
+      <c r="A239" s="41"/>
+      <c r="B239" s="42"/>
+      <c r="C239" s="43"/>
+      <c r="D239" s="43"/>
+      <c r="E239" s="42"/>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="37"/>
-      <c r="B240" s="38"/>
-      <c r="C240" s="39"/>
-      <c r="D240" s="39"/>
-      <c r="E240" s="38"/>
+      <c r="A240" s="41"/>
+      <c r="B240" s="42"/>
+      <c r="C240" s="43"/>
+      <c r="D240" s="43"/>
+      <c r="E240" s="42"/>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="37"/>
-      <c r="B241" s="38"/>
-      <c r="C241" s="39"/>
-      <c r="D241" s="39"/>
-      <c r="E241" s="38"/>
+      <c r="A241" s="41"/>
+      <c r="B241" s="42"/>
+      <c r="C241" s="43"/>
+      <c r="D241" s="43"/>
+      <c r="E241" s="42"/>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="37"/>
-      <c r="B242" s="38"/>
-      <c r="C242" s="39"/>
-      <c r="D242" s="39"/>
-      <c r="E242" s="38"/>
+      <c r="A242" s="41"/>
+      <c r="B242" s="42"/>
+      <c r="C242" s="43"/>
+      <c r="D242" s="43"/>
+      <c r="E242" s="42"/>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="37"/>
-      <c r="B243" s="38"/>
-      <c r="C243" s="39"/>
-      <c r="D243" s="39"/>
-      <c r="E243" s="38"/>
+      <c r="A243" s="41"/>
+      <c r="B243" s="42"/>
+      <c r="C243" s="43"/>
+      <c r="D243" s="43"/>
+      <c r="E243" s="42"/>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="37"/>
-      <c r="B244" s="38"/>
-      <c r="C244" s="39"/>
-      <c r="D244" s="39"/>
-      <c r="E244" s="38"/>
+      <c r="A244" s="41"/>
+      <c r="B244" s="42"/>
+      <c r="C244" s="43"/>
+      <c r="D244" s="43"/>
+      <c r="E244" s="42"/>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="37"/>
-      <c r="B245" s="38"/>
-      <c r="C245" s="39"/>
-      <c r="D245" s="39"/>
-      <c r="E245" s="38"/>
+      <c r="A245" s="41"/>
+      <c r="B245" s="42"/>
+      <c r="C245" s="43"/>
+      <c r="D245" s="43"/>
+      <c r="E245" s="42"/>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="37"/>
-      <c r="B246" s="38"/>
-      <c r="C246" s="39"/>
-      <c r="D246" s="39"/>
-      <c r="E246" s="38"/>
+      <c r="A246" s="41"/>
+      <c r="B246" s="42"/>
+      <c r="C246" s="43"/>
+      <c r="D246" s="43"/>
+      <c r="E246" s="42"/>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="37"/>
-      <c r="B247" s="38"/>
-      <c r="C247" s="39"/>
-      <c r="D247" s="39"/>
-      <c r="E247" s="38"/>
+      <c r="A247" s="41"/>
+      <c r="B247" s="42"/>
+      <c r="C247" s="43"/>
+      <c r="D247" s="43"/>
+      <c r="E247" s="42"/>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="37"/>
-      <c r="B248" s="38"/>
-      <c r="C248" s="39"/>
-      <c r="D248" s="39"/>
-      <c r="E248" s="38"/>
+      <c r="A248" s="41"/>
+      <c r="B248" s="42"/>
+      <c r="C248" s="43"/>
+      <c r="D248" s="43"/>
+      <c r="E248" s="42"/>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="37"/>
-      <c r="B249" s="38"/>
-      <c r="C249" s="39"/>
-      <c r="D249" s="39"/>
-      <c r="E249" s="38"/>
+      <c r="A249" s="41"/>
+      <c r="B249" s="42"/>
+      <c r="C249" s="43"/>
+      <c r="D249" s="43"/>
+      <c r="E249" s="42"/>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="37"/>
-      <c r="B250" s="38"/>
-      <c r="C250" s="39"/>
-      <c r="D250" s="39"/>
-      <c r="E250" s="38"/>
+      <c r="A250" s="41"/>
+      <c r="B250" s="42"/>
+      <c r="C250" s="43"/>
+      <c r="D250" s="43"/>
+      <c r="E250" s="42"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true" password="df10" objects="true" scenarios="true" autoFilter="false"/>
   <autoFilter ref="A6:E250"/>
   <dataValidations count="3">
     <dataValidation allowBlank="true" error="Pick a product from the dropdown so the entry reaches the Stock sheet." errorStyle="stop" errorTitle="Unknown product" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B7:B5000" type="list">
-      <formula1>Stock!$L$8:$L$49</formula1>
+      <formula1>Products</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Slabs cannot be negative. Record a despatch in the Shipment column." errorStyle="stop" errorTitle="Negative quantity" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C7:D5000" type="decimal">
@@ -5912,7 +6852,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
@@ -5928,283 +6868,358 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="C4" s="35" t="s">
-        <v>112</v>
+      <c r="A4" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="39" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="41" t="n">
-        <f aca="false">Stock!$H$50</f>
+      <c r="A5" s="45" t="n">
+        <f aca="false">Stock!$H$70</f>
         <v>107750</v>
       </c>
-      <c r="C5" s="42" t="str">
-        <f aca="false">IF(Stock!$J$50="","—",Stock!$J$50)</f>
+      <c r="C5" s="46" t="str">
+        <f aca="false">IF(Stock!$J$70="","—",Stock!$J$70)</f>
         <v>—</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B9" s="17" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A9,Stock!$C$8:$C$49)</f>
+        <f aca="false">IF($A9="","",SUMIF(Stock!$A$8:$A$69,$A9,Stock!$C$8:$C$69))</f>
         <v>28645</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A9,Stock!$D$8:$D$49)</f>
+        <f aca="false">IF($A9="","",SUMIF(Stock!$A$8:$A$69,$A9,Stock!$D$8:$D$69))</f>
         <v>1400</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A9,Stock!$E$8:$E$49)</f>
+        <f aca="false">IF($A9="","",SUMIF(Stock!$A$8:$A$69,$A9,Stock!$E$8:$E$69))</f>
         <v>0</v>
       </c>
       <c r="E9" s="18" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A9,Stock!$H$8:$H$49)</f>
+        <f aca="false">IF($A9="","",SUMIF(Stock!$A$8:$A$69,$A9,Stock!$H$8:$H$69))</f>
         <v>30045</v>
       </c>
       <c r="F9" s="20" t="str">
-        <f aca="false">IF(SUMIF(Stock!$A$8:$A$49,$A9,Stock!$J$8:$J$49)=0,"",SUMIF(Stock!$A$8:$A$49,$A9,Stock!$J$8:$J$49))</f>
+        <f aca="false">IF(OR($A9="",SUMIF(Stock!$A$8:$A$69,$A9,Stock!$J$8:$J$69)=0),"",SUMIF(Stock!$A$8:$A$69,$A9,Stock!$J$8:$J$69))</f>
         <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="22" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B10" s="25" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A10,Stock!$C$8:$C$49)</f>
+        <f aca="false">IF($A10="","",SUMIF(Stock!$A$8:$A$69,$A10,Stock!$C$8:$C$69))</f>
         <v>29316</v>
       </c>
       <c r="C10" s="24" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A10,Stock!$D$8:$D$49)</f>
+        <f aca="false">IF($A10="","",SUMIF(Stock!$A$8:$A$69,$A10,Stock!$D$8:$D$69))</f>
         <v>956</v>
       </c>
       <c r="D10" s="24" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A10,Stock!$E$8:$E$49)</f>
+        <f aca="false">IF($A10="","",SUMIF(Stock!$A$8:$A$69,$A10,Stock!$E$8:$E$69))</f>
         <v>0</v>
       </c>
       <c r="E10" s="26" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A10,Stock!$H$8:$H$49)</f>
+        <f aca="false">IF($A10="","",SUMIF(Stock!$A$8:$A$69,$A10,Stock!$H$8:$H$69))</f>
         <v>30272</v>
       </c>
       <c r="F10" s="27" t="str">
-        <f aca="false">IF(SUMIF(Stock!$A$8:$A$49,$A10,Stock!$J$8:$J$49)=0,"",SUMIF(Stock!$A$8:$A$49,$A10,Stock!$J$8:$J$49))</f>
+        <f aca="false">IF(OR($A10="",SUMIF(Stock!$A$8:$A$69,$A10,Stock!$J$8:$J$69)=0),"",SUMIF(Stock!$A$8:$A$69,$A10,Stock!$J$8:$J$69))</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B11" s="17" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A11,Stock!$C$8:$C$49)</f>
+        <f aca="false">IF($A11="","",SUMIF(Stock!$A$8:$A$69,$A11,Stock!$C$8:$C$69))</f>
         <v>26619</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A11,Stock!$D$8:$D$49)</f>
+        <f aca="false">IF($A11="","",SUMIF(Stock!$A$8:$A$69,$A11,Stock!$D$8:$D$69))</f>
         <v>52</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A11,Stock!$E$8:$E$49)</f>
+        <f aca="false">IF($A11="","",SUMIF(Stock!$A$8:$A$69,$A11,Stock!$E$8:$E$69))</f>
         <v>0</v>
       </c>
       <c r="E11" s="18" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A11,Stock!$H$8:$H$49)</f>
+        <f aca="false">IF($A11="","",SUMIF(Stock!$A$8:$A$69,$A11,Stock!$H$8:$H$69))</f>
         <v>26671</v>
       </c>
       <c r="F11" s="20" t="str">
-        <f aca="false">IF(SUMIF(Stock!$A$8:$A$49,$A11,Stock!$J$8:$J$49)=0,"",SUMIF(Stock!$A$8:$A$49,$A11,Stock!$J$8:$J$49))</f>
+        <f aca="false">IF(OR($A11="",SUMIF(Stock!$A$8:$A$69,$A11,Stock!$J$8:$J$69)=0),"",SUMIF(Stock!$A$8:$A$69,$A11,Stock!$J$8:$J$69))</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B12" s="25" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A12,Stock!$C$8:$C$49)</f>
+        <f aca="false">IF($A12="","",SUMIF(Stock!$A$8:$A$69,$A12,Stock!$C$8:$C$69))</f>
         <v>1534</v>
       </c>
       <c r="C12" s="24" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A12,Stock!$D$8:$D$49)</f>
+        <f aca="false">IF($A12="","",SUMIF(Stock!$A$8:$A$69,$A12,Stock!$D$8:$D$69))</f>
         <v>0</v>
       </c>
       <c r="D12" s="24" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A12,Stock!$E$8:$E$49)</f>
+        <f aca="false">IF($A12="","",SUMIF(Stock!$A$8:$A$69,$A12,Stock!$E$8:$E$69))</f>
         <v>0</v>
       </c>
       <c r="E12" s="26" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A12,Stock!$H$8:$H$49)</f>
+        <f aca="false">IF($A12="","",SUMIF(Stock!$A$8:$A$69,$A12,Stock!$H$8:$H$69))</f>
         <v>1534</v>
       </c>
       <c r="F12" s="27" t="str">
-        <f aca="false">IF(SUMIF(Stock!$A$8:$A$49,$A12,Stock!$J$8:$J$49)=0,"",SUMIF(Stock!$A$8:$A$49,$A12,Stock!$J$8:$J$49))</f>
+        <f aca="false">IF(OR($A12="",SUMIF(Stock!$A$8:$A$69,$A12,Stock!$J$8:$J$69)=0),"",SUMIF(Stock!$A$8:$A$69,$A12,Stock!$J$8:$J$69))</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B13" s="17" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A13,Stock!$C$8:$C$49)</f>
+        <f aca="false">IF($A13="","",SUMIF(Stock!$A$8:$A$69,$A13,Stock!$C$8:$C$69))</f>
         <v>13126</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A13,Stock!$D$8:$D$49)</f>
+        <f aca="false">IF($A13="","",SUMIF(Stock!$A$8:$A$69,$A13,Stock!$D$8:$D$69))</f>
         <v>2472</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A13,Stock!$E$8:$E$49)</f>
+        <f aca="false">IF($A13="","",SUMIF(Stock!$A$8:$A$69,$A13,Stock!$E$8:$E$69))</f>
         <v>0</v>
       </c>
       <c r="E13" s="18" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A13,Stock!$H$8:$H$49)</f>
+        <f aca="false">IF($A13="","",SUMIF(Stock!$A$8:$A$69,$A13,Stock!$H$8:$H$69))</f>
         <v>15598</v>
       </c>
       <c r="F13" s="20" t="str">
-        <f aca="false">IF(SUMIF(Stock!$A$8:$A$49,$A13,Stock!$J$8:$J$49)=0,"",SUMIF(Stock!$A$8:$A$49,$A13,Stock!$J$8:$J$49))</f>
+        <f aca="false">IF(OR($A13="",SUMIF(Stock!$A$8:$A$69,$A13,Stock!$J$8:$J$69)=0),"",SUMIF(Stock!$A$8:$A$69,$A13,Stock!$J$8:$J$69))</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="22" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B14" s="25" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A14,Stock!$C$8:$C$49)</f>
+        <f aca="false">IF($A14="","",SUMIF(Stock!$A$8:$A$69,$A14,Stock!$C$8:$C$69))</f>
         <v>670</v>
       </c>
       <c r="C14" s="24" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A14,Stock!$D$8:$D$49)</f>
+        <f aca="false">IF($A14="","",SUMIF(Stock!$A$8:$A$69,$A14,Stock!$D$8:$D$69))</f>
         <v>0</v>
       </c>
       <c r="D14" s="24" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A14,Stock!$E$8:$E$49)</f>
+        <f aca="false">IF($A14="","",SUMIF(Stock!$A$8:$A$69,$A14,Stock!$E$8:$E$69))</f>
         <v>0</v>
       </c>
       <c r="E14" s="26" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A14,Stock!$H$8:$H$49)</f>
+        <f aca="false">IF($A14="","",SUMIF(Stock!$A$8:$A$69,$A14,Stock!$H$8:$H$69))</f>
         <v>670</v>
       </c>
       <c r="F14" s="27" t="str">
-        <f aca="false">IF(SUMIF(Stock!$A$8:$A$49,$A14,Stock!$J$8:$J$49)=0,"",SUMIF(Stock!$A$8:$A$49,$A14,Stock!$J$8:$J$49))</f>
+        <f aca="false">IF(OR($A14="",SUMIF(Stock!$A$8:$A$69,$A14,Stock!$J$8:$J$69)=0),"",SUMIF(Stock!$A$8:$A$69,$A14,Stock!$J$8:$J$69))</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B15" s="17" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A15,Stock!$C$8:$C$49)</f>
+        <f aca="false">IF($A15="","",SUMIF(Stock!$A$8:$A$69,$A15,Stock!$C$8:$C$69))</f>
         <v>2960</v>
       </c>
       <c r="C15" s="16" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A15,Stock!$D$8:$D$49)</f>
+        <f aca="false">IF($A15="","",SUMIF(Stock!$A$8:$A$69,$A15,Stock!$D$8:$D$69))</f>
         <v>0</v>
       </c>
       <c r="D15" s="16" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A15,Stock!$E$8:$E$49)</f>
+        <f aca="false">IF($A15="","",SUMIF(Stock!$A$8:$A$69,$A15,Stock!$E$8:$E$69))</f>
         <v>0</v>
       </c>
       <c r="E15" s="18" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A15,Stock!$H$8:$H$49)</f>
+        <f aca="false">IF($A15="","",SUMIF(Stock!$A$8:$A$69,$A15,Stock!$H$8:$H$69))</f>
         <v>2960</v>
       </c>
       <c r="F15" s="20" t="str">
-        <f aca="false">IF(SUMIF(Stock!$A$8:$A$49,$A15,Stock!$J$8:$J$49)=0,"",SUMIF(Stock!$A$8:$A$49,$A15,Stock!$J$8:$J$49))</f>
+        <f aca="false">IF(OR($A15="",SUMIF(Stock!$A$8:$A$69,$A15,Stock!$J$8:$J$69)=0),"",SUMIF(Stock!$A$8:$A$69,$A15,Stock!$J$8:$J$69))</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="22" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="B16" s="25" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A16,Stock!$C$8:$C$49)</f>
+        <f aca="false">IF($A16="","",SUMIF(Stock!$A$8:$A$69,$A16,Stock!$C$8:$C$69))</f>
         <v>0</v>
       </c>
       <c r="C16" s="24" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A16,Stock!$D$8:$D$49)</f>
+        <f aca="false">IF($A16="","",SUMIF(Stock!$A$8:$A$69,$A16,Stock!$D$8:$D$69))</f>
         <v>0</v>
       </c>
       <c r="D16" s="24" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A16,Stock!$E$8:$E$49)</f>
+        <f aca="false">IF($A16="","",SUMIF(Stock!$A$8:$A$69,$A16,Stock!$E$8:$E$69))</f>
         <v>0</v>
       </c>
       <c r="E16" s="26" t="n">
-        <f aca="false">SUMIF(Stock!$A$8:$A$49,$A16,Stock!$H$8:$H$49)</f>
+        <f aca="false">IF($A16="","",SUMIF(Stock!$A$8:$A$69,$A16,Stock!$H$8:$H$69))</f>
         <v>0</v>
       </c>
       <c r="F16" s="27" t="str">
-        <f aca="false">IF(SUMIF(Stock!$A$8:$A$49,$A16,Stock!$J$8:$J$49)=0,"",SUMIF(Stock!$A$8:$A$49,$A16,Stock!$J$8:$J$49))</f>
+        <f aca="false">IF(OR($A16="",SUMIF(Stock!$A$8:$A$69,$A16,Stock!$J$8:$J$69)=0),"",SUMIF(Stock!$A$8:$A$69,$A16,Stock!$J$8:$J$69))</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="B17" s="29" t="n">
-        <f aca="false">SUM(B9:B16)</f>
+      <c r="A17" s="28"/>
+      <c r="B17" s="17" t="str">
+        <f aca="false">IF($A17="","",SUMIF(Stock!$A$8:$A$69,$A17,Stock!$C$8:$C$69))</f>
+        <v/>
+      </c>
+      <c r="C17" s="16" t="str">
+        <f aca="false">IF($A17="","",SUMIF(Stock!$A$8:$A$69,$A17,Stock!$D$8:$D$69))</f>
+        <v/>
+      </c>
+      <c r="D17" s="16" t="str">
+        <f aca="false">IF($A17="","",SUMIF(Stock!$A$8:$A$69,$A17,Stock!$E$8:$E$69))</f>
+        <v/>
+      </c>
+      <c r="E17" s="18" t="str">
+        <f aca="false">IF($A17="","",SUMIF(Stock!$A$8:$A$69,$A17,Stock!$H$8:$H$69))</f>
+        <v/>
+      </c>
+      <c r="F17" s="20" t="str">
+        <f aca="false">IF(OR($A17="",SUMIF(Stock!$A$8:$A$69,$A17,Stock!$J$8:$J$69)=0),"",SUMIF(Stock!$A$8:$A$69,$A17,Stock!$J$8:$J$69))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="30"/>
+      <c r="B18" s="25" t="str">
+        <f aca="false">IF($A18="","",SUMIF(Stock!$A$8:$A$69,$A18,Stock!$C$8:$C$69))</f>
+        <v/>
+      </c>
+      <c r="C18" s="24" t="str">
+        <f aca="false">IF($A18="","",SUMIF(Stock!$A$8:$A$69,$A18,Stock!$D$8:$D$69))</f>
+        <v/>
+      </c>
+      <c r="D18" s="24" t="str">
+        <f aca="false">IF($A18="","",SUMIF(Stock!$A$8:$A$69,$A18,Stock!$E$8:$E$69))</f>
+        <v/>
+      </c>
+      <c r="E18" s="26" t="str">
+        <f aca="false">IF($A18="","",SUMIF(Stock!$A$8:$A$69,$A18,Stock!$H$8:$H$69))</f>
+        <v/>
+      </c>
+      <c r="F18" s="27" t="str">
+        <f aca="false">IF(OR($A18="",SUMIF(Stock!$A$8:$A$69,$A18,Stock!$J$8:$J$69)=0),"",SUMIF(Stock!$A$8:$A$69,$A18,Stock!$J$8:$J$69))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="28"/>
+      <c r="B19" s="17" t="str">
+        <f aca="false">IF($A19="","",SUMIF(Stock!$A$8:$A$69,$A19,Stock!$C$8:$C$69))</f>
+        <v/>
+      </c>
+      <c r="C19" s="16" t="str">
+        <f aca="false">IF($A19="","",SUMIF(Stock!$A$8:$A$69,$A19,Stock!$D$8:$D$69))</f>
+        <v/>
+      </c>
+      <c r="D19" s="16" t="str">
+        <f aca="false">IF($A19="","",SUMIF(Stock!$A$8:$A$69,$A19,Stock!$E$8:$E$69))</f>
+        <v/>
+      </c>
+      <c r="E19" s="18" t="str">
+        <f aca="false">IF($A19="","",SUMIF(Stock!$A$8:$A$69,$A19,Stock!$H$8:$H$69))</f>
+        <v/>
+      </c>
+      <c r="F19" s="20" t="str">
+        <f aca="false">IF(OR($A19="",SUMIF(Stock!$A$8:$A$69,$A19,Stock!$J$8:$J$69)=0),"",SUMIF(Stock!$A$8:$A$69,$A19,Stock!$J$8:$J$69))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="33" t="n">
+        <f aca="false">SUM(B9:B19)</f>
         <v>102870</v>
       </c>
-      <c r="C17" s="30" t="n">
-        <f aca="false">SUM(C9:C16)</f>
+      <c r="C20" s="34" t="n">
+        <f aca="false">SUM(C9:C19)</f>
         <v>4880</v>
       </c>
-      <c r="D17" s="30" t="n">
-        <f aca="false">SUM(D9:D16)</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="29" t="n">
-        <f aca="false">SUM(E9:E16)</f>
+      <c r="D20" s="34" t="n">
+        <f aca="false">SUM(D9:D19)</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="33" t="n">
+        <f aca="false">SUM(E9:E19)</f>
         <v>107750</v>
       </c>
-      <c r="F17" s="31" t="str">
-        <f aca="false">IF(SUM(F9:F16)=0,"",SUM(F9:F16))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
-        <v>116</v>
+      <c r="F20" s="35" t="str">
+        <f aca="false">IF(SUM(F9:F19)=0,"",SUM(F9:F19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="40" t="str">
+        <f aca="false">IF(ROUND(SUM($E$9:$E$19),2)&lt;&gt;ROUND(Stock!$H$70,2),"A brand used on Stock is missing from this list — type it into a blank row above, or the totals understate the stock.","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -6224,7 +7239,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23"/>
@@ -6237,949 +7252,1038 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="E1" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="F1" s="44"/>
+      <c r="B1" s="47" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1" s="48"/>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E2" s="44" t="s">
-        <v>119</v>
-      </c>
-      <c r="F2" s="44"/>
+      <c r="E2" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2" s="48"/>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E3" s="44" t="s">
-        <v>120</v>
-      </c>
-      <c r="F3" s="44"/>
+      <c r="E3" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3" s="48"/>
     </row>
     <row r="4" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="45"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
+      <c r="A4" s="49"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="E5" s="47" t="n">
+      <c r="A5" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="E5" s="51" t="n">
         <f aca="false">Stock!$C$3</f>
         <v>46254</v>
       </c>
-      <c r="F5" s="47"/>
+      <c r="F5" s="51"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="48" t="s">
-        <v>122</v>
-      </c>
-      <c r="E6" s="49" t="s">
-        <v>123</v>
-      </c>
-      <c r="F6" s="49"/>
+      <c r="A6" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="E6" s="53" t="s">
+        <v>131</v>
+      </c>
+      <c r="F6" s="53"/>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="50" t="s">
-        <v>124</v>
-      </c>
-      <c r="B8" s="50" t="s">
-        <v>125</v>
-      </c>
-      <c r="C8" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="D8" s="50" t="s">
-        <v>127</v>
-      </c>
-      <c r="E8" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="F8" s="51"/>
+      <c r="A8" s="54" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="54" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="54" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="54" t="s">
+        <v>135</v>
+      </c>
+      <c r="E8" s="55" t="s">
+        <v>136</v>
+      </c>
+      <c r="F8" s="55"/>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="52" t="n">
-        <f aca="false">Stock!$C$50</f>
+      <c r="A9" s="56" t="n">
+        <f aca="false">Stock!$C$70</f>
         <v>102870</v>
       </c>
-      <c r="B9" s="53" t="n">
-        <f aca="false">Stock!$D$50</f>
+      <c r="B9" s="57" t="n">
+        <f aca="false">Stock!$D$70</f>
         <v>4880</v>
       </c>
-      <c r="C9" s="53" t="n">
-        <f aca="false">Stock!$E$50</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="52" t="n">
-        <f aca="false">Stock!$H$50</f>
+      <c r="C9" s="57" t="n">
+        <f aca="false">Stock!$E$70</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="56" t="n">
+        <f aca="false">Stock!$H$70</f>
         <v>107750</v>
       </c>
-      <c r="E9" s="54" t="str">
-        <f aca="false">IF(Stock!$J$50="","Rate not entered",Stock!$J$50)</f>
+      <c r="E9" s="58" t="str">
+        <f aca="false">IF(Stock!$J$70="","Rate not entered",Stock!$J$70)</f>
         <v>Rate not entered</v>
       </c>
-      <c r="F9" s="54"/>
+      <c r="F9" s="58"/>
+    </row>
+    <row r="10" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="59" t="str">
+        <f aca="false">IF(ROUND(Summary!$E$20,2)&lt;&gt;ROUND(Stock!$H$70,2),"A brand on Stock is missing from the Summary list — this report understates the total. Add it before sending.","")</f>
+        <v/>
+      </c>
+      <c r="B10" s="59"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="55" t="s">
-        <v>129</v>
-      </c>
-      <c r="B11" s="55"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="55"/>
+      <c r="A11" s="60" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="60"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="57" t="s">
+      <c r="A12" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="62" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="62" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="62" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="62" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="63" t="str">
+        <f aca="false">IF(Summary!$A$9="","",Summary!$A$9)</f>
+        <v>Blue Dolphin</v>
+      </c>
+      <c r="B13" s="64" t="n">
+        <f aca="false">IF(Summary!$A$9="","",Summary!$B$9)</f>
+        <v>28645</v>
+      </c>
+      <c r="C13" s="65" t="n">
+        <f aca="false">IF(Summary!$A$9="","",Summary!$C$9)</f>
+        <v>1400</v>
+      </c>
+      <c r="D13" s="65" t="n">
+        <f aca="false">IF(Summary!$A$9="","",Summary!$D$9)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="66" t="n">
+        <f aca="false">IF(Summary!$A$9="","",Summary!$E$9)</f>
+        <v>30045</v>
+      </c>
+      <c r="F13" s="67" t="str">
+        <f aca="false">IF(Summary!$A$9="","",Summary!$F$9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="68" t="str">
+        <f aca="false">IF(Summary!$A$10="","",Summary!$A$10)</f>
+        <v>Primus Japan</v>
+      </c>
+      <c r="B14" s="69" t="n">
+        <f aca="false">IF(Summary!$A$10="","",Summary!$B$10)</f>
+        <v>29316</v>
+      </c>
+      <c r="C14" s="70" t="n">
+        <f aca="false">IF(Summary!$A$10="","",Summary!$C$10)</f>
+        <v>956</v>
+      </c>
+      <c r="D14" s="70" t="n">
+        <f aca="false">IF(Summary!$A$10="","",Summary!$D$10)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="71" t="n">
+        <f aca="false">IF(Summary!$A$10="","",Summary!$E$10)</f>
+        <v>30272</v>
+      </c>
+      <c r="F14" s="72" t="str">
+        <f aca="false">IF(Summary!$A$10="","",Summary!$F$10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="63" t="str">
+        <f aca="false">IF(Summary!$A$11="","",Summary!$A$11)</f>
+        <v>Primus EU</v>
+      </c>
+      <c r="B15" s="64" t="n">
+        <f aca="false">IF(Summary!$A$11="","",Summary!$B$11)</f>
+        <v>26619</v>
+      </c>
+      <c r="C15" s="65" t="n">
+        <f aca="false">IF(Summary!$A$11="","",Summary!$C$11)</f>
+        <v>52</v>
+      </c>
+      <c r="D15" s="65" t="n">
+        <f aca="false">IF(Summary!$A$11="","",Summary!$D$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="66" t="n">
+        <f aca="false">IF(Summary!$A$11="","",Summary!$E$11)</f>
+        <v>26671</v>
+      </c>
+      <c r="F15" s="67" t="str">
+        <f aca="false">IF(Summary!$A$11="","",Summary!$F$11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="68" t="str">
+        <f aca="false">IF(Summary!$A$12="","",Summary!$A$12)</f>
+        <v>AMF Brand</v>
+      </c>
+      <c r="B16" s="69" t="n">
+        <f aca="false">IF(Summary!$A$12="","",Summary!$B$12)</f>
+        <v>1534</v>
+      </c>
+      <c r="C16" s="70" t="n">
+        <f aca="false">IF(Summary!$A$12="","",Summary!$C$12)</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="70" t="n">
+        <f aca="false">IF(Summary!$A$12="","",Summary!$D$12)</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="71" t="n">
+        <f aca="false">IF(Summary!$A$12="","",Summary!$E$12)</f>
+        <v>1534</v>
+      </c>
+      <c r="F16" s="72" t="str">
+        <f aca="false">IF(Summary!$A$12="","",Summary!$F$12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="63" t="str">
+        <f aca="false">IF(Summary!$A$13="","",Summary!$A$13)</f>
+        <v>THT Brand</v>
+      </c>
+      <c r="B17" s="64" t="n">
+        <f aca="false">IF(Summary!$A$13="","",Summary!$B$13)</f>
+        <v>13126</v>
+      </c>
+      <c r="C17" s="65" t="n">
+        <f aca="false">IF(Summary!$A$13="","",Summary!$C$13)</f>
+        <v>2472</v>
+      </c>
+      <c r="D17" s="65" t="n">
+        <f aca="false">IF(Summary!$A$13="","",Summary!$D$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="66" t="n">
+        <f aca="false">IF(Summary!$A$13="","",Summary!$E$13)</f>
+        <v>15598</v>
+      </c>
+      <c r="F17" s="67" t="str">
+        <f aca="false">IF(Summary!$A$13="","",Summary!$F$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="68" t="str">
+        <f aca="false">IF(Summary!$A$14="","",Summary!$A$14)</f>
+        <v>Deepsea</v>
+      </c>
+      <c r="B18" s="69" t="n">
+        <f aca="false">IF(Summary!$A$14="","",Summary!$B$14)</f>
+        <v>670</v>
+      </c>
+      <c r="C18" s="70" t="n">
+        <f aca="false">IF(Summary!$A$14="","",Summary!$C$14)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="70" t="n">
+        <f aca="false">IF(Summary!$A$14="","",Summary!$D$14)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="71" t="n">
+        <f aca="false">IF(Summary!$A$14="","",Summary!$E$14)</f>
+        <v>670</v>
+      </c>
+      <c r="F18" s="72" t="str">
+        <f aca="false">IF(Summary!$A$14="","",Summary!$F$14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="63" t="str">
+        <f aca="false">IF(Summary!$A$15="","",Summary!$A$15)</f>
+        <v>China</v>
+      </c>
+      <c r="B19" s="64" t="n">
+        <f aca="false">IF(Summary!$A$15="","",Summary!$B$15)</f>
+        <v>2960</v>
+      </c>
+      <c r="C19" s="65" t="n">
+        <f aca="false">IF(Summary!$A$15="","",Summary!$C$15)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="65" t="n">
+        <f aca="false">IF(Summary!$A$15="","",Summary!$D$15)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="66" t="n">
+        <f aca="false">IF(Summary!$A$15="","",Summary!$E$15)</f>
+        <v>2960</v>
+      </c>
+      <c r="F19" s="67" t="str">
+        <f aca="false">IF(Summary!$A$15="","",Summary!$F$15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="68" t="str">
+        <f aca="false">IF(Summary!$A$16="","",Summary!$A$16)</f>
+        <v>Shrimp Whole 5x3kgs</v>
+      </c>
+      <c r="B20" s="69" t="n">
+        <f aca="false">IF(Summary!$A$16="","",Summary!$B$16)</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="70" t="n">
+        <f aca="false">IF(Summary!$A$16="","",Summary!$C$16)</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="70" t="n">
+        <f aca="false">IF(Summary!$A$16="","",Summary!$D$16)</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="71" t="n">
+        <f aca="false">IF(Summary!$A$16="","",Summary!$E$16)</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="72" t="str">
+        <f aca="false">IF(Summary!$A$16="","",Summary!$F$16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="63" t="str">
+        <f aca="false">IF(Summary!$A$17="","",Summary!$A$17)</f>
+        <v/>
+      </c>
+      <c r="B21" s="64" t="str">
+        <f aca="false">IF(Summary!$A$17="","",Summary!$B$17)</f>
+        <v/>
+      </c>
+      <c r="C21" s="65" t="str">
+        <f aca="false">IF(Summary!$A$17="","",Summary!$C$17)</f>
+        <v/>
+      </c>
+      <c r="D21" s="65" t="str">
+        <f aca="false">IF(Summary!$A$17="","",Summary!$D$17)</f>
+        <v/>
+      </c>
+      <c r="E21" s="66" t="str">
+        <f aca="false">IF(Summary!$A$17="","",Summary!$E$17)</f>
+        <v/>
+      </c>
+      <c r="F21" s="67" t="str">
+        <f aca="false">IF(Summary!$A$17="","",Summary!$F$17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="68" t="str">
+        <f aca="false">IF(Summary!$A$18="","",Summary!$A$18)</f>
+        <v/>
+      </c>
+      <c r="B22" s="69" t="str">
+        <f aca="false">IF(Summary!$A$18="","",Summary!$B$18)</f>
+        <v/>
+      </c>
+      <c r="C22" s="70" t="str">
+        <f aca="false">IF(Summary!$A$18="","",Summary!$C$18)</f>
+        <v/>
+      </c>
+      <c r="D22" s="70" t="str">
+        <f aca="false">IF(Summary!$A$18="","",Summary!$D$18)</f>
+        <v/>
+      </c>
+      <c r="E22" s="71" t="str">
+        <f aca="false">IF(Summary!$A$18="","",Summary!$E$18)</f>
+        <v/>
+      </c>
+      <c r="F22" s="72" t="str">
+        <f aca="false">IF(Summary!$A$18="","",Summary!$F$18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="63" t="str">
+        <f aca="false">IF(Summary!$A$19="","",Summary!$A$19)</f>
+        <v/>
+      </c>
+      <c r="B23" s="64" t="str">
+        <f aca="false">IF(Summary!$A$19="","",Summary!$B$19)</f>
+        <v/>
+      </c>
+      <c r="C23" s="65" t="str">
+        <f aca="false">IF(Summary!$A$19="","",Summary!$C$19)</f>
+        <v/>
+      </c>
+      <c r="D23" s="65" t="str">
+        <f aca="false">IF(Summary!$A$19="","",Summary!$D$19)</f>
+        <v/>
+      </c>
+      <c r="E23" s="66" t="str">
+        <f aca="false">IF(Summary!$A$19="","",Summary!$E$19)</f>
+        <v/>
+      </c>
+      <c r="F23" s="67" t="str">
+        <f aca="false">IF(Summary!$A$19="","",Summary!$F$19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="73" t="str">
+        <f aca="false">Summary!$A$20</f>
+        <v>GRAND TOTAL</v>
+      </c>
+      <c r="B24" s="74" t="n">
+        <f aca="false">Summary!$B$20</f>
+        <v>102870</v>
+      </c>
+      <c r="C24" s="75" t="n">
+        <f aca="false">Summary!$C$20</f>
+        <v>4880</v>
+      </c>
+      <c r="D24" s="75" t="n">
+        <f aca="false">Summary!$D$20</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="74" t="n">
+        <f aca="false">Summary!$E$20</f>
+        <v>107750</v>
+      </c>
+      <c r="F24" s="76" t="str">
+        <f aca="false">Summary!$F$20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="60" t="s">
+        <v>138</v>
+      </c>
+      <c r="B26" s="60"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="60"/>
+    </row>
+    <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="61" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="62" t="s">
+        <v>139</v>
+      </c>
+      <c r="D27" s="62" t="s">
+        <v>140</v>
+      </c>
+      <c r="E27" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="F27" s="62"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="77" t="str">
+        <f aca="false">IF($H28="","",INDEX(Stock!$A$8:$A$69,$H28))</f>
+        <v>Blue Dolphin</v>
+      </c>
+      <c r="B28" s="77" t="str">
+        <f aca="false">IF($H28="","",INDEX(Stock!$B$8:$B$69,$H28))</f>
+        <v>PD PVN 100/200</v>
+      </c>
+      <c r="C28" s="78" t="n">
+        <f aca="false">IF($H28="","",INDEX(Stock!$D$8:$D$69,$H28))</f>
+        <v>1068</v>
+      </c>
+      <c r="D28" s="78" t="n">
+        <f aca="false">IF($H28="","",INDEX(Stock!$E$8:$E$69,$H28))</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="79" t="n">
+        <f aca="false">IF($H28="","",INDEX(Stock!$H$8:$H$69,$H28))</f>
+        <v>12527</v>
+      </c>
+      <c r="H28" s="80" t="n">
+        <f aca="false">IFERROR(MATCH(1,Stock!$N$8:$N$69,0),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="77" t="str">
+        <f aca="false">IF($H29="","",INDEX(Stock!$A$8:$A$69,$H29))</f>
+        <v>Blue Dolphin</v>
+      </c>
+      <c r="B29" s="77" t="str">
+        <f aca="false">IF($H29="","",INDEX(Stock!$B$8:$B$69,$H29))</f>
+        <v>PD KKD 100/200</v>
+      </c>
+      <c r="C29" s="78" t="n">
+        <f aca="false">IF($H29="","",INDEX(Stock!$D$8:$D$69,$H29))</f>
+        <v>65</v>
+      </c>
+      <c r="D29" s="78" t="n">
+        <f aca="false">IF($H29="","",INDEX(Stock!$E$8:$E$69,$H29))</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="79" t="n">
+        <f aca="false">IF($H29="","",INDEX(Stock!$H$8:$H$69,$H29))</f>
+        <v>582</v>
+      </c>
+      <c r="H29" s="80" t="n">
+        <f aca="false">IFERROR(MATCH(2,Stock!$N$8:$N$69,0),"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="77" t="str">
+        <f aca="false">IF($H30="","",INDEX(Stock!$A$8:$A$69,$H30))</f>
+        <v>Blue Dolphin</v>
+      </c>
+      <c r="B30" s="77" t="str">
+        <f aca="false">IF($H30="","",INDEX(Stock!$B$8:$B$69,$H30))</f>
+        <v>PUD PVN 200/300</v>
+      </c>
+      <c r="C30" s="78" t="n">
+        <f aca="false">IF($H30="","",INDEX(Stock!$D$8:$D$69,$H30))</f>
+        <v>267</v>
+      </c>
+      <c r="D30" s="78" t="n">
+        <f aca="false">IF($H30="","",INDEX(Stock!$E$8:$E$69,$H30))</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="79" t="n">
+        <f aca="false">IF($H30="","",INDEX(Stock!$H$8:$H$69,$H30))</f>
+        <v>2529</v>
+      </c>
+      <c r="H30" s="80" t="n">
+        <f aca="false">IFERROR(MATCH(3,Stock!$N$8:$N$69,0),"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="77" t="str">
+        <f aca="false">IF($H31="","",INDEX(Stock!$A$8:$A$69,$H31))</f>
+        <v>Primus Japan</v>
+      </c>
+      <c r="B31" s="77" t="str">
+        <f aca="false">IF($H31="","",INDEX(Stock!$B$8:$B$69,$H31))</f>
+        <v>PUD KZN 40/60</v>
+      </c>
+      <c r="C31" s="78" t="n">
+        <f aca="false">IF($H31="","",INDEX(Stock!$D$8:$D$69,$H31))</f>
+        <v>29</v>
+      </c>
+      <c r="D31" s="78" t="n">
+        <f aca="false">IF($H31="","",INDEX(Stock!$E$8:$E$69,$H31))</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="79" t="n">
+        <f aca="false">IF($H31="","",INDEX(Stock!$H$8:$H$69,$H31))</f>
+        <v>93</v>
+      </c>
+      <c r="H31" s="80" t="n">
+        <f aca="false">IFERROR(MATCH(4,Stock!$N$8:$N$69,0),"")</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="77" t="str">
+        <f aca="false">IF($H32="","",INDEX(Stock!$A$8:$A$69,$H32))</f>
+        <v>Primus Japan</v>
+      </c>
+      <c r="B32" s="77" t="str">
+        <f aca="false">IF($H32="","",INDEX(Stock!$B$8:$B$69,$H32))</f>
+        <v>PUD KZN 60/80</v>
+      </c>
+      <c r="C32" s="78" t="n">
+        <f aca="false">IF($H32="","",INDEX(Stock!$D$8:$D$69,$H32))</f>
         <v>39</v>
       </c>
-      <c r="C12" s="57" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="57" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="57" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="57" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="58" t="str">
-        <f aca="false">Summary!$A$9</f>
-        <v>Blue Dolphin</v>
-      </c>
-      <c r="B13" s="59" t="n">
-        <f aca="false">Summary!$B$9</f>
-        <v>28645</v>
-      </c>
-      <c r="C13" s="60" t="n">
-        <f aca="false">Summary!$C$9</f>
-        <v>1400</v>
-      </c>
-      <c r="D13" s="60" t="n">
-        <f aca="false">Summary!$D$9</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="61" t="n">
-        <f aca="false">Summary!$E$9</f>
-        <v>30045</v>
-      </c>
-      <c r="F13" s="62" t="str">
-        <f aca="false">Summary!$F$9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="63" t="str">
-        <f aca="false">Summary!$A$10</f>
+      <c r="D32" s="78" t="n">
+        <f aca="false">IF($H32="","",INDEX(Stock!$E$8:$E$69,$H32))</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="79" t="n">
+        <f aca="false">IF($H32="","",INDEX(Stock!$H$8:$H$69,$H32))</f>
+        <v>230</v>
+      </c>
+      <c r="H32" s="80" t="n">
+        <f aca="false">IFERROR(MATCH(5,Stock!$N$8:$N$69,0),"")</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="77" t="str">
+        <f aca="false">IF($H33="","",INDEX(Stock!$A$8:$A$69,$H33))</f>
         <v>Primus Japan</v>
       </c>
-      <c r="B14" s="64" t="n">
-        <f aca="false">Summary!$B$10</f>
-        <v>29316</v>
-      </c>
-      <c r="C14" s="65" t="n">
-        <f aca="false">Summary!$C$10</f>
-        <v>956</v>
-      </c>
-      <c r="D14" s="65" t="n">
-        <f aca="false">Summary!$D$10</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="66" t="n">
-        <f aca="false">Summary!$E$10</f>
-        <v>30272</v>
-      </c>
-      <c r="F14" s="67" t="str">
-        <f aca="false">Summary!$F$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="58" t="str">
-        <f aca="false">Summary!$A$11</f>
+      <c r="B33" s="77" t="str">
+        <f aca="false">IF($H33="","",INDEX(Stock!$B$8:$B$69,$H33))</f>
+        <v>PUD KZN 80/120</v>
+      </c>
+      <c r="C33" s="78" t="n">
+        <f aca="false">IF($H33="","",INDEX(Stock!$D$8:$D$69,$H33))</f>
+        <v>50</v>
+      </c>
+      <c r="D33" s="78" t="n">
+        <f aca="false">IF($H33="","",INDEX(Stock!$E$8:$E$69,$H33))</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="79" t="n">
+        <f aca="false">IF($H33="","",INDEX(Stock!$H$8:$H$69,$H33))</f>
+        <v>516</v>
+      </c>
+      <c r="H33" s="80" t="n">
+        <f aca="false">IFERROR(MATCH(6,Stock!$N$8:$N$69,0),"")</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="77" t="str">
+        <f aca="false">IF($H34="","",INDEX(Stock!$A$8:$A$69,$H34))</f>
+        <v>Primus Japan</v>
+      </c>
+      <c r="B34" s="77" t="str">
+        <f aca="false">IF($H34="","",INDEX(Stock!$B$8:$B$69,$H34))</f>
+        <v>PUD NRN 80/120</v>
+      </c>
+      <c r="C34" s="78" t="n">
+        <f aca="false">IF($H34="","",INDEX(Stock!$D$8:$D$69,$H34))</f>
+        <v>3</v>
+      </c>
+      <c r="D34" s="78" t="n">
+        <f aca="false">IF($H34="","",INDEX(Stock!$E$8:$E$69,$H34))</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="79" t="n">
+        <f aca="false">IF($H34="","",INDEX(Stock!$H$8:$H$69,$H34))</f>
+        <v>72</v>
+      </c>
+      <c r="H34" s="80" t="n">
+        <f aca="false">IFERROR(MATCH(7,Stock!$N$8:$N$69,0),"")</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="77" t="str">
+        <f aca="false">IF($H35="","",INDEX(Stock!$A$8:$A$69,$H35))</f>
+        <v>Primus Japan</v>
+      </c>
+      <c r="B35" s="77" t="str">
+        <f aca="false">IF($H35="","",INDEX(Stock!$B$8:$B$69,$H35))</f>
+        <v>PUD KZN 100/200</v>
+      </c>
+      <c r="C35" s="78" t="n">
+        <f aca="false">IF($H35="","",INDEX(Stock!$D$8:$D$69,$H35))</f>
+        <v>50</v>
+      </c>
+      <c r="D35" s="78" t="n">
+        <f aca="false">IF($H35="","",INDEX(Stock!$E$8:$E$69,$H35))</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="79" t="n">
+        <f aca="false">IF($H35="","",INDEX(Stock!$H$8:$H$69,$H35))</f>
+        <v>4259</v>
+      </c>
+      <c r="H35" s="80" t="n">
+        <f aca="false">IFERROR(MATCH(8,Stock!$N$8:$N$69,0),"")</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="77" t="str">
+        <f aca="false">IF($H36="","",INDEX(Stock!$A$8:$A$69,$H36))</f>
+        <v>Primus Japan</v>
+      </c>
+      <c r="B36" s="77" t="str">
+        <f aca="false">IF($H36="","",INDEX(Stock!$B$8:$B$69,$H36))</f>
+        <v>PUD KZN 200/300</v>
+      </c>
+      <c r="C36" s="78" t="n">
+        <f aca="false">IF($H36="","",INDEX(Stock!$D$8:$D$69,$H36))</f>
+        <v>33</v>
+      </c>
+      <c r="D36" s="78" t="n">
+        <f aca="false">IF($H36="","",INDEX(Stock!$E$8:$E$69,$H36))</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="79" t="n">
+        <f aca="false">IF($H36="","",INDEX(Stock!$H$8:$H$69,$H36))</f>
+        <v>1113</v>
+      </c>
+      <c r="H36" s="80" t="n">
+        <f aca="false">IFERROR(MATCH(9,Stock!$N$8:$N$69,0),"")</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="77" t="str">
+        <f aca="false">IF($H37="","",INDEX(Stock!$A$8:$A$69,$H37))</f>
+        <v>Primus Japan</v>
+      </c>
+      <c r="B37" s="77" t="str">
+        <f aca="false">IF($H37="","",INDEX(Stock!$B$8:$B$69,$H37))</f>
+        <v>PUD PVN 300/500</v>
+      </c>
+      <c r="C37" s="78" t="n">
+        <f aca="false">IF($H37="","",INDEX(Stock!$D$8:$D$69,$H37))</f>
+        <v>156</v>
+      </c>
+      <c r="D37" s="78" t="n">
+        <f aca="false">IF($H37="","",INDEX(Stock!$E$8:$E$69,$H37))</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="79" t="n">
+        <f aca="false">IF($H37="","",INDEX(Stock!$H$8:$H$69,$H37))</f>
+        <v>577</v>
+      </c>
+      <c r="H37" s="80" t="n">
+        <f aca="false">IFERROR(MATCH(10,Stock!$N$8:$N$69,0),"")</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="77" t="str">
+        <f aca="false">IF($H38="","",INDEX(Stock!$A$8:$A$69,$H38))</f>
+        <v>Primus Japan</v>
+      </c>
+      <c r="B38" s="77" t="str">
+        <f aca="false">IF($H38="","",INDEX(Stock!$B$8:$B$69,$H38))</f>
+        <v>PUD KKD 300/500</v>
+      </c>
+      <c r="C38" s="78" t="n">
+        <f aca="false">IF($H38="","",INDEX(Stock!$D$8:$D$69,$H38))</f>
+        <v>596</v>
+      </c>
+      <c r="D38" s="78" t="n">
+        <f aca="false">IF($H38="","",INDEX(Stock!$E$8:$E$69,$H38))</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="79" t="n">
+        <f aca="false">IF($H38="","",INDEX(Stock!$H$8:$H$69,$H38))</f>
+        <v>1176</v>
+      </c>
+      <c r="H38" s="80" t="n">
+        <f aca="false">IFERROR(MATCH(11,Stock!$N$8:$N$69,0),"")</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="77" t="str">
+        <f aca="false">IF($H39="","",INDEX(Stock!$A$8:$A$69,$H39))</f>
         <v>Primus EU</v>
       </c>
-      <c r="B15" s="59" t="n">
-        <f aca="false">Summary!$B$11</f>
-        <v>26619</v>
-      </c>
-      <c r="C15" s="60" t="n">
-        <f aca="false">Summary!$C$11</f>
+      <c r="B39" s="77" t="str">
+        <f aca="false">IF($H39="","",INDEX(Stock!$B$8:$B$69,$H39))</f>
+        <v>BKN</v>
+      </c>
+      <c r="C39" s="78" t="n">
+        <f aca="false">IF($H39="","",INDEX(Stock!$D$8:$D$69,$H39))</f>
         <v>52</v>
       </c>
-      <c r="D15" s="60" t="n">
-        <f aca="false">Summary!$D$11</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="61" t="n">
-        <f aca="false">Summary!$E$11</f>
-        <v>26671</v>
-      </c>
-      <c r="F15" s="62" t="str">
-        <f aca="false">Summary!$F$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="63" t="str">
-        <f aca="false">Summary!$A$12</f>
-        <v>AMF Brand</v>
-      </c>
-      <c r="B16" s="64" t="n">
-        <f aca="false">Summary!$B$12</f>
-        <v>1534</v>
-      </c>
-      <c r="C16" s="65" t="n">
-        <f aca="false">Summary!$C$12</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="65" t="n">
-        <f aca="false">Summary!$D$12</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="66" t="n">
-        <f aca="false">Summary!$E$12</f>
-        <v>1534</v>
-      </c>
-      <c r="F16" s="67" t="str">
-        <f aca="false">Summary!$F$12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="58" t="str">
-        <f aca="false">Summary!$A$13</f>
+      <c r="D39" s="78" t="n">
+        <f aca="false">IF($H39="","",INDEX(Stock!$E$8:$E$69,$H39))</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="79" t="n">
+        <f aca="false">IF($H39="","",INDEX(Stock!$H$8:$H$69,$H39))</f>
+        <v>15182</v>
+      </c>
+      <c r="H39" s="80" t="n">
+        <f aca="false">IFERROR(MATCH(12,Stock!$N$8:$N$69,0),"")</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="77" t="str">
+        <f aca="false">IF($H40="","",INDEX(Stock!$A$8:$A$69,$H40))</f>
         <v>THT Brand</v>
       </c>
-      <c r="B17" s="59" t="n">
-        <f aca="false">Summary!$B$13</f>
-        <v>13126</v>
-      </c>
-      <c r="C17" s="60" t="n">
-        <f aca="false">Summary!$C$13</f>
-        <v>2472</v>
-      </c>
-      <c r="D17" s="60" t="n">
-        <f aca="false">Summary!$D$13</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="61" t="n">
-        <f aca="false">Summary!$E$13</f>
-        <v>15598</v>
-      </c>
-      <c r="F17" s="62" t="str">
-        <f aca="false">Summary!$F$13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="63" t="str">
-        <f aca="false">Summary!$A$14</f>
-        <v>Deepsea</v>
-      </c>
-      <c r="B18" s="64" t="n">
-        <f aca="false">Summary!$B$14</f>
-        <v>670</v>
-      </c>
-      <c r="C18" s="65" t="n">
-        <f aca="false">Summary!$C$14</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="65" t="n">
-        <f aca="false">Summary!$D$14</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="66" t="n">
-        <f aca="false">Summary!$E$14</f>
-        <v>670</v>
-      </c>
-      <c r="F18" s="67" t="str">
-        <f aca="false">Summary!$F$14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="58" t="str">
-        <f aca="false">Summary!$A$15</f>
-        <v>China</v>
-      </c>
-      <c r="B19" s="59" t="n">
-        <f aca="false">Summary!$B$15</f>
-        <v>2960</v>
-      </c>
-      <c r="C19" s="60" t="n">
-        <f aca="false">Summary!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="60" t="n">
-        <f aca="false">Summary!$D$15</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="61" t="n">
-        <f aca="false">Summary!$E$15</f>
-        <v>2960</v>
-      </c>
-      <c r="F19" s="62" t="str">
-        <f aca="false">Summary!$F$15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="63" t="str">
-        <f aca="false">Summary!$A$16</f>
-        <v>Shrimp Whole 5x3kgs</v>
-      </c>
-      <c r="B20" s="64" t="n">
-        <f aca="false">Summary!$B$16</f>
-        <v>0</v>
-      </c>
-      <c r="C20" s="65" t="n">
-        <f aca="false">Summary!$C$16</f>
-        <v>0</v>
-      </c>
-      <c r="D20" s="65" t="n">
-        <f aca="false">Summary!$D$16</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="66" t="n">
-        <f aca="false">Summary!$E$16</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="67" t="str">
-        <f aca="false">Summary!$F$16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="68" t="str">
-        <f aca="false">Summary!$A$17</f>
-        <v>GRAND TOTAL</v>
-      </c>
-      <c r="B21" s="69" t="n">
-        <f aca="false">Summary!$B$17</f>
-        <v>102870</v>
-      </c>
-      <c r="C21" s="70" t="n">
-        <f aca="false">Summary!$C$17</f>
+      <c r="B40" s="77" t="str">
+        <f aca="false">IF($H40="","",INDEX(Stock!$B$8:$B$69,$H40))</f>
+        <v>PUD PVN 80/120</v>
+      </c>
+      <c r="C40" s="78" t="n">
+        <f aca="false">IF($H40="","",INDEX(Stock!$D$8:$D$69,$H40))</f>
+        <v>1872</v>
+      </c>
+      <c r="D40" s="78" t="n">
+        <f aca="false">IF($H40="","",INDEX(Stock!$E$8:$E$69,$H40))</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="79" t="n">
+        <f aca="false">IF($H40="","",INDEX(Stock!$H$8:$H$69,$H40))</f>
+        <v>3261</v>
+      </c>
+      <c r="H40" s="80" t="n">
+        <f aca="false">IFERROR(MATCH(13,Stock!$N$8:$N$69,0),"")</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="77" t="str">
+        <f aca="false">IF($H41="","",INDEX(Stock!$A$8:$A$69,$H41))</f>
+        <v>THT Brand</v>
+      </c>
+      <c r="B41" s="77" t="str">
+        <f aca="false">IF($H41="","",INDEX(Stock!$B$8:$B$69,$H41))</f>
+        <v>PUD PVN 100/200</v>
+      </c>
+      <c r="C41" s="78" t="n">
+        <f aca="false">IF($H41="","",INDEX(Stock!$D$8:$D$69,$H41))</f>
+        <v>600</v>
+      </c>
+      <c r="D41" s="78" t="n">
+        <f aca="false">IF($H41="","",INDEX(Stock!$E$8:$E$69,$H41))</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="79" t="n">
+        <f aca="false">IF($H41="","",INDEX(Stock!$H$8:$H$69,$H41))</f>
+        <v>7655</v>
+      </c>
+      <c r="H41" s="80" t="n">
+        <f aca="false">IFERROR(MATCH(14,Stock!$N$8:$N$69,0),"")</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="77" t="str">
+        <f aca="false">IF($H42="","",INDEX(Stock!$A$8:$A$69,$H42))</f>
+        <v/>
+      </c>
+      <c r="B42" s="77" t="str">
+        <f aca="false">IF($H42="","",INDEX(Stock!$B$8:$B$69,$H42))</f>
+        <v/>
+      </c>
+      <c r="C42" s="78" t="str">
+        <f aca="false">IF($H42="","",INDEX(Stock!$D$8:$D$69,$H42))</f>
+        <v/>
+      </c>
+      <c r="D42" s="78" t="str">
+        <f aca="false">IF($H42="","",INDEX(Stock!$E$8:$E$69,$H42))</f>
+        <v/>
+      </c>
+      <c r="E42" s="79" t="str">
+        <f aca="false">IF($H42="","",INDEX(Stock!$H$8:$H$69,$H42))</f>
+        <v/>
+      </c>
+      <c r="H42" s="80" t="str">
+        <f aca="false">IFERROR(MATCH(15,Stock!$N$8:$N$69,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="77" t="str">
+        <f aca="false">IF($H43="","",INDEX(Stock!$A$8:$A$69,$H43))</f>
+        <v/>
+      </c>
+      <c r="B43" s="77" t="str">
+        <f aca="false">IF($H43="","",INDEX(Stock!$B$8:$B$69,$H43))</f>
+        <v/>
+      </c>
+      <c r="C43" s="78" t="str">
+        <f aca="false">IF($H43="","",INDEX(Stock!$D$8:$D$69,$H43))</f>
+        <v/>
+      </c>
+      <c r="D43" s="78" t="str">
+        <f aca="false">IF($H43="","",INDEX(Stock!$E$8:$E$69,$H43))</f>
+        <v/>
+      </c>
+      <c r="E43" s="79" t="str">
+        <f aca="false">IF($H43="","",INDEX(Stock!$H$8:$H$69,$H43))</f>
+        <v/>
+      </c>
+      <c r="H43" s="80" t="str">
+        <f aca="false">IFERROR(MATCH(16,Stock!$N$8:$N$69,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="77" t="str">
+        <f aca="false">IF($H44="","",INDEX(Stock!$A$8:$A$69,$H44))</f>
+        <v/>
+      </c>
+      <c r="B44" s="77" t="str">
+        <f aca="false">IF($H44="","",INDEX(Stock!$B$8:$B$69,$H44))</f>
+        <v/>
+      </c>
+      <c r="C44" s="78" t="str">
+        <f aca="false">IF($H44="","",INDEX(Stock!$D$8:$D$69,$H44))</f>
+        <v/>
+      </c>
+      <c r="D44" s="78" t="str">
+        <f aca="false">IF($H44="","",INDEX(Stock!$E$8:$E$69,$H44))</f>
+        <v/>
+      </c>
+      <c r="E44" s="79" t="str">
+        <f aca="false">IF($H44="","",INDEX(Stock!$H$8:$H$69,$H44))</f>
+        <v/>
+      </c>
+      <c r="H44" s="80" t="str">
+        <f aca="false">IFERROR(MATCH(17,Stock!$N$8:$N$69,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="77" t="str">
+        <f aca="false">IF($H45="","",INDEX(Stock!$A$8:$A$69,$H45))</f>
+        <v/>
+      </c>
+      <c r="B45" s="77" t="str">
+        <f aca="false">IF($H45="","",INDEX(Stock!$B$8:$B$69,$H45))</f>
+        <v/>
+      </c>
+      <c r="C45" s="78" t="str">
+        <f aca="false">IF($H45="","",INDEX(Stock!$D$8:$D$69,$H45))</f>
+        <v/>
+      </c>
+      <c r="D45" s="78" t="str">
+        <f aca="false">IF($H45="","",INDEX(Stock!$E$8:$E$69,$H45))</f>
+        <v/>
+      </c>
+      <c r="E45" s="79" t="str">
+        <f aca="false">IF($H45="","",INDEX(Stock!$H$8:$H$69,$H45))</f>
+        <v/>
+      </c>
+      <c r="H45" s="80" t="str">
+        <f aca="false">IFERROR(MATCH(18,Stock!$N$8:$N$69,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="77" t="str">
+        <f aca="false">IF($H46="","",INDEX(Stock!$A$8:$A$69,$H46))</f>
+        <v/>
+      </c>
+      <c r="B46" s="77" t="str">
+        <f aca="false">IF($H46="","",INDEX(Stock!$B$8:$B$69,$H46))</f>
+        <v/>
+      </c>
+      <c r="C46" s="78" t="str">
+        <f aca="false">IF($H46="","",INDEX(Stock!$D$8:$D$69,$H46))</f>
+        <v/>
+      </c>
+      <c r="D46" s="78" t="str">
+        <f aca="false">IF($H46="","",INDEX(Stock!$E$8:$E$69,$H46))</f>
+        <v/>
+      </c>
+      <c r="E46" s="79" t="str">
+        <f aca="false">IF($H46="","",INDEX(Stock!$H$8:$H$69,$H46))</f>
+        <v/>
+      </c>
+      <c r="H46" s="80" t="str">
+        <f aca="false">IFERROR(MATCH(19,Stock!$N$8:$N$69,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="77" t="str">
+        <f aca="false">IF($H47="","",INDEX(Stock!$A$8:$A$69,$H47))</f>
+        <v/>
+      </c>
+      <c r="B47" s="77" t="str">
+        <f aca="false">IF($H47="","",INDEX(Stock!$B$8:$B$69,$H47))</f>
+        <v/>
+      </c>
+      <c r="C47" s="78" t="str">
+        <f aca="false">IF($H47="","",INDEX(Stock!$D$8:$D$69,$H47))</f>
+        <v/>
+      </c>
+      <c r="D47" s="78" t="str">
+        <f aca="false">IF($H47="","",INDEX(Stock!$E$8:$E$69,$H47))</f>
+        <v/>
+      </c>
+      <c r="E47" s="79" t="str">
+        <f aca="false">IF($H47="","",INDEX(Stock!$H$8:$H$69,$H47))</f>
+        <v/>
+      </c>
+      <c r="H47" s="80" t="str">
+        <f aca="false">IFERROR(MATCH(20,Stock!$N$8:$N$69,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="81" t="s">
+        <v>141</v>
+      </c>
+      <c r="B48" s="82" t="str">
+        <f aca="false">COUNTIF(Stock!$M$8:$M$69,1)&amp;" product(s)"</f>
+        <v>14 product(s)</v>
+      </c>
+      <c r="C48" s="83" t="n">
+        <f aca="false">SUM(C28:C47)</f>
         <v>4880</v>
       </c>
-      <c r="D21" s="70" t="n">
-        <f aca="false">Summary!$D$17</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="69" t="n">
-        <f aca="false">Summary!$E$17</f>
-        <v>107750</v>
-      </c>
-      <c r="F21" s="71" t="str">
-        <f aca="false">Summary!$F$17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="55" t="s">
-        <v>130</v>
-      </c>
-      <c r="B23" s="55"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="55"/>
-    </row>
-    <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="56" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="57" t="s">
-        <v>131</v>
-      </c>
-      <c r="D24" s="57" t="s">
-        <v>132</v>
-      </c>
-      <c r="E24" s="57" t="s">
-        <v>44</v>
-      </c>
-      <c r="F24" s="57"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="72" t="str">
-        <f aca="false">IF($H25="","",INDEX(Stock!$A$8:$A$49,$H25))</f>
-        <v>Blue Dolphin</v>
-      </c>
-      <c r="B25" s="72" t="str">
-        <f aca="false">IF($H25="","",INDEX(Stock!$B$8:$B$49,$H25))</f>
-        <v>PD PVN 100/200</v>
-      </c>
-      <c r="C25" s="73" t="n">
-        <f aca="false">IF($H25="","",INDEX(Stock!$D$8:$D$49,$H25))</f>
-        <v>1068</v>
-      </c>
-      <c r="D25" s="73" t="n">
-        <f aca="false">IF($H25="","",INDEX(Stock!$E$8:$E$49,$H25))</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="74" t="n">
-        <f aca="false">IF($H25="","",INDEX(Stock!$H$8:$H$49,$H25))</f>
-        <v>12527</v>
-      </c>
-      <c r="H25" s="75" t="n">
-        <f aca="false">IFERROR(MATCH(1,Stock!$N$8:$N$49,0),"")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="72" t="str">
-        <f aca="false">IF($H26="","",INDEX(Stock!$A$8:$A$49,$H26))</f>
-        <v>Blue Dolphin</v>
-      </c>
-      <c r="B26" s="72" t="str">
-        <f aca="false">IF($H26="","",INDEX(Stock!$B$8:$B$49,$H26))</f>
-        <v>PD KKD 100/200</v>
-      </c>
-      <c r="C26" s="73" t="n">
-        <f aca="false">IF($H26="","",INDEX(Stock!$D$8:$D$49,$H26))</f>
-        <v>65</v>
-      </c>
-      <c r="D26" s="73" t="n">
-        <f aca="false">IF($H26="","",INDEX(Stock!$E$8:$E$49,$H26))</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="74" t="n">
-        <f aca="false">IF($H26="","",INDEX(Stock!$H$8:$H$49,$H26))</f>
-        <v>582</v>
-      </c>
-      <c r="H26" s="75" t="n">
-        <f aca="false">IFERROR(MATCH(2,Stock!$N$8:$N$49,0),"")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="72" t="str">
-        <f aca="false">IF($H27="","",INDEX(Stock!$A$8:$A$49,$H27))</f>
-        <v>Blue Dolphin</v>
-      </c>
-      <c r="B27" s="72" t="str">
-        <f aca="false">IF($H27="","",INDEX(Stock!$B$8:$B$49,$H27))</f>
-        <v>PUD PVN 200/300</v>
-      </c>
-      <c r="C27" s="73" t="n">
-        <f aca="false">IF($H27="","",INDEX(Stock!$D$8:$D$49,$H27))</f>
-        <v>267</v>
-      </c>
-      <c r="D27" s="73" t="n">
-        <f aca="false">IF($H27="","",INDEX(Stock!$E$8:$E$49,$H27))</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="74" t="n">
-        <f aca="false">IF($H27="","",INDEX(Stock!$H$8:$H$49,$H27))</f>
-        <v>2529</v>
-      </c>
-      <c r="H27" s="75" t="n">
-        <f aca="false">IFERROR(MATCH(3,Stock!$N$8:$N$49,0),"")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="72" t="str">
-        <f aca="false">IF($H28="","",INDEX(Stock!$A$8:$A$49,$H28))</f>
-        <v>Primus Japan</v>
-      </c>
-      <c r="B28" s="72" t="str">
-        <f aca="false">IF($H28="","",INDEX(Stock!$B$8:$B$49,$H28))</f>
-        <v>PUD KZN 40/60</v>
-      </c>
-      <c r="C28" s="73" t="n">
-        <f aca="false">IF($H28="","",INDEX(Stock!$D$8:$D$49,$H28))</f>
-        <v>29</v>
-      </c>
-      <c r="D28" s="73" t="n">
-        <f aca="false">IF($H28="","",INDEX(Stock!$E$8:$E$49,$H28))</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="74" t="n">
-        <f aca="false">IF($H28="","",INDEX(Stock!$H$8:$H$49,$H28))</f>
-        <v>93</v>
-      </c>
-      <c r="H28" s="75" t="n">
-        <f aca="false">IFERROR(MATCH(4,Stock!$N$8:$N$49,0),"")</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="72" t="str">
-        <f aca="false">IF($H29="","",INDEX(Stock!$A$8:$A$49,$H29))</f>
-        <v>Primus Japan</v>
-      </c>
-      <c r="B29" s="72" t="str">
-        <f aca="false">IF($H29="","",INDEX(Stock!$B$8:$B$49,$H29))</f>
-        <v>PUD KZN 60/80</v>
-      </c>
-      <c r="C29" s="73" t="n">
-        <f aca="false">IF($H29="","",INDEX(Stock!$D$8:$D$49,$H29))</f>
-        <v>39</v>
-      </c>
-      <c r="D29" s="73" t="n">
-        <f aca="false">IF($H29="","",INDEX(Stock!$E$8:$E$49,$H29))</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="74" t="n">
-        <f aca="false">IF($H29="","",INDEX(Stock!$H$8:$H$49,$H29))</f>
-        <v>230</v>
-      </c>
-      <c r="H29" s="75" t="n">
-        <f aca="false">IFERROR(MATCH(5,Stock!$N$8:$N$49,0),"")</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="72" t="str">
-        <f aca="false">IF($H30="","",INDEX(Stock!$A$8:$A$49,$H30))</f>
-        <v>Primus Japan</v>
-      </c>
-      <c r="B30" s="72" t="str">
-        <f aca="false">IF($H30="","",INDEX(Stock!$B$8:$B$49,$H30))</f>
-        <v>PUD KZN 80/120</v>
-      </c>
-      <c r="C30" s="73" t="n">
-        <f aca="false">IF($H30="","",INDEX(Stock!$D$8:$D$49,$H30))</f>
-        <v>50</v>
-      </c>
-      <c r="D30" s="73" t="n">
-        <f aca="false">IF($H30="","",INDEX(Stock!$E$8:$E$49,$H30))</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="74" t="n">
-        <f aca="false">IF($H30="","",INDEX(Stock!$H$8:$H$49,$H30))</f>
-        <v>516</v>
-      </c>
-      <c r="H30" s="75" t="n">
-        <f aca="false">IFERROR(MATCH(6,Stock!$N$8:$N$49,0),"")</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="72" t="str">
-        <f aca="false">IF($H31="","",INDEX(Stock!$A$8:$A$49,$H31))</f>
-        <v>Primus Japan</v>
-      </c>
-      <c r="B31" s="72" t="str">
-        <f aca="false">IF($H31="","",INDEX(Stock!$B$8:$B$49,$H31))</f>
-        <v>PUD NRN 80/120</v>
-      </c>
-      <c r="C31" s="73" t="n">
-        <f aca="false">IF($H31="","",INDEX(Stock!$D$8:$D$49,$H31))</f>
-        <v>3</v>
-      </c>
-      <c r="D31" s="73" t="n">
-        <f aca="false">IF($H31="","",INDEX(Stock!$E$8:$E$49,$H31))</f>
-        <v>0</v>
-      </c>
-      <c r="E31" s="74" t="n">
-        <f aca="false">IF($H31="","",INDEX(Stock!$H$8:$H$49,$H31))</f>
-        <v>72</v>
-      </c>
-      <c r="H31" s="75" t="n">
-        <f aca="false">IFERROR(MATCH(7,Stock!$N$8:$N$49,0),"")</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="72" t="str">
-        <f aca="false">IF($H32="","",INDEX(Stock!$A$8:$A$49,$H32))</f>
-        <v>Primus Japan</v>
-      </c>
-      <c r="B32" s="72" t="str">
-        <f aca="false">IF($H32="","",INDEX(Stock!$B$8:$B$49,$H32))</f>
-        <v>PUD KZN 100/200</v>
-      </c>
-      <c r="C32" s="73" t="n">
-        <f aca="false">IF($H32="","",INDEX(Stock!$D$8:$D$49,$H32))</f>
-        <v>50</v>
-      </c>
-      <c r="D32" s="73" t="n">
-        <f aca="false">IF($H32="","",INDEX(Stock!$E$8:$E$49,$H32))</f>
-        <v>0</v>
-      </c>
-      <c r="E32" s="74" t="n">
-        <f aca="false">IF($H32="","",INDEX(Stock!$H$8:$H$49,$H32))</f>
-        <v>4259</v>
-      </c>
-      <c r="H32" s="75" t="n">
-        <f aca="false">IFERROR(MATCH(8,Stock!$N$8:$N$49,0),"")</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="72" t="str">
-        <f aca="false">IF($H33="","",INDEX(Stock!$A$8:$A$49,$H33))</f>
-        <v>Primus Japan</v>
-      </c>
-      <c r="B33" s="72" t="str">
-        <f aca="false">IF($H33="","",INDEX(Stock!$B$8:$B$49,$H33))</f>
-        <v>PUD KZN 200/300</v>
-      </c>
-      <c r="C33" s="73" t="n">
-        <f aca="false">IF($H33="","",INDEX(Stock!$D$8:$D$49,$H33))</f>
-        <v>33</v>
-      </c>
-      <c r="D33" s="73" t="n">
-        <f aca="false">IF($H33="","",INDEX(Stock!$E$8:$E$49,$H33))</f>
-        <v>0</v>
-      </c>
-      <c r="E33" s="74" t="n">
-        <f aca="false">IF($H33="","",INDEX(Stock!$H$8:$H$49,$H33))</f>
-        <v>1113</v>
-      </c>
-      <c r="H33" s="75" t="n">
-        <f aca="false">IFERROR(MATCH(9,Stock!$N$8:$N$49,0),"")</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="72" t="str">
-        <f aca="false">IF($H34="","",INDEX(Stock!$A$8:$A$49,$H34))</f>
-        <v>Primus Japan</v>
-      </c>
-      <c r="B34" s="72" t="str">
-        <f aca="false">IF($H34="","",INDEX(Stock!$B$8:$B$49,$H34))</f>
-        <v>PUD PVN 300/500</v>
-      </c>
-      <c r="C34" s="73" t="n">
-        <f aca="false">IF($H34="","",INDEX(Stock!$D$8:$D$49,$H34))</f>
-        <v>156</v>
-      </c>
-      <c r="D34" s="73" t="n">
-        <f aca="false">IF($H34="","",INDEX(Stock!$E$8:$E$49,$H34))</f>
-        <v>0</v>
-      </c>
-      <c r="E34" s="74" t="n">
-        <f aca="false">IF($H34="","",INDEX(Stock!$H$8:$H$49,$H34))</f>
-        <v>577</v>
-      </c>
-      <c r="H34" s="75" t="n">
-        <f aca="false">IFERROR(MATCH(10,Stock!$N$8:$N$49,0),"")</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="72" t="str">
-        <f aca="false">IF($H35="","",INDEX(Stock!$A$8:$A$49,$H35))</f>
-        <v>Primus Japan</v>
-      </c>
-      <c r="B35" s="72" t="str">
-        <f aca="false">IF($H35="","",INDEX(Stock!$B$8:$B$49,$H35))</f>
-        <v>PUD KKD 300/500</v>
-      </c>
-      <c r="C35" s="73" t="n">
-        <f aca="false">IF($H35="","",INDEX(Stock!$D$8:$D$49,$H35))</f>
-        <v>596</v>
-      </c>
-      <c r="D35" s="73" t="n">
-        <f aca="false">IF($H35="","",INDEX(Stock!$E$8:$E$49,$H35))</f>
-        <v>0</v>
-      </c>
-      <c r="E35" s="74" t="n">
-        <f aca="false">IF($H35="","",INDEX(Stock!$H$8:$H$49,$H35))</f>
-        <v>1176</v>
-      </c>
-      <c r="H35" s="75" t="n">
-        <f aca="false">IFERROR(MATCH(11,Stock!$N$8:$N$49,0),"")</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="72" t="str">
-        <f aca="false">IF($H36="","",INDEX(Stock!$A$8:$A$49,$H36))</f>
-        <v>Primus EU</v>
-      </c>
-      <c r="B36" s="72" t="str">
-        <f aca="false">IF($H36="","",INDEX(Stock!$B$8:$B$49,$H36))</f>
-        <v>BKN</v>
-      </c>
-      <c r="C36" s="73" t="n">
-        <f aca="false">IF($H36="","",INDEX(Stock!$D$8:$D$49,$H36))</f>
-        <v>52</v>
-      </c>
-      <c r="D36" s="73" t="n">
-        <f aca="false">IF($H36="","",INDEX(Stock!$E$8:$E$49,$H36))</f>
-        <v>0</v>
-      </c>
-      <c r="E36" s="74" t="n">
-        <f aca="false">IF($H36="","",INDEX(Stock!$H$8:$H$49,$H36))</f>
-        <v>15182</v>
-      </c>
-      <c r="H36" s="75" t="n">
-        <f aca="false">IFERROR(MATCH(12,Stock!$N$8:$N$49,0),"")</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="72" t="str">
-        <f aca="false">IF($H37="","",INDEX(Stock!$A$8:$A$49,$H37))</f>
-        <v>THT Brand</v>
-      </c>
-      <c r="B37" s="72" t="str">
-        <f aca="false">IF($H37="","",INDEX(Stock!$B$8:$B$49,$H37))</f>
-        <v>PUD PVN 80/120</v>
-      </c>
-      <c r="C37" s="73" t="n">
-        <f aca="false">IF($H37="","",INDEX(Stock!$D$8:$D$49,$H37))</f>
-        <v>1872</v>
-      </c>
-      <c r="D37" s="73" t="n">
-        <f aca="false">IF($H37="","",INDEX(Stock!$E$8:$E$49,$H37))</f>
-        <v>0</v>
-      </c>
-      <c r="E37" s="74" t="n">
-        <f aca="false">IF($H37="","",INDEX(Stock!$H$8:$H$49,$H37))</f>
-        <v>3261</v>
-      </c>
-      <c r="H37" s="75" t="n">
-        <f aca="false">IFERROR(MATCH(13,Stock!$N$8:$N$49,0),"")</f>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="72" t="str">
-        <f aca="false">IF($H38="","",INDEX(Stock!$A$8:$A$49,$H38))</f>
-        <v>THT Brand</v>
-      </c>
-      <c r="B38" s="72" t="str">
-        <f aca="false">IF($H38="","",INDEX(Stock!$B$8:$B$49,$H38))</f>
-        <v>PUD PVN 100/200</v>
-      </c>
-      <c r="C38" s="73" t="n">
-        <f aca="false">IF($H38="","",INDEX(Stock!$D$8:$D$49,$H38))</f>
-        <v>600</v>
-      </c>
-      <c r="D38" s="73" t="n">
-        <f aca="false">IF($H38="","",INDEX(Stock!$E$8:$E$49,$H38))</f>
-        <v>0</v>
-      </c>
-      <c r="E38" s="74" t="n">
-        <f aca="false">IF($H38="","",INDEX(Stock!$H$8:$H$49,$H38))</f>
-        <v>7655</v>
-      </c>
-      <c r="H38" s="75" t="n">
-        <f aca="false">IFERROR(MATCH(14,Stock!$N$8:$N$49,0),"")</f>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="72" t="str">
-        <f aca="false">IF($H39="","",INDEX(Stock!$A$8:$A$49,$H39))</f>
-        <v/>
-      </c>
-      <c r="B39" s="72" t="str">
-        <f aca="false">IF($H39="","",INDEX(Stock!$B$8:$B$49,$H39))</f>
-        <v/>
-      </c>
-      <c r="C39" s="73" t="str">
-        <f aca="false">IF($H39="","",INDEX(Stock!$D$8:$D$49,$H39))</f>
-        <v/>
-      </c>
-      <c r="D39" s="73" t="str">
-        <f aca="false">IF($H39="","",INDEX(Stock!$E$8:$E$49,$H39))</f>
-        <v/>
-      </c>
-      <c r="E39" s="74" t="str">
-        <f aca="false">IF($H39="","",INDEX(Stock!$H$8:$H$49,$H39))</f>
-        <v/>
-      </c>
-      <c r="H39" s="75" t="str">
-        <f aca="false">IFERROR(MATCH(15,Stock!$N$8:$N$49,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="72" t="str">
-        <f aca="false">IF($H40="","",INDEX(Stock!$A$8:$A$49,$H40))</f>
-        <v/>
-      </c>
-      <c r="B40" s="72" t="str">
-        <f aca="false">IF($H40="","",INDEX(Stock!$B$8:$B$49,$H40))</f>
-        <v/>
-      </c>
-      <c r="C40" s="73" t="str">
-        <f aca="false">IF($H40="","",INDEX(Stock!$D$8:$D$49,$H40))</f>
-        <v/>
-      </c>
-      <c r="D40" s="73" t="str">
-        <f aca="false">IF($H40="","",INDEX(Stock!$E$8:$E$49,$H40))</f>
-        <v/>
-      </c>
-      <c r="E40" s="74" t="str">
-        <f aca="false">IF($H40="","",INDEX(Stock!$H$8:$H$49,$H40))</f>
-        <v/>
-      </c>
-      <c r="H40" s="75" t="str">
-        <f aca="false">IFERROR(MATCH(16,Stock!$N$8:$N$49,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="72" t="str">
-        <f aca="false">IF($H41="","",INDEX(Stock!$A$8:$A$49,$H41))</f>
-        <v/>
-      </c>
-      <c r="B41" s="72" t="str">
-        <f aca="false">IF($H41="","",INDEX(Stock!$B$8:$B$49,$H41))</f>
-        <v/>
-      </c>
-      <c r="C41" s="73" t="str">
-        <f aca="false">IF($H41="","",INDEX(Stock!$D$8:$D$49,$H41))</f>
-        <v/>
-      </c>
-      <c r="D41" s="73" t="str">
-        <f aca="false">IF($H41="","",INDEX(Stock!$E$8:$E$49,$H41))</f>
-        <v/>
-      </c>
-      <c r="E41" s="74" t="str">
-        <f aca="false">IF($H41="","",INDEX(Stock!$H$8:$H$49,$H41))</f>
-        <v/>
-      </c>
-      <c r="H41" s="75" t="str">
-        <f aca="false">IFERROR(MATCH(17,Stock!$N$8:$N$49,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="72" t="str">
-        <f aca="false">IF($H42="","",INDEX(Stock!$A$8:$A$49,$H42))</f>
-        <v/>
-      </c>
-      <c r="B42" s="72" t="str">
-        <f aca="false">IF($H42="","",INDEX(Stock!$B$8:$B$49,$H42))</f>
-        <v/>
-      </c>
-      <c r="C42" s="73" t="str">
-        <f aca="false">IF($H42="","",INDEX(Stock!$D$8:$D$49,$H42))</f>
-        <v/>
-      </c>
-      <c r="D42" s="73" t="str">
-        <f aca="false">IF($H42="","",INDEX(Stock!$E$8:$E$49,$H42))</f>
-        <v/>
-      </c>
-      <c r="E42" s="74" t="str">
-        <f aca="false">IF($H42="","",INDEX(Stock!$H$8:$H$49,$H42))</f>
-        <v/>
-      </c>
-      <c r="H42" s="75" t="str">
-        <f aca="false">IFERROR(MATCH(18,Stock!$N$8:$N$49,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="72" t="str">
-        <f aca="false">IF($H43="","",INDEX(Stock!$A$8:$A$49,$H43))</f>
-        <v/>
-      </c>
-      <c r="B43" s="72" t="str">
-        <f aca="false">IF($H43="","",INDEX(Stock!$B$8:$B$49,$H43))</f>
-        <v/>
-      </c>
-      <c r="C43" s="73" t="str">
-        <f aca="false">IF($H43="","",INDEX(Stock!$D$8:$D$49,$H43))</f>
-        <v/>
-      </c>
-      <c r="D43" s="73" t="str">
-        <f aca="false">IF($H43="","",INDEX(Stock!$E$8:$E$49,$H43))</f>
-        <v/>
-      </c>
-      <c r="E43" s="74" t="str">
-        <f aca="false">IF($H43="","",INDEX(Stock!$H$8:$H$49,$H43))</f>
-        <v/>
-      </c>
-      <c r="H43" s="75" t="str">
-        <f aca="false">IFERROR(MATCH(19,Stock!$N$8:$N$49,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="72" t="str">
-        <f aca="false">IF($H44="","",INDEX(Stock!$A$8:$A$49,$H44))</f>
-        <v/>
-      </c>
-      <c r="B44" s="72" t="str">
-        <f aca="false">IF($H44="","",INDEX(Stock!$B$8:$B$49,$H44))</f>
-        <v/>
-      </c>
-      <c r="C44" s="73" t="str">
-        <f aca="false">IF($H44="","",INDEX(Stock!$D$8:$D$49,$H44))</f>
-        <v/>
-      </c>
-      <c r="D44" s="73" t="str">
-        <f aca="false">IF($H44="","",INDEX(Stock!$E$8:$E$49,$H44))</f>
-        <v/>
-      </c>
-      <c r="E44" s="74" t="str">
-        <f aca="false">IF($H44="","",INDEX(Stock!$H$8:$H$49,$H44))</f>
-        <v/>
-      </c>
-      <c r="H44" s="75" t="str">
-        <f aca="false">IFERROR(MATCH(20,Stock!$N$8:$N$49,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="76" t="s">
-        <v>133</v>
-      </c>
-      <c r="B45" s="77" t="str">
-        <f aca="false">COUNTIF(Stock!$M$8:$M$49,1)&amp;" product(s)"</f>
-        <v>14 product(s)</v>
-      </c>
-      <c r="C45" s="78" t="n">
-        <f aca="false">SUM(C25:C44)</f>
-        <v>4880</v>
-      </c>
-      <c r="D45" s="78" t="n">
-        <f aca="false">SUM(D25:D44)</f>
-        <v>0</v>
-      </c>
-      <c r="E45" s="76"/>
-      <c r="F45" s="76"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="79" t="str">
-        <f aca="false">IF(COUNTIF(Stock!$M$8:$M$49,1)&gt;20,"Note: "&amp;(COUNTIF(Stock!$M$8:$M$49,1)-20)&amp;" further product(s) moved today — see the Stock sheet for the full list.","")</f>
-        <v/>
-      </c>
-      <c r="B46" s="79"/>
-      <c r="C46" s="79"/>
-      <c r="D46" s="79"/>
-      <c r="E46" s="79"/>
-      <c r="F46" s="79"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="80" t="s">
-        <v>134</v>
-      </c>
-      <c r="B48" s="80"/>
-      <c r="C48" s="80"/>
-      <c r="D48" s="80"/>
-      <c r="E48" s="80"/>
-      <c r="F48" s="80"/>
+      <c r="D48" s="83" t="n">
+        <f aca="false">SUM(D28:D47)</f>
+        <v>0</v>
+      </c>
+      <c r="E48" s="81"/>
+      <c r="F48" s="81"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="84" t="str">
+        <f aca="false">IF(COUNTIF(Stock!$M$8:$M$69,1)&gt;20,"Note: "&amp;(COUNTIF(Stock!$M$8:$M$69,1)-20)&amp;" further product(s) moved today — see the Stock sheet for the full list.","")</f>
+        <v/>
+      </c>
+      <c r="B49" s="84"/>
+      <c r="C49" s="84"/>
+      <c r="D49" s="84"/>
+      <c r="E49" s="84"/>
+      <c r="F49" s="84"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="85" t="s">
+        <v>142</v>
+      </c>
+      <c r="B51" s="85"/>
+      <c r="C51" s="85"/>
+      <c r="D51" s="85"/>
+      <c r="E51" s="85"/>
+      <c r="F51" s="85"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true" password="df10" objects="true" scenarios="true" autoFilter="false"/>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="E3:F3"/>
@@ -7187,14 +8291,20 @@
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A10:F10"/>
     <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A51:F51"/>
   </mergeCells>
-  <conditionalFormatting sqref="A25:F44">
+  <conditionalFormatting sqref="A28:F47">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
-      <formula>$B25&lt;&gt;""</formula>
+      <formula>$B28&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13:F23">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>$A13=""</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/stock-statement/PEI-Stock-Register.xlsx
+++ b/stock-statement/PEI-Stock-Register.xlsx
@@ -18,7 +18,7 @@
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">'Daily Entry'!$6:$6</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Daily Entry'!$A$6:$E$250</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">'Daily Report'!$A$1:$F$51</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Read me'!$A$1:$B$51</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Read me'!$A$1:$B$58</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Stock!$A$1:$J$70</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">Stock!$7:$7</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Stock!$A$7:$J$69</definedName>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="152">
   <si>
     <t xml:space="preserve">PREMIER EXPORTS INTERNATIONAL</t>
   </si>
@@ -75,7 +75,7 @@
     <t xml:space="preserve">2.  Type the date, pick the product from the dropdown, enter slabs produced and/or shipped.</t>
   </si>
   <si>
-    <t xml:space="preserve">3.  On 'Stock', set the Statement date to today.</t>
+    <t xml:space="preserve">3.  On 'Stock', set the Statement date and the US$ → ₹ exchange rate for today.</t>
   </si>
   <si>
     <t xml:space="preserve">4.  Open 'Daily Report' and save it as PDF — that is the directors' copy.</t>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">'Daily Entry' — the whole grid: date, product, production, shipment, note.</t>
   </si>
   <si>
-    <t xml:space="preserve">'Stock' — the Statement date, and the yellow Rate / Slab column.</t>
+    <t xml:space="preserve">'Stock' — the Statement date, the US$ → ₹ exchange rate, and the Rate / Slab column.</t>
   </si>
   <si>
     <t xml:space="preserve">Every other cell is protected: headings, opening balances, formulas, totals,</t>
@@ -132,6 +132,24 @@
     <t xml:space="preserve">make the change, then Review ▸ Protect Sheet again to put the guard back.</t>
   </si>
   <si>
+    <t xml:space="preserve">How the stock is valued</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rate / Slab is the export price, in US dollars — that is what the column holds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stock Value (₹) = Closing Balance × Rate / Slab (US$) × the US$ → ₹ rate in C4.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The exchange rate lives in that one cell, so changing it revalues everything at once.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leave it blank and the value column stays blank rather than showing a wrong number;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the Daily Report says "Exchange rate not set" instead of a figure.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dates must be real dates</t>
   </si>
   <si>
@@ -192,6 +210,12 @@
     <t xml:space="preserve">← set to today; drives the two "today" columns and the Daily Report</t>
   </si>
   <si>
+    <t xml:space="preserve">US$ → ₹ exchange rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">← rupees per US dollar; converts the export rates into the value column</t>
+  </si>
+  <si>
     <t xml:space="preserve">Opening balance is a frozen baseline — never re-key it. Closing follows from the dated rows on 'Daily Entry'.</t>
   </si>
   <si>
@@ -219,7 +243,7 @@
     <t xml:space="preserve">Closing Balance</t>
   </si>
   <si>
-    <t xml:space="preserve">Rate / Slab (₹)</t>
+    <t xml:space="preserve">Rate / Slab (US$)</t>
   </si>
   <si>
     <t xml:space="preserve">Stock Value (₹)</t>
@@ -423,10 +447,16 @@
     <t xml:space="preserve">Stock Value</t>
   </si>
   <si>
+    <t xml:space="preserve">Stock Value (US$)</t>
+  </si>
+  <si>
     <t xml:space="preserve">slabs</t>
   </si>
   <si>
-    <t xml:space="preserve">at the rates entered on Stock</t>
+    <t xml:space="preserve">at the export rates and exchange rate on Stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the same stock at the export prices</t>
   </si>
   <si>
     <t xml:space="preserve">Shrimp Whole 5x3kgs</t>
@@ -466,9 +496,6 @@
   </si>
   <si>
     <t xml:space="preserve">CLOSING BALANCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STOCK VALUE</t>
   </si>
   <si>
     <t xml:space="preserve">POSITION BY BRAND</t>
@@ -493,14 +520,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="[&gt;=10000000]##\,##\,##\,##0;[&gt;=100000]##\,##\,##0;#,##0"/>
-    <numFmt numFmtId="167" formatCode="#,##0;\-#,##0;\–"/>
-    <numFmt numFmtId="168" formatCode="#,##0.00"/>
-    <numFmt numFmtId="169" formatCode="[&gt;=10000000]&quot;₹ &quot;##\,##\,##\,##0.00;[&gt;=100000]&quot;₹ &quot;##\,##\,##0.00;&quot;₹ &quot;#,##0.00"/>
-    <numFmt numFmtId="170" formatCode="General"/>
+    <numFmt numFmtId="166" formatCode="&quot;₹ &quot;#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="[&gt;=10000000]##\,##\,##\,##0;[&gt;=100000]##\,##\,##0;#,##0"/>
+    <numFmt numFmtId="168" formatCode="#,##0;\-#,##0;\–"/>
+    <numFmt numFmtId="169" formatCode="&quot;$ &quot;#,##0.00"/>
+    <numFmt numFmtId="170" formatCode="[&gt;=10000000]&quot;₹ &quot;##\,##\,##\,##0.00;[&gt;=100000]&quot;₹ &quot;##\,##\,##0.00;&quot;₹ &quot;#,##0.00"/>
+    <numFmt numFmtId="171" formatCode="General"/>
   </numFmts>
   <fonts count="35">
     <font>
@@ -927,7 +955,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="92">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -968,6 +996,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -988,7 +1020,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -996,19 +1032,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="169" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1020,7 +1052,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1028,15 +1064,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1044,7 +1076,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1052,7 +1084,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="167" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1060,15 +1092,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="167" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1080,7 +1112,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1088,7 +1120,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1100,7 +1132,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1108,7 +1140,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1152,15 +1188,15 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="26" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="167" fontId="26" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="27" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="26" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="27" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1184,19 +1220,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="167" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1204,19 +1240,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="167" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="32" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="32" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1224,15 +1260,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="167" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1240,15 +1276,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1260,7 +1296,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="32" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="32" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1280,7 +1316,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1688,7 +1724,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -1843,25 +1879,25 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="4"/>
+      <c r="B33" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="3" t="s">
-        <v>27</v>
+      <c r="B34" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="4" t="s">
-        <v>29</v>
-      </c>
+      <c r="B36" s="4"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="3" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1871,15 +1907,15 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="4"/>
+      <c r="B39" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="B40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="3" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1894,34 +1930,67 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="4"/>
+      <c r="B44" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="3" t="s">
-        <v>36</v>
+      <c r="B45" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="B46" s="4"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="4"/>
+      <c r="B47" s="3" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="3" t="s">
-        <v>38</v>
+      <c r="B48" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="4"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="4"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1962,2961 +2031,2970 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C3" s="8" t="n">
         <v>46254</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>43</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="9" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="I7" s="11" t="s">
+      <c r="A7" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="B7" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="K7" s="12"/>
-      <c r="L7" s="13" t="s">
+      <c r="C7" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="13" t="s">
+      <c r="D7" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="N7" s="13" t="s">
+      <c r="E7" s="12" t="s">
         <v>57</v>
       </c>
+      <c r="F7" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="K7" s="13"/>
+      <c r="L7" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="15" t="n">
+      <c r="A8" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="16" t="n">
         <v>11459</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <f aca="false">IF($A8="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L8,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>1068</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <f aca="false">IF($A8="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L8,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="18" t="n">
         <f aca="false">IF($A8="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L8))</f>
         <v>1068</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="18" t="n">
         <f aca="false">IF($A8="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L8))</f>
         <v>0</v>
       </c>
-      <c r="H8" s="18" t="n">
+      <c r="H8" s="19" t="n">
         <f aca="false">IF($A8="","",$C8+$F8-$G8)</f>
         <v>12527</v>
       </c>
-      <c r="I8" s="19"/>
-      <c r="J8" s="20" t="str">
-        <f aca="false">IF($I8="","",$H8*$I8)</f>
-        <v/>
-      </c>
-      <c r="L8" s="21" t="str">
+      <c r="I8" s="20"/>
+      <c r="J8" s="21" t="str">
+        <f aca="false">IF(OR($A8="",$I8="",$C$4=""),"",$H8*$I8*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L8" s="22" t="str">
         <f aca="false">IF($A8="","",$A8&amp;" - "&amp;$B8)</f>
         <v>Blue Dolphin - PD PVN 100/200</v>
       </c>
-      <c r="M8" s="21" t="n">
+      <c r="M8" s="22" t="n">
         <f aca="false">IF($A8="",0,IF(OR($D8&lt;&gt;0,$E8&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
-      <c r="N8" s="21" t="n">
+      <c r="N8" s="22" t="n">
         <f aca="false">IF($M8=1,SUM($M$8:$M8),"")</f>
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" s="23" t="n">
+      <c r="A9" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="24" t="n">
         <v>517</v>
       </c>
-      <c r="D9" s="24" t="n">
+      <c r="D9" s="25" t="n">
         <f aca="false">IF($A9="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L9,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>65</v>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="25" t="n">
         <f aca="false">IF($A9="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L9,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="F9" s="26" t="n">
         <f aca="false">IF($A9="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L9))</f>
         <v>65</v>
       </c>
-      <c r="G9" s="25" t="n">
+      <c r="G9" s="26" t="n">
         <f aca="false">IF($A9="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L9))</f>
         <v>0</v>
       </c>
-      <c r="H9" s="26" t="n">
+      <c r="H9" s="27" t="n">
         <f aca="false">IF($A9="","",$C9+$F9-$G9)</f>
         <v>582</v>
       </c>
-      <c r="I9" s="19"/>
-      <c r="J9" s="27" t="str">
-        <f aca="false">IF($I9="","",$H9*$I9)</f>
-        <v/>
-      </c>
-      <c r="L9" s="21" t="str">
+      <c r="I9" s="20"/>
+      <c r="J9" s="28" t="str">
+        <f aca="false">IF(OR($A9="",$I9="",$C$4=""),"",$H9*$I9*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L9" s="22" t="str">
         <f aca="false">IF($A9="","",$A9&amp;" - "&amp;$B9)</f>
         <v>Blue Dolphin - PD KKD 100/200</v>
       </c>
-      <c r="M9" s="21" t="n">
+      <c r="M9" s="22" t="n">
         <f aca="false">IF($A9="",0,IF(OR($D9&lt;&gt;0,$E9&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
-      <c r="N9" s="21" t="n">
+      <c r="N9" s="22" t="n">
         <f aca="false">IF($M9=1,SUM($M$8:$M9),"")</f>
         <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C10" s="15" t="n">
+      <c r="A10" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="16" t="n">
         <v>2262</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <f aca="false">IF($A10="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L10,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>267</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <f aca="false">IF($A10="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L10,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="18" t="n">
         <f aca="false">IF($A10="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L10))</f>
         <v>267</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="18" t="n">
         <f aca="false">IF($A10="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L10))</f>
         <v>0</v>
       </c>
-      <c r="H10" s="18" t="n">
+      <c r="H10" s="19" t="n">
         <f aca="false">IF($A10="","",$C10+$F10-$G10)</f>
         <v>2529</v>
       </c>
-      <c r="I10" s="19"/>
-      <c r="J10" s="20" t="str">
-        <f aca="false">IF($I10="","",$H10*$I10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="21" t="str">
+      <c r="I10" s="20"/>
+      <c r="J10" s="21" t="str">
+        <f aca="false">IF(OR($A10="",$I10="",$C$4=""),"",$H10*$I10*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L10" s="22" t="str">
         <f aca="false">IF($A10="","",$A10&amp;" - "&amp;$B10)</f>
         <v>Blue Dolphin - PUD PVN 200/300</v>
       </c>
-      <c r="M10" s="21" t="n">
+      <c r="M10" s="22" t="n">
         <f aca="false">IF($A10="",0,IF(OR($D10&lt;&gt;0,$E10&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
-      <c r="N10" s="21" t="n">
+      <c r="N10" s="22" t="n">
         <f aca="false">IF($M10=1,SUM($M$8:$M10),"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" s="23" t="n">
+      <c r="A11" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="24" t="n">
         <v>2835</v>
       </c>
-      <c r="D11" s="24" t="n">
+      <c r="D11" s="25" t="n">
         <f aca="false">IF($A11="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L11,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="25" t="n">
         <f aca="false">IF($A11="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L11,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F11" s="25" t="n">
+      <c r="F11" s="26" t="n">
         <f aca="false">IF($A11="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L11))</f>
         <v>0</v>
       </c>
-      <c r="G11" s="25" t="n">
+      <c r="G11" s="26" t="n">
         <f aca="false">IF($A11="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L11))</f>
         <v>0</v>
       </c>
-      <c r="H11" s="26" t="n">
+      <c r="H11" s="27" t="n">
         <f aca="false">IF($A11="","",$C11+$F11-$G11)</f>
         <v>2835</v>
       </c>
-      <c r="I11" s="19"/>
-      <c r="J11" s="27" t="str">
-        <f aca="false">IF($I11="","",$H11*$I11)</f>
-        <v/>
-      </c>
-      <c r="L11" s="21" t="str">
+      <c r="I11" s="20"/>
+      <c r="J11" s="28" t="str">
+        <f aca="false">IF(OR($A11="",$I11="",$C$4=""),"",$H11*$I11*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L11" s="22" t="str">
         <f aca="false">IF($A11="","",$A11&amp;" - "&amp;$B11)</f>
         <v>Blue Dolphin - PUD KKD 200/300</v>
       </c>
-      <c r="M11" s="21" t="n">
+      <c r="M11" s="22" t="n">
         <f aca="false">IF($A11="",0,IF(OR($D11&lt;&gt;0,$E11&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N11" s="21" t="str">
+      <c r="N11" s="22" t="str">
         <f aca="false">IF($M11=1,SUM($M$8:$M11),"")</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="15" t="n">
+      <c r="A12" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="16" t="n">
         <v>1673</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <f aca="false">IF($A12="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L12,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <f aca="false">IF($A12="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L12,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="18" t="n">
         <f aca="false">IF($A12="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L12))</f>
         <v>0</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="18" t="n">
         <f aca="false">IF($A12="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L12))</f>
         <v>0</v>
       </c>
-      <c r="H12" s="18" t="n">
+      <c r="H12" s="19" t="n">
         <f aca="false">IF($A12="","",$C12+$F12-$G12)</f>
         <v>1673</v>
       </c>
-      <c r="I12" s="19"/>
-      <c r="J12" s="20" t="str">
-        <f aca="false">IF($I12="","",$H12*$I12)</f>
-        <v/>
-      </c>
-      <c r="L12" s="21" t="str">
+      <c r="I12" s="20"/>
+      <c r="J12" s="21" t="str">
+        <f aca="false">IF(OR($A12="",$I12="",$C$4=""),"",$H12*$I12*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L12" s="22" t="str">
         <f aca="false">IF($A12="","",$A12&amp;" - "&amp;$B12)</f>
         <v>Blue Dolphin - PUD PVN 300/500</v>
       </c>
-      <c r="M12" s="21" t="n">
+      <c r="M12" s="22" t="n">
         <f aca="false">IF($A12="",0,IF(OR($D12&lt;&gt;0,$E12&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N12" s="21" t="str">
+      <c r="N12" s="22" t="str">
         <f aca="false">IF($M12=1,SUM($M$8:$M12),"")</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="23" t="n">
+      <c r="A13" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="24" t="n">
         <v>7542</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="25" t="n">
         <f aca="false">IF($A13="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L13,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="25" t="n">
         <f aca="false">IF($A13="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L13,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F13" s="25" t="n">
+      <c r="F13" s="26" t="n">
         <f aca="false">IF($A13="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L13))</f>
         <v>0</v>
       </c>
-      <c r="G13" s="25" t="n">
+      <c r="G13" s="26" t="n">
         <f aca="false">IF($A13="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L13))</f>
         <v>0</v>
       </c>
-      <c r="H13" s="26" t="n">
+      <c r="H13" s="27" t="n">
         <f aca="false">IF($A13="","",$C13+$F13-$G13)</f>
         <v>7542</v>
       </c>
-      <c r="I13" s="19"/>
-      <c r="J13" s="27" t="str">
-        <f aca="false">IF($I13="","",$H13*$I13)</f>
-        <v/>
-      </c>
-      <c r="L13" s="21" t="str">
+      <c r="I13" s="20"/>
+      <c r="J13" s="28" t="str">
+        <f aca="false">IF(OR($A13="",$I13="",$C$4=""),"",$H13*$I13*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L13" s="22" t="str">
         <f aca="false">IF($A13="","",$A13&amp;" - "&amp;$B13)</f>
         <v>Blue Dolphin - PUD KKD 300/500</v>
       </c>
-      <c r="M13" s="21" t="n">
+      <c r="M13" s="22" t="n">
         <f aca="false">IF($A13="",0,IF(OR($D13&lt;&gt;0,$E13&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N13" s="21" t="str">
+      <c r="N13" s="22" t="str">
         <f aca="false">IF($M13=1,SUM($M$8:$M13),"")</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" s="15" t="n">
+      <c r="A14" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="16" t="n">
         <v>2357</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <f aca="false">IF($A14="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L14,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <f aca="false">IF($A14="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L14,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F14" s="17" t="n">
+      <c r="F14" s="18" t="n">
         <f aca="false">IF($A14="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L14))</f>
         <v>0</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="18" t="n">
         <f aca="false">IF($A14="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L14))</f>
         <v>0</v>
       </c>
-      <c r="H14" s="18" t="n">
+      <c r="H14" s="19" t="n">
         <f aca="false">IF($A14="","",$C14+$F14-$G14)</f>
         <v>2357</v>
       </c>
-      <c r="I14" s="19"/>
-      <c r="J14" s="20" t="str">
-        <f aca="false">IF($I14="","",$H14*$I14)</f>
-        <v/>
-      </c>
-      <c r="L14" s="21" t="str">
+      <c r="I14" s="20"/>
+      <c r="J14" s="21" t="str">
+        <f aca="false">IF(OR($A14="",$I14="",$C$4=""),"",$H14*$I14*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L14" s="22" t="str">
         <f aca="false">IF($A14="","",$A14&amp;" - "&amp;$B14)</f>
         <v>Blue Dolphin - PD PVN 200/300</v>
       </c>
-      <c r="M14" s="21" t="n">
+      <c r="M14" s="22" t="n">
         <f aca="false">IF($A14="",0,IF(OR($D14&lt;&gt;0,$E14&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N14" s="21" t="str">
+      <c r="N14" s="22" t="str">
         <f aca="false">IF($M14=1,SUM($M$8:$M14),"")</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" s="23" t="n">
+      <c r="A15" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="24" t="n">
         <v>64</v>
       </c>
-      <c r="D15" s="24" t="n">
+      <c r="D15" s="25" t="n">
         <f aca="false">IF($A15="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L15,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>29</v>
       </c>
-      <c r="E15" s="24" t="n">
+      <c r="E15" s="25" t="n">
         <f aca="false">IF($A15="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L15,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F15" s="25" t="n">
+      <c r="F15" s="26" t="n">
         <f aca="false">IF($A15="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L15))</f>
         <v>29</v>
       </c>
-      <c r="G15" s="25" t="n">
+      <c r="G15" s="26" t="n">
         <f aca="false">IF($A15="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L15))</f>
         <v>0</v>
       </c>
-      <c r="H15" s="26" t="n">
+      <c r="H15" s="27" t="n">
         <f aca="false">IF($A15="","",$C15+$F15-$G15)</f>
         <v>93</v>
       </c>
-      <c r="I15" s="19"/>
-      <c r="J15" s="27" t="str">
-        <f aca="false">IF($I15="","",$H15*$I15)</f>
-        <v/>
-      </c>
-      <c r="L15" s="21" t="str">
+      <c r="I15" s="20"/>
+      <c r="J15" s="28" t="str">
+        <f aca="false">IF(OR($A15="",$I15="",$C$4=""),"",$H15*$I15*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L15" s="22" t="str">
         <f aca="false">IF($A15="","",$A15&amp;" - "&amp;$B15)</f>
         <v>Primus Japan - PUD KZN 40/60</v>
       </c>
-      <c r="M15" s="21" t="n">
+      <c r="M15" s="22" t="n">
         <f aca="false">IF($A15="",0,IF(OR($D15&lt;&gt;0,$E15&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
-      <c r="N15" s="21" t="n">
+      <c r="N15" s="22" t="n">
         <f aca="false">IF($M15=1,SUM($M$8:$M15),"")</f>
         <v>4</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" s="15" t="n">
+      <c r="A16" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="16" t="n">
         <v>191</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <f aca="false">IF($A16="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L16,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>39</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <f aca="false">IF($A16="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L16,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F16" s="17" t="n">
+      <c r="F16" s="18" t="n">
         <f aca="false">IF($A16="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L16))</f>
         <v>39</v>
       </c>
-      <c r="G16" s="17" t="n">
+      <c r="G16" s="18" t="n">
         <f aca="false">IF($A16="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L16))</f>
         <v>0</v>
       </c>
-      <c r="H16" s="18" t="n">
+      <c r="H16" s="19" t="n">
         <f aca="false">IF($A16="","",$C16+$F16-$G16)</f>
         <v>230</v>
       </c>
-      <c r="I16" s="19"/>
-      <c r="J16" s="20" t="str">
-        <f aca="false">IF($I16="","",$H16*$I16)</f>
-        <v/>
-      </c>
-      <c r="L16" s="21" t="str">
+      <c r="I16" s="20"/>
+      <c r="J16" s="21" t="str">
+        <f aca="false">IF(OR($A16="",$I16="",$C$4=""),"",$H16*$I16*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L16" s="22" t="str">
         <f aca="false">IF($A16="","",$A16&amp;" - "&amp;$B16)</f>
         <v>Primus Japan - PUD KZN 60/80</v>
       </c>
-      <c r="M16" s="21" t="n">
+      <c r="M16" s="22" t="n">
         <f aca="false">IF($A16="",0,IF(OR($D16&lt;&gt;0,$E16&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
-      <c r="N16" s="21" t="n">
+      <c r="N16" s="22" t="n">
         <f aca="false">IF($M16=1,SUM($M$8:$M16),"")</f>
         <v>5</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="B17" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="23" t="n">
+      <c r="A17" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="24" t="n">
         <v>16849</v>
       </c>
-      <c r="D17" s="24" t="n">
+      <c r="D17" s="25" t="n">
         <f aca="false">IF($A17="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L17,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E17" s="24" t="n">
+      <c r="E17" s="25" t="n">
         <f aca="false">IF($A17="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L17,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F17" s="25" t="n">
+      <c r="F17" s="26" t="n">
         <f aca="false">IF($A17="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L17))</f>
         <v>0</v>
       </c>
-      <c r="G17" s="25" t="n">
+      <c r="G17" s="26" t="n">
         <f aca="false">IF($A17="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L17))</f>
         <v>0</v>
       </c>
-      <c r="H17" s="26" t="n">
+      <c r="H17" s="27" t="n">
         <f aca="false">IF($A17="","",$C17+$F17-$G17)</f>
         <v>16849</v>
       </c>
-      <c r="I17" s="19"/>
-      <c r="J17" s="27" t="str">
-        <f aca="false">IF($I17="","",$H17*$I17)</f>
-        <v/>
-      </c>
-      <c r="L17" s="21" t="str">
+      <c r="I17" s="20"/>
+      <c r="J17" s="28" t="str">
+        <f aca="false">IF(OR($A17="",$I17="",$C$4=""),"",$H17*$I17*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L17" s="22" t="str">
         <f aca="false">IF($A17="","",$A17&amp;" - "&amp;$B17)</f>
         <v>Primus Japan - PUD PVN 80/120</v>
       </c>
-      <c r="M17" s="21" t="n">
+      <c r="M17" s="22" t="n">
         <f aca="false">IF($A17="",0,IF(OR($D17&lt;&gt;0,$E17&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N17" s="21" t="str">
+      <c r="N17" s="22" t="str">
         <f aca="false">IF($M17=1,SUM($M$8:$M17),"")</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="15" t="n">
+      <c r="A18" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="16" t="n">
         <v>466</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <f aca="false">IF($A18="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L18,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>50</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <f aca="false">IF($A18="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L18,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F18" s="17" t="n">
+      <c r="F18" s="18" t="n">
         <f aca="false">IF($A18="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L18))</f>
         <v>50</v>
       </c>
-      <c r="G18" s="17" t="n">
+      <c r="G18" s="18" t="n">
         <f aca="false">IF($A18="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L18))</f>
         <v>0</v>
       </c>
-      <c r="H18" s="18" t="n">
+      <c r="H18" s="19" t="n">
         <f aca="false">IF($A18="","",$C18+$F18-$G18)</f>
         <v>516</v>
       </c>
-      <c r="I18" s="19"/>
-      <c r="J18" s="20" t="str">
-        <f aca="false">IF($I18="","",$H18*$I18)</f>
-        <v/>
-      </c>
-      <c r="L18" s="21" t="str">
+      <c r="I18" s="20"/>
+      <c r="J18" s="21" t="str">
+        <f aca="false">IF(OR($A18="",$I18="",$C$4=""),"",$H18*$I18*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L18" s="22" t="str">
         <f aca="false">IF($A18="","",$A18&amp;" - "&amp;$B18)</f>
         <v>Primus Japan - PUD KZN 80/120</v>
       </c>
-      <c r="M18" s="21" t="n">
+      <c r="M18" s="22" t="n">
         <f aca="false">IF($A18="",0,IF(OR($D18&lt;&gt;0,$E18&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
-      <c r="N18" s="21" t="n">
+      <c r="N18" s="22" t="n">
         <f aca="false">IF($M18=1,SUM($M$8:$M18),"")</f>
         <v>6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" s="23" t="n">
+      <c r="A19" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="24" t="n">
         <v>69</v>
       </c>
-      <c r="D19" s="24" t="n">
+      <c r="D19" s="25" t="n">
         <f aca="false">IF($A19="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L19,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>3</v>
       </c>
-      <c r="E19" s="24" t="n">
+      <c r="E19" s="25" t="n">
         <f aca="false">IF($A19="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L19,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F19" s="25" t="n">
+      <c r="F19" s="26" t="n">
         <f aca="false">IF($A19="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L19))</f>
         <v>3</v>
       </c>
-      <c r="G19" s="25" t="n">
+      <c r="G19" s="26" t="n">
         <f aca="false">IF($A19="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L19))</f>
         <v>0</v>
       </c>
-      <c r="H19" s="26" t="n">
+      <c r="H19" s="27" t="n">
         <f aca="false">IF($A19="","",$C19+$F19-$G19)</f>
         <v>72</v>
       </c>
-      <c r="I19" s="19"/>
-      <c r="J19" s="27" t="str">
-        <f aca="false">IF($I19="","",$H19*$I19)</f>
-        <v/>
-      </c>
-      <c r="L19" s="21" t="str">
+      <c r="I19" s="20"/>
+      <c r="J19" s="28" t="str">
+        <f aca="false">IF(OR($A19="",$I19="",$C$4=""),"",$H19*$I19*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L19" s="22" t="str">
         <f aca="false">IF($A19="","",$A19&amp;" - "&amp;$B19)</f>
         <v>Primus Japan - PUD NRN 80/120</v>
       </c>
-      <c r="M19" s="21" t="n">
+      <c r="M19" s="22" t="n">
         <f aca="false">IF($A19="",0,IF(OR($D19&lt;&gt;0,$E19&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
-      <c r="N19" s="21" t="n">
+      <c r="N19" s="22" t="n">
         <f aca="false">IF($M19=1,SUM($M$8:$M19),"")</f>
         <v>7</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" s="15" t="n">
+      <c r="A20" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="16" t="n">
         <v>2617</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <f aca="false">IF($A20="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L20,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <f aca="false">IF($A20="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L20,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F20" s="17" t="n">
+      <c r="F20" s="18" t="n">
         <f aca="false">IF($A20="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L20))</f>
         <v>0</v>
       </c>
-      <c r="G20" s="17" t="n">
+      <c r="G20" s="18" t="n">
         <f aca="false">IF($A20="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L20))</f>
         <v>0</v>
       </c>
-      <c r="H20" s="18" t="n">
+      <c r="H20" s="19" t="n">
         <f aca="false">IF($A20="","",$C20+$F20-$G20)</f>
         <v>2617</v>
       </c>
-      <c r="I20" s="19"/>
-      <c r="J20" s="20" t="str">
-        <f aca="false">IF($I20="","",$H20*$I20)</f>
-        <v/>
-      </c>
-      <c r="L20" s="21" t="str">
+      <c r="I20" s="20"/>
+      <c r="J20" s="21" t="str">
+        <f aca="false">IF(OR($A20="",$I20="",$C$4=""),"",$H20*$I20*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L20" s="22" t="str">
         <f aca="false">IF($A20="","",$A20&amp;" - "&amp;$B20)</f>
         <v>Primus Japan - PUD PVN 100/200</v>
       </c>
-      <c r="M20" s="21" t="n">
+      <c r="M20" s="22" t="n">
         <f aca="false">IF($A20="",0,IF(OR($D20&lt;&gt;0,$E20&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N20" s="21" t="str">
+      <c r="N20" s="22" t="str">
         <f aca="false">IF($M20=1,SUM($M$8:$M20),"")</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" s="23" t="n">
+      <c r="A21" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="24" t="n">
         <v>13</v>
       </c>
-      <c r="D21" s="24" t="n">
+      <c r="D21" s="25" t="n">
         <f aca="false">IF($A21="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L21,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E21" s="24" t="n">
+      <c r="E21" s="25" t="n">
         <f aca="false">IF($A21="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L21,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F21" s="25" t="n">
+      <c r="F21" s="26" t="n">
         <f aca="false">IF($A21="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L21))</f>
         <v>0</v>
       </c>
-      <c r="G21" s="25" t="n">
+      <c r="G21" s="26" t="n">
         <f aca="false">IF($A21="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L21))</f>
         <v>0</v>
       </c>
-      <c r="H21" s="26" t="n">
+      <c r="H21" s="27" t="n">
         <f aca="false">IF($A21="","",$C21+$F21-$G21)</f>
         <v>13</v>
       </c>
-      <c r="I21" s="19"/>
-      <c r="J21" s="27" t="str">
-        <f aca="false">IF($I21="","",$H21*$I21)</f>
-        <v/>
-      </c>
-      <c r="L21" s="21" t="str">
+      <c r="I21" s="20"/>
+      <c r="J21" s="28" t="str">
+        <f aca="false">IF(OR($A21="",$I21="",$C$4=""),"",$H21*$I21*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L21" s="22" t="str">
         <f aca="false">IF($A21="","",$A21&amp;" - "&amp;$B21)</f>
         <v>Primus Japan - PUD NRN 100/200</v>
       </c>
-      <c r="M21" s="21" t="n">
+      <c r="M21" s="22" t="n">
         <f aca="false">IF($A21="",0,IF(OR($D21&lt;&gt;0,$E21&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N21" s="21" t="str">
+      <c r="N21" s="22" t="str">
         <f aca="false">IF($M21=1,SUM($M$8:$M21),"")</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B22" s="14" t="s">
+      <c r="A22" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="15" t="n">
+      <c r="B22" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="16" t="n">
         <v>4209</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="17" t="n">
         <f aca="false">IF($A22="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L22,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>50</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="17" t="n">
         <f aca="false">IF($A22="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L22,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F22" s="17" t="n">
+      <c r="F22" s="18" t="n">
         <f aca="false">IF($A22="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L22))</f>
         <v>50</v>
       </c>
-      <c r="G22" s="17" t="n">
+      <c r="G22" s="18" t="n">
         <f aca="false">IF($A22="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L22))</f>
         <v>0</v>
       </c>
-      <c r="H22" s="18" t="n">
+      <c r="H22" s="19" t="n">
         <f aca="false">IF($A22="","",$C22+$F22-$G22)</f>
         <v>4259</v>
       </c>
-      <c r="I22" s="19"/>
-      <c r="J22" s="20" t="str">
-        <f aca="false">IF($I22="","",$H22*$I22)</f>
-        <v/>
-      </c>
-      <c r="L22" s="21" t="str">
+      <c r="I22" s="20"/>
+      <c r="J22" s="21" t="str">
+        <f aca="false">IF(OR($A22="",$I22="",$C$4=""),"",$H22*$I22*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L22" s="22" t="str">
         <f aca="false">IF($A22="","",$A22&amp;" - "&amp;$B22)</f>
         <v>Primus Japan - PUD KZN 100/200</v>
       </c>
-      <c r="M22" s="21" t="n">
+      <c r="M22" s="22" t="n">
         <f aca="false">IF($A22="",0,IF(OR($D22&lt;&gt;0,$E22&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
-      <c r="N22" s="21" t="n">
+      <c r="N22" s="22" t="n">
         <f aca="false">IF($M22=1,SUM($M$8:$M22),"")</f>
         <v>8</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="24" t="n">
+      <c r="A23" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="25" t="n">
         <f aca="false">IF($A23="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L23,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E23" s="24" t="n">
+      <c r="E23" s="25" t="n">
         <f aca="false">IF($A23="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L23,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F23" s="25" t="n">
+      <c r="F23" s="26" t="n">
         <f aca="false">IF($A23="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L23))</f>
         <v>0</v>
       </c>
-      <c r="G23" s="25" t="n">
+      <c r="G23" s="26" t="n">
         <f aca="false">IF($A23="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L23))</f>
         <v>0</v>
       </c>
-      <c r="H23" s="26" t="n">
+      <c r="H23" s="27" t="n">
         <f aca="false">IF($A23="","",$C23+$F23-$G23)</f>
         <v>0</v>
       </c>
-      <c r="I23" s="19"/>
-      <c r="J23" s="27" t="str">
-        <f aca="false">IF($I23="","",$H23*$I23)</f>
-        <v/>
-      </c>
-      <c r="L23" s="21" t="str">
+      <c r="I23" s="20"/>
+      <c r="J23" s="28" t="str">
+        <f aca="false">IF(OR($A23="",$I23="",$C$4=""),"",$H23*$I23*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L23" s="22" t="str">
         <f aca="false">IF($A23="","",$A23&amp;" - "&amp;$B23)</f>
         <v>Primus Japan - PUD PVN 200/300</v>
       </c>
-      <c r="M23" s="21" t="n">
+      <c r="M23" s="22" t="n">
         <f aca="false">IF($A23="",0,IF(OR($D23&lt;&gt;0,$E23&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N23" s="21" t="str">
+      <c r="N23" s="22" t="str">
         <f aca="false">IF($M23=1,SUM($M$8:$M23),"")</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="15" t="n">
+      <c r="A24" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="16" t="n">
         <v>2757</v>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="D24" s="17" t="n">
         <f aca="false">IF($A24="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L24,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="E24" s="17" t="n">
         <f aca="false">IF($A24="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L24,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F24" s="17" t="n">
+      <c r="F24" s="18" t="n">
         <f aca="false">IF($A24="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L24))</f>
         <v>0</v>
       </c>
-      <c r="G24" s="17" t="n">
+      <c r="G24" s="18" t="n">
         <f aca="false">IF($A24="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L24))</f>
         <v>0</v>
       </c>
-      <c r="H24" s="18" t="n">
+      <c r="H24" s="19" t="n">
         <f aca="false">IF($A24="","",$C24+$F24-$G24)</f>
         <v>2757</v>
       </c>
-      <c r="I24" s="19"/>
-      <c r="J24" s="20" t="str">
-        <f aca="false">IF($I24="","",$H24*$I24)</f>
-        <v/>
-      </c>
-      <c r="L24" s="21" t="str">
+      <c r="I24" s="20"/>
+      <c r="J24" s="21" t="str">
+        <f aca="false">IF(OR($A24="",$I24="",$C$4=""),"",$H24*$I24*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L24" s="22" t="str">
         <f aca="false">IF($A24="","",$A24&amp;" - "&amp;$B24)</f>
         <v>Primus Japan - PUD KKD 200/300</v>
       </c>
-      <c r="M24" s="21" t="n">
+      <c r="M24" s="22" t="n">
         <f aca="false">IF($A24="",0,IF(OR($D24&lt;&gt;0,$E24&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N24" s="21" t="str">
+      <c r="N24" s="22" t="str">
         <f aca="false">IF($M24=1,SUM($M$8:$M24),"")</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="B25" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" s="23" t="n">
+      <c r="A25" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="24" t="n">
         <v>1080</v>
       </c>
-      <c r="D25" s="24" t="n">
+      <c r="D25" s="25" t="n">
         <f aca="false">IF($A25="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L25,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>33</v>
       </c>
-      <c r="E25" s="24" t="n">
+      <c r="E25" s="25" t="n">
         <f aca="false">IF($A25="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L25,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F25" s="25" t="n">
+      <c r="F25" s="26" t="n">
         <f aca="false">IF($A25="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L25))</f>
         <v>33</v>
       </c>
-      <c r="G25" s="25" t="n">
+      <c r="G25" s="26" t="n">
         <f aca="false">IF($A25="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L25))</f>
         <v>0</v>
       </c>
-      <c r="H25" s="26" t="n">
+      <c r="H25" s="27" t="n">
         <f aca="false">IF($A25="","",$C25+$F25-$G25)</f>
         <v>1113</v>
       </c>
-      <c r="I25" s="19"/>
-      <c r="J25" s="27" t="str">
-        <f aca="false">IF($I25="","",$H25*$I25)</f>
-        <v/>
-      </c>
-      <c r="L25" s="21" t="str">
+      <c r="I25" s="20"/>
+      <c r="J25" s="28" t="str">
+        <f aca="false">IF(OR($A25="",$I25="",$C$4=""),"",$H25*$I25*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L25" s="22" t="str">
         <f aca="false">IF($A25="","",$A25&amp;" - "&amp;$B25)</f>
         <v>Primus Japan - PUD KZN 200/300</v>
       </c>
-      <c r="M25" s="21" t="n">
+      <c r="M25" s="22" t="n">
         <f aca="false">IF($A25="",0,IF(OR($D25&lt;&gt;0,$E25&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
-      <c r="N25" s="21" t="n">
+      <c r="N25" s="22" t="n">
         <f aca="false">IF($M25=1,SUM($M$8:$M25),"")</f>
         <v>9</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C26" s="15" t="n">
+      <c r="A26" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="16" t="n">
         <v>421</v>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="D26" s="17" t="n">
         <f aca="false">IF($A26="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L26,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>156</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="E26" s="17" t="n">
         <f aca="false">IF($A26="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L26,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F26" s="17" t="n">
+      <c r="F26" s="18" t="n">
         <f aca="false">IF($A26="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L26))</f>
         <v>156</v>
       </c>
-      <c r="G26" s="17" t="n">
+      <c r="G26" s="18" t="n">
         <f aca="false">IF($A26="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L26))</f>
         <v>0</v>
       </c>
-      <c r="H26" s="18" t="n">
+      <c r="H26" s="19" t="n">
         <f aca="false">IF($A26="","",$C26+$F26-$G26)</f>
         <v>577</v>
       </c>
-      <c r="I26" s="19"/>
-      <c r="J26" s="20" t="str">
-        <f aca="false">IF($I26="","",$H26*$I26)</f>
-        <v/>
-      </c>
-      <c r="L26" s="21" t="str">
+      <c r="I26" s="20"/>
+      <c r="J26" s="21" t="str">
+        <f aca="false">IF(OR($A26="",$I26="",$C$4=""),"",$H26*$I26*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L26" s="22" t="str">
         <f aca="false">IF($A26="","",$A26&amp;" - "&amp;$B26)</f>
         <v>Primus Japan - PUD PVN 300/500</v>
       </c>
-      <c r="M26" s="21" t="n">
+      <c r="M26" s="22" t="n">
         <f aca="false">IF($A26="",0,IF(OR($D26&lt;&gt;0,$E26&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
-      <c r="N26" s="21" t="n">
+      <c r="N26" s="22" t="n">
         <f aca="false">IF($M26=1,SUM($M$8:$M26),"")</f>
         <v>10</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="B27" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" s="23" t="n">
+      <c r="A27" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" s="24" t="n">
         <v>580</v>
       </c>
-      <c r="D27" s="24" t="n">
+      <c r="D27" s="25" t="n">
         <f aca="false">IF($A27="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L27,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>596</v>
       </c>
-      <c r="E27" s="24" t="n">
+      <c r="E27" s="25" t="n">
         <f aca="false">IF($A27="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L27,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F27" s="25" t="n">
+      <c r="F27" s="26" t="n">
         <f aca="false">IF($A27="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L27))</f>
         <v>596</v>
       </c>
-      <c r="G27" s="25" t="n">
+      <c r="G27" s="26" t="n">
         <f aca="false">IF($A27="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L27))</f>
         <v>0</v>
       </c>
-      <c r="H27" s="26" t="n">
+      <c r="H27" s="27" t="n">
         <f aca="false">IF($A27="","",$C27+$F27-$G27)</f>
         <v>1176</v>
       </c>
-      <c r="I27" s="19"/>
-      <c r="J27" s="27" t="str">
-        <f aca="false">IF($I27="","",$H27*$I27)</f>
-        <v/>
-      </c>
-      <c r="L27" s="21" t="str">
+      <c r="I27" s="20"/>
+      <c r="J27" s="28" t="str">
+        <f aca="false">IF(OR($A27="",$I27="",$C$4=""),"",$H27*$I27*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L27" s="22" t="str">
         <f aca="false">IF($A27="","",$A27&amp;" - "&amp;$B27)</f>
         <v>Primus Japan - PUD KKD 300/500</v>
       </c>
-      <c r="M27" s="21" t="n">
+      <c r="M27" s="22" t="n">
         <f aca="false">IF($A27="",0,IF(OR($D27&lt;&gt;0,$E27&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
-      <c r="N27" s="21" t="n">
+      <c r="N27" s="22" t="n">
         <f aca="false">IF($M27=1,SUM($M$8:$M27),"")</f>
         <v>11</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" s="15" t="n">
+      <c r="A28" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="16" t="n">
         <v>185</v>
       </c>
-      <c r="D28" s="16" t="n">
+      <c r="D28" s="17" t="n">
         <f aca="false">IF($A28="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L28,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E28" s="16" t="n">
+      <c r="E28" s="17" t="n">
         <f aca="false">IF($A28="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L28,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F28" s="17" t="n">
+      <c r="F28" s="18" t="n">
         <f aca="false">IF($A28="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L28))</f>
         <v>0</v>
       </c>
-      <c r="G28" s="17" t="n">
+      <c r="G28" s="18" t="n">
         <f aca="false">IF($A28="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L28))</f>
         <v>0</v>
       </c>
-      <c r="H28" s="18" t="n">
+      <c r="H28" s="19" t="n">
         <f aca="false">IF($A28="","",$C28+$F28-$G28)</f>
         <v>185</v>
       </c>
-      <c r="I28" s="19"/>
-      <c r="J28" s="20" t="str">
-        <f aca="false">IF($I28="","",$H28*$I28)</f>
-        <v/>
-      </c>
-      <c r="L28" s="21" t="str">
+      <c r="I28" s="20"/>
+      <c r="J28" s="21" t="str">
+        <f aca="false">IF(OR($A28="",$I28="",$C$4=""),"",$H28*$I28*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L28" s="22" t="str">
         <f aca="false">IF($A28="","",$A28&amp;" - "&amp;$B28)</f>
         <v>Primus EU - PUD 20/40</v>
       </c>
-      <c r="M28" s="21" t="n">
+      <c r="M28" s="22" t="n">
         <f aca="false">IF($A28="",0,IF(OR($D28&lt;&gt;0,$E28&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N28" s="21" t="str">
+      <c r="N28" s="22" t="str">
         <f aca="false">IF($M28=1,SUM($M$8:$M28),"")</f>
         <v/>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="B29" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" s="23" t="n">
+      <c r="A29" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" s="24" t="n">
         <v>368</v>
       </c>
-      <c r="D29" s="24" t="n">
+      <c r="D29" s="25" t="n">
         <f aca="false">IF($A29="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L29,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E29" s="24" t="n">
+      <c r="E29" s="25" t="n">
         <f aca="false">IF($A29="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L29,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F29" s="25" t="n">
+      <c r="F29" s="26" t="n">
         <f aca="false">IF($A29="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L29))</f>
         <v>0</v>
       </c>
-      <c r="G29" s="25" t="n">
+      <c r="G29" s="26" t="n">
         <f aca="false">IF($A29="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L29))</f>
         <v>0</v>
       </c>
-      <c r="H29" s="26" t="n">
+      <c r="H29" s="27" t="n">
         <f aca="false">IF($A29="","",$C29+$F29-$G29)</f>
         <v>368</v>
       </c>
-      <c r="I29" s="19"/>
-      <c r="J29" s="27" t="str">
-        <f aca="false">IF($I29="","",$H29*$I29)</f>
-        <v/>
-      </c>
-      <c r="L29" s="21" t="str">
+      <c r="I29" s="20"/>
+      <c r="J29" s="28" t="str">
+        <f aca="false">IF(OR($A29="",$I29="",$C$4=""),"",$H29*$I29*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L29" s="22" t="str">
         <f aca="false">IF($A29="","",$A29&amp;" - "&amp;$B29)</f>
         <v>Primus EU - PUD 40/60</v>
       </c>
-      <c r="M29" s="21" t="n">
+      <c r="M29" s="22" t="n">
         <f aca="false">IF($A29="",0,IF(OR($D29&lt;&gt;0,$E29&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N29" s="21" t="str">
+      <c r="N29" s="22" t="str">
         <f aca="false">IF($M29=1,SUM($M$8:$M29),"")</f>
         <v/>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" s="15" t="n">
+      <c r="A30" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="16" t="n">
         <v>380</v>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="D30" s="17" t="n">
         <f aca="false">IF($A30="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L30,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="E30" s="17" t="n">
         <f aca="false">IF($A30="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L30,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F30" s="17" t="n">
+      <c r="F30" s="18" t="n">
         <f aca="false">IF($A30="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L30))</f>
         <v>0</v>
       </c>
-      <c r="G30" s="17" t="n">
+      <c r="G30" s="18" t="n">
         <f aca="false">IF($A30="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L30))</f>
         <v>0</v>
       </c>
-      <c r="H30" s="18" t="n">
+      <c r="H30" s="19" t="n">
         <f aca="false">IF($A30="","",$C30+$F30-$G30)</f>
         <v>380</v>
       </c>
-      <c r="I30" s="19"/>
-      <c r="J30" s="20" t="str">
-        <f aca="false">IF($I30="","",$H30*$I30)</f>
-        <v/>
-      </c>
-      <c r="L30" s="21" t="str">
+      <c r="I30" s="20"/>
+      <c r="J30" s="21" t="str">
+        <f aca="false">IF(OR($A30="",$I30="",$C$4=""),"",$H30*$I30*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L30" s="22" t="str">
         <f aca="false">IF($A30="","",$A30&amp;" - "&amp;$B30)</f>
         <v>Primus EU - PUD 60/80</v>
       </c>
-      <c r="M30" s="21" t="n">
+      <c r="M30" s="22" t="n">
         <f aca="false">IF($A30="",0,IF(OR($D30&lt;&gt;0,$E30&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N30" s="21" t="str">
+      <c r="N30" s="22" t="str">
         <f aca="false">IF($M30=1,SUM($M$8:$M30),"")</f>
         <v/>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="B31" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" s="23" t="n">
+      <c r="A31" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="24" t="n">
         <v>1151</v>
       </c>
-      <c r="D31" s="24" t="n">
+      <c r="D31" s="25" t="n">
         <f aca="false">IF($A31="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L31,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E31" s="24" t="n">
+      <c r="E31" s="25" t="n">
         <f aca="false">IF($A31="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L31,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F31" s="25" t="n">
+      <c r="F31" s="26" t="n">
         <f aca="false">IF($A31="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L31))</f>
         <v>0</v>
       </c>
-      <c r="G31" s="25" t="n">
+      <c r="G31" s="26" t="n">
         <f aca="false">IF($A31="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L31))</f>
         <v>0</v>
       </c>
-      <c r="H31" s="26" t="n">
+      <c r="H31" s="27" t="n">
         <f aca="false">IF($A31="","",$C31+$F31-$G31)</f>
         <v>1151</v>
       </c>
-      <c r="I31" s="19"/>
-      <c r="J31" s="27" t="str">
-        <f aca="false">IF($I31="","",$H31*$I31)</f>
-        <v/>
-      </c>
-      <c r="L31" s="21" t="str">
+      <c r="I31" s="20"/>
+      <c r="J31" s="28" t="str">
+        <f aca="false">IF(OR($A31="",$I31="",$C$4=""),"",$H31*$I31*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L31" s="22" t="str">
         <f aca="false">IF($A31="","",$A31&amp;" - "&amp;$B31)</f>
         <v>Primus EU - PUD 80/120</v>
       </c>
-      <c r="M31" s="21" t="n">
+      <c r="M31" s="22" t="n">
         <f aca="false">IF($A31="",0,IF(OR($D31&lt;&gt;0,$E31&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N31" s="21" t="str">
+      <c r="N31" s="22" t="str">
         <f aca="false">IF($M31=1,SUM($M$8:$M31),"")</f>
         <v/>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C32" s="15" t="n">
+      <c r="A32" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="16" t="n">
         <v>3797</v>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="D32" s="17" t="n">
         <f aca="false">IF($A32="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L32,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="E32" s="17" t="n">
         <f aca="false">IF($A32="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L32,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F32" s="17" t="n">
+      <c r="F32" s="18" t="n">
         <f aca="false">IF($A32="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L32))</f>
         <v>0</v>
       </c>
-      <c r="G32" s="17" t="n">
+      <c r="G32" s="18" t="n">
         <f aca="false">IF($A32="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L32))</f>
         <v>0</v>
       </c>
-      <c r="H32" s="18" t="n">
+      <c r="H32" s="19" t="n">
         <f aca="false">IF($A32="","",$C32+$F32-$G32)</f>
         <v>3797</v>
       </c>
-      <c r="I32" s="19"/>
-      <c r="J32" s="20" t="str">
-        <f aca="false">IF($I32="","",$H32*$I32)</f>
-        <v/>
-      </c>
-      <c r="L32" s="21" t="str">
+      <c r="I32" s="20"/>
+      <c r="J32" s="21" t="str">
+        <f aca="false">IF(OR($A32="",$I32="",$C$4=""),"",$H32*$I32*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L32" s="22" t="str">
         <f aca="false">IF($A32="","",$A32&amp;" - "&amp;$B32)</f>
         <v>Primus EU - PUD 100/200</v>
       </c>
-      <c r="M32" s="21" t="n">
+      <c r="M32" s="22" t="n">
         <f aca="false">IF($A32="",0,IF(OR($D32&lt;&gt;0,$E32&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N32" s="21" t="str">
+      <c r="N32" s="22" t="str">
         <f aca="false">IF($M32=1,SUM($M$8:$M32),"")</f>
         <v/>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="B33" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="C33" s="23" t="n">
+      <c r="A33" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C33" s="24" t="n">
         <v>4118</v>
       </c>
-      <c r="D33" s="24" t="n">
+      <c r="D33" s="25" t="n">
         <f aca="false">IF($A33="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L33,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E33" s="24" t="n">
+      <c r="E33" s="25" t="n">
         <f aca="false">IF($A33="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L33,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F33" s="25" t="n">
+      <c r="F33" s="26" t="n">
         <f aca="false">IF($A33="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L33))</f>
         <v>0</v>
       </c>
-      <c r="G33" s="25" t="n">
+      <c r="G33" s="26" t="n">
         <f aca="false">IF($A33="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L33))</f>
         <v>0</v>
       </c>
-      <c r="H33" s="26" t="n">
+      <c r="H33" s="27" t="n">
         <f aca="false">IF($A33="","",$C33+$F33-$G33)</f>
         <v>4118</v>
       </c>
-      <c r="I33" s="19"/>
-      <c r="J33" s="27" t="str">
-        <f aca="false">IF($I33="","",$H33*$I33)</f>
-        <v/>
-      </c>
-      <c r="L33" s="21" t="str">
+      <c r="I33" s="20"/>
+      <c r="J33" s="28" t="str">
+        <f aca="false">IF(OR($A33="",$I33="",$C$4=""),"",$H33*$I33*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L33" s="22" t="str">
         <f aca="false">IF($A33="","",$A33&amp;" - "&amp;$B33)</f>
         <v>Primus EU - PUD 200/300</v>
       </c>
-      <c r="M33" s="21" t="n">
+      <c r="M33" s="22" t="n">
         <f aca="false">IF($A33="",0,IF(OR($D33&lt;&gt;0,$E33&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N33" s="21" t="str">
+      <c r="N33" s="22" t="str">
         <f aca="false">IF($M33=1,SUM($M$8:$M33),"")</f>
         <v/>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C34" s="15" t="n">
+      <c r="A34" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C34" s="16" t="n">
         <v>1490</v>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="D34" s="17" t="n">
         <f aca="false">IF($A34="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L34,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E34" s="16" t="n">
+      <c r="E34" s="17" t="n">
         <f aca="false">IF($A34="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L34,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F34" s="17" t="n">
+      <c r="F34" s="18" t="n">
         <f aca="false">IF($A34="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L34))</f>
         <v>0</v>
       </c>
-      <c r="G34" s="17" t="n">
+      <c r="G34" s="18" t="n">
         <f aca="false">IF($A34="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L34))</f>
         <v>0</v>
       </c>
-      <c r="H34" s="18" t="n">
+      <c r="H34" s="19" t="n">
         <f aca="false">IF($A34="","",$C34+$F34-$G34)</f>
         <v>1490</v>
       </c>
-      <c r="I34" s="19"/>
-      <c r="J34" s="20" t="str">
-        <f aca="false">IF($I34="","",$H34*$I34)</f>
-        <v/>
-      </c>
-      <c r="L34" s="21" t="str">
+      <c r="I34" s="20"/>
+      <c r="J34" s="21" t="str">
+        <f aca="false">IF(OR($A34="",$I34="",$C$4=""),"",$H34*$I34*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L34" s="22" t="str">
         <f aca="false">IF($A34="","",$A34&amp;" - "&amp;$B34)</f>
         <v>Primus EU - PUD 300/500</v>
       </c>
-      <c r="M34" s="21" t="n">
+      <c r="M34" s="22" t="n">
         <f aca="false">IF($A34="",0,IF(OR($D34&lt;&gt;0,$E34&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N34" s="21" t="str">
+      <c r="N34" s="22" t="str">
         <f aca="false">IF($M34=1,SUM($M$8:$M34),"")</f>
         <v/>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="B35" s="22" t="s">
+      <c r="A35" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="C35" s="23" t="n">
+      <c r="B35" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="C35" s="24" t="n">
         <v>15130</v>
       </c>
-      <c r="D35" s="24" t="n">
+      <c r="D35" s="25" t="n">
         <f aca="false">IF($A35="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L35,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>52</v>
       </c>
-      <c r="E35" s="24" t="n">
+      <c r="E35" s="25" t="n">
         <f aca="false">IF($A35="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L35,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F35" s="25" t="n">
+      <c r="F35" s="26" t="n">
         <f aca="false">IF($A35="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L35))</f>
         <v>52</v>
       </c>
-      <c r="G35" s="25" t="n">
+      <c r="G35" s="26" t="n">
         <f aca="false">IF($A35="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L35))</f>
         <v>0</v>
       </c>
-      <c r="H35" s="26" t="n">
+      <c r="H35" s="27" t="n">
         <f aca="false">IF($A35="","",$C35+$F35-$G35)</f>
         <v>15182</v>
       </c>
-      <c r="I35" s="19"/>
-      <c r="J35" s="27" t="str">
-        <f aca="false">IF($I35="","",$H35*$I35)</f>
-        <v/>
-      </c>
-      <c r="L35" s="21" t="str">
+      <c r="I35" s="20"/>
+      <c r="J35" s="28" t="str">
+        <f aca="false">IF(OR($A35="",$I35="",$C$4=""),"",$H35*$I35*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L35" s="22" t="str">
         <f aca="false">IF($A35="","",$A35&amp;" - "&amp;$B35)</f>
         <v>Primus EU - BKN</v>
       </c>
-      <c r="M35" s="21" t="n">
+      <c r="M35" s="22" t="n">
         <f aca="false">IF($A35="",0,IF(OR($D35&lt;&gt;0,$E35&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
-      <c r="N35" s="21" t="n">
+      <c r="N35" s="22" t="n">
         <f aca="false">IF($M35=1,SUM($M$8:$M35),"")</f>
         <v>12</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="16" t="n">
+      <c r="A36" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="17" t="n">
         <f aca="false">IF($A36="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L36,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="E36" s="17" t="n">
         <f aca="false">IF($A36="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L36,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F36" s="17" t="n">
+      <c r="F36" s="18" t="n">
         <f aca="false">IF($A36="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L36))</f>
         <v>0</v>
       </c>
-      <c r="G36" s="17" t="n">
+      <c r="G36" s="18" t="n">
         <f aca="false">IF($A36="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L36))</f>
         <v>0</v>
       </c>
-      <c r="H36" s="18" t="n">
+      <c r="H36" s="19" t="n">
         <f aca="false">IF($A36="","",$C36+$F36-$G36)</f>
         <v>0</v>
       </c>
-      <c r="I36" s="19"/>
-      <c r="J36" s="20" t="str">
-        <f aca="false">IF($I36="","",$H36*$I36)</f>
-        <v/>
-      </c>
-      <c r="L36" s="21" t="str">
+      <c r="I36" s="20"/>
+      <c r="J36" s="21" t="str">
+        <f aca="false">IF(OR($A36="",$I36="",$C$4=""),"",$H36*$I36*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L36" s="22" t="str">
         <f aca="false">IF($A36="","",$A36&amp;" - "&amp;$B36)</f>
         <v>AMF Brand - PD PVN 100/200</v>
       </c>
-      <c r="M36" s="21" t="n">
+      <c r="M36" s="22" t="n">
         <f aca="false">IF($A36="",0,IF(OR($D36&lt;&gt;0,$E36&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N36" s="21" t="str">
+      <c r="N36" s="22" t="str">
         <f aca="false">IF($M36=1,SUM($M$8:$M36),"")</f>
         <v/>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="B37" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="C37" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="24" t="n">
+      <c r="A37" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="25" t="n">
         <f aca="false">IF($A37="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L37,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E37" s="24" t="n">
+      <c r="E37" s="25" t="n">
         <f aca="false">IF($A37="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L37,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F37" s="25" t="n">
+      <c r="F37" s="26" t="n">
         <f aca="false">IF($A37="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L37))</f>
         <v>0</v>
       </c>
-      <c r="G37" s="25" t="n">
+      <c r="G37" s="26" t="n">
         <f aca="false">IF($A37="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L37))</f>
         <v>0</v>
       </c>
-      <c r="H37" s="26" t="n">
+      <c r="H37" s="27" t="n">
         <f aca="false">IF($A37="","",$C37+$F37-$G37)</f>
         <v>0</v>
       </c>
-      <c r="I37" s="19"/>
-      <c r="J37" s="27" t="str">
-        <f aca="false">IF($I37="","",$H37*$I37)</f>
-        <v/>
-      </c>
-      <c r="L37" s="21" t="str">
+      <c r="I37" s="20"/>
+      <c r="J37" s="28" t="str">
+        <f aca="false">IF(OR($A37="",$I37="",$C$4=""),"",$H37*$I37*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L37" s="22" t="str">
         <f aca="false">IF($A37="","",$A37&amp;" - "&amp;$B37)</f>
         <v>AMF Brand - PD KKD 100/200</v>
       </c>
-      <c r="M37" s="21" t="n">
+      <c r="M37" s="22" t="n">
         <f aca="false">IF($A37="",0,IF(OR($D37&lt;&gt;0,$E37&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N37" s="21" t="str">
+      <c r="N37" s="22" t="str">
         <f aca="false">IF($M37=1,SUM($M$8:$M37),"")</f>
         <v/>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C38" s="15" t="n">
+      <c r="A38" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" s="16" t="n">
         <v>1516</v>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="D38" s="17" t="n">
         <f aca="false">IF($A38="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L38,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E38" s="16" t="n">
+      <c r="E38" s="17" t="n">
         <f aca="false">IF($A38="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L38,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F38" s="17" t="n">
+      <c r="F38" s="18" t="n">
         <f aca="false">IF($A38="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L38))</f>
         <v>0</v>
       </c>
-      <c r="G38" s="17" t="n">
+      <c r="G38" s="18" t="n">
         <f aca="false">IF($A38="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L38))</f>
         <v>0</v>
       </c>
-      <c r="H38" s="18" t="n">
+      <c r="H38" s="19" t="n">
         <f aca="false">IF($A38="","",$C38+$F38-$G38)</f>
         <v>1516</v>
       </c>
-      <c r="I38" s="19"/>
-      <c r="J38" s="20" t="str">
-        <f aca="false">IF($I38="","",$H38*$I38)</f>
-        <v/>
-      </c>
-      <c r="L38" s="21" t="str">
+      <c r="I38" s="20"/>
+      <c r="J38" s="21" t="str">
+        <f aca="false">IF(OR($A38="",$I38="",$C$4=""),"",$H38*$I38*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L38" s="22" t="str">
         <f aca="false">IF($A38="","",$A38&amp;" - "&amp;$B38)</f>
         <v>AMF Brand - PUD PVN 200/300</v>
       </c>
-      <c r="M38" s="21" t="n">
+      <c r="M38" s="22" t="n">
         <f aca="false">IF($A38="",0,IF(OR($D38&lt;&gt;0,$E38&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N38" s="21" t="str">
+      <c r="N38" s="22" t="str">
         <f aca="false">IF($M38=1,SUM($M$8:$M38),"")</f>
         <v/>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="B39" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="C39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="24" t="n">
+      <c r="A39" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C39" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="25" t="n">
         <f aca="false">IF($A39="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L39,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E39" s="24" t="n">
+      <c r="E39" s="25" t="n">
         <f aca="false">IF($A39="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L39,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F39" s="25" t="n">
+      <c r="F39" s="26" t="n">
         <f aca="false">IF($A39="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L39))</f>
         <v>0</v>
       </c>
-      <c r="G39" s="25" t="n">
+      <c r="G39" s="26" t="n">
         <f aca="false">IF($A39="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L39))</f>
         <v>0</v>
       </c>
-      <c r="H39" s="26" t="n">
+      <c r="H39" s="27" t="n">
         <f aca="false">IF($A39="","",$C39+$F39-$G39)</f>
         <v>0</v>
       </c>
-      <c r="I39" s="19"/>
-      <c r="J39" s="27" t="str">
-        <f aca="false">IF($I39="","",$H39*$I39)</f>
-        <v/>
-      </c>
-      <c r="L39" s="21" t="str">
+      <c r="I39" s="20"/>
+      <c r="J39" s="28" t="str">
+        <f aca="false">IF(OR($A39="",$I39="",$C$4=""),"",$H39*$I39*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L39" s="22" t="str">
         <f aca="false">IF($A39="","",$A39&amp;" - "&amp;$B39)</f>
         <v>AMF Brand - PUD KKD 200/300</v>
       </c>
-      <c r="M39" s="21" t="n">
+      <c r="M39" s="22" t="n">
         <f aca="false">IF($A39="",0,IF(OR($D39&lt;&gt;0,$E39&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N39" s="21" t="str">
+      <c r="N39" s="22" t="str">
         <f aca="false">IF($M39=1,SUM($M$8:$M39),"")</f>
         <v/>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C40" s="15" t="n">
+      <c r="A40" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="16" t="n">
         <v>18</v>
       </c>
-      <c r="D40" s="16" t="n">
+      <c r="D40" s="17" t="n">
         <f aca="false">IF($A40="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L40,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E40" s="16" t="n">
+      <c r="E40" s="17" t="n">
         <f aca="false">IF($A40="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L40,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F40" s="17" t="n">
+      <c r="F40" s="18" t="n">
         <f aca="false">IF($A40="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L40))</f>
         <v>0</v>
       </c>
-      <c r="G40" s="17" t="n">
+      <c r="G40" s="18" t="n">
         <f aca="false">IF($A40="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L40))</f>
         <v>0</v>
       </c>
-      <c r="H40" s="18" t="n">
+      <c r="H40" s="19" t="n">
         <f aca="false">IF($A40="","",$C40+$F40-$G40)</f>
         <v>18</v>
       </c>
-      <c r="I40" s="19"/>
-      <c r="J40" s="20" t="str">
-        <f aca="false">IF($I40="","",$H40*$I40)</f>
-        <v/>
-      </c>
-      <c r="L40" s="21" t="str">
+      <c r="I40" s="20"/>
+      <c r="J40" s="21" t="str">
+        <f aca="false">IF(OR($A40="",$I40="",$C$4=""),"",$H40*$I40*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L40" s="22" t="str">
         <f aca="false">IF($A40="","",$A40&amp;" - "&amp;$B40)</f>
         <v>AMF Brand - PUD PVN 300/500</v>
       </c>
-      <c r="M40" s="21" t="n">
+      <c r="M40" s="22" t="n">
         <f aca="false">IF($A40="",0,IF(OR($D40&lt;&gt;0,$E40&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N40" s="21" t="str">
+      <c r="N40" s="22" t="str">
         <f aca="false">IF($M40=1,SUM($M$8:$M40),"")</f>
         <v/>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="B41" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="24" t="n">
+      <c r="A41" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B41" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C41" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="25" t="n">
         <f aca="false">IF($A41="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L41,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E41" s="24" t="n">
+      <c r="E41" s="25" t="n">
         <f aca="false">IF($A41="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L41,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F41" s="25" t="n">
+      <c r="F41" s="26" t="n">
         <f aca="false">IF($A41="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L41))</f>
         <v>0</v>
       </c>
-      <c r="G41" s="25" t="n">
+      <c r="G41" s="26" t="n">
         <f aca="false">IF($A41="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L41))</f>
         <v>0</v>
       </c>
-      <c r="H41" s="26" t="n">
+      <c r="H41" s="27" t="n">
         <f aca="false">IF($A41="","",$C41+$F41-$G41)</f>
         <v>0</v>
       </c>
-      <c r="I41" s="19"/>
-      <c r="J41" s="27" t="str">
-        <f aca="false">IF($I41="","",$H41*$I41)</f>
-        <v/>
-      </c>
-      <c r="L41" s="21" t="str">
+      <c r="I41" s="20"/>
+      <c r="J41" s="28" t="str">
+        <f aca="false">IF(OR($A41="",$I41="",$C$4=""),"",$H41*$I41*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L41" s="22" t="str">
         <f aca="false">IF($A41="","",$A41&amp;" - "&amp;$B41)</f>
         <v>AMF Brand - PUD KKD 300/500</v>
       </c>
-      <c r="M41" s="21" t="n">
+      <c r="M41" s="22" t="n">
         <f aca="false">IF($A41="",0,IF(OR($D41&lt;&gt;0,$E41&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N41" s="21" t="str">
+      <c r="N41" s="22" t="str">
         <f aca="false">IF($M41=1,SUM($M$8:$M41),"")</f>
         <v/>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C42" s="15" t="n">
+      <c r="A42" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C42" s="16" t="n">
         <v>1389</v>
       </c>
-      <c r="D42" s="16" t="n">
+      <c r="D42" s="17" t="n">
         <f aca="false">IF($A42="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L42,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>1872</v>
       </c>
-      <c r="E42" s="16" t="n">
+      <c r="E42" s="17" t="n">
         <f aca="false">IF($A42="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L42,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F42" s="17" t="n">
+      <c r="F42" s="18" t="n">
         <f aca="false">IF($A42="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L42))</f>
         <v>1872</v>
       </c>
-      <c r="G42" s="17" t="n">
+      <c r="G42" s="18" t="n">
         <f aca="false">IF($A42="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L42))</f>
         <v>0</v>
       </c>
-      <c r="H42" s="18" t="n">
+      <c r="H42" s="19" t="n">
         <f aca="false">IF($A42="","",$C42+$F42-$G42)</f>
         <v>3261</v>
       </c>
-      <c r="I42" s="19"/>
-      <c r="J42" s="20" t="str">
-        <f aca="false">IF($I42="","",$H42*$I42)</f>
-        <v/>
-      </c>
-      <c r="L42" s="21" t="str">
+      <c r="I42" s="20"/>
+      <c r="J42" s="21" t="str">
+        <f aca="false">IF(OR($A42="",$I42="",$C$4=""),"",$H42*$I42*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L42" s="22" t="str">
         <f aca="false">IF($A42="","",$A42&amp;" - "&amp;$B42)</f>
         <v>THT Brand - PUD PVN 80/120</v>
       </c>
-      <c r="M42" s="21" t="n">
+      <c r="M42" s="22" t="n">
         <f aca="false">IF($A42="",0,IF(OR($D42&lt;&gt;0,$E42&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
-      <c r="N42" s="21" t="n">
+      <c r="N42" s="22" t="n">
         <f aca="false">IF($M42=1,SUM($M$8:$M42),"")</f>
         <v>13</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="B43" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C43" s="23" t="n">
+      <c r="A43" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C43" s="24" t="n">
         <v>7055</v>
       </c>
-      <c r="D43" s="24" t="n">
+      <c r="D43" s="25" t="n">
         <f aca="false">IF($A43="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L43,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>600</v>
       </c>
-      <c r="E43" s="24" t="n">
+      <c r="E43" s="25" t="n">
         <f aca="false">IF($A43="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L43,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F43" s="25" t="n">
+      <c r="F43" s="26" t="n">
         <f aca="false">IF($A43="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L43))</f>
         <v>600</v>
       </c>
-      <c r="G43" s="25" t="n">
+      <c r="G43" s="26" t="n">
         <f aca="false">IF($A43="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L43))</f>
         <v>0</v>
       </c>
-      <c r="H43" s="26" t="n">
+      <c r="H43" s="27" t="n">
         <f aca="false">IF($A43="","",$C43+$F43-$G43)</f>
         <v>7655</v>
       </c>
-      <c r="I43" s="19"/>
-      <c r="J43" s="27" t="str">
-        <f aca="false">IF($I43="","",$H43*$I43)</f>
-        <v/>
-      </c>
-      <c r="L43" s="21" t="str">
+      <c r="I43" s="20"/>
+      <c r="J43" s="28" t="str">
+        <f aca="false">IF(OR($A43="",$I43="",$C$4=""),"",$H43*$I43*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L43" s="22" t="str">
         <f aca="false">IF($A43="","",$A43&amp;" - "&amp;$B43)</f>
         <v>THT Brand - PUD PVN 100/200</v>
       </c>
-      <c r="M43" s="21" t="n">
+      <c r="M43" s="22" t="n">
         <f aca="false">IF($A43="",0,IF(OR($D43&lt;&gt;0,$E43&lt;&gt;0),1,0))</f>
         <v>1</v>
       </c>
-      <c r="N43" s="21" t="n">
+      <c r="N43" s="22" t="n">
         <f aca="false">IF($M43=1,SUM($M$8:$M43),"")</f>
         <v>14</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="B44" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C44" s="15" t="n">
+      <c r="A44" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" s="16" t="n">
         <v>4682</v>
       </c>
-      <c r="D44" s="16" t="n">
+      <c r="D44" s="17" t="n">
         <f aca="false">IF($A44="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L44,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E44" s="16" t="n">
+      <c r="E44" s="17" t="n">
         <f aca="false">IF($A44="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L44,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F44" s="17" t="n">
+      <c r="F44" s="18" t="n">
         <f aca="false">IF($A44="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L44))</f>
         <v>0</v>
       </c>
-      <c r="G44" s="17" t="n">
+      <c r="G44" s="18" t="n">
         <f aca="false">IF($A44="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L44))</f>
         <v>0</v>
       </c>
-      <c r="H44" s="18" t="n">
+      <c r="H44" s="19" t="n">
         <f aca="false">IF($A44="","",$C44+$F44-$G44)</f>
         <v>4682</v>
       </c>
-      <c r="I44" s="19"/>
-      <c r="J44" s="20" t="str">
-        <f aca="false">IF($I44="","",$H44*$I44)</f>
-        <v/>
-      </c>
-      <c r="L44" s="21" t="str">
+      <c r="I44" s="20"/>
+      <c r="J44" s="21" t="str">
+        <f aca="false">IF(OR($A44="",$I44="",$C$4=""),"",$H44*$I44*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L44" s="22" t="str">
         <f aca="false">IF($A44="","",$A44&amp;" - "&amp;$B44)</f>
         <v>THT Brand - PUD PVN 200/300</v>
       </c>
-      <c r="M44" s="21" t="n">
+      <c r="M44" s="22" t="n">
         <f aca="false">IF($A44="",0,IF(OR($D44&lt;&gt;0,$E44&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N44" s="21" t="str">
+      <c r="N44" s="22" t="str">
         <f aca="false">IF($M44=1,SUM($M$8:$M44),"")</f>
         <v/>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="B45" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C45" s="23" t="n">
+      <c r="A45" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="B45" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45" s="24" t="n">
         <v>670</v>
       </c>
-      <c r="D45" s="24" t="n">
+      <c r="D45" s="25" t="n">
         <f aca="false">IF($A45="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L45,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E45" s="24" t="n">
+      <c r="E45" s="25" t="n">
         <f aca="false">IF($A45="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L45,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F45" s="25" t="n">
+      <c r="F45" s="26" t="n">
         <f aca="false">IF($A45="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L45))</f>
         <v>0</v>
       </c>
-      <c r="G45" s="25" t="n">
+      <c r="G45" s="26" t="n">
         <f aca="false">IF($A45="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L45))</f>
         <v>0</v>
       </c>
-      <c r="H45" s="26" t="n">
+      <c r="H45" s="27" t="n">
         <f aca="false">IF($A45="","",$C45+$F45-$G45)</f>
         <v>670</v>
       </c>
-      <c r="I45" s="19"/>
-      <c r="J45" s="27" t="str">
-        <f aca="false">IF($I45="","",$H45*$I45)</f>
-        <v/>
-      </c>
-      <c r="L45" s="21" t="str">
+      <c r="I45" s="20"/>
+      <c r="J45" s="28" t="str">
+        <f aca="false">IF(OR($A45="",$I45="",$C$4=""),"",$H45*$I45*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L45" s="22" t="str">
         <f aca="false">IF($A45="","",$A45&amp;" - "&amp;$B45)</f>
         <v>Deepsea - 300/500</v>
       </c>
-      <c r="M45" s="21" t="n">
+      <c r="M45" s="22" t="n">
         <f aca="false">IF($A45="",0,IF(OR($D45&lt;&gt;0,$E45&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N45" s="21" t="str">
+      <c r="N45" s="22" t="str">
         <f aca="false">IF($M45=1,SUM($M$8:$M45),"")</f>
         <v/>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="B46" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C46" s="15" t="n">
+      <c r="A46" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C46" s="16" t="n">
         <v>451</v>
       </c>
-      <c r="D46" s="16" t="n">
+      <c r="D46" s="17" t="n">
         <f aca="false">IF($A46="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L46,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E46" s="16" t="n">
+      <c r="E46" s="17" t="n">
         <f aca="false">IF($A46="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L46,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F46" s="17" t="n">
+      <c r="F46" s="18" t="n">
         <f aca="false">IF($A46="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L46))</f>
         <v>0</v>
       </c>
-      <c r="G46" s="17" t="n">
+      <c r="G46" s="18" t="n">
         <f aca="false">IF($A46="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L46))</f>
         <v>0</v>
       </c>
-      <c r="H46" s="18" t="n">
+      <c r="H46" s="19" t="n">
         <f aca="false">IF($A46="","",$C46+$F46-$G46)</f>
         <v>451</v>
       </c>
-      <c r="I46" s="19"/>
-      <c r="J46" s="20" t="str">
-        <f aca="false">IF($I46="","",$H46*$I46)</f>
-        <v/>
-      </c>
-      <c r="L46" s="21" t="str">
+      <c r="I46" s="20"/>
+      <c r="J46" s="21" t="str">
+        <f aca="false">IF(OR($A46="",$I46="",$C$4=""),"",$H46*$I46*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L46" s="22" t="str">
         <f aca="false">IF($A46="","",$A46&amp;" - "&amp;$B46)</f>
         <v>China - PUD PVN 300/500</v>
       </c>
-      <c r="M46" s="21" t="n">
+      <c r="M46" s="22" t="n">
         <f aca="false">IF($A46="",0,IF(OR($D46&lt;&gt;0,$E46&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N46" s="21" t="str">
+      <c r="N46" s="22" t="str">
         <f aca="false">IF($M46=1,SUM($M$8:$M46),"")</f>
         <v/>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="B47" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C47" s="23" t="n">
+      <c r="A47" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="B47" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C47" s="24" t="n">
         <v>188</v>
       </c>
-      <c r="D47" s="24" t="n">
+      <c r="D47" s="25" t="n">
         <f aca="false">IF($A47="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L47,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E47" s="24" t="n">
+      <c r="E47" s="25" t="n">
         <f aca="false">IF($A47="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L47,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F47" s="25" t="n">
+      <c r="F47" s="26" t="n">
         <f aca="false">IF($A47="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L47))</f>
         <v>0</v>
       </c>
-      <c r="G47" s="25" t="n">
+      <c r="G47" s="26" t="n">
         <f aca="false">IF($A47="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L47))</f>
         <v>0</v>
       </c>
-      <c r="H47" s="26" t="n">
+      <c r="H47" s="27" t="n">
         <f aca="false">IF($A47="","",$C47+$F47-$G47)</f>
         <v>188</v>
       </c>
-      <c r="I47" s="19"/>
-      <c r="J47" s="27" t="str">
-        <f aca="false">IF($I47="","",$H47*$I47)</f>
-        <v/>
-      </c>
-      <c r="L47" s="21" t="str">
+      <c r="I47" s="20"/>
+      <c r="J47" s="28" t="str">
+        <f aca="false">IF(OR($A47="",$I47="",$C$4=""),"",$H47*$I47*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L47" s="22" t="str">
         <f aca="false">IF($A47="","",$A47&amp;" - "&amp;$B47)</f>
         <v>China - PUD KKD 300/500</v>
       </c>
-      <c r="M47" s="21" t="n">
+      <c r="M47" s="22" t="n">
         <f aca="false">IF($A47="",0,IF(OR($D47&lt;&gt;0,$E47&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N47" s="21" t="str">
+      <c r="N47" s="22" t="str">
         <f aca="false">IF($M47=1,SUM($M$8:$M47),"")</f>
         <v/>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="B48" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="C48" s="15" t="n">
+      <c r="A48" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48" s="16" t="n">
         <v>401</v>
       </c>
-      <c r="D48" s="16" t="n">
+      <c r="D48" s="17" t="n">
         <f aca="false">IF($A48="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L48,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E48" s="16" t="n">
+      <c r="E48" s="17" t="n">
         <f aca="false">IF($A48="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L48,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F48" s="17" t="n">
+      <c r="F48" s="18" t="n">
         <f aca="false">IF($A48="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L48))</f>
         <v>0</v>
       </c>
-      <c r="G48" s="17" t="n">
+      <c r="G48" s="18" t="n">
         <f aca="false">IF($A48="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L48))</f>
         <v>0</v>
       </c>
-      <c r="H48" s="18" t="n">
+      <c r="H48" s="19" t="n">
         <f aca="false">IF($A48="","",$C48+$F48-$G48)</f>
         <v>401</v>
       </c>
-      <c r="I48" s="19"/>
-      <c r="J48" s="20" t="str">
-        <f aca="false">IF($I48="","",$H48*$I48)</f>
-        <v/>
-      </c>
-      <c r="L48" s="21" t="str">
+      <c r="I48" s="20"/>
+      <c r="J48" s="21" t="str">
+        <f aca="false">IF(OR($A48="",$I48="",$C$4=""),"",$H48*$I48*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L48" s="22" t="str">
         <f aca="false">IF($A48="","",$A48&amp;" - "&amp;$B48)</f>
         <v>China - PUD PVN 500/800</v>
       </c>
-      <c r="M48" s="21" t="n">
+      <c r="M48" s="22" t="n">
         <f aca="false">IF($A48="",0,IF(OR($D48&lt;&gt;0,$E48&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N48" s="21" t="str">
+      <c r="N48" s="22" t="str">
         <f aca="false">IF($M48=1,SUM($M$8:$M48),"")</f>
         <v/>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="B49" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C49" s="23" t="n">
+      <c r="A49" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="C49" s="24" t="n">
         <v>1920</v>
       </c>
-      <c r="D49" s="24" t="n">
+      <c r="D49" s="25" t="n">
         <f aca="false">IF($A49="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L49,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="E49" s="24" t="n">
+      <c r="E49" s="25" t="n">
         <f aca="false">IF($A49="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L49,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v>0</v>
       </c>
-      <c r="F49" s="25" t="n">
+      <c r="F49" s="26" t="n">
         <f aca="false">IF($A49="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L49))</f>
         <v>0</v>
       </c>
-      <c r="G49" s="25" t="n">
+      <c r="G49" s="26" t="n">
         <f aca="false">IF($A49="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L49))</f>
         <v>0</v>
       </c>
-      <c r="H49" s="26" t="n">
+      <c r="H49" s="27" t="n">
         <f aca="false">IF($A49="","",$C49+$F49-$G49)</f>
         <v>1920</v>
       </c>
-      <c r="I49" s="19"/>
-      <c r="J49" s="27" t="str">
-        <f aca="false">IF($I49="","",$H49*$I49)</f>
-        <v/>
-      </c>
-      <c r="L49" s="21" t="str">
+      <c r="I49" s="20"/>
+      <c r="J49" s="28" t="str">
+        <f aca="false">IF(OR($A49="",$I49="",$C$4=""),"",$H49*$I49*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L49" s="22" t="str">
         <f aca="false">IF($A49="","",$A49&amp;" - "&amp;$B49)</f>
         <v>China - PUD KKD 500/800</v>
       </c>
-      <c r="M49" s="21" t="n">
+      <c r="M49" s="22" t="n">
         <f aca="false">IF($A49="",0,IF(OR($D49&lt;&gt;0,$E49&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N49" s="21" t="str">
+      <c r="N49" s="22" t="str">
         <f aca="false">IF($M49=1,SUM($M$8:$M49),"")</f>
         <v/>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="28"/>
-      <c r="B50" s="28"/>
-      <c r="C50" s="29"/>
-      <c r="D50" s="16" t="str">
+      <c r="A50" s="29"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="17" t="str">
         <f aca="false">IF($A50="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L50,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="E50" s="16" t="str">
+      <c r="E50" s="17" t="str">
         <f aca="false">IF($A50="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L50,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="F50" s="17" t="str">
+      <c r="F50" s="18" t="str">
         <f aca="false">IF($A50="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L50))</f>
         <v/>
       </c>
-      <c r="G50" s="17" t="str">
+      <c r="G50" s="18" t="str">
         <f aca="false">IF($A50="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L50))</f>
         <v/>
       </c>
-      <c r="H50" s="18" t="str">
+      <c r="H50" s="19" t="str">
         <f aca="false">IF($A50="","",$C50+$F50-$G50)</f>
         <v/>
       </c>
-      <c r="I50" s="19"/>
-      <c r="J50" s="20" t="str">
-        <f aca="false">IF($I50="","",$H50*$I50)</f>
-        <v/>
-      </c>
-      <c r="L50" s="21" t="str">
+      <c r="I50" s="20"/>
+      <c r="J50" s="21" t="str">
+        <f aca="false">IF(OR($A50="",$I50="",$C$4=""),"",$H50*$I50*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L50" s="22" t="str">
         <f aca="false">IF($A50="","",$A50&amp;" - "&amp;$B50)</f>
         <v/>
       </c>
-      <c r="M50" s="21" t="n">
+      <c r="M50" s="22" t="n">
         <f aca="false">IF($A50="",0,IF(OR($D50&lt;&gt;0,$E50&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N50" s="21" t="str">
+      <c r="N50" s="22" t="str">
         <f aca="false">IF($M50=1,SUM($M$8:$M50),"")</f>
         <v/>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="30"/>
-      <c r="B51" s="30"/>
-      <c r="C51" s="31"/>
-      <c r="D51" s="24" t="str">
+      <c r="A51" s="31"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="25" t="str">
         <f aca="false">IF($A51="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L51,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="E51" s="24" t="str">
+      <c r="E51" s="25" t="str">
         <f aca="false">IF($A51="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L51,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="F51" s="25" t="str">
+      <c r="F51" s="26" t="str">
         <f aca="false">IF($A51="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L51))</f>
         <v/>
       </c>
-      <c r="G51" s="25" t="str">
+      <c r="G51" s="26" t="str">
         <f aca="false">IF($A51="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L51))</f>
         <v/>
       </c>
-      <c r="H51" s="26" t="str">
+      <c r="H51" s="27" t="str">
         <f aca="false">IF($A51="","",$C51+$F51-$G51)</f>
         <v/>
       </c>
-      <c r="I51" s="19"/>
-      <c r="J51" s="27" t="str">
-        <f aca="false">IF($I51="","",$H51*$I51)</f>
-        <v/>
-      </c>
-      <c r="L51" s="21" t="str">
+      <c r="I51" s="20"/>
+      <c r="J51" s="28" t="str">
+        <f aca="false">IF(OR($A51="",$I51="",$C$4=""),"",$H51*$I51*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L51" s="22" t="str">
         <f aca="false">IF($A51="","",$A51&amp;" - "&amp;$B51)</f>
         <v/>
       </c>
-      <c r="M51" s="21" t="n">
+      <c r="M51" s="22" t="n">
         <f aca="false">IF($A51="",0,IF(OR($D51&lt;&gt;0,$E51&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N51" s="21" t="str">
+      <c r="N51" s="22" t="str">
         <f aca="false">IF($M51=1,SUM($M$8:$M51),"")</f>
         <v/>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="28"/>
-      <c r="B52" s="28"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="16" t="str">
+      <c r="A52" s="29"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="17" t="str">
         <f aca="false">IF($A52="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L52,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="E52" s="16" t="str">
+      <c r="E52" s="17" t="str">
         <f aca="false">IF($A52="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L52,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="F52" s="17" t="str">
+      <c r="F52" s="18" t="str">
         <f aca="false">IF($A52="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L52))</f>
         <v/>
       </c>
-      <c r="G52" s="17" t="str">
+      <c r="G52" s="18" t="str">
         <f aca="false">IF($A52="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L52))</f>
         <v/>
       </c>
-      <c r="H52" s="18" t="str">
+      <c r="H52" s="19" t="str">
         <f aca="false">IF($A52="","",$C52+$F52-$G52)</f>
         <v/>
       </c>
-      <c r="I52" s="19"/>
-      <c r="J52" s="20" t="str">
-        <f aca="false">IF($I52="","",$H52*$I52)</f>
-        <v/>
-      </c>
-      <c r="L52" s="21" t="str">
+      <c r="I52" s="20"/>
+      <c r="J52" s="21" t="str">
+        <f aca="false">IF(OR($A52="",$I52="",$C$4=""),"",$H52*$I52*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L52" s="22" t="str">
         <f aca="false">IF($A52="","",$A52&amp;" - "&amp;$B52)</f>
         <v/>
       </c>
-      <c r="M52" s="21" t="n">
+      <c r="M52" s="22" t="n">
         <f aca="false">IF($A52="",0,IF(OR($D52&lt;&gt;0,$E52&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N52" s="21" t="str">
+      <c r="N52" s="22" t="str">
         <f aca="false">IF($M52=1,SUM($M$8:$M52),"")</f>
         <v/>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="30"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="24" t="str">
+      <c r="A53" s="31"/>
+      <c r="B53" s="31"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="25" t="str">
         <f aca="false">IF($A53="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L53,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="E53" s="24" t="str">
+      <c r="E53" s="25" t="str">
         <f aca="false">IF($A53="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L53,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="F53" s="25" t="str">
+      <c r="F53" s="26" t="str">
         <f aca="false">IF($A53="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L53))</f>
         <v/>
       </c>
-      <c r="G53" s="25" t="str">
+      <c r="G53" s="26" t="str">
         <f aca="false">IF($A53="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L53))</f>
         <v/>
       </c>
-      <c r="H53" s="26" t="str">
+      <c r="H53" s="27" t="str">
         <f aca="false">IF($A53="","",$C53+$F53-$G53)</f>
         <v/>
       </c>
-      <c r="I53" s="19"/>
-      <c r="J53" s="27" t="str">
-        <f aca="false">IF($I53="","",$H53*$I53)</f>
-        <v/>
-      </c>
-      <c r="L53" s="21" t="str">
+      <c r="I53" s="20"/>
+      <c r="J53" s="28" t="str">
+        <f aca="false">IF(OR($A53="",$I53="",$C$4=""),"",$H53*$I53*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L53" s="22" t="str">
         <f aca="false">IF($A53="","",$A53&amp;" - "&amp;$B53)</f>
         <v/>
       </c>
-      <c r="M53" s="21" t="n">
+      <c r="M53" s="22" t="n">
         <f aca="false">IF($A53="",0,IF(OR($D53&lt;&gt;0,$E53&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N53" s="21" t="str">
+      <c r="N53" s="22" t="str">
         <f aca="false">IF($M53=1,SUM($M$8:$M53),"")</f>
         <v/>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="28"/>
-      <c r="B54" s="28"/>
-      <c r="C54" s="29"/>
-      <c r="D54" s="16" t="str">
+      <c r="A54" s="29"/>
+      <c r="B54" s="29"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="17" t="str">
         <f aca="false">IF($A54="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L54,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="E54" s="16" t="str">
+      <c r="E54" s="17" t="str">
         <f aca="false">IF($A54="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L54,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="F54" s="17" t="str">
+      <c r="F54" s="18" t="str">
         <f aca="false">IF($A54="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L54))</f>
         <v/>
       </c>
-      <c r="G54" s="17" t="str">
+      <c r="G54" s="18" t="str">
         <f aca="false">IF($A54="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L54))</f>
         <v/>
       </c>
-      <c r="H54" s="18" t="str">
+      <c r="H54" s="19" t="str">
         <f aca="false">IF($A54="","",$C54+$F54-$G54)</f>
         <v/>
       </c>
-      <c r="I54" s="19"/>
-      <c r="J54" s="20" t="str">
-        <f aca="false">IF($I54="","",$H54*$I54)</f>
-        <v/>
-      </c>
-      <c r="L54" s="21" t="str">
+      <c r="I54" s="20"/>
+      <c r="J54" s="21" t="str">
+        <f aca="false">IF(OR($A54="",$I54="",$C$4=""),"",$H54*$I54*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L54" s="22" t="str">
         <f aca="false">IF($A54="","",$A54&amp;" - "&amp;$B54)</f>
         <v/>
       </c>
-      <c r="M54" s="21" t="n">
+      <c r="M54" s="22" t="n">
         <f aca="false">IF($A54="",0,IF(OR($D54&lt;&gt;0,$E54&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N54" s="21" t="str">
+      <c r="N54" s="22" t="str">
         <f aca="false">IF($M54=1,SUM($M$8:$M54),"")</f>
         <v/>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="30"/>
-      <c r="B55" s="30"/>
-      <c r="C55" s="31"/>
-      <c r="D55" s="24" t="str">
+      <c r="A55" s="31"/>
+      <c r="B55" s="31"/>
+      <c r="C55" s="32"/>
+      <c r="D55" s="25" t="str">
         <f aca="false">IF($A55="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L55,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="E55" s="24" t="str">
+      <c r="E55" s="25" t="str">
         <f aca="false">IF($A55="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L55,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="F55" s="25" t="str">
+      <c r="F55" s="26" t="str">
         <f aca="false">IF($A55="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L55))</f>
         <v/>
       </c>
-      <c r="G55" s="25" t="str">
+      <c r="G55" s="26" t="str">
         <f aca="false">IF($A55="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L55))</f>
         <v/>
       </c>
-      <c r="H55" s="26" t="str">
+      <c r="H55" s="27" t="str">
         <f aca="false">IF($A55="","",$C55+$F55-$G55)</f>
         <v/>
       </c>
-      <c r="I55" s="19"/>
-      <c r="J55" s="27" t="str">
-        <f aca="false">IF($I55="","",$H55*$I55)</f>
-        <v/>
-      </c>
-      <c r="L55" s="21" t="str">
+      <c r="I55" s="20"/>
+      <c r="J55" s="28" t="str">
+        <f aca="false">IF(OR($A55="",$I55="",$C$4=""),"",$H55*$I55*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L55" s="22" t="str">
         <f aca="false">IF($A55="","",$A55&amp;" - "&amp;$B55)</f>
         <v/>
       </c>
-      <c r="M55" s="21" t="n">
+      <c r="M55" s="22" t="n">
         <f aca="false">IF($A55="",0,IF(OR($D55&lt;&gt;0,$E55&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N55" s="21" t="str">
+      <c r="N55" s="22" t="str">
         <f aca="false">IF($M55=1,SUM($M$8:$M55),"")</f>
         <v/>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="28"/>
-      <c r="B56" s="28"/>
-      <c r="C56" s="29"/>
-      <c r="D56" s="16" t="str">
+      <c r="A56" s="29"/>
+      <c r="B56" s="29"/>
+      <c r="C56" s="30"/>
+      <c r="D56" s="17" t="str">
         <f aca="false">IF($A56="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L56,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="E56" s="16" t="str">
+      <c r="E56" s="17" t="str">
         <f aca="false">IF($A56="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L56,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="F56" s="17" t="str">
+      <c r="F56" s="18" t="str">
         <f aca="false">IF($A56="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L56))</f>
         <v/>
       </c>
-      <c r="G56" s="17" t="str">
+      <c r="G56" s="18" t="str">
         <f aca="false">IF($A56="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L56))</f>
         <v/>
       </c>
-      <c r="H56" s="18" t="str">
+      <c r="H56" s="19" t="str">
         <f aca="false">IF($A56="","",$C56+$F56-$G56)</f>
         <v/>
       </c>
-      <c r="I56" s="19"/>
-      <c r="J56" s="20" t="str">
-        <f aca="false">IF($I56="","",$H56*$I56)</f>
-        <v/>
-      </c>
-      <c r="L56" s="21" t="str">
+      <c r="I56" s="20"/>
+      <c r="J56" s="21" t="str">
+        <f aca="false">IF(OR($A56="",$I56="",$C$4=""),"",$H56*$I56*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L56" s="22" t="str">
         <f aca="false">IF($A56="","",$A56&amp;" - "&amp;$B56)</f>
         <v/>
       </c>
-      <c r="M56" s="21" t="n">
+      <c r="M56" s="22" t="n">
         <f aca="false">IF($A56="",0,IF(OR($D56&lt;&gt;0,$E56&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N56" s="21" t="str">
+      <c r="N56" s="22" t="str">
         <f aca="false">IF($M56=1,SUM($M$8:$M56),"")</f>
         <v/>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="30"/>
-      <c r="B57" s="30"/>
-      <c r="C57" s="31"/>
-      <c r="D57" s="24" t="str">
+      <c r="A57" s="31"/>
+      <c r="B57" s="31"/>
+      <c r="C57" s="32"/>
+      <c r="D57" s="25" t="str">
         <f aca="false">IF($A57="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L57,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="E57" s="24" t="str">
+      <c r="E57" s="25" t="str">
         <f aca="false">IF($A57="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L57,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="F57" s="25" t="str">
+      <c r="F57" s="26" t="str">
         <f aca="false">IF($A57="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L57))</f>
         <v/>
       </c>
-      <c r="G57" s="25" t="str">
+      <c r="G57" s="26" t="str">
         <f aca="false">IF($A57="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L57))</f>
         <v/>
       </c>
-      <c r="H57" s="26" t="str">
+      <c r="H57" s="27" t="str">
         <f aca="false">IF($A57="","",$C57+$F57-$G57)</f>
         <v/>
       </c>
-      <c r="I57" s="19"/>
-      <c r="J57" s="27" t="str">
-        <f aca="false">IF($I57="","",$H57*$I57)</f>
-        <v/>
-      </c>
-      <c r="L57" s="21" t="str">
+      <c r="I57" s="20"/>
+      <c r="J57" s="28" t="str">
+        <f aca="false">IF(OR($A57="",$I57="",$C$4=""),"",$H57*$I57*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L57" s="22" t="str">
         <f aca="false">IF($A57="","",$A57&amp;" - "&amp;$B57)</f>
         <v/>
       </c>
-      <c r="M57" s="21" t="n">
+      <c r="M57" s="22" t="n">
         <f aca="false">IF($A57="",0,IF(OR($D57&lt;&gt;0,$E57&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N57" s="21" t="str">
+      <c r="N57" s="22" t="str">
         <f aca="false">IF($M57=1,SUM($M$8:$M57),"")</f>
         <v/>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="28"/>
-      <c r="B58" s="28"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="16" t="str">
+      <c r="A58" s="29"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="17" t="str">
         <f aca="false">IF($A58="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L58,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="E58" s="16" t="str">
+      <c r="E58" s="17" t="str">
         <f aca="false">IF($A58="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L58,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="F58" s="17" t="str">
+      <c r="F58" s="18" t="str">
         <f aca="false">IF($A58="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L58))</f>
         <v/>
       </c>
-      <c r="G58" s="17" t="str">
+      <c r="G58" s="18" t="str">
         <f aca="false">IF($A58="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L58))</f>
         <v/>
       </c>
-      <c r="H58" s="18" t="str">
+      <c r="H58" s="19" t="str">
         <f aca="false">IF($A58="","",$C58+$F58-$G58)</f>
         <v/>
       </c>
-      <c r="I58" s="19"/>
-      <c r="J58" s="20" t="str">
-        <f aca="false">IF($I58="","",$H58*$I58)</f>
-        <v/>
-      </c>
-      <c r="L58" s="21" t="str">
+      <c r="I58" s="20"/>
+      <c r="J58" s="21" t="str">
+        <f aca="false">IF(OR($A58="",$I58="",$C$4=""),"",$H58*$I58*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L58" s="22" t="str">
         <f aca="false">IF($A58="","",$A58&amp;" - "&amp;$B58)</f>
         <v/>
       </c>
-      <c r="M58" s="21" t="n">
+      <c r="M58" s="22" t="n">
         <f aca="false">IF($A58="",0,IF(OR($D58&lt;&gt;0,$E58&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N58" s="21" t="str">
+      <c r="N58" s="22" t="str">
         <f aca="false">IF($M58=1,SUM($M$8:$M58),"")</f>
         <v/>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="30"/>
-      <c r="B59" s="30"/>
-      <c r="C59" s="31"/>
-      <c r="D59" s="24" t="str">
+      <c r="A59" s="31"/>
+      <c r="B59" s="31"/>
+      <c r="C59" s="32"/>
+      <c r="D59" s="25" t="str">
         <f aca="false">IF($A59="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L59,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="E59" s="24" t="str">
+      <c r="E59" s="25" t="str">
         <f aca="false">IF($A59="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L59,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="F59" s="25" t="str">
+      <c r="F59" s="26" t="str">
         <f aca="false">IF($A59="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L59))</f>
         <v/>
       </c>
-      <c r="G59" s="25" t="str">
+      <c r="G59" s="26" t="str">
         <f aca="false">IF($A59="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L59))</f>
         <v/>
       </c>
-      <c r="H59" s="26" t="str">
+      <c r="H59" s="27" t="str">
         <f aca="false">IF($A59="","",$C59+$F59-$G59)</f>
         <v/>
       </c>
-      <c r="I59" s="19"/>
-      <c r="J59" s="27" t="str">
-        <f aca="false">IF($I59="","",$H59*$I59)</f>
-        <v/>
-      </c>
-      <c r="L59" s="21" t="str">
+      <c r="I59" s="20"/>
+      <c r="J59" s="28" t="str">
+        <f aca="false">IF(OR($A59="",$I59="",$C$4=""),"",$H59*$I59*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L59" s="22" t="str">
         <f aca="false">IF($A59="","",$A59&amp;" - "&amp;$B59)</f>
         <v/>
       </c>
-      <c r="M59" s="21" t="n">
+      <c r="M59" s="22" t="n">
         <f aca="false">IF($A59="",0,IF(OR($D59&lt;&gt;0,$E59&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N59" s="21" t="str">
+      <c r="N59" s="22" t="str">
         <f aca="false">IF($M59=1,SUM($M$8:$M59),"")</f>
         <v/>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="28"/>
-      <c r="B60" s="28"/>
-      <c r="C60" s="29"/>
-      <c r="D60" s="16" t="str">
+      <c r="A60" s="29"/>
+      <c r="B60" s="29"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="17" t="str">
         <f aca="false">IF($A60="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L60,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="E60" s="16" t="str">
+      <c r="E60" s="17" t="str">
         <f aca="false">IF($A60="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L60,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="F60" s="17" t="str">
+      <c r="F60" s="18" t="str">
         <f aca="false">IF($A60="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L60))</f>
         <v/>
       </c>
-      <c r="G60" s="17" t="str">
+      <c r="G60" s="18" t="str">
         <f aca="false">IF($A60="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L60))</f>
         <v/>
       </c>
-      <c r="H60" s="18" t="str">
+      <c r="H60" s="19" t="str">
         <f aca="false">IF($A60="","",$C60+$F60-$G60)</f>
         <v/>
       </c>
-      <c r="I60" s="19"/>
-      <c r="J60" s="20" t="str">
-        <f aca="false">IF($I60="","",$H60*$I60)</f>
-        <v/>
-      </c>
-      <c r="L60" s="21" t="str">
+      <c r="I60" s="20"/>
+      <c r="J60" s="21" t="str">
+        <f aca="false">IF(OR($A60="",$I60="",$C$4=""),"",$H60*$I60*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L60" s="22" t="str">
         <f aca="false">IF($A60="","",$A60&amp;" - "&amp;$B60)</f>
         <v/>
       </c>
-      <c r="M60" s="21" t="n">
+      <c r="M60" s="22" t="n">
         <f aca="false">IF($A60="",0,IF(OR($D60&lt;&gt;0,$E60&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N60" s="21" t="str">
+      <c r="N60" s="22" t="str">
         <f aca="false">IF($M60=1,SUM($M$8:$M60),"")</f>
         <v/>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="30"/>
-      <c r="B61" s="30"/>
-      <c r="C61" s="31"/>
-      <c r="D61" s="24" t="str">
+      <c r="A61" s="31"/>
+      <c r="B61" s="31"/>
+      <c r="C61" s="32"/>
+      <c r="D61" s="25" t="str">
         <f aca="false">IF($A61="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L61,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="E61" s="24" t="str">
+      <c r="E61" s="25" t="str">
         <f aca="false">IF($A61="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L61,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="F61" s="25" t="str">
+      <c r="F61" s="26" t="str">
         <f aca="false">IF($A61="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L61))</f>
         <v/>
       </c>
-      <c r="G61" s="25" t="str">
+      <c r="G61" s="26" t="str">
         <f aca="false">IF($A61="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L61))</f>
         <v/>
       </c>
-      <c r="H61" s="26" t="str">
+      <c r="H61" s="27" t="str">
         <f aca="false">IF($A61="","",$C61+$F61-$G61)</f>
         <v/>
       </c>
-      <c r="I61" s="19"/>
-      <c r="J61" s="27" t="str">
-        <f aca="false">IF($I61="","",$H61*$I61)</f>
-        <v/>
-      </c>
-      <c r="L61" s="21" t="str">
+      <c r="I61" s="20"/>
+      <c r="J61" s="28" t="str">
+        <f aca="false">IF(OR($A61="",$I61="",$C$4=""),"",$H61*$I61*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L61" s="22" t="str">
         <f aca="false">IF($A61="","",$A61&amp;" - "&amp;$B61)</f>
         <v/>
       </c>
-      <c r="M61" s="21" t="n">
+      <c r="M61" s="22" t="n">
         <f aca="false">IF($A61="",0,IF(OR($D61&lt;&gt;0,$E61&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N61" s="21" t="str">
+      <c r="N61" s="22" t="str">
         <f aca="false">IF($M61=1,SUM($M$8:$M61),"")</f>
         <v/>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="28"/>
-      <c r="B62" s="28"/>
-      <c r="C62" s="29"/>
-      <c r="D62" s="16" t="str">
+      <c r="A62" s="29"/>
+      <c r="B62" s="29"/>
+      <c r="C62" s="30"/>
+      <c r="D62" s="17" t="str">
         <f aca="false">IF($A62="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L62,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="E62" s="16" t="str">
+      <c r="E62" s="17" t="str">
         <f aca="false">IF($A62="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L62,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="F62" s="17" t="str">
+      <c r="F62" s="18" t="str">
         <f aca="false">IF($A62="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L62))</f>
         <v/>
       </c>
-      <c r="G62" s="17" t="str">
+      <c r="G62" s="18" t="str">
         <f aca="false">IF($A62="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L62))</f>
         <v/>
       </c>
-      <c r="H62" s="18" t="str">
+      <c r="H62" s="19" t="str">
         <f aca="false">IF($A62="","",$C62+$F62-$G62)</f>
         <v/>
       </c>
-      <c r="I62" s="19"/>
-      <c r="J62" s="20" t="str">
-        <f aca="false">IF($I62="","",$H62*$I62)</f>
-        <v/>
-      </c>
-      <c r="L62" s="21" t="str">
+      <c r="I62" s="20"/>
+      <c r="J62" s="21" t="str">
+        <f aca="false">IF(OR($A62="",$I62="",$C$4=""),"",$H62*$I62*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L62" s="22" t="str">
         <f aca="false">IF($A62="","",$A62&amp;" - "&amp;$B62)</f>
         <v/>
       </c>
-      <c r="M62" s="21" t="n">
+      <c r="M62" s="22" t="n">
         <f aca="false">IF($A62="",0,IF(OR($D62&lt;&gt;0,$E62&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N62" s="21" t="str">
+      <c r="N62" s="22" t="str">
         <f aca="false">IF($M62=1,SUM($M$8:$M62),"")</f>
         <v/>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="30"/>
-      <c r="B63" s="30"/>
-      <c r="C63" s="31"/>
-      <c r="D63" s="24" t="str">
+      <c r="A63" s="31"/>
+      <c r="B63" s="31"/>
+      <c r="C63" s="32"/>
+      <c r="D63" s="25" t="str">
         <f aca="false">IF($A63="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L63,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="E63" s="24" t="str">
+      <c r="E63" s="25" t="str">
         <f aca="false">IF($A63="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L63,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="F63" s="25" t="str">
+      <c r="F63" s="26" t="str">
         <f aca="false">IF($A63="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L63))</f>
         <v/>
       </c>
-      <c r="G63" s="25" t="str">
+      <c r="G63" s="26" t="str">
         <f aca="false">IF($A63="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L63))</f>
         <v/>
       </c>
-      <c r="H63" s="26" t="str">
+      <c r="H63" s="27" t="str">
         <f aca="false">IF($A63="","",$C63+$F63-$G63)</f>
         <v/>
       </c>
-      <c r="I63" s="19"/>
-      <c r="J63" s="27" t="str">
-        <f aca="false">IF($I63="","",$H63*$I63)</f>
-        <v/>
-      </c>
-      <c r="L63" s="21" t="str">
+      <c r="I63" s="20"/>
+      <c r="J63" s="28" t="str">
+        <f aca="false">IF(OR($A63="",$I63="",$C$4=""),"",$H63*$I63*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L63" s="22" t="str">
         <f aca="false">IF($A63="","",$A63&amp;" - "&amp;$B63)</f>
         <v/>
       </c>
-      <c r="M63" s="21" t="n">
+      <c r="M63" s="22" t="n">
         <f aca="false">IF($A63="",0,IF(OR($D63&lt;&gt;0,$E63&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N63" s="21" t="str">
+      <c r="N63" s="22" t="str">
         <f aca="false">IF($M63=1,SUM($M$8:$M63),"")</f>
         <v/>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="28"/>
-      <c r="B64" s="28"/>
-      <c r="C64" s="29"/>
-      <c r="D64" s="16" t="str">
+      <c r="A64" s="29"/>
+      <c r="B64" s="29"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="17" t="str">
         <f aca="false">IF($A64="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L64,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="E64" s="16" t="str">
+      <c r="E64" s="17" t="str">
         <f aca="false">IF($A64="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L64,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="F64" s="17" t="str">
+      <c r="F64" s="18" t="str">
         <f aca="false">IF($A64="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L64))</f>
         <v/>
       </c>
-      <c r="G64" s="17" t="str">
+      <c r="G64" s="18" t="str">
         <f aca="false">IF($A64="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L64))</f>
         <v/>
       </c>
-      <c r="H64" s="18" t="str">
+      <c r="H64" s="19" t="str">
         <f aca="false">IF($A64="","",$C64+$F64-$G64)</f>
         <v/>
       </c>
-      <c r="I64" s="19"/>
-      <c r="J64" s="20" t="str">
-        <f aca="false">IF($I64="","",$H64*$I64)</f>
-        <v/>
-      </c>
-      <c r="L64" s="21" t="str">
+      <c r="I64" s="20"/>
+      <c r="J64" s="21" t="str">
+        <f aca="false">IF(OR($A64="",$I64="",$C$4=""),"",$H64*$I64*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L64" s="22" t="str">
         <f aca="false">IF($A64="","",$A64&amp;" - "&amp;$B64)</f>
         <v/>
       </c>
-      <c r="M64" s="21" t="n">
+      <c r="M64" s="22" t="n">
         <f aca="false">IF($A64="",0,IF(OR($D64&lt;&gt;0,$E64&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N64" s="21" t="str">
+      <c r="N64" s="22" t="str">
         <f aca="false">IF($M64=1,SUM($M$8:$M64),"")</f>
         <v/>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="30"/>
-      <c r="B65" s="30"/>
-      <c r="C65" s="31"/>
-      <c r="D65" s="24" t="str">
+      <c r="A65" s="31"/>
+      <c r="B65" s="31"/>
+      <c r="C65" s="32"/>
+      <c r="D65" s="25" t="str">
         <f aca="false">IF($A65="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L65,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="E65" s="24" t="str">
+      <c r="E65" s="25" t="str">
         <f aca="false">IF($A65="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L65,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="F65" s="25" t="str">
+      <c r="F65" s="26" t="str">
         <f aca="false">IF($A65="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L65))</f>
         <v/>
       </c>
-      <c r="G65" s="25" t="str">
+      <c r="G65" s="26" t="str">
         <f aca="false">IF($A65="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L65))</f>
         <v/>
       </c>
-      <c r="H65" s="26" t="str">
+      <c r="H65" s="27" t="str">
         <f aca="false">IF($A65="","",$C65+$F65-$G65)</f>
         <v/>
       </c>
-      <c r="I65" s="19"/>
-      <c r="J65" s="27" t="str">
-        <f aca="false">IF($I65="","",$H65*$I65)</f>
-        <v/>
-      </c>
-      <c r="L65" s="21" t="str">
+      <c r="I65" s="20"/>
+      <c r="J65" s="28" t="str">
+        <f aca="false">IF(OR($A65="",$I65="",$C$4=""),"",$H65*$I65*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L65" s="22" t="str">
         <f aca="false">IF($A65="","",$A65&amp;" - "&amp;$B65)</f>
         <v/>
       </c>
-      <c r="M65" s="21" t="n">
+      <c r="M65" s="22" t="n">
         <f aca="false">IF($A65="",0,IF(OR($D65&lt;&gt;0,$E65&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N65" s="21" t="str">
+      <c r="N65" s="22" t="str">
         <f aca="false">IF($M65=1,SUM($M$8:$M65),"")</f>
         <v/>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="28"/>
-      <c r="B66" s="28"/>
-      <c r="C66" s="29"/>
-      <c r="D66" s="16" t="str">
+      <c r="A66" s="29"/>
+      <c r="B66" s="29"/>
+      <c r="C66" s="30"/>
+      <c r="D66" s="17" t="str">
         <f aca="false">IF($A66="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L66,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="E66" s="16" t="str">
+      <c r="E66" s="17" t="str">
         <f aca="false">IF($A66="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L66,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="F66" s="17" t="str">
+      <c r="F66" s="18" t="str">
         <f aca="false">IF($A66="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L66))</f>
         <v/>
       </c>
-      <c r="G66" s="17" t="str">
+      <c r="G66" s="18" t="str">
         <f aca="false">IF($A66="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L66))</f>
         <v/>
       </c>
-      <c r="H66" s="18" t="str">
+      <c r="H66" s="19" t="str">
         <f aca="false">IF($A66="","",$C66+$F66-$G66)</f>
         <v/>
       </c>
-      <c r="I66" s="19"/>
-      <c r="J66" s="20" t="str">
-        <f aca="false">IF($I66="","",$H66*$I66)</f>
-        <v/>
-      </c>
-      <c r="L66" s="21" t="str">
+      <c r="I66" s="20"/>
+      <c r="J66" s="21" t="str">
+        <f aca="false">IF(OR($A66="",$I66="",$C$4=""),"",$H66*$I66*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L66" s="22" t="str">
         <f aca="false">IF($A66="","",$A66&amp;" - "&amp;$B66)</f>
         <v/>
       </c>
-      <c r="M66" s="21" t="n">
+      <c r="M66" s="22" t="n">
         <f aca="false">IF($A66="",0,IF(OR($D66&lt;&gt;0,$E66&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N66" s="21" t="str">
+      <c r="N66" s="22" t="str">
         <f aca="false">IF($M66=1,SUM($M$8:$M66),"")</f>
         <v/>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="30"/>
-      <c r="B67" s="30"/>
-      <c r="C67" s="31"/>
-      <c r="D67" s="24" t="str">
+      <c r="A67" s="31"/>
+      <c r="B67" s="31"/>
+      <c r="C67" s="32"/>
+      <c r="D67" s="25" t="str">
         <f aca="false">IF($A67="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L67,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="E67" s="24" t="str">
+      <c r="E67" s="25" t="str">
         <f aca="false">IF($A67="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L67,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="F67" s="25" t="str">
+      <c r="F67" s="26" t="str">
         <f aca="false">IF($A67="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L67))</f>
         <v/>
       </c>
-      <c r="G67" s="25" t="str">
+      <c r="G67" s="26" t="str">
         <f aca="false">IF($A67="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L67))</f>
         <v/>
       </c>
-      <c r="H67" s="26" t="str">
+      <c r="H67" s="27" t="str">
         <f aca="false">IF($A67="","",$C67+$F67-$G67)</f>
         <v/>
       </c>
-      <c r="I67" s="19"/>
-      <c r="J67" s="27" t="str">
-        <f aca="false">IF($I67="","",$H67*$I67)</f>
-        <v/>
-      </c>
-      <c r="L67" s="21" t="str">
+      <c r="I67" s="20"/>
+      <c r="J67" s="28" t="str">
+        <f aca="false">IF(OR($A67="",$I67="",$C$4=""),"",$H67*$I67*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L67" s="22" t="str">
         <f aca="false">IF($A67="","",$A67&amp;" - "&amp;$B67)</f>
         <v/>
       </c>
-      <c r="M67" s="21" t="n">
+      <c r="M67" s="22" t="n">
         <f aca="false">IF($A67="",0,IF(OR($D67&lt;&gt;0,$E67&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N67" s="21" t="str">
+      <c r="N67" s="22" t="str">
         <f aca="false">IF($M67=1,SUM($M$8:$M67),"")</f>
         <v/>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="28"/>
-      <c r="B68" s="28"/>
-      <c r="C68" s="29"/>
-      <c r="D68" s="16" t="str">
+      <c r="A68" s="29"/>
+      <c r="B68" s="29"/>
+      <c r="C68" s="30"/>
+      <c r="D68" s="17" t="str">
         <f aca="false">IF($A68="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L68,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="E68" s="16" t="str">
+      <c r="E68" s="17" t="str">
         <f aca="false">IF($A68="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L68,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="F68" s="17" t="str">
+      <c r="F68" s="18" t="str">
         <f aca="false">IF($A68="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L68))</f>
         <v/>
       </c>
-      <c r="G68" s="17" t="str">
+      <c r="G68" s="18" t="str">
         <f aca="false">IF($A68="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L68))</f>
         <v/>
       </c>
-      <c r="H68" s="18" t="str">
+      <c r="H68" s="19" t="str">
         <f aca="false">IF($A68="","",$C68+$F68-$G68)</f>
         <v/>
       </c>
-      <c r="I68" s="19"/>
-      <c r="J68" s="20" t="str">
-        <f aca="false">IF($I68="","",$H68*$I68)</f>
-        <v/>
-      </c>
-      <c r="L68" s="21" t="str">
+      <c r="I68" s="20"/>
+      <c r="J68" s="21" t="str">
+        <f aca="false">IF(OR($A68="",$I68="",$C$4=""),"",$H68*$I68*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L68" s="22" t="str">
         <f aca="false">IF($A68="","",$A68&amp;" - "&amp;$B68)</f>
         <v/>
       </c>
-      <c r="M68" s="21" t="n">
+      <c r="M68" s="22" t="n">
         <f aca="false">IF($A68="",0,IF(OR($D68&lt;&gt;0,$E68&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N68" s="21" t="str">
+      <c r="N68" s="22" t="str">
         <f aca="false">IF($M68=1,SUM($M$8:$M68),"")</f>
         <v/>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="30"/>
-      <c r="B69" s="30"/>
-      <c r="C69" s="31"/>
-      <c r="D69" s="24" t="str">
+      <c r="A69" s="31"/>
+      <c r="B69" s="31"/>
+      <c r="C69" s="32"/>
+      <c r="D69" s="25" t="str">
         <f aca="false">IF($A69="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L69,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="E69" s="24" t="str">
+      <c r="E69" s="25" t="str">
         <f aca="false">IF($A69="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L69,'Daily Entry'!$A$7:$A$5000,$C$3))</f>
         <v/>
       </c>
-      <c r="F69" s="25" t="str">
+      <c r="F69" s="26" t="str">
         <f aca="false">IF($A69="","",SUMIFS('Daily Entry'!$C$7:$C$5000,'Daily Entry'!$B$7:$B$5000,$L69))</f>
         <v/>
       </c>
-      <c r="G69" s="25" t="str">
+      <c r="G69" s="26" t="str">
         <f aca="false">IF($A69="","",SUMIFS('Daily Entry'!$D$7:$D$5000,'Daily Entry'!$B$7:$B$5000,$L69))</f>
         <v/>
       </c>
-      <c r="H69" s="26" t="str">
+      <c r="H69" s="27" t="str">
         <f aca="false">IF($A69="","",$C69+$F69-$G69)</f>
         <v/>
       </c>
-      <c r="I69" s="19"/>
-      <c r="J69" s="27" t="str">
-        <f aca="false">IF($I69="","",$H69*$I69)</f>
-        <v/>
-      </c>
-      <c r="L69" s="21" t="str">
+      <c r="I69" s="20"/>
+      <c r="J69" s="28" t="str">
+        <f aca="false">IF(OR($A69="",$I69="",$C$4=""),"",$H69*$I69*$C$4)</f>
+        <v/>
+      </c>
+      <c r="L69" s="22" t="str">
         <f aca="false">IF($A69="","",$A69&amp;" - "&amp;$B69)</f>
         <v/>
       </c>
-      <c r="M69" s="21" t="n">
+      <c r="M69" s="22" t="n">
         <f aca="false">IF($A69="",0,IF(OR($D69&lt;&gt;0,$E69&lt;&gt;0),1,0))</f>
         <v>0</v>
       </c>
-      <c r="N69" s="21" t="str">
+      <c r="N69" s="22" t="str">
         <f aca="false">IF($M69=1,SUM($M$8:$M69),"")</f>
         <v/>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="32" t="s">
-        <v>92</v>
-      </c>
-      <c r="B70" s="32"/>
-      <c r="C70" s="33" t="n">
+      <c r="A70" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B70" s="33"/>
+      <c r="C70" s="34" t="n">
         <f aca="false">SUM(C8:C69)</f>
         <v>102870</v>
       </c>
-      <c r="D70" s="34" t="n">
+      <c r="D70" s="35" t="n">
         <f aca="false">SUM(D8:D69)</f>
         <v>4880</v>
       </c>
-      <c r="E70" s="34" t="n">
+      <c r="E70" s="35" t="n">
         <f aca="false">SUM(E8:E69)</f>
         <v>0</v>
       </c>
-      <c r="F70" s="33" t="n">
+      <c r="F70" s="34" t="n">
         <f aca="false">SUM(F8:F69)</f>
         <v>4880</v>
       </c>
-      <c r="G70" s="33" t="n">
+      <c r="G70" s="34" t="n">
         <f aca="false">SUM(G8:G69)</f>
         <v>0</v>
       </c>
-      <c r="H70" s="33" t="n">
+      <c r="H70" s="34" t="n">
         <f aca="false">SUM(H8:H69)</f>
         <v>107750</v>
       </c>
-      <c r="I70" s="32"/>
-      <c r="J70" s="35" t="str">
+      <c r="I70" s="33"/>
+      <c r="J70" s="36" t="str">
         <f aca="false">IF(SUM(J8:J69)=0,"",SUM(J8:J69))</f>
         <v/>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="9" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -4947,10 +5025,10 @@
   <dimension ref="A1:K250"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="86" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="87" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="88" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="89" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="88" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="89" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="90" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="91" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="6"/>
   </cols>
@@ -4962,1862 +5040,1862 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="G4" s="39" t="s">
-        <v>96</v>
-      </c>
-      <c r="J4" s="40" t="n">
+        <v>103</v>
+      </c>
+      <c r="G4" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="J4" s="41" t="n">
         <f aca="false">SUMPRODUCT((B7:B5000&lt;&gt;"")*(COUNTIF(Stock!$L$8:$L$69,B7:B5000)=0))</f>
         <v>0</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>102</v>
+      <c r="A6" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="41" t="n">
+      <c r="A7" s="42" t="n">
         <v>46254</v>
       </c>
-      <c r="B7" s="42" t="s">
-        <v>103</v>
-      </c>
-      <c r="C7" s="43" t="n">
+      <c r="B7" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="44" t="n">
         <v>1068</v>
       </c>
-      <c r="D7" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="44" t="s">
-        <v>104</v>
+      <c r="D7" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="45" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="41" t="n">
+      <c r="A8" s="42" t="n">
         <v>46254</v>
       </c>
-      <c r="B8" s="42" t="s">
-        <v>105</v>
-      </c>
-      <c r="C8" s="43" t="n">
+      <c r="B8" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" s="44" t="n">
         <v>65</v>
       </c>
-      <c r="D8" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="44"/>
+      <c r="D8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="45"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="41" t="n">
+      <c r="A9" s="42" t="n">
         <v>46254</v>
       </c>
-      <c r="B9" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="C9" s="43" t="n">
+      <c r="B9" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9" s="44" t="n">
         <v>267</v>
       </c>
-      <c r="D9" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="44"/>
+      <c r="D9" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="45"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="41" t="n">
+      <c r="A10" s="42" t="n">
         <v>46254</v>
       </c>
-      <c r="B10" s="42" t="s">
-        <v>107</v>
-      </c>
-      <c r="C10" s="43" t="n">
+      <c r="B10" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" s="44" t="n">
         <v>29</v>
       </c>
-      <c r="D10" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="44"/>
+      <c r="D10" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="45"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="41" t="n">
+      <c r="A11" s="42" t="n">
         <v>46254</v>
       </c>
-      <c r="B11" s="42" t="s">
-        <v>108</v>
-      </c>
-      <c r="C11" s="43" t="n">
+      <c r="B11" s="43" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="44" t="n">
         <v>39</v>
       </c>
-      <c r="D11" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="44"/>
+      <c r="D11" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="45"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="41" t="n">
+      <c r="A12" s="42" t="n">
         <v>46254</v>
       </c>
-      <c r="B12" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="C12" s="43" t="n">
+      <c r="B12" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12" s="44" t="n">
         <v>50</v>
       </c>
-      <c r="D12" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="44"/>
+      <c r="D12" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="45"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="41" t="n">
+      <c r="A13" s="42" t="n">
         <v>46254</v>
       </c>
-      <c r="B13" s="42" t="s">
-        <v>110</v>
-      </c>
-      <c r="C13" s="43" t="n">
+      <c r="B13" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="C13" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="44"/>
+      <c r="D13" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="45"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="41" t="n">
+      <c r="A14" s="42" t="n">
         <v>46254</v>
       </c>
-      <c r="B14" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="C14" s="43" t="n">
+      <c r="B14" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="44" t="n">
         <v>50</v>
       </c>
-      <c r="D14" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="44"/>
+      <c r="D14" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="45"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="41" t="n">
+      <c r="A15" s="42" t="n">
         <v>46254</v>
       </c>
-      <c r="B15" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="C15" s="43" t="n">
+      <c r="B15" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="44" t="n">
         <v>33</v>
       </c>
-      <c r="D15" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="44"/>
+      <c r="D15" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="45"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="41" t="n">
+      <c r="A16" s="42" t="n">
         <v>46254</v>
       </c>
-      <c r="B16" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="C16" s="43" t="n">
+      <c r="B16" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" s="44" t="n">
         <v>156</v>
       </c>
-      <c r="D16" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="44"/>
+      <c r="D16" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="45"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="41" t="n">
+      <c r="A17" s="42" t="n">
         <v>46254</v>
       </c>
-      <c r="B17" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="C17" s="43" t="n">
+      <c r="B17" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="44" t="n">
         <v>596</v>
       </c>
-      <c r="D17" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="44"/>
+      <c r="D17" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="45"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="41" t="n">
+      <c r="A18" s="42" t="n">
         <v>46254</v>
       </c>
-      <c r="B18" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="C18" s="43" t="n">
+      <c r="B18" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="C18" s="44" t="n">
         <v>52</v>
       </c>
-      <c r="D18" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="44"/>
+      <c r="D18" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="45"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="41" t="n">
+      <c r="A19" s="42" t="n">
         <v>46254</v>
       </c>
-      <c r="B19" s="42" t="s">
-        <v>116</v>
-      </c>
-      <c r="C19" s="43" t="n">
+      <c r="B19" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="44" t="n">
         <v>1872</v>
       </c>
-      <c r="D19" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="44"/>
+      <c r="D19" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="45"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="41" t="n">
+      <c r="A20" s="42" t="n">
         <v>46254</v>
       </c>
-      <c r="B20" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="C20" s="43" t="n">
+      <c r="B20" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" s="44" t="n">
         <v>600</v>
       </c>
-      <c r="D20" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="44"/>
+      <c r="D20" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="45"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="41"/>
-      <c r="B21" s="42"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="42"/>
+      <c r="A21" s="42"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="43"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="41"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="42"/>
+      <c r="A22" s="42"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="43"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="41"/>
-      <c r="B23" s="42"/>
-      <c r="C23" s="43"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="42"/>
+      <c r="A23" s="42"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="43"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="41"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="42"/>
+      <c r="A24" s="42"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="43"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="41"/>
-      <c r="B25" s="42"/>
-      <c r="C25" s="43"/>
-      <c r="D25" s="43"/>
-      <c r="E25" s="42"/>
+      <c r="A25" s="42"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="43"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="41"/>
-      <c r="B26" s="42"/>
-      <c r="C26" s="43"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="42"/>
+      <c r="A26" s="42"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="43"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="41"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="42"/>
+      <c r="A27" s="42"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="43"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="41"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="43"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="42"/>
+      <c r="A28" s="42"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="43"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="41"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="42"/>
+      <c r="A29" s="42"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="43"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="41"/>
-      <c r="B30" s="42"/>
-      <c r="C30" s="43"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="42"/>
+      <c r="A30" s="42"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="43"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="41"/>
-      <c r="B31" s="42"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="42"/>
+      <c r="A31" s="42"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="44"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="43"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="41"/>
-      <c r="B32" s="42"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="42"/>
+      <c r="A32" s="42"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="44"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="43"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="41"/>
-      <c r="B33" s="42"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="42"/>
+      <c r="A33" s="42"/>
+      <c r="B33" s="43"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="43"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="41"/>
-      <c r="B34" s="42"/>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="42"/>
+      <c r="A34" s="42"/>
+      <c r="B34" s="43"/>
+      <c r="C34" s="44"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="43"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="41"/>
-      <c r="B35" s="42"/>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="42"/>
+      <c r="A35" s="42"/>
+      <c r="B35" s="43"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="43"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="41"/>
-      <c r="B36" s="42"/>
-      <c r="C36" s="43"/>
-      <c r="D36" s="43"/>
-      <c r="E36" s="42"/>
+      <c r="A36" s="42"/>
+      <c r="B36" s="43"/>
+      <c r="C36" s="44"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="43"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="41"/>
-      <c r="B37" s="42"/>
-      <c r="C37" s="43"/>
-      <c r="D37" s="43"/>
-      <c r="E37" s="42"/>
+      <c r="A37" s="42"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="44"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="43"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="41"/>
-      <c r="B38" s="42"/>
-      <c r="C38" s="43"/>
-      <c r="D38" s="43"/>
-      <c r="E38" s="42"/>
+      <c r="A38" s="42"/>
+      <c r="B38" s="43"/>
+      <c r="C38" s="44"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="43"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="41"/>
-      <c r="B39" s="42"/>
-      <c r="C39" s="43"/>
-      <c r="D39" s="43"/>
-      <c r="E39" s="42"/>
+      <c r="A39" s="42"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="43"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="41"/>
-      <c r="B40" s="42"/>
-      <c r="C40" s="43"/>
-      <c r="D40" s="43"/>
-      <c r="E40" s="42"/>
+      <c r="A40" s="42"/>
+      <c r="B40" s="43"/>
+      <c r="C40" s="44"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="43"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="41"/>
-      <c r="B41" s="42"/>
-      <c r="C41" s="43"/>
-      <c r="D41" s="43"/>
-      <c r="E41" s="42"/>
+      <c r="A41" s="42"/>
+      <c r="B41" s="43"/>
+      <c r="C41" s="44"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="43"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="41"/>
-      <c r="B42" s="42"/>
-      <c r="C42" s="43"/>
-      <c r="D42" s="43"/>
-      <c r="E42" s="42"/>
+      <c r="A42" s="42"/>
+      <c r="B42" s="43"/>
+      <c r="C42" s="44"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="43"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="41"/>
-      <c r="B43" s="42"/>
-      <c r="C43" s="43"/>
-      <c r="D43" s="43"/>
-      <c r="E43" s="42"/>
+      <c r="A43" s="42"/>
+      <c r="B43" s="43"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="43"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="41"/>
-      <c r="B44" s="42"/>
-      <c r="C44" s="43"/>
-      <c r="D44" s="43"/>
-      <c r="E44" s="42"/>
+      <c r="A44" s="42"/>
+      <c r="B44" s="43"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="43"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="41"/>
-      <c r="B45" s="42"/>
-      <c r="C45" s="43"/>
-      <c r="D45" s="43"/>
-      <c r="E45" s="42"/>
+      <c r="A45" s="42"/>
+      <c r="B45" s="43"/>
+      <c r="C45" s="44"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="43"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="41"/>
-      <c r="B46" s="42"/>
-      <c r="C46" s="43"/>
-      <c r="D46" s="43"/>
-      <c r="E46" s="42"/>
+      <c r="A46" s="42"/>
+      <c r="B46" s="43"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="43"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="41"/>
-      <c r="B47" s="42"/>
-      <c r="C47" s="43"/>
-      <c r="D47" s="43"/>
-      <c r="E47" s="42"/>
+      <c r="A47" s="42"/>
+      <c r="B47" s="43"/>
+      <c r="C47" s="44"/>
+      <c r="D47" s="44"/>
+      <c r="E47" s="43"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="41"/>
-      <c r="B48" s="42"/>
-      <c r="C48" s="43"/>
-      <c r="D48" s="43"/>
-      <c r="E48" s="42"/>
+      <c r="A48" s="42"/>
+      <c r="B48" s="43"/>
+      <c r="C48" s="44"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="43"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="41"/>
-      <c r="B49" s="42"/>
-      <c r="C49" s="43"/>
-      <c r="D49" s="43"/>
-      <c r="E49" s="42"/>
+      <c r="A49" s="42"/>
+      <c r="B49" s="43"/>
+      <c r="C49" s="44"/>
+      <c r="D49" s="44"/>
+      <c r="E49" s="43"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="41"/>
-      <c r="B50" s="42"/>
-      <c r="C50" s="43"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="42"/>
+      <c r="A50" s="42"/>
+      <c r="B50" s="43"/>
+      <c r="C50" s="44"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="43"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="41"/>
-      <c r="B51" s="42"/>
-      <c r="C51" s="43"/>
-      <c r="D51" s="43"/>
-      <c r="E51" s="42"/>
+      <c r="A51" s="42"/>
+      <c r="B51" s="43"/>
+      <c r="C51" s="44"/>
+      <c r="D51" s="44"/>
+      <c r="E51" s="43"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="41"/>
-      <c r="B52" s="42"/>
-      <c r="C52" s="43"/>
-      <c r="D52" s="43"/>
-      <c r="E52" s="42"/>
+      <c r="A52" s="42"/>
+      <c r="B52" s="43"/>
+      <c r="C52" s="44"/>
+      <c r="D52" s="44"/>
+      <c r="E52" s="43"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="41"/>
-      <c r="B53" s="42"/>
-      <c r="C53" s="43"/>
-      <c r="D53" s="43"/>
-      <c r="E53" s="42"/>
+      <c r="A53" s="42"/>
+      <c r="B53" s="43"/>
+      <c r="C53" s="44"/>
+      <c r="D53" s="44"/>
+      <c r="E53" s="43"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="41"/>
-      <c r="B54" s="42"/>
-      <c r="C54" s="43"/>
-      <c r="D54" s="43"/>
-      <c r="E54" s="42"/>
+      <c r="A54" s="42"/>
+      <c r="B54" s="43"/>
+      <c r="C54" s="44"/>
+      <c r="D54" s="44"/>
+      <c r="E54" s="43"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="41"/>
-      <c r="B55" s="42"/>
-      <c r="C55" s="43"/>
-      <c r="D55" s="43"/>
-      <c r="E55" s="42"/>
+      <c r="A55" s="42"/>
+      <c r="B55" s="43"/>
+      <c r="C55" s="44"/>
+      <c r="D55" s="44"/>
+      <c r="E55" s="43"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="41"/>
-      <c r="B56" s="42"/>
-      <c r="C56" s="43"/>
-      <c r="D56" s="43"/>
-      <c r="E56" s="42"/>
+      <c r="A56" s="42"/>
+      <c r="B56" s="43"/>
+      <c r="C56" s="44"/>
+      <c r="D56" s="44"/>
+      <c r="E56" s="43"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="41"/>
-      <c r="B57" s="42"/>
-      <c r="C57" s="43"/>
-      <c r="D57" s="43"/>
-      <c r="E57" s="42"/>
+      <c r="A57" s="42"/>
+      <c r="B57" s="43"/>
+      <c r="C57" s="44"/>
+      <c r="D57" s="44"/>
+      <c r="E57" s="43"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="41"/>
-      <c r="B58" s="42"/>
-      <c r="C58" s="43"/>
-      <c r="D58" s="43"/>
-      <c r="E58" s="42"/>
+      <c r="A58" s="42"/>
+      <c r="B58" s="43"/>
+      <c r="C58" s="44"/>
+      <c r="D58" s="44"/>
+      <c r="E58" s="43"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="41"/>
-      <c r="B59" s="42"/>
-      <c r="C59" s="43"/>
-      <c r="D59" s="43"/>
-      <c r="E59" s="42"/>
+      <c r="A59" s="42"/>
+      <c r="B59" s="43"/>
+      <c r="C59" s="44"/>
+      <c r="D59" s="44"/>
+      <c r="E59" s="43"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="41"/>
-      <c r="B60" s="42"/>
-      <c r="C60" s="43"/>
-      <c r="D60" s="43"/>
-      <c r="E60" s="42"/>
+      <c r="A60" s="42"/>
+      <c r="B60" s="43"/>
+      <c r="C60" s="44"/>
+      <c r="D60" s="44"/>
+      <c r="E60" s="43"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="41"/>
-      <c r="B61" s="42"/>
-      <c r="C61" s="43"/>
-      <c r="D61" s="43"/>
-      <c r="E61" s="42"/>
+      <c r="A61" s="42"/>
+      <c r="B61" s="43"/>
+      <c r="C61" s="44"/>
+      <c r="D61" s="44"/>
+      <c r="E61" s="43"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="41"/>
-      <c r="B62" s="42"/>
-      <c r="C62" s="43"/>
-      <c r="D62" s="43"/>
-      <c r="E62" s="42"/>
+      <c r="A62" s="42"/>
+      <c r="B62" s="43"/>
+      <c r="C62" s="44"/>
+      <c r="D62" s="44"/>
+      <c r="E62" s="43"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="41"/>
-      <c r="B63" s="42"/>
-      <c r="C63" s="43"/>
-      <c r="D63" s="43"/>
-      <c r="E63" s="42"/>
+      <c r="A63" s="42"/>
+      <c r="B63" s="43"/>
+      <c r="C63" s="44"/>
+      <c r="D63" s="44"/>
+      <c r="E63" s="43"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="41"/>
-      <c r="B64" s="42"/>
-      <c r="C64" s="43"/>
-      <c r="D64" s="43"/>
-      <c r="E64" s="42"/>
+      <c r="A64" s="42"/>
+      <c r="B64" s="43"/>
+      <c r="C64" s="44"/>
+      <c r="D64" s="44"/>
+      <c r="E64" s="43"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="41"/>
-      <c r="B65" s="42"/>
-      <c r="C65" s="43"/>
-      <c r="D65" s="43"/>
-      <c r="E65" s="42"/>
+      <c r="A65" s="42"/>
+      <c r="B65" s="43"/>
+      <c r="C65" s="44"/>
+      <c r="D65" s="44"/>
+      <c r="E65" s="43"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="41"/>
-      <c r="B66" s="42"/>
-      <c r="C66" s="43"/>
-      <c r="D66" s="43"/>
-      <c r="E66" s="42"/>
+      <c r="A66" s="42"/>
+      <c r="B66" s="43"/>
+      <c r="C66" s="44"/>
+      <c r="D66" s="44"/>
+      <c r="E66" s="43"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="41"/>
-      <c r="B67" s="42"/>
-      <c r="C67" s="43"/>
-      <c r="D67" s="43"/>
-      <c r="E67" s="42"/>
+      <c r="A67" s="42"/>
+      <c r="B67" s="43"/>
+      <c r="C67" s="44"/>
+      <c r="D67" s="44"/>
+      <c r="E67" s="43"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="41"/>
-      <c r="B68" s="42"/>
-      <c r="C68" s="43"/>
-      <c r="D68" s="43"/>
-      <c r="E68" s="42"/>
+      <c r="A68" s="42"/>
+      <c r="B68" s="43"/>
+      <c r="C68" s="44"/>
+      <c r="D68" s="44"/>
+      <c r="E68" s="43"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="41"/>
-      <c r="B69" s="42"/>
-      <c r="C69" s="43"/>
-      <c r="D69" s="43"/>
-      <c r="E69" s="42"/>
+      <c r="A69" s="42"/>
+      <c r="B69" s="43"/>
+      <c r="C69" s="44"/>
+      <c r="D69" s="44"/>
+      <c r="E69" s="43"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="41"/>
-      <c r="B70" s="42"/>
-      <c r="C70" s="43"/>
-      <c r="D70" s="43"/>
-      <c r="E70" s="42"/>
+      <c r="A70" s="42"/>
+      <c r="B70" s="43"/>
+      <c r="C70" s="44"/>
+      <c r="D70" s="44"/>
+      <c r="E70" s="43"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="41"/>
-      <c r="B71" s="42"/>
-      <c r="C71" s="43"/>
-      <c r="D71" s="43"/>
-      <c r="E71" s="42"/>
+      <c r="A71" s="42"/>
+      <c r="B71" s="43"/>
+      <c r="C71" s="44"/>
+      <c r="D71" s="44"/>
+      <c r="E71" s="43"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="41"/>
-      <c r="B72" s="42"/>
-      <c r="C72" s="43"/>
-      <c r="D72" s="43"/>
-      <c r="E72" s="42"/>
+      <c r="A72" s="42"/>
+      <c r="B72" s="43"/>
+      <c r="C72" s="44"/>
+      <c r="D72" s="44"/>
+      <c r="E72" s="43"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="41"/>
-      <c r="B73" s="42"/>
-      <c r="C73" s="43"/>
-      <c r="D73" s="43"/>
-      <c r="E73" s="42"/>
+      <c r="A73" s="42"/>
+      <c r="B73" s="43"/>
+      <c r="C73" s="44"/>
+      <c r="D73" s="44"/>
+      <c r="E73" s="43"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="41"/>
-      <c r="B74" s="42"/>
-      <c r="C74" s="43"/>
-      <c r="D74" s="43"/>
-      <c r="E74" s="42"/>
+      <c r="A74" s="42"/>
+      <c r="B74" s="43"/>
+      <c r="C74" s="44"/>
+      <c r="D74" s="44"/>
+      <c r="E74" s="43"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="41"/>
-      <c r="B75" s="42"/>
-      <c r="C75" s="43"/>
-      <c r="D75" s="43"/>
-      <c r="E75" s="42"/>
+      <c r="A75" s="42"/>
+      <c r="B75" s="43"/>
+      <c r="C75" s="44"/>
+      <c r="D75" s="44"/>
+      <c r="E75" s="43"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="41"/>
-      <c r="B76" s="42"/>
-      <c r="C76" s="43"/>
-      <c r="D76" s="43"/>
-      <c r="E76" s="42"/>
+      <c r="A76" s="42"/>
+      <c r="B76" s="43"/>
+      <c r="C76" s="44"/>
+      <c r="D76" s="44"/>
+      <c r="E76" s="43"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="41"/>
-      <c r="B77" s="42"/>
-      <c r="C77" s="43"/>
-      <c r="D77" s="43"/>
-      <c r="E77" s="42"/>
+      <c r="A77" s="42"/>
+      <c r="B77" s="43"/>
+      <c r="C77" s="44"/>
+      <c r="D77" s="44"/>
+      <c r="E77" s="43"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="41"/>
-      <c r="B78" s="42"/>
-      <c r="C78" s="43"/>
-      <c r="D78" s="43"/>
-      <c r="E78" s="42"/>
+      <c r="A78" s="42"/>
+      <c r="B78" s="43"/>
+      <c r="C78" s="44"/>
+      <c r="D78" s="44"/>
+      <c r="E78" s="43"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="41"/>
-      <c r="B79" s="42"/>
-      <c r="C79" s="43"/>
-      <c r="D79" s="43"/>
-      <c r="E79" s="42"/>
+      <c r="A79" s="42"/>
+      <c r="B79" s="43"/>
+      <c r="C79" s="44"/>
+      <c r="D79" s="44"/>
+      <c r="E79" s="43"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="41"/>
-      <c r="B80" s="42"/>
-      <c r="C80" s="43"/>
-      <c r="D80" s="43"/>
-      <c r="E80" s="42"/>
+      <c r="A80" s="42"/>
+      <c r="B80" s="43"/>
+      <c r="C80" s="44"/>
+      <c r="D80" s="44"/>
+      <c r="E80" s="43"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="41"/>
-      <c r="B81" s="42"/>
-      <c r="C81" s="43"/>
-      <c r="D81" s="43"/>
-      <c r="E81" s="42"/>
+      <c r="A81" s="42"/>
+      <c r="B81" s="43"/>
+      <c r="C81" s="44"/>
+      <c r="D81" s="44"/>
+      <c r="E81" s="43"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="41"/>
-      <c r="B82" s="42"/>
-      <c r="C82" s="43"/>
-      <c r="D82" s="43"/>
-      <c r="E82" s="42"/>
+      <c r="A82" s="42"/>
+      <c r="B82" s="43"/>
+      <c r="C82" s="44"/>
+      <c r="D82" s="44"/>
+      <c r="E82" s="43"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="41"/>
-      <c r="B83" s="42"/>
-      <c r="C83" s="43"/>
-      <c r="D83" s="43"/>
-      <c r="E83" s="42"/>
+      <c r="A83" s="42"/>
+      <c r="B83" s="43"/>
+      <c r="C83" s="44"/>
+      <c r="D83" s="44"/>
+      <c r="E83" s="43"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="41"/>
-      <c r="B84" s="42"/>
-      <c r="C84" s="43"/>
-      <c r="D84" s="43"/>
-      <c r="E84" s="42"/>
+      <c r="A84" s="42"/>
+      <c r="B84" s="43"/>
+      <c r="C84" s="44"/>
+      <c r="D84" s="44"/>
+      <c r="E84" s="43"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="41"/>
-      <c r="B85" s="42"/>
-      <c r="C85" s="43"/>
-      <c r="D85" s="43"/>
-      <c r="E85" s="42"/>
+      <c r="A85" s="42"/>
+      <c r="B85" s="43"/>
+      <c r="C85" s="44"/>
+      <c r="D85" s="44"/>
+      <c r="E85" s="43"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="41"/>
-      <c r="B86" s="42"/>
-      <c r="C86" s="43"/>
-      <c r="D86" s="43"/>
-      <c r="E86" s="42"/>
+      <c r="A86" s="42"/>
+      <c r="B86" s="43"/>
+      <c r="C86" s="44"/>
+      <c r="D86" s="44"/>
+      <c r="E86" s="43"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="41"/>
-      <c r="B87" s="42"/>
-      <c r="C87" s="43"/>
-      <c r="D87" s="43"/>
-      <c r="E87" s="42"/>
+      <c r="A87" s="42"/>
+      <c r="B87" s="43"/>
+      <c r="C87" s="44"/>
+      <c r="D87" s="44"/>
+      <c r="E87" s="43"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="41"/>
-      <c r="B88" s="42"/>
-      <c r="C88" s="43"/>
-      <c r="D88" s="43"/>
-      <c r="E88" s="42"/>
+      <c r="A88" s="42"/>
+      <c r="B88" s="43"/>
+      <c r="C88" s="44"/>
+      <c r="D88" s="44"/>
+      <c r="E88" s="43"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="41"/>
-      <c r="B89" s="42"/>
-      <c r="C89" s="43"/>
-      <c r="D89" s="43"/>
-      <c r="E89" s="42"/>
+      <c r="A89" s="42"/>
+      <c r="B89" s="43"/>
+      <c r="C89" s="44"/>
+      <c r="D89" s="44"/>
+      <c r="E89" s="43"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="41"/>
-      <c r="B90" s="42"/>
-      <c r="C90" s="43"/>
-      <c r="D90" s="43"/>
-      <c r="E90" s="42"/>
+      <c r="A90" s="42"/>
+      <c r="B90" s="43"/>
+      <c r="C90" s="44"/>
+      <c r="D90" s="44"/>
+      <c r="E90" s="43"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="41"/>
-      <c r="B91" s="42"/>
-      <c r="C91" s="43"/>
-      <c r="D91" s="43"/>
-      <c r="E91" s="42"/>
+      <c r="A91" s="42"/>
+      <c r="B91" s="43"/>
+      <c r="C91" s="44"/>
+      <c r="D91" s="44"/>
+      <c r="E91" s="43"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="41"/>
-      <c r="B92" s="42"/>
-      <c r="C92" s="43"/>
-      <c r="D92" s="43"/>
-      <c r="E92" s="42"/>
+      <c r="A92" s="42"/>
+      <c r="B92" s="43"/>
+      <c r="C92" s="44"/>
+      <c r="D92" s="44"/>
+      <c r="E92" s="43"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="41"/>
-      <c r="B93" s="42"/>
-      <c r="C93" s="43"/>
-      <c r="D93" s="43"/>
-      <c r="E93" s="42"/>
+      <c r="A93" s="42"/>
+      <c r="B93" s="43"/>
+      <c r="C93" s="44"/>
+      <c r="D93" s="44"/>
+      <c r="E93" s="43"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="41"/>
-      <c r="B94" s="42"/>
-      <c r="C94" s="43"/>
-      <c r="D94" s="43"/>
-      <c r="E94" s="42"/>
+      <c r="A94" s="42"/>
+      <c r="B94" s="43"/>
+      <c r="C94" s="44"/>
+      <c r="D94" s="44"/>
+      <c r="E94" s="43"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="41"/>
-      <c r="B95" s="42"/>
-      <c r="C95" s="43"/>
-      <c r="D95" s="43"/>
-      <c r="E95" s="42"/>
+      <c r="A95" s="42"/>
+      <c r="B95" s="43"/>
+      <c r="C95" s="44"/>
+      <c r="D95" s="44"/>
+      <c r="E95" s="43"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="41"/>
-      <c r="B96" s="42"/>
-      <c r="C96" s="43"/>
-      <c r="D96" s="43"/>
-      <c r="E96" s="42"/>
+      <c r="A96" s="42"/>
+      <c r="B96" s="43"/>
+      <c r="C96" s="44"/>
+      <c r="D96" s="44"/>
+      <c r="E96" s="43"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="41"/>
-      <c r="B97" s="42"/>
-      <c r="C97" s="43"/>
-      <c r="D97" s="43"/>
-      <c r="E97" s="42"/>
+      <c r="A97" s="42"/>
+      <c r="B97" s="43"/>
+      <c r="C97" s="44"/>
+      <c r="D97" s="44"/>
+      <c r="E97" s="43"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="41"/>
-      <c r="B98" s="42"/>
-      <c r="C98" s="43"/>
-      <c r="D98" s="43"/>
-      <c r="E98" s="42"/>
+      <c r="A98" s="42"/>
+      <c r="B98" s="43"/>
+      <c r="C98" s="44"/>
+      <c r="D98" s="44"/>
+      <c r="E98" s="43"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="41"/>
-      <c r="B99" s="42"/>
-      <c r="C99" s="43"/>
-      <c r="D99" s="43"/>
-      <c r="E99" s="42"/>
+      <c r="A99" s="42"/>
+      <c r="B99" s="43"/>
+      <c r="C99" s="44"/>
+      <c r="D99" s="44"/>
+      <c r="E99" s="43"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="41"/>
-      <c r="B100" s="42"/>
-      <c r="C100" s="43"/>
-      <c r="D100" s="43"/>
-      <c r="E100" s="42"/>
+      <c r="A100" s="42"/>
+      <c r="B100" s="43"/>
+      <c r="C100" s="44"/>
+      <c r="D100" s="44"/>
+      <c r="E100" s="43"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="41"/>
-      <c r="B101" s="42"/>
-      <c r="C101" s="43"/>
-      <c r="D101" s="43"/>
-      <c r="E101" s="42"/>
+      <c r="A101" s="42"/>
+      <c r="B101" s="43"/>
+      <c r="C101" s="44"/>
+      <c r="D101" s="44"/>
+      <c r="E101" s="43"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="41"/>
-      <c r="B102" s="42"/>
-      <c r="C102" s="43"/>
-      <c r="D102" s="43"/>
-      <c r="E102" s="42"/>
+      <c r="A102" s="42"/>
+      <c r="B102" s="43"/>
+      <c r="C102" s="44"/>
+      <c r="D102" s="44"/>
+      <c r="E102" s="43"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="41"/>
-      <c r="B103" s="42"/>
-      <c r="C103" s="43"/>
-      <c r="D103" s="43"/>
-      <c r="E103" s="42"/>
+      <c r="A103" s="42"/>
+      <c r="B103" s="43"/>
+      <c r="C103" s="44"/>
+      <c r="D103" s="44"/>
+      <c r="E103" s="43"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="41"/>
-      <c r="B104" s="42"/>
-      <c r="C104" s="43"/>
-      <c r="D104" s="43"/>
-      <c r="E104" s="42"/>
+      <c r="A104" s="42"/>
+      <c r="B104" s="43"/>
+      <c r="C104" s="44"/>
+      <c r="D104" s="44"/>
+      <c r="E104" s="43"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="41"/>
-      <c r="B105" s="42"/>
-      <c r="C105" s="43"/>
-      <c r="D105" s="43"/>
-      <c r="E105" s="42"/>
+      <c r="A105" s="42"/>
+      <c r="B105" s="43"/>
+      <c r="C105" s="44"/>
+      <c r="D105" s="44"/>
+      <c r="E105" s="43"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="41"/>
-      <c r="B106" s="42"/>
-      <c r="C106" s="43"/>
-      <c r="D106" s="43"/>
-      <c r="E106" s="42"/>
+      <c r="A106" s="42"/>
+      <c r="B106" s="43"/>
+      <c r="C106" s="44"/>
+      <c r="D106" s="44"/>
+      <c r="E106" s="43"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="41"/>
-      <c r="B107" s="42"/>
-      <c r="C107" s="43"/>
-      <c r="D107" s="43"/>
-      <c r="E107" s="42"/>
+      <c r="A107" s="42"/>
+      <c r="B107" s="43"/>
+      <c r="C107" s="44"/>
+      <c r="D107" s="44"/>
+      <c r="E107" s="43"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="41"/>
-      <c r="B108" s="42"/>
-      <c r="C108" s="43"/>
-      <c r="D108" s="43"/>
-      <c r="E108" s="42"/>
+      <c r="A108" s="42"/>
+      <c r="B108" s="43"/>
+      <c r="C108" s="44"/>
+      <c r="D108" s="44"/>
+      <c r="E108" s="43"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="41"/>
-      <c r="B109" s="42"/>
-      <c r="C109" s="43"/>
-      <c r="D109" s="43"/>
-      <c r="E109" s="42"/>
+      <c r="A109" s="42"/>
+      <c r="B109" s="43"/>
+      <c r="C109" s="44"/>
+      <c r="D109" s="44"/>
+      <c r="E109" s="43"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="41"/>
-      <c r="B110" s="42"/>
-      <c r="C110" s="43"/>
-      <c r="D110" s="43"/>
-      <c r="E110" s="42"/>
+      <c r="A110" s="42"/>
+      <c r="B110" s="43"/>
+      <c r="C110" s="44"/>
+      <c r="D110" s="44"/>
+      <c r="E110" s="43"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="41"/>
-      <c r="B111" s="42"/>
-      <c r="C111" s="43"/>
-      <c r="D111" s="43"/>
-      <c r="E111" s="42"/>
+      <c r="A111" s="42"/>
+      <c r="B111" s="43"/>
+      <c r="C111" s="44"/>
+      <c r="D111" s="44"/>
+      <c r="E111" s="43"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="41"/>
-      <c r="B112" s="42"/>
-      <c r="C112" s="43"/>
-      <c r="D112" s="43"/>
-      <c r="E112" s="42"/>
+      <c r="A112" s="42"/>
+      <c r="B112" s="43"/>
+      <c r="C112" s="44"/>
+      <c r="D112" s="44"/>
+      <c r="E112" s="43"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="41"/>
-      <c r="B113" s="42"/>
-      <c r="C113" s="43"/>
-      <c r="D113" s="43"/>
-      <c r="E113" s="42"/>
+      <c r="A113" s="42"/>
+      <c r="B113" s="43"/>
+      <c r="C113" s="44"/>
+      <c r="D113" s="44"/>
+      <c r="E113" s="43"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="41"/>
-      <c r="B114" s="42"/>
-      <c r="C114" s="43"/>
-      <c r="D114" s="43"/>
-      <c r="E114" s="42"/>
+      <c r="A114" s="42"/>
+      <c r="B114" s="43"/>
+      <c r="C114" s="44"/>
+      <c r="D114" s="44"/>
+      <c r="E114" s="43"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="41"/>
-      <c r="B115" s="42"/>
-      <c r="C115" s="43"/>
-      <c r="D115" s="43"/>
-      <c r="E115" s="42"/>
+      <c r="A115" s="42"/>
+      <c r="B115" s="43"/>
+      <c r="C115" s="44"/>
+      <c r="D115" s="44"/>
+      <c r="E115" s="43"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="41"/>
-      <c r="B116" s="42"/>
-      <c r="C116" s="43"/>
-      <c r="D116" s="43"/>
-      <c r="E116" s="42"/>
+      <c r="A116" s="42"/>
+      <c r="B116" s="43"/>
+      <c r="C116" s="44"/>
+      <c r="D116" s="44"/>
+      <c r="E116" s="43"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="41"/>
-      <c r="B117" s="42"/>
-      <c r="C117" s="43"/>
-      <c r="D117" s="43"/>
-      <c r="E117" s="42"/>
+      <c r="A117" s="42"/>
+      <c r="B117" s="43"/>
+      <c r="C117" s="44"/>
+      <c r="D117" s="44"/>
+      <c r="E117" s="43"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="41"/>
-      <c r="B118" s="42"/>
-      <c r="C118" s="43"/>
-      <c r="D118" s="43"/>
-      <c r="E118" s="42"/>
+      <c r="A118" s="42"/>
+      <c r="B118" s="43"/>
+      <c r="C118" s="44"/>
+      <c r="D118" s="44"/>
+      <c r="E118" s="43"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="41"/>
-      <c r="B119" s="42"/>
-      <c r="C119" s="43"/>
-      <c r="D119" s="43"/>
-      <c r="E119" s="42"/>
+      <c r="A119" s="42"/>
+      <c r="B119" s="43"/>
+      <c r="C119" s="44"/>
+      <c r="D119" s="44"/>
+      <c r="E119" s="43"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="41"/>
-      <c r="B120" s="42"/>
-      <c r="C120" s="43"/>
-      <c r="D120" s="43"/>
-      <c r="E120" s="42"/>
+      <c r="A120" s="42"/>
+      <c r="B120" s="43"/>
+      <c r="C120" s="44"/>
+      <c r="D120" s="44"/>
+      <c r="E120" s="43"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="41"/>
-      <c r="B121" s="42"/>
-      <c r="C121" s="43"/>
-      <c r="D121" s="43"/>
-      <c r="E121" s="42"/>
+      <c r="A121" s="42"/>
+      <c r="B121" s="43"/>
+      <c r="C121" s="44"/>
+      <c r="D121" s="44"/>
+      <c r="E121" s="43"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="41"/>
-      <c r="B122" s="42"/>
-      <c r="C122" s="43"/>
-      <c r="D122" s="43"/>
-      <c r="E122" s="42"/>
+      <c r="A122" s="42"/>
+      <c r="B122" s="43"/>
+      <c r="C122" s="44"/>
+      <c r="D122" s="44"/>
+      <c r="E122" s="43"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="41"/>
-      <c r="B123" s="42"/>
-      <c r="C123" s="43"/>
-      <c r="D123" s="43"/>
-      <c r="E123" s="42"/>
+      <c r="A123" s="42"/>
+      <c r="B123" s="43"/>
+      <c r="C123" s="44"/>
+      <c r="D123" s="44"/>
+      <c r="E123" s="43"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="41"/>
-      <c r="B124" s="42"/>
-      <c r="C124" s="43"/>
-      <c r="D124" s="43"/>
-      <c r="E124" s="42"/>
+      <c r="A124" s="42"/>
+      <c r="B124" s="43"/>
+      <c r="C124" s="44"/>
+      <c r="D124" s="44"/>
+      <c r="E124" s="43"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="41"/>
-      <c r="B125" s="42"/>
-      <c r="C125" s="43"/>
-      <c r="D125" s="43"/>
-      <c r="E125" s="42"/>
+      <c r="A125" s="42"/>
+      <c r="B125" s="43"/>
+      <c r="C125" s="44"/>
+      <c r="D125" s="44"/>
+      <c r="E125" s="43"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="41"/>
-      <c r="B126" s="42"/>
-      <c r="C126" s="43"/>
-      <c r="D126" s="43"/>
-      <c r="E126" s="42"/>
+      <c r="A126" s="42"/>
+      <c r="B126" s="43"/>
+      <c r="C126" s="44"/>
+      <c r="D126" s="44"/>
+      <c r="E126" s="43"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="41"/>
-      <c r="B127" s="42"/>
-      <c r="C127" s="43"/>
-      <c r="D127" s="43"/>
-      <c r="E127" s="42"/>
+      <c r="A127" s="42"/>
+      <c r="B127" s="43"/>
+      <c r="C127" s="44"/>
+      <c r="D127" s="44"/>
+      <c r="E127" s="43"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="41"/>
-      <c r="B128" s="42"/>
-      <c r="C128" s="43"/>
-      <c r="D128" s="43"/>
-      <c r="E128" s="42"/>
+      <c r="A128" s="42"/>
+      <c r="B128" s="43"/>
+      <c r="C128" s="44"/>
+      <c r="D128" s="44"/>
+      <c r="E128" s="43"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="41"/>
-      <c r="B129" s="42"/>
-      <c r="C129" s="43"/>
-      <c r="D129" s="43"/>
-      <c r="E129" s="42"/>
+      <c r="A129" s="42"/>
+      <c r="B129" s="43"/>
+      <c r="C129" s="44"/>
+      <c r="D129" s="44"/>
+      <c r="E129" s="43"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="41"/>
-      <c r="B130" s="42"/>
-      <c r="C130" s="43"/>
-      <c r="D130" s="43"/>
-      <c r="E130" s="42"/>
+      <c r="A130" s="42"/>
+      <c r="B130" s="43"/>
+      <c r="C130" s="44"/>
+      <c r="D130" s="44"/>
+      <c r="E130" s="43"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="41"/>
-      <c r="B131" s="42"/>
-      <c r="C131" s="43"/>
-      <c r="D131" s="43"/>
-      <c r="E131" s="42"/>
+      <c r="A131" s="42"/>
+      <c r="B131" s="43"/>
+      <c r="C131" s="44"/>
+      <c r="D131" s="44"/>
+      <c r="E131" s="43"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="41"/>
-      <c r="B132" s="42"/>
-      <c r="C132" s="43"/>
-      <c r="D132" s="43"/>
-      <c r="E132" s="42"/>
+      <c r="A132" s="42"/>
+      <c r="B132" s="43"/>
+      <c r="C132" s="44"/>
+      <c r="D132" s="44"/>
+      <c r="E132" s="43"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="41"/>
-      <c r="B133" s="42"/>
-      <c r="C133" s="43"/>
-      <c r="D133" s="43"/>
-      <c r="E133" s="42"/>
+      <c r="A133" s="42"/>
+      <c r="B133" s="43"/>
+      <c r="C133" s="44"/>
+      <c r="D133" s="44"/>
+      <c r="E133" s="43"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="41"/>
-      <c r="B134" s="42"/>
-      <c r="C134" s="43"/>
-      <c r="D134" s="43"/>
-      <c r="E134" s="42"/>
+      <c r="A134" s="42"/>
+      <c r="B134" s="43"/>
+      <c r="C134" s="44"/>
+      <c r="D134" s="44"/>
+      <c r="E134" s="43"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="41"/>
-      <c r="B135" s="42"/>
-      <c r="C135" s="43"/>
-      <c r="D135" s="43"/>
-      <c r="E135" s="42"/>
+      <c r="A135" s="42"/>
+      <c r="B135" s="43"/>
+      <c r="C135" s="44"/>
+      <c r="D135" s="44"/>
+      <c r="E135" s="43"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="41"/>
-      <c r="B136" s="42"/>
-      <c r="C136" s="43"/>
-      <c r="D136" s="43"/>
-      <c r="E136" s="42"/>
+      <c r="A136" s="42"/>
+      <c r="B136" s="43"/>
+      <c r="C136" s="44"/>
+      <c r="D136" s="44"/>
+      <c r="E136" s="43"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="41"/>
-      <c r="B137" s="42"/>
-      <c r="C137" s="43"/>
-      <c r="D137" s="43"/>
-      <c r="E137" s="42"/>
+      <c r="A137" s="42"/>
+      <c r="B137" s="43"/>
+      <c r="C137" s="44"/>
+      <c r="D137" s="44"/>
+      <c r="E137" s="43"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="41"/>
-      <c r="B138" s="42"/>
-      <c r="C138" s="43"/>
-      <c r="D138" s="43"/>
-      <c r="E138" s="42"/>
+      <c r="A138" s="42"/>
+      <c r="B138" s="43"/>
+      <c r="C138" s="44"/>
+      <c r="D138" s="44"/>
+      <c r="E138" s="43"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="41"/>
-      <c r="B139" s="42"/>
-      <c r="C139" s="43"/>
-      <c r="D139" s="43"/>
-      <c r="E139" s="42"/>
+      <c r="A139" s="42"/>
+      <c r="B139" s="43"/>
+      <c r="C139" s="44"/>
+      <c r="D139" s="44"/>
+      <c r="E139" s="43"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="41"/>
-      <c r="B140" s="42"/>
-      <c r="C140" s="43"/>
-      <c r="D140" s="43"/>
-      <c r="E140" s="42"/>
+      <c r="A140" s="42"/>
+      <c r="B140" s="43"/>
+      <c r="C140" s="44"/>
+      <c r="D140" s="44"/>
+      <c r="E140" s="43"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="41"/>
-      <c r="B141" s="42"/>
-      <c r="C141" s="43"/>
-      <c r="D141" s="43"/>
-      <c r="E141" s="42"/>
+      <c r="A141" s="42"/>
+      <c r="B141" s="43"/>
+      <c r="C141" s="44"/>
+      <c r="D141" s="44"/>
+      <c r="E141" s="43"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="41"/>
-      <c r="B142" s="42"/>
-      <c r="C142" s="43"/>
-      <c r="D142" s="43"/>
-      <c r="E142" s="42"/>
+      <c r="A142" s="42"/>
+      <c r="B142" s="43"/>
+      <c r="C142" s="44"/>
+      <c r="D142" s="44"/>
+      <c r="E142" s="43"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="41"/>
-      <c r="B143" s="42"/>
-      <c r="C143" s="43"/>
-      <c r="D143" s="43"/>
-      <c r="E143" s="42"/>
+      <c r="A143" s="42"/>
+      <c r="B143" s="43"/>
+      <c r="C143" s="44"/>
+      <c r="D143" s="44"/>
+      <c r="E143" s="43"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="41"/>
-      <c r="B144" s="42"/>
-      <c r="C144" s="43"/>
-      <c r="D144" s="43"/>
-      <c r="E144" s="42"/>
+      <c r="A144" s="42"/>
+      <c r="B144" s="43"/>
+      <c r="C144" s="44"/>
+      <c r="D144" s="44"/>
+      <c r="E144" s="43"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="41"/>
-      <c r="B145" s="42"/>
-      <c r="C145" s="43"/>
-      <c r="D145" s="43"/>
-      <c r="E145" s="42"/>
+      <c r="A145" s="42"/>
+      <c r="B145" s="43"/>
+      <c r="C145" s="44"/>
+      <c r="D145" s="44"/>
+      <c r="E145" s="43"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="41"/>
-      <c r="B146" s="42"/>
-      <c r="C146" s="43"/>
-      <c r="D146" s="43"/>
-      <c r="E146" s="42"/>
+      <c r="A146" s="42"/>
+      <c r="B146" s="43"/>
+      <c r="C146" s="44"/>
+      <c r="D146" s="44"/>
+      <c r="E146" s="43"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="41"/>
-      <c r="B147" s="42"/>
-      <c r="C147" s="43"/>
-      <c r="D147" s="43"/>
-      <c r="E147" s="42"/>
+      <c r="A147" s="42"/>
+      <c r="B147" s="43"/>
+      <c r="C147" s="44"/>
+      <c r="D147" s="44"/>
+      <c r="E147" s="43"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="41"/>
-      <c r="B148" s="42"/>
-      <c r="C148" s="43"/>
-      <c r="D148" s="43"/>
-      <c r="E148" s="42"/>
+      <c r="A148" s="42"/>
+      <c r="B148" s="43"/>
+      <c r="C148" s="44"/>
+      <c r="D148" s="44"/>
+      <c r="E148" s="43"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="41"/>
-      <c r="B149" s="42"/>
-      <c r="C149" s="43"/>
-      <c r="D149" s="43"/>
-      <c r="E149" s="42"/>
+      <c r="A149" s="42"/>
+      <c r="B149" s="43"/>
+      <c r="C149" s="44"/>
+      <c r="D149" s="44"/>
+      <c r="E149" s="43"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="41"/>
-      <c r="B150" s="42"/>
-      <c r="C150" s="43"/>
-      <c r="D150" s="43"/>
-      <c r="E150" s="42"/>
+      <c r="A150" s="42"/>
+      <c r="B150" s="43"/>
+      <c r="C150" s="44"/>
+      <c r="D150" s="44"/>
+      <c r="E150" s="43"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="41"/>
-      <c r="B151" s="42"/>
-      <c r="C151" s="43"/>
-      <c r="D151" s="43"/>
-      <c r="E151" s="42"/>
+      <c r="A151" s="42"/>
+      <c r="B151" s="43"/>
+      <c r="C151" s="44"/>
+      <c r="D151" s="44"/>
+      <c r="E151" s="43"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="41"/>
-      <c r="B152" s="42"/>
-      <c r="C152" s="43"/>
-      <c r="D152" s="43"/>
-      <c r="E152" s="42"/>
+      <c r="A152" s="42"/>
+      <c r="B152" s="43"/>
+      <c r="C152" s="44"/>
+      <c r="D152" s="44"/>
+      <c r="E152" s="43"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="41"/>
-      <c r="B153" s="42"/>
-      <c r="C153" s="43"/>
-      <c r="D153" s="43"/>
-      <c r="E153" s="42"/>
+      <c r="A153" s="42"/>
+      <c r="B153" s="43"/>
+      <c r="C153" s="44"/>
+      <c r="D153" s="44"/>
+      <c r="E153" s="43"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="41"/>
-      <c r="B154" s="42"/>
-      <c r="C154" s="43"/>
-      <c r="D154" s="43"/>
-      <c r="E154" s="42"/>
+      <c r="A154" s="42"/>
+      <c r="B154" s="43"/>
+      <c r="C154" s="44"/>
+      <c r="D154" s="44"/>
+      <c r="E154" s="43"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="41"/>
-      <c r="B155" s="42"/>
-      <c r="C155" s="43"/>
-      <c r="D155" s="43"/>
-      <c r="E155" s="42"/>
+      <c r="A155" s="42"/>
+      <c r="B155" s="43"/>
+      <c r="C155" s="44"/>
+      <c r="D155" s="44"/>
+      <c r="E155" s="43"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="41"/>
-      <c r="B156" s="42"/>
-      <c r="C156" s="43"/>
-      <c r="D156" s="43"/>
-      <c r="E156" s="42"/>
+      <c r="A156" s="42"/>
+      <c r="B156" s="43"/>
+      <c r="C156" s="44"/>
+      <c r="D156" s="44"/>
+      <c r="E156" s="43"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="41"/>
-      <c r="B157" s="42"/>
-      <c r="C157" s="43"/>
-      <c r="D157" s="43"/>
-      <c r="E157" s="42"/>
+      <c r="A157" s="42"/>
+      <c r="B157" s="43"/>
+      <c r="C157" s="44"/>
+      <c r="D157" s="44"/>
+      <c r="E157" s="43"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="41"/>
-      <c r="B158" s="42"/>
-      <c r="C158" s="43"/>
-      <c r="D158" s="43"/>
-      <c r="E158" s="42"/>
+      <c r="A158" s="42"/>
+      <c r="B158" s="43"/>
+      <c r="C158" s="44"/>
+      <c r="D158" s="44"/>
+      <c r="E158" s="43"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="41"/>
-      <c r="B159" s="42"/>
-      <c r="C159" s="43"/>
-      <c r="D159" s="43"/>
-      <c r="E159" s="42"/>
+      <c r="A159" s="42"/>
+      <c r="B159" s="43"/>
+      <c r="C159" s="44"/>
+      <c r="D159" s="44"/>
+      <c r="E159" s="43"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="41"/>
-      <c r="B160" s="42"/>
-      <c r="C160" s="43"/>
-      <c r="D160" s="43"/>
-      <c r="E160" s="42"/>
+      <c r="A160" s="42"/>
+      <c r="B160" s="43"/>
+      <c r="C160" s="44"/>
+      <c r="D160" s="44"/>
+      <c r="E160" s="43"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="41"/>
-      <c r="B161" s="42"/>
-      <c r="C161" s="43"/>
-      <c r="D161" s="43"/>
-      <c r="E161" s="42"/>
+      <c r="A161" s="42"/>
+      <c r="B161" s="43"/>
+      <c r="C161" s="44"/>
+      <c r="D161" s="44"/>
+      <c r="E161" s="43"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="41"/>
-      <c r="B162" s="42"/>
-      <c r="C162" s="43"/>
-      <c r="D162" s="43"/>
-      <c r="E162" s="42"/>
+      <c r="A162" s="42"/>
+      <c r="B162" s="43"/>
+      <c r="C162" s="44"/>
+      <c r="D162" s="44"/>
+      <c r="E162" s="43"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="41"/>
-      <c r="B163" s="42"/>
-      <c r="C163" s="43"/>
-      <c r="D163" s="43"/>
-      <c r="E163" s="42"/>
+      <c r="A163" s="42"/>
+      <c r="B163" s="43"/>
+      <c r="C163" s="44"/>
+      <c r="D163" s="44"/>
+      <c r="E163" s="43"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="41"/>
-      <c r="B164" s="42"/>
-      <c r="C164" s="43"/>
-      <c r="D164" s="43"/>
-      <c r="E164" s="42"/>
+      <c r="A164" s="42"/>
+      <c r="B164" s="43"/>
+      <c r="C164" s="44"/>
+      <c r="D164" s="44"/>
+      <c r="E164" s="43"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="41"/>
-      <c r="B165" s="42"/>
-      <c r="C165" s="43"/>
-      <c r="D165" s="43"/>
-      <c r="E165" s="42"/>
+      <c r="A165" s="42"/>
+      <c r="B165" s="43"/>
+      <c r="C165" s="44"/>
+      <c r="D165" s="44"/>
+      <c r="E165" s="43"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="41"/>
-      <c r="B166" s="42"/>
-      <c r="C166" s="43"/>
-      <c r="D166" s="43"/>
-      <c r="E166" s="42"/>
+      <c r="A166" s="42"/>
+      <c r="B166" s="43"/>
+      <c r="C166" s="44"/>
+      <c r="D166" s="44"/>
+      <c r="E166" s="43"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="41"/>
-      <c r="B167" s="42"/>
-      <c r="C167" s="43"/>
-      <c r="D167" s="43"/>
-      <c r="E167" s="42"/>
+      <c r="A167" s="42"/>
+      <c r="B167" s="43"/>
+      <c r="C167" s="44"/>
+      <c r="D167" s="44"/>
+      <c r="E167" s="43"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="41"/>
-      <c r="B168" s="42"/>
-      <c r="C168" s="43"/>
-      <c r="D168" s="43"/>
-      <c r="E168" s="42"/>
+      <c r="A168" s="42"/>
+      <c r="B168" s="43"/>
+      <c r="C168" s="44"/>
+      <c r="D168" s="44"/>
+      <c r="E168" s="43"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="41"/>
-      <c r="B169" s="42"/>
-      <c r="C169" s="43"/>
-      <c r="D169" s="43"/>
-      <c r="E169" s="42"/>
+      <c r="A169" s="42"/>
+      <c r="B169" s="43"/>
+      <c r="C169" s="44"/>
+      <c r="D169" s="44"/>
+      <c r="E169" s="43"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="41"/>
-      <c r="B170" s="42"/>
-      <c r="C170" s="43"/>
-      <c r="D170" s="43"/>
-      <c r="E170" s="42"/>
+      <c r="A170" s="42"/>
+      <c r="B170" s="43"/>
+      <c r="C170" s="44"/>
+      <c r="D170" s="44"/>
+      <c r="E170" s="43"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="41"/>
-      <c r="B171" s="42"/>
-      <c r="C171" s="43"/>
-      <c r="D171" s="43"/>
-      <c r="E171" s="42"/>
+      <c r="A171" s="42"/>
+      <c r="B171" s="43"/>
+      <c r="C171" s="44"/>
+      <c r="D171" s="44"/>
+      <c r="E171" s="43"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="41"/>
-      <c r="B172" s="42"/>
-      <c r="C172" s="43"/>
-      <c r="D172" s="43"/>
-      <c r="E172" s="42"/>
+      <c r="A172" s="42"/>
+      <c r="B172" s="43"/>
+      <c r="C172" s="44"/>
+      <c r="D172" s="44"/>
+      <c r="E172" s="43"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="41"/>
-      <c r="B173" s="42"/>
-      <c r="C173" s="43"/>
-      <c r="D173" s="43"/>
-      <c r="E173" s="42"/>
+      <c r="A173" s="42"/>
+      <c r="B173" s="43"/>
+      <c r="C173" s="44"/>
+      <c r="D173" s="44"/>
+      <c r="E173" s="43"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="41"/>
-      <c r="B174" s="42"/>
-      <c r="C174" s="43"/>
-      <c r="D174" s="43"/>
-      <c r="E174" s="42"/>
+      <c r="A174" s="42"/>
+      <c r="B174" s="43"/>
+      <c r="C174" s="44"/>
+      <c r="D174" s="44"/>
+      <c r="E174" s="43"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="41"/>
-      <c r="B175" s="42"/>
-      <c r="C175" s="43"/>
-      <c r="D175" s="43"/>
-      <c r="E175" s="42"/>
+      <c r="A175" s="42"/>
+      <c r="B175" s="43"/>
+      <c r="C175" s="44"/>
+      <c r="D175" s="44"/>
+      <c r="E175" s="43"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="41"/>
-      <c r="B176" s="42"/>
-      <c r="C176" s="43"/>
-      <c r="D176" s="43"/>
-      <c r="E176" s="42"/>
+      <c r="A176" s="42"/>
+      <c r="B176" s="43"/>
+      <c r="C176" s="44"/>
+      <c r="D176" s="44"/>
+      <c r="E176" s="43"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="41"/>
-      <c r="B177" s="42"/>
-      <c r="C177" s="43"/>
-      <c r="D177" s="43"/>
-      <c r="E177" s="42"/>
+      <c r="A177" s="42"/>
+      <c r="B177" s="43"/>
+      <c r="C177" s="44"/>
+      <c r="D177" s="44"/>
+      <c r="E177" s="43"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="41"/>
-      <c r="B178" s="42"/>
-      <c r="C178" s="43"/>
-      <c r="D178" s="43"/>
-      <c r="E178" s="42"/>
+      <c r="A178" s="42"/>
+      <c r="B178" s="43"/>
+      <c r="C178" s="44"/>
+      <c r="D178" s="44"/>
+      <c r="E178" s="43"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="41"/>
-      <c r="B179" s="42"/>
-      <c r="C179" s="43"/>
-      <c r="D179" s="43"/>
-      <c r="E179" s="42"/>
+      <c r="A179" s="42"/>
+      <c r="B179" s="43"/>
+      <c r="C179" s="44"/>
+      <c r="D179" s="44"/>
+      <c r="E179" s="43"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="41"/>
-      <c r="B180" s="42"/>
-      <c r="C180" s="43"/>
-      <c r="D180" s="43"/>
-      <c r="E180" s="42"/>
+      <c r="A180" s="42"/>
+      <c r="B180" s="43"/>
+      <c r="C180" s="44"/>
+      <c r="D180" s="44"/>
+      <c r="E180" s="43"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="41"/>
-      <c r="B181" s="42"/>
-      <c r="C181" s="43"/>
-      <c r="D181" s="43"/>
-      <c r="E181" s="42"/>
+      <c r="A181" s="42"/>
+      <c r="B181" s="43"/>
+      <c r="C181" s="44"/>
+      <c r="D181" s="44"/>
+      <c r="E181" s="43"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="41"/>
-      <c r="B182" s="42"/>
-      <c r="C182" s="43"/>
-      <c r="D182" s="43"/>
-      <c r="E182" s="42"/>
+      <c r="A182" s="42"/>
+      <c r="B182" s="43"/>
+      <c r="C182" s="44"/>
+      <c r="D182" s="44"/>
+      <c r="E182" s="43"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="41"/>
-      <c r="B183" s="42"/>
-      <c r="C183" s="43"/>
-      <c r="D183" s="43"/>
-      <c r="E183" s="42"/>
+      <c r="A183" s="42"/>
+      <c r="B183" s="43"/>
+      <c r="C183" s="44"/>
+      <c r="D183" s="44"/>
+      <c r="E183" s="43"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="41"/>
-      <c r="B184" s="42"/>
-      <c r="C184" s="43"/>
-      <c r="D184" s="43"/>
-      <c r="E184" s="42"/>
+      <c r="A184" s="42"/>
+      <c r="B184" s="43"/>
+      <c r="C184" s="44"/>
+      <c r="D184" s="44"/>
+      <c r="E184" s="43"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="41"/>
-      <c r="B185" s="42"/>
-      <c r="C185" s="43"/>
-      <c r="D185" s="43"/>
-      <c r="E185" s="42"/>
+      <c r="A185" s="42"/>
+      <c r="B185" s="43"/>
+      <c r="C185" s="44"/>
+      <c r="D185" s="44"/>
+      <c r="E185" s="43"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="41"/>
-      <c r="B186" s="42"/>
-      <c r="C186" s="43"/>
-      <c r="D186" s="43"/>
-      <c r="E186" s="42"/>
+      <c r="A186" s="42"/>
+      <c r="B186" s="43"/>
+      <c r="C186" s="44"/>
+      <c r="D186" s="44"/>
+      <c r="E186" s="43"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="41"/>
-      <c r="B187" s="42"/>
-      <c r="C187" s="43"/>
-      <c r="D187" s="43"/>
-      <c r="E187" s="42"/>
+      <c r="A187" s="42"/>
+      <c r="B187" s="43"/>
+      <c r="C187" s="44"/>
+      <c r="D187" s="44"/>
+      <c r="E187" s="43"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="41"/>
-      <c r="B188" s="42"/>
-      <c r="C188" s="43"/>
-      <c r="D188" s="43"/>
-      <c r="E188" s="42"/>
+      <c r="A188" s="42"/>
+      <c r="B188" s="43"/>
+      <c r="C188" s="44"/>
+      <c r="D188" s="44"/>
+      <c r="E188" s="43"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="41"/>
-      <c r="B189" s="42"/>
-      <c r="C189" s="43"/>
-      <c r="D189" s="43"/>
-      <c r="E189" s="42"/>
+      <c r="A189" s="42"/>
+      <c r="B189" s="43"/>
+      <c r="C189" s="44"/>
+      <c r="D189" s="44"/>
+      <c r="E189" s="43"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="41"/>
-      <c r="B190" s="42"/>
-      <c r="C190" s="43"/>
-      <c r="D190" s="43"/>
-      <c r="E190" s="42"/>
+      <c r="A190" s="42"/>
+      <c r="B190" s="43"/>
+      <c r="C190" s="44"/>
+      <c r="D190" s="44"/>
+      <c r="E190" s="43"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="41"/>
-      <c r="B191" s="42"/>
-      <c r="C191" s="43"/>
-      <c r="D191" s="43"/>
-      <c r="E191" s="42"/>
+      <c r="A191" s="42"/>
+      <c r="B191" s="43"/>
+      <c r="C191" s="44"/>
+      <c r="D191" s="44"/>
+      <c r="E191" s="43"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="41"/>
-      <c r="B192" s="42"/>
-      <c r="C192" s="43"/>
-      <c r="D192" s="43"/>
-      <c r="E192" s="42"/>
+      <c r="A192" s="42"/>
+      <c r="B192" s="43"/>
+      <c r="C192" s="44"/>
+      <c r="D192" s="44"/>
+      <c r="E192" s="43"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="41"/>
-      <c r="B193" s="42"/>
-      <c r="C193" s="43"/>
-      <c r="D193" s="43"/>
-      <c r="E193" s="42"/>
+      <c r="A193" s="42"/>
+      <c r="B193" s="43"/>
+      <c r="C193" s="44"/>
+      <c r="D193" s="44"/>
+      <c r="E193" s="43"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="41"/>
-      <c r="B194" s="42"/>
-      <c r="C194" s="43"/>
-      <c r="D194" s="43"/>
-      <c r="E194" s="42"/>
+      <c r="A194" s="42"/>
+      <c r="B194" s="43"/>
+      <c r="C194" s="44"/>
+      <c r="D194" s="44"/>
+      <c r="E194" s="43"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="41"/>
-      <c r="B195" s="42"/>
-      <c r="C195" s="43"/>
-      <c r="D195" s="43"/>
-      <c r="E195" s="42"/>
+      <c r="A195" s="42"/>
+      <c r="B195" s="43"/>
+      <c r="C195" s="44"/>
+      <c r="D195" s="44"/>
+      <c r="E195" s="43"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="41"/>
-      <c r="B196" s="42"/>
-      <c r="C196" s="43"/>
-      <c r="D196" s="43"/>
-      <c r="E196" s="42"/>
+      <c r="A196" s="42"/>
+      <c r="B196" s="43"/>
+      <c r="C196" s="44"/>
+      <c r="D196" s="44"/>
+      <c r="E196" s="43"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="41"/>
-      <c r="B197" s="42"/>
-      <c r="C197" s="43"/>
-      <c r="D197" s="43"/>
-      <c r="E197" s="42"/>
+      <c r="A197" s="42"/>
+      <c r="B197" s="43"/>
+      <c r="C197" s="44"/>
+      <c r="D197" s="44"/>
+      <c r="E197" s="43"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="41"/>
-      <c r="B198" s="42"/>
-      <c r="C198" s="43"/>
-      <c r="D198" s="43"/>
-      <c r="E198" s="42"/>
+      <c r="A198" s="42"/>
+      <c r="B198" s="43"/>
+      <c r="C198" s="44"/>
+      <c r="D198" s="44"/>
+      <c r="E198" s="43"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="41"/>
-      <c r="B199" s="42"/>
-      <c r="C199" s="43"/>
-      <c r="D199" s="43"/>
-      <c r="E199" s="42"/>
+      <c r="A199" s="42"/>
+      <c r="B199" s="43"/>
+      <c r="C199" s="44"/>
+      <c r="D199" s="44"/>
+      <c r="E199" s="43"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="41"/>
-      <c r="B200" s="42"/>
-      <c r="C200" s="43"/>
-      <c r="D200" s="43"/>
-      <c r="E200" s="42"/>
+      <c r="A200" s="42"/>
+      <c r="B200" s="43"/>
+      <c r="C200" s="44"/>
+      <c r="D200" s="44"/>
+      <c r="E200" s="43"/>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="41"/>
-      <c r="B201" s="42"/>
-      <c r="C201" s="43"/>
-      <c r="D201" s="43"/>
-      <c r="E201" s="42"/>
+      <c r="A201" s="42"/>
+      <c r="B201" s="43"/>
+      <c r="C201" s="44"/>
+      <c r="D201" s="44"/>
+      <c r="E201" s="43"/>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="41"/>
-      <c r="B202" s="42"/>
-      <c r="C202" s="43"/>
-      <c r="D202" s="43"/>
-      <c r="E202" s="42"/>
+      <c r="A202" s="42"/>
+      <c r="B202" s="43"/>
+      <c r="C202" s="44"/>
+      <c r="D202" s="44"/>
+      <c r="E202" s="43"/>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="41"/>
-      <c r="B203" s="42"/>
-      <c r="C203" s="43"/>
-      <c r="D203" s="43"/>
-      <c r="E203" s="42"/>
+      <c r="A203" s="42"/>
+      <c r="B203" s="43"/>
+      <c r="C203" s="44"/>
+      <c r="D203" s="44"/>
+      <c r="E203" s="43"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="41"/>
-      <c r="B204" s="42"/>
-      <c r="C204" s="43"/>
-      <c r="D204" s="43"/>
-      <c r="E204" s="42"/>
+      <c r="A204" s="42"/>
+      <c r="B204" s="43"/>
+      <c r="C204" s="44"/>
+      <c r="D204" s="44"/>
+      <c r="E204" s="43"/>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="41"/>
-      <c r="B205" s="42"/>
-      <c r="C205" s="43"/>
-      <c r="D205" s="43"/>
-      <c r="E205" s="42"/>
+      <c r="A205" s="42"/>
+      <c r="B205" s="43"/>
+      <c r="C205" s="44"/>
+      <c r="D205" s="44"/>
+      <c r="E205" s="43"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="41"/>
-      <c r="B206" s="42"/>
-      <c r="C206" s="43"/>
-      <c r="D206" s="43"/>
-      <c r="E206" s="42"/>
+      <c r="A206" s="42"/>
+      <c r="B206" s="43"/>
+      <c r="C206" s="44"/>
+      <c r="D206" s="44"/>
+      <c r="E206" s="43"/>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="41"/>
-      <c r="B207" s="42"/>
-      <c r="C207" s="43"/>
-      <c r="D207" s="43"/>
-      <c r="E207" s="42"/>
+      <c r="A207" s="42"/>
+      <c r="B207" s="43"/>
+      <c r="C207" s="44"/>
+      <c r="D207" s="44"/>
+      <c r="E207" s="43"/>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="41"/>
-      <c r="B208" s="42"/>
-      <c r="C208" s="43"/>
-      <c r="D208" s="43"/>
-      <c r="E208" s="42"/>
+      <c r="A208" s="42"/>
+      <c r="B208" s="43"/>
+      <c r="C208" s="44"/>
+      <c r="D208" s="44"/>
+      <c r="E208" s="43"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="41"/>
-      <c r="B209" s="42"/>
-      <c r="C209" s="43"/>
-      <c r="D209" s="43"/>
-      <c r="E209" s="42"/>
+      <c r="A209" s="42"/>
+      <c r="B209" s="43"/>
+      <c r="C209" s="44"/>
+      <c r="D209" s="44"/>
+      <c r="E209" s="43"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="41"/>
-      <c r="B210" s="42"/>
-      <c r="C210" s="43"/>
-      <c r="D210" s="43"/>
-      <c r="E210" s="42"/>
+      <c r="A210" s="42"/>
+      <c r="B210" s="43"/>
+      <c r="C210" s="44"/>
+      <c r="D210" s="44"/>
+      <c r="E210" s="43"/>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="41"/>
-      <c r="B211" s="42"/>
-      <c r="C211" s="43"/>
-      <c r="D211" s="43"/>
-      <c r="E211" s="42"/>
+      <c r="A211" s="42"/>
+      <c r="B211" s="43"/>
+      <c r="C211" s="44"/>
+      <c r="D211" s="44"/>
+      <c r="E211" s="43"/>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="41"/>
-      <c r="B212" s="42"/>
-      <c r="C212" s="43"/>
-      <c r="D212" s="43"/>
-      <c r="E212" s="42"/>
+      <c r="A212" s="42"/>
+      <c r="B212" s="43"/>
+      <c r="C212" s="44"/>
+      <c r="D212" s="44"/>
+      <c r="E212" s="43"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="41"/>
-      <c r="B213" s="42"/>
-      <c r="C213" s="43"/>
-      <c r="D213" s="43"/>
-      <c r="E213" s="42"/>
+      <c r="A213" s="42"/>
+      <c r="B213" s="43"/>
+      <c r="C213" s="44"/>
+      <c r="D213" s="44"/>
+      <c r="E213" s="43"/>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="41"/>
-      <c r="B214" s="42"/>
-      <c r="C214" s="43"/>
-      <c r="D214" s="43"/>
-      <c r="E214" s="42"/>
+      <c r="A214" s="42"/>
+      <c r="B214" s="43"/>
+      <c r="C214" s="44"/>
+      <c r="D214" s="44"/>
+      <c r="E214" s="43"/>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="41"/>
-      <c r="B215" s="42"/>
-      <c r="C215" s="43"/>
-      <c r="D215" s="43"/>
-      <c r="E215" s="42"/>
+      <c r="A215" s="42"/>
+      <c r="B215" s="43"/>
+      <c r="C215" s="44"/>
+      <c r="D215" s="44"/>
+      <c r="E215" s="43"/>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="41"/>
-      <c r="B216" s="42"/>
-      <c r="C216" s="43"/>
-      <c r="D216" s="43"/>
-      <c r="E216" s="42"/>
+      <c r="A216" s="42"/>
+      <c r="B216" s="43"/>
+      <c r="C216" s="44"/>
+      <c r="D216" s="44"/>
+      <c r="E216" s="43"/>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="41"/>
-      <c r="B217" s="42"/>
-      <c r="C217" s="43"/>
-      <c r="D217" s="43"/>
-      <c r="E217" s="42"/>
+      <c r="A217" s="42"/>
+      <c r="B217" s="43"/>
+      <c r="C217" s="44"/>
+      <c r="D217" s="44"/>
+      <c r="E217" s="43"/>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="41"/>
-      <c r="B218" s="42"/>
-      <c r="C218" s="43"/>
-      <c r="D218" s="43"/>
-      <c r="E218" s="42"/>
+      <c r="A218" s="42"/>
+      <c r="B218" s="43"/>
+      <c r="C218" s="44"/>
+      <c r="D218" s="44"/>
+      <c r="E218" s="43"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="41"/>
-      <c r="B219" s="42"/>
-      <c r="C219" s="43"/>
-      <c r="D219" s="43"/>
-      <c r="E219" s="42"/>
+      <c r="A219" s="42"/>
+      <c r="B219" s="43"/>
+      <c r="C219" s="44"/>
+      <c r="D219" s="44"/>
+      <c r="E219" s="43"/>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="41"/>
-      <c r="B220" s="42"/>
-      <c r="C220" s="43"/>
-      <c r="D220" s="43"/>
-      <c r="E220" s="42"/>
+      <c r="A220" s="42"/>
+      <c r="B220" s="43"/>
+      <c r="C220" s="44"/>
+      <c r="D220" s="44"/>
+      <c r="E220" s="43"/>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="41"/>
-      <c r="B221" s="42"/>
-      <c r="C221" s="43"/>
-      <c r="D221" s="43"/>
-      <c r="E221" s="42"/>
+      <c r="A221" s="42"/>
+      <c r="B221" s="43"/>
+      <c r="C221" s="44"/>
+      <c r="D221" s="44"/>
+      <c r="E221" s="43"/>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="41"/>
-      <c r="B222" s="42"/>
-      <c r="C222" s="43"/>
-      <c r="D222" s="43"/>
-      <c r="E222" s="42"/>
+      <c r="A222" s="42"/>
+      <c r="B222" s="43"/>
+      <c r="C222" s="44"/>
+      <c r="D222" s="44"/>
+      <c r="E222" s="43"/>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="41"/>
-      <c r="B223" s="42"/>
-      <c r="C223" s="43"/>
-      <c r="D223" s="43"/>
-      <c r="E223" s="42"/>
+      <c r="A223" s="42"/>
+      <c r="B223" s="43"/>
+      <c r="C223" s="44"/>
+      <c r="D223" s="44"/>
+      <c r="E223" s="43"/>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="41"/>
-      <c r="B224" s="42"/>
-      <c r="C224" s="43"/>
-      <c r="D224" s="43"/>
-      <c r="E224" s="42"/>
+      <c r="A224" s="42"/>
+      <c r="B224" s="43"/>
+      <c r="C224" s="44"/>
+      <c r="D224" s="44"/>
+      <c r="E224" s="43"/>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="41"/>
-      <c r="B225" s="42"/>
-      <c r="C225" s="43"/>
-      <c r="D225" s="43"/>
-      <c r="E225" s="42"/>
+      <c r="A225" s="42"/>
+      <c r="B225" s="43"/>
+      <c r="C225" s="44"/>
+      <c r="D225" s="44"/>
+      <c r="E225" s="43"/>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="41"/>
-      <c r="B226" s="42"/>
-      <c r="C226" s="43"/>
-      <c r="D226" s="43"/>
-      <c r="E226" s="42"/>
+      <c r="A226" s="42"/>
+      <c r="B226" s="43"/>
+      <c r="C226" s="44"/>
+      <c r="D226" s="44"/>
+      <c r="E226" s="43"/>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="41"/>
-      <c r="B227" s="42"/>
-      <c r="C227" s="43"/>
-      <c r="D227" s="43"/>
-      <c r="E227" s="42"/>
+      <c r="A227" s="42"/>
+      <c r="B227" s="43"/>
+      <c r="C227" s="44"/>
+      <c r="D227" s="44"/>
+      <c r="E227" s="43"/>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="41"/>
-      <c r="B228" s="42"/>
-      <c r="C228" s="43"/>
-      <c r="D228" s="43"/>
-      <c r="E228" s="42"/>
+      <c r="A228" s="42"/>
+      <c r="B228" s="43"/>
+      <c r="C228" s="44"/>
+      <c r="D228" s="44"/>
+      <c r="E228" s="43"/>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="41"/>
-      <c r="B229" s="42"/>
-      <c r="C229" s="43"/>
-      <c r="D229" s="43"/>
-      <c r="E229" s="42"/>
+      <c r="A229" s="42"/>
+      <c r="B229" s="43"/>
+      <c r="C229" s="44"/>
+      <c r="D229" s="44"/>
+      <c r="E229" s="43"/>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="41"/>
-      <c r="B230" s="42"/>
-      <c r="C230" s="43"/>
-      <c r="D230" s="43"/>
-      <c r="E230" s="42"/>
+      <c r="A230" s="42"/>
+      <c r="B230" s="43"/>
+      <c r="C230" s="44"/>
+      <c r="D230" s="44"/>
+      <c r="E230" s="43"/>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="41"/>
-      <c r="B231" s="42"/>
-      <c r="C231" s="43"/>
-      <c r="D231" s="43"/>
-      <c r="E231" s="42"/>
+      <c r="A231" s="42"/>
+      <c r="B231" s="43"/>
+      <c r="C231" s="44"/>
+      <c r="D231" s="44"/>
+      <c r="E231" s="43"/>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="41"/>
-      <c r="B232" s="42"/>
-      <c r="C232" s="43"/>
-      <c r="D232" s="43"/>
-      <c r="E232" s="42"/>
+      <c r="A232" s="42"/>
+      <c r="B232" s="43"/>
+      <c r="C232" s="44"/>
+      <c r="D232" s="44"/>
+      <c r="E232" s="43"/>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="41"/>
-      <c r="B233" s="42"/>
-      <c r="C233" s="43"/>
-      <c r="D233" s="43"/>
-      <c r="E233" s="42"/>
+      <c r="A233" s="42"/>
+      <c r="B233" s="43"/>
+      <c r="C233" s="44"/>
+      <c r="D233" s="44"/>
+      <c r="E233" s="43"/>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="41"/>
-      <c r="B234" s="42"/>
-      <c r="C234" s="43"/>
-      <c r="D234" s="43"/>
-      <c r="E234" s="42"/>
+      <c r="A234" s="42"/>
+      <c r="B234" s="43"/>
+      <c r="C234" s="44"/>
+      <c r="D234" s="44"/>
+      <c r="E234" s="43"/>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="41"/>
-      <c r="B235" s="42"/>
-      <c r="C235" s="43"/>
-      <c r="D235" s="43"/>
-      <c r="E235" s="42"/>
+      <c r="A235" s="42"/>
+      <c r="B235" s="43"/>
+      <c r="C235" s="44"/>
+      <c r="D235" s="44"/>
+      <c r="E235" s="43"/>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="41"/>
-      <c r="B236" s="42"/>
-      <c r="C236" s="43"/>
-      <c r="D236" s="43"/>
-      <c r="E236" s="42"/>
+      <c r="A236" s="42"/>
+      <c r="B236" s="43"/>
+      <c r="C236" s="44"/>
+      <c r="D236" s="44"/>
+      <c r="E236" s="43"/>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="41"/>
-      <c r="B237" s="42"/>
-      <c r="C237" s="43"/>
-      <c r="D237" s="43"/>
-      <c r="E237" s="42"/>
+      <c r="A237" s="42"/>
+      <c r="B237" s="43"/>
+      <c r="C237" s="44"/>
+      <c r="D237" s="44"/>
+      <c r="E237" s="43"/>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="41"/>
-      <c r="B238" s="42"/>
-      <c r="C238" s="43"/>
-      <c r="D238" s="43"/>
-      <c r="E238" s="42"/>
+      <c r="A238" s="42"/>
+      <c r="B238" s="43"/>
+      <c r="C238" s="44"/>
+      <c r="D238" s="44"/>
+      <c r="E238" s="43"/>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="41"/>
-      <c r="B239" s="42"/>
-      <c r="C239" s="43"/>
-      <c r="D239" s="43"/>
-      <c r="E239" s="42"/>
+      <c r="A239" s="42"/>
+      <c r="B239" s="43"/>
+      <c r="C239" s="44"/>
+      <c r="D239" s="44"/>
+      <c r="E239" s="43"/>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="41"/>
-      <c r="B240" s="42"/>
-      <c r="C240" s="43"/>
-      <c r="D240" s="43"/>
-      <c r="E240" s="42"/>
+      <c r="A240" s="42"/>
+      <c r="B240" s="43"/>
+      <c r="C240" s="44"/>
+      <c r="D240" s="44"/>
+      <c r="E240" s="43"/>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="41"/>
-      <c r="B241" s="42"/>
-      <c r="C241" s="43"/>
-      <c r="D241" s="43"/>
-      <c r="E241" s="42"/>
+      <c r="A241" s="42"/>
+      <c r="B241" s="43"/>
+      <c r="C241" s="44"/>
+      <c r="D241" s="44"/>
+      <c r="E241" s="43"/>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="41"/>
-      <c r="B242" s="42"/>
-      <c r="C242" s="43"/>
-      <c r="D242" s="43"/>
-      <c r="E242" s="42"/>
+      <c r="A242" s="42"/>
+      <c r="B242" s="43"/>
+      <c r="C242" s="44"/>
+      <c r="D242" s="44"/>
+      <c r="E242" s="43"/>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="41"/>
-      <c r="B243" s="42"/>
-      <c r="C243" s="43"/>
-      <c r="D243" s="43"/>
-      <c r="E243" s="42"/>
+      <c r="A243" s="42"/>
+      <c r="B243" s="43"/>
+      <c r="C243" s="44"/>
+      <c r="D243" s="44"/>
+      <c r="E243" s="43"/>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="41"/>
-      <c r="B244" s="42"/>
-      <c r="C244" s="43"/>
-      <c r="D244" s="43"/>
-      <c r="E244" s="42"/>
+      <c r="A244" s="42"/>
+      <c r="B244" s="43"/>
+      <c r="C244" s="44"/>
+      <c r="D244" s="44"/>
+      <c r="E244" s="43"/>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="41"/>
-      <c r="B245" s="42"/>
-      <c r="C245" s="43"/>
-      <c r="D245" s="43"/>
-      <c r="E245" s="42"/>
+      <c r="A245" s="42"/>
+      <c r="B245" s="43"/>
+      <c r="C245" s="44"/>
+      <c r="D245" s="44"/>
+      <c r="E245" s="43"/>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="41"/>
-      <c r="B246" s="42"/>
-      <c r="C246" s="43"/>
-      <c r="D246" s="43"/>
-      <c r="E246" s="42"/>
+      <c r="A246" s="42"/>
+      <c r="B246" s="43"/>
+      <c r="C246" s="44"/>
+      <c r="D246" s="44"/>
+      <c r="E246" s="43"/>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="41"/>
-      <c r="B247" s="42"/>
-      <c r="C247" s="43"/>
-      <c r="D247" s="43"/>
-      <c r="E247" s="42"/>
+      <c r="A247" s="42"/>
+      <c r="B247" s="43"/>
+      <c r="C247" s="44"/>
+      <c r="D247" s="44"/>
+      <c r="E247" s="43"/>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="41"/>
-      <c r="B248" s="42"/>
-      <c r="C248" s="43"/>
-      <c r="D248" s="43"/>
-      <c r="E248" s="42"/>
+      <c r="A248" s="42"/>
+      <c r="B248" s="43"/>
+      <c r="C248" s="44"/>
+      <c r="D248" s="44"/>
+      <c r="E248" s="43"/>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="41"/>
-      <c r="B249" s="42"/>
-      <c r="C249" s="43"/>
-      <c r="D249" s="43"/>
-      <c r="E249" s="42"/>
+      <c r="A249" s="42"/>
+      <c r="B249" s="43"/>
+      <c r="C249" s="44"/>
+      <c r="D249" s="44"/>
+      <c r="E249" s="43"/>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="41"/>
-      <c r="B250" s="42"/>
-      <c r="C250" s="43"/>
-      <c r="D250" s="43"/>
-      <c r="E250" s="42"/>
+      <c r="A250" s="42"/>
+      <c r="B250" s="43"/>
+      <c r="C250" s="44"/>
+      <c r="D250" s="44"/>
+      <c r="E250" s="43"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true" password="df10" objects="true" scenarios="true" autoFilter="false"/>
@@ -6868,358 +6946,368 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="C4" s="39" t="s">
-        <v>120</v>
+      <c r="A4" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" s="40" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="45" t="n">
+      <c r="A5" s="46" t="n">
         <f aca="false">Stock!$H$70</f>
         <v>107750</v>
       </c>
-      <c r="C5" s="46" t="str">
+      <c r="C5" s="47" t="str">
         <f aca="false">IF(Stock!$J$70="","—",Stock!$J$70)</f>
         <v>—</v>
       </c>
+      <c r="E5" s="48" t="str">
+        <f aca="false">IF(OR(Stock!$C$4="",Stock!$J$70=""),"—",Stock!$J$70/Stock!$C$4)</f>
+        <v>—</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>122</v>
+      <c r="A6" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>54</v>
+      <c r="A8" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="17" t="n">
+      <c r="A9" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="18" t="n">
         <f aca="false">IF($A9="","",SUMIF(Stock!$A$8:$A$69,$A9,Stock!$C$8:$C$69))</f>
         <v>28645</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <f aca="false">IF($A9="","",SUMIF(Stock!$A$8:$A$69,$A9,Stock!$D$8:$D$69))</f>
         <v>1400</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <f aca="false">IF($A9="","",SUMIF(Stock!$A$8:$A$69,$A9,Stock!$E$8:$E$69))</f>
         <v>0</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="19" t="n">
         <f aca="false">IF($A9="","",SUMIF(Stock!$A$8:$A$69,$A9,Stock!$H$8:$H$69))</f>
         <v>30045</v>
       </c>
-      <c r="F9" s="20" t="str">
+      <c r="F9" s="21" t="str">
         <f aca="false">IF(OR($A9="",SUMIF(Stock!$A$8:$A$69,$A9,Stock!$J$8:$J$69)=0),"",SUMIF(Stock!$A$8:$A$69,$A9,Stock!$J$8:$J$69))</f>
         <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" s="25" t="n">
+      <c r="A10" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="26" t="n">
         <f aca="false">IF($A10="","",SUMIF(Stock!$A$8:$A$69,$A10,Stock!$C$8:$C$69))</f>
         <v>29316</v>
       </c>
-      <c r="C10" s="24" t="n">
+      <c r="C10" s="25" t="n">
         <f aca="false">IF($A10="","",SUMIF(Stock!$A$8:$A$69,$A10,Stock!$D$8:$D$69))</f>
         <v>956</v>
       </c>
-      <c r="D10" s="24" t="n">
+      <c r="D10" s="25" t="n">
         <f aca="false">IF($A10="","",SUMIF(Stock!$A$8:$A$69,$A10,Stock!$E$8:$E$69))</f>
         <v>0</v>
       </c>
-      <c r="E10" s="26" t="n">
+      <c r="E10" s="27" t="n">
         <f aca="false">IF($A10="","",SUMIF(Stock!$A$8:$A$69,$A10,Stock!$H$8:$H$69))</f>
         <v>30272</v>
       </c>
-      <c r="F10" s="27" t="str">
+      <c r="F10" s="28" t="str">
         <f aca="false">IF(OR($A10="",SUMIF(Stock!$A$8:$A$69,$A10,Stock!$J$8:$J$69)=0),"",SUMIF(Stock!$A$8:$A$69,$A10,Stock!$J$8:$J$69))</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="B11" s="17" t="n">
+      <c r="A11" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="18" t="n">
         <f aca="false">IF($A11="","",SUMIF(Stock!$A$8:$A$69,$A11,Stock!$C$8:$C$69))</f>
         <v>26619</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <f aca="false">IF($A11="","",SUMIF(Stock!$A$8:$A$69,$A11,Stock!$D$8:$D$69))</f>
         <v>52</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <f aca="false">IF($A11="","",SUMIF(Stock!$A$8:$A$69,$A11,Stock!$E$8:$E$69))</f>
         <v>0</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="19" t="n">
         <f aca="false">IF($A11="","",SUMIF(Stock!$A$8:$A$69,$A11,Stock!$H$8:$H$69))</f>
         <v>26671</v>
       </c>
-      <c r="F11" s="20" t="str">
+      <c r="F11" s="21" t="str">
         <f aca="false">IF(OR($A11="",SUMIF(Stock!$A$8:$A$69,$A11,Stock!$J$8:$J$69)=0),"",SUMIF(Stock!$A$8:$A$69,$A11,Stock!$J$8:$J$69))</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="B12" s="25" t="n">
+      <c r="A12" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="26" t="n">
         <f aca="false">IF($A12="","",SUMIF(Stock!$A$8:$A$69,$A12,Stock!$C$8:$C$69))</f>
         <v>1534</v>
       </c>
-      <c r="C12" s="24" t="n">
+      <c r="C12" s="25" t="n">
         <f aca="false">IF($A12="","",SUMIF(Stock!$A$8:$A$69,$A12,Stock!$D$8:$D$69))</f>
         <v>0</v>
       </c>
-      <c r="D12" s="24" t="n">
+      <c r="D12" s="25" t="n">
         <f aca="false">IF($A12="","",SUMIF(Stock!$A$8:$A$69,$A12,Stock!$E$8:$E$69))</f>
         <v>0</v>
       </c>
-      <c r="E12" s="26" t="n">
+      <c r="E12" s="27" t="n">
         <f aca="false">IF($A12="","",SUMIF(Stock!$A$8:$A$69,$A12,Stock!$H$8:$H$69))</f>
         <v>1534</v>
       </c>
-      <c r="F12" s="27" t="str">
+      <c r="F12" s="28" t="str">
         <f aca="false">IF(OR($A12="",SUMIF(Stock!$A$8:$A$69,$A12,Stock!$J$8:$J$69)=0),"",SUMIF(Stock!$A$8:$A$69,$A12,Stock!$J$8:$J$69))</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="B13" s="17" t="n">
+      <c r="A13" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" s="18" t="n">
         <f aca="false">IF($A13="","",SUMIF(Stock!$A$8:$A$69,$A13,Stock!$C$8:$C$69))</f>
         <v>13126</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <f aca="false">IF($A13="","",SUMIF(Stock!$A$8:$A$69,$A13,Stock!$D$8:$D$69))</f>
         <v>2472</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <f aca="false">IF($A13="","",SUMIF(Stock!$A$8:$A$69,$A13,Stock!$E$8:$E$69))</f>
         <v>0</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="19" t="n">
         <f aca="false">IF($A13="","",SUMIF(Stock!$A$8:$A$69,$A13,Stock!$H$8:$H$69))</f>
         <v>15598</v>
       </c>
-      <c r="F13" s="20" t="str">
+      <c r="F13" s="21" t="str">
         <f aca="false">IF(OR($A13="",SUMIF(Stock!$A$8:$A$69,$A13,Stock!$J$8:$J$69)=0),"",SUMIF(Stock!$A$8:$A$69,$A13,Stock!$J$8:$J$69))</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="B14" s="25" t="n">
+      <c r="A14" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="26" t="n">
         <f aca="false">IF($A14="","",SUMIF(Stock!$A$8:$A$69,$A14,Stock!$C$8:$C$69))</f>
         <v>670</v>
       </c>
-      <c r="C14" s="24" t="n">
+      <c r="C14" s="25" t="n">
         <f aca="false">IF($A14="","",SUMIF(Stock!$A$8:$A$69,$A14,Stock!$D$8:$D$69))</f>
         <v>0</v>
       </c>
-      <c r="D14" s="24" t="n">
+      <c r="D14" s="25" t="n">
         <f aca="false">IF($A14="","",SUMIF(Stock!$A$8:$A$69,$A14,Stock!$E$8:$E$69))</f>
         <v>0</v>
       </c>
-      <c r="E14" s="26" t="n">
+      <c r="E14" s="27" t="n">
         <f aca="false">IF($A14="","",SUMIF(Stock!$A$8:$A$69,$A14,Stock!$H$8:$H$69))</f>
         <v>670</v>
       </c>
-      <c r="F14" s="27" t="str">
+      <c r="F14" s="28" t="str">
         <f aca="false">IF(OR($A14="",SUMIF(Stock!$A$8:$A$69,$A14,Stock!$J$8:$J$69)=0),"",SUMIF(Stock!$A$8:$A$69,$A14,Stock!$J$8:$J$69))</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="B15" s="17" t="n">
+      <c r="A15" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" s="18" t="n">
         <f aca="false">IF($A15="","",SUMIF(Stock!$A$8:$A$69,$A15,Stock!$C$8:$C$69))</f>
         <v>2960</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <f aca="false">IF($A15="","",SUMIF(Stock!$A$8:$A$69,$A15,Stock!$D$8:$D$69))</f>
         <v>0</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <f aca="false">IF($A15="","",SUMIF(Stock!$A$8:$A$69,$A15,Stock!$E$8:$E$69))</f>
         <v>0</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="19" t="n">
         <f aca="false">IF($A15="","",SUMIF(Stock!$A$8:$A$69,$A15,Stock!$H$8:$H$69))</f>
         <v>2960</v>
       </c>
-      <c r="F15" s="20" t="str">
+      <c r="F15" s="21" t="str">
         <f aca="false">IF(OR($A15="",SUMIF(Stock!$A$8:$A$69,$A15,Stock!$J$8:$J$69)=0),"",SUMIF(Stock!$A$8:$A$69,$A15,Stock!$J$8:$J$69))</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="B16" s="25" t="n">
+      <c r="A16" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="B16" s="26" t="n">
         <f aca="false">IF($A16="","",SUMIF(Stock!$A$8:$A$69,$A16,Stock!$C$8:$C$69))</f>
         <v>0</v>
       </c>
-      <c r="C16" s="24" t="n">
+      <c r="C16" s="25" t="n">
         <f aca="false">IF($A16="","",SUMIF(Stock!$A$8:$A$69,$A16,Stock!$D$8:$D$69))</f>
         <v>0</v>
       </c>
-      <c r="D16" s="24" t="n">
+      <c r="D16" s="25" t="n">
         <f aca="false">IF($A16="","",SUMIF(Stock!$A$8:$A$69,$A16,Stock!$E$8:$E$69))</f>
         <v>0</v>
       </c>
-      <c r="E16" s="26" t="n">
+      <c r="E16" s="27" t="n">
         <f aca="false">IF($A16="","",SUMIF(Stock!$A$8:$A$69,$A16,Stock!$H$8:$H$69))</f>
         <v>0</v>
       </c>
-      <c r="F16" s="27" t="str">
+      <c r="F16" s="28" t="str">
         <f aca="false">IF(OR($A16="",SUMIF(Stock!$A$8:$A$69,$A16,Stock!$J$8:$J$69)=0),"",SUMIF(Stock!$A$8:$A$69,$A16,Stock!$J$8:$J$69))</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="28"/>
-      <c r="B17" s="17" t="str">
+      <c r="A17" s="29"/>
+      <c r="B17" s="18" t="str">
         <f aca="false">IF($A17="","",SUMIF(Stock!$A$8:$A$69,$A17,Stock!$C$8:$C$69))</f>
         <v/>
       </c>
-      <c r="C17" s="16" t="str">
+      <c r="C17" s="17" t="str">
         <f aca="false">IF($A17="","",SUMIF(Stock!$A$8:$A$69,$A17,Stock!$D$8:$D$69))</f>
         <v/>
       </c>
-      <c r="D17" s="16" t="str">
+      <c r="D17" s="17" t="str">
         <f aca="false">IF($A17="","",SUMIF(Stock!$A$8:$A$69,$A17,Stock!$E$8:$E$69))</f>
         <v/>
       </c>
-      <c r="E17" s="18" t="str">
+      <c r="E17" s="19" t="str">
         <f aca="false">IF($A17="","",SUMIF(Stock!$A$8:$A$69,$A17,Stock!$H$8:$H$69))</f>
         <v/>
       </c>
-      <c r="F17" s="20" t="str">
+      <c r="F17" s="21" t="str">
         <f aca="false">IF(OR($A17="",SUMIF(Stock!$A$8:$A$69,$A17,Stock!$J$8:$J$69)=0),"",SUMIF(Stock!$A$8:$A$69,$A17,Stock!$J$8:$J$69))</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="30"/>
-      <c r="B18" s="25" t="str">
+      <c r="A18" s="31"/>
+      <c r="B18" s="26" t="str">
         <f aca="false">IF($A18="","",SUMIF(Stock!$A$8:$A$69,$A18,Stock!$C$8:$C$69))</f>
         <v/>
       </c>
-      <c r="C18" s="24" t="str">
+      <c r="C18" s="25" t="str">
         <f aca="false">IF($A18="","",SUMIF(Stock!$A$8:$A$69,$A18,Stock!$D$8:$D$69))</f>
         <v/>
       </c>
-      <c r="D18" s="24" t="str">
+      <c r="D18" s="25" t="str">
         <f aca="false">IF($A18="","",SUMIF(Stock!$A$8:$A$69,$A18,Stock!$E$8:$E$69))</f>
         <v/>
       </c>
-      <c r="E18" s="26" t="str">
+      <c r="E18" s="27" t="str">
         <f aca="false">IF($A18="","",SUMIF(Stock!$A$8:$A$69,$A18,Stock!$H$8:$H$69))</f>
         <v/>
       </c>
-      <c r="F18" s="27" t="str">
+      <c r="F18" s="28" t="str">
         <f aca="false">IF(OR($A18="",SUMIF(Stock!$A$8:$A$69,$A18,Stock!$J$8:$J$69)=0),"",SUMIF(Stock!$A$8:$A$69,$A18,Stock!$J$8:$J$69))</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="28"/>
-      <c r="B19" s="17" t="str">
+      <c r="A19" s="29"/>
+      <c r="B19" s="18" t="str">
         <f aca="false">IF($A19="","",SUMIF(Stock!$A$8:$A$69,$A19,Stock!$C$8:$C$69))</f>
         <v/>
       </c>
-      <c r="C19" s="16" t="str">
+      <c r="C19" s="17" t="str">
         <f aca="false">IF($A19="","",SUMIF(Stock!$A$8:$A$69,$A19,Stock!$D$8:$D$69))</f>
         <v/>
       </c>
-      <c r="D19" s="16" t="str">
+      <c r="D19" s="17" t="str">
         <f aca="false">IF($A19="","",SUMIF(Stock!$A$8:$A$69,$A19,Stock!$E$8:$E$69))</f>
         <v/>
       </c>
-      <c r="E19" s="18" t="str">
+      <c r="E19" s="19" t="str">
         <f aca="false">IF($A19="","",SUMIF(Stock!$A$8:$A$69,$A19,Stock!$H$8:$H$69))</f>
         <v/>
       </c>
-      <c r="F19" s="20" t="str">
+      <c r="F19" s="21" t="str">
         <f aca="false">IF(OR($A19="",SUMIF(Stock!$A$8:$A$69,$A19,Stock!$J$8:$J$69)=0),"",SUMIF(Stock!$A$8:$A$69,$A19,Stock!$J$8:$J$69))</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="32" t="s">
-        <v>92</v>
-      </c>
-      <c r="B20" s="33" t="n">
+      <c r="A20" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20" s="34" t="n">
         <f aca="false">SUM(B9:B19)</f>
         <v>102870</v>
       </c>
-      <c r="C20" s="34" t="n">
+      <c r="C20" s="35" t="n">
         <f aca="false">SUM(C9:C19)</f>
         <v>4880</v>
       </c>
-      <c r="D20" s="34" t="n">
+      <c r="D20" s="35" t="n">
         <f aca="false">SUM(D9:D19)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="33" t="n">
+      <c r="E20" s="34" t="n">
         <f aca="false">SUM(E9:E19)</f>
         <v>107750</v>
       </c>
-      <c r="F20" s="35" t="str">
+      <c r="F20" s="36" t="str">
         <f aca="false">IF(SUM(F9:F19)=0,"",SUM(F9:F19))</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="40" t="str">
+      <c r="A22" s="41" t="str">
         <f aca="false">IF(ROUND(SUM($E$9:$E$19),2)&lt;&gt;ROUND(Stock!$H$70,2),"A brand used on Stock is missing from this list — type it into a blank row above, or the totals understate the stock.","")</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -7252,1034 +7340,1035 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="47" t="s">
-        <v>125</v>
-      </c>
-      <c r="E1" s="48" t="s">
-        <v>126</v>
-      </c>
-      <c r="F1" s="48"/>
+      <c r="B1" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="E1" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1" s="50"/>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E2" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="F2" s="48"/>
+      <c r="E2" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="F2" s="50"/>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E3" s="48" t="s">
-        <v>128</v>
-      </c>
-      <c r="F3" s="48"/>
+      <c r="E3" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="F3" s="50"/>
     </row>
     <row r="4" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="49"/>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="50" t="s">
-        <v>129</v>
-      </c>
-      <c r="E5" s="51" t="n">
+      <c r="A5" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="E5" s="53" t="n">
         <f aca="false">Stock!$C$3</f>
         <v>46254</v>
       </c>
-      <c r="F5" s="51"/>
+      <c r="F5" s="53"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="52" t="s">
-        <v>130</v>
-      </c>
-      <c r="E6" s="53" t="s">
-        <v>131</v>
-      </c>
-      <c r="F6" s="53"/>
+      <c r="A6" s="54" t="s">
+        <v>140</v>
+      </c>
+      <c r="E6" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="F6" s="55"/>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="54" t="s">
-        <v>132</v>
-      </c>
-      <c r="B8" s="54" t="s">
-        <v>133</v>
-      </c>
-      <c r="C8" s="54" t="s">
-        <v>134</v>
-      </c>
-      <c r="D8" s="54" t="s">
-        <v>135</v>
-      </c>
-      <c r="E8" s="55" t="s">
-        <v>136</v>
-      </c>
-      <c r="F8" s="55"/>
+      <c r="A8" s="56" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="56" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="56" t="s">
+        <v>144</v>
+      </c>
+      <c r="D8" s="56" t="s">
+        <v>145</v>
+      </c>
+      <c r="E8" s="57" t="str">
+        <f aca="false">IF(Stock!$C$4="","STOCK VALUE (₹)","STOCK VALUE (₹) AT "&amp;TEXT(Stock!$C$4,"0.00")&amp;" / US$")</f>
+        <v>STOCK VALUE (₹)</v>
+      </c>
+      <c r="F8" s="57"/>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="56" t="n">
+      <c r="A9" s="58" t="n">
         <f aca="false">Stock!$C$70</f>
         <v>102870</v>
       </c>
-      <c r="B9" s="57" t="n">
+      <c r="B9" s="59" t="n">
         <f aca="false">Stock!$D$70</f>
         <v>4880</v>
       </c>
-      <c r="C9" s="57" t="n">
+      <c r="C9" s="59" t="n">
         <f aca="false">Stock!$E$70</f>
         <v>0</v>
       </c>
-      <c r="D9" s="56" t="n">
+      <c r="D9" s="58" t="n">
         <f aca="false">Stock!$H$70</f>
         <v>107750</v>
       </c>
-      <c r="E9" s="58" t="str">
-        <f aca="false">IF(Stock!$J$70="","Rate not entered",Stock!$J$70)</f>
-        <v>Rate not entered</v>
-      </c>
-      <c r="F9" s="58"/>
+      <c r="E9" s="60" t="str">
+        <f aca="false">IF(Stock!$C$4="","Exchange rate not set",IF(Stock!$J$70="","Export rates not entered",Stock!$J$70))</f>
+        <v>Exchange rate not set</v>
+      </c>
+      <c r="F9" s="60"/>
     </row>
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="59" t="str">
+      <c r="A10" s="61" t="str">
         <f aca="false">IF(ROUND(Summary!$E$20,2)&lt;&gt;ROUND(Stock!$H$70,2),"A brand on Stock is missing from the Summary list — this report understates the total. Add it before sending.","")</f>
         <v/>
       </c>
-      <c r="B10" s="59"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
+      <c r="B10" s="61"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="60" t="s">
-        <v>137</v>
-      </c>
-      <c r="B11" s="60"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
+      <c r="A11" s="62" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11" s="62"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="61" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="62" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="62" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="62" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" s="62" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12" s="62" t="s">
-        <v>54</v>
+      <c r="A12" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="64" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="64" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="64" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="63" t="str">
+      <c r="A13" s="65" t="str">
         <f aca="false">IF(Summary!$A$9="","",Summary!$A$9)</f>
         <v>Blue Dolphin</v>
       </c>
-      <c r="B13" s="64" t="n">
+      <c r="B13" s="66" t="n">
         <f aca="false">IF(Summary!$A$9="","",Summary!$B$9)</f>
         <v>28645</v>
       </c>
-      <c r="C13" s="65" t="n">
+      <c r="C13" s="67" t="n">
         <f aca="false">IF(Summary!$A$9="","",Summary!$C$9)</f>
         <v>1400</v>
       </c>
-      <c r="D13" s="65" t="n">
+      <c r="D13" s="67" t="n">
         <f aca="false">IF(Summary!$A$9="","",Summary!$D$9)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="66" t="n">
+      <c r="E13" s="68" t="n">
         <f aca="false">IF(Summary!$A$9="","",Summary!$E$9)</f>
         <v>30045</v>
       </c>
-      <c r="F13" s="67" t="str">
+      <c r="F13" s="69" t="str">
         <f aca="false">IF(Summary!$A$9="","",Summary!$F$9)</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="68" t="str">
+      <c r="A14" s="70" t="str">
         <f aca="false">IF(Summary!$A$10="","",Summary!$A$10)</f>
         <v>Primus Japan</v>
       </c>
-      <c r="B14" s="69" t="n">
+      <c r="B14" s="71" t="n">
         <f aca="false">IF(Summary!$A$10="","",Summary!$B$10)</f>
         <v>29316</v>
       </c>
-      <c r="C14" s="70" t="n">
+      <c r="C14" s="72" t="n">
         <f aca="false">IF(Summary!$A$10="","",Summary!$C$10)</f>
         <v>956</v>
       </c>
-      <c r="D14" s="70" t="n">
+      <c r="D14" s="72" t="n">
         <f aca="false">IF(Summary!$A$10="","",Summary!$D$10)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="71" t="n">
+      <c r="E14" s="73" t="n">
         <f aca="false">IF(Summary!$A$10="","",Summary!$E$10)</f>
         <v>30272</v>
       </c>
-      <c r="F14" s="72" t="str">
+      <c r="F14" s="74" t="str">
         <f aca="false">IF(Summary!$A$10="","",Summary!$F$10)</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="63" t="str">
+      <c r="A15" s="65" t="str">
         <f aca="false">IF(Summary!$A$11="","",Summary!$A$11)</f>
         <v>Primus EU</v>
       </c>
-      <c r="B15" s="64" t="n">
+      <c r="B15" s="66" t="n">
         <f aca="false">IF(Summary!$A$11="","",Summary!$B$11)</f>
         <v>26619</v>
       </c>
-      <c r="C15" s="65" t="n">
+      <c r="C15" s="67" t="n">
         <f aca="false">IF(Summary!$A$11="","",Summary!$C$11)</f>
         <v>52</v>
       </c>
-      <c r="D15" s="65" t="n">
+      <c r="D15" s="67" t="n">
         <f aca="false">IF(Summary!$A$11="","",Summary!$D$11)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="66" t="n">
+      <c r="E15" s="68" t="n">
         <f aca="false">IF(Summary!$A$11="","",Summary!$E$11)</f>
         <v>26671</v>
       </c>
-      <c r="F15" s="67" t="str">
+      <c r="F15" s="69" t="str">
         <f aca="false">IF(Summary!$A$11="","",Summary!$F$11)</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="68" t="str">
+      <c r="A16" s="70" t="str">
         <f aca="false">IF(Summary!$A$12="","",Summary!$A$12)</f>
         <v>AMF Brand</v>
       </c>
-      <c r="B16" s="69" t="n">
+      <c r="B16" s="71" t="n">
         <f aca="false">IF(Summary!$A$12="","",Summary!$B$12)</f>
         <v>1534</v>
       </c>
-      <c r="C16" s="70" t="n">
+      <c r="C16" s="72" t="n">
         <f aca="false">IF(Summary!$A$12="","",Summary!$C$12)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="70" t="n">
+      <c r="D16" s="72" t="n">
         <f aca="false">IF(Summary!$A$12="","",Summary!$D$12)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="71" t="n">
+      <c r="E16" s="73" t="n">
         <f aca="false">IF(Summary!$A$12="","",Summary!$E$12)</f>
         <v>1534</v>
       </c>
-      <c r="F16" s="72" t="str">
+      <c r="F16" s="74" t="str">
         <f aca="false">IF(Summary!$A$12="","",Summary!$F$12)</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="63" t="str">
+      <c r="A17" s="65" t="str">
         <f aca="false">IF(Summary!$A$13="","",Summary!$A$13)</f>
         <v>THT Brand</v>
       </c>
-      <c r="B17" s="64" t="n">
+      <c r="B17" s="66" t="n">
         <f aca="false">IF(Summary!$A$13="","",Summary!$B$13)</f>
         <v>13126</v>
       </c>
-      <c r="C17" s="65" t="n">
+      <c r="C17" s="67" t="n">
         <f aca="false">IF(Summary!$A$13="","",Summary!$C$13)</f>
         <v>2472</v>
       </c>
-      <c r="D17" s="65" t="n">
+      <c r="D17" s="67" t="n">
         <f aca="false">IF(Summary!$A$13="","",Summary!$D$13)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="66" t="n">
+      <c r="E17" s="68" t="n">
         <f aca="false">IF(Summary!$A$13="","",Summary!$E$13)</f>
         <v>15598</v>
       </c>
-      <c r="F17" s="67" t="str">
+      <c r="F17" s="69" t="str">
         <f aca="false">IF(Summary!$A$13="","",Summary!$F$13)</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="68" t="str">
+      <c r="A18" s="70" t="str">
         <f aca="false">IF(Summary!$A$14="","",Summary!$A$14)</f>
         <v>Deepsea</v>
       </c>
-      <c r="B18" s="69" t="n">
+      <c r="B18" s="71" t="n">
         <f aca="false">IF(Summary!$A$14="","",Summary!$B$14)</f>
         <v>670</v>
       </c>
-      <c r="C18" s="70" t="n">
+      <c r="C18" s="72" t="n">
         <f aca="false">IF(Summary!$A$14="","",Summary!$C$14)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="70" t="n">
+      <c r="D18" s="72" t="n">
         <f aca="false">IF(Summary!$A$14="","",Summary!$D$14)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="71" t="n">
+      <c r="E18" s="73" t="n">
         <f aca="false">IF(Summary!$A$14="","",Summary!$E$14)</f>
         <v>670</v>
       </c>
-      <c r="F18" s="72" t="str">
+      <c r="F18" s="74" t="str">
         <f aca="false">IF(Summary!$A$14="","",Summary!$F$14)</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="63" t="str">
+      <c r="A19" s="65" t="str">
         <f aca="false">IF(Summary!$A$15="","",Summary!$A$15)</f>
         <v>China</v>
       </c>
-      <c r="B19" s="64" t="n">
+      <c r="B19" s="66" t="n">
         <f aca="false">IF(Summary!$A$15="","",Summary!$B$15)</f>
         <v>2960</v>
       </c>
-      <c r="C19" s="65" t="n">
+      <c r="C19" s="67" t="n">
         <f aca="false">IF(Summary!$A$15="","",Summary!$C$15)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="65" t="n">
+      <c r="D19" s="67" t="n">
         <f aca="false">IF(Summary!$A$15="","",Summary!$D$15)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="66" t="n">
+      <c r="E19" s="68" t="n">
         <f aca="false">IF(Summary!$A$15="","",Summary!$E$15)</f>
         <v>2960</v>
       </c>
-      <c r="F19" s="67" t="str">
+      <c r="F19" s="69" t="str">
         <f aca="false">IF(Summary!$A$15="","",Summary!$F$15)</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="68" t="str">
+      <c r="A20" s="70" t="str">
         <f aca="false">IF(Summary!$A$16="","",Summary!$A$16)</f>
         <v>Shrimp Whole 5x3kgs</v>
       </c>
-      <c r="B20" s="69" t="n">
+      <c r="B20" s="71" t="n">
         <f aca="false">IF(Summary!$A$16="","",Summary!$B$16)</f>
         <v>0</v>
       </c>
-      <c r="C20" s="70" t="n">
+      <c r="C20" s="72" t="n">
         <f aca="false">IF(Summary!$A$16="","",Summary!$C$16)</f>
         <v>0</v>
       </c>
-      <c r="D20" s="70" t="n">
+      <c r="D20" s="72" t="n">
         <f aca="false">IF(Summary!$A$16="","",Summary!$D$16)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="71" t="n">
+      <c r="E20" s="73" t="n">
         <f aca="false">IF(Summary!$A$16="","",Summary!$E$16)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="72" t="str">
+      <c r="F20" s="74" t="str">
         <f aca="false">IF(Summary!$A$16="","",Summary!$F$16)</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="63" t="str">
+      <c r="A21" s="65" t="str">
         <f aca="false">IF(Summary!$A$17="","",Summary!$A$17)</f>
         <v/>
       </c>
-      <c r="B21" s="64" t="str">
+      <c r="B21" s="66" t="str">
         <f aca="false">IF(Summary!$A$17="","",Summary!$B$17)</f>
         <v/>
       </c>
-      <c r="C21" s="65" t="str">
+      <c r="C21" s="67" t="str">
         <f aca="false">IF(Summary!$A$17="","",Summary!$C$17)</f>
         <v/>
       </c>
-      <c r="D21" s="65" t="str">
+      <c r="D21" s="67" t="str">
         <f aca="false">IF(Summary!$A$17="","",Summary!$D$17)</f>
         <v/>
       </c>
-      <c r="E21" s="66" t="str">
+      <c r="E21" s="68" t="str">
         <f aca="false">IF(Summary!$A$17="","",Summary!$E$17)</f>
         <v/>
       </c>
-      <c r="F21" s="67" t="str">
+      <c r="F21" s="69" t="str">
         <f aca="false">IF(Summary!$A$17="","",Summary!$F$17)</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="68" t="str">
+      <c r="A22" s="70" t="str">
         <f aca="false">IF(Summary!$A$18="","",Summary!$A$18)</f>
         <v/>
       </c>
-      <c r="B22" s="69" t="str">
+      <c r="B22" s="71" t="str">
         <f aca="false">IF(Summary!$A$18="","",Summary!$B$18)</f>
         <v/>
       </c>
-      <c r="C22" s="70" t="str">
+      <c r="C22" s="72" t="str">
         <f aca="false">IF(Summary!$A$18="","",Summary!$C$18)</f>
         <v/>
       </c>
-      <c r="D22" s="70" t="str">
+      <c r="D22" s="72" t="str">
         <f aca="false">IF(Summary!$A$18="","",Summary!$D$18)</f>
         <v/>
       </c>
-      <c r="E22" s="71" t="str">
+      <c r="E22" s="73" t="str">
         <f aca="false">IF(Summary!$A$18="","",Summary!$E$18)</f>
         <v/>
       </c>
-      <c r="F22" s="72" t="str">
+      <c r="F22" s="74" t="str">
         <f aca="false">IF(Summary!$A$18="","",Summary!$F$18)</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="63" t="str">
+      <c r="A23" s="65" t="str">
         <f aca="false">IF(Summary!$A$19="","",Summary!$A$19)</f>
         <v/>
       </c>
-      <c r="B23" s="64" t="str">
+      <c r="B23" s="66" t="str">
         <f aca="false">IF(Summary!$A$19="","",Summary!$B$19)</f>
         <v/>
       </c>
-      <c r="C23" s="65" t="str">
+      <c r="C23" s="67" t="str">
         <f aca="false">IF(Summary!$A$19="","",Summary!$C$19)</f>
         <v/>
       </c>
-      <c r="D23" s="65" t="str">
+      <c r="D23" s="67" t="str">
         <f aca="false">IF(Summary!$A$19="","",Summary!$D$19)</f>
         <v/>
       </c>
-      <c r="E23" s="66" t="str">
+      <c r="E23" s="68" t="str">
         <f aca="false">IF(Summary!$A$19="","",Summary!$E$19)</f>
         <v/>
       </c>
-      <c r="F23" s="67" t="str">
+      <c r="F23" s="69" t="str">
         <f aca="false">IF(Summary!$A$19="","",Summary!$F$19)</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="73" t="str">
+      <c r="A24" s="75" t="str">
         <f aca="false">Summary!$A$20</f>
         <v>GRAND TOTAL</v>
       </c>
-      <c r="B24" s="74" t="n">
+      <c r="B24" s="76" t="n">
         <f aca="false">Summary!$B$20</f>
         <v>102870</v>
       </c>
-      <c r="C24" s="75" t="n">
+      <c r="C24" s="77" t="n">
         <f aca="false">Summary!$C$20</f>
         <v>4880</v>
       </c>
-      <c r="D24" s="75" t="n">
+      <c r="D24" s="77" t="n">
         <f aca="false">Summary!$D$20</f>
         <v>0</v>
       </c>
-      <c r="E24" s="74" t="n">
+      <c r="E24" s="76" t="n">
         <f aca="false">Summary!$E$20</f>
         <v>107750</v>
       </c>
-      <c r="F24" s="76" t="str">
+      <c r="F24" s="78" t="str">
         <f aca="false">Summary!$F$20</f>
         <v/>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="60" t="s">
-        <v>138</v>
-      </c>
-      <c r="B26" s="60"/>
-      <c r="C26" s="60"/>
-      <c r="D26" s="60"/>
-      <c r="E26" s="60"/>
-      <c r="F26" s="60"/>
+      <c r="A26" s="62" t="s">
+        <v>147</v>
+      </c>
+      <c r="B26" s="62"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="62"/>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="61" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="61" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" s="62" t="s">
-        <v>139</v>
-      </c>
-      <c r="D27" s="62" t="s">
-        <v>140</v>
-      </c>
-      <c r="E27" s="62" t="s">
-        <v>52</v>
-      </c>
-      <c r="F27" s="62"/>
+      <c r="A27" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="64" t="s">
+        <v>148</v>
+      </c>
+      <c r="D27" s="64" t="s">
+        <v>149</v>
+      </c>
+      <c r="E27" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="F27" s="64"/>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="77" t="str">
+      <c r="A28" s="79" t="str">
         <f aca="false">IF($H28="","",INDEX(Stock!$A$8:$A$69,$H28))</f>
         <v>Blue Dolphin</v>
       </c>
-      <c r="B28" s="77" t="str">
+      <c r="B28" s="79" t="str">
         <f aca="false">IF($H28="","",INDEX(Stock!$B$8:$B$69,$H28))</f>
         <v>PD PVN 100/200</v>
       </c>
-      <c r="C28" s="78" t="n">
+      <c r="C28" s="80" t="n">
         <f aca="false">IF($H28="","",INDEX(Stock!$D$8:$D$69,$H28))</f>
         <v>1068</v>
       </c>
-      <c r="D28" s="78" t="n">
+      <c r="D28" s="80" t="n">
         <f aca="false">IF($H28="","",INDEX(Stock!$E$8:$E$69,$H28))</f>
         <v>0</v>
       </c>
-      <c r="E28" s="79" t="n">
+      <c r="E28" s="81" t="n">
         <f aca="false">IF($H28="","",INDEX(Stock!$H$8:$H$69,$H28))</f>
         <v>12527</v>
       </c>
-      <c r="H28" s="80" t="n">
+      <c r="H28" s="82" t="n">
         <f aca="false">IFERROR(MATCH(1,Stock!$N$8:$N$69,0),"")</f>
         <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="77" t="str">
+      <c r="A29" s="79" t="str">
         <f aca="false">IF($H29="","",INDEX(Stock!$A$8:$A$69,$H29))</f>
         <v>Blue Dolphin</v>
       </c>
-      <c r="B29" s="77" t="str">
+      <c r="B29" s="79" t="str">
         <f aca="false">IF($H29="","",INDEX(Stock!$B$8:$B$69,$H29))</f>
         <v>PD KKD 100/200</v>
       </c>
-      <c r="C29" s="78" t="n">
+      <c r="C29" s="80" t="n">
         <f aca="false">IF($H29="","",INDEX(Stock!$D$8:$D$69,$H29))</f>
         <v>65</v>
       </c>
-      <c r="D29" s="78" t="n">
+      <c r="D29" s="80" t="n">
         <f aca="false">IF($H29="","",INDEX(Stock!$E$8:$E$69,$H29))</f>
         <v>0</v>
       </c>
-      <c r="E29" s="79" t="n">
+      <c r="E29" s="81" t="n">
         <f aca="false">IF($H29="","",INDEX(Stock!$H$8:$H$69,$H29))</f>
         <v>582</v>
       </c>
-      <c r="H29" s="80" t="n">
+      <c r="H29" s="82" t="n">
         <f aca="false">IFERROR(MATCH(2,Stock!$N$8:$N$69,0),"")</f>
         <v>2</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="77" t="str">
+      <c r="A30" s="79" t="str">
         <f aca="false">IF($H30="","",INDEX(Stock!$A$8:$A$69,$H30))</f>
         <v>Blue Dolphin</v>
       </c>
-      <c r="B30" s="77" t="str">
+      <c r="B30" s="79" t="str">
         <f aca="false">IF($H30="","",INDEX(Stock!$B$8:$B$69,$H30))</f>
         <v>PUD PVN 200/300</v>
       </c>
-      <c r="C30" s="78" t="n">
+      <c r="C30" s="80" t="n">
         <f aca="false">IF($H30="","",INDEX(Stock!$D$8:$D$69,$H30))</f>
         <v>267</v>
       </c>
-      <c r="D30" s="78" t="n">
+      <c r="D30" s="80" t="n">
         <f aca="false">IF($H30="","",INDEX(Stock!$E$8:$E$69,$H30))</f>
         <v>0</v>
       </c>
-      <c r="E30" s="79" t="n">
+      <c r="E30" s="81" t="n">
         <f aca="false">IF($H30="","",INDEX(Stock!$H$8:$H$69,$H30))</f>
         <v>2529</v>
       </c>
-      <c r="H30" s="80" t="n">
+      <c r="H30" s="82" t="n">
         <f aca="false">IFERROR(MATCH(3,Stock!$N$8:$N$69,0),"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="77" t="str">
+      <c r="A31" s="79" t="str">
         <f aca="false">IF($H31="","",INDEX(Stock!$A$8:$A$69,$H31))</f>
         <v>Primus Japan</v>
       </c>
-      <c r="B31" s="77" t="str">
+      <c r="B31" s="79" t="str">
         <f aca="false">IF($H31="","",INDEX(Stock!$B$8:$B$69,$H31))</f>
         <v>PUD KZN 40/60</v>
       </c>
-      <c r="C31" s="78" t="n">
+      <c r="C31" s="80" t="n">
         <f aca="false">IF($H31="","",INDEX(Stock!$D$8:$D$69,$H31))</f>
         <v>29</v>
       </c>
-      <c r="D31" s="78" t="n">
+      <c r="D31" s="80" t="n">
         <f aca="false">IF($H31="","",INDEX(Stock!$E$8:$E$69,$H31))</f>
         <v>0</v>
       </c>
-      <c r="E31" s="79" t="n">
+      <c r="E31" s="81" t="n">
         <f aca="false">IF($H31="","",INDEX(Stock!$H$8:$H$69,$H31))</f>
         <v>93</v>
       </c>
-      <c r="H31" s="80" t="n">
+      <c r="H31" s="82" t="n">
         <f aca="false">IFERROR(MATCH(4,Stock!$N$8:$N$69,0),"")</f>
         <v>8</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="77" t="str">
+      <c r="A32" s="79" t="str">
         <f aca="false">IF($H32="","",INDEX(Stock!$A$8:$A$69,$H32))</f>
         <v>Primus Japan</v>
       </c>
-      <c r="B32" s="77" t="str">
+      <c r="B32" s="79" t="str">
         <f aca="false">IF($H32="","",INDEX(Stock!$B$8:$B$69,$H32))</f>
         <v>PUD KZN 60/80</v>
       </c>
-      <c r="C32" s="78" t="n">
+      <c r="C32" s="80" t="n">
         <f aca="false">IF($H32="","",INDEX(Stock!$D$8:$D$69,$H32))</f>
         <v>39</v>
       </c>
-      <c r="D32" s="78" t="n">
+      <c r="D32" s="80" t="n">
         <f aca="false">IF($H32="","",INDEX(Stock!$E$8:$E$69,$H32))</f>
         <v>0</v>
       </c>
-      <c r="E32" s="79" t="n">
+      <c r="E32" s="81" t="n">
         <f aca="false">IF($H32="","",INDEX(Stock!$H$8:$H$69,$H32))</f>
         <v>230</v>
       </c>
-      <c r="H32" s="80" t="n">
+      <c r="H32" s="82" t="n">
         <f aca="false">IFERROR(MATCH(5,Stock!$N$8:$N$69,0),"")</f>
         <v>9</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="77" t="str">
+      <c r="A33" s="79" t="str">
         <f aca="false">IF($H33="","",INDEX(Stock!$A$8:$A$69,$H33))</f>
         <v>Primus Japan</v>
       </c>
-      <c r="B33" s="77" t="str">
+      <c r="B33" s="79" t="str">
         <f aca="false">IF($H33="","",INDEX(Stock!$B$8:$B$69,$H33))</f>
         <v>PUD KZN 80/120</v>
       </c>
-      <c r="C33" s="78" t="n">
+      <c r="C33" s="80" t="n">
         <f aca="false">IF($H33="","",INDEX(Stock!$D$8:$D$69,$H33))</f>
         <v>50</v>
       </c>
-      <c r="D33" s="78" t="n">
+      <c r="D33" s="80" t="n">
         <f aca="false">IF($H33="","",INDEX(Stock!$E$8:$E$69,$H33))</f>
         <v>0</v>
       </c>
-      <c r="E33" s="79" t="n">
+      <c r="E33" s="81" t="n">
         <f aca="false">IF($H33="","",INDEX(Stock!$H$8:$H$69,$H33))</f>
         <v>516</v>
       </c>
-      <c r="H33" s="80" t="n">
+      <c r="H33" s="82" t="n">
         <f aca="false">IFERROR(MATCH(6,Stock!$N$8:$N$69,0),"")</f>
         <v>11</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="77" t="str">
+      <c r="A34" s="79" t="str">
         <f aca="false">IF($H34="","",INDEX(Stock!$A$8:$A$69,$H34))</f>
         <v>Primus Japan</v>
       </c>
-      <c r="B34" s="77" t="str">
+      <c r="B34" s="79" t="str">
         <f aca="false">IF($H34="","",INDEX(Stock!$B$8:$B$69,$H34))</f>
         <v>PUD NRN 80/120</v>
       </c>
-      <c r="C34" s="78" t="n">
+      <c r="C34" s="80" t="n">
         <f aca="false">IF($H34="","",INDEX(Stock!$D$8:$D$69,$H34))</f>
         <v>3</v>
       </c>
-      <c r="D34" s="78" t="n">
+      <c r="D34" s="80" t="n">
         <f aca="false">IF($H34="","",INDEX(Stock!$E$8:$E$69,$H34))</f>
         <v>0</v>
       </c>
-      <c r="E34" s="79" t="n">
+      <c r="E34" s="81" t="n">
         <f aca="false">IF($H34="","",INDEX(Stock!$H$8:$H$69,$H34))</f>
         <v>72</v>
       </c>
-      <c r="H34" s="80" t="n">
+      <c r="H34" s="82" t="n">
         <f aca="false">IFERROR(MATCH(7,Stock!$N$8:$N$69,0),"")</f>
         <v>12</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="77" t="str">
+      <c r="A35" s="79" t="str">
         <f aca="false">IF($H35="","",INDEX(Stock!$A$8:$A$69,$H35))</f>
         <v>Primus Japan</v>
       </c>
-      <c r="B35" s="77" t="str">
+      <c r="B35" s="79" t="str">
         <f aca="false">IF($H35="","",INDEX(Stock!$B$8:$B$69,$H35))</f>
         <v>PUD KZN 100/200</v>
       </c>
-      <c r="C35" s="78" t="n">
+      <c r="C35" s="80" t="n">
         <f aca="false">IF($H35="","",INDEX(Stock!$D$8:$D$69,$H35))</f>
         <v>50</v>
       </c>
-      <c r="D35" s="78" t="n">
+      <c r="D35" s="80" t="n">
         <f aca="false">IF($H35="","",INDEX(Stock!$E$8:$E$69,$H35))</f>
         <v>0</v>
       </c>
-      <c r="E35" s="79" t="n">
+      <c r="E35" s="81" t="n">
         <f aca="false">IF($H35="","",INDEX(Stock!$H$8:$H$69,$H35))</f>
         <v>4259</v>
       </c>
-      <c r="H35" s="80" t="n">
+      <c r="H35" s="82" t="n">
         <f aca="false">IFERROR(MATCH(8,Stock!$N$8:$N$69,0),"")</f>
         <v>15</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="77" t="str">
+      <c r="A36" s="79" t="str">
         <f aca="false">IF($H36="","",INDEX(Stock!$A$8:$A$69,$H36))</f>
         <v>Primus Japan</v>
       </c>
-      <c r="B36" s="77" t="str">
+      <c r="B36" s="79" t="str">
         <f aca="false">IF($H36="","",INDEX(Stock!$B$8:$B$69,$H36))</f>
         <v>PUD KZN 200/300</v>
       </c>
-      <c r="C36" s="78" t="n">
+      <c r="C36" s="80" t="n">
         <f aca="false">IF($H36="","",INDEX(Stock!$D$8:$D$69,$H36))</f>
         <v>33</v>
       </c>
-      <c r="D36" s="78" t="n">
+      <c r="D36" s="80" t="n">
         <f aca="false">IF($H36="","",INDEX(Stock!$E$8:$E$69,$H36))</f>
         <v>0</v>
       </c>
-      <c r="E36" s="79" t="n">
+      <c r="E36" s="81" t="n">
         <f aca="false">IF($H36="","",INDEX(Stock!$H$8:$H$69,$H36))</f>
         <v>1113</v>
       </c>
-      <c r="H36" s="80" t="n">
+      <c r="H36" s="82" t="n">
         <f aca="false">IFERROR(MATCH(9,Stock!$N$8:$N$69,0),"")</f>
         <v>18</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="77" t="str">
+      <c r="A37" s="79" t="str">
         <f aca="false">IF($H37="","",INDEX(Stock!$A$8:$A$69,$H37))</f>
         <v>Primus Japan</v>
       </c>
-      <c r="B37" s="77" t="str">
+      <c r="B37" s="79" t="str">
         <f aca="false">IF($H37="","",INDEX(Stock!$B$8:$B$69,$H37))</f>
         <v>PUD PVN 300/500</v>
       </c>
-      <c r="C37" s="78" t="n">
+      <c r="C37" s="80" t="n">
         <f aca="false">IF($H37="","",INDEX(Stock!$D$8:$D$69,$H37))</f>
         <v>156</v>
       </c>
-      <c r="D37" s="78" t="n">
+      <c r="D37" s="80" t="n">
         <f aca="false">IF($H37="","",INDEX(Stock!$E$8:$E$69,$H37))</f>
         <v>0</v>
       </c>
-      <c r="E37" s="79" t="n">
+      <c r="E37" s="81" t="n">
         <f aca="false">IF($H37="","",INDEX(Stock!$H$8:$H$69,$H37))</f>
         <v>577</v>
       </c>
-      <c r="H37" s="80" t="n">
+      <c r="H37" s="82" t="n">
         <f aca="false">IFERROR(MATCH(10,Stock!$N$8:$N$69,0),"")</f>
         <v>19</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="77" t="str">
+      <c r="A38" s="79" t="str">
         <f aca="false">IF($H38="","",INDEX(Stock!$A$8:$A$69,$H38))</f>
         <v>Primus Japan</v>
       </c>
-      <c r="B38" s="77" t="str">
+      <c r="B38" s="79" t="str">
         <f aca="false">IF($H38="","",INDEX(Stock!$B$8:$B$69,$H38))</f>
         <v>PUD KKD 300/500</v>
       </c>
-      <c r="C38" s="78" t="n">
+      <c r="C38" s="80" t="n">
         <f aca="false">IF($H38="","",INDEX(Stock!$D$8:$D$69,$H38))</f>
         <v>596</v>
       </c>
-      <c r="D38" s="78" t="n">
+      <c r="D38" s="80" t="n">
         <f aca="false">IF($H38="","",INDEX(Stock!$E$8:$E$69,$H38))</f>
         <v>0</v>
       </c>
-      <c r="E38" s="79" t="n">
+      <c r="E38" s="81" t="n">
         <f aca="false">IF($H38="","",INDEX(Stock!$H$8:$H$69,$H38))</f>
         <v>1176</v>
       </c>
-      <c r="H38" s="80" t="n">
+      <c r="H38" s="82" t="n">
         <f aca="false">IFERROR(MATCH(11,Stock!$N$8:$N$69,0),"")</f>
         <v>20</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="77" t="str">
+      <c r="A39" s="79" t="str">
         <f aca="false">IF($H39="","",INDEX(Stock!$A$8:$A$69,$H39))</f>
         <v>Primus EU</v>
       </c>
-      <c r="B39" s="77" t="str">
+      <c r="B39" s="79" t="str">
         <f aca="false">IF($H39="","",INDEX(Stock!$B$8:$B$69,$H39))</f>
         <v>BKN</v>
       </c>
-      <c r="C39" s="78" t="n">
+      <c r="C39" s="80" t="n">
         <f aca="false">IF($H39="","",INDEX(Stock!$D$8:$D$69,$H39))</f>
         <v>52</v>
       </c>
-      <c r="D39" s="78" t="n">
+      <c r="D39" s="80" t="n">
         <f aca="false">IF($H39="","",INDEX(Stock!$E$8:$E$69,$H39))</f>
         <v>0</v>
       </c>
-      <c r="E39" s="79" t="n">
+      <c r="E39" s="81" t="n">
         <f aca="false">IF($H39="","",INDEX(Stock!$H$8:$H$69,$H39))</f>
         <v>15182</v>
       </c>
-      <c r="H39" s="80" t="n">
+      <c r="H39" s="82" t="n">
         <f aca="false">IFERROR(MATCH(12,Stock!$N$8:$N$69,0),"")</f>
         <v>28</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="77" t="str">
+      <c r="A40" s="79" t="str">
         <f aca="false">IF($H40="","",INDEX(Stock!$A$8:$A$69,$H40))</f>
         <v>THT Brand</v>
       </c>
-      <c r="B40" s="77" t="str">
+      <c r="B40" s="79" t="str">
         <f aca="false">IF($H40="","",INDEX(Stock!$B$8:$B$69,$H40))</f>
         <v>PUD PVN 80/120</v>
       </c>
-      <c r="C40" s="78" t="n">
+      <c r="C40" s="80" t="n">
         <f aca="false">IF($H40="","",INDEX(Stock!$D$8:$D$69,$H40))</f>
         <v>1872</v>
       </c>
-      <c r="D40" s="78" t="n">
+      <c r="D40" s="80" t="n">
         <f aca="false">IF($H40="","",INDEX(Stock!$E$8:$E$69,$H40))</f>
         <v>0</v>
       </c>
-      <c r="E40" s="79" t="n">
+      <c r="E40" s="81" t="n">
         <f aca="false">IF($H40="","",INDEX(Stock!$H$8:$H$69,$H40))</f>
         <v>3261</v>
       </c>
-      <c r="H40" s="80" t="n">
+      <c r="H40" s="82" t="n">
         <f aca="false">IFERROR(MATCH(13,Stock!$N$8:$N$69,0),"")</f>
         <v>35</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="77" t="str">
+      <c r="A41" s="79" t="str">
         <f aca="false">IF($H41="","",INDEX(Stock!$A$8:$A$69,$H41))</f>
         <v>THT Brand</v>
       </c>
-      <c r="B41" s="77" t="str">
+      <c r="B41" s="79" t="str">
         <f aca="false">IF($H41="","",INDEX(Stock!$B$8:$B$69,$H41))</f>
         <v>PUD PVN 100/200</v>
       </c>
-      <c r="C41" s="78" t="n">
+      <c r="C41" s="80" t="n">
         <f aca="false">IF($H41="","",INDEX(Stock!$D$8:$D$69,$H41))</f>
         <v>600</v>
       </c>
-      <c r="D41" s="78" t="n">
+      <c r="D41" s="80" t="n">
         <f aca="false">IF($H41="","",INDEX(Stock!$E$8:$E$69,$H41))</f>
         <v>0</v>
       </c>
-      <c r="E41" s="79" t="n">
+      <c r="E41" s="81" t="n">
         <f aca="false">IF($H41="","",INDEX(Stock!$H$8:$H$69,$H41))</f>
         <v>7655</v>
       </c>
-      <c r="H41" s="80" t="n">
+      <c r="H41" s="82" t="n">
         <f aca="false">IFERROR(MATCH(14,Stock!$N$8:$N$69,0),"")</f>
         <v>36</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="77" t="str">
+      <c r="A42" s="79" t="str">
         <f aca="false">IF($H42="","",INDEX(Stock!$A$8:$A$69,$H42))</f>
         <v/>
       </c>
-      <c r="B42" s="77" t="str">
+      <c r="B42" s="79" t="str">
         <f aca="false">IF($H42="","",INDEX(Stock!$B$8:$B$69,$H42))</f>
         <v/>
       </c>
-      <c r="C42" s="78" t="str">
+      <c r="C42" s="80" t="str">
         <f aca="false">IF($H42="","",INDEX(Stock!$D$8:$D$69,$H42))</f>
         <v/>
       </c>
-      <c r="D42" s="78" t="str">
+      <c r="D42" s="80" t="str">
         <f aca="false">IF($H42="","",INDEX(Stock!$E$8:$E$69,$H42))</f>
         <v/>
       </c>
-      <c r="E42" s="79" t="str">
+      <c r="E42" s="81" t="str">
         <f aca="false">IF($H42="","",INDEX(Stock!$H$8:$H$69,$H42))</f>
         <v/>
       </c>
-      <c r="H42" s="80" t="str">
+      <c r="H42" s="82" t="str">
         <f aca="false">IFERROR(MATCH(15,Stock!$N$8:$N$69,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="77" t="str">
+      <c r="A43" s="79" t="str">
         <f aca="false">IF($H43="","",INDEX(Stock!$A$8:$A$69,$H43))</f>
         <v/>
       </c>
-      <c r="B43" s="77" t="str">
+      <c r="B43" s="79" t="str">
         <f aca="false">IF($H43="","",INDEX(Stock!$B$8:$B$69,$H43))</f>
         <v/>
       </c>
-      <c r="C43" s="78" t="str">
+      <c r="C43" s="80" t="str">
         <f aca="false">IF($H43="","",INDEX(Stock!$D$8:$D$69,$H43))</f>
         <v/>
       </c>
-      <c r="D43" s="78" t="str">
+      <c r="D43" s="80" t="str">
         <f aca="false">IF($H43="","",INDEX(Stock!$E$8:$E$69,$H43))</f>
         <v/>
       </c>
-      <c r="E43" s="79" t="str">
+      <c r="E43" s="81" t="str">
         <f aca="false">IF($H43="","",INDEX(Stock!$H$8:$H$69,$H43))</f>
         <v/>
       </c>
-      <c r="H43" s="80" t="str">
+      <c r="H43" s="82" t="str">
         <f aca="false">IFERROR(MATCH(16,Stock!$N$8:$N$69,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="77" t="str">
+      <c r="A44" s="79" t="str">
         <f aca="false">IF($H44="","",INDEX(Stock!$A$8:$A$69,$H44))</f>
         <v/>
       </c>
-      <c r="B44" s="77" t="str">
+      <c r="B44" s="79" t="str">
         <f aca="false">IF($H44="","",INDEX(Stock!$B$8:$B$69,$H44))</f>
         <v/>
       </c>
-      <c r="C44" s="78" t="str">
+      <c r="C44" s="80" t="str">
         <f aca="false">IF($H44="","",INDEX(Stock!$D$8:$D$69,$H44))</f>
         <v/>
       </c>
-      <c r="D44" s="78" t="str">
+      <c r="D44" s="80" t="str">
         <f aca="false">IF($H44="","",INDEX(Stock!$E$8:$E$69,$H44))</f>
         <v/>
       </c>
-      <c r="E44" s="79" t="str">
+      <c r="E44" s="81" t="str">
         <f aca="false">IF($H44="","",INDEX(Stock!$H$8:$H$69,$H44))</f>
         <v/>
       </c>
-      <c r="H44" s="80" t="str">
+      <c r="H44" s="82" t="str">
         <f aca="false">IFERROR(MATCH(17,Stock!$N$8:$N$69,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="77" t="str">
+      <c r="A45" s="79" t="str">
         <f aca="false">IF($H45="","",INDEX(Stock!$A$8:$A$69,$H45))</f>
         <v/>
       </c>
-      <c r="B45" s="77" t="str">
+      <c r="B45" s="79" t="str">
         <f aca="false">IF($H45="","",INDEX(Stock!$B$8:$B$69,$H45))</f>
         <v/>
       </c>
-      <c r="C45" s="78" t="str">
+      <c r="C45" s="80" t="str">
         <f aca="false">IF($H45="","",INDEX(Stock!$D$8:$D$69,$H45))</f>
         <v/>
       </c>
-      <c r="D45" s="78" t="str">
+      <c r="D45" s="80" t="str">
         <f aca="false">IF($H45="","",INDEX(Stock!$E$8:$E$69,$H45))</f>
         <v/>
       </c>
-      <c r="E45" s="79" t="str">
+      <c r="E45" s="81" t="str">
         <f aca="false">IF($H45="","",INDEX(Stock!$H$8:$H$69,$H45))</f>
         <v/>
       </c>
-      <c r="H45" s="80" t="str">
+      <c r="H45" s="82" t="str">
         <f aca="false">IFERROR(MATCH(18,Stock!$N$8:$N$69,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="77" t="str">
+      <c r="A46" s="79" t="str">
         <f aca="false">IF($H46="","",INDEX(Stock!$A$8:$A$69,$H46))</f>
         <v/>
       </c>
-      <c r="B46" s="77" t="str">
+      <c r="B46" s="79" t="str">
         <f aca="false">IF($H46="","",INDEX(Stock!$B$8:$B$69,$H46))</f>
         <v/>
       </c>
-      <c r="C46" s="78" t="str">
+      <c r="C46" s="80" t="str">
         <f aca="false">IF($H46="","",INDEX(Stock!$D$8:$D$69,$H46))</f>
         <v/>
       </c>
-      <c r="D46" s="78" t="str">
+      <c r="D46" s="80" t="str">
         <f aca="false">IF($H46="","",INDEX(Stock!$E$8:$E$69,$H46))</f>
         <v/>
       </c>
-      <c r="E46" s="79" t="str">
+      <c r="E46" s="81" t="str">
         <f aca="false">IF($H46="","",INDEX(Stock!$H$8:$H$69,$H46))</f>
         <v/>
       </c>
-      <c r="H46" s="80" t="str">
+      <c r="H46" s="82" t="str">
         <f aca="false">IFERROR(MATCH(19,Stock!$N$8:$N$69,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="77" t="str">
+      <c r="A47" s="79" t="str">
         <f aca="false">IF($H47="","",INDEX(Stock!$A$8:$A$69,$H47))</f>
         <v/>
       </c>
-      <c r="B47" s="77" t="str">
+      <c r="B47" s="79" t="str">
         <f aca="false">IF($H47="","",INDEX(Stock!$B$8:$B$69,$H47))</f>
         <v/>
       </c>
-      <c r="C47" s="78" t="str">
+      <c r="C47" s="80" t="str">
         <f aca="false">IF($H47="","",INDEX(Stock!$D$8:$D$69,$H47))</f>
         <v/>
       </c>
-      <c r="D47" s="78" t="str">
+      <c r="D47" s="80" t="str">
         <f aca="false">IF($H47="","",INDEX(Stock!$E$8:$E$69,$H47))</f>
         <v/>
       </c>
-      <c r="E47" s="79" t="str">
+      <c r="E47" s="81" t="str">
         <f aca="false">IF($H47="","",INDEX(Stock!$H$8:$H$69,$H47))</f>
         <v/>
       </c>
-      <c r="H47" s="80" t="str">
+      <c r="H47" s="82" t="str">
         <f aca="false">IFERROR(MATCH(20,Stock!$N$8:$N$69,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="81" t="s">
-        <v>141</v>
-      </c>
-      <c r="B48" s="82" t="str">
+      <c r="A48" s="83" t="s">
+        <v>150</v>
+      </c>
+      <c r="B48" s="84" t="str">
         <f aca="false">COUNTIF(Stock!$M$8:$M$69,1)&amp;" product(s)"</f>
         <v>14 product(s)</v>
       </c>
-      <c r="C48" s="83" t="n">
+      <c r="C48" s="85" t="n">
         <f aca="false">SUM(C28:C47)</f>
         <v>4880</v>
       </c>
-      <c r="D48" s="83" t="n">
+      <c r="D48" s="85" t="n">
         <f aca="false">SUM(D28:D47)</f>
         <v>0</v>
       </c>
-      <c r="E48" s="81"/>
-      <c r="F48" s="81"/>
+      <c r="E48" s="83"/>
+      <c r="F48" s="83"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="84" t="str">
+      <c r="A49" s="86" t="str">
         <f aca="false">IF(COUNTIF(Stock!$M$8:$M$69,1)&gt;20,"Note: "&amp;(COUNTIF(Stock!$M$8:$M$69,1)-20)&amp;" further product(s) moved today — see the Stock sheet for the full list.","")</f>
         <v/>
       </c>
-      <c r="B49" s="84"/>
-      <c r="C49" s="84"/>
-      <c r="D49" s="84"/>
-      <c r="E49" s="84"/>
-      <c r="F49" s="84"/>
+      <c r="B49" s="86"/>
+      <c r="C49" s="86"/>
+      <c r="D49" s="86"/>
+      <c r="E49" s="86"/>
+      <c r="F49" s="86"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="85" t="s">
-        <v>142</v>
-      </c>
-      <c r="B51" s="85"/>
-      <c r="C51" s="85"/>
-      <c r="D51" s="85"/>
-      <c r="E51" s="85"/>
-      <c r="F51" s="85"/>
+      <c r="A51" s="87" t="s">
+        <v>151</v>
+      </c>
+      <c r="B51" s="87"/>
+      <c r="C51" s="87"/>
+      <c r="D51" s="87"/>
+      <c r="E51" s="87"/>
+      <c r="F51" s="87"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true" password="df10" objects="true" scenarios="true" autoFilter="false"/>
